--- a/data/historico/historico_baixas.xlsx
+++ b/data/historico/historico_baixas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K256"/>
+  <dimension ref="A1:K262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -579,13 +579,13 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -732,13 +732,13 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J6" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="K6" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
@@ -983,13 +983,13 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
@@ -1025,18 +1025,22 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Denis Reis</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Cristiana Grizostomo</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1067,27 +1071,23 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cristina Leite</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Ricardo Fischer</t>
-        </is>
-      </c>
+          <t>Denis Reis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K13" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14">
@@ -1118,17 +1118,21 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Victoria Virgens</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Priscila Volpe</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1165,23 +1169,27 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cristiane Simões</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Cristina Leite</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Ricardo Fischer</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K15" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
@@ -1212,12 +1220,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Victoria Virgens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -1225,10 +1233,10 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1264,7 +1272,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Cristiane Simões</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
@@ -1272,10 +1280,10 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1301,28 +1309,28 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>GOIAS</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Caroline Alves</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="K18" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19">
@@ -1348,32 +1356,28 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>GOIAS</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>RJ - CTB</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crislaine Maia</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Walace Gonçalves|Maicon Costa</t>
-        </is>
-      </c>
+          <t>Sergio Fernandes</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1399,32 +1403,28 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>GOIAS</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>RJ - CTB</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Gabriela Lopes</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Walace Gonçalves|Maicon Costa</t>
-        </is>
-      </c>
+          <t>Vander Silva</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1455,27 +1455,23 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>RJ - CTB</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Jeniffer Cristina</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Walace Gonçalves|Maicon Costa</t>
-        </is>
-      </c>
+          <t>Caroline Alves</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1511,7 +1507,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Jessica Roque</t>
+          <t>Crislaine Maia</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1520,13 +1516,13 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J22" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K22" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23">
@@ -1562,7 +1558,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Kellem Freitas</t>
+          <t>Gabriela Lopes</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1571,13 +1567,13 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J23" t="n">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="K23" t="n">
-        <v>7</v>
+        <v>40</v>
       </c>
     </row>
     <row r="24">
@@ -1613,7 +1609,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leidiane Paulino</t>
+          <t>Jeniffer Cristina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1625,10 +1621,10 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1664,7 +1660,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leticia Barbosa</t>
+          <t>Jessica Roque</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1676,10 +1672,10 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="K25" t="n">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
@@ -1715,7 +1711,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nicoly Rodrigues</t>
+          <t>Kellem Freitas</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1724,13 +1720,13 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J26" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K26" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27">
@@ -1766,7 +1762,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rafaella Silva</t>
+          <t>Leidiane Paulino</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1775,13 +1771,13 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K27" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28">
@@ -1817,7 +1813,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rangel Rocha</t>
+          <t>Leticia Barbosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1829,10 +1825,10 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="K28" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29">
@@ -1868,7 +1864,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Veronica Barbosa</t>
+          <t>Nicoly Rodrigues</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1877,13 +1873,13 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J29" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="K29" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30">
@@ -1919,7 +1915,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Vitoria Silva</t>
+          <t>Rafaella Silva</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1931,10 +1927,10 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1965,19 +1961,27 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>RJ - DP</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+          <t>RJ - CTB</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Rangel Rocha</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Walace Gonçalves|Maicon Costa</t>
+        </is>
+      </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32">
@@ -2008,27 +2012,27 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>RJ - DP</t>
+          <t>RJ - CTB</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Barbara Mello</t>
+          <t>Simone Soares</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Karina Oliveira|Liliane Costa</t>
+          <t>Walace Gonçalves|Maicon Costa</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J32" t="n">
-        <v>70</v>
+        <v>5</v>
       </c>
       <c r="K32" t="n">
-        <v>70</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33">
@@ -2059,27 +2063,27 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>RJ - DP</t>
+          <t>RJ - CTB</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Debora Nunes</t>
+          <t>Suzana Silva</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Karina Oliveira|Liliane Costa</t>
+          <t>Walace Gonçalves|Maicon Costa</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J33" t="n">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="K33" t="n">
-        <v>64</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2110,27 +2114,27 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>RJ - DP</t>
+          <t>RJ - CTB</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Graziele Almeida</t>
+          <t>Veronica Barbosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Karina Oliveira|Liliane Costa</t>
+          <t>Walace Gonçalves|Maicon Costa</t>
         </is>
       </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>63</v>
+        <v>3</v>
       </c>
       <c r="K34" t="n">
-        <v>63</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -2161,27 +2165,27 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>RJ - DP</t>
+          <t>RJ - CTB</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Janiele Ferreira</t>
+          <t>Vitor Monteiro</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Karina Oliveira|Liliane Costa</t>
+          <t>Walace Gonçalves|Maicon Costa</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="K35" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36">
@@ -2212,27 +2216,27 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>RJ - DP</t>
+          <t>RJ - CTB</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Jefferson Barros</t>
+          <t>Vitoria Silva</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Karina Oliveira|Liliane Costa</t>
+          <t>Walace Gonçalves|Maicon Costa</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J36" t="n">
-        <v>71</v>
+        <v>8</v>
       </c>
       <c r="K36" t="n">
-        <v>71</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37">
@@ -2266,24 +2270,16 @@
           <t>RJ - DP</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Karina Oliveira</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Karina Oliveira|Liliane Costa</t>
-        </is>
-      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J37" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="K37" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
@@ -2319,7 +2315,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Leonardo Assunção</t>
+          <t>Barbara Mello</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2331,10 +2327,10 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="K38" t="n">
-        <v>1</v>
+        <v>70</v>
       </c>
     </row>
     <row r="39">
@@ -2370,7 +2366,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Liliane Costa</t>
+          <t>Debora Nunes</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2379,13 +2375,13 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J39" t="n">
-        <v>15</v>
+        <v>68</v>
       </c>
       <c r="K39" t="n">
-        <v>15</v>
+        <v>68</v>
       </c>
     </row>
     <row r="40">
@@ -2421,7 +2417,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Luciene Pimenta</t>
+          <t>Graziele Almeida</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2433,10 +2429,10 @@
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="K40" t="n">
-        <v>2</v>
+        <v>63</v>
       </c>
     </row>
     <row r="41">
@@ -2472,7 +2468,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lucirene Souza</t>
+          <t>Janiele Ferreira</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2484,10 +2480,10 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>66</v>
+        <v>20</v>
       </c>
       <c r="K41" t="n">
-        <v>66</v>
+        <v>20</v>
       </c>
     </row>
     <row r="42">
@@ -2523,7 +2519,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Marlon Silva</t>
+          <t>Jefferson Barros</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2532,13 +2528,13 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J42" t="n">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="K42" t="n">
-        <v>53</v>
+        <v>89</v>
       </c>
     </row>
     <row r="43">
@@ -2574,7 +2570,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Monique Britto</t>
+          <t>Karina Oliveira</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2586,10 +2582,10 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="K43" t="n">
-        <v>61</v>
+        <v>27</v>
       </c>
     </row>
     <row r="44">
@@ -2625,7 +2621,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Romulo Ferreira</t>
+          <t>Leonardo Assunção</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2634,13 +2630,13 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J44" t="n">
-        <v>101</v>
+        <v>18</v>
       </c>
       <c r="K44" t="n">
-        <v>101</v>
+        <v>18</v>
       </c>
     </row>
     <row r="45">
@@ -2676,7 +2672,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rosilene Silva</t>
+          <t>Liliane Costa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2688,10 +2684,10 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K45" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="46">
@@ -2727,7 +2723,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Thais Santos</t>
+          <t>Luciene Pimenta</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2739,10 +2735,10 @@
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>85</v>
+        <v>8</v>
       </c>
       <c r="K46" t="n">
-        <v>85</v>
+        <v>8</v>
       </c>
     </row>
     <row r="47">
@@ -2778,7 +2774,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Vitoria Tavares</t>
+          <t>Lucirene Souza</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2787,13 +2783,13 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J47" t="n">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="K47" t="n">
-        <v>91</v>
+        <v>71</v>
       </c>
     </row>
     <row r="48">
@@ -2829,7 +2825,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Viviane Moura</t>
+          <t>Marlon Silva</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2838,13 +2834,13 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="J48" t="n">
-        <v>27</v>
+        <v>82</v>
       </c>
       <c r="K48" t="n">
-        <v>27</v>
+        <v>82</v>
       </c>
     </row>
     <row r="49">
@@ -2880,7 +2876,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Yasmin Lopes</t>
+          <t>Monique Britto</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2892,10 +2888,10 @@
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="K49" t="n">
-        <v>39</v>
+        <v>61</v>
       </c>
     </row>
     <row r="50">
@@ -2926,27 +2922,27 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>RJ - EF</t>
+          <t>RJ - DP</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Altamir Nogueira</t>
+          <t>Romulo Ferreira</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Julio Santos|Jessica Benjamin</t>
+          <t>Karina Oliveira|Liliane Costa</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>163</v>
       </c>
       <c r="J50" t="n">
-        <v>25</v>
+        <v>264</v>
       </c>
       <c r="K50" t="n">
-        <v>25</v>
+        <v>264</v>
       </c>
     </row>
     <row r="51">
@@ -2977,27 +2973,27 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>RJ - EF</t>
+          <t>RJ - DP</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Beatriz Oliveira</t>
+          <t>Rosilene Silva</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Julio Santos|Jessica Benjamin</t>
+          <t>Karina Oliveira|Liliane Costa</t>
         </is>
       </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="K51" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="52">
@@ -3028,27 +3024,27 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>RJ - EF</t>
+          <t>RJ - DP</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Glaucia Santos</t>
+          <t>Thais Santos</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Julio Santos|Jessica Benjamin</t>
+          <t>Karina Oliveira|Liliane Costa</t>
         </is>
       </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>25</v>
+        <v>85</v>
       </c>
       <c r="K52" t="n">
-        <v>25</v>
+        <v>85</v>
       </c>
     </row>
     <row r="53">
@@ -3079,27 +3075,27 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>RJ - EF</t>
+          <t>RJ - DP</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Isabela Barbosa</t>
+          <t>Vitoria Tavares</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Julio Santos|Jessica Benjamin</t>
+          <t>Karina Oliveira|Liliane Costa</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="J53" t="n">
-        <v>5</v>
+        <v>113</v>
       </c>
       <c r="K53" t="n">
-        <v>5</v>
+        <v>113</v>
       </c>
     </row>
     <row r="54">
@@ -3130,27 +3126,27 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>RJ - EF</t>
+          <t>RJ - DP</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Jessica Benjamin</t>
+          <t>Viviane Moura</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Julio Santos|Jessica Benjamin</t>
+          <t>Karina Oliveira|Liliane Costa</t>
         </is>
       </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="K54" t="n">
-        <v>59</v>
+        <v>27</v>
       </c>
     </row>
     <row r="55">
@@ -3181,27 +3177,27 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>RJ - EF</t>
+          <t>RJ - DP</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Juliana Perfeito</t>
+          <t>Yasmin Lopes</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Julio Santos|Jessica Benjamin</t>
+          <t>Karina Oliveira|Liliane Costa</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="J55" t="n">
-        <v>10</v>
+        <v>84</v>
       </c>
       <c r="K55" t="n">
-        <v>10</v>
+        <v>84</v>
       </c>
     </row>
     <row r="56">
@@ -3237,7 +3233,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lais Catrine EF</t>
+          <t>Altamir Nogueira</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3246,13 +3242,13 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="K56" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="57">
@@ -3288,7 +3284,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Luana Meneses</t>
+          <t>Beatriz Oliveira</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3297,13 +3293,13 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J57" t="n">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="K57" t="n">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="58">
@@ -3339,7 +3335,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Otacilia Ferreira</t>
+          <t>Glaucia Santos</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3351,10 +3347,10 @@
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="K58" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="59">
@@ -3390,7 +3386,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Renata Paixão</t>
+          <t>Isabela Barbosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3402,10 +3398,10 @@
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>70</v>
+        <v>5</v>
       </c>
       <c r="K59" t="n">
-        <v>70</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60">
@@ -3441,7 +3437,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Thamara Jordes</t>
+          <t>Jessica Benjamin</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3453,10 +3449,10 @@
         <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="K60" t="n">
-        <v>41</v>
+        <v>59</v>
       </c>
     </row>
     <row r="61">
@@ -3492,7 +3488,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Wellington Oliveira</t>
+          <t>Juliana Perfeito</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3501,13 +3497,13 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J61" t="n">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="K61" t="n">
-        <v>52</v>
+        <v>14</v>
       </c>
     </row>
     <row r="62">
@@ -3538,17 +3534,21 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>RJ - GC</t>
+          <t>RJ - EF</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Bruno Mota</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr"/>
+          <t>Lais Catrine EF</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Julio Santos|Jessica Benjamin</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J62" t="n">
         <v>62</v>
@@ -3585,23 +3585,27 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>RJ - GC</t>
+          <t>RJ - EF</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cavalcante Peres</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr"/>
+          <t>Luana Meneses</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Julio Santos|Jessica Benjamin</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J63" t="n">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="K63" t="n">
-        <v>19</v>
+        <v>41</v>
       </c>
     </row>
     <row r="64">
@@ -3632,23 +3636,27 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>RJ - GC ADMINISTRATIVO</t>
+          <t>RJ - EF</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Amanda Mesquita</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr"/>
+          <t>Otacilia Ferreira</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Julio Santos|Jessica Benjamin</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J64" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K64" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="65">
@@ -3679,23 +3687,27 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>RJ - GC ADMINISTRATIVO</t>
+          <t>RJ - EF</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lohany Martins</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr"/>
+          <t>Renata Paixão</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Julio Santos|Jessica Benjamin</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J65" t="n">
-        <v>187</v>
+        <v>79</v>
       </c>
       <c r="K65" t="n">
-        <v>187</v>
+        <v>79</v>
       </c>
     </row>
     <row r="66">
@@ -3726,23 +3738,27 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>S.A.C</t>
+          <t>RJ - EF</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Milena Campos - SAC</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
+          <t>Thamara Jordes</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Julio Santos|Jessica Benjamin</t>
+        </is>
+      </c>
       <c r="I66" t="n">
         <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="K66" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
     </row>
     <row r="67">
@@ -3768,32 +3784,32 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>CONTABILIDADE (Outsourcing)</t>
+          <t>RJ - EF</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Aline Petrini</t>
+          <t>Wellington Oliveira</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Julio Santos|Jessica Benjamin</t>
         </is>
       </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="K67" t="n">
-        <v>1</v>
+        <v>51</v>
       </c>
     </row>
     <row r="68">
@@ -3819,32 +3835,28 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>CONTABILIDADE (Outsourcing)</t>
+          <t>RJ - GC</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Daniele Leite</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Edileide Dias</t>
-        </is>
-      </c>
+          <t>Bruno Mota</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
       <c r="I68" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="J68" t="n">
-        <v>1</v>
+        <v>85</v>
       </c>
       <c r="K68" t="n">
-        <v>1</v>
+        <v>85</v>
       </c>
     </row>
     <row r="69">
@@ -3870,32 +3882,28 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>CONTABILIDADE (Outsourcing)</t>
+          <t>RJ - GC</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Jaqueline Sousa</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Lucas Fischer</t>
-        </is>
-      </c>
+          <t>Cavalcante Peres</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J69" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="K69" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="70">
@@ -3921,32 +3929,28 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>CONTABILIDADE (Outsourcing)</t>
+          <t>RJ - GC ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Patricia Borges</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Edileide Dias</t>
-        </is>
-      </c>
+          <t>Amanda Mesquita</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
       <c r="I70" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="K70" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
     </row>
     <row r="71">
@@ -3972,32 +3976,28 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>CONTABILIDADE (Outsourcing)</t>
+          <t>RJ - GC ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Rejane Coelho</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Karina Santos</t>
-        </is>
-      </c>
+          <t>Lohany Martins</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
       <c r="I71" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J71" t="n">
-        <v>4</v>
+        <v>190</v>
       </c>
       <c r="K71" t="n">
-        <v>4</v>
+        <v>190</v>
       </c>
     </row>
     <row r="72">
@@ -4023,24 +4023,20 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>CONTABILIDADE (Outsourcing)</t>
+          <t>S.A.C</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Thiago Ceconelli</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Karina Santos</t>
-        </is>
-      </c>
+          <t>Milena Campos - SAC</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
       <c r="I72" t="n">
         <v>0</v>
       </c>
@@ -4079,17 +4075,17 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL HOLDING</t>
+          <t>CONTABILIDADE (Outsourcing)</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ana Flavia Silva</t>
+          <t>Aline Petrini</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="I73" t="n">
@@ -4130,27 +4126,27 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL HOLDING</t>
+          <t>CONTABILIDADE (Outsourcing)</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Vitor de Souza</t>
+          <t>Daniele Leite</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I74" t="n">
         <v>0</v>
       </c>
       <c r="J74" t="n">
-        <v>59</v>
+        <v>1</v>
       </c>
       <c r="K74" t="n">
-        <v>59</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -4181,27 +4177,27 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL HOLDING</t>
+          <t>CONTABILIDADE (Outsourcing)</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Vitoria Regina</t>
+          <t>Jaqueline Sousa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Lucas Fischer</t>
         </is>
       </c>
       <c r="I75" t="n">
         <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="K75" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -4232,27 +4228,27 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL INDUSTRIA</t>
+          <t>CONTABILIDADE (Outsourcing)</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Adriano Barros</t>
+          <t>Patricia Borges</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Erika Santana|Isabella Nascimento</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J76" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K76" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77">
@@ -4283,27 +4279,27 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL INDUSTRIA</t>
+          <t>CONTABILIDADE (Outsourcing)</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Bianca Silva</t>
+          <t>Rejane Coelho</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Erika Santana|Isabella Nascimento</t>
+          <t>Karina Santos</t>
         </is>
       </c>
       <c r="I77" t="n">
         <v>0</v>
       </c>
       <c r="J77" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K77" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="78">
@@ -4334,27 +4330,27 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL INDUSTRIA</t>
+          <t>CONTABILIDADE (Outsourcing)</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Emylle Souza</t>
+          <t>Thiago Ceconelli</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Erika Santana|Isabella Nascimento</t>
+          <t>Karina Santos</t>
         </is>
       </c>
       <c r="I78" t="n">
         <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -4385,27 +4381,27 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL INDUSTRIA</t>
+          <t>CTB - CONTÁBIL HOLDING</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Fatima Rocha</t>
+          <t>Ana Flavia Silva</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Erika Santana|Isabella Nascimento</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J79" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K79" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80">
@@ -4436,27 +4432,27 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL INDUSTRIA</t>
+          <t>CTB - CONTÁBIL HOLDING</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Gabriel Correia</t>
+          <t>Vitor de Souza</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Erika Santana|Isabella Nascimento</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J80" t="n">
-        <v>4</v>
+        <v>67</v>
       </c>
       <c r="K80" t="n">
-        <v>4</v>
+        <v>67</v>
       </c>
     </row>
     <row r="81">
@@ -4487,27 +4483,27 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL INDUSTRIA</t>
+          <t>CTB - CONTÁBIL HOLDING</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Isabella Nascimento</t>
+          <t>Vitoria Regina</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Erika Santana|Isabella Nascimento</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J81" t="n">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="K81" t="n">
-        <v>2</v>
+        <v>46</v>
       </c>
     </row>
     <row r="82">
@@ -4543,7 +4539,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Laisa Rocha</t>
+          <t>Adriano Barros</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4555,10 +4551,10 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -4594,7 +4590,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lucas Alves</t>
+          <t>Bianca Silva</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4645,7 +4641,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Luciana Silva</t>
+          <t>Emylle Souza</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4657,10 +4653,10 @@
         <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K84" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
@@ -4696,18 +4692,22 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Luiz Ferreira</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr"/>
+          <t>Fatima Rocha</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Erika Santana|Isabella Nascimento</t>
+        </is>
+      </c>
       <c r="I85" t="n">
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K85" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
@@ -4743,7 +4743,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Marcus Oliveira</t>
+          <t>Gabriel Correia</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4755,10 +4755,10 @@
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K86" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="87">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Mateus Miranda</t>
+          <t>Isabella Nascimento</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4806,10 +4806,10 @@
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
@@ -4845,7 +4845,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Mirian Lima</t>
+          <t>Laisa Rocha</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Nathalia Lourenco</t>
+          <t>Lucas Alves</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -4908,10 +4908,10 @@
         <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
@@ -4947,7 +4947,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Nicolas Dias</t>
+          <t>Luciana Silva</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4959,10 +4959,10 @@
         <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K90" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91">
@@ -4998,22 +4998,18 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Rodrigo Nunes</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Erika Santana|Isabella Nascimento</t>
-        </is>
-      </c>
+          <t>Luiz Ferreira</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr"/>
       <c r="I91" t="n">
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K91" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="92">
@@ -5044,27 +5040,27 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Aline Petrini</t>
+          <t>Marcus Oliveira</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Erika Santana|Isabella Nascimento</t>
         </is>
       </c>
       <c r="I92" t="n">
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K92" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
@@ -5095,27 +5091,27 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Ana Barbosa</t>
+          <t>Mateus Miranda</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Erika Santana|Isabella Nascimento</t>
         </is>
       </c>
       <c r="I93" t="n">
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="K93" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
@@ -5146,27 +5142,27 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Daniele Leite</t>
+          <t>Mirian Lima</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Erika Santana|Isabella Nascimento</t>
         </is>
       </c>
       <c r="I94" t="n">
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K94" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
@@ -5197,27 +5193,27 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Danielle Silva</t>
+          <t>Nathalia Lourenco</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Erika Santana|Isabella Nascimento</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J95" t="n">
-        <v>47</v>
+        <v>3</v>
       </c>
       <c r="K95" t="n">
-        <v>47</v>
+        <v>3</v>
       </c>
     </row>
     <row r="96">
@@ -5248,27 +5244,27 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Danilo Oliveira</t>
+          <t>Nicolas Dias</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Erika Santana|Isabella Nascimento</t>
         </is>
       </c>
       <c r="I96" t="n">
         <v>0</v>
       </c>
       <c r="J96" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="K96" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
@@ -5299,27 +5295,27 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Debora Silva</t>
+          <t>Rodrigo Nunes</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Erika Santana|Isabella Nascimento</t>
         </is>
       </c>
       <c r="I97" t="n">
         <v>0</v>
       </c>
       <c r="J97" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K97" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="98">
@@ -5355,22 +5351,22 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Diogo Calazans</t>
+          <t>Aline Petrini</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J98" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="K98" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="99">
@@ -5406,22 +5402,22 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Eduardo Cruz</t>
+          <t>Ana Barbosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I99" t="n">
         <v>0</v>
       </c>
       <c r="J99" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="K99" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="100">
@@ -5457,22 +5453,22 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Eveny Silva</t>
+          <t>Daniele Leite</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I100" t="n">
         <v>0</v>
       </c>
       <c r="J100" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="K100" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="101">
@@ -5508,22 +5504,22 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Everton Moura</t>
+          <t>Danielle Silva</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Karina Santos</t>
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J101" t="n">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="K101" t="n">
-        <v>2</v>
+        <v>51</v>
       </c>
     </row>
     <row r="102">
@@ -5559,22 +5555,22 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Guilherme Dantas</t>
+          <t>Danilo Oliveira</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Karina Santos</t>
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J102" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="K102" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="103">
@@ -5610,7 +5606,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Isabela Lemos</t>
+          <t>Debora Silva</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -5619,7 +5615,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J103" t="n">
         <v>9</v>
@@ -5661,22 +5657,22 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Jackson Silva</t>
+          <t>Diogo Calazans</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Karina Santos</t>
         </is>
       </c>
       <c r="I104" t="n">
         <v>0</v>
       </c>
       <c r="J104" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="K104" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
     </row>
     <row r="105">
@@ -5712,22 +5708,22 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Jaqueline Sousa</t>
+          <t>Eduardo Cruz</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Lucas Fischer</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="I105" t="n">
         <v>0</v>
       </c>
       <c r="J105" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K105" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="106">
@@ -5763,22 +5759,22 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Leticia Medeiros</t>
+          <t>Eveny Silva</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Lucas Fischer</t>
+          <t>Karina Santos</t>
         </is>
       </c>
       <c r="I106" t="n">
         <v>0</v>
       </c>
       <c r="J106" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K106" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="107">
@@ -5814,22 +5810,22 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Monica Medeiros</t>
+          <t>Everton Moura</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="I107" t="n">
         <v>0</v>
       </c>
       <c r="J107" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K107" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
@@ -5865,22 +5861,22 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Naiara Dutra</t>
+          <t>Guilherme Dantas</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Lucas Fischer</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I108" t="n">
         <v>0</v>
       </c>
       <c r="J108" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K108" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="109">
@@ -5916,22 +5912,22 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Patricia Borges</t>
+          <t>Isabela Lemos</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="I109" t="n">
         <v>0</v>
       </c>
       <c r="J109" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="K109" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="110">
@@ -5967,22 +5963,22 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Paulo Silva</t>
+          <t>Jackson Silva</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J110" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="K110" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="111">
@@ -6018,22 +6014,22 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Rachel Lima</t>
+          <t>Jaqueline Sousa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Lucas Fischer</t>
         </is>
       </c>
       <c r="I111" t="n">
         <v>0</v>
       </c>
       <c r="J111" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="K111" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112">
@@ -6069,22 +6065,22 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Raiane Barbosa</t>
+          <t>Leticia Medeiros</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Lucas Fischer</t>
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J112" t="n">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="K112" t="n">
-        <v>47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="113">
@@ -6120,22 +6116,22 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Rejane Coelho</t>
+          <t>Monica Medeiros</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I113" t="n">
         <v>0</v>
       </c>
       <c r="J113" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K113" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="114">
@@ -6171,7 +6167,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Renata Alves - CTV</t>
+          <t>Naiara Dutra</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -6183,10 +6179,10 @@
         <v>0</v>
       </c>
       <c r="J114" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K114" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="115">
@@ -6222,18 +6218,22 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Renata Cavalheiro</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr"/>
+          <t>Patricia Borges</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Edileide Dias</t>
+        </is>
+      </c>
       <c r="I115" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J115" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K115" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="116">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Ryan Godinho</t>
+          <t>Paulo Silva</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J116" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="K116" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
     </row>
     <row r="117">
@@ -6320,22 +6320,22 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Vitor Domingues</t>
+          <t>Rachel Lima</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I117" t="n">
         <v>0</v>
       </c>
       <c r="J117" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="K117" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="118">
@@ -6366,27 +6366,27 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO PESSOAL (Outsourcing)</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Bruna Santana</t>
+          <t>Raiane Barbosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I118" t="n">
         <v>0</v>
       </c>
       <c r="J118" t="n">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="K118" t="n">
-        <v>2</v>
+        <v>47</v>
       </c>
     </row>
     <row r="119">
@@ -6417,27 +6417,27 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO PESSOAL (Outsourcing)</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Camila Oliveira</t>
+          <t>Rejane Coelho</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Karina Santos</t>
         </is>
       </c>
       <c r="I119" t="n">
         <v>0</v>
       </c>
       <c r="J119" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="K119" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120">
@@ -6468,27 +6468,27 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO PESSOAL (Outsourcing)</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Elaine Assis</t>
+          <t>Renata Alves - CTV</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Lucas Fischer</t>
         </is>
       </c>
       <c r="I120" t="n">
         <v>0</v>
       </c>
       <c r="J120" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K120" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="121">
@@ -6519,27 +6519,23 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO PESSOAL (Outsourcing)</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Fabiane Branco</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Sara Cavalheiro</t>
-        </is>
-      </c>
+          <t>Renata Cavalheiro</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr"/>
       <c r="I121" t="n">
         <v>0</v>
       </c>
       <c r="J121" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K121" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122">
@@ -6570,27 +6566,27 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO PESSOAL (Outsourcing)</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Jonas Nunes</t>
+          <t>Ryan Godinho</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Karina Santos</t>
         </is>
       </c>
       <c r="I122" t="n">
         <v>0</v>
       </c>
       <c r="J122" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K122" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="123">
@@ -6621,27 +6617,27 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Bruna Santana</t>
+          <t>Vitor Domingues</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="I123" t="n">
         <v>0</v>
       </c>
       <c r="J123" t="n">
-        <v>82</v>
+        <v>21</v>
       </c>
       <c r="K123" t="n">
-        <v>82</v>
+        <v>21</v>
       </c>
     </row>
     <row r="124">
@@ -6672,12 +6668,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>DEPARTAMENTO PESSOAL (Outsourcing)</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Camila Oliveira</t>
+          <t>Bruna Santana</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -6686,13 +6682,13 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J124" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="K124" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="125">
@@ -6723,27 +6719,27 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>DEPARTAMENTO PESSOAL (Outsourcing)</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Daniel Moraes</t>
+          <t>Camila Oliveira</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I125" t="n">
         <v>0</v>
       </c>
       <c r="J125" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K125" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="126">
@@ -6774,12 +6770,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>DEPARTAMENTO PESSOAL (Outsourcing)</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Danilo Xavier</t>
+          <t>Elaine Assis</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -6791,10 +6787,10 @@
         <v>0</v>
       </c>
       <c r="J126" t="n">
-        <v>120</v>
+        <v>4</v>
       </c>
       <c r="K126" t="n">
-        <v>120</v>
+        <v>4</v>
       </c>
     </row>
     <row r="127">
@@ -6825,27 +6821,27 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>DEPARTAMENTO PESSOAL (Outsourcing)</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Elaine Assis</t>
+          <t>Fabiane Branco</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J127" t="n">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="K127" t="n">
-        <v>42</v>
+        <v>8</v>
       </c>
     </row>
     <row r="128">
@@ -6876,27 +6872,27 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>DEPARTAMENTO PESSOAL (Outsourcing)</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Eliene Lima</t>
+          <t>Jonas Nunes</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J128" t="n">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="K128" t="n">
-        <v>43</v>
+        <v>13</v>
       </c>
     </row>
     <row r="129">
@@ -6932,22 +6928,22 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Erica Oliveira</t>
+          <t>Bruna Santana</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J129" t="n">
-        <v>28</v>
+        <v>92</v>
       </c>
       <c r="K129" t="n">
-        <v>28</v>
+        <v>92</v>
       </c>
     </row>
     <row r="130">
@@ -6983,22 +6979,22 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Evellin Bispo</t>
+          <t>Camila Oliveira</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Leandro Matos</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I130" t="n">
         <v>0</v>
       </c>
       <c r="J130" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="K130" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="131">
@@ -7034,22 +7030,22 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Fabiane Branco</t>
+          <t>Daniel Moraes</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J131" t="n">
-        <v>92</v>
+        <v>14</v>
       </c>
       <c r="K131" t="n">
-        <v>92</v>
+        <v>14</v>
       </c>
     </row>
     <row r="132">
@@ -7085,7 +7081,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Franciele Alves</t>
+          <t>Danilo Xavier</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -7094,13 +7090,13 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J132" t="n">
-        <v>3</v>
+        <v>140</v>
       </c>
       <c r="K132" t="n">
-        <v>3</v>
+        <v>140</v>
       </c>
     </row>
     <row r="133">
@@ -7136,22 +7132,22 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Gabriela Peres</t>
+          <t>Elaine Assis</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Leandro Matos</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I133" t="n">
         <v>0</v>
       </c>
       <c r="J133" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="K133" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
     </row>
     <row r="134">
@@ -7187,22 +7183,22 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Grasiele Santos</t>
+          <t>Eliene Lima</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I134" t="n">
         <v>0</v>
       </c>
       <c r="J134" t="n">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="K134" t="n">
-        <v>57</v>
+        <v>43</v>
       </c>
     </row>
     <row r="135">
@@ -7238,7 +7234,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Erica Oliveira</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -7247,13 +7243,13 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J135" t="n">
-        <v>91</v>
+        <v>33</v>
       </c>
       <c r="K135" t="n">
-        <v>91</v>
+        <v>33</v>
       </c>
     </row>
     <row r="136">
@@ -7289,22 +7285,22 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Janaina Rocha</t>
+          <t>Evellin Bispo</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Leandro Matos</t>
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J136" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="K136" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
     </row>
     <row r="137">
@@ -7340,7 +7336,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Jayne Tavares</t>
+          <t>Fabiane Branco</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -7349,13 +7345,13 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="J137" t="n">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="K137" t="n">
-        <v>124</v>
+        <v>118</v>
       </c>
     </row>
     <row r="138">
@@ -7391,22 +7387,22 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Jhenifer Tenorio</t>
+          <t>Franciele Alves</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I138" t="n">
         <v>0</v>
       </c>
       <c r="J138" t="n">
-        <v>69</v>
+        <v>26</v>
       </c>
       <c r="K138" t="n">
-        <v>69</v>
+        <v>26</v>
       </c>
     </row>
     <row r="139">
@@ -7442,22 +7438,22 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Jonas Nunes</t>
+          <t>Gabriela Peres</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Leandro Matos</t>
         </is>
       </c>
       <c r="I139" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J139" t="n">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="K139" t="n">
-        <v>37</v>
+        <v>12</v>
       </c>
     </row>
     <row r="140">
@@ -7493,22 +7489,22 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Kaique Souza</t>
+          <t>Grasiele Santos</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="J140" t="n">
-        <v>59</v>
+        <v>95</v>
       </c>
       <c r="K140" t="n">
-        <v>59</v>
+        <v>95</v>
       </c>
     </row>
     <row r="141">
@@ -7544,22 +7540,22 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Karine Sousa</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I141" t="n">
         <v>0</v>
       </c>
       <c r="J141" t="n">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="K141" t="n">
-        <v>50</v>
+        <v>91</v>
       </c>
     </row>
     <row r="142">
@@ -7595,7 +7591,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Laysla Alves</t>
+          <t>Janaina Rocha</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -7604,13 +7600,13 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J142" t="n">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="K142" t="n">
-        <v>36</v>
+        <v>66</v>
       </c>
     </row>
     <row r="143">
@@ -7646,22 +7642,22 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Luana Marques</t>
+          <t>Jayne Tavares</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J143" t="n">
-        <v>14</v>
+        <v>125</v>
       </c>
       <c r="K143" t="n">
-        <v>14</v>
+        <v>125</v>
       </c>
     </row>
     <row r="144">
@@ -7697,22 +7693,22 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Maria Pires</t>
+          <t>Jhenifer Tenorio</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I144" t="n">
         <v>0</v>
       </c>
       <c r="J144" t="n">
-        <v>1</v>
+        <v>69</v>
       </c>
       <c r="K144" t="n">
-        <v>1</v>
+        <v>69</v>
       </c>
     </row>
     <row r="145">
@@ -7748,22 +7744,22 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Mauricio Lermen</t>
+          <t>Jonas Nunes</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Mauricio Lermen</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I145" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J145" t="n">
-        <v>13</v>
+        <v>61</v>
       </c>
       <c r="K145" t="n">
-        <v>13</v>
+        <v>61</v>
       </c>
     </row>
     <row r="146">
@@ -7799,7 +7795,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Micaele Cordeiro</t>
+          <t>Kaique Souza</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -7811,10 +7807,10 @@
         <v>0</v>
       </c>
       <c r="J146" t="n">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="K146" t="n">
-        <v>73</v>
+        <v>59</v>
       </c>
     </row>
     <row r="147">
@@ -7850,7 +7846,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Michele Silva</t>
+          <t>Karine Sousa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -7862,10 +7858,10 @@
         <v>0</v>
       </c>
       <c r="J147" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="K147" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="148">
@@ -7901,22 +7897,22 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Murilo Marques</t>
+          <t>Laysla Alves</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I148" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J148" t="n">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="K148" t="n">
-        <v>21</v>
+        <v>53</v>
       </c>
     </row>
     <row r="149">
@@ -7952,22 +7948,22 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Natalia Batista</t>
+          <t>Luana Marques</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J149" t="n">
-        <v>89</v>
+        <v>17</v>
       </c>
       <c r="K149" t="n">
-        <v>89</v>
+        <v>17</v>
       </c>
     </row>
     <row r="150">
@@ -8003,7 +7999,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Natalia Silva</t>
+          <t>Maria Pires</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -8012,13 +8008,13 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="J150" t="n">
-        <v>73</v>
+        <v>1</v>
       </c>
       <c r="K150" t="n">
-        <v>73</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151">
@@ -8054,22 +8050,22 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Oliene Mariano</t>
+          <t>Mauricio Lermen</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>Mauricio Lermen</t>
         </is>
       </c>
       <c r="I151" t="n">
         <v>0</v>
       </c>
       <c r="J151" t="n">
-        <v>62</v>
+        <v>13</v>
       </c>
       <c r="K151" t="n">
-        <v>62</v>
+        <v>13</v>
       </c>
     </row>
     <row r="152">
@@ -8105,22 +8101,22 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Priscila Aguiar</t>
+          <t>Micaele Cordeiro</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J152" t="n">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="K152" t="n">
-        <v>41</v>
+        <v>79</v>
       </c>
     </row>
     <row r="153">
@@ -8156,12 +8152,12 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Rebeca Ribeiro</t>
+          <t>Michele Silva</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I153" t="n">
@@ -8207,22 +8203,22 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Roberta Souza</t>
+          <t>Murilo Marques</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I154" t="n">
         <v>0</v>
       </c>
       <c r="J154" t="n">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="K154" t="n">
-        <v>67</v>
+        <v>21</v>
       </c>
     </row>
     <row r="155">
@@ -8258,7 +8254,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Ronildo Santos</t>
+          <t>Natalia Batista</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -8267,13 +8263,13 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J155" t="n">
-        <v>3</v>
+        <v>92</v>
       </c>
       <c r="K155" t="n">
-        <v>3</v>
+        <v>92</v>
       </c>
     </row>
     <row r="156">
@@ -8309,7 +8305,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Rozania Santos</t>
+          <t>Natalia Silva</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -8318,13 +8314,13 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J156" t="n">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="K156" t="n">
-        <v>57</v>
+        <v>81</v>
       </c>
     </row>
     <row r="157">
@@ -8360,22 +8356,22 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Sibelly Pereira</t>
+          <t>Oliene Mariano</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I157" t="n">
         <v>0</v>
       </c>
       <c r="J157" t="n">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="K157" t="n">
-        <v>28</v>
+        <v>62</v>
       </c>
     </row>
     <row r="158">
@@ -8411,22 +8407,22 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Tania Luz</t>
+          <t>Priscila Aguiar</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J158" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="K158" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
     </row>
     <row r="159">
@@ -8462,22 +8458,22 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Vitor Guedes</t>
+          <t>Rebeca Ribeiro</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I159" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J159" t="n">
-        <v>87</v>
+        <v>58</v>
       </c>
       <c r="K159" t="n">
-        <v>87</v>
+        <v>58</v>
       </c>
     </row>
     <row r="160">
@@ -8508,27 +8504,27 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Andrea Medeiros</t>
+          <t>Roberta Souza</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I160" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J160" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="K160" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
     </row>
     <row r="161">
@@ -8559,27 +8555,27 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Caroline Nascimento</t>
+          <t>Ronildo Santos</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I161" t="n">
         <v>0</v>
       </c>
       <c r="J161" t="n">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="K161" t="n">
-        <v>48</v>
+        <v>3</v>
       </c>
     </row>
     <row r="162">
@@ -8610,27 +8606,27 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Cristiana Grizostomo</t>
+          <t>Rozania Santos</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I162" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J162" t="n">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="K162" t="n">
-        <v>21</v>
+        <v>58</v>
       </c>
     </row>
     <row r="163">
@@ -8661,23 +8657,27 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Denis Reis</t>
-        </is>
-      </c>
-      <c r="H163" t="inlineStr"/>
+          <t>Sibelly Pereira</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>David Bragança</t>
+        </is>
+      </c>
       <c r="I163" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J163" t="n">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="K163" t="n">
-        <v>52</v>
+        <v>40</v>
       </c>
     </row>
     <row r="164">
@@ -8708,27 +8708,27 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Eliane Moreira</t>
+          <t>Tania Luz</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J164" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="K164" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
     </row>
     <row r="165">
@@ -8759,27 +8759,27 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Gustavo Tonan</t>
+          <t>Vitor Guedes</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I165" t="n">
         <v>0</v>
       </c>
       <c r="J165" t="n">
-        <v>50</v>
+        <v>87</v>
       </c>
       <c r="K165" t="n">
-        <v>50</v>
+        <v>87</v>
       </c>
     </row>
     <row r="166">
@@ -8815,7 +8815,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Jonatan Hayashibara</t>
+          <t>Andrea Medeiros</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -8824,13 +8824,13 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J166" t="n">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="K166" t="n">
-        <v>8</v>
+        <v>38</v>
       </c>
     </row>
     <row r="167">
@@ -8866,7 +8866,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Lais Arruda</t>
+          <t>Caroline Nascimento</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -8875,13 +8875,13 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J167" t="n">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="K167" t="n">
-        <v>31</v>
+        <v>50</v>
       </c>
     </row>
     <row r="168">
@@ -8917,7 +8917,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Luan Batista</t>
+          <t>Cristiana Grizostomo</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -8929,10 +8929,10 @@
         <v>0</v>
       </c>
       <c r="J168" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="K168" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
     </row>
     <row r="169">
@@ -8968,22 +8968,18 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Maria Garcia</t>
-        </is>
-      </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>Nayara Oliveira</t>
-        </is>
-      </c>
+          <t>Denis Reis</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr"/>
       <c r="I169" t="n">
         <v>0</v>
       </c>
       <c r="J169" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="K169" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
     </row>
     <row r="170">
@@ -9019,7 +9015,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Priscila Volpe</t>
+          <t>Eliane Moreira</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -9031,10 +9027,10 @@
         <v>0</v>
       </c>
       <c r="J170" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="K170" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
     </row>
     <row r="171">
@@ -9070,7 +9066,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Rodrigo Souza</t>
+          <t>Gustavo Tonan</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -9082,10 +9078,10 @@
         <v>0</v>
       </c>
       <c r="J171" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="K171" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
     </row>
     <row r="172">
@@ -9121,7 +9117,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Romario Silva</t>
+          <t>Jonatan Hayashibara</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -9130,13 +9126,13 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J172" t="n">
-        <v>57</v>
+        <v>10</v>
       </c>
       <c r="K172" t="n">
-        <v>57</v>
+        <v>10</v>
       </c>
     </row>
     <row r="173">
@@ -9172,7 +9168,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Rosilene Santos</t>
+          <t>Lais Arruda</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -9181,13 +9177,13 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J173" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="K173" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
     </row>
     <row r="174">
@@ -9223,7 +9219,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Suede Gomes</t>
+          <t>Luan Batista</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -9235,10 +9231,10 @@
         <v>0</v>
       </c>
       <c r="J174" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="K174" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="175">
@@ -9274,7 +9270,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Taina Silva</t>
+          <t>Maria Garcia</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -9286,10 +9282,10 @@
         <v>0</v>
       </c>
       <c r="J175" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="K175" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
     </row>
     <row r="176">
@@ -9325,7 +9321,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Thayna Melo</t>
+          <t>Priscila Volpe</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -9334,13 +9330,13 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J176" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K176" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="177">
@@ -9376,7 +9372,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Vanessa Santana</t>
+          <t>Rodrigo Souza</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -9385,13 +9381,13 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J177" t="n">
-        <v>116</v>
+        <v>9</v>
       </c>
       <c r="K177" t="n">
-        <v>116</v>
+        <v>9</v>
       </c>
     </row>
     <row r="178">
@@ -9422,27 +9418,27 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Alaine Neres</t>
+          <t>Romario Silva</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
       <c r="I178" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J178" t="n">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="K178" t="n">
-        <v>2</v>
+        <v>63</v>
       </c>
     </row>
     <row r="179">
@@ -9473,27 +9469,27 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Andre Silva</t>
+          <t>Rosilene Santos</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
       <c r="I179" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J179" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="K179" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
     </row>
     <row r="180">
@@ -9524,27 +9520,27 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Anna Ramalho</t>
+          <t>Suede Gomes</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
       <c r="I180" t="n">
         <v>0</v>
       </c>
       <c r="J180" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="K180" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="181">
@@ -9575,27 +9571,27 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Beatriz Ferreira</t>
+          <t>Taina Silva</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
       <c r="I181" t="n">
         <v>0</v>
       </c>
       <c r="J181" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="K181" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
     </row>
     <row r="182">
@@ -9626,27 +9622,27 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Brenda Batista</t>
+          <t>Thayna Melo</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
       <c r="I182" t="n">
         <v>0</v>
       </c>
       <c r="J182" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="K182" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
     </row>
     <row r="183">
@@ -9677,27 +9673,27 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Bruna Souza</t>
+          <t>Vanessa Santana</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
       <c r="I183" t="n">
         <v>0</v>
       </c>
       <c r="J183" t="n">
-        <v>27</v>
+        <v>116</v>
       </c>
       <c r="K183" t="n">
-        <v>27</v>
+        <v>116</v>
       </c>
     </row>
     <row r="184">
@@ -9733,7 +9729,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Bruno Henrique</t>
+          <t>Alaine Neres</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -9742,13 +9738,13 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J184" t="n">
-        <v>58</v>
+        <v>9</v>
       </c>
       <c r="K184" t="n">
-        <v>58</v>
+        <v>9</v>
       </c>
     </row>
     <row r="185">
@@ -9784,18 +9780,22 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Claudineia Rodrigues</t>
-        </is>
-      </c>
-      <c r="H185" t="inlineStr"/>
+          <t>Andre Silva</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Larice Souza</t>
+        </is>
+      </c>
       <c r="I185" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J185" t="n">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="K185" t="n">
-        <v>64</v>
+        <v>39</v>
       </c>
     </row>
     <row r="186">
@@ -9831,7 +9831,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Cristina Leite</t>
+          <t>Anna Ramalho</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -9840,13 +9840,13 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J186" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K186" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="187">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Davi Santos</t>
+          <t>Beatriz Ferreira</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="I187" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J187" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K187" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="188">
@@ -9933,22 +9933,22 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Deleia Oliveira</t>
+          <t>Brenda Batista</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J188" t="n">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="K188" t="n">
-        <v>48</v>
+        <v>22</v>
       </c>
     </row>
     <row r="189">
@@ -9984,7 +9984,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Diego Pereira</t>
+          <t>Bruna Souza</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -9993,13 +9993,13 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J189" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="K189" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="190">
@@ -10035,22 +10035,22 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Eduardo Lopes</t>
+          <t>Bruno Henrique</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Idna Sousa</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I190" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J190" t="n">
-        <v>9</v>
+        <v>61</v>
       </c>
       <c r="K190" t="n">
-        <v>9</v>
+        <v>61</v>
       </c>
     </row>
     <row r="191">
@@ -10086,22 +10086,18 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Gislaine Lima</t>
-        </is>
-      </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>Lorrane Santos</t>
-        </is>
-      </c>
+          <t>Claudineia Rodrigues</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr"/>
       <c r="I191" t="n">
         <v>0</v>
       </c>
       <c r="J191" t="n">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="K191" t="n">
-        <v>18</v>
+        <v>64</v>
       </c>
     </row>
     <row r="192">
@@ -10137,7 +10133,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Gustavo Santos</t>
+          <t>Cristina Leite</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -10146,13 +10142,13 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J192" t="n">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="K192" t="n">
-        <v>62</v>
+        <v>34</v>
       </c>
     </row>
     <row r="193">
@@ -10188,22 +10184,22 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Igor Valezi</t>
+          <t>Davi Santos</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I193" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J193" t="n">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="K193" t="n">
-        <v>14</v>
+        <v>39</v>
       </c>
     </row>
     <row r="194">
@@ -10239,22 +10235,22 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Izabely Araujo</t>
+          <t>Deleia Oliveira</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Idna Sousa</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J194" t="n">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="K194" t="n">
-        <v>4</v>
+        <v>49</v>
       </c>
     </row>
     <row r="195">
@@ -10290,22 +10286,22 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Joanna Costa</t>
+          <t>Diego Pereira</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J195" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="K195" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
     </row>
     <row r="196">
@@ -10341,22 +10337,22 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Jose Natan</t>
+          <t>Eduardo Lopes</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Idna Sousa</t>
         </is>
       </c>
       <c r="I196" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J196" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="K196" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="197">
@@ -10392,22 +10388,22 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>João Oliveira</t>
+          <t>Gislaine Lima</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I197" t="n">
         <v>0</v>
       </c>
       <c r="J197" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="K197" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="198">
@@ -10443,22 +10439,22 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Juan Ribeiro</t>
+          <t>Gustavo Santos</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="I198" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="J198" t="n">
-        <v>35</v>
+        <v>110</v>
       </c>
       <c r="K198" t="n">
-        <v>35</v>
+        <v>110</v>
       </c>
     </row>
     <row r="199">
@@ -10494,7 +10490,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Juliana Valeria</t>
+          <t>Igor Valezi</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -10506,10 +10502,10 @@
         <v>0</v>
       </c>
       <c r="J199" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="K199" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="200">
@@ -10545,22 +10541,22 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Juliane Vaz</t>
+          <t>Izabely Araujo</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Idna Sousa</t>
         </is>
       </c>
       <c r="I200" t="n">
         <v>0</v>
       </c>
       <c r="J200" t="n">
-        <v>68</v>
+        <v>4</v>
       </c>
       <c r="K200" t="n">
-        <v>68</v>
+        <v>4</v>
       </c>
     </row>
     <row r="201">
@@ -10596,22 +10592,22 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Katia Xavier</t>
+          <t>Joanna Costa</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I201" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J201" t="n">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="K201" t="n">
-        <v>44</v>
+        <v>5</v>
       </c>
     </row>
     <row r="202">
@@ -10647,22 +10643,22 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Larissa Félix</t>
+          <t>Jose Natan</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I202" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="J202" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K202" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="203">
@@ -10698,22 +10694,22 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Léia de Oliveira</t>
+          <t>João Oliveira</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I203" t="n">
         <v>0</v>
       </c>
       <c r="J203" t="n">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="K203" t="n">
-        <v>54</v>
+        <v>5</v>
       </c>
     </row>
     <row r="204">
@@ -10749,22 +10745,22 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Maria Gualberto</t>
+          <t>Juan Ribeiro</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J204" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="K204" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="205">
@@ -10800,22 +10796,22 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Priscila Moreira</t>
+          <t>Juliana Valeria</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I205" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J205" t="n">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="K205" t="n">
-        <v>44</v>
+        <v>33</v>
       </c>
     </row>
     <row r="206">
@@ -10851,7 +10847,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Regiane Santos</t>
+          <t>Juliane Vaz</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -10860,13 +10856,13 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J206" t="n">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="K206" t="n">
-        <v>40</v>
+        <v>69</v>
       </c>
     </row>
     <row r="207">
@@ -10902,22 +10898,22 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Shofia Gomes</t>
+          <t>Katia Xavier</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I207" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J207" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="K207" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="208">
@@ -10953,22 +10949,22 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Vanessa Tavares</t>
+          <t>Larissa Félix</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I208" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J208" t="n">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="K208" t="n">
-        <v>25</v>
+        <v>52</v>
       </c>
     </row>
     <row r="209">
@@ -11004,22 +11000,22 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Willian Luz</t>
+          <t>Léia de Oliveira</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I209" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J209" t="n">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="K209" t="n">
-        <v>8</v>
+        <v>60</v>
       </c>
     </row>
     <row r="210">
@@ -11055,22 +11051,22 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Yasmim Oliveira</t>
+          <t>Maria Gualberto</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I210" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J210" t="n">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="K210" t="n">
-        <v>15</v>
+        <v>51</v>
       </c>
     </row>
     <row r="211">
@@ -11101,23 +11097,27 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>ESCRITA FISCAL (Outsourcing)</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Claudineia Rodrigues</t>
-        </is>
-      </c>
-      <c r="H211" t="inlineStr"/>
+          <t>Priscila Moreira</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Ricardo Fischer</t>
+        </is>
+      </c>
       <c r="I211" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J211" t="n">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="K211" t="n">
-        <v>2</v>
+        <v>45</v>
       </c>
     </row>
     <row r="212">
@@ -11148,27 +11148,27 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>ESCRITA FISCAL (Outsourcing)</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Diego Pereira</t>
+          <t>Regiane Santos</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I212" t="n">
         <v>0</v>
       </c>
       <c r="J212" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="K212" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="213">
@@ -11199,27 +11199,27 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>ESCRITA FISCAL (Outsourcing)</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Gislaine Lima</t>
+          <t>Shofia Gomes</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="I213" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J213" t="n">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="K213" t="n">
-        <v>11</v>
+        <v>65</v>
       </c>
     </row>
     <row r="214">
@@ -11250,27 +11250,27 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>ESCRITA FISCAL (Outsourcing)</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Joanna Costa</t>
+          <t>Vanessa Tavares</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I214" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J214" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="K214" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
     </row>
     <row r="215">
@@ -11301,12 +11301,12 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>ESCRITA FISCAL (Outsourcing)</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>João Oliveira</t>
+          <t>Willian Luz</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -11315,13 +11315,13 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J215" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="K215" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="216">
@@ -11352,12 +11352,12 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>ESCRITA FISCAL (Outsourcing)</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Regiane Santos</t>
+          <t>Yasmim Oliveira</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -11366,13 +11366,13 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J216" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="K216" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="217">
@@ -11408,14 +11408,10 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Yasmim Oliveira</t>
-        </is>
-      </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>Larice Souza</t>
-        </is>
-      </c>
+          <t>Claudineia Rodrigues</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr"/>
       <c r="I217" t="n">
         <v>0</v>
       </c>
@@ -11454,23 +11450,27 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>ESCRITA FISCAL (Outsourcing)</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Ana Santana</t>
-        </is>
-      </c>
-      <c r="H218" t="inlineStr"/>
+          <t>Diego Pereira</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Thaiza Oliveira</t>
+        </is>
+      </c>
       <c r="I218" t="n">
         <v>0</v>
       </c>
       <c r="J218" t="n">
-        <v>181</v>
+        <v>5</v>
       </c>
       <c r="K218" t="n">
-        <v>181</v>
+        <v>5</v>
       </c>
     </row>
     <row r="219">
@@ -11501,23 +11501,27 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>ESCRITA FISCAL (Outsourcing)</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Andre Coelho</t>
-        </is>
-      </c>
-      <c r="H219" t="inlineStr"/>
+          <t>Gislaine Lima</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Lorrane Santos</t>
+        </is>
+      </c>
       <c r="I219" t="n">
         <v>0</v>
       </c>
       <c r="J219" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="K219" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="220">
@@ -11548,23 +11552,27 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>ESCRITA FISCAL (Outsourcing)</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Bianca Castro</t>
-        </is>
-      </c>
-      <c r="H220" t="inlineStr"/>
+          <t>Joanna Costa</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Lorrane Santos</t>
+        </is>
+      </c>
       <c r="I220" t="n">
         <v>0</v>
       </c>
       <c r="J220" t="n">
-        <v>207</v>
+        <v>8</v>
       </c>
       <c r="K220" t="n">
-        <v>207</v>
+        <v>8</v>
       </c>
     </row>
     <row r="221">
@@ -11595,23 +11603,27 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>ESCRITA FISCAL (Outsourcing)</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Bruna Costa</t>
-        </is>
-      </c>
-      <c r="H221" t="inlineStr"/>
+          <t>João Oliveira</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>Larice Souza</t>
+        </is>
+      </c>
       <c r="I221" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J221" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K221" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="222">
@@ -11642,23 +11654,27 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>ESCRITA FISCAL (Outsourcing)</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Daniela Silva</t>
-        </is>
-      </c>
-      <c r="H222" t="inlineStr"/>
+          <t>Regiane Santos</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Larice Souza</t>
+        </is>
+      </c>
       <c r="I222" t="n">
         <v>0</v>
       </c>
       <c r="J222" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K222" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="223">
@@ -11689,23 +11705,27 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>ESCRITA FISCAL (Outsourcing)</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Isabelli Afonso</t>
-        </is>
-      </c>
-      <c r="H223" t="inlineStr"/>
+          <t>Yasmim Oliveira</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>Larice Souza</t>
+        </is>
+      </c>
       <c r="I223" t="n">
         <v>0</v>
       </c>
       <c r="J223" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="K223" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
     </row>
     <row r="224">
@@ -11741,7 +11761,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Jurema Damacena - SAC</t>
+          <t>Ana Santana</t>
         </is>
       </c>
       <c r="H224" t="inlineStr"/>
@@ -11749,10 +11769,10 @@
         <v>0</v>
       </c>
       <c r="J224" t="n">
-        <v>1</v>
+        <v>181</v>
       </c>
       <c r="K224" t="n">
-        <v>1</v>
+        <v>181</v>
       </c>
     </row>
     <row r="225">
@@ -11788,7 +11808,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Leticia Queiroz</t>
+          <t>Andre Coelho</t>
         </is>
       </c>
       <c r="H225" t="inlineStr"/>
@@ -11796,10 +11816,10 @@
         <v>0</v>
       </c>
       <c r="J225" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="K225" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
     </row>
     <row r="226">
@@ -11835,7 +11855,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Bianca Castro</t>
         </is>
       </c>
       <c r="H226" t="inlineStr"/>
@@ -11843,10 +11863,10 @@
         <v>0</v>
       </c>
       <c r="J226" t="n">
-        <v>3</v>
+        <v>207</v>
       </c>
       <c r="K226" t="n">
-        <v>3</v>
+        <v>207</v>
       </c>
     </row>
     <row r="227">
@@ -11882,7 +11902,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Victoria Virgens</t>
+          <t>Bruna Costa</t>
         </is>
       </c>
       <c r="H227" t="inlineStr"/>
@@ -11890,10 +11910,10 @@
         <v>0</v>
       </c>
       <c r="J227" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="K227" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
     </row>
     <row r="228">
@@ -11929,7 +11949,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Yasmin Peixoto</t>
+          <t>Daniela Silva</t>
         </is>
       </c>
       <c r="H228" t="inlineStr"/>
@@ -11937,10 +11957,10 @@
         <v>0</v>
       </c>
       <c r="J228" t="n">
-        <v>63</v>
+        <v>1</v>
       </c>
       <c r="K228" t="n">
-        <v>63</v>
+        <v>1</v>
       </c>
     </row>
     <row r="229">
@@ -11971,12 +11991,12 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Andre Coelho</t>
+          <t>Isabelli Afonso</t>
         </is>
       </c>
       <c r="H229" t="inlineStr"/>
@@ -11984,10 +12004,10 @@
         <v>0</v>
       </c>
       <c r="J229" t="n">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="K229" t="n">
-        <v>4</v>
+        <v>29</v>
       </c>
     </row>
     <row r="230">
@@ -12018,12 +12038,12 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Beatriz Rangel</t>
+          <t>Jurema Damacena - SAC</t>
         </is>
       </c>
       <c r="H230" t="inlineStr"/>
@@ -12031,10 +12051,10 @@
         <v>0</v>
       </c>
       <c r="J230" t="n">
-        <v>247</v>
+        <v>1</v>
       </c>
       <c r="K230" t="n">
-        <v>247</v>
+        <v>1</v>
       </c>
     </row>
     <row r="231">
@@ -12065,12 +12085,12 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
+          <t>Leticia Queiroz</t>
         </is>
       </c>
       <c r="H231" t="inlineStr"/>
@@ -12078,10 +12098,10 @@
         <v>0</v>
       </c>
       <c r="J231" t="n">
-        <v>143</v>
+        <v>35</v>
       </c>
       <c r="K231" t="n">
-        <v>143</v>
+        <v>35</v>
       </c>
     </row>
     <row r="232">
@@ -12112,12 +12132,12 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Cristiane Simões</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="H232" t="inlineStr"/>
@@ -12125,10 +12145,10 @@
         <v>0</v>
       </c>
       <c r="J232" t="n">
-        <v>172</v>
+        <v>3</v>
       </c>
       <c r="K232" t="n">
-        <v>172</v>
+        <v>3</v>
       </c>
     </row>
     <row r="233">
@@ -12159,23 +12179,23 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Daniel Oliveira</t>
+          <t>Victoria Virgens</t>
         </is>
       </c>
       <c r="H233" t="inlineStr"/>
       <c r="I233" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J233" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="K233" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="234">
@@ -12206,23 +12226,23 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Diego Lima</t>
+          <t>Yasmin Peixoto</t>
         </is>
       </c>
       <c r="H234" t="inlineStr"/>
       <c r="I234" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J234" t="n">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="K234" t="n">
-        <v>79</v>
+        <v>67</v>
       </c>
     </row>
     <row r="235">
@@ -12258,7 +12278,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Luiz Ferreira</t>
+          <t>Andre Coelho</t>
         </is>
       </c>
       <c r="H235" t="inlineStr"/>
@@ -12266,10 +12286,10 @@
         <v>0</v>
       </c>
       <c r="J235" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K235" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="236">
@@ -12305,7 +12325,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Beatriz Rangel</t>
         </is>
       </c>
       <c r="H236" t="inlineStr"/>
@@ -12313,10 +12333,10 @@
         <v>0</v>
       </c>
       <c r="J236" t="n">
-        <v>83</v>
+        <v>246</v>
       </c>
       <c r="K236" t="n">
-        <v>83</v>
+        <v>246</v>
       </c>
     </row>
     <row r="237">
@@ -12352,18 +12372,18 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Rodrigo Rego</t>
+          <t>Bruno Contieri</t>
         </is>
       </c>
       <c r="H237" t="inlineStr"/>
       <c r="I237" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J237" t="n">
-        <v>172</v>
+        <v>147</v>
       </c>
       <c r="K237" t="n">
-        <v>172</v>
+        <v>147</v>
       </c>
     </row>
     <row r="238">
@@ -12399,18 +12419,18 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Rogerio Egidio</t>
+          <t>Cristiane Simões</t>
         </is>
       </c>
       <c r="H238" t="inlineStr"/>
       <c r="I238" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J238" t="n">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="K238" t="n">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="239">
@@ -12446,12 +12466,12 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Daniel Oliveira</t>
         </is>
       </c>
       <c r="H239" t="inlineStr"/>
       <c r="I239" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J239" t="n">
         <v>31</v>
@@ -12493,7 +12513,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Simone Marques</t>
+          <t>Diego Lima</t>
         </is>
       </c>
       <c r="H240" t="inlineStr"/>
@@ -12501,10 +12521,10 @@
         <v>0</v>
       </c>
       <c r="J240" t="n">
-        <v>105</v>
+        <v>79</v>
       </c>
       <c r="K240" t="n">
-        <v>105</v>
+        <v>79</v>
       </c>
     </row>
     <row r="241">
@@ -12540,7 +12560,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Luiz Ferreira</t>
         </is>
       </c>
       <c r="H241" t="inlineStr"/>
@@ -12548,10 +12568,10 @@
         <v>0</v>
       </c>
       <c r="J241" t="n">
-        <v>99</v>
+        <v>7</v>
       </c>
       <c r="K241" t="n">
-        <v>99</v>
+        <v>7</v>
       </c>
     </row>
     <row r="242">
@@ -12582,23 +12602,23 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="H242" t="inlineStr"/>
       <c r="I242" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J242" t="n">
-        <v>1</v>
+        <v>87</v>
       </c>
       <c r="K242" t="n">
-        <v>1</v>
+        <v>87</v>
       </c>
     </row>
     <row r="243">
@@ -12629,23 +12649,23 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Jurema Damacena - SAC</t>
+          <t>Rodrigo Rego</t>
         </is>
       </c>
       <c r="H243" t="inlineStr"/>
       <c r="I243" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J243" t="n">
-        <v>14</v>
+        <v>176</v>
       </c>
       <c r="K243" t="n">
-        <v>14</v>
+        <v>176</v>
       </c>
     </row>
     <row r="244">
@@ -12671,28 +12691,28 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Jurema Damacena - SAC</t>
+          <t>Rogerio Egidio</t>
         </is>
       </c>
       <c r="H244" t="inlineStr"/>
       <c r="I244" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J244" t="n">
-        <v>1</v>
+        <v>180</v>
       </c>
       <c r="K244" t="n">
-        <v>1</v>
+        <v>180</v>
       </c>
     </row>
     <row r="245">
@@ -12718,28 +12738,28 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>SANTOS - ADM</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Kauany Pereira</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="H245" t="inlineStr"/>
       <c r="I245" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J245" t="n">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="K245" t="n">
-        <v>90</v>
+        <v>33</v>
       </c>
     </row>
     <row r="246">
@@ -12765,32 +12785,28 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>SANTOS - CTB</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Roberto Silva</t>
-        </is>
-      </c>
-      <c r="H246" t="inlineStr">
-        <is>
-          <t>Roberto Silva</t>
-        </is>
-      </c>
+          <t>Simone Marques</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr"/>
       <c r="I246" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J246" t="n">
-        <v>11</v>
+        <v>111</v>
       </c>
       <c r="K246" t="n">
-        <v>11</v>
+        <v>111</v>
       </c>
     </row>
     <row r="247">
@@ -12816,32 +12832,28 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>SANTOS - CTB</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Thaina Rodrigues</t>
-        </is>
-      </c>
-      <c r="H247" t="inlineStr">
-        <is>
-          <t>Roberto Silva</t>
-        </is>
-      </c>
+          <t>Vander Silva</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr"/>
       <c r="I247" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="J247" t="n">
-        <v>3</v>
+        <v>125</v>
       </c>
       <c r="K247" t="n">
-        <v>3</v>
+        <v>125</v>
       </c>
     </row>
     <row r="248">
@@ -12867,32 +12879,28 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>SANTOS - DP</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Bruna Silva</t>
-        </is>
-      </c>
-      <c r="H248" t="inlineStr">
-        <is>
-          <t>Katia Valeria</t>
-        </is>
-      </c>
+          <t>Edimir Santos</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr"/>
       <c r="I248" t="n">
         <v>0</v>
       </c>
       <c r="J248" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="K248" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="249">
@@ -12918,32 +12926,28 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>SANTOS - DP</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Carliane Silva</t>
-        </is>
-      </c>
-      <c r="H249" t="inlineStr">
-        <is>
-          <t>Katia Valeria</t>
-        </is>
-      </c>
+          <t>Jurema Damacena - SAC</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr"/>
       <c r="I249" t="n">
         <v>0</v>
       </c>
       <c r="J249" t="n">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="K249" t="n">
-        <v>74</v>
+        <v>14</v>
       </c>
     </row>
     <row r="250">
@@ -12974,27 +12978,23 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>SANTOS - DP</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Cintia Andrade</t>
-        </is>
-      </c>
-      <c r="H250" t="inlineStr">
-        <is>
-          <t>Katia Valeria</t>
-        </is>
-      </c>
+          <t>Jurema Damacena - SAC</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr"/>
       <c r="I250" t="n">
         <v>0</v>
       </c>
       <c r="J250" t="n">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="K250" t="n">
-        <v>51</v>
+        <v>1</v>
       </c>
     </row>
     <row r="251">
@@ -13025,27 +13025,23 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>SANTOS - DP</t>
+          <t>SANTOS - ADM</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Katia Valeria</t>
-        </is>
-      </c>
-      <c r="H251" t="inlineStr">
-        <is>
-          <t>Katia Valeria</t>
-        </is>
-      </c>
+          <t>Kauany Pereira</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr"/>
       <c r="I251" t="n">
         <v>0</v>
       </c>
       <c r="J251" t="n">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K251" t="n">
-        <v>77</v>
+        <v>90</v>
       </c>
     </row>
     <row r="252">
@@ -13076,27 +13072,27 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>SANTOS - EF</t>
+          <t>SANTOS - CTB</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Jasmina Melo</t>
+          <t>Roberto Silva</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>Lidia Tavares</t>
+          <t>Roberto Silva</t>
         </is>
       </c>
       <c r="I252" t="n">
         <v>0</v>
       </c>
       <c r="J252" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="K252" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="253">
@@ -13127,27 +13123,27 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>SANTOS - EF</t>
+          <t>SANTOS - CTB</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Karen Saadi</t>
+          <t>Thaina Rodrigues</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>Lidia Tavares</t>
+          <t>Roberto Silva</t>
         </is>
       </c>
       <c r="I253" t="n">
         <v>0</v>
       </c>
       <c r="J253" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="K253" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="254">
@@ -13178,27 +13174,27 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>SANTOS - EF</t>
+          <t>SANTOS - DP</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Luckas Andrade</t>
+          <t>Bruna Silva</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>Lidia Tavares</t>
+          <t>Katia Valeria</t>
         </is>
       </c>
       <c r="I254" t="n">
         <v>0</v>
       </c>
       <c r="J254" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K254" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="255">
@@ -13229,27 +13225,27 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>SANTOS - EF</t>
+          <t>SANTOS - DP</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Mirian Rodrigues</t>
+          <t>Carliane Silva</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>Lidia Tavares</t>
+          <t>Katia Valeria</t>
         </is>
       </c>
       <c r="I255" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J255" t="n">
-        <v>27</v>
+        <v>98</v>
       </c>
       <c r="K255" t="n">
-        <v>27</v>
+        <v>98</v>
       </c>
     </row>
     <row r="256">
@@ -13280,22 +13276,328 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
+          <t>SANTOS - DP</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>Cintia Andrade</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>Katia Valeria</t>
+        </is>
+      </c>
+      <c r="I256" t="n">
+        <v>18</v>
+      </c>
+      <c r="J256" t="n">
+        <v>69</v>
+      </c>
+      <c r="K256" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Sexta</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>2026-W23</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>SANTOS - DP</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>Katia Valeria</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>Katia Valeria</t>
+        </is>
+      </c>
+      <c r="I257" t="n">
+        <v>33</v>
+      </c>
+      <c r="J257" t="n">
+        <v>110</v>
+      </c>
+      <c r="K257" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Sexta</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>2026-W23</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>SANTOS - EF</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>Jasmina Melo</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>Lidia Tavares</t>
+        </is>
+      </c>
+      <c r="I258" t="n">
+        <v>1</v>
+      </c>
+      <c r="J258" t="n">
+        <v>25</v>
+      </c>
+      <c r="K258" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Sexta</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>2026-W23</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>SANTOS - EF</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>Karen Saadi</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>Lidia Tavares</t>
+        </is>
+      </c>
+      <c r="I259" t="n">
+        <v>1</v>
+      </c>
+      <c r="J259" t="n">
+        <v>11</v>
+      </c>
+      <c r="K259" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Sexta</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>2026-W23</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>SANTOS - EF</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>Luckas Andrade</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>Lidia Tavares</t>
+        </is>
+      </c>
+      <c r="I260" t="n">
+        <v>2</v>
+      </c>
+      <c r="J260" t="n">
+        <v>18</v>
+      </c>
+      <c r="K260" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Sexta</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>2026-W23</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>SANTOS - EF</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>Mirian Rodrigues</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>Lidia Tavares</t>
+        </is>
+      </c>
+      <c r="I261" t="n">
+        <v>0</v>
+      </c>
+      <c r="J261" t="n">
+        <v>27</v>
+      </c>
+      <c r="K261" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Sexta</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>2026-W23</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
           <t>SANTOS - GC</t>
         </is>
       </c>
-      <c r="G256" t="inlineStr">
+      <c r="G262" t="inlineStr">
         <is>
           <t>Rafaella Massuia</t>
         </is>
       </c>
-      <c r="H256" t="inlineStr"/>
-      <c r="I256" t="n">
+      <c r="H262" t="inlineStr"/>
+      <c r="I262" t="n">
         <v>0</v>
       </c>
-      <c r="J256" t="n">
+      <c r="J262" t="n">
         <v>96</v>
       </c>
-      <c r="K256" t="n">
+      <c r="K262" t="n">
         <v>96</v>
       </c>
     </row>

--- a/data/historico/historico_baixas.xlsx
+++ b/data/historico/historico_baixas.xlsx
@@ -14886,13 +14886,13 @@
         </is>
       </c>
       <c r="I288" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J288" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K288" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="289">
@@ -15898,10 +15898,10 @@
         </is>
       </c>
       <c r="I308" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J308" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K308" t="n">
         <v>27</v>
@@ -16255,7 +16255,7 @@
         </is>
       </c>
       <c r="I315" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J315" t="n">
         <v>0</v>
@@ -16306,10 +16306,10 @@
         </is>
       </c>
       <c r="I316" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J316" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K316" t="n">
         <v>18</v>
@@ -16357,10 +16357,10 @@
         </is>
       </c>
       <c r="I317" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J317" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K317" t="n">
         <v>96</v>
@@ -16459,13 +16459,13 @@
         </is>
       </c>
       <c r="I319" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J319" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K319" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="320">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="I321" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J321" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="K321" t="n">
-        <v>74</v>
+        <v>85</v>
       </c>
     </row>
     <row r="322">
@@ -16612,13 +16612,13 @@
         </is>
       </c>
       <c r="I322" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J322" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K322" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="323">
@@ -16663,13 +16663,13 @@
         </is>
       </c>
       <c r="I323" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J323" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K323" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="324">
@@ -16765,13 +16765,13 @@
         </is>
       </c>
       <c r="I325" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J325" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K325" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="326">
@@ -16816,13 +16816,13 @@
         </is>
       </c>
       <c r="I326" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J326" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K326" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="327">
@@ -16918,13 +16918,13 @@
         </is>
       </c>
       <c r="I328" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J328" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K328" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="329">
@@ -16969,13 +16969,13 @@
         </is>
       </c>
       <c r="I329" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J329" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K329" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
     </row>
     <row r="330">
@@ -17023,10 +17023,10 @@
         <v>0</v>
       </c>
       <c r="J330" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K330" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="331">
@@ -17071,13 +17071,13 @@
         </is>
       </c>
       <c r="I331" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J331" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K331" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
     <row r="332">
@@ -17220,10 +17220,10 @@
       </c>
       <c r="H334" t="inlineStr"/>
       <c r="I334" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J334" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K334" t="n">
         <v>89</v>
@@ -17361,10 +17361,10 @@
       </c>
       <c r="H337" t="inlineStr"/>
       <c r="I337" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J337" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K337" t="n">
         <v>45</v>
@@ -17414,7 +17414,7 @@
         <v>1</v>
       </c>
       <c r="K338" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="339">
@@ -17961,13 +17961,13 @@
         </is>
       </c>
       <c r="I349" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J349" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K349" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="350">
@@ -18114,13 +18114,13 @@
         </is>
       </c>
       <c r="I352" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J352" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K352" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="353">
@@ -18471,13 +18471,13 @@
         </is>
       </c>
       <c r="I359" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J359" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K359" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="360">
@@ -18926,13 +18926,13 @@
         </is>
       </c>
       <c r="I368" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J368" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K368" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="369">
@@ -18977,13 +18977,13 @@
         </is>
       </c>
       <c r="I369" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J369" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K369" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="370">
@@ -19028,10 +19028,10 @@
         </is>
       </c>
       <c r="I370" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J370" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="K370" t="n">
         <v>4</v>
@@ -19385,13 +19385,13 @@
         </is>
       </c>
       <c r="I377" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J377" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K377" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="378">
@@ -19442,7 +19442,7 @@
         <v>0</v>
       </c>
       <c r="K378" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="379">
@@ -19691,13 +19691,13 @@
         </is>
       </c>
       <c r="I383" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J383" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K383" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="384">
@@ -19742,13 +19742,13 @@
         </is>
       </c>
       <c r="I384" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J384" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K384" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="385">
@@ -20299,13 +20299,13 @@
         </is>
       </c>
       <c r="I395" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J395" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K395" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="396">
@@ -20554,13 +20554,13 @@
         </is>
       </c>
       <c r="I400" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J400" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K400" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="401">
@@ -20605,13 +20605,13 @@
         </is>
       </c>
       <c r="I401" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J401" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K401" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="402">
@@ -21268,13 +21268,13 @@
         </is>
       </c>
       <c r="I414" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J414" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K414" t="n">
-        <v>106</v>
+        <v>113</v>
       </c>
     </row>
     <row r="415">
@@ -21727,13 +21727,13 @@
         </is>
       </c>
       <c r="I423" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J423" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K423" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="424">
@@ -21829,13 +21829,13 @@
         </is>
       </c>
       <c r="I425" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J425" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K425" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="426">
@@ -21931,13 +21931,13 @@
         </is>
       </c>
       <c r="I427" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J427" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K427" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="428">
@@ -22033,13 +22033,13 @@
         </is>
       </c>
       <c r="I429" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J429" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K429" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="430">
@@ -22339,13 +22339,13 @@
         </is>
       </c>
       <c r="I435" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J435" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K435" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="436">
@@ -22441,13 +22441,13 @@
         </is>
       </c>
       <c r="I437" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J437" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K437" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="438">
@@ -22492,13 +22492,13 @@
         </is>
       </c>
       <c r="I438" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J438" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K438" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="439">
@@ -22743,13 +22743,13 @@
         </is>
       </c>
       <c r="I443" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J443" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K443" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="444">
@@ -22794,13 +22794,13 @@
         </is>
       </c>
       <c r="I444" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J444" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K444" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="445">
@@ -22896,13 +22896,13 @@
         </is>
       </c>
       <c r="I446" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J446" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K446" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="447">
@@ -23049,13 +23049,13 @@
         </is>
       </c>
       <c r="I449" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J449" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K449" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="450">
@@ -23202,13 +23202,13 @@
         </is>
       </c>
       <c r="I452" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J452" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K452" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="453">
@@ -23253,13 +23253,13 @@
         </is>
       </c>
       <c r="I453" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J453" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K453" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="454">
@@ -23355,13 +23355,13 @@
         </is>
       </c>
       <c r="I455" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J455" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="K455" t="n">
-        <v>59</v>
+        <v>75</v>
       </c>
     </row>
     <row r="456">
@@ -23406,13 +23406,13 @@
         </is>
       </c>
       <c r="I456" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J456" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K456" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="457">
@@ -23508,13 +23508,13 @@
         </is>
       </c>
       <c r="I458" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J458" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K458" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="459">
@@ -23559,13 +23559,13 @@
         </is>
       </c>
       <c r="I459" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J459" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K459" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="460">
@@ -23610,13 +23610,13 @@
         </is>
       </c>
       <c r="I460" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J460" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K460" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="461">
@@ -23661,13 +23661,13 @@
         </is>
       </c>
       <c r="I461" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J461" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K461" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="462">
@@ -23708,13 +23708,13 @@
       </c>
       <c r="H462" t="inlineStr"/>
       <c r="I462" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J462" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K462" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="463">
@@ -23810,13 +23810,13 @@
         </is>
       </c>
       <c r="I464" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J464" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K464" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="465">
@@ -23861,13 +23861,13 @@
         </is>
       </c>
       <c r="I465" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J465" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K465" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="466">
@@ -23912,13 +23912,13 @@
         </is>
       </c>
       <c r="I466" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J466" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K466" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="467">
@@ -23963,13 +23963,13 @@
         </is>
       </c>
       <c r="I467" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J467" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K467" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="468">
@@ -24014,13 +24014,13 @@
         </is>
       </c>
       <c r="I468" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J468" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="K468" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="469">
@@ -24065,7 +24065,7 @@
         </is>
       </c>
       <c r="I469" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J469" t="n">
         <v>14</v>
@@ -24269,13 +24269,13 @@
         </is>
       </c>
       <c r="I473" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J473" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K473" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="474">
@@ -24371,13 +24371,13 @@
         </is>
       </c>
       <c r="I475" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J475" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K475" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
     </row>
     <row r="476">
@@ -24422,13 +24422,13 @@
         </is>
       </c>
       <c r="I476" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J476" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K476" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="477">
@@ -24473,13 +24473,13 @@
         </is>
       </c>
       <c r="I477" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J477" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K477" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="478">
@@ -24575,13 +24575,13 @@
         </is>
       </c>
       <c r="I479" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="J479" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="K479" t="n">
-        <v>64</v>
+        <v>90</v>
       </c>
     </row>
     <row r="480">
@@ -24626,13 +24626,13 @@
         </is>
       </c>
       <c r="I480" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J480" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K480" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="481">
@@ -24677,13 +24677,13 @@
         </is>
       </c>
       <c r="I481" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J481" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K481" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="482">
@@ -24728,13 +24728,13 @@
         </is>
       </c>
       <c r="I482" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J482" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K482" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="483">
@@ -24881,13 +24881,13 @@
         </is>
       </c>
       <c r="I485" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J485" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K485" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="486">
@@ -25138,7 +25138,7 @@
         <v>1</v>
       </c>
       <c r="K490" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="491">
@@ -25183,13 +25183,13 @@
         </is>
       </c>
       <c r="I491" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J491" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K491" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="492">
@@ -25285,13 +25285,13 @@
         </is>
       </c>
       <c r="I493" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J493" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K493" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="494">
@@ -25430,7 +25430,7 @@
       </c>
       <c r="H496" t="inlineStr"/>
       <c r="I496" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J496" t="n">
         <v>9</v>
@@ -25759,10 +25759,10 @@
       </c>
       <c r="H503" t="inlineStr"/>
       <c r="I503" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J503" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K503" t="n">
         <v>47</v>
@@ -25853,10 +25853,10 @@
       </c>
       <c r="H505" t="inlineStr"/>
       <c r="I505" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J505" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K505" t="n">
         <v>9</v>
@@ -26135,10 +26135,10 @@
       </c>
       <c r="H511" t="inlineStr"/>
       <c r="I511" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J511" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K511" t="n">
         <v>80</v>
@@ -26329,7 +26329,7 @@
         <v>3</v>
       </c>
       <c r="K515" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="516">
@@ -26801,13 +26801,13 @@
         </is>
       </c>
       <c r="I525" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J525" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K525" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="526">
@@ -27005,13 +27005,13 @@
         </is>
       </c>
       <c r="I529" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J529" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="K529" t="n">
-        <v>162</v>
+        <v>167</v>
       </c>
     </row>
     <row r="530">
@@ -27107,13 +27107,13 @@
         </is>
       </c>
       <c r="I531" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J531" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K531" t="n">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="532">
@@ -27209,7 +27209,7 @@
         </is>
       </c>
       <c r="I533" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J533" t="n">
         <v>0</v>
@@ -27260,13 +27260,13 @@
         </is>
       </c>
       <c r="I534" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J534" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K534" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="535">
@@ -27311,13 +27311,13 @@
         </is>
       </c>
       <c r="I535" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J535" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K535" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="536">

--- a/data/historico/historico_baixas.xlsx
+++ b/data/historico/historico_baixas.xlsx
@@ -14784,13 +14784,13 @@
         </is>
       </c>
       <c r="I286" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J286" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K286" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="287">
@@ -14835,13 +14835,13 @@
         </is>
       </c>
       <c r="I287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J287" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K287" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="288">
@@ -15039,13 +15039,13 @@
         </is>
       </c>
       <c r="I291" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J291" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K291" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="292">
@@ -15090,13 +15090,13 @@
         </is>
       </c>
       <c r="I292" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J292" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K292" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="293">
@@ -15192,13 +15192,13 @@
         </is>
       </c>
       <c r="I294" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J294" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K294" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="295">
@@ -15643,10 +15643,10 @@
         </is>
       </c>
       <c r="I303" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J303" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K303" t="n">
         <v>89</v>
@@ -15745,13 +15745,13 @@
         </is>
       </c>
       <c r="I305" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J305" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K305" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="306">
@@ -16102,10 +16102,10 @@
         </is>
       </c>
       <c r="I312" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J312" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K312" t="n">
         <v>73</v>
@@ -16153,13 +16153,13 @@
         </is>
       </c>
       <c r="I313" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J313" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K313" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="314">
@@ -16459,13 +16459,13 @@
         </is>
       </c>
       <c r="I319" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J319" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="K319" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="320">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="I321" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="J321" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="K321" t="n">
-        <v>85</v>
+        <v>99</v>
       </c>
     </row>
     <row r="322">
@@ -16663,13 +16663,13 @@
         </is>
       </c>
       <c r="I323" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J323" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K323" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="324">
@@ -16714,13 +16714,13 @@
         </is>
       </c>
       <c r="I324" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J324" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K324" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="325">
@@ -16765,13 +16765,13 @@
         </is>
       </c>
       <c r="I325" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J325" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K325" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="326">
@@ -16816,13 +16816,13 @@
         </is>
       </c>
       <c r="I326" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J326" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K326" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="327">
@@ -16918,13 +16918,13 @@
         </is>
       </c>
       <c r="I328" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J328" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K328" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="329">
@@ -16969,13 +16969,13 @@
         </is>
       </c>
       <c r="I329" t="n">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="J329" t="n">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="K329" t="n">
-        <v>52</v>
+        <v>80</v>
       </c>
     </row>
     <row r="330">
@@ -17020,13 +17020,13 @@
         </is>
       </c>
       <c r="I330" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J330" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K330" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="331">
@@ -17071,13 +17071,13 @@
         </is>
       </c>
       <c r="I331" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J331" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K331" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="332">
@@ -17173,13 +17173,13 @@
         </is>
       </c>
       <c r="I333" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J333" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K333" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="334">
@@ -17220,7 +17220,7 @@
       </c>
       <c r="H334" t="inlineStr"/>
       <c r="I334" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J334" t="n">
         <v>4</v>
@@ -17267,10 +17267,10 @@
       </c>
       <c r="H335" t="inlineStr"/>
       <c r="I335" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J335" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K335" t="n">
         <v>21</v>
@@ -17361,13 +17361,13 @@
       </c>
       <c r="H337" t="inlineStr"/>
       <c r="I337" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J337" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K337" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="338">
@@ -17659,13 +17659,13 @@
         </is>
       </c>
       <c r="I343" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J343" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K343" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="344">
@@ -17863,13 +17863,13 @@
         </is>
       </c>
       <c r="I347" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J347" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K347" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="348">
@@ -17961,13 +17961,13 @@
         </is>
       </c>
       <c r="I349" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J349" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K349" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="350">
@@ -18012,13 +18012,13 @@
         </is>
       </c>
       <c r="I350" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J350" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K350" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="351">
@@ -18926,13 +18926,13 @@
         </is>
       </c>
       <c r="I368" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J368" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K368" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="369">
@@ -18977,13 +18977,13 @@
         </is>
       </c>
       <c r="I369" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J369" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K369" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="370">
@@ -19028,10 +19028,10 @@
         </is>
       </c>
       <c r="I370" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J370" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K370" t="n">
         <v>4</v>
@@ -19589,13 +19589,13 @@
         </is>
       </c>
       <c r="I381" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J381" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K381" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="382">
@@ -19640,13 +19640,13 @@
         </is>
       </c>
       <c r="I382" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J382" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K382" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="383">
@@ -19742,13 +19742,13 @@
         </is>
       </c>
       <c r="I384" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J384" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K384" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="385">
@@ -19793,13 +19793,13 @@
         </is>
       </c>
       <c r="I385" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J385" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K385" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="386">
@@ -20656,13 +20656,13 @@
         </is>
       </c>
       <c r="I402" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J402" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K402" t="n">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="403">
@@ -21319,13 +21319,13 @@
         </is>
       </c>
       <c r="I415" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J415" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K415" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="416">
@@ -21370,13 +21370,13 @@
         </is>
       </c>
       <c r="I416" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J416" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="K416" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
     </row>
     <row r="417">
@@ -21829,13 +21829,13 @@
         </is>
       </c>
       <c r="I425" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J425" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="K425" t="n">
-        <v>94</v>
+        <v>102</v>
       </c>
     </row>
     <row r="426">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="I426" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J426" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K426" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="427">
@@ -22186,10 +22186,10 @@
         </is>
       </c>
       <c r="I432" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J432" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K432" t="n">
         <v>98</v>
@@ -22543,13 +22543,13 @@
         </is>
       </c>
       <c r="I439" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J439" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K439" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="440">
@@ -22641,13 +22641,13 @@
         </is>
       </c>
       <c r="I441" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J441" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="K441" t="n">
-        <v>75</v>
+        <v>92</v>
       </c>
     </row>
     <row r="442">
@@ -22743,13 +22743,13 @@
         </is>
       </c>
       <c r="I443" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J443" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K443" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="444">
@@ -23049,13 +23049,13 @@
         </is>
       </c>
       <c r="I449" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J449" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K449" t="n">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="450">
@@ -23253,13 +23253,13 @@
         </is>
       </c>
       <c r="I453" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J453" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K453" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="454">
@@ -23355,13 +23355,13 @@
         </is>
       </c>
       <c r="I455" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J455" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K455" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="456">
@@ -23457,13 +23457,13 @@
         </is>
       </c>
       <c r="I457" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J457" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K457" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="458">
@@ -23559,13 +23559,13 @@
         </is>
       </c>
       <c r="I459" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J459" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K459" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="460">
@@ -23610,13 +23610,13 @@
         </is>
       </c>
       <c r="I460" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J460" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K460" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="461">
@@ -23661,13 +23661,13 @@
         </is>
       </c>
       <c r="I461" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J461" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K461" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="462">
@@ -23708,13 +23708,13 @@
       </c>
       <c r="H462" t="inlineStr"/>
       <c r="I462" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J462" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K462" t="n">
-        <v>109</v>
+        <v>115</v>
       </c>
     </row>
     <row r="463">
@@ -23810,13 +23810,13 @@
         </is>
       </c>
       <c r="I464" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J464" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="K464" t="n">
-        <v>75</v>
+        <v>84</v>
       </c>
     </row>
     <row r="465">
@@ -23861,13 +23861,13 @@
         </is>
       </c>
       <c r="I465" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J465" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K465" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="466">
@@ -23912,13 +23912,13 @@
         </is>
       </c>
       <c r="I466" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="J466" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="K466" t="n">
-        <v>54</v>
+        <v>65</v>
       </c>
     </row>
     <row r="467">
@@ -24014,13 +24014,13 @@
         </is>
       </c>
       <c r="I468" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J468" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K468" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="469">
@@ -24116,13 +24116,13 @@
         </is>
       </c>
       <c r="I470" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J470" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K470" t="n">
-        <v>58</v>
+        <v>74</v>
       </c>
     </row>
     <row r="471">
@@ -24269,13 +24269,13 @@
         </is>
       </c>
       <c r="I473" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="J473" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="K473" t="n">
-        <v>72</v>
+        <v>86</v>
       </c>
     </row>
     <row r="474">
@@ -24320,13 +24320,13 @@
         </is>
       </c>
       <c r="I474" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J474" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K474" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="475">
@@ -24371,13 +24371,13 @@
         </is>
       </c>
       <c r="I475" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="J475" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="K475" t="n">
-        <v>61</v>
+        <v>75</v>
       </c>
     </row>
     <row r="476">
@@ -24422,13 +24422,13 @@
         </is>
       </c>
       <c r="I476" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J476" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K476" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="477">
@@ -24473,13 +24473,13 @@
         </is>
       </c>
       <c r="I477" t="n">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="J477" t="n">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="K477" t="n">
-        <v>117</v>
+        <v>156</v>
       </c>
     </row>
     <row r="478">
@@ -24524,13 +24524,13 @@
         </is>
       </c>
       <c r="I478" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J478" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K478" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="479">
@@ -24575,13 +24575,13 @@
         </is>
       </c>
       <c r="I479" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="J479" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="K479" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="480">
@@ -24626,13 +24626,13 @@
         </is>
       </c>
       <c r="I480" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J480" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K480" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="481">
@@ -24677,13 +24677,13 @@
         </is>
       </c>
       <c r="I481" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J481" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K481" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="482">
@@ -24830,13 +24830,13 @@
         </is>
       </c>
       <c r="I484" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J484" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K484" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="485">
@@ -24932,13 +24932,13 @@
         </is>
       </c>
       <c r="I486" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J486" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K486" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="487">
@@ -25081,13 +25081,13 @@
         </is>
       </c>
       <c r="I489" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J489" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K489" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="490">
@@ -25132,13 +25132,13 @@
         </is>
       </c>
       <c r="I490" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J490" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K490" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="491">
@@ -25183,13 +25183,13 @@
         </is>
       </c>
       <c r="I491" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="J491" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="K491" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="492">
@@ -25234,13 +25234,13 @@
         </is>
       </c>
       <c r="I492" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J492" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K492" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="493">
@@ -25383,13 +25383,13 @@
       </c>
       <c r="H495" t="inlineStr"/>
       <c r="I495" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J495" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K495" t="n">
-        <v>42</v>
+        <v>59</v>
       </c>
     </row>
     <row r="496">
@@ -25430,13 +25430,13 @@
       </c>
       <c r="H496" t="inlineStr"/>
       <c r="I496" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J496" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K496" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="497">
@@ -25665,10 +25665,10 @@
       </c>
       <c r="H501" t="inlineStr"/>
       <c r="I501" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J501" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K501" t="n">
         <v>29</v>
@@ -25853,13 +25853,13 @@
       </c>
       <c r="H505" t="inlineStr"/>
       <c r="I505" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J505" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K505" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="506">
@@ -26094,7 +26094,7 @@
         <v>0</v>
       </c>
       <c r="K510" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="511">
@@ -26141,7 +26141,7 @@
         <v>13</v>
       </c>
       <c r="K511" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="512">
@@ -26605,13 +26605,13 @@
       </c>
       <c r="H521" t="inlineStr"/>
       <c r="I521" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J521" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="K521" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
     </row>
     <row r="522">
@@ -26652,13 +26652,13 @@
       </c>
       <c r="H522" t="inlineStr"/>
       <c r="I522" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J522" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K522" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="523">
@@ -26699,13 +26699,13 @@
       </c>
       <c r="H523" t="inlineStr"/>
       <c r="I523" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J523" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K523" t="n">
-        <v>104</v>
+        <v>120</v>
       </c>
     </row>
     <row r="524">
@@ -26801,13 +26801,13 @@
         </is>
       </c>
       <c r="I525" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J525" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K525" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="526">
@@ -26852,13 +26852,13 @@
         </is>
       </c>
       <c r="I526" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J526" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K526" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="527">
@@ -27005,13 +27005,13 @@
         </is>
       </c>
       <c r="I529" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J529" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="K529" t="n">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="530">
@@ -27056,13 +27056,13 @@
         </is>
       </c>
       <c r="I530" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J530" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K530" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="531">
@@ -27107,13 +27107,13 @@
         </is>
       </c>
       <c r="I531" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="J531" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K531" t="n">
-        <v>192</v>
+        <v>202</v>
       </c>
     </row>
     <row r="532">
@@ -27209,13 +27209,13 @@
         </is>
       </c>
       <c r="I533" t="n">
+        <v>2</v>
+      </c>
+      <c r="J533" t="n">
         <v>1</v>
       </c>
-      <c r="J533" t="n">
-        <v>0</v>
-      </c>
       <c r="K533" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="534">
@@ -27260,13 +27260,13 @@
         </is>
       </c>
       <c r="I534" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J534" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K534" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="535">
@@ -27311,13 +27311,13 @@
         </is>
       </c>
       <c r="I535" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J535" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K535" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="536">

--- a/data/historico/historico_baixas.xlsx
+++ b/data/historico/historico_baixas.xlsx
@@ -15643,10 +15643,10 @@
         </is>
       </c>
       <c r="I303" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J303" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K303" t="n">
         <v>89</v>
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="I321" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J321" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K321" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="322">
@@ -16765,13 +16765,13 @@
         </is>
       </c>
       <c r="I325" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J325" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K325" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="326">
@@ -17173,13 +17173,13 @@
         </is>
       </c>
       <c r="I333" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J333" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K333" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="334">
@@ -23861,13 +23861,13 @@
         </is>
       </c>
       <c r="I465" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J465" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K465" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="466">
@@ -24269,13 +24269,13 @@
         </is>
       </c>
       <c r="I473" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J473" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K473" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="474">
@@ -27260,13 +27260,13 @@
         </is>
       </c>
       <c r="I534" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J534" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K534" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="535">

--- a/data/historico/historico_baixas.xlsx
+++ b/data/historico/historico_baixas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K536"/>
+  <dimension ref="A1:K537"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="I270" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J270" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K270" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="271">
@@ -14451,13 +14451,13 @@
         </is>
       </c>
       <c r="I279" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J279" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K279" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="280">
@@ -14784,13 +14784,13 @@
         </is>
       </c>
       <c r="I286" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J286" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K286" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="287">
@@ -14886,13 +14886,13 @@
         </is>
       </c>
       <c r="I288" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J288" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K288" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="289">
@@ -15090,13 +15090,13 @@
         </is>
       </c>
       <c r="I292" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J292" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K292" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="293">
@@ -15294,13 +15294,13 @@
         </is>
       </c>
       <c r="I296" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J296" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K296" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="297">
@@ -15345,13 +15345,13 @@
         </is>
       </c>
       <c r="I297" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J297" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K297" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="298">
@@ -15498,13 +15498,13 @@
         </is>
       </c>
       <c r="I300" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J300" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K300" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="301">
@@ -15549,13 +15549,13 @@
         </is>
       </c>
       <c r="I301" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J301" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K301" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="302">
@@ -15586,19 +15586,27 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>RJ - DP</t>
-        </is>
-      </c>
-      <c r="G302" t="inlineStr"/>
-      <c r="H302" t="inlineStr"/>
+          <t>RJ - CTB</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>Walace Gonçalves</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>Walace Gonçalves|Maicon Costa</t>
+        </is>
+      </c>
       <c r="I302" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J302" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K302" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="303">
@@ -15632,24 +15640,16 @@
           <t>RJ - DP</t>
         </is>
       </c>
-      <c r="G303" t="inlineStr">
-        <is>
-          <t>Barbara Mello</t>
-        </is>
-      </c>
-      <c r="H303" t="inlineStr">
-        <is>
-          <t>Karina Oliveira|Liliane Costa</t>
-        </is>
-      </c>
+      <c r="G303" t="inlineStr"/>
+      <c r="H303" t="inlineStr"/>
       <c r="I303" t="n">
+        <v>0</v>
+      </c>
+      <c r="J303" t="n">
+        <v>0</v>
+      </c>
+      <c r="K303" t="n">
         <v>3</v>
-      </c>
-      <c r="J303" t="n">
-        <v>3</v>
-      </c>
-      <c r="K303" t="n">
-        <v>89</v>
       </c>
     </row>
     <row r="304">
@@ -15685,7 +15685,7 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Debora Nunes</t>
+          <t>Barbara Mello</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -15694,13 +15694,13 @@
         </is>
       </c>
       <c r="I304" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J304" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K304" t="n">
-        <v>74</v>
+        <v>89</v>
       </c>
     </row>
     <row r="305">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Graziele Almeida</t>
+          <t>Debora Nunes</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -15745,13 +15745,13 @@
         </is>
       </c>
       <c r="I305" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J305" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K305" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="306">
@@ -15787,7 +15787,7 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Janiele Ferreira</t>
+          <t>Graziele Almeida</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -15796,13 +15796,13 @@
         </is>
       </c>
       <c r="I306" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J306" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K306" t="n">
-        <v>20</v>
+        <v>75</v>
       </c>
     </row>
     <row r="307">
@@ -15838,7 +15838,7 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Jefferson Barros</t>
+          <t>Janiele Ferreira</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -15853,7 +15853,7 @@
         <v>0</v>
       </c>
       <c r="K307" t="n">
-        <v>89</v>
+        <v>20</v>
       </c>
     </row>
     <row r="308">
@@ -15889,7 +15889,7 @@
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Karina Oliveira</t>
+          <t>Jefferson Barros</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -15898,13 +15898,13 @@
         </is>
       </c>
       <c r="I308" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J308" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K308" t="n">
-        <v>27</v>
+        <v>89</v>
       </c>
     </row>
     <row r="309">
@@ -15940,7 +15940,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Leonardo Assunção</t>
+          <t>Karina Oliveira</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -15949,13 +15949,13 @@
         </is>
       </c>
       <c r="I309" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J309" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K309" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="310">
@@ -15991,7 +15991,7 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Liliane Costa</t>
+          <t>Leonardo Assunção</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -16006,7 +16006,7 @@
         <v>0</v>
       </c>
       <c r="K310" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="311">
@@ -16042,7 +16042,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Luciene Pimenta</t>
+          <t>Liliane Costa</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -16057,7 +16057,7 @@
         <v>0</v>
       </c>
       <c r="K311" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="312">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Lucirene Souza</t>
+          <t>Luciene Pimenta</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -16102,13 +16102,13 @@
         </is>
       </c>
       <c r="I312" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J312" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K312" t="n">
-        <v>73</v>
+        <v>10</v>
       </c>
     </row>
     <row r="313">
@@ -16144,7 +16144,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Marlon Silva</t>
+          <t>Lucirene Souza</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -16153,13 +16153,13 @@
         </is>
       </c>
       <c r="I313" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J313" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K313" t="n">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="314">
@@ -16195,7 +16195,7 @@
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Monique Britto</t>
+          <t>Marlon Silva</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -16204,13 +16204,13 @@
         </is>
       </c>
       <c r="I314" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J314" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K314" t="n">
-        <v>64</v>
+        <v>109</v>
       </c>
     </row>
     <row r="315">
@@ -16246,7 +16246,7 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Romulo Ferreira</t>
+          <t>Monique Britto</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -16258,10 +16258,10 @@
         <v>1</v>
       </c>
       <c r="J315" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K315" t="n">
-        <v>304</v>
+        <v>65</v>
       </c>
     </row>
     <row r="316">
@@ -16297,7 +16297,7 @@
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>Rosilene Silva</t>
+          <t>Romulo Ferreira</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -16309,10 +16309,10 @@
         <v>1</v>
       </c>
       <c r="J316" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K316" t="n">
-        <v>18</v>
+        <v>304</v>
       </c>
     </row>
     <row r="317">
@@ -16348,7 +16348,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>Thais Santos</t>
+          <t>Rosilene Silva</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -16357,13 +16357,13 @@
         </is>
       </c>
       <c r="I317" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J317" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K317" t="n">
-        <v>96</v>
+        <v>18</v>
       </c>
     </row>
     <row r="318">
@@ -16399,7 +16399,7 @@
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>Vitoria Tavares</t>
+          <t>Thais Santos</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -16408,13 +16408,13 @@
         </is>
       </c>
       <c r="I318" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J318" t="n">
         <v>2</v>
       </c>
       <c r="K318" t="n">
-        <v>154</v>
+        <v>96</v>
       </c>
     </row>
     <row r="319">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>Viviane Moura</t>
+          <t>Vitoria Tavares</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -16459,13 +16459,13 @@
         </is>
       </c>
       <c r="I319" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J319" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="K319" t="n">
-        <v>70</v>
+        <v>154</v>
       </c>
     </row>
     <row r="320">
@@ -16501,7 +16501,7 @@
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>Yasmin Lopes</t>
+          <t>Viviane Moura</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -16510,13 +16510,13 @@
         </is>
       </c>
       <c r="I320" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J320" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K320" t="n">
-        <v>85</v>
+        <v>74</v>
       </c>
     </row>
     <row r="321">
@@ -16547,27 +16547,27 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>RJ - EF</t>
+          <t>RJ - DP</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>Altamir Nogueira</t>
+          <t>Yasmin Lopes</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>Julio Santos|Jessica Benjamin</t>
+          <t>Karina Oliveira|Liliane Costa</t>
         </is>
       </c>
       <c r="I321" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="J321" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="K321" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
     </row>
     <row r="322">
@@ -16603,7 +16603,7 @@
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Beatriz Oliveira</t>
+          <t>Altamir Nogueira</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
@@ -16612,13 +16612,13 @@
         </is>
       </c>
       <c r="I322" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="J322" t="n">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="K322" t="n">
-        <v>27</v>
+        <v>100</v>
       </c>
     </row>
     <row r="323">
@@ -16654,7 +16654,7 @@
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>Glaucia Santos</t>
+          <t>Beatriz Oliveira</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -16663,13 +16663,13 @@
         </is>
       </c>
       <c r="I323" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J323" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K323" t="n">
-        <v>51</v>
+        <v>27</v>
       </c>
     </row>
     <row r="324">
@@ -16705,7 +16705,7 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>Isabela Barbosa</t>
+          <t>Glaucia Santos</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -16714,13 +16714,13 @@
         </is>
       </c>
       <c r="I324" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J324" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K324" t="n">
-        <v>28</v>
+        <v>51</v>
       </c>
     </row>
     <row r="325">
@@ -16756,7 +16756,7 @@
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>Jessica Benjamin</t>
+          <t>Isabela Barbosa</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
@@ -16765,13 +16765,13 @@
         </is>
       </c>
       <c r="I325" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J325" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="K325" t="n">
-        <v>63</v>
+        <v>33</v>
       </c>
     </row>
     <row r="326">
@@ -16807,7 +16807,7 @@
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>Juliana Perfeito</t>
+          <t>Jessica Benjamin</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
@@ -16816,13 +16816,13 @@
         </is>
       </c>
       <c r="I326" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J326" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K326" t="n">
-        <v>28</v>
+        <v>64</v>
       </c>
     </row>
     <row r="327">
@@ -16858,7 +16858,7 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>Julio Santos</t>
+          <t>Juliana Perfeito</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -16867,13 +16867,13 @@
         </is>
       </c>
       <c r="I327" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J327" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K327" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="328">
@@ -16909,7 +16909,7 @@
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>Lais Catrine EF</t>
+          <t>Julio Santos</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -16918,13 +16918,13 @@
         </is>
       </c>
       <c r="I328" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J328" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K328" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
     </row>
     <row r="329">
@@ -16960,7 +16960,7 @@
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>Luana Meneses</t>
+          <t>Lais Catrine EF</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -16969,13 +16969,13 @@
         </is>
       </c>
       <c r="I329" t="n">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="J329" t="n">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="K329" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
     </row>
     <row r="330">
@@ -17011,7 +17011,7 @@
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>Otacilia Ferreira</t>
+          <t>Luana Meneses</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -17020,13 +17020,13 @@
         </is>
       </c>
       <c r="I330" t="n">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="J330" t="n">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="K330" t="n">
-        <v>26</v>
+        <v>81</v>
       </c>
     </row>
     <row r="331">
@@ -17062,7 +17062,7 @@
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>Renata Paixão</t>
+          <t>Otacilia Ferreira</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
@@ -17071,13 +17071,13 @@
         </is>
       </c>
       <c r="I331" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J331" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K331" t="n">
-        <v>89</v>
+        <v>25</v>
       </c>
     </row>
     <row r="332">
@@ -17113,7 +17113,7 @@
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>Thamara Jordes</t>
+          <t>Renata Paixão</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
@@ -17122,13 +17122,13 @@
         </is>
       </c>
       <c r="I332" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J332" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K332" t="n">
-        <v>43</v>
+        <v>86</v>
       </c>
     </row>
     <row r="333">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>Wellington Oliveira</t>
+          <t>Thamara Jordes</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -17173,13 +17173,13 @@
         </is>
       </c>
       <c r="I333" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J333" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K333" t="n">
-        <v>82</v>
+        <v>43</v>
       </c>
     </row>
     <row r="334">
@@ -17210,23 +17210,27 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>RJ - GC</t>
+          <t>RJ - EF</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>Bruno Mota</t>
-        </is>
-      </c>
-      <c r="H334" t="inlineStr"/>
+          <t>Wellington Oliveira</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>Julio Santos|Jessica Benjamin</t>
+        </is>
+      </c>
       <c r="I334" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J334" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="K334" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="335">
@@ -17262,18 +17266,18 @@
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>Cavalcante Peres</t>
+          <t>Bruno Mota</t>
         </is>
       </c>
       <c r="H335" t="inlineStr"/>
       <c r="I335" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J335" t="n">
         <v>4</v>
       </c>
       <c r="K335" t="n">
-        <v>21</v>
+        <v>89</v>
       </c>
     </row>
     <row r="336">
@@ -17309,7 +17313,7 @@
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>Tiago Rodrigues</t>
+          <t>Cavalcante Peres</t>
         </is>
       </c>
       <c r="H336" t="inlineStr"/>
@@ -17317,10 +17321,10 @@
         <v>0</v>
       </c>
       <c r="J336" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K336" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="337">
@@ -17351,23 +17355,23 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>RJ - GC ADMINISTRATIVO</t>
+          <t>RJ - GC</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>Amanda Mesquita</t>
+          <t>Tiago Rodrigues</t>
         </is>
       </c>
       <c r="H337" t="inlineStr"/>
       <c r="I337" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J337" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K337" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="338">
@@ -17403,18 +17407,18 @@
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>Lohany Martins</t>
+          <t>Amanda Mesquita</t>
         </is>
       </c>
       <c r="H338" t="inlineStr"/>
       <c r="I338" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J338" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K338" t="n">
-        <v>197</v>
+        <v>48</v>
       </c>
     </row>
     <row r="339">
@@ -17445,12 +17449,12 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>S.A.C</t>
+          <t>RJ - GC ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>Milena Campos - SAC</t>
+          <t>Lohany Martins</t>
         </is>
       </c>
       <c r="H339" t="inlineStr"/>
@@ -17458,10 +17462,10 @@
         <v>0</v>
       </c>
       <c r="J339" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K339" t="n">
-        <v>1</v>
+        <v>197</v>
       </c>
     </row>
     <row r="340">
@@ -17487,24 +17491,20 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>CONTABILIDADE (Outsourcing)</t>
+          <t>S.A.C</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Aline Petrini</t>
-        </is>
-      </c>
-      <c r="H340" t="inlineStr">
-        <is>
-          <t>Fernanda Araujo</t>
-        </is>
-      </c>
+          <t>Milena Campos - SAC</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr"/>
       <c r="I340" t="n">
         <v>0</v>
       </c>
@@ -17548,12 +17548,12 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>Daniele Leite</t>
+          <t>Aline Petrini</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="I341" t="n">
@@ -17599,12 +17599,12 @@
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>Diogo Calazans</t>
+          <t>Daniele Leite</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I342" t="n">
@@ -17650,22 +17650,22 @@
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>Jaqueline Sousa</t>
+          <t>Diogo Calazans</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>Lucas Fischer</t>
+          <t>Karina Santos</t>
         </is>
       </c>
       <c r="I343" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J343" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K343" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="344">
@@ -17701,22 +17701,22 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>Patricia Borges</t>
+          <t>Jaqueline Sousa</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Lucas Fischer</t>
         </is>
       </c>
       <c r="I344" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J344" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K344" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="345">
@@ -17752,12 +17752,12 @@
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>Rejane Coelho</t>
+          <t>Patricia Borges</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I345" t="n">
@@ -17767,7 +17767,7 @@
         <v>0</v>
       </c>
       <c r="K345" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="346">
@@ -17803,7 +17803,7 @@
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>Thiago Ceconelli</t>
+          <t>Rejane Coelho</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
@@ -17815,10 +17815,10 @@
         <v>0</v>
       </c>
       <c r="J346" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K346" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="347">
@@ -17849,27 +17849,27 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL HOLDING</t>
+          <t>CONTABILIDADE (Outsourcing)</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>Ana Flavia Silva</t>
+          <t>Thiago Ceconelli</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Karina Santos</t>
         </is>
       </c>
       <c r="I347" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J347" t="n">
+        <v>1</v>
+      </c>
+      <c r="K347" t="n">
         <v>3</v>
-      </c>
-      <c r="K347" t="n">
-        <v>15</v>
       </c>
     </row>
     <row r="348">
@@ -17905,18 +17905,22 @@
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>Daniele Faria</t>
-        </is>
-      </c>
-      <c r="H348" t="inlineStr"/>
+          <t>Ana Flavia Silva</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>Tatiana Linardi</t>
+        </is>
+      </c>
       <c r="I348" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J348" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K348" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="349">
@@ -17952,22 +17956,18 @@
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>Vitor de Souza</t>
-        </is>
-      </c>
-      <c r="H349" t="inlineStr">
-        <is>
-          <t>Tatiana Linardi</t>
-        </is>
-      </c>
+          <t>Daniele Faria</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr"/>
       <c r="I349" t="n">
+        <v>0</v>
+      </c>
+      <c r="J349" t="n">
         <v>2</v>
       </c>
-      <c r="J349" t="n">
-        <v>4</v>
-      </c>
       <c r="K349" t="n">
-        <v>106</v>
+        <v>2</v>
       </c>
     </row>
     <row r="350">
@@ -18003,7 +18003,7 @@
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>Vitoria Regina</t>
+          <t>Vitor de Souza</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
@@ -18012,13 +18012,13 @@
         </is>
       </c>
       <c r="I350" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J350" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K350" t="n">
-        <v>58</v>
+        <v>107</v>
       </c>
     </row>
     <row r="351">
@@ -18049,27 +18049,27 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL INDUSTRIA</t>
+          <t>CTB - CONTÁBIL HOLDING</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>Adriano Barros</t>
+          <t>Vitoria Regina</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>Erika Santana|Isabella Nascimento</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="I351" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J351" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K351" t="n">
-        <v>1</v>
+        <v>58</v>
       </c>
     </row>
     <row r="352">
@@ -18105,7 +18105,7 @@
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>Bianca Silva</t>
+          <t>Adriano Barros</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
@@ -18114,13 +18114,13 @@
         </is>
       </c>
       <c r="I352" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J352" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K352" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="353">
@@ -18156,7 +18156,7 @@
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>Emylle Souza</t>
+          <t>Bianca Silva</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
@@ -18165,13 +18165,13 @@
         </is>
       </c>
       <c r="I353" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J353" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K353" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="354">
@@ -18207,7 +18207,7 @@
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>Fatima Rocha</t>
+          <t>Emylle Souza</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
@@ -18219,10 +18219,10 @@
         <v>0</v>
       </c>
       <c r="J354" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K354" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="355">
@@ -18258,7 +18258,7 @@
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>Gabriel Correia</t>
+          <t>Fatima Rocha</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
@@ -18270,7 +18270,7 @@
         <v>0</v>
       </c>
       <c r="J355" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K355" t="n">
         <v>4</v>
@@ -18309,7 +18309,7 @@
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>Isabella Nascimento</t>
+          <t>Gabriel Correia</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
@@ -18324,7 +18324,7 @@
         <v>0</v>
       </c>
       <c r="K356" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="357">
@@ -18360,7 +18360,7 @@
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>Laisa Rocha</t>
+          <t>Isabella Nascimento</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
@@ -18411,7 +18411,7 @@
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>Lucas Alves</t>
+          <t>Laisa Rocha</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
@@ -18423,10 +18423,10 @@
         <v>0</v>
       </c>
       <c r="J358" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K358" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="359">
@@ -18462,7 +18462,7 @@
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>Luciana Silva</t>
+          <t>Lucas Alves</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
@@ -18471,13 +18471,13 @@
         </is>
       </c>
       <c r="I359" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J359" t="n">
         <v>1</v>
       </c>
       <c r="K359" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
     </row>
     <row r="360">
@@ -18513,18 +18513,22 @@
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>Luiz Ferreira</t>
-        </is>
-      </c>
-      <c r="H360" t="inlineStr"/>
+          <t>Luciana Silva</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>Erika Santana|Isabella Nascimento</t>
+        </is>
+      </c>
       <c r="I360" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J360" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K360" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
     </row>
     <row r="361">
@@ -18560,22 +18564,18 @@
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>Marcus Oliveira</t>
-        </is>
-      </c>
-      <c r="H361" t="inlineStr">
-        <is>
-          <t>Erika Santana|Isabella Nascimento</t>
-        </is>
-      </c>
+          <t>Luiz Ferreira</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr"/>
       <c r="I361" t="n">
         <v>0</v>
       </c>
       <c r="J361" t="n">
+        <v>0</v>
+      </c>
+      <c r="K361" t="n">
         <v>4</v>
-      </c>
-      <c r="K361" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="362">
@@ -18611,7 +18611,7 @@
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>Mariana Pires</t>
+          <t>Marcus Oliveira</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
@@ -18623,10 +18623,10 @@
         <v>0</v>
       </c>
       <c r="J362" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K362" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="363">
@@ -18662,7 +18662,7 @@
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>Mateus Miranda</t>
+          <t>Mariana Pires</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
@@ -18677,7 +18677,7 @@
         <v>0</v>
       </c>
       <c r="K363" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="364">
@@ -18713,7 +18713,7 @@
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>Mirian Lima</t>
+          <t>Mateus Miranda</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
@@ -18725,7 +18725,7 @@
         <v>0</v>
       </c>
       <c r="J364" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K364" t="n">
         <v>3</v>
@@ -18764,7 +18764,7 @@
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>Nathalia Lourenco</t>
+          <t>Mirian Lima</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
@@ -18776,10 +18776,10 @@
         <v>0</v>
       </c>
       <c r="J365" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K365" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="366">
@@ -18815,7 +18815,7 @@
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>Nicolas Dias</t>
+          <t>Nathalia Lourenco</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
@@ -18827,10 +18827,10 @@
         <v>0</v>
       </c>
       <c r="J366" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K366" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="367">
@@ -18866,7 +18866,7 @@
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>Rodrigo Nunes</t>
+          <t>Nicolas Dias</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
@@ -18875,13 +18875,13 @@
         </is>
       </c>
       <c r="I367" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J367" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K367" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="368">
@@ -18912,27 +18912,27 @@
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>Aline Petrini</t>
+          <t>Rodrigo Nunes</t>
         </is>
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Erika Santana|Isabella Nascimento</t>
         </is>
       </c>
       <c r="I368" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J368" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K368" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="369">
@@ -18968,22 +18968,22 @@
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>Ana Barbosa</t>
+          <t>Aline Petrini</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="I369" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J369" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K369" t="n">
-        <v>43</v>
+        <v>17</v>
       </c>
     </row>
     <row r="370">
@@ -19019,7 +19019,7 @@
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>Daniele Leite</t>
+          <t>Ana Barbosa</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
@@ -19028,13 +19028,13 @@
         </is>
       </c>
       <c r="I370" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J370" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="K370" t="n">
-        <v>4</v>
+        <v>43</v>
       </c>
     </row>
     <row r="371">
@@ -19070,22 +19070,22 @@
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>Danielle Silva</t>
+          <t>Daniele Leite</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I371" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J371" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="K371" t="n">
-        <v>61</v>
+        <v>4</v>
       </c>
     </row>
     <row r="372">
@@ -19121,7 +19121,7 @@
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>Danilo Oliveira</t>
+          <t>Danielle Silva</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
@@ -19133,10 +19133,10 @@
         <v>0</v>
       </c>
       <c r="J372" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K372" t="n">
-        <v>18</v>
+        <v>61</v>
       </c>
     </row>
     <row r="373">
@@ -19172,12 +19172,12 @@
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>Debora Silva</t>
+          <t>Danilo Oliveira</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Karina Santos</t>
         </is>
       </c>
       <c r="I373" t="n">
@@ -19187,7 +19187,7 @@
         <v>0</v>
       </c>
       <c r="K373" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="374">
@@ -19223,12 +19223,12 @@
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>Diogo Calazans</t>
+          <t>Debora Silva</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="I374" t="n">
@@ -19238,7 +19238,7 @@
         <v>0</v>
       </c>
       <c r="K374" t="n">
-        <v>76</v>
+        <v>17</v>
       </c>
     </row>
     <row r="375">
@@ -19274,12 +19274,12 @@
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>Eduardo Cruz</t>
+          <t>Diogo Calazans</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Karina Santos</t>
         </is>
       </c>
       <c r="I375" t="n">
@@ -19289,7 +19289,7 @@
         <v>0</v>
       </c>
       <c r="K375" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="376">
@@ -19325,22 +19325,22 @@
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>Eveny Silva</t>
+          <t>Eduardo Cruz</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="I376" t="n">
         <v>0</v>
       </c>
       <c r="J376" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K376" t="n">
-        <v>27</v>
+        <v>75</v>
       </c>
     </row>
     <row r="377">
@@ -19376,22 +19376,22 @@
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>Everton Moura</t>
+          <t>Eveny Silva</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Karina Santos</t>
         </is>
       </c>
       <c r="I377" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J377" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K377" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="378">
@@ -19427,22 +19427,22 @@
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>Guilherme Dantas</t>
+          <t>Everton Moura</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="I378" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J378" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K378" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="379">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>Isabela Lemos</t>
+          <t>Guilherme Dantas</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I379" t="n">
@@ -19493,7 +19493,7 @@
         <v>0</v>
       </c>
       <c r="K379" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="380">
@@ -19529,12 +19529,12 @@
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>Jackson Silva</t>
+          <t>Isabela Lemos</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="I380" t="n">
@@ -19544,7 +19544,7 @@
         <v>0</v>
       </c>
       <c r="K380" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="381">
@@ -19580,22 +19580,22 @@
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>Jaqueline Sousa</t>
+          <t>Jackson Silva</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>Lucas Fischer</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I381" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J381" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K381" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="382">
@@ -19631,7 +19631,7 @@
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>Leticia Medeiros</t>
+          <t>Jaqueline Sousa</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
@@ -19640,13 +19640,13 @@
         </is>
       </c>
       <c r="I382" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J382" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K382" t="n">
-        <v>54</v>
+        <v>16</v>
       </c>
     </row>
     <row r="383">
@@ -19682,22 +19682,22 @@
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>Monica Medeiros</t>
+          <t>Leticia Medeiros</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Lucas Fischer</t>
         </is>
       </c>
       <c r="I383" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J383" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K383" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
     </row>
     <row r="384">
@@ -19733,22 +19733,22 @@
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>Naiara Dutra</t>
+          <t>Monica Medeiros</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>Lucas Fischer</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I384" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J384" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K384" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
     </row>
     <row r="385">
@@ -19784,22 +19784,22 @@
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>Patricia Borges</t>
+          <t>Naiara Dutra</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Lucas Fischer</t>
         </is>
       </c>
       <c r="I385" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J385" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K385" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
     </row>
     <row r="386">
@@ -19835,22 +19835,22 @@
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>Paulo Silva</t>
+          <t>Patricia Borges</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I386" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J386" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K386" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
     </row>
     <row r="387">
@@ -19886,22 +19886,22 @@
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>Rachel Lima</t>
+          <t>Paulo Silva</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="I387" t="n">
         <v>0</v>
       </c>
       <c r="J387" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K387" t="n">
-        <v>29</v>
+        <v>56</v>
       </c>
     </row>
     <row r="388">
@@ -19937,7 +19937,7 @@
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>Raiane Barbosa</t>
+          <t>Rachel Lima</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
@@ -19949,10 +19949,10 @@
         <v>0</v>
       </c>
       <c r="J388" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K388" t="n">
-        <v>55</v>
+        <v>29</v>
       </c>
     </row>
     <row r="389">
@@ -19988,22 +19988,22 @@
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>Rejane Coelho</t>
+          <t>Raiane Barbosa</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I389" t="n">
         <v>0</v>
       </c>
       <c r="J389" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K389" t="n">
-        <v>1</v>
+        <v>55</v>
       </c>
     </row>
     <row r="390">
@@ -20039,12 +20039,12 @@
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>Renata Alves - CTV</t>
+          <t>Rejane Coelho</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>Lucas Fischer</t>
+          <t>Karina Santos</t>
         </is>
       </c>
       <c r="I390" t="n">
@@ -20054,7 +20054,7 @@
         <v>0</v>
       </c>
       <c r="K390" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="391">
@@ -20090,10 +20090,14 @@
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>Renata Cavalheiro</t>
-        </is>
-      </c>
-      <c r="H391" t="inlineStr"/>
+          <t>Renata Alves - CTV</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>Lucas Fischer</t>
+        </is>
+      </c>
       <c r="I391" t="n">
         <v>0</v>
       </c>
@@ -20101,7 +20105,7 @@
         <v>0</v>
       </c>
       <c r="K391" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="392">
@@ -20137,14 +20141,10 @@
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>Ryan Godinho</t>
-        </is>
-      </c>
-      <c r="H392" t="inlineStr">
-        <is>
-          <t>Karina Santos</t>
-        </is>
-      </c>
+          <t>Renata Cavalheiro</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr"/>
       <c r="I392" t="n">
         <v>0</v>
       </c>
@@ -20152,7 +20152,7 @@
         <v>0</v>
       </c>
       <c r="K392" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
     </row>
     <row r="393">
@@ -20188,12 +20188,12 @@
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>Vitor Domingues</t>
+          <t>Ryan Godinho</t>
         </is>
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Karina Santos</t>
         </is>
       </c>
       <c r="I393" t="n">
@@ -20203,7 +20203,7 @@
         <v>0</v>
       </c>
       <c r="K393" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="394">
@@ -20234,27 +20234,27 @@
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO PESSOAL (Outsourcing)</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>Bruna Santana</t>
+          <t>Vitor Domingues</t>
         </is>
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="I394" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="J394" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="K394" t="n">
-        <v>3</v>
+        <v>65</v>
       </c>
     </row>
     <row r="395">
@@ -20290,7 +20290,7 @@
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>Camila Oliveira</t>
+          <t>Bruna Santana</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
@@ -20299,13 +20299,13 @@
         </is>
       </c>
       <c r="I395" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J395" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K395" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="396">
@@ -20341,22 +20341,22 @@
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>Elaine Assis</t>
+          <t>Camila Oliveira</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I396" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J396" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K396" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="397">
@@ -20392,12 +20392,12 @@
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>Fabiane Branco</t>
+          <t>Elaine Assis</t>
         </is>
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I397" t="n">
@@ -20407,7 +20407,7 @@
         <v>0</v>
       </c>
       <c r="K397" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="398">
@@ -20443,22 +20443,22 @@
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>Jonas Nunes</t>
+          <t>Fabiane Branco</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I398" t="n">
         <v>0</v>
       </c>
       <c r="J398" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K398" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="399">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>DEPARTAMENTO PESSOAL (Outsourcing)</t>
         </is>
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>Bruna Santana</t>
+          <t>Jonas Nunes</t>
         </is>
       </c>
       <c r="H399" t="inlineStr">
@@ -20506,10 +20506,10 @@
         <v>0</v>
       </c>
       <c r="J399" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K399" t="n">
-        <v>99</v>
+        <v>15</v>
       </c>
     </row>
     <row r="400">
@@ -20545,7 +20545,7 @@
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>Camila Oliveira</t>
+          <t>Bruna Santana</t>
         </is>
       </c>
       <c r="H400" t="inlineStr">
@@ -20554,13 +20554,13 @@
         </is>
       </c>
       <c r="I400" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J400" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K400" t="n">
-        <v>31</v>
+        <v>99</v>
       </c>
     </row>
     <row r="401">
@@ -20596,22 +20596,22 @@
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>Daniel Moraes</t>
+          <t>Camila Oliveira</t>
         </is>
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I401" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J401" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K401" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
     </row>
     <row r="402">
@@ -20647,7 +20647,7 @@
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>Danilo Xavier</t>
+          <t>Daniel Moraes</t>
         </is>
       </c>
       <c r="H402" t="inlineStr">
@@ -20659,10 +20659,10 @@
         <v>3</v>
       </c>
       <c r="J402" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K402" t="n">
-        <v>151</v>
+        <v>41</v>
       </c>
     </row>
     <row r="403">
@@ -20698,7 +20698,7 @@
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>Elaine Assis</t>
+          <t>Danilo Xavier</t>
         </is>
       </c>
       <c r="H403" t="inlineStr">
@@ -20707,13 +20707,13 @@
         </is>
       </c>
       <c r="I403" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J403" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K403" t="n">
-        <v>56</v>
+        <v>151</v>
       </c>
     </row>
     <row r="404">
@@ -20749,12 +20749,12 @@
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>Eliene Lima</t>
+          <t>Elaine Assis</t>
         </is>
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I404" t="n">
@@ -20764,7 +20764,7 @@
         <v>0</v>
       </c>
       <c r="K404" t="n">
-        <v>43</v>
+        <v>56</v>
       </c>
     </row>
     <row r="405">
@@ -20800,22 +20800,22 @@
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>Erica Oliveira</t>
+          <t>Eliene Lima</t>
         </is>
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I405" t="n">
         <v>0</v>
       </c>
       <c r="J405" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K405" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="406">
@@ -20851,22 +20851,22 @@
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>Evellin Bispo</t>
+          <t>Erica Oliveira</t>
         </is>
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>Leandro Matos</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I406" t="n">
         <v>0</v>
       </c>
       <c r="J406" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K406" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
     </row>
     <row r="407">
@@ -20902,12 +20902,12 @@
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>Fabiane Branco</t>
+          <t>Evellin Bispo</t>
         </is>
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>Leandro Matos</t>
         </is>
       </c>
       <c r="I407" t="n">
@@ -20917,7 +20917,7 @@
         <v>0</v>
       </c>
       <c r="K407" t="n">
-        <v>118</v>
+        <v>23</v>
       </c>
     </row>
     <row r="408">
@@ -20953,12 +20953,12 @@
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>Franciele Alves</t>
+          <t>Fabiane Branco</t>
         </is>
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I408" t="n">
@@ -20968,7 +20968,7 @@
         <v>0</v>
       </c>
       <c r="K408" t="n">
-        <v>36</v>
+        <v>118</v>
       </c>
     </row>
     <row r="409">
@@ -21004,12 +21004,12 @@
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>Gabriela Peres</t>
+          <t>Franciele Alves</t>
         </is>
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>Leandro Matos</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I409" t="n">
@@ -21019,7 +21019,7 @@
         <v>0</v>
       </c>
       <c r="K409" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="410">
@@ -21055,12 +21055,12 @@
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>Grasiele Santos</t>
+          <t>Gabriela Peres</t>
         </is>
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Leandro Matos</t>
         </is>
       </c>
       <c r="I410" t="n">
@@ -21070,7 +21070,7 @@
         <v>0</v>
       </c>
       <c r="K410" t="n">
-        <v>112</v>
+        <v>12</v>
       </c>
     </row>
     <row r="411">
@@ -21106,12 +21106,12 @@
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Grasiele Santos</t>
         </is>
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I411" t="n">
@@ -21121,7 +21121,7 @@
         <v>0</v>
       </c>
       <c r="K411" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="412">
@@ -21157,12 +21157,12 @@
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>Janaina Rocha</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I412" t="n">
@@ -21172,7 +21172,7 @@
         <v>0</v>
       </c>
       <c r="K412" t="n">
-        <v>82</v>
+        <v>110</v>
       </c>
     </row>
     <row r="413">
@@ -21208,22 +21208,22 @@
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>Jayne Tavares</t>
+          <t>Janaina Rocha</t>
         </is>
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I413" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J413" t="n">
         <v>2</v>
       </c>
       <c r="K413" t="n">
-        <v>127</v>
+        <v>84</v>
       </c>
     </row>
     <row r="414">
@@ -21259,22 +21259,22 @@
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>Jhenifer Tenorio</t>
+          <t>Jayne Tavares</t>
         </is>
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I414" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J414" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K414" t="n">
-        <v>113</v>
+        <v>127</v>
       </c>
     </row>
     <row r="415">
@@ -21310,7 +21310,7 @@
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>Jonas Nunes</t>
+          <t>Jhenifer Tenorio</t>
         </is>
       </c>
       <c r="H415" t="inlineStr">
@@ -21319,13 +21319,13 @@
         </is>
       </c>
       <c r="I415" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J415" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K415" t="n">
-        <v>85</v>
+        <v>113</v>
       </c>
     </row>
     <row r="416">
@@ -21361,22 +21361,22 @@
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>Kaique Souza</t>
+          <t>Jonas Nunes</t>
         </is>
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I416" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J416" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="K416" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
     </row>
     <row r="417">
@@ -21412,7 +21412,7 @@
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>Karine Sousa</t>
+          <t>Kaique Souza</t>
         </is>
       </c>
       <c r="H417" t="inlineStr">
@@ -21421,13 +21421,13 @@
         </is>
       </c>
       <c r="I417" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J417" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="K417" t="n">
-        <v>51</v>
+        <v>78</v>
       </c>
     </row>
     <row r="418">
@@ -21463,22 +21463,22 @@
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>Laysla Alves</t>
+          <t>Karine Sousa</t>
         </is>
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I418" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J418" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K418" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="419">
@@ -21514,22 +21514,22 @@
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>Luana Marques</t>
+          <t>Laysla Alves</t>
         </is>
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I419" t="n">
         <v>0</v>
       </c>
       <c r="J419" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K419" t="n">
-        <v>17</v>
+        <v>56</v>
       </c>
     </row>
     <row r="420">
@@ -21565,7 +21565,7 @@
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>Maria Pires</t>
+          <t>Luana Marques</t>
         </is>
       </c>
       <c r="H420" t="inlineStr">
@@ -21580,7 +21580,7 @@
         <v>0</v>
       </c>
       <c r="K420" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="421">
@@ -21616,22 +21616,22 @@
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>Mauricio Lermen</t>
+          <t>Maria Pires</t>
         </is>
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>Mauricio Lermen</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I421" t="n">
         <v>0</v>
       </c>
       <c r="J421" t="n">
+        <v>0</v>
+      </c>
+      <c r="K421" t="n">
         <v>1</v>
-      </c>
-      <c r="K421" t="n">
-        <v>13</v>
       </c>
     </row>
     <row r="422">
@@ -21667,22 +21667,22 @@
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>Micaele Cordeiro</t>
+          <t>Mauricio Lermen</t>
         </is>
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>Mauricio Lermen</t>
         </is>
       </c>
       <c r="I422" t="n">
         <v>0</v>
       </c>
       <c r="J422" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K422" t="n">
-        <v>84</v>
+        <v>13</v>
       </c>
     </row>
     <row r="423">
@@ -21718,7 +21718,7 @@
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>Michele Silva</t>
+          <t>Micaele Cordeiro</t>
         </is>
       </c>
       <c r="H423" t="inlineStr">
@@ -21727,13 +21727,13 @@
         </is>
       </c>
       <c r="I423" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J423" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K423" t="n">
-        <v>67</v>
+        <v>84</v>
       </c>
     </row>
     <row r="424">
@@ -21769,22 +21769,22 @@
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>Murilo Marques</t>
+          <t>Michele Silva</t>
         </is>
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I424" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J424" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K424" t="n">
-        <v>42</v>
+        <v>67</v>
       </c>
     </row>
     <row r="425">
@@ -21820,22 +21820,22 @@
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>Natalia Batista</t>
+          <t>Murilo Marques</t>
         </is>
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I425" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J425" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K425" t="n">
-        <v>102</v>
+        <v>42</v>
       </c>
     </row>
     <row r="426">
@@ -21871,22 +21871,22 @@
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>Natalia Silva</t>
+          <t>Natalia Batista</t>
         </is>
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I426" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="J426" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="K426" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="427">
@@ -21922,22 +21922,22 @@
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>Oliene Mariano</t>
+          <t>Natalia Silva</t>
         </is>
       </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I427" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J427" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K427" t="n">
-        <v>75</v>
+        <v>103</v>
       </c>
     </row>
     <row r="428">
@@ -21973,22 +21973,22 @@
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>Priscila Aguiar</t>
+          <t>Oliene Mariano</t>
         </is>
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I428" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J428" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K428" t="n">
-        <v>61</v>
+        <v>73</v>
       </c>
     </row>
     <row r="429">
@@ -22024,7 +22024,7 @@
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>Rebeca Ribeiro</t>
+          <t>Priscila Aguiar</t>
         </is>
       </c>
       <c r="H429" t="inlineStr">
@@ -22033,13 +22033,13 @@
         </is>
       </c>
       <c r="I429" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J429" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K429" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="430">
@@ -22075,7 +22075,7 @@
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>Roberta Souza</t>
+          <t>Rebeca Ribeiro</t>
         </is>
       </c>
       <c r="H430" t="inlineStr">
@@ -22084,13 +22084,13 @@
         </is>
       </c>
       <c r="I430" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J430" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K430" t="n">
-        <v>76</v>
+        <v>66</v>
       </c>
     </row>
     <row r="431">
@@ -22126,7 +22126,7 @@
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>Ronildo Santos</t>
+          <t>Roberta Souza</t>
         </is>
       </c>
       <c r="H431" t="inlineStr">
@@ -22141,7 +22141,7 @@
         <v>0</v>
       </c>
       <c r="K431" t="n">
-        <v>3</v>
+        <v>76</v>
       </c>
     </row>
     <row r="432">
@@ -22177,22 +22177,22 @@
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>Rozania Santos</t>
+          <t>Ronildo Santos</t>
         </is>
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I432" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J432" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K432" t="n">
-        <v>98</v>
+        <v>4</v>
       </c>
     </row>
     <row r="433">
@@ -22228,22 +22228,22 @@
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>Santos Karina</t>
+          <t>Rozania Santos</t>
         </is>
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>Leandro Matos</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I433" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J433" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K433" t="n">
-        <v>2</v>
+        <v>99</v>
       </c>
     </row>
     <row r="434">
@@ -22279,12 +22279,12 @@
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>Sibelly Pereira</t>
+          <t>Santos Karina</t>
         </is>
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Leandro Matos</t>
         </is>
       </c>
       <c r="I434" t="n">
@@ -22294,7 +22294,7 @@
         <v>0</v>
       </c>
       <c r="K434" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
     </row>
     <row r="435">
@@ -22330,22 +22330,22 @@
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>Tania Luz</t>
+          <t>Sibelly Pereira</t>
         </is>
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I435" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J435" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K435" t="n">
-        <v>53</v>
+        <v>41</v>
       </c>
     </row>
     <row r="436">
@@ -22381,22 +22381,22 @@
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>Vitor Guedes</t>
+          <t>Tania Luz</t>
         </is>
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I436" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J436" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K436" t="n">
-        <v>134</v>
+        <v>54</v>
       </c>
     </row>
     <row r="437">
@@ -22427,27 +22427,27 @@
       </c>
       <c r="F437" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>Andrea Medeiros</t>
+          <t>Vitor Guedes</t>
         </is>
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I437" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J437" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K437" t="n">
-        <v>52</v>
+        <v>134</v>
       </c>
     </row>
     <row r="438">
@@ -22483,7 +22483,7 @@
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>Caroline Nascimento</t>
+          <t>Andrea Medeiros</t>
         </is>
       </c>
       <c r="H438" t="inlineStr">
@@ -22495,10 +22495,10 @@
         <v>1</v>
       </c>
       <c r="J438" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K438" t="n">
-        <v>70</v>
+        <v>52</v>
       </c>
     </row>
     <row r="439">
@@ -22534,7 +22534,7 @@
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>Cristiana Grizostomo</t>
+          <t>Caroline Nascimento</t>
         </is>
       </c>
       <c r="H439" t="inlineStr">
@@ -22543,13 +22543,13 @@
         </is>
       </c>
       <c r="I439" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J439" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="K439" t="n">
-        <v>33</v>
+        <v>76</v>
       </c>
     </row>
     <row r="440">
@@ -22585,18 +22585,22 @@
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>Denis Reis</t>
-        </is>
-      </c>
-      <c r="H440" t="inlineStr"/>
+          <t>Cristiana Grizostomo</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
       <c r="I440" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J440" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="K440" t="n">
-        <v>79</v>
+        <v>37</v>
       </c>
     </row>
     <row r="441">
@@ -22632,22 +22636,18 @@
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>Eliane Moreira</t>
-        </is>
-      </c>
-      <c r="H441" t="inlineStr">
-        <is>
-          <t>Nayara Oliveira</t>
-        </is>
-      </c>
+          <t>Denis Reis</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr"/>
       <c r="I441" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="J441" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="K441" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
     </row>
     <row r="442">
@@ -22683,7 +22683,7 @@
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>Gustavo Tonan</t>
+          <t>Eliane Moreira</t>
         </is>
       </c>
       <c r="H442" t="inlineStr">
@@ -22692,13 +22692,13 @@
         </is>
       </c>
       <c r="I442" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J442" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="K442" t="n">
-        <v>55</v>
+        <v>89</v>
       </c>
     </row>
     <row r="443">
@@ -22734,7 +22734,7 @@
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>Jonatan Hayashibara</t>
+          <t>Gustavo Tonan</t>
         </is>
       </c>
       <c r="H443" t="inlineStr">
@@ -22743,13 +22743,13 @@
         </is>
       </c>
       <c r="I443" t="n">
+        <v>1</v>
+      </c>
+      <c r="J443" t="n">
         <v>2</v>
       </c>
-      <c r="J443" t="n">
-        <v>68</v>
-      </c>
       <c r="K443" t="n">
-        <v>180</v>
+        <v>56</v>
       </c>
     </row>
     <row r="444">
@@ -22785,7 +22785,7 @@
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>Lais Arruda</t>
+          <t>Jonatan Hayashibara</t>
         </is>
       </c>
       <c r="H444" t="inlineStr">
@@ -22797,10 +22797,10 @@
         <v>2</v>
       </c>
       <c r="J444" t="n">
-        <v>3</v>
+        <v>68</v>
       </c>
       <c r="K444" t="n">
-        <v>61</v>
+        <v>180</v>
       </c>
     </row>
     <row r="445">
@@ -22836,7 +22836,7 @@
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>Luan Batista</t>
+          <t>Lais Arruda</t>
         </is>
       </c>
       <c r="H445" t="inlineStr">
@@ -22845,13 +22845,13 @@
         </is>
       </c>
       <c r="I445" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J445" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K445" t="n">
-        <v>38</v>
+        <v>61</v>
       </c>
     </row>
     <row r="446">
@@ -22887,7 +22887,7 @@
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>Maria Garcia</t>
+          <t>Luan Batista</t>
         </is>
       </c>
       <c r="H446" t="inlineStr">
@@ -22896,13 +22896,13 @@
         </is>
       </c>
       <c r="I446" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J446" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="K446" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
     </row>
     <row r="447">
@@ -22938,7 +22938,7 @@
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>Priscila Volpe</t>
+          <t>Maria Garcia</t>
         </is>
       </c>
       <c r="H447" t="inlineStr">
@@ -22947,13 +22947,13 @@
         </is>
       </c>
       <c r="I447" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J447" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="K447" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
     </row>
     <row r="448">
@@ -22989,7 +22989,7 @@
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>Rodrigo Souza</t>
+          <t>Priscila Volpe</t>
         </is>
       </c>
       <c r="H448" t="inlineStr">
@@ -23001,10 +23001,10 @@
         <v>0</v>
       </c>
       <c r="J448" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K448" t="n">
-        <v>53</v>
+        <v>10</v>
       </c>
     </row>
     <row r="449">
@@ -23040,7 +23040,7 @@
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>Romario Silva</t>
+          <t>Rodrigo Souza</t>
         </is>
       </c>
       <c r="H449" t="inlineStr">
@@ -23049,13 +23049,13 @@
         </is>
       </c>
       <c r="I449" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J449" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="K449" t="n">
-        <v>133</v>
+        <v>53</v>
       </c>
     </row>
     <row r="450">
@@ -23091,7 +23091,7 @@
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>Rosilene Santos</t>
+          <t>Romario Silva</t>
         </is>
       </c>
       <c r="H450" t="inlineStr">
@@ -23100,13 +23100,13 @@
         </is>
       </c>
       <c r="I450" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J450" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="K450" t="n">
-        <v>60</v>
+        <v>136</v>
       </c>
     </row>
     <row r="451">
@@ -23142,7 +23142,7 @@
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>Suede Gomes</t>
+          <t>Rosilene Santos</t>
         </is>
       </c>
       <c r="H451" t="inlineStr">
@@ -23151,13 +23151,13 @@
         </is>
       </c>
       <c r="I451" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J451" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="K451" t="n">
-        <v>28</v>
+        <v>63</v>
       </c>
     </row>
     <row r="452">
@@ -23193,7 +23193,7 @@
       </c>
       <c r="G452" t="inlineStr">
         <is>
-          <t>Taina Silva</t>
+          <t>Suede Gomes</t>
         </is>
       </c>
       <c r="H452" t="inlineStr">
@@ -23202,13 +23202,13 @@
         </is>
       </c>
       <c r="I452" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J452" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K452" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="453">
@@ -23244,7 +23244,7 @@
       </c>
       <c r="G453" t="inlineStr">
         <is>
-          <t>Thayna Melo</t>
+          <t>Taina Silva</t>
         </is>
       </c>
       <c r="H453" t="inlineStr">
@@ -23253,13 +23253,13 @@
         </is>
       </c>
       <c r="I453" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J453" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="K453" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="454">
@@ -23295,7 +23295,7 @@
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>Vanessa Santana</t>
+          <t>Thayna Melo</t>
         </is>
       </c>
       <c r="H454" t="inlineStr">
@@ -23304,13 +23304,13 @@
         </is>
       </c>
       <c r="I454" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J454" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="K454" t="n">
-        <v>125</v>
+        <v>32</v>
       </c>
     </row>
     <row r="455">
@@ -23341,27 +23341,27 @@
       </c>
       <c r="F455" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="G455" t="inlineStr">
         <is>
-          <t>Alaine Neres</t>
+          <t>Vanessa Santana</t>
         </is>
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
       <c r="I455" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="J455" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="K455" t="n">
-        <v>78</v>
+        <v>125</v>
       </c>
     </row>
     <row r="456">
@@ -23397,22 +23397,22 @@
       </c>
       <c r="G456" t="inlineStr">
         <is>
-          <t>Andre Silva</t>
+          <t>Alaine Neres</t>
         </is>
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I456" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="J456" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="K456" t="n">
-        <v>60</v>
+        <v>81</v>
       </c>
     </row>
     <row r="457">
@@ -23448,22 +23448,22 @@
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>Anna Ramalho</t>
+          <t>Andre Silva</t>
         </is>
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I457" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J457" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K457" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="458">
@@ -23499,7 +23499,7 @@
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>Beatriz Ferreira</t>
+          <t>Anna Ramalho</t>
         </is>
       </c>
       <c r="H458" t="inlineStr">
@@ -23508,13 +23508,13 @@
         </is>
       </c>
       <c r="I458" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J458" t="n">
         <v>7</v>
       </c>
       <c r="K458" t="n">
-        <v>51</v>
+        <v>63</v>
       </c>
     </row>
     <row r="459">
@@ -23550,22 +23550,22 @@
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>Brenda Batista</t>
+          <t>Beatriz Ferreira</t>
         </is>
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="I459" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J459" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="K459" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
     </row>
     <row r="460">
@@ -23601,22 +23601,22 @@
       </c>
       <c r="G460" t="inlineStr">
         <is>
-          <t>Bruna Souza</t>
+          <t>Brenda Batista</t>
         </is>
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I460" t="n">
         <v>5</v>
       </c>
       <c r="J460" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="K460" t="n">
-        <v>58</v>
+        <v>43</v>
       </c>
     </row>
     <row r="461">
@@ -23652,22 +23652,22 @@
       </c>
       <c r="G461" t="inlineStr">
         <is>
-          <t>Bruno Henrique</t>
+          <t>Bruna Souza</t>
         </is>
       </c>
       <c r="H461" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I461" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J461" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="K461" t="n">
-        <v>77</v>
+        <v>58</v>
       </c>
     </row>
     <row r="462">
@@ -23703,18 +23703,22 @@
       </c>
       <c r="G462" t="inlineStr">
         <is>
-          <t>Claudineia Rodrigues</t>
-        </is>
-      </c>
-      <c r="H462" t="inlineStr"/>
+          <t>Bruno Henrique</t>
+        </is>
+      </c>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>Lorrane Santos</t>
+        </is>
+      </c>
       <c r="I462" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J462" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K462" t="n">
-        <v>115</v>
+        <v>80</v>
       </c>
     </row>
     <row r="463">
@@ -23750,22 +23754,18 @@
       </c>
       <c r="G463" t="inlineStr">
         <is>
-          <t>Cristina Leite</t>
-        </is>
-      </c>
-      <c r="H463" t="inlineStr">
-        <is>
-          <t>Ricardo Fischer</t>
-        </is>
-      </c>
+          <t>Claudineia Rodrigues</t>
+        </is>
+      </c>
+      <c r="H463" t="inlineStr"/>
       <c r="I463" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J463" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K463" t="n">
-        <v>100</v>
+        <v>115</v>
       </c>
     </row>
     <row r="464">
@@ -23801,22 +23801,22 @@
       </c>
       <c r="G464" t="inlineStr">
         <is>
-          <t>Davi Santos</t>
+          <t>Cristina Leite</t>
         </is>
       </c>
       <c r="H464" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="I464" t="n">
+        <v>1</v>
+      </c>
+      <c r="J464" t="n">
         <v>10</v>
       </c>
-      <c r="J464" t="n">
-        <v>13</v>
-      </c>
       <c r="K464" t="n">
-        <v>84</v>
+        <v>101</v>
       </c>
     </row>
     <row r="465">
@@ -23852,22 +23852,22 @@
       </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t>Deleia Oliveira</t>
+          <t>Davi Santos</t>
         </is>
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I465" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J465" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K465" t="n">
-        <v>69</v>
+        <v>84</v>
       </c>
     </row>
     <row r="466">
@@ -23903,22 +23903,22 @@
       </c>
       <c r="G466" t="inlineStr">
         <is>
-          <t>Diego Pereira</t>
+          <t>Deleia Oliveira</t>
         </is>
       </c>
       <c r="H466" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I466" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J466" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="K466" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
     </row>
     <row r="467">
@@ -23954,22 +23954,22 @@
       </c>
       <c r="G467" t="inlineStr">
         <is>
-          <t>Eduardo Lopes</t>
+          <t>Diego Pereira</t>
         </is>
       </c>
       <c r="H467" t="inlineStr">
         <is>
-          <t>Idna Sousa</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I467" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="J467" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="K467" t="n">
-        <v>13</v>
+        <v>65</v>
       </c>
     </row>
     <row r="468">
@@ -24005,22 +24005,22 @@
       </c>
       <c r="G468" t="inlineStr">
         <is>
-          <t>Gislaine Lima</t>
+          <t>Eduardo Lopes</t>
         </is>
       </c>
       <c r="H468" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Idna Sousa</t>
         </is>
       </c>
       <c r="I468" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J468" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="K468" t="n">
-        <v>57</v>
+        <v>14</v>
       </c>
     </row>
     <row r="469">
@@ -24056,22 +24056,22 @@
       </c>
       <c r="G469" t="inlineStr">
         <is>
-          <t>Gustavo Santos</t>
+          <t>Gislaine Lima</t>
         </is>
       </c>
       <c r="H469" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I469" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J469" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K469" t="n">
-        <v>129</v>
+        <v>58</v>
       </c>
     </row>
     <row r="470">
@@ -24107,22 +24107,22 @@
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>Igor Valezi</t>
+          <t>Gustavo Santos</t>
         </is>
       </c>
       <c r="H470" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="I470" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J470" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K470" t="n">
-        <v>74</v>
+        <v>129</v>
       </c>
     </row>
     <row r="471">
@@ -24158,22 +24158,22 @@
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>Izabely Araujo</t>
+          <t>Igor Valezi</t>
         </is>
       </c>
       <c r="H471" t="inlineStr">
         <is>
-          <t>Idna Sousa</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I471" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J471" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K471" t="n">
-        <v>4</v>
+        <v>74</v>
       </c>
     </row>
     <row r="472">
@@ -24209,12 +24209,12 @@
       </c>
       <c r="G472" t="inlineStr">
         <is>
-          <t>Joanna Costa</t>
+          <t>Izabely Araujo</t>
         </is>
       </c>
       <c r="H472" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Idna Sousa</t>
         </is>
       </c>
       <c r="I472" t="n">
@@ -24224,7 +24224,7 @@
         <v>0</v>
       </c>
       <c r="K472" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="473">
@@ -24260,22 +24260,22 @@
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t>Jose Natan</t>
+          <t>Joanna Costa</t>
         </is>
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I473" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J473" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K473" t="n">
-        <v>88</v>
+        <v>14</v>
       </c>
     </row>
     <row r="474">
@@ -24311,7 +24311,7 @@
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>João Oliveira</t>
+          <t>Jose Natan</t>
         </is>
       </c>
       <c r="H474" t="inlineStr">
@@ -24320,13 +24320,13 @@
         </is>
       </c>
       <c r="I474" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="J474" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="K474" t="n">
-        <v>9</v>
+        <v>88</v>
       </c>
     </row>
     <row r="475">
@@ -24362,22 +24362,22 @@
       </c>
       <c r="G475" t="inlineStr">
         <is>
-          <t>Juan Ribeiro</t>
+          <t>João Oliveira</t>
         </is>
       </c>
       <c r="H475" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I475" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="J475" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="K475" t="n">
-        <v>75</v>
+        <v>9</v>
       </c>
     </row>
     <row r="476">
@@ -24413,22 +24413,22 @@
       </c>
       <c r="G476" t="inlineStr">
         <is>
-          <t>Juliana Valeria</t>
+          <t>Juan Ribeiro</t>
         </is>
       </c>
       <c r="H476" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I476" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="J476" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="K476" t="n">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="477">
@@ -24464,7 +24464,7 @@
       </c>
       <c r="G477" t="inlineStr">
         <is>
-          <t>Juliane Vaz</t>
+          <t>Juliana Valeria</t>
         </is>
       </c>
       <c r="H477" t="inlineStr">
@@ -24473,13 +24473,13 @@
         </is>
       </c>
       <c r="I477" t="n">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="J477" t="n">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="K477" t="n">
-        <v>156</v>
+        <v>83</v>
       </c>
     </row>
     <row r="478">
@@ -24515,22 +24515,22 @@
       </c>
       <c r="G478" t="inlineStr">
         <is>
-          <t>Katia Xavier</t>
+          <t>Juliane Vaz</t>
         </is>
       </c>
       <c r="H478" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I478" t="n">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="J478" t="n">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="K478" t="n">
-        <v>59</v>
+        <v>157</v>
       </c>
     </row>
     <row r="479">
@@ -24566,22 +24566,22 @@
       </c>
       <c r="G479" t="inlineStr">
         <is>
-          <t>Larissa Félix</t>
+          <t>Katia Xavier</t>
         </is>
       </c>
       <c r="H479" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I479" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="J479" t="n">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="K479" t="n">
-        <v>95</v>
+        <v>59</v>
       </c>
     </row>
     <row r="480">
@@ -24617,22 +24617,22 @@
       </c>
       <c r="G480" t="inlineStr">
         <is>
-          <t>Léia de Oliveira</t>
+          <t>Larissa Félix</t>
         </is>
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I480" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="J480" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="K480" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="481">
@@ -24668,7 +24668,7 @@
       </c>
       <c r="G481" t="inlineStr">
         <is>
-          <t>Maria Gualberto</t>
+          <t>Léia de Oliveira</t>
         </is>
       </c>
       <c r="H481" t="inlineStr">
@@ -24677,13 +24677,13 @@
         </is>
       </c>
       <c r="I481" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J481" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K481" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="482">
@@ -24719,22 +24719,22 @@
       </c>
       <c r="G482" t="inlineStr">
         <is>
-          <t>Priscila Moreira</t>
+          <t>Maria Gualberto</t>
         </is>
       </c>
       <c r="H482" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I482" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J482" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K482" t="n">
-        <v>75</v>
+        <v>92</v>
       </c>
     </row>
     <row r="483">
@@ -24770,22 +24770,22 @@
       </c>
       <c r="G483" t="inlineStr">
         <is>
-          <t>Regiane Santos</t>
+          <t>Priscila Moreira</t>
         </is>
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="I483" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J483" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="K483" t="n">
-        <v>52</v>
+        <v>76</v>
       </c>
     </row>
     <row r="484">
@@ -24821,22 +24821,22 @@
       </c>
       <c r="G484" t="inlineStr">
         <is>
-          <t>Shofia Gomes</t>
+          <t>Regiane Santos</t>
         </is>
       </c>
       <c r="H484" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I484" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J484" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K484" t="n">
-        <v>94</v>
+        <v>52</v>
       </c>
     </row>
     <row r="485">
@@ -24872,22 +24872,22 @@
       </c>
       <c r="G485" t="inlineStr">
         <is>
-          <t>Vanessa Tavares</t>
+          <t>Shofia Gomes</t>
         </is>
       </c>
       <c r="H485" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="I485" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J485" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K485" t="n">
-        <v>47</v>
+        <v>95</v>
       </c>
     </row>
     <row r="486">
@@ -24923,7 +24923,7 @@
       </c>
       <c r="G486" t="inlineStr">
         <is>
-          <t>Willian Luz</t>
+          <t>Vanessa Tavares</t>
         </is>
       </c>
       <c r="H486" t="inlineStr">
@@ -24935,10 +24935,10 @@
         <v>1</v>
       </c>
       <c r="J486" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K486" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="487">
@@ -24974,7 +24974,7 @@
       </c>
       <c r="G487" t="inlineStr">
         <is>
-          <t>Yasmim Oliveira</t>
+          <t>Willian Luz</t>
         </is>
       </c>
       <c r="H487" t="inlineStr">
@@ -24983,13 +24983,13 @@
         </is>
       </c>
       <c r="I487" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J487" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K487" t="n">
-        <v>33</v>
+        <v>55</v>
       </c>
     </row>
     <row r="488">
@@ -25020,15 +25020,19 @@
       </c>
       <c r="F488" t="inlineStr">
         <is>
-          <t>ESCRITA FISCAL (Outsourcing)</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="G488" t="inlineStr">
         <is>
-          <t>Claudineia Rodrigues</t>
-        </is>
-      </c>
-      <c r="H488" t="inlineStr"/>
+          <t>Yasmim Oliveira</t>
+        </is>
+      </c>
+      <c r="H488" t="inlineStr">
+        <is>
+          <t>Larice Souza</t>
+        </is>
+      </c>
       <c r="I488" t="n">
         <v>0</v>
       </c>
@@ -25036,7 +25040,7 @@
         <v>0</v>
       </c>
       <c r="K488" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
     </row>
     <row r="489">
@@ -25072,22 +25076,18 @@
       </c>
       <c r="G489" t="inlineStr">
         <is>
-          <t>Diego Pereira</t>
-        </is>
-      </c>
-      <c r="H489" t="inlineStr">
-        <is>
-          <t>Thaiza Oliveira</t>
-        </is>
-      </c>
+          <t>Claudineia Rodrigues</t>
+        </is>
+      </c>
+      <c r="H489" t="inlineStr"/>
       <c r="I489" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J489" t="n">
+        <v>0</v>
+      </c>
+      <c r="K489" t="n">
         <v>2</v>
-      </c>
-      <c r="K489" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="490">
@@ -25123,12 +25123,12 @@
       </c>
       <c r="G490" t="inlineStr">
         <is>
-          <t>Gislaine Lima</t>
+          <t>Diego Pereira</t>
         </is>
       </c>
       <c r="H490" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I490" t="n">
@@ -25138,7 +25138,7 @@
         <v>2</v>
       </c>
       <c r="K490" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
     </row>
     <row r="491">
@@ -25174,7 +25174,7 @@
       </c>
       <c r="G491" t="inlineStr">
         <is>
-          <t>Joanna Costa</t>
+          <t>Gislaine Lima</t>
         </is>
       </c>
       <c r="H491" t="inlineStr">
@@ -25183,13 +25183,13 @@
         </is>
       </c>
       <c r="I491" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="J491" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="K491" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
     </row>
     <row r="492">
@@ -25225,22 +25225,22 @@
       </c>
       <c r="G492" t="inlineStr">
         <is>
-          <t>João Oliveira</t>
+          <t>Joanna Costa</t>
         </is>
       </c>
       <c r="H492" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I492" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="J492" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="K492" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="493">
@@ -25276,7 +25276,7 @@
       </c>
       <c r="G493" t="inlineStr">
         <is>
-          <t>Regiane Santos</t>
+          <t>João Oliveira</t>
         </is>
       </c>
       <c r="H493" t="inlineStr">
@@ -25285,13 +25285,13 @@
         </is>
       </c>
       <c r="I493" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J493" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K493" t="n">
-        <v>13</v>
+        <v>37</v>
       </c>
     </row>
     <row r="494">
@@ -25327,7 +25327,7 @@
       </c>
       <c r="G494" t="inlineStr">
         <is>
-          <t>Yasmim Oliveira</t>
+          <t>Regiane Santos</t>
         </is>
       </c>
       <c r="H494" t="inlineStr">
@@ -25336,13 +25336,13 @@
         </is>
       </c>
       <c r="I494" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J494" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K494" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="495">
@@ -25373,23 +25373,27 @@
       </c>
       <c r="F495" t="inlineStr">
         <is>
-          <t>FIN - CONTÁBIL</t>
+          <t>ESCRITA FISCAL (Outsourcing)</t>
         </is>
       </c>
       <c r="G495" t="inlineStr">
         <is>
-          <t>Daniele Faria</t>
-        </is>
-      </c>
-      <c r="H495" t="inlineStr"/>
+          <t>Yasmim Oliveira</t>
+        </is>
+      </c>
+      <c r="H495" t="inlineStr">
+        <is>
+          <t>Larice Souza</t>
+        </is>
+      </c>
       <c r="I495" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="J495" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K495" t="n">
-        <v>59</v>
+        <v>4</v>
       </c>
     </row>
     <row r="496">
@@ -25420,23 +25424,23 @@
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>FIN - CONTÁBIL</t>
         </is>
       </c>
       <c r="G496" t="inlineStr">
         <is>
-          <t>Ana Santana</t>
+          <t>Daniele Faria</t>
         </is>
       </c>
       <c r="H496" t="inlineStr"/>
       <c r="I496" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="J496" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="K496" t="n">
-        <v>394</v>
+        <v>59</v>
       </c>
     </row>
     <row r="497">
@@ -25472,18 +25476,18 @@
       </c>
       <c r="G497" t="inlineStr">
         <is>
-          <t>Andre Coelho</t>
+          <t>Ana Santana</t>
         </is>
       </c>
       <c r="H497" t="inlineStr"/>
       <c r="I497" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J497" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K497" t="n">
-        <v>3</v>
+        <v>394</v>
       </c>
     </row>
     <row r="498">
@@ -25519,7 +25523,7 @@
       </c>
       <c r="G498" t="inlineStr">
         <is>
-          <t>Bianca Castro</t>
+          <t>Andre Coelho</t>
         </is>
       </c>
       <c r="H498" t="inlineStr"/>
@@ -25527,10 +25531,10 @@
         <v>0</v>
       </c>
       <c r="J498" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K498" t="n">
-        <v>324</v>
+        <v>3</v>
       </c>
     </row>
     <row r="499">
@@ -25566,7 +25570,7 @@
       </c>
       <c r="G499" t="inlineStr">
         <is>
-          <t>Bruna Costa</t>
+          <t>Bianca Castro</t>
         </is>
       </c>
       <c r="H499" t="inlineStr"/>
@@ -25574,10 +25578,10 @@
         <v>0</v>
       </c>
       <c r="J499" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K499" t="n">
-        <v>34</v>
+        <v>324</v>
       </c>
     </row>
     <row r="500">
@@ -25613,7 +25617,7 @@
       </c>
       <c r="G500" t="inlineStr">
         <is>
-          <t>Daniela Silva</t>
+          <t>Bruna Costa</t>
         </is>
       </c>
       <c r="H500" t="inlineStr"/>
@@ -25621,10 +25625,10 @@
         <v>0</v>
       </c>
       <c r="J500" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K500" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
     </row>
     <row r="501">
@@ -25660,7 +25664,7 @@
       </c>
       <c r="G501" t="inlineStr">
         <is>
-          <t>Isabelli Afonso</t>
+          <t>Daniela Silva</t>
         </is>
       </c>
       <c r="H501" t="inlineStr"/>
@@ -25668,10 +25672,10 @@
         <v>14</v>
       </c>
       <c r="J501" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="K501" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
     </row>
     <row r="502">
@@ -25707,18 +25711,18 @@
       </c>
       <c r="G502" t="inlineStr">
         <is>
-          <t>Jurema Damacena - SAC</t>
+          <t>Isabelli Afonso</t>
         </is>
       </c>
       <c r="H502" t="inlineStr"/>
       <c r="I502" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J502" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K502" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
     </row>
     <row r="503">
@@ -25754,18 +25758,18 @@
       </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t>Leticia Queiroz</t>
+          <t>Jurema Damacena - SAC</t>
         </is>
       </c>
       <c r="H503" t="inlineStr"/>
       <c r="I503" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J503" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K503" t="n">
-        <v>47</v>
+        <v>1</v>
       </c>
     </row>
     <row r="504">
@@ -25801,18 +25805,18 @@
       </c>
       <c r="G504" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Leticia Queiroz</t>
         </is>
       </c>
       <c r="H504" t="inlineStr"/>
       <c r="I504" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J504" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K504" t="n">
-        <v>6</v>
+        <v>47</v>
       </c>
     </row>
     <row r="505">
@@ -25848,18 +25852,18 @@
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>Victoria Virgens</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="H505" t="inlineStr"/>
       <c r="I505" t="n">
+        <v>0</v>
+      </c>
+      <c r="J505" t="n">
+        <v>0</v>
+      </c>
+      <c r="K505" t="n">
         <v>6</v>
-      </c>
-      <c r="J505" t="n">
-        <v>4</v>
-      </c>
-      <c r="K505" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="506">
@@ -25895,18 +25899,18 @@
       </c>
       <c r="G506" t="inlineStr">
         <is>
-          <t>Yasmin Peixoto</t>
+          <t>Victoria Virgens</t>
         </is>
       </c>
       <c r="H506" t="inlineStr"/>
       <c r="I506" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J506" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K506" t="n">
-        <v>263</v>
+        <v>11</v>
       </c>
     </row>
     <row r="507">
@@ -25937,12 +25941,12 @@
       </c>
       <c r="F507" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="G507" t="inlineStr">
         <is>
-          <t>Andre Coelho</t>
+          <t>Yasmin Peixoto</t>
         </is>
       </c>
       <c r="H507" t="inlineStr"/>
@@ -25950,10 +25954,10 @@
         <v>0</v>
       </c>
       <c r="J507" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K507" t="n">
-        <v>4</v>
+        <v>263</v>
       </c>
     </row>
     <row r="508">
@@ -25989,7 +25993,7 @@
       </c>
       <c r="G508" t="inlineStr">
         <is>
-          <t>Beatriz Rangel</t>
+          <t>Andre Coelho</t>
         </is>
       </c>
       <c r="H508" t="inlineStr"/>
@@ -25997,10 +26001,10 @@
         <v>0</v>
       </c>
       <c r="J508" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K508" t="n">
-        <v>264</v>
+        <v>4</v>
       </c>
     </row>
     <row r="509">
@@ -26036,7 +26040,7 @@
       </c>
       <c r="G509" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
+          <t>Beatriz Rangel</t>
         </is>
       </c>
       <c r="H509" t="inlineStr"/>
@@ -26044,10 +26048,10 @@
         <v>0</v>
       </c>
       <c r="J509" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K509" t="n">
-        <v>147</v>
+        <v>264</v>
       </c>
     </row>
     <row r="510">
@@ -26083,7 +26087,7 @@
       </c>
       <c r="G510" t="inlineStr">
         <is>
-          <t>Cristiane Simões</t>
+          <t>Bruno Contieri</t>
         </is>
       </c>
       <c r="H510" t="inlineStr"/>
@@ -26091,10 +26095,10 @@
         <v>0</v>
       </c>
       <c r="J510" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K510" t="n">
-        <v>173</v>
+        <v>147</v>
       </c>
     </row>
     <row r="511">
@@ -26130,18 +26134,18 @@
       </c>
       <c r="G511" t="inlineStr">
         <is>
-          <t>Daniel Oliveira</t>
+          <t>Cristiane Simões</t>
         </is>
       </c>
       <c r="H511" t="inlineStr"/>
       <c r="I511" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J511" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K511" t="n">
-        <v>79</v>
+        <v>173</v>
       </c>
     </row>
     <row r="512">
@@ -26177,18 +26181,18 @@
       </c>
       <c r="G512" t="inlineStr">
         <is>
-          <t>Diego Lima</t>
+          <t>Daniel Oliveira</t>
         </is>
       </c>
       <c r="H512" t="inlineStr"/>
       <c r="I512" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J512" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K512" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="513">
@@ -26224,7 +26228,7 @@
       </c>
       <c r="G513" t="inlineStr">
         <is>
-          <t>Luiz Ferreira</t>
+          <t>Diego Lima</t>
         </is>
       </c>
       <c r="H513" t="inlineStr"/>
@@ -26235,7 +26239,7 @@
         <v>0</v>
       </c>
       <c r="K513" t="n">
-        <v>7</v>
+        <v>79</v>
       </c>
     </row>
     <row r="514">
@@ -26271,7 +26275,7 @@
       </c>
       <c r="G514" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Luiz Ferreira</t>
         </is>
       </c>
       <c r="H514" t="inlineStr"/>
@@ -26282,7 +26286,7 @@
         <v>0</v>
       </c>
       <c r="K514" t="n">
-        <v>87</v>
+        <v>7</v>
       </c>
     </row>
     <row r="515">
@@ -26318,7 +26322,7 @@
       </c>
       <c r="G515" t="inlineStr">
         <is>
-          <t>Rodrigo Rego</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="H515" t="inlineStr"/>
@@ -26326,10 +26330,10 @@
         <v>0</v>
       </c>
       <c r="J515" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K515" t="n">
-        <v>176</v>
+        <v>87</v>
       </c>
     </row>
     <row r="516">
@@ -26365,7 +26369,7 @@
       </c>
       <c r="G516" t="inlineStr">
         <is>
-          <t>Rogerio Egidio</t>
+          <t>Rodrigo Rego</t>
         </is>
       </c>
       <c r="H516" t="inlineStr"/>
@@ -26373,10 +26377,10 @@
         <v>0</v>
       </c>
       <c r="J516" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K516" t="n">
-        <v>180</v>
+        <v>176</v>
       </c>
     </row>
     <row r="517">
@@ -26412,7 +26416,7 @@
       </c>
       <c r="G517" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Rogerio Egidio</t>
         </is>
       </c>
       <c r="H517" t="inlineStr"/>
@@ -26420,10 +26424,10 @@
         <v>0</v>
       </c>
       <c r="J517" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K517" t="n">
-        <v>34</v>
+        <v>180</v>
       </c>
     </row>
     <row r="518">
@@ -26459,7 +26463,7 @@
       </c>
       <c r="G518" t="inlineStr">
         <is>
-          <t>Simone Marques</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="H518" t="inlineStr"/>
@@ -26470,7 +26474,7 @@
         <v>0</v>
       </c>
       <c r="K518" t="n">
-        <v>116</v>
+        <v>34</v>
       </c>
     </row>
     <row r="519">
@@ -26506,18 +26510,18 @@
       </c>
       <c r="G519" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Simone Marques</t>
         </is>
       </c>
       <c r="H519" t="inlineStr"/>
       <c r="I519" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J519" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K519" t="n">
-        <v>126</v>
+        <v>118</v>
       </c>
     </row>
     <row r="520">
@@ -26548,12 +26552,12 @@
       </c>
       <c r="F520" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="G520" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="H520" t="inlineStr"/>
@@ -26561,10 +26565,10 @@
         <v>0</v>
       </c>
       <c r="J520" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K520" t="n">
-        <v>1</v>
+        <v>126</v>
       </c>
     </row>
     <row r="521">
@@ -26600,18 +26604,18 @@
       </c>
       <c r="G521" t="inlineStr">
         <is>
-          <t>Jurema Damacena - SAC</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="H521" t="inlineStr"/>
       <c r="I521" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J521" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K521" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
     </row>
     <row r="522">
@@ -26637,7 +26641,7 @@
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F522" t="inlineStr">
@@ -26652,13 +26656,13 @@
       </c>
       <c r="H522" t="inlineStr"/>
       <c r="I522" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J522" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="K522" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
     </row>
     <row r="523">
@@ -26689,23 +26693,23 @@
       </c>
       <c r="F523" t="inlineStr">
         <is>
-          <t>SANTOS - ADM</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="G523" t="inlineStr">
         <is>
-          <t>Kauany Pereira</t>
+          <t>Jurema Damacena - SAC</t>
         </is>
       </c>
       <c r="H523" t="inlineStr"/>
       <c r="I523" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J523" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="K523" t="n">
-        <v>120</v>
+        <v>2</v>
       </c>
     </row>
     <row r="524">
@@ -26736,27 +26740,23 @@
       </c>
       <c r="F524" t="inlineStr">
         <is>
-          <t>SANTOS - CTB</t>
+          <t>SANTOS - ADM</t>
         </is>
       </c>
       <c r="G524" t="inlineStr">
         <is>
-          <t>Ivia Oliveira</t>
-        </is>
-      </c>
-      <c r="H524" t="inlineStr">
-        <is>
-          <t>Roberto Silva</t>
-        </is>
-      </c>
+          <t>Kauany Pereira</t>
+        </is>
+      </c>
+      <c r="H524" t="inlineStr"/>
       <c r="I524" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="J524" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="K524" t="n">
-        <v>8</v>
+        <v>133</v>
       </c>
     </row>
     <row r="525">
@@ -26792,7 +26792,7 @@
       </c>
       <c r="G525" t="inlineStr">
         <is>
-          <t>Nata Trindade</t>
+          <t>Ivia Oliveira</t>
         </is>
       </c>
       <c r="H525" t="inlineStr">
@@ -26801,13 +26801,13 @@
         </is>
       </c>
       <c r="I525" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J525" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K525" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
     </row>
     <row r="526">
@@ -26843,22 +26843,22 @@
       </c>
       <c r="G526" t="inlineStr">
         <is>
+          <t>Nata Trindade</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
           <t>Roberto Silva</t>
         </is>
       </c>
-      <c r="H526" t="inlineStr">
-        <is>
-          <t>Roberto Silva</t>
-        </is>
-      </c>
       <c r="I526" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J526" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K526" t="n">
-        <v>37</v>
+        <v>22</v>
       </c>
     </row>
     <row r="527">
@@ -26894,7 +26894,7 @@
       </c>
       <c r="G527" t="inlineStr">
         <is>
-          <t>Thaina Rodrigues</t>
+          <t>Roberto Silva</t>
         </is>
       </c>
       <c r="H527" t="inlineStr">
@@ -26903,13 +26903,13 @@
         </is>
       </c>
       <c r="I527" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J527" t="n">
         <v>1</v>
       </c>
       <c r="K527" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
     </row>
     <row r="528">
@@ -26940,27 +26940,27 @@
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>SANTOS - DP</t>
+          <t>SANTOS - CTB</t>
         </is>
       </c>
       <c r="G528" t="inlineStr">
         <is>
-          <t>Bruna Silva</t>
+          <t>Thaina Rodrigues</t>
         </is>
       </c>
       <c r="H528" t="inlineStr">
         <is>
-          <t>Katia Valeria</t>
+          <t>Roberto Silva</t>
         </is>
       </c>
       <c r="I528" t="n">
         <v>0</v>
       </c>
       <c r="J528" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K528" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
     </row>
     <row r="529">
@@ -26996,7 +26996,7 @@
       </c>
       <c r="G529" t="inlineStr">
         <is>
-          <t>Carliane Silva</t>
+          <t>Bruna Silva</t>
         </is>
       </c>
       <c r="H529" t="inlineStr">
@@ -27005,13 +27005,13 @@
         </is>
       </c>
       <c r="I529" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J529" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K529" t="n">
-        <v>172</v>
+        <v>14</v>
       </c>
     </row>
     <row r="530">
@@ -27047,7 +27047,7 @@
       </c>
       <c r="G530" t="inlineStr">
         <is>
-          <t>Cintia Andrade</t>
+          <t>Carliane Silva</t>
         </is>
       </c>
       <c r="H530" t="inlineStr">
@@ -27056,13 +27056,13 @@
         </is>
       </c>
       <c r="I530" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="J530" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="K530" t="n">
-        <v>110</v>
+        <v>172</v>
       </c>
     </row>
     <row r="531">
@@ -27098,22 +27098,22 @@
       </c>
       <c r="G531" t="inlineStr">
         <is>
+          <t>Cintia Andrade</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
           <t>Katia Valeria</t>
         </is>
       </c>
-      <c r="H531" t="inlineStr">
-        <is>
-          <t>Katia Valeria</t>
-        </is>
-      </c>
       <c r="I531" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="J531" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="K531" t="n">
-        <v>202</v>
+        <v>111</v>
       </c>
     </row>
     <row r="532">
@@ -27144,27 +27144,27 @@
       </c>
       <c r="F532" t="inlineStr">
         <is>
-          <t>SANTOS - EF</t>
+          <t>SANTOS - DP</t>
         </is>
       </c>
       <c r="G532" t="inlineStr">
         <is>
-          <t>Jasmina Melo</t>
+          <t>Katia Valeria</t>
         </is>
       </c>
       <c r="H532" t="inlineStr">
         <is>
-          <t>Lidia Tavares</t>
+          <t>Katia Valeria</t>
         </is>
       </c>
       <c r="I532" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="J532" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="K532" t="n">
-        <v>26</v>
+        <v>211</v>
       </c>
     </row>
     <row r="533">
@@ -27200,7 +27200,7 @@
       </c>
       <c r="G533" t="inlineStr">
         <is>
-          <t>Karen Saadi</t>
+          <t>Jasmina Melo</t>
         </is>
       </c>
       <c r="H533" t="inlineStr">
@@ -27209,13 +27209,13 @@
         </is>
       </c>
       <c r="I533" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J533" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K533" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
     <row r="534">
@@ -27251,7 +27251,7 @@
       </c>
       <c r="G534" t="inlineStr">
         <is>
-          <t>Luckas Andrade</t>
+          <t>Karen Saadi</t>
         </is>
       </c>
       <c r="H534" t="inlineStr">
@@ -27260,13 +27260,13 @@
         </is>
       </c>
       <c r="I534" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J534" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="K534" t="n">
-        <v>54</v>
+        <v>35</v>
       </c>
     </row>
     <row r="535">
@@ -27302,7 +27302,7 @@
       </c>
       <c r="G535" t="inlineStr">
         <is>
-          <t>Mirian Rodrigues</t>
+          <t>Luckas Andrade</t>
         </is>
       </c>
       <c r="H535" t="inlineStr">
@@ -27311,13 +27311,13 @@
         </is>
       </c>
       <c r="I535" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J535" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="K535" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="536">
@@ -27348,22 +27348,73 @@
       </c>
       <c r="F536" t="inlineStr">
         <is>
+          <t>SANTOS - EF</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>Mirian Rodrigues</t>
+        </is>
+      </c>
+      <c r="H536" t="inlineStr">
+        <is>
+          <t>Lidia Tavares</t>
+        </is>
+      </c>
+      <c r="I536" t="n">
+        <v>5</v>
+      </c>
+      <c r="J536" t="n">
+        <v>7</v>
+      </c>
+      <c r="K536" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>Terça</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
           <t>SANTOS - GC</t>
         </is>
       </c>
-      <c r="G536" t="inlineStr">
+      <c r="G537" t="inlineStr">
         <is>
           <t>Rafaella Massuia</t>
         </is>
       </c>
-      <c r="H536" t="inlineStr"/>
-      <c r="I536" t="n">
-        <v>0</v>
-      </c>
-      <c r="J536" t="n">
-        <v>0</v>
-      </c>
-      <c r="K536" t="n">
+      <c r="H537" t="inlineStr"/>
+      <c r="I537" t="n">
+        <v>0</v>
+      </c>
+      <c r="J537" t="n">
+        <v>0</v>
+      </c>
+      <c r="K537" t="n">
         <v>109</v>
       </c>
     </row>

--- a/data/historico/historico_baixas.xlsx
+++ b/data/historico/historico_baixas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K537"/>
+  <dimension ref="A1:K541"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14098,13 +14098,13 @@
       </c>
       <c r="H272" t="inlineStr"/>
       <c r="I272" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J272" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K272" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="273">
@@ -14400,13 +14400,13 @@
         </is>
       </c>
       <c r="I278" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J278" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K278" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="279">
@@ -14451,13 +14451,13 @@
         </is>
       </c>
       <c r="I279" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="J279" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="K279" t="n">
-        <v>37</v>
+        <v>51</v>
       </c>
     </row>
     <row r="280">
@@ -15141,13 +15141,13 @@
         </is>
       </c>
       <c r="I293" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J293" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K293" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="294">
@@ -15294,13 +15294,13 @@
         </is>
       </c>
       <c r="I296" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J296" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K296" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="297">
@@ -15345,13 +15345,13 @@
         </is>
       </c>
       <c r="I297" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J297" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K297" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="298">
@@ -15447,13 +15447,13 @@
         </is>
       </c>
       <c r="I299" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J299" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K299" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="300">
@@ -15649,7 +15649,7 @@
         <v>0</v>
       </c>
       <c r="K303" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="304">
@@ -15694,10 +15694,10 @@
         </is>
       </c>
       <c r="I304" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J304" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K304" t="n">
         <v>89</v>
@@ -15745,13 +15745,13 @@
         </is>
       </c>
       <c r="I305" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J305" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K305" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="306">
@@ -15796,13 +15796,13 @@
         </is>
       </c>
       <c r="I306" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J306" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K306" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="307">
@@ -16051,13 +16051,13 @@
         </is>
       </c>
       <c r="I311" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J311" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K311" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="312">
@@ -16153,13 +16153,13 @@
         </is>
       </c>
       <c r="I313" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J313" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K313" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="314">
@@ -16255,13 +16255,13 @@
         </is>
       </c>
       <c r="I315" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J315" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K315" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="316">
@@ -16408,13 +16408,13 @@
         </is>
       </c>
       <c r="I318" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J318" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K318" t="n">
-        <v>96</v>
+        <v>104</v>
       </c>
     </row>
     <row r="319">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="I321" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="J321" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="K321" t="n">
-        <v>85</v>
+        <v>101</v>
       </c>
     </row>
     <row r="322">
@@ -16612,13 +16612,13 @@
         </is>
       </c>
       <c r="I322" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J322" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K322" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="323">
@@ -16663,13 +16663,13 @@
         </is>
       </c>
       <c r="I323" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J323" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="K323" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
     </row>
     <row r="324">
@@ -16714,13 +16714,13 @@
         </is>
       </c>
       <c r="I324" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J324" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K324" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
     </row>
     <row r="325">
@@ -16765,13 +16765,13 @@
         </is>
       </c>
       <c r="I325" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="J325" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="K325" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
     </row>
     <row r="326">
@@ -16867,13 +16867,13 @@
         </is>
       </c>
       <c r="I327" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J327" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K327" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="328">
@@ -16969,13 +16969,13 @@
         </is>
       </c>
       <c r="I329" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J329" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K329" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="330">
@@ -17020,13 +17020,13 @@
         </is>
       </c>
       <c r="I330" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="J330" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="K330" t="n">
-        <v>81</v>
+        <v>91</v>
       </c>
     </row>
     <row r="331">
@@ -17071,13 +17071,13 @@
         </is>
       </c>
       <c r="I331" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J331" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K331" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="332">
@@ -17122,13 +17122,13 @@
         </is>
       </c>
       <c r="I332" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="J332" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="K332" t="n">
-        <v>86</v>
+        <v>95</v>
       </c>
     </row>
     <row r="333">
@@ -17230,7 +17230,7 @@
         <v>26</v>
       </c>
       <c r="K334" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="335">
@@ -17318,10 +17318,10 @@
       </c>
       <c r="H336" t="inlineStr"/>
       <c r="I336" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J336" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K336" t="n">
         <v>21</v>
@@ -17459,13 +17459,13 @@
       </c>
       <c r="H339" t="inlineStr"/>
       <c r="I339" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J339" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K339" t="n">
-        <v>197</v>
+        <v>200</v>
       </c>
     </row>
     <row r="340">
@@ -17710,13 +17710,13 @@
         </is>
       </c>
       <c r="I344" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J344" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K344" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="345">
@@ -18012,13 +18012,13 @@
         </is>
       </c>
       <c r="I350" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J350" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K350" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="351">
@@ -18671,13 +18671,13 @@
         </is>
       </c>
       <c r="I363" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J363" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K363" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="364">
@@ -18977,13 +18977,13 @@
         </is>
       </c>
       <c r="I369" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J369" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K369" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="370">
@@ -19640,13 +19640,13 @@
         </is>
       </c>
       <c r="I382" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="J382" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="K382" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="383">
@@ -19691,13 +19691,13 @@
         </is>
       </c>
       <c r="I383" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J383" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K383" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="384">
@@ -19997,13 +19997,13 @@
         </is>
       </c>
       <c r="I389" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J389" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K389" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="390">
@@ -20197,13 +20197,13 @@
         </is>
       </c>
       <c r="I393" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J393" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K393" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="394">
@@ -20239,22 +20239,22 @@
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>Vitor Domingues</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="I394" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="J394" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="K394" t="n">
-        <v>65</v>
+        <v>1</v>
       </c>
     </row>
     <row r="395">
@@ -20285,27 +20285,27 @@
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO PESSOAL (Outsourcing)</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>Bruna Santana</t>
+          <t>Vitor Domingues</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="I395" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="J395" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="K395" t="n">
-        <v>3</v>
+        <v>65</v>
       </c>
     </row>
     <row r="396">
@@ -20341,7 +20341,7 @@
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>Camila Oliveira</t>
+          <t>Bruna Santana</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
@@ -20350,13 +20350,13 @@
         </is>
       </c>
       <c r="I396" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J396" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K396" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="397">
@@ -20392,22 +20392,22 @@
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>Elaine Assis</t>
+          <t>Camila Oliveira</t>
         </is>
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I397" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J397" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K397" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="398">
@@ -20443,12 +20443,12 @@
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>Fabiane Branco</t>
+          <t>Elaine Assis</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I398" t="n">
@@ -20458,7 +20458,7 @@
         <v>0</v>
       </c>
       <c r="K398" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="399">
@@ -20494,22 +20494,22 @@
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>Jonas Nunes</t>
+          <t>Fabiane Branco</t>
         </is>
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I399" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J399" t="n">
         <v>1</v>
       </c>
       <c r="K399" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="400">
@@ -20540,12 +20540,12 @@
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>DEPARTAMENTO PESSOAL (Outsourcing)</t>
         </is>
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>Bruna Santana</t>
+          <t>Jonas Nunes</t>
         </is>
       </c>
       <c r="H400" t="inlineStr">
@@ -20554,13 +20554,13 @@
         </is>
       </c>
       <c r="I400" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J400" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K400" t="n">
-        <v>99</v>
+        <v>15</v>
       </c>
     </row>
     <row r="401">
@@ -20596,7 +20596,7 @@
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>Camila Oliveira</t>
+          <t>Bruna Santana</t>
         </is>
       </c>
       <c r="H401" t="inlineStr">
@@ -20605,13 +20605,13 @@
         </is>
       </c>
       <c r="I401" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J401" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K401" t="n">
-        <v>31</v>
+        <v>99</v>
       </c>
     </row>
     <row r="402">
@@ -20647,22 +20647,22 @@
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>Daniel Moraes</t>
+          <t>Camila Oliveira</t>
         </is>
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I402" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J402" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K402" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
     </row>
     <row r="403">
@@ -20698,7 +20698,7 @@
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>Danilo Xavier</t>
+          <t>Daniel Moraes</t>
         </is>
       </c>
       <c r="H403" t="inlineStr">
@@ -20710,10 +20710,10 @@
         <v>3</v>
       </c>
       <c r="J403" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K403" t="n">
-        <v>151</v>
+        <v>41</v>
       </c>
     </row>
     <row r="404">
@@ -20749,7 +20749,7 @@
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>Elaine Assis</t>
+          <t>Danilo Xavier</t>
         </is>
       </c>
       <c r="H404" t="inlineStr">
@@ -20758,13 +20758,13 @@
         </is>
       </c>
       <c r="I404" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J404" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K404" t="n">
-        <v>56</v>
+        <v>151</v>
       </c>
     </row>
     <row r="405">
@@ -20800,12 +20800,12 @@
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>Eliene Lima</t>
+          <t>Elaine Assis</t>
         </is>
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I405" t="n">
@@ -20815,7 +20815,7 @@
         <v>0</v>
       </c>
       <c r="K405" t="n">
-        <v>43</v>
+        <v>56</v>
       </c>
     </row>
     <row r="406">
@@ -20851,22 +20851,22 @@
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>Erica Oliveira</t>
+          <t>Eliene Lima</t>
         </is>
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I406" t="n">
         <v>0</v>
       </c>
       <c r="J406" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K406" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="407">
@@ -20902,22 +20902,22 @@
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>Evellin Bispo</t>
+          <t>Erica Oliveira</t>
         </is>
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>Leandro Matos</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I407" t="n">
         <v>0</v>
       </c>
       <c r="J407" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K407" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
     </row>
     <row r="408">
@@ -20953,12 +20953,12 @@
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>Fabiane Branco</t>
+          <t>Evellin Bispo</t>
         </is>
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>Leandro Matos</t>
         </is>
       </c>
       <c r="I408" t="n">
@@ -20968,7 +20968,7 @@
         <v>0</v>
       </c>
       <c r="K408" t="n">
-        <v>118</v>
+        <v>23</v>
       </c>
     </row>
     <row r="409">
@@ -21004,22 +21004,22 @@
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>Franciele Alves</t>
+          <t>Fabiane Branco</t>
         </is>
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I409" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J409" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K409" t="n">
-        <v>36</v>
+        <v>123</v>
       </c>
     </row>
     <row r="410">
@@ -21055,12 +21055,12 @@
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>Gabriela Peres</t>
+          <t>Franciele Alves</t>
         </is>
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>Leandro Matos</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I410" t="n">
@@ -21070,7 +21070,7 @@
         <v>0</v>
       </c>
       <c r="K410" t="n">
-        <v>12</v>
+        <v>38</v>
       </c>
     </row>
     <row r="411">
@@ -21106,12 +21106,12 @@
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>Grasiele Santos</t>
+          <t>Gabriela Peres</t>
         </is>
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Leandro Matos</t>
         </is>
       </c>
       <c r="I411" t="n">
@@ -21121,7 +21121,7 @@
         <v>0</v>
       </c>
       <c r="K411" t="n">
-        <v>112</v>
+        <v>12</v>
       </c>
     </row>
     <row r="412">
@@ -21157,22 +21157,22 @@
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Grasiele Santos</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I412" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J412" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K412" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="413">
@@ -21208,22 +21208,22 @@
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>Janaina Rocha</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I413" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J413" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K413" t="n">
-        <v>84</v>
+        <v>110</v>
       </c>
     </row>
     <row r="414">
@@ -21259,22 +21259,22 @@
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>Jayne Tavares</t>
+          <t>Janaina Rocha</t>
         </is>
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I414" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J414" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K414" t="n">
-        <v>127</v>
+        <v>86</v>
       </c>
     </row>
     <row r="415">
@@ -21310,22 +21310,22 @@
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>Jhenifer Tenorio</t>
+          <t>Jayne Tavares</t>
         </is>
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I415" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J415" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K415" t="n">
-        <v>113</v>
+        <v>127</v>
       </c>
     </row>
     <row r="416">
@@ -21361,7 +21361,7 @@
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>Jonas Nunes</t>
+          <t>Jhenifer Tenorio</t>
         </is>
       </c>
       <c r="H416" t="inlineStr">
@@ -21370,13 +21370,13 @@
         </is>
       </c>
       <c r="I416" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J416" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K416" t="n">
-        <v>85</v>
+        <v>114</v>
       </c>
     </row>
     <row r="417">
@@ -21412,22 +21412,22 @@
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>Kaique Souza</t>
+          <t>Jonas Nunes</t>
         </is>
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I417" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J417" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="K417" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
     </row>
     <row r="418">
@@ -21463,7 +21463,7 @@
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>Karine Sousa</t>
+          <t>Kaique Souza</t>
         </is>
       </c>
       <c r="H418" t="inlineStr">
@@ -21472,13 +21472,13 @@
         </is>
       </c>
       <c r="I418" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="J418" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="K418" t="n">
-        <v>54</v>
+        <v>78</v>
       </c>
     </row>
     <row r="419">
@@ -21514,22 +21514,22 @@
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>Laysla Alves</t>
+          <t>Karine Sousa</t>
         </is>
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I419" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J419" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K419" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="420">
@@ -21565,22 +21565,22 @@
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>Luana Marques</t>
+          <t>Laysla Alves</t>
         </is>
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I420" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J420" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K420" t="n">
-        <v>17</v>
+        <v>58</v>
       </c>
     </row>
     <row r="421">
@@ -21616,7 +21616,7 @@
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>Maria Pires</t>
+          <t>Luana Marques</t>
         </is>
       </c>
       <c r="H421" t="inlineStr">
@@ -21631,7 +21631,7 @@
         <v>0</v>
       </c>
       <c r="K421" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="422">
@@ -21667,22 +21667,22 @@
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>Mauricio Lermen</t>
+          <t>Maria Pires</t>
         </is>
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>Mauricio Lermen</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I422" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J422" t="n">
+        <v>2</v>
+      </c>
+      <c r="K422" t="n">
         <v>1</v>
-      </c>
-      <c r="K422" t="n">
-        <v>13</v>
       </c>
     </row>
     <row r="423">
@@ -21718,22 +21718,22 @@
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>Micaele Cordeiro</t>
+          <t>Mauricio Lermen</t>
         </is>
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>Mauricio Lermen</t>
         </is>
       </c>
       <c r="I423" t="n">
         <v>0</v>
       </c>
       <c r="J423" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K423" t="n">
-        <v>84</v>
+        <v>13</v>
       </c>
     </row>
     <row r="424">
@@ -21769,7 +21769,7 @@
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>Michele Silva</t>
+          <t>Micaele Cordeiro</t>
         </is>
       </c>
       <c r="H424" t="inlineStr">
@@ -21778,13 +21778,13 @@
         </is>
       </c>
       <c r="I424" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J424" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K424" t="n">
-        <v>67</v>
+        <v>84</v>
       </c>
     </row>
     <row r="425">
@@ -21820,22 +21820,22 @@
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>Murilo Marques</t>
+          <t>Michele Silva</t>
         </is>
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I425" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J425" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K425" t="n">
-        <v>42</v>
+        <v>67</v>
       </c>
     </row>
     <row r="426">
@@ -21871,22 +21871,18 @@
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>Natalia Batista</t>
-        </is>
-      </c>
-      <c r="H426" t="inlineStr">
-        <is>
-          <t>Edivaldo Veiga</t>
-        </is>
-      </c>
+          <t>Mikael Teixeira</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr"/>
       <c r="I426" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="J426" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="K426" t="n">
-        <v>102</v>
+        <v>4</v>
       </c>
     </row>
     <row r="427">
@@ -21922,7 +21918,7 @@
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>Natalia Silva</t>
+          <t>Murilo Marques</t>
         </is>
       </c>
       <c r="H427" t="inlineStr">
@@ -21931,13 +21927,13 @@
         </is>
       </c>
       <c r="I427" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J427" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K427" t="n">
-        <v>103</v>
+        <v>42</v>
       </c>
     </row>
     <row r="428">
@@ -21973,22 +21969,22 @@
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>Oliene Mariano</t>
+          <t>Natalia Batista</t>
         </is>
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I428" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="J428" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="K428" t="n">
-        <v>73</v>
+        <v>102</v>
       </c>
     </row>
     <row r="429">
@@ -22024,22 +22020,22 @@
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>Priscila Aguiar</t>
+          <t>Natalia Silva</t>
         </is>
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I429" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J429" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K429" t="n">
-        <v>61</v>
+        <v>103</v>
       </c>
     </row>
     <row r="430">
@@ -22075,22 +22071,22 @@
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>Rebeca Ribeiro</t>
+          <t>Oliene Mariano</t>
         </is>
       </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I430" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J430" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K430" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
     </row>
     <row r="431">
@@ -22126,7 +22122,7 @@
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>Roberta Souza</t>
+          <t>Priscila Aguiar</t>
         </is>
       </c>
       <c r="H431" t="inlineStr">
@@ -22138,10 +22134,10 @@
         <v>0</v>
       </c>
       <c r="J431" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K431" t="n">
-        <v>76</v>
+        <v>61</v>
       </c>
     </row>
     <row r="432">
@@ -22177,7 +22173,7 @@
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>Ronildo Santos</t>
+          <t>Rebeca Ribeiro</t>
         </is>
       </c>
       <c r="H432" t="inlineStr">
@@ -22186,13 +22182,13 @@
         </is>
       </c>
       <c r="I432" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J432" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K432" t="n">
-        <v>4</v>
+        <v>66</v>
       </c>
     </row>
     <row r="433">
@@ -22228,22 +22224,22 @@
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>Rozania Santos</t>
+          <t>Roberta Souza</t>
         </is>
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I433" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J433" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K433" t="n">
-        <v>99</v>
+        <v>76</v>
       </c>
     </row>
     <row r="434">
@@ -22279,22 +22275,22 @@
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>Santos Karina</t>
+          <t>Ronildo Santos</t>
         </is>
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>Leandro Matos</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I434" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J434" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K434" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="435">
@@ -22330,7 +22326,7 @@
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>Sibelly Pereira</t>
+          <t>Rozania Santos</t>
         </is>
       </c>
       <c r="H435" t="inlineStr">
@@ -22339,13 +22335,13 @@
         </is>
       </c>
       <c r="I435" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J435" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K435" t="n">
-        <v>41</v>
+        <v>106</v>
       </c>
     </row>
     <row r="436">
@@ -22381,22 +22377,22 @@
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>Tania Luz</t>
+          <t>Santos Karina</t>
         </is>
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>Leandro Matos</t>
         </is>
       </c>
       <c r="I436" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J436" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K436" t="n">
-        <v>54</v>
+        <v>2</v>
       </c>
     </row>
     <row r="437">
@@ -22432,7 +22428,7 @@
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>Vitor Guedes</t>
+          <t>Sibelly Pereira</t>
         </is>
       </c>
       <c r="H437" t="inlineStr">
@@ -22441,13 +22437,13 @@
         </is>
       </c>
       <c r="I437" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J437" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K437" t="n">
-        <v>134</v>
+        <v>42</v>
       </c>
     </row>
     <row r="438">
@@ -22478,27 +22474,27 @@
       </c>
       <c r="F438" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>Andrea Medeiros</t>
+          <t>Tania Luz</t>
         </is>
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I438" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J438" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="K438" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="439">
@@ -22529,27 +22525,27 @@
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>Caroline Nascimento</t>
+          <t>Vitor Guedes</t>
         </is>
       </c>
       <c r="H439" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I439" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J439" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K439" t="n">
-        <v>76</v>
+        <v>134</v>
       </c>
     </row>
     <row r="440">
@@ -22585,7 +22581,7 @@
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>Cristiana Grizostomo</t>
+          <t>Andrea Medeiros</t>
         </is>
       </c>
       <c r="H440" t="inlineStr">
@@ -22594,13 +22590,13 @@
         </is>
       </c>
       <c r="I440" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J440" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="K440" t="n">
-        <v>37</v>
+        <v>55</v>
       </c>
     </row>
     <row r="441">
@@ -22636,18 +22632,22 @@
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>Denis Reis</t>
-        </is>
-      </c>
-      <c r="H441" t="inlineStr"/>
+          <t>Caroline Nascimento</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
       <c r="I441" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="J441" t="n">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="K441" t="n">
-        <v>79</v>
+        <v>122</v>
       </c>
     </row>
     <row r="442">
@@ -22683,7 +22683,7 @@
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>Eliane Moreira</t>
+          <t>Cristiana Grizostomo</t>
         </is>
       </c>
       <c r="H442" t="inlineStr">
@@ -22692,13 +22692,13 @@
         </is>
       </c>
       <c r="I442" t="n">
+        <v>13</v>
+      </c>
+      <c r="J442" t="n">
         <v>14</v>
       </c>
-      <c r="J442" t="n">
-        <v>28</v>
-      </c>
       <c r="K442" t="n">
-        <v>89</v>
+        <v>45</v>
       </c>
     </row>
     <row r="443">
@@ -22734,22 +22734,18 @@
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>Gustavo Tonan</t>
-        </is>
-      </c>
-      <c r="H443" t="inlineStr">
-        <is>
-          <t>Nayara Oliveira</t>
-        </is>
-      </c>
+          <t>Denis Reis</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr"/>
       <c r="I443" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J443" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="K443" t="n">
-        <v>56</v>
+        <v>79</v>
       </c>
     </row>
     <row r="444">
@@ -22785,7 +22781,7 @@
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>Jonatan Hayashibara</t>
+          <t>Eliane Moreira</t>
         </is>
       </c>
       <c r="H444" t="inlineStr">
@@ -22794,13 +22790,13 @@
         </is>
       </c>
       <c r="I444" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="J444" t="n">
-        <v>68</v>
+        <v>29</v>
       </c>
       <c r="K444" t="n">
-        <v>180</v>
+        <v>90</v>
       </c>
     </row>
     <row r="445">
@@ -22836,7 +22832,7 @@
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>Lais Arruda</t>
+          <t>Gustavo Tonan</t>
         </is>
       </c>
       <c r="H445" t="inlineStr">
@@ -22845,13 +22841,13 @@
         </is>
       </c>
       <c r="I445" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="J445" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="K445" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
     </row>
     <row r="446">
@@ -22887,7 +22883,7 @@
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>Luan Batista</t>
+          <t>Jonatan Hayashibara</t>
         </is>
       </c>
       <c r="H446" t="inlineStr">
@@ -22896,13 +22892,13 @@
         </is>
       </c>
       <c r="I446" t="n">
-        <v>4</v>
+        <v>99</v>
       </c>
       <c r="J446" t="n">
-        <v>4</v>
+        <v>165</v>
       </c>
       <c r="K446" t="n">
-        <v>42</v>
+        <v>277</v>
       </c>
     </row>
     <row r="447">
@@ -22938,7 +22934,7 @@
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>Maria Garcia</t>
+          <t>Lais Arruda</t>
         </is>
       </c>
       <c r="H447" t="inlineStr">
@@ -22947,13 +22943,13 @@
         </is>
       </c>
       <c r="I447" t="n">
+        <v>2</v>
+      </c>
+      <c r="J447" t="n">
         <v>3</v>
       </c>
-      <c r="J447" t="n">
-        <v>18</v>
-      </c>
       <c r="K447" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
     </row>
     <row r="448">
@@ -22989,7 +22985,7 @@
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>Priscila Volpe</t>
+          <t>Luan Batista</t>
         </is>
       </c>
       <c r="H448" t="inlineStr">
@@ -22998,13 +22994,13 @@
         </is>
       </c>
       <c r="I448" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J448" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K448" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
     </row>
     <row r="449">
@@ -23040,7 +23036,7 @@
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>Rodrigo Souza</t>
+          <t>Maria Garcia</t>
         </is>
       </c>
       <c r="H449" t="inlineStr">
@@ -23049,13 +23045,13 @@
         </is>
       </c>
       <c r="I449" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J449" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="K449" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="450">
@@ -23091,7 +23087,7 @@
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>Romario Silva</t>
+          <t>Priscila Volpe</t>
         </is>
       </c>
       <c r="H450" t="inlineStr">
@@ -23100,13 +23096,13 @@
         </is>
       </c>
       <c r="I450" t="n">
+        <v>0</v>
+      </c>
+      <c r="J450" t="n">
+        <v>0</v>
+      </c>
+      <c r="K450" t="n">
         <v>10</v>
-      </c>
-      <c r="J450" t="n">
-        <v>11</v>
-      </c>
-      <c r="K450" t="n">
-        <v>136</v>
       </c>
     </row>
     <row r="451">
@@ -23142,7 +23138,7 @@
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>Rosilene Santos</t>
+          <t>Rodrigo Souza</t>
         </is>
       </c>
       <c r="H451" t="inlineStr">
@@ -23151,13 +23147,13 @@
         </is>
       </c>
       <c r="I451" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J451" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K451" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
     </row>
     <row r="452">
@@ -23193,7 +23189,7 @@
       </c>
       <c r="G452" t="inlineStr">
         <is>
-          <t>Suede Gomes</t>
+          <t>Romario Silva</t>
         </is>
       </c>
       <c r="H452" t="inlineStr">
@@ -23202,13 +23198,13 @@
         </is>
       </c>
       <c r="I452" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J452" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K452" t="n">
-        <v>28</v>
+        <v>141</v>
       </c>
     </row>
     <row r="453">
@@ -23244,7 +23240,7 @@
       </c>
       <c r="G453" t="inlineStr">
         <is>
-          <t>Taina Silva</t>
+          <t>Rosilene Santos</t>
         </is>
       </c>
       <c r="H453" t="inlineStr">
@@ -23253,13 +23249,13 @@
         </is>
       </c>
       <c r="I453" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="J453" t="n">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="K453" t="n">
-        <v>24</v>
+        <v>74</v>
       </c>
     </row>
     <row r="454">
@@ -23295,7 +23291,7 @@
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>Thayna Melo</t>
+          <t>Suede Gomes</t>
         </is>
       </c>
       <c r="H454" t="inlineStr">
@@ -23304,13 +23300,13 @@
         </is>
       </c>
       <c r="I454" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J454" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K454" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="455">
@@ -23346,7 +23342,7 @@
       </c>
       <c r="G455" t="inlineStr">
         <is>
-          <t>Vanessa Santana</t>
+          <t>Taina Silva</t>
         </is>
       </c>
       <c r="H455" t="inlineStr">
@@ -23355,13 +23351,13 @@
         </is>
       </c>
       <c r="I455" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J455" t="n">
         <v>7</v>
       </c>
       <c r="K455" t="n">
-        <v>125</v>
+        <v>24</v>
       </c>
     </row>
     <row r="456">
@@ -23392,27 +23388,27 @@
       </c>
       <c r="F456" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="G456" t="inlineStr">
         <is>
-          <t>Alaine Neres</t>
+          <t>Thayna Melo</t>
         </is>
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
       <c r="I456" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J456" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="K456" t="n">
-        <v>81</v>
+        <v>40</v>
       </c>
     </row>
     <row r="457">
@@ -23443,27 +23439,27 @@
       </c>
       <c r="F457" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>Andre Silva</t>
+          <t>Vanessa Santana</t>
         </is>
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
       <c r="I457" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="J457" t="n">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="K457" t="n">
-        <v>60</v>
+        <v>152</v>
       </c>
     </row>
     <row r="458">
@@ -23499,22 +23495,22 @@
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>Anna Ramalho</t>
+          <t>Alaine Neres</t>
         </is>
       </c>
       <c r="H458" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I458" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="J458" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="K458" t="n">
-        <v>63</v>
+        <v>81</v>
       </c>
     </row>
     <row r="459">
@@ -23550,22 +23546,22 @@
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>Beatriz Ferreira</t>
+          <t>Andre Silva</t>
         </is>
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I459" t="n">
         <v>3</v>
       </c>
       <c r="J459" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K459" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
     </row>
     <row r="460">
@@ -23601,22 +23597,22 @@
       </c>
       <c r="G460" t="inlineStr">
         <is>
-          <t>Brenda Batista</t>
+          <t>Anna Ramalho</t>
         </is>
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="I460" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J460" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="K460" t="n">
-        <v>43</v>
+        <v>63</v>
       </c>
     </row>
     <row r="461">
@@ -23652,22 +23648,22 @@
       </c>
       <c r="G461" t="inlineStr">
         <is>
-          <t>Bruna Souza</t>
+          <t>Beatriz Ferreira</t>
         </is>
       </c>
       <c r="H461" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="I461" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J461" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K461" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="462">
@@ -23703,22 +23699,22 @@
       </c>
       <c r="G462" t="inlineStr">
         <is>
-          <t>Bruno Henrique</t>
+          <t>Brenda Batista</t>
         </is>
       </c>
       <c r="H462" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I462" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J462" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="K462" t="n">
-        <v>80</v>
+        <v>46</v>
       </c>
     </row>
     <row r="463">
@@ -23754,18 +23750,22 @@
       </c>
       <c r="G463" t="inlineStr">
         <is>
-          <t>Claudineia Rodrigues</t>
-        </is>
-      </c>
-      <c r="H463" t="inlineStr"/>
+          <t>Bruna Souza</t>
+        </is>
+      </c>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>Thaiza Oliveira</t>
+        </is>
+      </c>
       <c r="I463" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="J463" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="K463" t="n">
-        <v>115</v>
+        <v>71</v>
       </c>
     </row>
     <row r="464">
@@ -23801,22 +23801,22 @@
       </c>
       <c r="G464" t="inlineStr">
         <is>
-          <t>Cristina Leite</t>
+          <t>Bruno Henrique</t>
         </is>
       </c>
       <c r="H464" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I464" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J464" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K464" t="n">
-        <v>101</v>
+        <v>84</v>
       </c>
     </row>
     <row r="465">
@@ -23852,22 +23852,18 @@
       </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t>Davi Santos</t>
-        </is>
-      </c>
-      <c r="H465" t="inlineStr">
-        <is>
-          <t>Thaiza Oliveira</t>
-        </is>
-      </c>
+          <t>Claudineia Rodrigues</t>
+        </is>
+      </c>
+      <c r="H465" t="inlineStr"/>
       <c r="I465" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J465" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K465" t="n">
-        <v>84</v>
+        <v>120</v>
       </c>
     </row>
     <row r="466">
@@ -23903,22 +23899,22 @@
       </c>
       <c r="G466" t="inlineStr">
         <is>
-          <t>Deleia Oliveira</t>
+          <t>Cristina Leite</t>
         </is>
       </c>
       <c r="H466" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="I466" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="J466" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="K466" t="n">
-        <v>72</v>
+        <v>117</v>
       </c>
     </row>
     <row r="467">
@@ -23954,7 +23950,7 @@
       </c>
       <c r="G467" t="inlineStr">
         <is>
-          <t>Diego Pereira</t>
+          <t>Davi Santos</t>
         </is>
       </c>
       <c r="H467" t="inlineStr">
@@ -23963,13 +23959,13 @@
         </is>
       </c>
       <c r="I467" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J467" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="K467" t="n">
-        <v>65</v>
+        <v>84</v>
       </c>
     </row>
     <row r="468">
@@ -24005,22 +24001,22 @@
       </c>
       <c r="G468" t="inlineStr">
         <is>
-          <t>Eduardo Lopes</t>
+          <t>Deleia Oliveira</t>
         </is>
       </c>
       <c r="H468" t="inlineStr">
         <is>
-          <t>Idna Sousa</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I468" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="J468" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="K468" t="n">
-        <v>14</v>
+        <v>77</v>
       </c>
     </row>
     <row r="469">
@@ -24056,22 +24052,22 @@
       </c>
       <c r="G469" t="inlineStr">
         <is>
-          <t>Gislaine Lima</t>
+          <t>Diego Pereira</t>
         </is>
       </c>
       <c r="H469" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I469" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J469" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K469" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
     </row>
     <row r="470">
@@ -24107,22 +24103,22 @@
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>Gustavo Santos</t>
+          <t>Eduardo Lopes</t>
         </is>
       </c>
       <c r="H470" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Idna Sousa</t>
         </is>
       </c>
       <c r="I470" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J470" t="n">
+        <v>1</v>
+      </c>
+      <c r="K470" t="n">
         <v>14</v>
-      </c>
-      <c r="K470" t="n">
-        <v>129</v>
       </c>
     </row>
     <row r="471">
@@ -24158,22 +24154,22 @@
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>Igor Valezi</t>
+          <t>Gislaine Lima</t>
         </is>
       </c>
       <c r="H471" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I471" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J471" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="K471" t="n">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="472">
@@ -24209,22 +24205,22 @@
       </c>
       <c r="G472" t="inlineStr">
         <is>
-          <t>Izabely Araujo</t>
+          <t>Gustavo Santos</t>
         </is>
       </c>
       <c r="H472" t="inlineStr">
         <is>
-          <t>Idna Sousa</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="I472" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J472" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K472" t="n">
-        <v>4</v>
+        <v>131</v>
       </c>
     </row>
     <row r="473">
@@ -24260,22 +24256,22 @@
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t>Joanna Costa</t>
+          <t>Igor Valezi</t>
         </is>
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I473" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J473" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K473" t="n">
-        <v>14</v>
+        <v>74</v>
       </c>
     </row>
     <row r="474">
@@ -24311,22 +24307,22 @@
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>Jose Natan</t>
+          <t>Izabely Araujo</t>
         </is>
       </c>
       <c r="H474" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Idna Sousa</t>
         </is>
       </c>
       <c r="I474" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J474" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K474" t="n">
-        <v>88</v>
+        <v>4</v>
       </c>
     </row>
     <row r="475">
@@ -24362,22 +24358,22 @@
       </c>
       <c r="G475" t="inlineStr">
         <is>
-          <t>João Oliveira</t>
+          <t>Joanna Costa</t>
         </is>
       </c>
       <c r="H475" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I475" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J475" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K475" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="476">
@@ -24413,22 +24409,22 @@
       </c>
       <c r="G476" t="inlineStr">
         <is>
-          <t>Juan Ribeiro</t>
+          <t>Jose Natan</t>
         </is>
       </c>
       <c r="H476" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I476" t="n">
         <v>25</v>
       </c>
       <c r="J476" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K476" t="n">
-        <v>75</v>
+        <v>93</v>
       </c>
     </row>
     <row r="477">
@@ -24464,7 +24460,7 @@
       </c>
       <c r="G477" t="inlineStr">
         <is>
-          <t>Juliana Valeria</t>
+          <t>João Oliveira</t>
         </is>
       </c>
       <c r="H477" t="inlineStr">
@@ -24473,13 +24469,13 @@
         </is>
       </c>
       <c r="I477" t="n">
+        <v>1</v>
+      </c>
+      <c r="J477" t="n">
+        <v>1</v>
+      </c>
+      <c r="K477" t="n">
         <v>9</v>
-      </c>
-      <c r="J477" t="n">
-        <v>21</v>
-      </c>
-      <c r="K477" t="n">
-        <v>83</v>
       </c>
     </row>
     <row r="478">
@@ -24515,22 +24511,22 @@
       </c>
       <c r="G478" t="inlineStr">
         <is>
-          <t>Juliane Vaz</t>
+          <t>Juan Ribeiro</t>
         </is>
       </c>
       <c r="H478" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I478" t="n">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="J478" t="n">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="K478" t="n">
-        <v>157</v>
+        <v>77</v>
       </c>
     </row>
     <row r="479">
@@ -24566,22 +24562,22 @@
       </c>
       <c r="G479" t="inlineStr">
         <is>
-          <t>Katia Xavier</t>
+          <t>Juliana Valeria</t>
         </is>
       </c>
       <c r="H479" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I479" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J479" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="K479" t="n">
-        <v>59</v>
+        <v>84</v>
       </c>
     </row>
     <row r="480">
@@ -24617,22 +24613,22 @@
       </c>
       <c r="G480" t="inlineStr">
         <is>
-          <t>Larissa Félix</t>
+          <t>Juliane Vaz</t>
         </is>
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I480" t="n">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="J480" t="n">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="K480" t="n">
-        <v>95</v>
+        <v>160</v>
       </c>
     </row>
     <row r="481">
@@ -24668,7 +24664,7 @@
       </c>
       <c r="G481" t="inlineStr">
         <is>
-          <t>Léia de Oliveira</t>
+          <t>Katia Xavier</t>
         </is>
       </c>
       <c r="H481" t="inlineStr">
@@ -24683,7 +24679,7 @@
         <v>9</v>
       </c>
       <c r="K481" t="n">
-        <v>95</v>
+        <v>61</v>
       </c>
     </row>
     <row r="482">
@@ -24719,22 +24715,22 @@
       </c>
       <c r="G482" t="inlineStr">
         <is>
-          <t>Maria Gualberto</t>
+          <t>Larissa Félix</t>
         </is>
       </c>
       <c r="H482" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I482" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="J482" t="n">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="K482" t="n">
-        <v>92</v>
+        <v>105</v>
       </c>
     </row>
     <row r="483">
@@ -24770,22 +24766,22 @@
       </c>
       <c r="G483" t="inlineStr">
         <is>
-          <t>Priscila Moreira</t>
+          <t>Léia de Oliveira</t>
         </is>
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I483" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="J483" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K483" t="n">
-        <v>76</v>
+        <v>99</v>
       </c>
     </row>
     <row r="484">
@@ -24821,22 +24817,22 @@
       </c>
       <c r="G484" t="inlineStr">
         <is>
-          <t>Regiane Santos</t>
+          <t>Maria Gualberto</t>
         </is>
       </c>
       <c r="H484" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I484" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J484" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="K484" t="n">
-        <v>52</v>
+        <v>94</v>
       </c>
     </row>
     <row r="485">
@@ -24872,22 +24868,22 @@
       </c>
       <c r="G485" t="inlineStr">
         <is>
-          <t>Shofia Gomes</t>
+          <t>Nathany Silva</t>
         </is>
       </c>
       <c r="H485" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I485" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J485" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K485" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
     </row>
     <row r="486">
@@ -24923,22 +24919,22 @@
       </c>
       <c r="G486" t="inlineStr">
         <is>
-          <t>Vanessa Tavares</t>
+          <t>Priscila Moreira</t>
         </is>
       </c>
       <c r="H486" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="I486" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J486" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="K486" t="n">
-        <v>47</v>
+        <v>78</v>
       </c>
     </row>
     <row r="487">
@@ -24974,7 +24970,7 @@
       </c>
       <c r="G487" t="inlineStr">
         <is>
-          <t>Willian Luz</t>
+          <t>Regiane Santos</t>
         </is>
       </c>
       <c r="H487" t="inlineStr">
@@ -24986,10 +24982,10 @@
         <v>1</v>
       </c>
       <c r="J487" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K487" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="488">
@@ -25025,22 +25021,22 @@
       </c>
       <c r="G488" t="inlineStr">
         <is>
-          <t>Yasmim Oliveira</t>
+          <t>Shofia Gomes</t>
         </is>
       </c>
       <c r="H488" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="I488" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J488" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K488" t="n">
-        <v>33</v>
+        <v>97</v>
       </c>
     </row>
     <row r="489">
@@ -25071,23 +25067,27 @@
       </c>
       <c r="F489" t="inlineStr">
         <is>
-          <t>ESCRITA FISCAL (Outsourcing)</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="G489" t="inlineStr">
         <is>
-          <t>Claudineia Rodrigues</t>
-        </is>
-      </c>
-      <c r="H489" t="inlineStr"/>
+          <t>Vanessa Tavares</t>
+        </is>
+      </c>
+      <c r="H489" t="inlineStr">
+        <is>
+          <t>Larice Souza</t>
+        </is>
+      </c>
       <c r="I489" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J489" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K489" t="n">
-        <v>2</v>
+        <v>47</v>
       </c>
     </row>
     <row r="490">
@@ -25118,27 +25118,27 @@
       </c>
       <c r="F490" t="inlineStr">
         <is>
-          <t>ESCRITA FISCAL (Outsourcing)</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="G490" t="inlineStr">
         <is>
-          <t>Diego Pereira</t>
+          <t>Willian Luz</t>
         </is>
       </c>
       <c r="H490" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I490" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J490" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K490" t="n">
-        <v>6</v>
+        <v>56</v>
       </c>
     </row>
     <row r="491">
@@ -25169,27 +25169,27 @@
       </c>
       <c r="F491" t="inlineStr">
         <is>
-          <t>ESCRITA FISCAL (Outsourcing)</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="G491" t="inlineStr">
         <is>
-          <t>Gislaine Lima</t>
+          <t>Yasmim Oliveira</t>
         </is>
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I491" t="n">
         <v>1</v>
       </c>
       <c r="J491" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K491" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="492">
@@ -25225,22 +25225,18 @@
       </c>
       <c r="G492" t="inlineStr">
         <is>
-          <t>Joanna Costa</t>
-        </is>
-      </c>
-      <c r="H492" t="inlineStr">
-        <is>
-          <t>Lorrane Santos</t>
-        </is>
-      </c>
+          <t>Claudineia Rodrigues</t>
+        </is>
+      </c>
+      <c r="H492" t="inlineStr"/>
       <c r="I492" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="J492" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="K492" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
     </row>
     <row r="493">
@@ -25276,22 +25272,22 @@
       </c>
       <c r="G493" t="inlineStr">
         <is>
-          <t>João Oliveira</t>
+          <t>Diego Pereira</t>
         </is>
       </c>
       <c r="H493" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I493" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J493" t="n">
+        <v>2</v>
+      </c>
+      <c r="K493" t="n">
         <v>6</v>
-      </c>
-      <c r="K493" t="n">
-        <v>37</v>
       </c>
     </row>
     <row r="494">
@@ -25327,22 +25323,22 @@
       </c>
       <c r="G494" t="inlineStr">
         <is>
-          <t>Regiane Santos</t>
+          <t>Gislaine Lima</t>
         </is>
       </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I494" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J494" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K494" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="495">
@@ -25378,22 +25374,22 @@
       </c>
       <c r="G495" t="inlineStr">
         <is>
-          <t>Yasmim Oliveira</t>
+          <t>Joanna Costa</t>
         </is>
       </c>
       <c r="H495" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I495" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="J495" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K495" t="n">
-        <v>4</v>
+        <v>39</v>
       </c>
     </row>
     <row r="496">
@@ -25424,23 +25420,27 @@
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>FIN - CONTÁBIL</t>
+          <t>ESCRITA FISCAL (Outsourcing)</t>
         </is>
       </c>
       <c r="G496" t="inlineStr">
         <is>
-          <t>Daniele Faria</t>
-        </is>
-      </c>
-      <c r="H496" t="inlineStr"/>
+          <t>João Oliveira</t>
+        </is>
+      </c>
+      <c r="H496" t="inlineStr">
+        <is>
+          <t>Larice Souza</t>
+        </is>
+      </c>
       <c r="I496" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="J496" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="K496" t="n">
-        <v>59</v>
+        <v>37</v>
       </c>
     </row>
     <row r="497">
@@ -25471,23 +25471,27 @@
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>ESCRITA FISCAL (Outsourcing)</t>
         </is>
       </c>
       <c r="G497" t="inlineStr">
         <is>
-          <t>Ana Santana</t>
-        </is>
-      </c>
-      <c r="H497" t="inlineStr"/>
+          <t>Regiane Santos</t>
+        </is>
+      </c>
+      <c r="H497" t="inlineStr">
+        <is>
+          <t>Larice Souza</t>
+        </is>
+      </c>
       <c r="I497" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J497" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="K497" t="n">
-        <v>394</v>
+        <v>13</v>
       </c>
     </row>
     <row r="498">
@@ -25518,15 +25522,19 @@
       </c>
       <c r="F498" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>ESCRITA FISCAL (Outsourcing)</t>
         </is>
       </c>
       <c r="G498" t="inlineStr">
         <is>
-          <t>Andre Coelho</t>
-        </is>
-      </c>
-      <c r="H498" t="inlineStr"/>
+          <t>Yasmim Oliveira</t>
+        </is>
+      </c>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>Larice Souza</t>
+        </is>
+      </c>
       <c r="I498" t="n">
         <v>0</v>
       </c>
@@ -25534,7 +25542,7 @@
         <v>0</v>
       </c>
       <c r="K498" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="499">
@@ -25565,23 +25573,23 @@
       </c>
       <c r="F499" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>FIN - CONTÁBIL</t>
         </is>
       </c>
       <c r="G499" t="inlineStr">
         <is>
-          <t>Bianca Castro</t>
+          <t>Daniele Faria</t>
         </is>
       </c>
       <c r="H499" t="inlineStr"/>
       <c r="I499" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J499" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="K499" t="n">
-        <v>324</v>
+        <v>62</v>
       </c>
     </row>
     <row r="500">
@@ -25617,18 +25625,18 @@
       </c>
       <c r="G500" t="inlineStr">
         <is>
-          <t>Bruna Costa</t>
+          <t>Ana Santana</t>
         </is>
       </c>
       <c r="H500" t="inlineStr"/>
       <c r="I500" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J500" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="K500" t="n">
-        <v>34</v>
+        <v>394</v>
       </c>
     </row>
     <row r="501">
@@ -25664,18 +25672,18 @@
       </c>
       <c r="G501" t="inlineStr">
         <is>
-          <t>Daniela Silva</t>
+          <t>Andre Coelho</t>
         </is>
       </c>
       <c r="H501" t="inlineStr"/>
       <c r="I501" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J501" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K501" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="502">
@@ -25711,18 +25719,18 @@
       </c>
       <c r="G502" t="inlineStr">
         <is>
-          <t>Isabelli Afonso</t>
+          <t>Bianca Castro</t>
         </is>
       </c>
       <c r="H502" t="inlineStr"/>
       <c r="I502" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J502" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K502" t="n">
-        <v>29</v>
+        <v>325</v>
       </c>
     </row>
     <row r="503">
@@ -25758,18 +25766,18 @@
       </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t>Jurema Damacena - SAC</t>
+          <t>Bruna Costa</t>
         </is>
       </c>
       <c r="H503" t="inlineStr"/>
       <c r="I503" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J503" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K503" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
     </row>
     <row r="504">
@@ -25805,18 +25813,18 @@
       </c>
       <c r="G504" t="inlineStr">
         <is>
-          <t>Leticia Queiroz</t>
+          <t>Daniela Silva</t>
         </is>
       </c>
       <c r="H504" t="inlineStr"/>
       <c r="I504" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="J504" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="K504" t="n">
-        <v>47</v>
+        <v>11</v>
       </c>
     </row>
     <row r="505">
@@ -25852,18 +25860,18 @@
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Isabelli Afonso</t>
         </is>
       </c>
       <c r="H505" t="inlineStr"/>
       <c r="I505" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J505" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K505" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
     </row>
     <row r="506">
@@ -25899,18 +25907,18 @@
       </c>
       <c r="G506" t="inlineStr">
         <is>
-          <t>Victoria Virgens</t>
+          <t>Jurema Damacena - SAC</t>
         </is>
       </c>
       <c r="H506" t="inlineStr"/>
       <c r="I506" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J506" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K506" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="507">
@@ -25946,18 +25954,18 @@
       </c>
       <c r="G507" t="inlineStr">
         <is>
-          <t>Yasmin Peixoto</t>
+          <t>Leticia Queiroz</t>
         </is>
       </c>
       <c r="H507" t="inlineStr"/>
       <c r="I507" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J507" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K507" t="n">
-        <v>263</v>
+        <v>47</v>
       </c>
     </row>
     <row r="508">
@@ -25988,12 +25996,12 @@
       </c>
       <c r="F508" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="G508" t="inlineStr">
         <is>
-          <t>Andre Coelho</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="H508" t="inlineStr"/>
@@ -26004,7 +26012,7 @@
         <v>0</v>
       </c>
       <c r="K508" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="509">
@@ -26035,23 +26043,23 @@
       </c>
       <c r="F509" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="G509" t="inlineStr">
         <is>
-          <t>Beatriz Rangel</t>
+          <t>Victoria Virgens</t>
         </is>
       </c>
       <c r="H509" t="inlineStr"/>
       <c r="I509" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J509" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K509" t="n">
-        <v>264</v>
+        <v>11</v>
       </c>
     </row>
     <row r="510">
@@ -26082,12 +26090,12 @@
       </c>
       <c r="F510" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="G510" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
+          <t>Yasmin Peixoto</t>
         </is>
       </c>
       <c r="H510" t="inlineStr"/>
@@ -26095,10 +26103,10 @@
         <v>0</v>
       </c>
       <c r="J510" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="K510" t="n">
-        <v>147</v>
+        <v>263</v>
       </c>
     </row>
     <row r="511">
@@ -26134,7 +26142,7 @@
       </c>
       <c r="G511" t="inlineStr">
         <is>
-          <t>Cristiane Simões</t>
+          <t>Andre Coelho</t>
         </is>
       </c>
       <c r="H511" t="inlineStr"/>
@@ -26145,7 +26153,7 @@
         <v>0</v>
       </c>
       <c r="K511" t="n">
-        <v>173</v>
+        <v>4</v>
       </c>
     </row>
     <row r="512">
@@ -26181,18 +26189,18 @@
       </c>
       <c r="G512" t="inlineStr">
         <is>
-          <t>Daniel Oliveira</t>
+          <t>Beatriz Rangel</t>
         </is>
       </c>
       <c r="H512" t="inlineStr"/>
       <c r="I512" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="J512" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="K512" t="n">
-        <v>80</v>
+        <v>264</v>
       </c>
     </row>
     <row r="513">
@@ -26228,18 +26236,18 @@
       </c>
       <c r="G513" t="inlineStr">
         <is>
-          <t>Diego Lima</t>
+          <t>Bruno Contieri</t>
         </is>
       </c>
       <c r="H513" t="inlineStr"/>
       <c r="I513" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J513" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K513" t="n">
-        <v>79</v>
+        <v>147</v>
       </c>
     </row>
     <row r="514">
@@ -26275,7 +26283,7 @@
       </c>
       <c r="G514" t="inlineStr">
         <is>
-          <t>Luiz Ferreira</t>
+          <t>Cristiane Simões</t>
         </is>
       </c>
       <c r="H514" t="inlineStr"/>
@@ -26286,7 +26294,7 @@
         <v>0</v>
       </c>
       <c r="K514" t="n">
-        <v>7</v>
+        <v>173</v>
       </c>
     </row>
     <row r="515">
@@ -26322,18 +26330,18 @@
       </c>
       <c r="G515" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Daniel Oliveira</t>
         </is>
       </c>
       <c r="H515" t="inlineStr"/>
       <c r="I515" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J515" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K515" t="n">
-        <v>87</v>
+        <v>80</v>
       </c>
     </row>
     <row r="516">
@@ -26369,7 +26377,7 @@
       </c>
       <c r="G516" t="inlineStr">
         <is>
-          <t>Rodrigo Rego</t>
+          <t>Diego Lima</t>
         </is>
       </c>
       <c r="H516" t="inlineStr"/>
@@ -26377,10 +26385,10 @@
         <v>0</v>
       </c>
       <c r="J516" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K516" t="n">
-        <v>176</v>
+        <v>79</v>
       </c>
     </row>
     <row r="517">
@@ -26416,18 +26424,18 @@
       </c>
       <c r="G517" t="inlineStr">
         <is>
-          <t>Rogerio Egidio</t>
+          <t>Karine Gusmão</t>
         </is>
       </c>
       <c r="H517" t="inlineStr"/>
       <c r="I517" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J517" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="K517" t="n">
-        <v>180</v>
+        <v>6</v>
       </c>
     </row>
     <row r="518">
@@ -26463,7 +26471,7 @@
       </c>
       <c r="G518" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Luiz Ferreira</t>
         </is>
       </c>
       <c r="H518" t="inlineStr"/>
@@ -26474,7 +26482,7 @@
         <v>0</v>
       </c>
       <c r="K518" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
     </row>
     <row r="519">
@@ -26510,18 +26518,18 @@
       </c>
       <c r="G519" t="inlineStr">
         <is>
-          <t>Simone Marques</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="H519" t="inlineStr"/>
       <c r="I519" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J519" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K519" t="n">
-        <v>118</v>
+        <v>90</v>
       </c>
     </row>
     <row r="520">
@@ -26557,18 +26565,18 @@
       </c>
       <c r="G520" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Rodrigo Rego</t>
         </is>
       </c>
       <c r="H520" t="inlineStr"/>
       <c r="I520" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J520" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K520" t="n">
-        <v>126</v>
+        <v>177</v>
       </c>
     </row>
     <row r="521">
@@ -26599,23 +26607,23 @@
       </c>
       <c r="F521" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="G521" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Rogerio Egidio</t>
         </is>
       </c>
       <c r="H521" t="inlineStr"/>
       <c r="I521" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J521" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K521" t="n">
-        <v>1</v>
+        <v>181</v>
       </c>
     </row>
     <row r="522">
@@ -26646,23 +26654,23 @@
       </c>
       <c r="F522" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="G522" t="inlineStr">
         <is>
-          <t>Jurema Damacena - SAC</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="H522" t="inlineStr"/>
       <c r="I522" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J522" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K522" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="523">
@@ -26688,28 +26696,28 @@
       </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F523" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="G523" t="inlineStr">
         <is>
-          <t>Jurema Damacena - SAC</t>
+          <t>Simone Marques</t>
         </is>
       </c>
       <c r="H523" t="inlineStr"/>
       <c r="I523" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J523" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K523" t="n">
-        <v>2</v>
+        <v>118</v>
       </c>
     </row>
     <row r="524">
@@ -26735,28 +26743,28 @@
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F524" t="inlineStr">
         <is>
-          <t>SANTOS - ADM</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="G524" t="inlineStr">
         <is>
-          <t>Kauany Pereira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="H524" t="inlineStr"/>
       <c r="I524" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="J524" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="K524" t="n">
-        <v>133</v>
+        <v>126</v>
       </c>
     </row>
     <row r="525">
@@ -26782,24 +26790,20 @@
       </c>
       <c r="E525" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F525" t="inlineStr">
         <is>
-          <t>SANTOS - CTB</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="G525" t="inlineStr">
         <is>
-          <t>Ivia Oliveira</t>
-        </is>
-      </c>
-      <c r="H525" t="inlineStr">
-        <is>
-          <t>Roberto Silva</t>
-        </is>
-      </c>
+          <t>Edimir Santos</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr"/>
       <c r="I525" t="n">
         <v>0</v>
       </c>
@@ -26807,7 +26811,7 @@
         <v>0</v>
       </c>
       <c r="K525" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="526">
@@ -26833,32 +26837,28 @@
       </c>
       <c r="E526" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F526" t="inlineStr">
         <is>
-          <t>SANTOS - CTB</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="G526" t="inlineStr">
         <is>
-          <t>Nata Trindade</t>
-        </is>
-      </c>
-      <c r="H526" t="inlineStr">
-        <is>
-          <t>Roberto Silva</t>
-        </is>
-      </c>
+          <t>Jurema Damacena - SAC</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr"/>
       <c r="I526" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="J526" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="K526" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
     </row>
     <row r="527">
@@ -26889,27 +26889,23 @@
       </c>
       <c r="F527" t="inlineStr">
         <is>
-          <t>SANTOS - CTB</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="G527" t="inlineStr">
         <is>
-          <t>Roberto Silva</t>
-        </is>
-      </c>
-      <c r="H527" t="inlineStr">
-        <is>
-          <t>Roberto Silva</t>
-        </is>
-      </c>
+          <t>Jurema Damacena - SAC</t>
+        </is>
+      </c>
+      <c r="H527" t="inlineStr"/>
       <c r="I527" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J527" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K527" t="n">
-        <v>37</v>
+        <v>2</v>
       </c>
     </row>
     <row r="528">
@@ -26940,27 +26936,23 @@
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>SANTOS - CTB</t>
+          <t>SANTOS - ADM</t>
         </is>
       </c>
       <c r="G528" t="inlineStr">
         <is>
-          <t>Thaina Rodrigues</t>
-        </is>
-      </c>
-      <c r="H528" t="inlineStr">
-        <is>
-          <t>Roberto Silva</t>
-        </is>
-      </c>
+          <t>Kauany Pereira</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr"/>
       <c r="I528" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="J528" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="K528" t="n">
-        <v>25</v>
+        <v>136</v>
       </c>
     </row>
     <row r="529">
@@ -26991,17 +26983,17 @@
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>SANTOS - DP</t>
+          <t>SANTOS - CTB</t>
         </is>
       </c>
       <c r="G529" t="inlineStr">
         <is>
-          <t>Bruna Silva</t>
+          <t>Ivia Oliveira</t>
         </is>
       </c>
       <c r="H529" t="inlineStr">
         <is>
-          <t>Katia Valeria</t>
+          <t>Roberto Silva</t>
         </is>
       </c>
       <c r="I529" t="n">
@@ -27011,7 +27003,7 @@
         <v>0</v>
       </c>
       <c r="K529" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="530">
@@ -27042,27 +27034,27 @@
       </c>
       <c r="F530" t="inlineStr">
         <is>
-          <t>SANTOS - DP</t>
+          <t>SANTOS - CTB</t>
         </is>
       </c>
       <c r="G530" t="inlineStr">
         <is>
-          <t>Carliane Silva</t>
+          <t>Nata Trindade</t>
         </is>
       </c>
       <c r="H530" t="inlineStr">
         <is>
-          <t>Katia Valeria</t>
+          <t>Roberto Silva</t>
         </is>
       </c>
       <c r="I530" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J530" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="K530" t="n">
-        <v>172</v>
+        <v>22</v>
       </c>
     </row>
     <row r="531">
@@ -27093,27 +27085,27 @@
       </c>
       <c r="F531" t="inlineStr">
         <is>
-          <t>SANTOS - DP</t>
+          <t>SANTOS - CTB</t>
         </is>
       </c>
       <c r="G531" t="inlineStr">
         <is>
-          <t>Cintia Andrade</t>
+          <t>Roberto Silva</t>
         </is>
       </c>
       <c r="H531" t="inlineStr">
         <is>
-          <t>Katia Valeria</t>
+          <t>Roberto Silva</t>
         </is>
       </c>
       <c r="I531" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J531" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K531" t="n">
-        <v>111</v>
+        <v>37</v>
       </c>
     </row>
     <row r="532">
@@ -27144,27 +27136,27 @@
       </c>
       <c r="F532" t="inlineStr">
         <is>
-          <t>SANTOS - DP</t>
+          <t>SANTOS - CTB</t>
         </is>
       </c>
       <c r="G532" t="inlineStr">
         <is>
-          <t>Katia Valeria</t>
+          <t>Thaina Rodrigues</t>
         </is>
       </c>
       <c r="H532" t="inlineStr">
         <is>
-          <t>Katia Valeria</t>
+          <t>Roberto Silva</t>
         </is>
       </c>
       <c r="I532" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="J532" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="K532" t="n">
-        <v>211</v>
+        <v>26</v>
       </c>
     </row>
     <row r="533">
@@ -27195,17 +27187,17 @@
       </c>
       <c r="F533" t="inlineStr">
         <is>
-          <t>SANTOS - EF</t>
+          <t>SANTOS - DP</t>
         </is>
       </c>
       <c r="G533" t="inlineStr">
         <is>
-          <t>Jasmina Melo</t>
+          <t>Bruna Silva</t>
         </is>
       </c>
       <c r="H533" t="inlineStr">
         <is>
-          <t>Lidia Tavares</t>
+          <t>Katia Valeria</t>
         </is>
       </c>
       <c r="I533" t="n">
@@ -27215,7 +27207,7 @@
         <v>0</v>
       </c>
       <c r="K533" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
     </row>
     <row r="534">
@@ -27246,27 +27238,27 @@
       </c>
       <c r="F534" t="inlineStr">
         <is>
-          <t>SANTOS - EF</t>
+          <t>SANTOS - DP</t>
         </is>
       </c>
       <c r="G534" t="inlineStr">
         <is>
-          <t>Karen Saadi</t>
+          <t>Carliane Silva</t>
         </is>
       </c>
       <c r="H534" t="inlineStr">
         <is>
-          <t>Lidia Tavares</t>
+          <t>Katia Valeria</t>
         </is>
       </c>
       <c r="I534" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J534" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="K534" t="n">
-        <v>35</v>
+        <v>176</v>
       </c>
     </row>
     <row r="535">
@@ -27297,27 +27289,27 @@
       </c>
       <c r="F535" t="inlineStr">
         <is>
-          <t>SANTOS - EF</t>
+          <t>SANTOS - DP</t>
         </is>
       </c>
       <c r="G535" t="inlineStr">
         <is>
-          <t>Luckas Andrade</t>
+          <t>Cintia Andrade</t>
         </is>
       </c>
       <c r="H535" t="inlineStr">
         <is>
-          <t>Lidia Tavares</t>
+          <t>Katia Valeria</t>
         </is>
       </c>
       <c r="I535" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="J535" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="K535" t="n">
-        <v>54</v>
+        <v>128</v>
       </c>
     </row>
     <row r="536">
@@ -27348,27 +27340,27 @@
       </c>
       <c r="F536" t="inlineStr">
         <is>
-          <t>SANTOS - EF</t>
+          <t>SANTOS - DP</t>
         </is>
       </c>
       <c r="G536" t="inlineStr">
         <is>
-          <t>Mirian Rodrigues</t>
+          <t>Katia Valeria</t>
         </is>
       </c>
       <c r="H536" t="inlineStr">
         <is>
-          <t>Lidia Tavares</t>
+          <t>Katia Valeria</t>
         </is>
       </c>
       <c r="I536" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="J536" t="n">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="K536" t="n">
-        <v>61</v>
+        <v>224</v>
       </c>
     </row>
     <row r="537">
@@ -27399,22 +27391,226 @@
       </c>
       <c r="F537" t="inlineStr">
         <is>
+          <t>SANTOS - EF</t>
+        </is>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>Jasmina Melo</t>
+        </is>
+      </c>
+      <c r="H537" t="inlineStr">
+        <is>
+          <t>Lidia Tavares</t>
+        </is>
+      </c>
+      <c r="I537" t="n">
+        <v>8</v>
+      </c>
+      <c r="J537" t="n">
+        <v>8</v>
+      </c>
+      <c r="K537" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>Terça</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>SANTOS - EF</t>
+        </is>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>Karen Saadi</t>
+        </is>
+      </c>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>Lidia Tavares</t>
+        </is>
+      </c>
+      <c r="I538" t="n">
+        <v>8</v>
+      </c>
+      <c r="J538" t="n">
+        <v>7</v>
+      </c>
+      <c r="K538" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>Terça</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>SANTOS - EF</t>
+        </is>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>Luckas Andrade</t>
+        </is>
+      </c>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>Lidia Tavares</t>
+        </is>
+      </c>
+      <c r="I539" t="n">
+        <v>10</v>
+      </c>
+      <c r="J539" t="n">
+        <v>19</v>
+      </c>
+      <c r="K539" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>Terça</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>SANTOS - EF</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>Mirian Rodrigues</t>
+        </is>
+      </c>
+      <c r="H540" t="inlineStr">
+        <is>
+          <t>Lidia Tavares</t>
+        </is>
+      </c>
+      <c r="I540" t="n">
+        <v>5</v>
+      </c>
+      <c r="J540" t="n">
+        <v>7</v>
+      </c>
+      <c r="K540" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>Terça</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
           <t>SANTOS - GC</t>
         </is>
       </c>
-      <c r="G537" t="inlineStr">
+      <c r="G541" t="inlineStr">
         <is>
           <t>Rafaella Massuia</t>
         </is>
       </c>
-      <c r="H537" t="inlineStr"/>
-      <c r="I537" t="n">
-        <v>0</v>
-      </c>
-      <c r="J537" t="n">
-        <v>0</v>
-      </c>
-      <c r="K537" t="n">
+      <c r="H541" t="inlineStr"/>
+      <c r="I541" t="n">
+        <v>0</v>
+      </c>
+      <c r="J541" t="n">
+        <v>0</v>
+      </c>
+      <c r="K541" t="n">
         <v>109</v>
       </c>
     </row>

--- a/data/historico/historico_baixas.xlsx
+++ b/data/historico/historico_baixas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K820"/>
+  <dimension ref="A1:K823"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -28013,13 +28013,13 @@
         </is>
       </c>
       <c r="I549" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J549" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K549" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="550">
@@ -28464,13 +28464,13 @@
         </is>
       </c>
       <c r="I558" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J558" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K558" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="559">
@@ -28611,7 +28611,7 @@
         <v>13</v>
       </c>
       <c r="K561" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="562">
@@ -28752,7 +28752,7 @@
         <v>5</v>
       </c>
       <c r="K564" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="565">
@@ -28797,13 +28797,13 @@
         </is>
       </c>
       <c r="I565" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J565" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K565" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="566">
@@ -28899,13 +28899,13 @@
         </is>
       </c>
       <c r="I567" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J567" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K567" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="568">
@@ -28950,13 +28950,13 @@
         </is>
       </c>
       <c r="I568" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="J568" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="K568" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
     </row>
     <row r="569">
@@ -29103,13 +29103,13 @@
         </is>
       </c>
       <c r="I571" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J571" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="K571" t="n">
-        <v>40</v>
+        <v>51</v>
       </c>
     </row>
     <row r="572">
@@ -29256,13 +29256,13 @@
         </is>
       </c>
       <c r="I574" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J574" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K574" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="575">
@@ -29409,13 +29409,13 @@
         </is>
       </c>
       <c r="I577" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J577" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K577" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="578">
@@ -29460,13 +29460,13 @@
         </is>
       </c>
       <c r="I578" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J578" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K578" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="579">
@@ -29562,13 +29562,13 @@
         </is>
       </c>
       <c r="I580" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J580" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K580" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="581">
@@ -29613,7 +29613,7 @@
         </is>
       </c>
       <c r="I581" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J581" t="n">
         <v>4</v>
@@ -29758,7 +29758,7 @@
         </is>
       </c>
       <c r="I584" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J584" t="n">
         <v>3</v>
@@ -29809,13 +29809,13 @@
         </is>
       </c>
       <c r="I585" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J585" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K585" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="586">
@@ -29962,7 +29962,7 @@
         </is>
       </c>
       <c r="I588" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J588" t="n">
         <v>2</v>
@@ -30013,13 +30013,13 @@
         </is>
       </c>
       <c r="I589" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J589" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K589" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="590">
@@ -30166,13 +30166,13 @@
         </is>
       </c>
       <c r="I592" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J592" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K592" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
     </row>
     <row r="593">
@@ -30268,13 +30268,13 @@
         </is>
       </c>
       <c r="I594" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J594" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K594" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="595">
@@ -30472,13 +30472,13 @@
         </is>
       </c>
       <c r="I598" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J598" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="K598" t="n">
-        <v>154</v>
+        <v>163</v>
       </c>
     </row>
     <row r="599">
@@ -30574,13 +30574,13 @@
         </is>
       </c>
       <c r="I600" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J600" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K600" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="601">
@@ -30676,13 +30676,13 @@
         </is>
       </c>
       <c r="I602" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J602" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="K602" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
     </row>
     <row r="603">
@@ -30727,13 +30727,13 @@
         </is>
       </c>
       <c r="I603" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J603" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K603" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="604">
@@ -30880,13 +30880,13 @@
         </is>
       </c>
       <c r="I606" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J606" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="K606" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="607">
@@ -30982,13 +30982,13 @@
         </is>
       </c>
       <c r="I608" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J608" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K608" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="609">
@@ -31033,13 +31033,13 @@
         </is>
       </c>
       <c r="I609" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J609" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K609" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="610">
@@ -31135,13 +31135,13 @@
         </is>
       </c>
       <c r="I611" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J611" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K611" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="612">
@@ -31237,13 +31237,13 @@
         </is>
       </c>
       <c r="I613" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J613" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K613" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="614">
@@ -31284,7 +31284,7 @@
       </c>
       <c r="H614" t="inlineStr"/>
       <c r="I614" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J614" t="n">
         <v>50</v>
@@ -31425,13 +31425,13 @@
       </c>
       <c r="H617" t="inlineStr"/>
       <c r="I617" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="J617" t="n">
-        <v>12</v>
+        <v>111</v>
       </c>
       <c r="K617" t="n">
-        <v>53</v>
+        <v>151</v>
       </c>
     </row>
     <row r="618">
@@ -31478,7 +31478,7 @@
         <v>50</v>
       </c>
       <c r="K618" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="619">
@@ -31867,22 +31867,22 @@
       </c>
       <c r="G626" t="inlineStr">
         <is>
-          <t>Thiago Ceconelli</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="H626" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="I626" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J626" t="n">
         <v>1</v>
       </c>
       <c r="K626" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="627">
@@ -31913,27 +31913,27 @@
       </c>
       <c r="F627" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL HOLDING</t>
+          <t>CONTABILIDADE (Outsourcing)</t>
         </is>
       </c>
       <c r="G627" t="inlineStr">
         <is>
-          <t>Ana Flavia Silva</t>
+          <t>Thiago Ceconelli</t>
         </is>
       </c>
       <c r="H627" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Karina Santos</t>
         </is>
       </c>
       <c r="I627" t="n">
         <v>0</v>
       </c>
       <c r="J627" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K627" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
     </row>
     <row r="628">
@@ -31969,18 +31969,22 @@
       </c>
       <c r="G628" t="inlineStr">
         <is>
-          <t>Daniele Faria</t>
-        </is>
-      </c>
-      <c r="H628" t="inlineStr"/>
+          <t>Ana Flavia Silva</t>
+        </is>
+      </c>
+      <c r="H628" t="inlineStr">
+        <is>
+          <t>Tatiana Linardi</t>
+        </is>
+      </c>
       <c r="I628" t="n">
         <v>0</v>
       </c>
       <c r="J628" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K628" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="629">
@@ -32016,22 +32020,18 @@
       </c>
       <c r="G629" t="inlineStr">
         <is>
-          <t>Vitor de Souza</t>
-        </is>
-      </c>
-      <c r="H629" t="inlineStr">
-        <is>
-          <t>Tatiana Linardi</t>
-        </is>
-      </c>
+          <t>Daniele Faria</t>
+        </is>
+      </c>
+      <c r="H629" t="inlineStr"/>
       <c r="I629" t="n">
         <v>0</v>
       </c>
       <c r="J629" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K629" t="n">
-        <v>108</v>
+        <v>2</v>
       </c>
     </row>
     <row r="630">
@@ -32067,7 +32067,7 @@
       </c>
       <c r="G630" t="inlineStr">
         <is>
-          <t>Vitoria Regina</t>
+          <t>Vitor de Souza</t>
         </is>
       </c>
       <c r="H630" t="inlineStr">
@@ -32076,13 +32076,13 @@
         </is>
       </c>
       <c r="I630" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J630" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K630" t="n">
-        <v>60</v>
+        <v>110</v>
       </c>
     </row>
     <row r="631">
@@ -32113,27 +32113,27 @@
       </c>
       <c r="F631" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL INDUSTRIA</t>
+          <t>CTB - CONTÁBIL HOLDING</t>
         </is>
       </c>
       <c r="G631" t="inlineStr">
         <is>
-          <t>Adriano Barros</t>
+          <t>Vitoria Regina</t>
         </is>
       </c>
       <c r="H631" t="inlineStr">
         <is>
-          <t>Erika Santana|Isabella Nascimento</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="I631" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J631" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K631" t="n">
-        <v>1</v>
+        <v>62</v>
       </c>
     </row>
     <row r="632">
@@ -32169,7 +32169,7 @@
       </c>
       <c r="G632" t="inlineStr">
         <is>
-          <t>Bianca Silva</t>
+          <t>Adriano Barros</t>
         </is>
       </c>
       <c r="H632" t="inlineStr">
@@ -32181,10 +32181,10 @@
         <v>0</v>
       </c>
       <c r="J632" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K632" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="633">
@@ -32220,7 +32220,7 @@
       </c>
       <c r="G633" t="inlineStr">
         <is>
-          <t>Emylle Souza</t>
+          <t>Bianca Silva</t>
         </is>
       </c>
       <c r="H633" t="inlineStr">
@@ -32232,10 +32232,10 @@
         <v>0</v>
       </c>
       <c r="J633" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K633" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="634">
@@ -32271,7 +32271,7 @@
       </c>
       <c r="G634" t="inlineStr">
         <is>
-          <t>Fatima Rocha</t>
+          <t>Emylle Souza</t>
         </is>
       </c>
       <c r="H634" t="inlineStr">
@@ -32283,10 +32283,10 @@
         <v>0</v>
       </c>
       <c r="J634" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K634" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="635">
@@ -32322,7 +32322,7 @@
       </c>
       <c r="G635" t="inlineStr">
         <is>
-          <t>Gabriel Correia</t>
+          <t>Fatima Rocha</t>
         </is>
       </c>
       <c r="H635" t="inlineStr">
@@ -32334,10 +32334,10 @@
         <v>0</v>
       </c>
       <c r="J635" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K635" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="636">
@@ -32373,7 +32373,7 @@
       </c>
       <c r="G636" t="inlineStr">
         <is>
-          <t>Isabella Nascimento</t>
+          <t>Gabriel Correia</t>
         </is>
       </c>
       <c r="H636" t="inlineStr">
@@ -32385,10 +32385,10 @@
         <v>0</v>
       </c>
       <c r="J636" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K636" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="637">
@@ -32424,7 +32424,7 @@
       </c>
       <c r="G637" t="inlineStr">
         <is>
-          <t>Laisa Rocha</t>
+          <t>Isabella Nascimento</t>
         </is>
       </c>
       <c r="H637" t="inlineStr">
@@ -32475,7 +32475,7 @@
       </c>
       <c r="G638" t="inlineStr">
         <is>
-          <t>Lucas Alves</t>
+          <t>Laisa Rocha</t>
         </is>
       </c>
       <c r="H638" t="inlineStr">
@@ -32487,10 +32487,10 @@
         <v>0</v>
       </c>
       <c r="J638" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K638" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="639">
@@ -32526,7 +32526,7 @@
       </c>
       <c r="G639" t="inlineStr">
         <is>
-          <t>Luciana Silva</t>
+          <t>Lucas Alves</t>
         </is>
       </c>
       <c r="H639" t="inlineStr">
@@ -32538,10 +32538,10 @@
         <v>0</v>
       </c>
       <c r="J639" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K639" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="640">
@@ -32577,18 +32577,22 @@
       </c>
       <c r="G640" t="inlineStr">
         <is>
-          <t>Luiz Ferreira</t>
-        </is>
-      </c>
-      <c r="H640" t="inlineStr"/>
+          <t>Luciana Silva</t>
+        </is>
+      </c>
+      <c r="H640" t="inlineStr">
+        <is>
+          <t>Erika Santana|Isabella Nascimento</t>
+        </is>
+      </c>
       <c r="I640" t="n">
         <v>0</v>
       </c>
       <c r="J640" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K640" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
     </row>
     <row r="641">
@@ -32624,22 +32628,18 @@
       </c>
       <c r="G641" t="inlineStr">
         <is>
-          <t>Marcus Oliveira</t>
-        </is>
-      </c>
-      <c r="H641" t="inlineStr">
-        <is>
-          <t>Erika Santana|Isabella Nascimento</t>
-        </is>
-      </c>
+          <t>Luiz Ferreira</t>
+        </is>
+      </c>
+      <c r="H641" t="inlineStr"/>
       <c r="I641" t="n">
         <v>0</v>
       </c>
       <c r="J641" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K641" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="642">
@@ -32675,7 +32675,7 @@
       </c>
       <c r="G642" t="inlineStr">
         <is>
-          <t>Mariana Pires</t>
+          <t>Marcus Oliveira</t>
         </is>
       </c>
       <c r="H642" t="inlineStr">
@@ -32687,10 +32687,10 @@
         <v>0</v>
       </c>
       <c r="J642" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K642" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="643">
@@ -32726,7 +32726,7 @@
       </c>
       <c r="G643" t="inlineStr">
         <is>
-          <t>Mateus Miranda</t>
+          <t>Mariana Pires</t>
         </is>
       </c>
       <c r="H643" t="inlineStr">
@@ -32738,10 +32738,10 @@
         <v>0</v>
       </c>
       <c r="J643" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K643" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="644">
@@ -32777,7 +32777,7 @@
       </c>
       <c r="G644" t="inlineStr">
         <is>
-          <t>Mirian Lima</t>
+          <t>Mateus Miranda</t>
         </is>
       </c>
       <c r="H644" t="inlineStr">
@@ -32789,10 +32789,10 @@
         <v>0</v>
       </c>
       <c r="J644" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K644" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="645">
@@ -32828,7 +32828,7 @@
       </c>
       <c r="G645" t="inlineStr">
         <is>
-          <t>Nathalia Lourenco</t>
+          <t>Mirian Lima</t>
         </is>
       </c>
       <c r="H645" t="inlineStr">
@@ -32840,10 +32840,10 @@
         <v>0</v>
       </c>
       <c r="J645" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K645" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="646">
@@ -32879,7 +32879,7 @@
       </c>
       <c r="G646" t="inlineStr">
         <is>
-          <t>Nicolas Dias</t>
+          <t>Nathalia Lourenco</t>
         </is>
       </c>
       <c r="H646" t="inlineStr">
@@ -32891,10 +32891,10 @@
         <v>0</v>
       </c>
       <c r="J646" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K646" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="647">
@@ -32930,7 +32930,7 @@
       </c>
       <c r="G647" t="inlineStr">
         <is>
-          <t>Rodrigo Nunes</t>
+          <t>Nicolas Dias</t>
         </is>
       </c>
       <c r="H647" t="inlineStr">
@@ -32942,10 +32942,10 @@
         <v>0</v>
       </c>
       <c r="J647" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K647" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="648">
@@ -32981,7 +32981,7 @@
       </c>
       <c r="G648" t="inlineStr">
         <is>
-          <t>Thais Souza</t>
+          <t>Rodrigo Nunes</t>
         </is>
       </c>
       <c r="H648" t="inlineStr">
@@ -32993,10 +32993,10 @@
         <v>0</v>
       </c>
       <c r="J648" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K648" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="649">
@@ -33027,27 +33027,27 @@
       </c>
       <c r="F649" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="G649" t="inlineStr">
         <is>
-          <t>Aline Petrini</t>
+          <t>Thais Souza</t>
         </is>
       </c>
       <c r="H649" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Erika Santana|Isabella Nascimento</t>
         </is>
       </c>
       <c r="I649" t="n">
         <v>0</v>
       </c>
       <c r="J649" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="K649" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
     </row>
     <row r="650">
@@ -33083,22 +33083,22 @@
       </c>
       <c r="G650" t="inlineStr">
         <is>
-          <t>Ana Barbosa</t>
+          <t>Aline Petrini</t>
         </is>
       </c>
       <c r="H650" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="I650" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J650" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="K650" t="n">
-        <v>44</v>
+        <v>20</v>
       </c>
     </row>
     <row r="651">
@@ -33134,7 +33134,7 @@
       </c>
       <c r="G651" t="inlineStr">
         <is>
-          <t>Daniele Leite</t>
+          <t>Ana Barbosa</t>
         </is>
       </c>
       <c r="H651" t="inlineStr">
@@ -33146,10 +33146,10 @@
         <v>0</v>
       </c>
       <c r="J651" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="K651" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
     </row>
     <row r="652">
@@ -33185,22 +33185,22 @@
       </c>
       <c r="G652" t="inlineStr">
         <is>
-          <t>Danielle Silva</t>
+          <t>Daniele Leite</t>
         </is>
       </c>
       <c r="H652" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I652" t="n">
         <v>0</v>
       </c>
       <c r="J652" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="K652" t="n">
-        <v>63</v>
+        <v>4</v>
       </c>
     </row>
     <row r="653">
@@ -33236,7 +33236,7 @@
       </c>
       <c r="G653" t="inlineStr">
         <is>
-          <t>Danilo Oliveira</t>
+          <t>Danielle Silva</t>
         </is>
       </c>
       <c r="H653" t="inlineStr">
@@ -33248,10 +33248,10 @@
         <v>0</v>
       </c>
       <c r="J653" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K653" t="n">
-        <v>18</v>
+        <v>63</v>
       </c>
     </row>
     <row r="654">
@@ -33287,19 +33287,19 @@
       </c>
       <c r="G654" t="inlineStr">
         <is>
-          <t>Debora Silva</t>
+          <t>Danilo Oliveira</t>
         </is>
       </c>
       <c r="H654" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Karina Santos</t>
         </is>
       </c>
       <c r="I654" t="n">
         <v>0</v>
       </c>
       <c r="J654" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K654" t="n">
         <v>18</v>
@@ -33338,22 +33338,22 @@
       </c>
       <c r="G655" t="inlineStr">
         <is>
-          <t>Diogo Calazans</t>
+          <t>Debora Silva</t>
         </is>
       </c>
       <c r="H655" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="I655" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J655" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K655" t="n">
-        <v>79</v>
+        <v>19</v>
       </c>
     </row>
     <row r="656">
@@ -33389,22 +33389,22 @@
       </c>
       <c r="G656" t="inlineStr">
         <is>
-          <t>Eduardo Cruz</t>
+          <t>Diogo Calazans</t>
         </is>
       </c>
       <c r="H656" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Karina Santos</t>
         </is>
       </c>
       <c r="I656" t="n">
         <v>0</v>
       </c>
       <c r="J656" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K656" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="657">
@@ -33440,22 +33440,22 @@
       </c>
       <c r="G657" t="inlineStr">
         <is>
-          <t>Eveny Silva</t>
+          <t>Eduardo Cruz</t>
         </is>
       </c>
       <c r="H657" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="I657" t="n">
         <v>0</v>
       </c>
       <c r="J657" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K657" t="n">
-        <v>28</v>
+        <v>75</v>
       </c>
     </row>
     <row r="658">
@@ -33491,22 +33491,22 @@
       </c>
       <c r="G658" t="inlineStr">
         <is>
-          <t>Everton Moura</t>
+          <t>Eveny Silva</t>
         </is>
       </c>
       <c r="H658" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Karina Santos</t>
         </is>
       </c>
       <c r="I658" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J658" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K658" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
     </row>
     <row r="659">
@@ -33542,22 +33542,22 @@
       </c>
       <c r="G659" t="inlineStr">
         <is>
-          <t>Guilherme Dantas</t>
+          <t>Everton Moura</t>
         </is>
       </c>
       <c r="H659" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="I659" t="n">
         <v>0</v>
       </c>
       <c r="J659" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K659" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="660">
@@ -33593,22 +33593,22 @@
       </c>
       <c r="G660" t="inlineStr">
         <is>
-          <t>Isabela Lemos</t>
+          <t>Guilherme Dantas</t>
         </is>
       </c>
       <c r="H660" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I660" t="n">
         <v>0</v>
       </c>
       <c r="J660" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K660" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="661">
@@ -33644,22 +33644,22 @@
       </c>
       <c r="G661" t="inlineStr">
         <is>
-          <t>Jackson Silva</t>
+          <t>Isabela Lemos</t>
         </is>
       </c>
       <c r="H661" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="I661" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J661" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K661" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="662">
@@ -33695,22 +33695,22 @@
       </c>
       <c r="G662" t="inlineStr">
         <is>
-          <t>Jaqueline Sousa</t>
+          <t>Jackson Silva</t>
         </is>
       </c>
       <c r="H662" t="inlineStr">
         <is>
-          <t>Lucas Fischer</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I662" t="n">
         <v>0</v>
       </c>
       <c r="J662" t="n">
+        <v>0</v>
+      </c>
+      <c r="K662" t="n">
         <v>20</v>
-      </c>
-      <c r="K662" t="n">
-        <v>26</v>
       </c>
     </row>
     <row r="663">
@@ -33746,7 +33746,7 @@
       </c>
       <c r="G663" t="inlineStr">
         <is>
-          <t>Leticia Medeiros</t>
+          <t>Jaqueline Sousa</t>
         </is>
       </c>
       <c r="H663" t="inlineStr">
@@ -33758,10 +33758,10 @@
         <v>0</v>
       </c>
       <c r="J663" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K663" t="n">
-        <v>57</v>
+        <v>26</v>
       </c>
     </row>
     <row r="664">
@@ -33797,22 +33797,22 @@
       </c>
       <c r="G664" t="inlineStr">
         <is>
-          <t>Monica Medeiros</t>
+          <t>Leticia Medeiros</t>
         </is>
       </c>
       <c r="H664" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Lucas Fischer</t>
         </is>
       </c>
       <c r="I664" t="n">
         <v>0</v>
       </c>
       <c r="J664" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="K664" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
     </row>
     <row r="665">
@@ -33848,22 +33848,22 @@
       </c>
       <c r="G665" t="inlineStr">
         <is>
-          <t>Naiara Dutra</t>
+          <t>Monica Medeiros</t>
         </is>
       </c>
       <c r="H665" t="inlineStr">
         <is>
-          <t>Lucas Fischer</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I665" t="n">
         <v>0</v>
       </c>
       <c r="J665" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K665" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
     </row>
     <row r="666">
@@ -33899,22 +33899,22 @@
       </c>
       <c r="G666" t="inlineStr">
         <is>
-          <t>Patricia Borges</t>
+          <t>Naiara Dutra</t>
         </is>
       </c>
       <c r="H666" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Lucas Fischer</t>
         </is>
       </c>
       <c r="I666" t="n">
         <v>0</v>
       </c>
       <c r="J666" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K666" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
     </row>
     <row r="667">
@@ -33950,22 +33950,22 @@
       </c>
       <c r="G667" t="inlineStr">
         <is>
-          <t>Paulo Silva</t>
+          <t>Patricia Borges</t>
         </is>
       </c>
       <c r="H667" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I667" t="n">
         <v>0</v>
       </c>
       <c r="J667" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K667" t="n">
-        <v>57</v>
+        <v>28</v>
       </c>
     </row>
     <row r="668">
@@ -34001,22 +34001,22 @@
       </c>
       <c r="G668" t="inlineStr">
         <is>
-          <t>Rachel Lima</t>
+          <t>Paulo Silva</t>
         </is>
       </c>
       <c r="H668" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="I668" t="n">
         <v>0</v>
       </c>
       <c r="J668" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="K668" t="n">
-        <v>31</v>
+        <v>57</v>
       </c>
     </row>
     <row r="669">
@@ -34052,7 +34052,7 @@
       </c>
       <c r="G669" t="inlineStr">
         <is>
-          <t>Raiane Barbosa</t>
+          <t>Rachel Lima</t>
         </is>
       </c>
       <c r="H669" t="inlineStr">
@@ -34064,10 +34064,10 @@
         <v>0</v>
       </c>
       <c r="J669" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K669" t="n">
-        <v>60</v>
+        <v>31</v>
       </c>
     </row>
     <row r="670">
@@ -34103,22 +34103,22 @@
       </c>
       <c r="G670" t="inlineStr">
         <is>
-          <t>Rejane Coelho</t>
+          <t>Raiane Barbosa</t>
         </is>
       </c>
       <c r="H670" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I670" t="n">
         <v>0</v>
       </c>
       <c r="J670" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K670" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
     </row>
     <row r="671">
@@ -34154,22 +34154,22 @@
       </c>
       <c r="G671" t="inlineStr">
         <is>
-          <t>Renata Alves - CTV</t>
+          <t>Rejane Coelho</t>
         </is>
       </c>
       <c r="H671" t="inlineStr">
         <is>
-          <t>Lucas Fischer</t>
+          <t>Karina Santos</t>
         </is>
       </c>
       <c r="I671" t="n">
         <v>0</v>
       </c>
       <c r="J671" t="n">
+        <v>0</v>
+      </c>
+      <c r="K671" t="n">
         <v>1</v>
-      </c>
-      <c r="K671" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="672">
@@ -34205,18 +34205,22 @@
       </c>
       <c r="G672" t="inlineStr">
         <is>
-          <t>Renata Cavalheiro</t>
-        </is>
-      </c>
-      <c r="H672" t="inlineStr"/>
+          <t>Renata Alves - CTV</t>
+        </is>
+      </c>
+      <c r="H672" t="inlineStr">
+        <is>
+          <t>Lucas Fischer</t>
+        </is>
+      </c>
       <c r="I672" t="n">
         <v>0</v>
       </c>
       <c r="J672" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K672" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="673">
@@ -34252,22 +34256,18 @@
       </c>
       <c r="G673" t="inlineStr">
         <is>
-          <t>Ryan Godinho</t>
-        </is>
-      </c>
-      <c r="H673" t="inlineStr">
-        <is>
-          <t>Karina Santos</t>
-        </is>
-      </c>
+          <t>Renata Cavalheiro</t>
+        </is>
+      </c>
+      <c r="H673" t="inlineStr"/>
       <c r="I673" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J673" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K673" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="674">
@@ -34303,22 +34303,22 @@
       </c>
       <c r="G674" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Ryan Godinho</t>
         </is>
       </c>
       <c r="H674" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Karina Santos</t>
         </is>
       </c>
       <c r="I674" t="n">
         <v>0</v>
       </c>
       <c r="J674" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K674" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="675">
@@ -34354,22 +34354,22 @@
       </c>
       <c r="G675" t="inlineStr">
         <is>
-          <t>Vitor Domingues</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="H675" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="I675" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J675" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="K675" t="n">
-        <v>65</v>
+        <v>1</v>
       </c>
     </row>
     <row r="676">
@@ -34400,27 +34400,27 @@
       </c>
       <c r="F676" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO PESSOAL (Outsourcing)</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="G676" t="inlineStr">
         <is>
-          <t>Bruna Santana</t>
+          <t>Vitor Domingues</t>
         </is>
       </c>
       <c r="H676" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="I676" t="n">
         <v>0</v>
       </c>
       <c r="J676" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="K676" t="n">
-        <v>3</v>
+        <v>65</v>
       </c>
     </row>
     <row r="677">
@@ -34456,7 +34456,7 @@
       </c>
       <c r="G677" t="inlineStr">
         <is>
-          <t>Camila Oliveira</t>
+          <t>Bruna Santana</t>
         </is>
       </c>
       <c r="H677" t="inlineStr">
@@ -34468,10 +34468,10 @@
         <v>0</v>
       </c>
       <c r="J677" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K677" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="678">
@@ -34507,22 +34507,22 @@
       </c>
       <c r="G678" t="inlineStr">
         <is>
-          <t>Elaine Assis</t>
+          <t>Camila Oliveira</t>
         </is>
       </c>
       <c r="H678" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I678" t="n">
         <v>0</v>
       </c>
       <c r="J678" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K678" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="679">
@@ -34558,22 +34558,22 @@
       </c>
       <c r="G679" t="inlineStr">
         <is>
-          <t>Fabiane Branco</t>
+          <t>Elaine Assis</t>
         </is>
       </c>
       <c r="H679" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I679" t="n">
         <v>0</v>
       </c>
       <c r="J679" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K679" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="680">
@@ -34609,12 +34609,12 @@
       </c>
       <c r="G680" t="inlineStr">
         <is>
-          <t>Jonas Nunes</t>
+          <t>Fabiane Branco</t>
         </is>
       </c>
       <c r="H680" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I680" t="n">
@@ -34624,7 +34624,7 @@
         <v>1</v>
       </c>
       <c r="K680" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="681">
@@ -34655,12 +34655,12 @@
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>DEPARTAMENTO PESSOAL (Outsourcing)</t>
         </is>
       </c>
       <c r="G681" t="inlineStr">
         <is>
-          <t>Bruna Santana</t>
+          <t>Jonas Nunes</t>
         </is>
       </c>
       <c r="H681" t="inlineStr">
@@ -34672,10 +34672,10 @@
         <v>0</v>
       </c>
       <c r="J681" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K681" t="n">
-        <v>99</v>
+        <v>15</v>
       </c>
     </row>
     <row r="682">
@@ -34711,7 +34711,7 @@
       </c>
       <c r="G682" t="inlineStr">
         <is>
-          <t>Camila Oliveira</t>
+          <t>Bruna Santana</t>
         </is>
       </c>
       <c r="H682" t="inlineStr">
@@ -34723,10 +34723,10 @@
         <v>0</v>
       </c>
       <c r="J682" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K682" t="n">
-        <v>31</v>
+        <v>99</v>
       </c>
     </row>
     <row r="683">
@@ -34762,22 +34762,22 @@
       </c>
       <c r="G683" t="inlineStr">
         <is>
-          <t>Daniel Moraes</t>
+          <t>Camila Oliveira</t>
         </is>
       </c>
       <c r="H683" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I683" t="n">
         <v>0</v>
       </c>
       <c r="J683" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K683" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
     </row>
     <row r="684">
@@ -34813,7 +34813,7 @@
       </c>
       <c r="G684" t="inlineStr">
         <is>
-          <t>Danilo Xavier</t>
+          <t>Daniel Moraes</t>
         </is>
       </c>
       <c r="H684" t="inlineStr">
@@ -34825,10 +34825,10 @@
         <v>0</v>
       </c>
       <c r="J684" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K684" t="n">
-        <v>151</v>
+        <v>41</v>
       </c>
     </row>
     <row r="685">
@@ -34864,7 +34864,7 @@
       </c>
       <c r="G685" t="inlineStr">
         <is>
-          <t>Elaine Assis</t>
+          <t>Danilo Xavier</t>
         </is>
       </c>
       <c r="H685" t="inlineStr">
@@ -34876,10 +34876,10 @@
         <v>0</v>
       </c>
       <c r="J685" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K685" t="n">
-        <v>56</v>
+        <v>151</v>
       </c>
     </row>
     <row r="686">
@@ -34915,12 +34915,12 @@
       </c>
       <c r="G686" t="inlineStr">
         <is>
-          <t>Eliene Lima</t>
+          <t>Elaine Assis</t>
         </is>
       </c>
       <c r="H686" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I686" t="n">
@@ -34930,7 +34930,7 @@
         <v>0</v>
       </c>
       <c r="K686" t="n">
-        <v>43</v>
+        <v>56</v>
       </c>
     </row>
     <row r="687">
@@ -34966,22 +34966,22 @@
       </c>
       <c r="G687" t="inlineStr">
         <is>
-          <t>Erica Oliveira</t>
+          <t>Eliene Lima</t>
         </is>
       </c>
       <c r="H687" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I687" t="n">
         <v>0</v>
       </c>
       <c r="J687" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K687" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="688">
@@ -35017,22 +35017,22 @@
       </c>
       <c r="G688" t="inlineStr">
         <is>
-          <t>Evellin Bispo</t>
+          <t>Erica Oliveira</t>
         </is>
       </c>
       <c r="H688" t="inlineStr">
         <is>
-          <t>Leandro Matos</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I688" t="n">
         <v>0</v>
       </c>
       <c r="J688" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K688" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
     </row>
     <row r="689">
@@ -35068,22 +35068,22 @@
       </c>
       <c r="G689" t="inlineStr">
         <is>
-          <t>Fabiane Branco</t>
+          <t>Evellin Bispo</t>
         </is>
       </c>
       <c r="H689" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>Leandro Matos</t>
         </is>
       </c>
       <c r="I689" t="n">
         <v>0</v>
       </c>
       <c r="J689" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K689" t="n">
-        <v>123</v>
+        <v>23</v>
       </c>
     </row>
     <row r="690">
@@ -35119,22 +35119,22 @@
       </c>
       <c r="G690" t="inlineStr">
         <is>
-          <t>Franciele Alves</t>
+          <t>Fabiane Branco</t>
         </is>
       </c>
       <c r="H690" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I690" t="n">
         <v>0</v>
       </c>
       <c r="J690" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K690" t="n">
-        <v>38</v>
+        <v>123</v>
       </c>
     </row>
     <row r="691">
@@ -35170,12 +35170,12 @@
       </c>
       <c r="G691" t="inlineStr">
         <is>
-          <t>Gabriela Peres</t>
+          <t>Franciele Alves</t>
         </is>
       </c>
       <c r="H691" t="inlineStr">
         <is>
-          <t>Leandro Matos</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I691" t="n">
@@ -35185,7 +35185,7 @@
         <v>0</v>
       </c>
       <c r="K691" t="n">
-        <v>12</v>
+        <v>38</v>
       </c>
     </row>
     <row r="692">
@@ -35221,22 +35221,22 @@
       </c>
       <c r="G692" t="inlineStr">
         <is>
-          <t>Grasiele Santos</t>
+          <t>Gabriela Peres</t>
         </is>
       </c>
       <c r="H692" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Leandro Matos</t>
         </is>
       </c>
       <c r="I692" t="n">
         <v>0</v>
       </c>
       <c r="J692" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K692" t="n">
-        <v>115</v>
+        <v>12</v>
       </c>
     </row>
     <row r="693">
@@ -35272,22 +35272,22 @@
       </c>
       <c r="G693" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Grasiele Santos</t>
         </is>
       </c>
       <c r="H693" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I693" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J693" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K693" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
     </row>
     <row r="694">
@@ -35323,22 +35323,22 @@
       </c>
       <c r="G694" t="inlineStr">
         <is>
-          <t>Janaina Rocha</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="H694" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I694" t="n">
         <v>0</v>
       </c>
       <c r="J694" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K694" t="n">
-        <v>86</v>
+        <v>110</v>
       </c>
     </row>
     <row r="695">
@@ -35374,22 +35374,22 @@
       </c>
       <c r="G695" t="inlineStr">
         <is>
-          <t>Jayne Tavares</t>
+          <t>Janaina Rocha</t>
         </is>
       </c>
       <c r="H695" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I695" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J695" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K695" t="n">
-        <v>127</v>
+        <v>88</v>
       </c>
     </row>
     <row r="696">
@@ -35425,22 +35425,22 @@
       </c>
       <c r="G696" t="inlineStr">
         <is>
-          <t>Jhenifer Tenorio</t>
+          <t>Jayne Tavares</t>
         </is>
       </c>
       <c r="H696" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I696" t="n">
         <v>0</v>
       </c>
       <c r="J696" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K696" t="n">
-        <v>114</v>
+        <v>127</v>
       </c>
     </row>
     <row r="697">
@@ -35476,7 +35476,7 @@
       </c>
       <c r="G697" t="inlineStr">
         <is>
-          <t>Jonas Nunes</t>
+          <t>Jhenifer Tenorio</t>
         </is>
       </c>
       <c r="H697" t="inlineStr">
@@ -35485,13 +35485,13 @@
         </is>
       </c>
       <c r="I697" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J697" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K697" t="n">
-        <v>88</v>
+        <v>115</v>
       </c>
     </row>
     <row r="698">
@@ -35527,22 +35527,22 @@
       </c>
       <c r="G698" t="inlineStr">
         <is>
-          <t>Kaique Souza</t>
+          <t>Jonas Nunes</t>
         </is>
       </c>
       <c r="H698" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I698" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J698" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K698" t="n">
-        <v>79</v>
+        <v>91</v>
       </c>
     </row>
     <row r="699">
@@ -35578,7 +35578,7 @@
       </c>
       <c r="G699" t="inlineStr">
         <is>
-          <t>Karine Sousa</t>
+          <t>Kaique Souza</t>
         </is>
       </c>
       <c r="H699" t="inlineStr">
@@ -35590,10 +35590,10 @@
         <v>0</v>
       </c>
       <c r="J699" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="K699" t="n">
-        <v>54</v>
+        <v>79</v>
       </c>
     </row>
     <row r="700">
@@ -35629,22 +35629,22 @@
       </c>
       <c r="G700" t="inlineStr">
         <is>
-          <t>Laysla Alves</t>
+          <t>Karine Sousa</t>
         </is>
       </c>
       <c r="H700" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I700" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J700" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K700" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="701">
@@ -35680,22 +35680,22 @@
       </c>
       <c r="G701" t="inlineStr">
         <is>
-          <t>Luana Marques</t>
+          <t>Laysla Alves</t>
         </is>
       </c>
       <c r="H701" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I701" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J701" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K701" t="n">
-        <v>17</v>
+        <v>60</v>
       </c>
     </row>
     <row r="702">
@@ -35731,7 +35731,7 @@
       </c>
       <c r="G702" t="inlineStr">
         <is>
-          <t>Maria Pires</t>
+          <t>Luana Marques</t>
         </is>
       </c>
       <c r="H702" t="inlineStr">
@@ -35743,10 +35743,10 @@
         <v>0</v>
       </c>
       <c r="J702" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K702" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="703">
@@ -35782,22 +35782,22 @@
       </c>
       <c r="G703" t="inlineStr">
         <is>
-          <t>Mauricio Lermen</t>
+          <t>Maria Pires</t>
         </is>
       </c>
       <c r="H703" t="inlineStr">
         <is>
-          <t>Mauricio Lermen</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I703" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J703" t="n">
+        <v>2</v>
+      </c>
+      <c r="K703" t="n">
         <v>1</v>
-      </c>
-      <c r="K703" t="n">
-        <v>14</v>
       </c>
     </row>
     <row r="704">
@@ -35833,22 +35833,22 @@
       </c>
       <c r="G704" t="inlineStr">
         <is>
-          <t>Micaele Cordeiro</t>
+          <t>Mauricio Lermen</t>
         </is>
       </c>
       <c r="H704" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>Mauricio Lermen</t>
         </is>
       </c>
       <c r="I704" t="n">
         <v>0</v>
       </c>
       <c r="J704" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K704" t="n">
-        <v>84</v>
+        <v>14</v>
       </c>
     </row>
     <row r="705">
@@ -35884,7 +35884,7 @@
       </c>
       <c r="G705" t="inlineStr">
         <is>
-          <t>Michele Silva</t>
+          <t>Micaele Cordeiro</t>
         </is>
       </c>
       <c r="H705" t="inlineStr">
@@ -35896,10 +35896,10 @@
         <v>0</v>
       </c>
       <c r="J705" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K705" t="n">
-        <v>67</v>
+        <v>84</v>
       </c>
     </row>
     <row r="706">
@@ -35935,18 +35935,22 @@
       </c>
       <c r="G706" t="inlineStr">
         <is>
-          <t>Mikael Teixeira</t>
-        </is>
-      </c>
-      <c r="H706" t="inlineStr"/>
+          <t>Michele Silva</t>
+        </is>
+      </c>
+      <c r="H706" t="inlineStr">
+        <is>
+          <t>Sara Cavalheiro</t>
+        </is>
+      </c>
       <c r="I706" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J706" t="n">
         <v>5</v>
       </c>
       <c r="K706" t="n">
-        <v>4</v>
+        <v>67</v>
       </c>
     </row>
     <row r="707">
@@ -35982,22 +35986,18 @@
       </c>
       <c r="G707" t="inlineStr">
         <is>
-          <t>Murilo Marques</t>
-        </is>
-      </c>
-      <c r="H707" t="inlineStr">
-        <is>
-          <t>David Bragança</t>
-        </is>
-      </c>
+          <t>Mikael Teixeira</t>
+        </is>
+      </c>
+      <c r="H707" t="inlineStr"/>
       <c r="I707" t="n">
         <v>0</v>
       </c>
       <c r="J707" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K707" t="n">
-        <v>42</v>
+        <v>4</v>
       </c>
     </row>
     <row r="708">
@@ -36033,22 +36033,22 @@
       </c>
       <c r="G708" t="inlineStr">
         <is>
-          <t>Natalia Batista</t>
+          <t>Murilo Marques</t>
         </is>
       </c>
       <c r="H708" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I708" t="n">
         <v>0</v>
       </c>
       <c r="J708" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K708" t="n">
-        <v>102</v>
+        <v>42</v>
       </c>
     </row>
     <row r="709">
@@ -36084,22 +36084,22 @@
       </c>
       <c r="G709" t="inlineStr">
         <is>
-          <t>Natalia Silva</t>
+          <t>Natalia Batista</t>
         </is>
       </c>
       <c r="H709" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I709" t="n">
         <v>0</v>
       </c>
       <c r="J709" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="K709" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="710">
@@ -36135,22 +36135,22 @@
       </c>
       <c r="G710" t="inlineStr">
         <is>
-          <t>Oliene Mariano</t>
+          <t>Natalia Silva</t>
         </is>
       </c>
       <c r="H710" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I710" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J710" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="K710" t="n">
-        <v>75</v>
+        <v>104</v>
       </c>
     </row>
     <row r="711">
@@ -36186,22 +36186,22 @@
       </c>
       <c r="G711" t="inlineStr">
         <is>
-          <t>Priscila Aguiar</t>
+          <t>Oliene Mariano</t>
         </is>
       </c>
       <c r="H711" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I711" t="n">
         <v>0</v>
       </c>
       <c r="J711" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K711" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
     </row>
     <row r="712">
@@ -36237,7 +36237,7 @@
       </c>
       <c r="G712" t="inlineStr">
         <is>
-          <t>Rebeca Ribeiro</t>
+          <t>Priscila Aguiar</t>
         </is>
       </c>
       <c r="H712" t="inlineStr">
@@ -36246,13 +36246,13 @@
         </is>
       </c>
       <c r="I712" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="J712" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="K712" t="n">
-        <v>66</v>
+        <v>98</v>
       </c>
     </row>
     <row r="713">
@@ -36288,7 +36288,7 @@
       </c>
       <c r="G713" t="inlineStr">
         <is>
-          <t>Roberta Souza</t>
+          <t>Rebeca Ribeiro</t>
         </is>
       </c>
       <c r="H713" t="inlineStr">
@@ -36300,10 +36300,10 @@
         <v>0</v>
       </c>
       <c r="J713" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K713" t="n">
-        <v>76</v>
+        <v>66</v>
       </c>
     </row>
     <row r="714">
@@ -36339,7 +36339,7 @@
       </c>
       <c r="G714" t="inlineStr">
         <is>
-          <t>Ronildo Santos</t>
+          <t>Roberta Souza</t>
         </is>
       </c>
       <c r="H714" t="inlineStr">
@@ -36354,7 +36354,7 @@
         <v>1</v>
       </c>
       <c r="K714" t="n">
-        <v>4</v>
+        <v>76</v>
       </c>
     </row>
     <row r="715">
@@ -36390,22 +36390,22 @@
       </c>
       <c r="G715" t="inlineStr">
         <is>
-          <t>Rozania Santos</t>
+          <t>Ronildo Santos</t>
         </is>
       </c>
       <c r="H715" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I715" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J715" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="K715" t="n">
-        <v>106</v>
+        <v>6</v>
       </c>
     </row>
     <row r="716">
@@ -36441,22 +36441,22 @@
       </c>
       <c r="G716" t="inlineStr">
         <is>
-          <t>Santos Karina</t>
+          <t>Rozania Santos</t>
         </is>
       </c>
       <c r="H716" t="inlineStr">
         <is>
-          <t>Leandro Matos</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I716" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J716" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K716" t="n">
-        <v>2</v>
+        <v>106</v>
       </c>
     </row>
     <row r="717">
@@ -36492,22 +36492,22 @@
       </c>
       <c r="G717" t="inlineStr">
         <is>
-          <t>Sibelly Pereira</t>
+          <t>Santos Karina</t>
         </is>
       </c>
       <c r="H717" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Leandro Matos</t>
         </is>
       </c>
       <c r="I717" t="n">
         <v>0</v>
       </c>
       <c r="J717" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K717" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
     </row>
     <row r="718">
@@ -36543,22 +36543,22 @@
       </c>
       <c r="G718" t="inlineStr">
         <is>
-          <t>Tania Luz</t>
+          <t>Sibelly Pereira</t>
         </is>
       </c>
       <c r="H718" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I718" t="n">
         <v>0</v>
       </c>
       <c r="J718" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K718" t="n">
-        <v>54</v>
+        <v>42</v>
       </c>
     </row>
     <row r="719">
@@ -36594,22 +36594,22 @@
       </c>
       <c r="G719" t="inlineStr">
         <is>
-          <t>Vitor Guedes</t>
+          <t>Tania Luz</t>
         </is>
       </c>
       <c r="H719" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I719" t="n">
         <v>0</v>
       </c>
       <c r="J719" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K719" t="n">
-        <v>134</v>
+        <v>54</v>
       </c>
     </row>
     <row r="720">
@@ -36640,27 +36640,27 @@
       </c>
       <c r="F720" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="G720" t="inlineStr">
         <is>
-          <t>Andrea Medeiros</t>
+          <t>Vitor Guedes</t>
         </is>
       </c>
       <c r="H720" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I720" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J720" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="K720" t="n">
-        <v>55</v>
+        <v>134</v>
       </c>
     </row>
     <row r="721">
@@ -36696,7 +36696,7 @@
       </c>
       <c r="G721" t="inlineStr">
         <is>
-          <t>Caroline Nascimento</t>
+          <t>Andrea Medeiros</t>
         </is>
       </c>
       <c r="H721" t="inlineStr">
@@ -36705,13 +36705,13 @@
         </is>
       </c>
       <c r="I721" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J721" t="n">
-        <v>72</v>
+        <v>20</v>
       </c>
       <c r="K721" t="n">
-        <v>125</v>
+        <v>58</v>
       </c>
     </row>
     <row r="722">
@@ -36747,7 +36747,7 @@
       </c>
       <c r="G722" t="inlineStr">
         <is>
-          <t>Cristiana Grizostomo</t>
+          <t>Caroline Nascimento</t>
         </is>
       </c>
       <c r="H722" t="inlineStr">
@@ -36756,13 +36756,13 @@
         </is>
       </c>
       <c r="I722" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J722" t="n">
-        <v>17</v>
+        <v>80</v>
       </c>
       <c r="K722" t="n">
-        <v>49</v>
+        <v>133</v>
       </c>
     </row>
     <row r="723">
@@ -36798,18 +36798,22 @@
       </c>
       <c r="G723" t="inlineStr">
         <is>
-          <t>Denis Reis</t>
-        </is>
-      </c>
-      <c r="H723" t="inlineStr"/>
+          <t>Cristiana Grizostomo</t>
+        </is>
+      </c>
+      <c r="H723" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
       <c r="I723" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J723" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K723" t="n">
-        <v>83</v>
+        <v>52</v>
       </c>
     </row>
     <row r="724">
@@ -36845,22 +36849,18 @@
       </c>
       <c r="G724" t="inlineStr">
         <is>
-          <t>Eliane Moreira</t>
-        </is>
-      </c>
-      <c r="H724" t="inlineStr">
-        <is>
-          <t>Nayara Oliveira</t>
-        </is>
-      </c>
+          <t>Denis Reis</t>
+        </is>
+      </c>
+      <c r="H724" t="inlineStr"/>
       <c r="I724" t="n">
         <v>0</v>
       </c>
       <c r="J724" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="K724" t="n">
-        <v>91</v>
+        <v>83</v>
       </c>
     </row>
     <row r="725">
@@ -36896,7 +36896,7 @@
       </c>
       <c r="G725" t="inlineStr">
         <is>
-          <t>Gustavo Tonan</t>
+          <t>Eliane Moreira</t>
         </is>
       </c>
       <c r="H725" t="inlineStr">
@@ -36905,13 +36905,13 @@
         </is>
       </c>
       <c r="I725" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J725" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="K725" t="n">
-        <v>68</v>
+        <v>96</v>
       </c>
     </row>
     <row r="726">
@@ -36947,7 +36947,7 @@
       </c>
       <c r="G726" t="inlineStr">
         <is>
-          <t>Jonatan Hayashibara</t>
+          <t>Gustavo Tonan</t>
         </is>
       </c>
       <c r="H726" t="inlineStr">
@@ -36956,13 +36956,13 @@
         </is>
       </c>
       <c r="I726" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J726" t="n">
-        <v>171</v>
+        <v>26</v>
       </c>
       <c r="K726" t="n">
-        <v>283</v>
+        <v>78</v>
       </c>
     </row>
     <row r="727">
@@ -36998,7 +36998,7 @@
       </c>
       <c r="G727" t="inlineStr">
         <is>
-          <t>Lais Arruda</t>
+          <t>Jonatan Hayashibara</t>
         </is>
       </c>
       <c r="H727" t="inlineStr">
@@ -37007,13 +37007,13 @@
         </is>
       </c>
       <c r="I727" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J727" t="n">
-        <v>5</v>
+        <v>180</v>
       </c>
       <c r="K727" t="n">
-        <v>63</v>
+        <v>292</v>
       </c>
     </row>
     <row r="728">
@@ -37049,7 +37049,7 @@
       </c>
       <c r="G728" t="inlineStr">
         <is>
-          <t>Luan Batista</t>
+          <t>Lais Arruda</t>
         </is>
       </c>
       <c r="H728" t="inlineStr">
@@ -37058,13 +37058,13 @@
         </is>
       </c>
       <c r="I728" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="J728" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="K728" t="n">
-        <v>63</v>
+        <v>94</v>
       </c>
     </row>
     <row r="729">
@@ -37100,7 +37100,7 @@
       </c>
       <c r="G729" t="inlineStr">
         <is>
-          <t>Maria Garcia</t>
+          <t>Luan Batista</t>
         </is>
       </c>
       <c r="H729" t="inlineStr">
@@ -37112,10 +37112,10 @@
         <v>0</v>
       </c>
       <c r="J729" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K729" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="730">
@@ -37151,7 +37151,7 @@
       </c>
       <c r="G730" t="inlineStr">
         <is>
-          <t>Priscila Volpe</t>
+          <t>Maria Garcia</t>
         </is>
       </c>
       <c r="H730" t="inlineStr">
@@ -37163,10 +37163,10 @@
         <v>0</v>
       </c>
       <c r="J730" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="K730" t="n">
-        <v>10</v>
+        <v>59</v>
       </c>
     </row>
     <row r="731">
@@ -37202,7 +37202,7 @@
       </c>
       <c r="G731" t="inlineStr">
         <is>
-          <t>Rodrigo Souza</t>
+          <t>Priscila Volpe</t>
         </is>
       </c>
       <c r="H731" t="inlineStr">
@@ -37214,10 +37214,10 @@
         <v>0</v>
       </c>
       <c r="J731" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K731" t="n">
-        <v>54</v>
+        <v>10</v>
       </c>
     </row>
     <row r="732">
@@ -37253,7 +37253,7 @@
       </c>
       <c r="G732" t="inlineStr">
         <is>
-          <t>Romario Silva</t>
+          <t>Rodrigo Souza</t>
         </is>
       </c>
       <c r="H732" t="inlineStr">
@@ -37262,13 +37262,13 @@
         </is>
       </c>
       <c r="I732" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J732" t="n">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="K732" t="n">
-        <v>152</v>
+        <v>78</v>
       </c>
     </row>
     <row r="733">
@@ -37304,7 +37304,7 @@
       </c>
       <c r="G733" t="inlineStr">
         <is>
-          <t>Rosilene Santos</t>
+          <t>Romario Silva</t>
         </is>
       </c>
       <c r="H733" t="inlineStr">
@@ -37313,13 +37313,13 @@
         </is>
       </c>
       <c r="I733" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J733" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="K733" t="n">
-        <v>75</v>
+        <v>155</v>
       </c>
     </row>
     <row r="734">
@@ -37355,7 +37355,7 @@
       </c>
       <c r="G734" t="inlineStr">
         <is>
-          <t>Suede Gomes</t>
+          <t>Rosilene Santos</t>
         </is>
       </c>
       <c r="H734" t="inlineStr">
@@ -37364,13 +37364,13 @@
         </is>
       </c>
       <c r="I734" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J734" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="K734" t="n">
-        <v>28</v>
+        <v>77</v>
       </c>
     </row>
     <row r="735">
@@ -37406,7 +37406,7 @@
       </c>
       <c r="G735" t="inlineStr">
         <is>
-          <t>Taina Silva</t>
+          <t>Suede Gomes</t>
         </is>
       </c>
       <c r="H735" t="inlineStr">
@@ -37415,13 +37415,13 @@
         </is>
       </c>
       <c r="I735" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J735" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="K735" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="736">
@@ -37457,7 +37457,7 @@
       </c>
       <c r="G736" t="inlineStr">
         <is>
-          <t>Thayna Melo</t>
+          <t>Taina Silva</t>
         </is>
       </c>
       <c r="H736" t="inlineStr">
@@ -37466,13 +37466,13 @@
         </is>
       </c>
       <c r="I736" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J736" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K736" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="737">
@@ -37508,7 +37508,7 @@
       </c>
       <c r="G737" t="inlineStr">
         <is>
-          <t>Vanessa Santana</t>
+          <t>Thayna Melo</t>
         </is>
       </c>
       <c r="H737" t="inlineStr">
@@ -37520,10 +37520,10 @@
         <v>0</v>
       </c>
       <c r="J737" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="K737" t="n">
-        <v>161</v>
+        <v>40</v>
       </c>
     </row>
     <row r="738">
@@ -37554,27 +37554,27 @@
       </c>
       <c r="F738" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="G738" t="inlineStr">
         <is>
-          <t>Alaine Neres</t>
+          <t>Vanessa Santana</t>
         </is>
       </c>
       <c r="H738" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
       <c r="I738" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J738" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="K738" t="n">
-        <v>81</v>
+        <v>163</v>
       </c>
     </row>
     <row r="739">
@@ -37610,22 +37610,22 @@
       </c>
       <c r="G739" t="inlineStr">
         <is>
-          <t>Andre Silva</t>
+          <t>Alaine Neres</t>
         </is>
       </c>
       <c r="H739" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I739" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J739" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="K739" t="n">
-        <v>60</v>
+        <v>83</v>
       </c>
     </row>
     <row r="740">
@@ -37661,22 +37661,22 @@
       </c>
       <c r="G740" t="inlineStr">
         <is>
-          <t>Anna Ramalho</t>
+          <t>Andre Silva</t>
         </is>
       </c>
       <c r="H740" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I740" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J740" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K740" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="741">
@@ -37712,7 +37712,7 @@
       </c>
       <c r="G741" t="inlineStr">
         <is>
-          <t>Beatriz Ferreira</t>
+          <t>Anna Ramalho</t>
         </is>
       </c>
       <c r="H741" t="inlineStr">
@@ -37721,13 +37721,13 @@
         </is>
       </c>
       <c r="I741" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J741" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="K741" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
     </row>
     <row r="742">
@@ -37763,22 +37763,22 @@
       </c>
       <c r="G742" t="inlineStr">
         <is>
-          <t>Brenda Batista</t>
+          <t>Beatriz Ferreira</t>
         </is>
       </c>
       <c r="H742" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="I742" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J742" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="K742" t="n">
-        <v>46</v>
+        <v>74</v>
       </c>
     </row>
     <row r="743">
@@ -37814,22 +37814,22 @@
       </c>
       <c r="G743" t="inlineStr">
         <is>
-          <t>Bruna Souza</t>
+          <t>Brenda Batista</t>
         </is>
       </c>
       <c r="H743" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I743" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J743" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K743" t="n">
-        <v>71</v>
+        <v>46</v>
       </c>
     </row>
     <row r="744">
@@ -37865,22 +37865,22 @@
       </c>
       <c r="G744" t="inlineStr">
         <is>
-          <t>Bruno Henrique</t>
+          <t>Bruna Souza</t>
         </is>
       </c>
       <c r="H744" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I744" t="n">
         <v>0</v>
       </c>
       <c r="J744" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="K744" t="n">
-        <v>85</v>
+        <v>71</v>
       </c>
     </row>
     <row r="745">
@@ -37916,18 +37916,22 @@
       </c>
       <c r="G745" t="inlineStr">
         <is>
-          <t>Claudineia Rodrigues</t>
-        </is>
-      </c>
-      <c r="H745" t="inlineStr"/>
+          <t>Bruno Henrique</t>
+        </is>
+      </c>
+      <c r="H745" t="inlineStr">
+        <is>
+          <t>Lorrane Santos</t>
+        </is>
+      </c>
       <c r="I745" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J745" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K745" t="n">
-        <v>128</v>
+        <v>91</v>
       </c>
     </row>
     <row r="746">
@@ -37963,22 +37967,18 @@
       </c>
       <c r="G746" t="inlineStr">
         <is>
-          <t>Cristina Leite</t>
-        </is>
-      </c>
-      <c r="H746" t="inlineStr">
-        <is>
-          <t>Ricardo Fischer</t>
-        </is>
-      </c>
+          <t>Claudineia Rodrigues</t>
+        </is>
+      </c>
+      <c r="H746" t="inlineStr"/>
       <c r="I746" t="n">
         <v>0</v>
       </c>
       <c r="J746" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="K746" t="n">
-        <v>120</v>
+        <v>131</v>
       </c>
     </row>
     <row r="747">
@@ -38014,22 +38014,22 @@
       </c>
       <c r="G747" t="inlineStr">
         <is>
-          <t>Davi Santos</t>
+          <t>Cristina Leite</t>
         </is>
       </c>
       <c r="H747" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="I747" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J747" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="K747" t="n">
-        <v>85</v>
+        <v>124</v>
       </c>
     </row>
     <row r="748">
@@ -38065,22 +38065,22 @@
       </c>
       <c r="G748" t="inlineStr">
         <is>
-          <t>Deleia Oliveira</t>
+          <t>Davi Santos</t>
         </is>
       </c>
       <c r="H748" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I748" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J748" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K748" t="n">
-        <v>80</v>
+        <v>89</v>
       </c>
     </row>
     <row r="749">
@@ -38116,22 +38116,22 @@
       </c>
       <c r="G749" t="inlineStr">
         <is>
-          <t>Diego Pereira</t>
+          <t>Deleia Oliveira</t>
         </is>
       </c>
       <c r="H749" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I749" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J749" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K749" t="n">
-        <v>65</v>
+        <v>81</v>
       </c>
     </row>
     <row r="750">
@@ -38167,22 +38167,22 @@
       </c>
       <c r="G750" t="inlineStr">
         <is>
-          <t>Eduardo Lopes</t>
+          <t>Diego Pereira</t>
         </is>
       </c>
       <c r="H750" t="inlineStr">
         <is>
-          <t>Idna Sousa</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I750" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J750" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="K750" t="n">
-        <v>16</v>
+        <v>68</v>
       </c>
     </row>
     <row r="751">
@@ -38218,22 +38218,22 @@
       </c>
       <c r="G751" t="inlineStr">
         <is>
-          <t>Gislaine Lima</t>
+          <t>Eduardo Lopes</t>
         </is>
       </c>
       <c r="H751" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Idna Sousa</t>
         </is>
       </c>
       <c r="I751" t="n">
         <v>0</v>
       </c>
       <c r="J751" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="K751" t="n">
-        <v>71</v>
+        <v>16</v>
       </c>
     </row>
     <row r="752">
@@ -38269,22 +38269,22 @@
       </c>
       <c r="G752" t="inlineStr">
         <is>
-          <t>Gustavo Santos</t>
+          <t>Gislaine Lima</t>
         </is>
       </c>
       <c r="H752" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I752" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J752" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="K752" t="n">
-        <v>143</v>
+        <v>73</v>
       </c>
     </row>
     <row r="753">
@@ -38320,22 +38320,22 @@
       </c>
       <c r="G753" t="inlineStr">
         <is>
-          <t>Igor Valezi</t>
+          <t>Gustavo Santos</t>
         </is>
       </c>
       <c r="H753" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="I753" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="J753" t="n">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="K753" t="n">
-        <v>74</v>
+        <v>178</v>
       </c>
     </row>
     <row r="754">
@@ -38371,22 +38371,22 @@
       </c>
       <c r="G754" t="inlineStr">
         <is>
-          <t>Izabely Araujo</t>
+          <t>Igor Valezi</t>
         </is>
       </c>
       <c r="H754" t="inlineStr">
         <is>
-          <t>Idna Sousa</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I754" t="n">
         <v>0</v>
       </c>
       <c r="J754" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K754" t="n">
-        <v>4</v>
+        <v>74</v>
       </c>
     </row>
     <row r="755">
@@ -38422,22 +38422,22 @@
       </c>
       <c r="G755" t="inlineStr">
         <is>
-          <t>Joanna Costa</t>
+          <t>Izabely Araujo</t>
         </is>
       </c>
       <c r="H755" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Idna Sousa</t>
         </is>
       </c>
       <c r="I755" t="n">
         <v>0</v>
       </c>
       <c r="J755" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K755" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
     </row>
     <row r="756">
@@ -38473,22 +38473,22 @@
       </c>
       <c r="G756" t="inlineStr">
         <is>
-          <t>Jose Natan</t>
+          <t>Joanna Costa</t>
         </is>
       </c>
       <c r="H756" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I756" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J756" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="K756" t="n">
-        <v>94</v>
+        <v>18</v>
       </c>
     </row>
     <row r="757">
@@ -38524,7 +38524,7 @@
       </c>
       <c r="G757" t="inlineStr">
         <is>
-          <t>João Oliveira</t>
+          <t>Jose Natan</t>
         </is>
       </c>
       <c r="H757" t="inlineStr">
@@ -38533,13 +38533,13 @@
         </is>
       </c>
       <c r="I757" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J757" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="K757" t="n">
-        <v>9</v>
+        <v>98</v>
       </c>
     </row>
     <row r="758">
@@ -38575,22 +38575,22 @@
       </c>
       <c r="G758" t="inlineStr">
         <is>
-          <t>Juan Ribeiro</t>
+          <t>João Oliveira</t>
         </is>
       </c>
       <c r="H758" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I758" t="n">
         <v>0</v>
       </c>
       <c r="J758" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="K758" t="n">
-        <v>78</v>
+        <v>9</v>
       </c>
     </row>
     <row r="759">
@@ -38626,22 +38626,22 @@
       </c>
       <c r="G759" t="inlineStr">
         <is>
-          <t>Juliana Valeria</t>
+          <t>Juan Ribeiro</t>
         </is>
       </c>
       <c r="H759" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I759" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J759" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="K759" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="760">
@@ -38677,7 +38677,7 @@
       </c>
       <c r="G760" t="inlineStr">
         <is>
-          <t>Juliane Vaz</t>
+          <t>Juliana Valeria</t>
         </is>
       </c>
       <c r="H760" t="inlineStr">
@@ -38686,13 +38686,13 @@
         </is>
       </c>
       <c r="I760" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J760" t="n">
-        <v>72</v>
+        <v>31</v>
       </c>
       <c r="K760" t="n">
-        <v>173</v>
+        <v>93</v>
       </c>
     </row>
     <row r="761">
@@ -38728,22 +38728,22 @@
       </c>
       <c r="G761" t="inlineStr">
         <is>
-          <t>Katia Xavier</t>
+          <t>Juliane Vaz</t>
         </is>
       </c>
       <c r="H761" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I761" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J761" t="n">
-        <v>25</v>
+        <v>81</v>
       </c>
       <c r="K761" t="n">
-        <v>77</v>
+        <v>182</v>
       </c>
     </row>
     <row r="762">
@@ -38779,22 +38779,22 @@
       </c>
       <c r="G762" t="inlineStr">
         <is>
-          <t>Larissa Félix</t>
+          <t>Katia Xavier</t>
         </is>
       </c>
       <c r="H762" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I762" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J762" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="K762" t="n">
-        <v>110</v>
+        <v>81</v>
       </c>
     </row>
     <row r="763">
@@ -38830,22 +38830,22 @@
       </c>
       <c r="G763" t="inlineStr">
         <is>
-          <t>Léia de Oliveira</t>
+          <t>Larissa Félix</t>
         </is>
       </c>
       <c r="H763" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I763" t="n">
         <v>0</v>
       </c>
       <c r="J763" t="n">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="K763" t="n">
-        <v>99</v>
+        <v>110</v>
       </c>
     </row>
     <row r="764">
@@ -38881,7 +38881,7 @@
       </c>
       <c r="G764" t="inlineStr">
         <is>
-          <t>Maria Gualberto</t>
+          <t>Léia de Oliveira</t>
         </is>
       </c>
       <c r="H764" t="inlineStr">
@@ -38890,13 +38890,13 @@
         </is>
       </c>
       <c r="I764" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J764" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K764" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="765">
@@ -38932,22 +38932,22 @@
       </c>
       <c r="G765" t="inlineStr">
         <is>
-          <t>Priscila Moreira</t>
+          <t>Maria Gualberto</t>
         </is>
       </c>
       <c r="H765" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I765" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J765" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K765" t="n">
-        <v>79</v>
+        <v>95</v>
       </c>
     </row>
     <row r="766">
@@ -38983,22 +38983,22 @@
       </c>
       <c r="G766" t="inlineStr">
         <is>
-          <t>Regiane Santos</t>
+          <t>Nathany Silva</t>
         </is>
       </c>
       <c r="H766" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I766" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J766" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K766" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="767">
@@ -39034,7 +39034,7 @@
       </c>
       <c r="G767" t="inlineStr">
         <is>
-          <t>Shofia Gomes</t>
+          <t>Priscila Moreira</t>
         </is>
       </c>
       <c r="H767" t="inlineStr">
@@ -39043,13 +39043,13 @@
         </is>
       </c>
       <c r="I767" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J767" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K767" t="n">
-        <v>98</v>
+        <v>79</v>
       </c>
     </row>
     <row r="768">
@@ -39085,7 +39085,7 @@
       </c>
       <c r="G768" t="inlineStr">
         <is>
-          <t>Vanessa Tavares</t>
+          <t>Regiane Santos</t>
         </is>
       </c>
       <c r="H768" t="inlineStr">
@@ -39097,10 +39097,10 @@
         <v>0</v>
       </c>
       <c r="J768" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K768" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
     <row r="769">
@@ -39136,22 +39136,22 @@
       </c>
       <c r="G769" t="inlineStr">
         <is>
-          <t>Willian Luz</t>
+          <t>Shofia Gomes</t>
         </is>
       </c>
       <c r="H769" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="I769" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="J769" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="K769" t="n">
-        <v>60</v>
+        <v>118</v>
       </c>
     </row>
     <row r="770">
@@ -39187,7 +39187,7 @@
       </c>
       <c r="G770" t="inlineStr">
         <is>
-          <t>Yasmim Oliveira</t>
+          <t>Vanessa Tavares</t>
         </is>
       </c>
       <c r="H770" t="inlineStr">
@@ -39196,13 +39196,13 @@
         </is>
       </c>
       <c r="I770" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J770" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K770" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
     </row>
     <row r="771">
@@ -39233,23 +39233,27 @@
       </c>
       <c r="F771" t="inlineStr">
         <is>
-          <t>ESCRITA FISCAL (Outsourcing)</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="G771" t="inlineStr">
         <is>
-          <t>Claudineia Rodrigues</t>
-        </is>
-      </c>
-      <c r="H771" t="inlineStr"/>
+          <t>Willian Luz</t>
+        </is>
+      </c>
+      <c r="H771" t="inlineStr">
+        <is>
+          <t>Larice Souza</t>
+        </is>
+      </c>
       <c r="I771" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J771" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="K771" t="n">
-        <v>4</v>
+        <v>62</v>
       </c>
     </row>
     <row r="772">
@@ -39280,27 +39284,27 @@
       </c>
       <c r="F772" t="inlineStr">
         <is>
-          <t>ESCRITA FISCAL (Outsourcing)</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="G772" t="inlineStr">
         <is>
-          <t>Diego Pereira</t>
+          <t>Yasmim Oliveira</t>
         </is>
       </c>
       <c r="H772" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I772" t="n">
         <v>0</v>
       </c>
       <c r="J772" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K772" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
     </row>
     <row r="773">
@@ -39336,22 +39340,18 @@
       </c>
       <c r="G773" t="inlineStr">
         <is>
-          <t>Gislaine Lima</t>
-        </is>
-      </c>
-      <c r="H773" t="inlineStr">
-        <is>
-          <t>Lorrane Santos</t>
-        </is>
-      </c>
+          <t>Claudineia Rodrigues</t>
+        </is>
+      </c>
+      <c r="H773" t="inlineStr"/>
       <c r="I773" t="n">
         <v>0</v>
       </c>
       <c r="J773" t="n">
+        <v>2</v>
+      </c>
+      <c r="K773" t="n">
         <v>4</v>
-      </c>
-      <c r="K773" t="n">
-        <v>24</v>
       </c>
     </row>
     <row r="774">
@@ -39387,22 +39387,22 @@
       </c>
       <c r="G774" t="inlineStr">
         <is>
-          <t>Joanna Costa</t>
+          <t>Diego Pereira</t>
         </is>
       </c>
       <c r="H774" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I774" t="n">
         <v>0</v>
       </c>
       <c r="J774" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="K774" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
     </row>
     <row r="775">
@@ -39438,22 +39438,22 @@
       </c>
       <c r="G775" t="inlineStr">
         <is>
-          <t>João Oliveira</t>
+          <t>Gislaine Lima</t>
         </is>
       </c>
       <c r="H775" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I775" t="n">
         <v>0</v>
       </c>
       <c r="J775" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K775" t="n">
-        <v>37</v>
+        <v>24</v>
       </c>
     </row>
     <row r="776">
@@ -39489,22 +39489,22 @@
       </c>
       <c r="G776" t="inlineStr">
         <is>
-          <t>Regiane Santos</t>
+          <t>Joanna Costa</t>
         </is>
       </c>
       <c r="H776" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I776" t="n">
         <v>0</v>
       </c>
       <c r="J776" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="K776" t="n">
-        <v>13</v>
+        <v>40</v>
       </c>
     </row>
     <row r="777">
@@ -39540,7 +39540,7 @@
       </c>
       <c r="G777" t="inlineStr">
         <is>
-          <t>Yasmim Oliveira</t>
+          <t>João Oliveira</t>
         </is>
       </c>
       <c r="H777" t="inlineStr">
@@ -39552,10 +39552,10 @@
         <v>0</v>
       </c>
       <c r="J777" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K777" t="n">
-        <v>4</v>
+        <v>37</v>
       </c>
     </row>
     <row r="778">
@@ -39586,23 +39586,27 @@
       </c>
       <c r="F778" t="inlineStr">
         <is>
-          <t>FIN - CONTÁBIL</t>
+          <t>ESCRITA FISCAL (Outsourcing)</t>
         </is>
       </c>
       <c r="G778" t="inlineStr">
         <is>
-          <t>Daniele Faria</t>
-        </is>
-      </c>
-      <c r="H778" t="inlineStr"/>
+          <t>Regiane Santos</t>
+        </is>
+      </c>
+      <c r="H778" t="inlineStr">
+        <is>
+          <t>Larice Souza</t>
+        </is>
+      </c>
       <c r="I778" t="n">
         <v>0</v>
       </c>
       <c r="J778" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="K778" t="n">
-        <v>62</v>
+        <v>13</v>
       </c>
     </row>
     <row r="779">
@@ -39633,23 +39637,27 @@
       </c>
       <c r="F779" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>ESCRITA FISCAL (Outsourcing)</t>
         </is>
       </c>
       <c r="G779" t="inlineStr">
         <is>
-          <t>Ana Santana</t>
-        </is>
-      </c>
-      <c r="H779" t="inlineStr"/>
+          <t>Yasmim Oliveira</t>
+        </is>
+      </c>
+      <c r="H779" t="inlineStr">
+        <is>
+          <t>Larice Souza</t>
+        </is>
+      </c>
       <c r="I779" t="n">
         <v>0</v>
       </c>
       <c r="J779" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K779" t="n">
-        <v>394</v>
+        <v>4</v>
       </c>
     </row>
     <row r="780">
@@ -39680,12 +39688,12 @@
       </c>
       <c r="F780" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>FIN - CONTÁBIL</t>
         </is>
       </c>
       <c r="G780" t="inlineStr">
         <is>
-          <t>Andre Coelho</t>
+          <t>Daniele Faria</t>
         </is>
       </c>
       <c r="H780" t="inlineStr"/>
@@ -39693,10 +39701,10 @@
         <v>0</v>
       </c>
       <c r="J780" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K780" t="n">
-        <v>3</v>
+        <v>62</v>
       </c>
     </row>
     <row r="781">
@@ -39732,18 +39740,18 @@
       </c>
       <c r="G781" t="inlineStr">
         <is>
-          <t>Bianca Castro</t>
+          <t>Ana Santana</t>
         </is>
       </c>
       <c r="H781" t="inlineStr"/>
       <c r="I781" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="J781" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="K781" t="n">
-        <v>325</v>
+        <v>397</v>
       </c>
     </row>
     <row r="782">
@@ -39779,7 +39787,7 @@
       </c>
       <c r="G782" t="inlineStr">
         <is>
-          <t>Bruna Costa</t>
+          <t>Andre Coelho</t>
         </is>
       </c>
       <c r="H782" t="inlineStr"/>
@@ -39787,10 +39795,10 @@
         <v>0</v>
       </c>
       <c r="J782" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K782" t="n">
-        <v>34</v>
+        <v>3</v>
       </c>
     </row>
     <row r="783">
@@ -39826,18 +39834,18 @@
       </c>
       <c r="G783" t="inlineStr">
         <is>
-          <t>Daniela Silva</t>
+          <t>Bianca Castro</t>
         </is>
       </c>
       <c r="H783" t="inlineStr"/>
       <c r="I783" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J783" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K783" t="n">
-        <v>11</v>
+        <v>325</v>
       </c>
     </row>
     <row r="784">
@@ -39873,7 +39881,7 @@
       </c>
       <c r="G784" t="inlineStr">
         <is>
-          <t>Isabelli Afonso</t>
+          <t>Bruna Costa</t>
         </is>
       </c>
       <c r="H784" t="inlineStr"/>
@@ -39881,10 +39889,10 @@
         <v>0</v>
       </c>
       <c r="J784" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K784" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="785">
@@ -39920,18 +39928,18 @@
       </c>
       <c r="G785" t="inlineStr">
         <is>
-          <t>Jurema Damacena - SAC</t>
+          <t>Daniela Silva</t>
         </is>
       </c>
       <c r="H785" t="inlineStr"/>
       <c r="I785" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J785" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K785" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="786">
@@ -39967,7 +39975,7 @@
       </c>
       <c r="G786" t="inlineStr">
         <is>
-          <t>Leticia Queiroz</t>
+          <t>Isabelli Afonso</t>
         </is>
       </c>
       <c r="H786" t="inlineStr"/>
@@ -39975,10 +39983,10 @@
         <v>0</v>
       </c>
       <c r="J786" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K786" t="n">
-        <v>47</v>
+        <v>29</v>
       </c>
     </row>
     <row r="787">
@@ -40014,7 +40022,7 @@
       </c>
       <c r="G787" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Jurema Damacena - SAC</t>
         </is>
       </c>
       <c r="H787" t="inlineStr"/>
@@ -40025,7 +40033,7 @@
         <v>0</v>
       </c>
       <c r="K787" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="788">
@@ -40061,18 +40069,18 @@
       </c>
       <c r="G788" t="inlineStr">
         <is>
-          <t>Victoria Virgens</t>
+          <t>Leticia Queiroz</t>
         </is>
       </c>
       <c r="H788" t="inlineStr"/>
       <c r="I788" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J788" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K788" t="n">
-        <v>11</v>
+        <v>48</v>
       </c>
     </row>
     <row r="789">
@@ -40108,7 +40116,7 @@
       </c>
       <c r="G789" t="inlineStr">
         <is>
-          <t>Yasmin Peixoto</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="H789" t="inlineStr"/>
@@ -40116,10 +40124,10 @@
         <v>0</v>
       </c>
       <c r="J789" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K789" t="n">
-        <v>263</v>
+        <v>7</v>
       </c>
     </row>
     <row r="790">
@@ -40150,23 +40158,23 @@
       </c>
       <c r="F790" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="G790" t="inlineStr">
         <is>
-          <t>Andre Coelho</t>
+          <t>Victoria Virgens</t>
         </is>
       </c>
       <c r="H790" t="inlineStr"/>
       <c r="I790" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J790" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K790" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="791">
@@ -40197,23 +40205,23 @@
       </c>
       <c r="F791" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="G791" t="inlineStr">
         <is>
-          <t>Beatriz Rangel</t>
+          <t>Yasmin Peixoto</t>
         </is>
       </c>
       <c r="H791" t="inlineStr"/>
       <c r="I791" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J791" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="K791" t="n">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="792">
@@ -40249,7 +40257,7 @@
       </c>
       <c r="G792" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
+          <t>Andre Coelho</t>
         </is>
       </c>
       <c r="H792" t="inlineStr"/>
@@ -40257,10 +40265,10 @@
         <v>0</v>
       </c>
       <c r="J792" t="n">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="K792" t="n">
-        <v>279</v>
+        <v>4</v>
       </c>
     </row>
     <row r="793">
@@ -40296,7 +40304,7 @@
       </c>
       <c r="G793" t="inlineStr">
         <is>
-          <t>Cristiane Simões</t>
+          <t>Beatriz Rangel</t>
         </is>
       </c>
       <c r="H793" t="inlineStr"/>
@@ -40304,10 +40312,10 @@
         <v>0</v>
       </c>
       <c r="J793" t="n">
-        <v>132</v>
+        <v>4</v>
       </c>
       <c r="K793" t="n">
-        <v>305</v>
+        <v>266</v>
       </c>
     </row>
     <row r="794">
@@ -40343,7 +40351,7 @@
       </c>
       <c r="G794" t="inlineStr">
         <is>
-          <t>Daniel Oliveira</t>
+          <t>Bruno Contieri</t>
         </is>
       </c>
       <c r="H794" t="inlineStr"/>
@@ -40351,10 +40359,10 @@
         <v>0</v>
       </c>
       <c r="J794" t="n">
-        <v>116</v>
+        <v>139</v>
       </c>
       <c r="K794" t="n">
-        <v>177</v>
+        <v>279</v>
       </c>
     </row>
     <row r="795">
@@ -40390,18 +40398,18 @@
       </c>
       <c r="G795" t="inlineStr">
         <is>
-          <t>Diego Lima</t>
+          <t>Cristiane Simões</t>
         </is>
       </c>
       <c r="H795" t="inlineStr"/>
       <c r="I795" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J795" t="n">
-        <v>35</v>
+        <v>133</v>
       </c>
       <c r="K795" t="n">
-        <v>114</v>
+        <v>305</v>
       </c>
     </row>
     <row r="796">
@@ -40437,7 +40445,7 @@
       </c>
       <c r="G796" t="inlineStr">
         <is>
-          <t>Karine Gusmão</t>
+          <t>Daniel Oliveira</t>
         </is>
       </c>
       <c r="H796" t="inlineStr"/>
@@ -40445,10 +40453,10 @@
         <v>0</v>
       </c>
       <c r="J796" t="n">
-        <v>25</v>
+        <v>116</v>
       </c>
       <c r="K796" t="n">
-        <v>6</v>
+        <v>176</v>
       </c>
     </row>
     <row r="797">
@@ -40484,7 +40492,7 @@
       </c>
       <c r="G797" t="inlineStr">
         <is>
-          <t>Luiz Ferreira</t>
+          <t>Diego Lima</t>
         </is>
       </c>
       <c r="H797" t="inlineStr"/>
@@ -40492,10 +40500,10 @@
         <v>0</v>
       </c>
       <c r="J797" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="K797" t="n">
-        <v>14</v>
+        <v>114</v>
       </c>
     </row>
     <row r="798">
@@ -40531,7 +40539,7 @@
       </c>
       <c r="G798" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Karine Gusmão</t>
         </is>
       </c>
       <c r="H798" t="inlineStr"/>
@@ -40539,10 +40547,10 @@
         <v>0</v>
       </c>
       <c r="J798" t="n">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="K798" t="n">
-        <v>150</v>
+        <v>6</v>
       </c>
     </row>
     <row r="799">
@@ -40578,7 +40586,7 @@
       </c>
       <c r="G799" t="inlineStr">
         <is>
-          <t>Rodrigo Rego</t>
+          <t>Luiz Ferreira</t>
         </is>
       </c>
       <c r="H799" t="inlineStr"/>
@@ -40586,10 +40594,10 @@
         <v>0</v>
       </c>
       <c r="J799" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K799" t="n">
-        <v>177</v>
+        <v>14</v>
       </c>
     </row>
     <row r="800">
@@ -40625,7 +40633,7 @@
       </c>
       <c r="G800" t="inlineStr">
         <is>
-          <t>Rogerio Egidio</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="H800" t="inlineStr"/>
@@ -40633,10 +40641,10 @@
         <v>0</v>
       </c>
       <c r="J800" t="n">
-        <v>105</v>
+        <v>66</v>
       </c>
       <c r="K800" t="n">
-        <v>282</v>
+        <v>150</v>
       </c>
     </row>
     <row r="801">
@@ -40672,7 +40680,7 @@
       </c>
       <c r="G801" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Rodrigo Rego</t>
         </is>
       </c>
       <c r="H801" t="inlineStr"/>
@@ -40680,10 +40688,10 @@
         <v>0</v>
       </c>
       <c r="J801" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K801" t="n">
-        <v>34</v>
+        <v>177</v>
       </c>
     </row>
     <row r="802">
@@ -40719,18 +40727,18 @@
       </c>
       <c r="G802" t="inlineStr">
         <is>
-          <t>Simone Marques</t>
+          <t>Rogerio Egidio</t>
         </is>
       </c>
       <c r="H802" t="inlineStr"/>
       <c r="I802" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J802" t="n">
-        <v>69</v>
+        <v>112</v>
       </c>
       <c r="K802" t="n">
-        <v>179</v>
+        <v>286</v>
       </c>
     </row>
     <row r="803">
@@ -40766,7 +40774,7 @@
       </c>
       <c r="G803" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="H803" t="inlineStr"/>
@@ -40774,10 +40782,10 @@
         <v>0</v>
       </c>
       <c r="J803" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="K803" t="n">
-        <v>188</v>
+        <v>34</v>
       </c>
     </row>
     <row r="804">
@@ -40808,12 +40816,12 @@
       </c>
       <c r="F804" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="G804" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Simone Marques</t>
         </is>
       </c>
       <c r="H804" t="inlineStr"/>
@@ -40821,10 +40829,10 @@
         <v>0</v>
       </c>
       <c r="J804" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="K804" t="n">
-        <v>1</v>
+        <v>179</v>
       </c>
     </row>
     <row r="805">
@@ -40855,23 +40863,23 @@
       </c>
       <c r="F805" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="G805" t="inlineStr">
         <is>
-          <t>Jurema Damacena - SAC</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="H805" t="inlineStr"/>
       <c r="I805" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J805" t="n">
-        <v>16</v>
+        <v>71</v>
       </c>
       <c r="K805" t="n">
-        <v>37</v>
+        <v>188</v>
       </c>
     </row>
     <row r="806">
@@ -40897,7 +40905,7 @@
       </c>
       <c r="E806" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F806" t="inlineStr">
@@ -40907,7 +40915,7 @@
       </c>
       <c r="G806" t="inlineStr">
         <is>
-          <t>Jurema Damacena - SAC</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="H806" t="inlineStr"/>
@@ -40915,10 +40923,10 @@
         <v>0</v>
       </c>
       <c r="J806" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K806" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="807">
@@ -40944,28 +40952,28 @@
       </c>
       <c r="E807" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F807" t="inlineStr">
         <is>
-          <t>SANTOS - ADM</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="G807" t="inlineStr">
         <is>
-          <t>Kauany Pereira</t>
+          <t>Jurema Damacena - SAC</t>
         </is>
       </c>
       <c r="H807" t="inlineStr"/>
       <c r="I807" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J807" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="K807" t="n">
-        <v>136</v>
+        <v>42</v>
       </c>
     </row>
     <row r="808">
@@ -40991,32 +40999,28 @@
       </c>
       <c r="E808" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F808" t="inlineStr">
         <is>
-          <t>SANTOS - CTB</t>
+          <t>S.A.C</t>
         </is>
       </c>
       <c r="G808" t="inlineStr">
         <is>
-          <t>Ivia Oliveira</t>
-        </is>
-      </c>
-      <c r="H808" t="inlineStr">
-        <is>
-          <t>Roberto Silva</t>
-        </is>
-      </c>
+          <t>Ana Celia - SAC</t>
+        </is>
+      </c>
+      <c r="H808" t="inlineStr"/>
       <c r="I808" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J808" t="n">
         <v>1</v>
       </c>
       <c r="K808" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="809">
@@ -41047,27 +41051,23 @@
       </c>
       <c r="F809" t="inlineStr">
         <is>
-          <t>SANTOS - CTB</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="G809" t="inlineStr">
         <is>
-          <t>Nata Trindade</t>
-        </is>
-      </c>
-      <c r="H809" t="inlineStr">
-        <is>
-          <t>Roberto Silva</t>
-        </is>
-      </c>
+          <t>Jurema Damacena - SAC</t>
+        </is>
+      </c>
+      <c r="H809" t="inlineStr"/>
       <c r="I809" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J809" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K809" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
     </row>
     <row r="810">
@@ -41098,27 +41098,23 @@
       </c>
       <c r="F810" t="inlineStr">
         <is>
-          <t>SANTOS - CTB</t>
+          <t>SANTOS - ADM</t>
         </is>
       </c>
       <c r="G810" t="inlineStr">
         <is>
-          <t>Roberto Silva</t>
-        </is>
-      </c>
-      <c r="H810" t="inlineStr">
-        <is>
-          <t>Roberto Silva</t>
-        </is>
-      </c>
+          <t>Kauany Pereira</t>
+        </is>
+      </c>
+      <c r="H810" t="inlineStr"/>
       <c r="I810" t="n">
         <v>0</v>
       </c>
       <c r="J810" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="K810" t="n">
-        <v>37</v>
+        <v>136</v>
       </c>
     </row>
     <row r="811">
@@ -41154,7 +41150,7 @@
       </c>
       <c r="G811" t="inlineStr">
         <is>
-          <t>Thaina Rodrigues</t>
+          <t>Ivia Oliveira</t>
         </is>
       </c>
       <c r="H811" t="inlineStr">
@@ -41166,10 +41162,10 @@
         <v>0</v>
       </c>
       <c r="J811" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K811" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
     </row>
     <row r="812">
@@ -41200,27 +41196,27 @@
       </c>
       <c r="F812" t="inlineStr">
         <is>
-          <t>SANTOS - DP</t>
+          <t>SANTOS - CTB</t>
         </is>
       </c>
       <c r="G812" t="inlineStr">
         <is>
-          <t>Bruna Silva</t>
+          <t>Nata Trindade</t>
         </is>
       </c>
       <c r="H812" t="inlineStr">
         <is>
-          <t>Katia Valeria</t>
+          <t>Roberto Silva</t>
         </is>
       </c>
       <c r="I812" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J812" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K812" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
     </row>
     <row r="813">
@@ -41251,27 +41247,27 @@
       </c>
       <c r="F813" t="inlineStr">
         <is>
-          <t>SANTOS - DP</t>
+          <t>SANTOS - CTB</t>
         </is>
       </c>
       <c r="G813" t="inlineStr">
         <is>
-          <t>Carliane Silva</t>
+          <t>Roberto Silva</t>
         </is>
       </c>
       <c r="H813" t="inlineStr">
         <is>
-          <t>Katia Valeria</t>
+          <t>Roberto Silva</t>
         </is>
       </c>
       <c r="I813" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J813" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="K813" t="n">
-        <v>177</v>
+        <v>37</v>
       </c>
     </row>
     <row r="814">
@@ -41302,27 +41298,27 @@
       </c>
       <c r="F814" t="inlineStr">
         <is>
-          <t>SANTOS - DP</t>
+          <t>SANTOS - CTB</t>
         </is>
       </c>
       <c r="G814" t="inlineStr">
         <is>
-          <t>Cintia Andrade</t>
+          <t>Thaina Rodrigues</t>
         </is>
       </c>
       <c r="H814" t="inlineStr">
         <is>
-          <t>Katia Valeria</t>
+          <t>Roberto Silva</t>
         </is>
       </c>
       <c r="I814" t="n">
         <v>0</v>
       </c>
       <c r="J814" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="K814" t="n">
-        <v>128</v>
+        <v>29</v>
       </c>
     </row>
     <row r="815">
@@ -41358,22 +41354,22 @@
       </c>
       <c r="G815" t="inlineStr">
         <is>
+          <t>Bruna Silva</t>
+        </is>
+      </c>
+      <c r="H815" t="inlineStr">
+        <is>
           <t>Katia Valeria</t>
         </is>
       </c>
-      <c r="H815" t="inlineStr">
-        <is>
-          <t>Katia Valeria</t>
-        </is>
-      </c>
       <c r="I815" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J815" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="K815" t="n">
-        <v>225</v>
+        <v>14</v>
       </c>
     </row>
     <row r="816">
@@ -41404,27 +41400,27 @@
       </c>
       <c r="F816" t="inlineStr">
         <is>
-          <t>SANTOS - EF</t>
+          <t>SANTOS - DP</t>
         </is>
       </c>
       <c r="G816" t="inlineStr">
         <is>
-          <t>Jasmina Melo</t>
+          <t>Carliane Silva</t>
         </is>
       </c>
       <c r="H816" t="inlineStr">
         <is>
-          <t>Lidia Tavares</t>
+          <t>Katia Valeria</t>
         </is>
       </c>
       <c r="I816" t="n">
         <v>0</v>
       </c>
       <c r="J816" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="K816" t="n">
-        <v>34</v>
+        <v>177</v>
       </c>
     </row>
     <row r="817">
@@ -41455,27 +41451,27 @@
       </c>
       <c r="F817" t="inlineStr">
         <is>
-          <t>SANTOS - EF</t>
+          <t>SANTOS - DP</t>
         </is>
       </c>
       <c r="G817" t="inlineStr">
         <is>
-          <t>Karen Saadi</t>
+          <t>Cintia Andrade</t>
         </is>
       </c>
       <c r="H817" t="inlineStr">
         <is>
-          <t>Lidia Tavares</t>
+          <t>Katia Valeria</t>
         </is>
       </c>
       <c r="I817" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="J817" t="n">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="K817" t="n">
-        <v>49</v>
+        <v>152</v>
       </c>
     </row>
     <row r="818">
@@ -41506,27 +41502,27 @@
       </c>
       <c r="F818" t="inlineStr">
         <is>
-          <t>SANTOS - EF</t>
+          <t>SANTOS - DP</t>
         </is>
       </c>
       <c r="G818" t="inlineStr">
         <is>
-          <t>Luckas Andrade</t>
+          <t>Katia Valeria</t>
         </is>
       </c>
       <c r="H818" t="inlineStr">
         <is>
-          <t>Lidia Tavares</t>
+          <t>Katia Valeria</t>
         </is>
       </c>
       <c r="I818" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J818" t="n">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="K818" t="n">
-        <v>58</v>
+        <v>229</v>
       </c>
     </row>
     <row r="819">
@@ -41562,7 +41558,7 @@
       </c>
       <c r="G819" t="inlineStr">
         <is>
-          <t>Mirian Rodrigues</t>
+          <t>Jasmina Melo</t>
         </is>
       </c>
       <c r="H819" t="inlineStr">
@@ -41571,13 +41567,13 @@
         </is>
       </c>
       <c r="I819" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="J819" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K819" t="n">
-        <v>75</v>
+        <v>49</v>
       </c>
     </row>
     <row r="820">
@@ -41608,22 +41604,175 @@
       </c>
       <c r="F820" t="inlineStr">
         <is>
+          <t>SANTOS - EF</t>
+        </is>
+      </c>
+      <c r="G820" t="inlineStr">
+        <is>
+          <t>Karen Saadi</t>
+        </is>
+      </c>
+      <c r="H820" t="inlineStr">
+        <is>
+          <t>Lidia Tavares</t>
+        </is>
+      </c>
+      <c r="I820" t="n">
+        <v>5</v>
+      </c>
+      <c r="J820" t="n">
+        <v>19</v>
+      </c>
+      <c r="K820" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>Quarta</t>
+        </is>
+      </c>
+      <c r="C821" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E821" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="F821" t="inlineStr">
+        <is>
+          <t>SANTOS - EF</t>
+        </is>
+      </c>
+      <c r="G821" t="inlineStr">
+        <is>
+          <t>Luckas Andrade</t>
+        </is>
+      </c>
+      <c r="H821" t="inlineStr">
+        <is>
+          <t>Lidia Tavares</t>
+        </is>
+      </c>
+      <c r="I821" t="n">
+        <v>5</v>
+      </c>
+      <c r="J821" t="n">
+        <v>25</v>
+      </c>
+      <c r="K821" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>Quarta</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D822" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E822" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="F822" t="inlineStr">
+        <is>
+          <t>SANTOS - EF</t>
+        </is>
+      </c>
+      <c r="G822" t="inlineStr">
+        <is>
+          <t>Mirian Rodrigues</t>
+        </is>
+      </c>
+      <c r="H822" t="inlineStr">
+        <is>
+          <t>Lidia Tavares</t>
+        </is>
+      </c>
+      <c r="I822" t="n">
+        <v>6</v>
+      </c>
+      <c r="J822" t="n">
+        <v>27</v>
+      </c>
+      <c r="K822" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>Quarta</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E823" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="F823" t="inlineStr">
+        <is>
           <t>SANTOS - GC</t>
         </is>
       </c>
-      <c r="G820" t="inlineStr">
+      <c r="G823" t="inlineStr">
         <is>
           <t>Rafaella Massuia</t>
         </is>
       </c>
-      <c r="H820" t="inlineStr"/>
-      <c r="I820" t="n">
-        <v>0</v>
-      </c>
-      <c r="J820" t="n">
-        <v>0</v>
-      </c>
-      <c r="K820" t="n">
+      <c r="H823" t="inlineStr"/>
+      <c r="I823" t="n">
+        <v>0</v>
+      </c>
+      <c r="J823" t="n">
+        <v>0</v>
+      </c>
+      <c r="K823" t="n">
         <v>109</v>
       </c>
     </row>

--- a/data/historico/historico_baixas.xlsx
+++ b/data/historico/historico_baixas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K823"/>
+  <dimension ref="A1:K826"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -28413,13 +28413,13 @@
         </is>
       </c>
       <c r="I557" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J557" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K557" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="558">
@@ -28464,13 +28464,13 @@
         </is>
       </c>
       <c r="I558" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J558" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K558" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="559">
@@ -28950,13 +28950,13 @@
         </is>
       </c>
       <c r="I568" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="J568" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="K568" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
     </row>
     <row r="569">
@@ -29001,13 +29001,13 @@
         </is>
       </c>
       <c r="I569" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J569" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K569" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="570">
@@ -29205,13 +29205,13 @@
         </is>
       </c>
       <c r="I573" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J573" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="K573" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="574">
@@ -29460,13 +29460,13 @@
         </is>
       </c>
       <c r="I578" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J578" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K578" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="579">
@@ -29562,13 +29562,13 @@
         </is>
       </c>
       <c r="I580" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J580" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K580" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="581">
@@ -29662,7 +29662,7 @@
         <v>0</v>
       </c>
       <c r="K582" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="583">
@@ -30064,10 +30064,10 @@
         </is>
       </c>
       <c r="I590" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J590" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K590" t="n">
         <v>16</v>
@@ -30166,13 +30166,13 @@
         </is>
       </c>
       <c r="I592" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J592" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K592" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="593">
@@ -30421,10 +30421,10 @@
         </is>
       </c>
       <c r="I597" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J597" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K597" t="n">
         <v>104</v>
@@ -30727,13 +30727,13 @@
         </is>
       </c>
       <c r="I603" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J603" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="K603" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
     </row>
     <row r="604">
@@ -30778,13 +30778,13 @@
         </is>
       </c>
       <c r="I604" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J604" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K604" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="605">
@@ -30829,13 +30829,13 @@
         </is>
       </c>
       <c r="I605" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J605" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K605" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="606">
@@ -30931,7 +30931,7 @@
         </is>
       </c>
       <c r="I607" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J607" t="n">
         <v>0</v>
@@ -30982,13 +30982,13 @@
         </is>
       </c>
       <c r="I608" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J608" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K608" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="609">
@@ -31084,13 +31084,13 @@
         </is>
       </c>
       <c r="I610" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J610" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K610" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="611">
@@ -31135,13 +31135,13 @@
         </is>
       </c>
       <c r="I611" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J611" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K611" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="612">
@@ -31237,13 +31237,13 @@
         </is>
       </c>
       <c r="I613" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J613" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K613" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="614">
@@ -31284,7 +31284,7 @@
       </c>
       <c r="H614" t="inlineStr"/>
       <c r="I614" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J614" t="n">
         <v>50</v>
@@ -31428,7 +31428,7 @@
         <v>99</v>
       </c>
       <c r="J617" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="K617" t="n">
         <v>151</v>
@@ -31472,13 +31472,13 @@
       </c>
       <c r="H618" t="inlineStr"/>
       <c r="I618" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="J618" t="n">
-        <v>50</v>
+        <v>102</v>
       </c>
       <c r="K618" t="n">
-        <v>247</v>
+        <v>303</v>
       </c>
     </row>
     <row r="619">
@@ -31825,13 +31825,13 @@
         </is>
       </c>
       <c r="I625" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J625" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K625" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="626">
@@ -32484,13 +32484,13 @@
         </is>
       </c>
       <c r="I638" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J638" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K638" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="639">
@@ -33500,13 +33500,13 @@
         </is>
       </c>
       <c r="I658" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J658" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K658" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="659">
@@ -33806,13 +33806,13 @@
         </is>
       </c>
       <c r="I664" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J664" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K664" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="665">
@@ -33908,13 +33908,13 @@
         </is>
       </c>
       <c r="I666" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J666" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K666" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="667">
@@ -33959,13 +33959,13 @@
         </is>
       </c>
       <c r="I667" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J667" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K667" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="668">
@@ -34516,10 +34516,10 @@
         </is>
       </c>
       <c r="I678" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J678" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K678" t="n">
         <v>15</v>
@@ -34720,10 +34720,10 @@
         </is>
       </c>
       <c r="I682" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J682" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K682" t="n">
         <v>99</v>
@@ -34771,10 +34771,10 @@
         </is>
       </c>
       <c r="I683" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J683" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K683" t="n">
         <v>31</v>
@@ -34822,7 +34822,7 @@
         </is>
       </c>
       <c r="I684" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J684" t="n">
         <v>3</v>
@@ -34873,13 +34873,13 @@
         </is>
       </c>
       <c r="I685" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J685" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K685" t="n">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="686">
@@ -34924,13 +34924,13 @@
         </is>
       </c>
       <c r="I686" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J686" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K686" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="687">
@@ -34975,13 +34975,13 @@
         </is>
       </c>
       <c r="I687" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J687" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K687" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="688">
@@ -35077,13 +35077,13 @@
         </is>
       </c>
       <c r="I689" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J689" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K689" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="690">
@@ -35128,13 +35128,13 @@
         </is>
       </c>
       <c r="I690" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J690" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K690" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="691">
@@ -35185,7 +35185,7 @@
         <v>0</v>
       </c>
       <c r="K691" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="692">
@@ -35281,13 +35281,13 @@
         </is>
       </c>
       <c r="I693" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="J693" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="K693" t="n">
-        <v>117</v>
+        <v>133</v>
       </c>
     </row>
     <row r="694">
@@ -35383,13 +35383,13 @@
         </is>
       </c>
       <c r="I695" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J695" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K695" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="696">
@@ -35689,10 +35689,10 @@
         </is>
       </c>
       <c r="I701" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J701" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K701" t="n">
         <v>60</v>
@@ -35791,10 +35791,10 @@
         </is>
       </c>
       <c r="I703" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J703" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K703" t="n">
         <v>1</v>
@@ -35944,13 +35944,13 @@
         </is>
       </c>
       <c r="I706" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J706" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K706" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="707">
@@ -36093,13 +36093,13 @@
         </is>
       </c>
       <c r="I709" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J709" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="K709" t="n">
-        <v>102</v>
+        <v>110</v>
       </c>
     </row>
     <row r="710">
@@ -36144,13 +36144,13 @@
         </is>
       </c>
       <c r="I710" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J710" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K710" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="711">
@@ -36348,13 +36348,13 @@
         </is>
       </c>
       <c r="I714" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J714" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K714" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
     </row>
     <row r="715">
@@ -36552,13 +36552,13 @@
         </is>
       </c>
       <c r="I718" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="J718" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="K718" t="n">
-        <v>42</v>
+        <v>64</v>
       </c>
     </row>
     <row r="719">
@@ -36603,13 +36603,13 @@
         </is>
       </c>
       <c r="I719" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J719" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K719" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="720">
@@ -36756,13 +36756,13 @@
         </is>
       </c>
       <c r="I722" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J722" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="K722" t="n">
-        <v>133</v>
+        <v>139</v>
       </c>
     </row>
     <row r="723">
@@ -36807,13 +36807,13 @@
         </is>
       </c>
       <c r="I723" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J723" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K723" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="724">
@@ -36854,13 +36854,13 @@
       </c>
       <c r="H724" t="inlineStr"/>
       <c r="I724" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J724" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K724" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="725">
@@ -36905,13 +36905,13 @@
         </is>
       </c>
       <c r="I725" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J725" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="K725" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
     </row>
     <row r="726">
@@ -37007,13 +37007,13 @@
         </is>
       </c>
       <c r="I727" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="J727" t="n">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="K727" t="n">
-        <v>292</v>
+        <v>304</v>
       </c>
     </row>
     <row r="728">
@@ -37058,13 +37058,13 @@
         </is>
       </c>
       <c r="I728" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="J728" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="K728" t="n">
-        <v>94</v>
+        <v>102</v>
       </c>
     </row>
     <row r="729">
@@ -37160,13 +37160,13 @@
         </is>
       </c>
       <c r="I730" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J730" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K730" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="731">
@@ -37217,7 +37217,7 @@
         <v>0</v>
       </c>
       <c r="K731" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="732">
@@ -37313,13 +37313,13 @@
         </is>
       </c>
       <c r="I733" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="J733" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="K733" t="n">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="734">
@@ -37364,13 +37364,13 @@
         </is>
       </c>
       <c r="I734" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J734" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K734" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="735">
@@ -37466,13 +37466,13 @@
         </is>
       </c>
       <c r="I736" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J736" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="K736" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="737">
@@ -37670,13 +37670,13 @@
         </is>
       </c>
       <c r="I740" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J740" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K740" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="741">
@@ -37772,13 +37772,13 @@
         </is>
       </c>
       <c r="I742" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J742" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K742" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="743">
@@ -37823,13 +37823,13 @@
         </is>
       </c>
       <c r="I743" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J743" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="K743" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
     </row>
     <row r="744">
@@ -37925,13 +37925,13 @@
         </is>
       </c>
       <c r="I745" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J745" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K745" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="746">
@@ -37975,10 +37975,10 @@
         <v>0</v>
       </c>
       <c r="J746" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K746" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="747">
@@ -38074,13 +38074,13 @@
         </is>
       </c>
       <c r="I748" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J748" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K748" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="749">
@@ -38125,13 +38125,13 @@
         </is>
       </c>
       <c r="I749" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J749" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K749" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="750">
@@ -38524,22 +38524,22 @@
       </c>
       <c r="G757" t="inlineStr">
         <is>
-          <t>Jose Natan</t>
+          <t>Jose Borges</t>
         </is>
       </c>
       <c r="H757" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="I757" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J757" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K757" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
     </row>
     <row r="758">
@@ -38575,7 +38575,7 @@
       </c>
       <c r="G758" t="inlineStr">
         <is>
-          <t>João Oliveira</t>
+          <t>Jose Natan</t>
         </is>
       </c>
       <c r="H758" t="inlineStr">
@@ -38584,13 +38584,13 @@
         </is>
       </c>
       <c r="I758" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J758" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="K758" t="n">
-        <v>9</v>
+        <v>98</v>
       </c>
     </row>
     <row r="759">
@@ -38626,22 +38626,22 @@
       </c>
       <c r="G759" t="inlineStr">
         <is>
-          <t>Juan Ribeiro</t>
+          <t>João Oliveira</t>
         </is>
       </c>
       <c r="H759" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I759" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J759" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="K759" t="n">
-        <v>80</v>
+        <v>9</v>
       </c>
     </row>
     <row r="760">
@@ -38677,22 +38677,22 @@
       </c>
       <c r="G760" t="inlineStr">
         <is>
-          <t>Juliana Valeria</t>
+          <t>Juan Ribeiro</t>
         </is>
       </c>
       <c r="H760" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I760" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J760" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="K760" t="n">
-        <v>93</v>
+        <v>80</v>
       </c>
     </row>
     <row r="761">
@@ -38728,7 +38728,7 @@
       </c>
       <c r="G761" t="inlineStr">
         <is>
-          <t>Juliane Vaz</t>
+          <t>Juliana Valeria</t>
         </is>
       </c>
       <c r="H761" t="inlineStr">
@@ -38740,10 +38740,10 @@
         <v>9</v>
       </c>
       <c r="J761" t="n">
-        <v>81</v>
+        <v>31</v>
       </c>
       <c r="K761" t="n">
-        <v>182</v>
+        <v>93</v>
       </c>
     </row>
     <row r="762">
@@ -38779,22 +38779,22 @@
       </c>
       <c r="G762" t="inlineStr">
         <is>
-          <t>Katia Xavier</t>
+          <t>Juliane Vaz</t>
         </is>
       </c>
       <c r="H762" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I762" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J762" t="n">
-        <v>27</v>
+        <v>82</v>
       </c>
       <c r="K762" t="n">
-        <v>81</v>
+        <v>183</v>
       </c>
     </row>
     <row r="763">
@@ -38830,22 +38830,22 @@
       </c>
       <c r="G763" t="inlineStr">
         <is>
-          <t>Larissa Félix</t>
+          <t>Katia Xavier</t>
         </is>
       </c>
       <c r="H763" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I763" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J763" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="K763" t="n">
-        <v>110</v>
+        <v>82</v>
       </c>
     </row>
     <row r="764">
@@ -38881,22 +38881,22 @@
       </c>
       <c r="G764" t="inlineStr">
         <is>
-          <t>Léia de Oliveira</t>
+          <t>Larissa Félix</t>
         </is>
       </c>
       <c r="H764" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I764" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J764" t="n">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="K764" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
     </row>
     <row r="765">
@@ -38932,7 +38932,7 @@
       </c>
       <c r="G765" t="inlineStr">
         <is>
-          <t>Maria Gualberto</t>
+          <t>Léia de Oliveira</t>
         </is>
       </c>
       <c r="H765" t="inlineStr">
@@ -38944,10 +38944,10 @@
         <v>1</v>
       </c>
       <c r="J765" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K765" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="766">
@@ -38983,22 +38983,22 @@
       </c>
       <c r="G766" t="inlineStr">
         <is>
-          <t>Nathany Silva</t>
+          <t>Maria Gualberto</t>
         </is>
       </c>
       <c r="H766" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I766" t="n">
         <v>1</v>
       </c>
       <c r="J766" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K766" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
     </row>
     <row r="767">
@@ -39034,22 +39034,22 @@
       </c>
       <c r="G767" t="inlineStr">
         <is>
-          <t>Priscila Moreira</t>
+          <t>Nathany Silva</t>
         </is>
       </c>
       <c r="H767" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I767" t="n">
         <v>1</v>
       </c>
       <c r="J767" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K767" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="768">
@@ -39085,22 +39085,22 @@
       </c>
       <c r="G768" t="inlineStr">
         <is>
-          <t>Regiane Santos</t>
+          <t>Priscila Moreira</t>
         </is>
       </c>
       <c r="H768" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="I768" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J768" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="K768" t="n">
-        <v>53</v>
+        <v>79</v>
       </c>
     </row>
     <row r="769">
@@ -39136,22 +39136,22 @@
       </c>
       <c r="G769" t="inlineStr">
         <is>
-          <t>Shofia Gomes</t>
+          <t>Regiane Santos</t>
         </is>
       </c>
       <c r="H769" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I769" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="J769" t="n">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="K769" t="n">
-        <v>118</v>
+        <v>53</v>
       </c>
     </row>
     <row r="770">
@@ -39187,22 +39187,22 @@
       </c>
       <c r="G770" t="inlineStr">
         <is>
-          <t>Vanessa Tavares</t>
+          <t>Shofia Gomes</t>
         </is>
       </c>
       <c r="H770" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="I770" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="J770" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="K770" t="n">
-        <v>50</v>
+        <v>118</v>
       </c>
     </row>
     <row r="771">
@@ -39238,7 +39238,7 @@
       </c>
       <c r="G771" t="inlineStr">
         <is>
-          <t>Willian Luz</t>
+          <t>Vanessa Tavares</t>
         </is>
       </c>
       <c r="H771" t="inlineStr">
@@ -39247,13 +39247,13 @@
         </is>
       </c>
       <c r="I771" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J771" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="K771" t="n">
-        <v>62</v>
+        <v>50</v>
       </c>
     </row>
     <row r="772">
@@ -39289,7 +39289,7 @@
       </c>
       <c r="G772" t="inlineStr">
         <is>
-          <t>Yasmim Oliveira</t>
+          <t>Willian Luz</t>
         </is>
       </c>
       <c r="H772" t="inlineStr">
@@ -39298,13 +39298,13 @@
         </is>
       </c>
       <c r="I772" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J772" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="K772" t="n">
-        <v>34</v>
+        <v>64</v>
       </c>
     </row>
     <row r="773">
@@ -39335,23 +39335,27 @@
       </c>
       <c r="F773" t="inlineStr">
         <is>
-          <t>ESCRITA FISCAL (Outsourcing)</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="G773" t="inlineStr">
         <is>
-          <t>Claudineia Rodrigues</t>
-        </is>
-      </c>
-      <c r="H773" t="inlineStr"/>
+          <t>Yasmim Oliveira</t>
+        </is>
+      </c>
+      <c r="H773" t="inlineStr">
+        <is>
+          <t>Larice Souza</t>
+        </is>
+      </c>
       <c r="I773" t="n">
         <v>0</v>
       </c>
       <c r="J773" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K773" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
     </row>
     <row r="774">
@@ -39387,14 +39391,10 @@
       </c>
       <c r="G774" t="inlineStr">
         <is>
-          <t>Diego Pereira</t>
-        </is>
-      </c>
-      <c r="H774" t="inlineStr">
-        <is>
-          <t>Thaiza Oliveira</t>
-        </is>
-      </c>
+          <t>Claudineia Rodrigues</t>
+        </is>
+      </c>
+      <c r="H774" t="inlineStr"/>
       <c r="I774" t="n">
         <v>0</v>
       </c>
@@ -39402,7 +39402,7 @@
         <v>2</v>
       </c>
       <c r="K774" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="775">
@@ -39438,22 +39438,22 @@
       </c>
       <c r="G775" t="inlineStr">
         <is>
-          <t>Gislaine Lima</t>
+          <t>Diego Pereira</t>
         </is>
       </c>
       <c r="H775" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I775" t="n">
         <v>0</v>
       </c>
       <c r="J775" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K775" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
     </row>
     <row r="776">
@@ -39489,7 +39489,7 @@
       </c>
       <c r="G776" t="inlineStr">
         <is>
-          <t>Joanna Costa</t>
+          <t>Gislaine Lima</t>
         </is>
       </c>
       <c r="H776" t="inlineStr">
@@ -39501,10 +39501,10 @@
         <v>0</v>
       </c>
       <c r="J776" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="K776" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
     </row>
     <row r="777">
@@ -39540,22 +39540,22 @@
       </c>
       <c r="G777" t="inlineStr">
         <is>
-          <t>João Oliveira</t>
+          <t>Joanna Costa</t>
         </is>
       </c>
       <c r="H777" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I777" t="n">
         <v>0</v>
       </c>
       <c r="J777" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="K777" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="778">
@@ -39591,22 +39591,22 @@
       </c>
       <c r="G778" t="inlineStr">
         <is>
-          <t>Regiane Santos</t>
+          <t>Jonatan Hayashibara</t>
         </is>
       </c>
       <c r="H778" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
       <c r="I778" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J778" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K778" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="779">
@@ -39642,7 +39642,7 @@
       </c>
       <c r="G779" t="inlineStr">
         <is>
-          <t>Yasmim Oliveira</t>
+          <t>João Oliveira</t>
         </is>
       </c>
       <c r="H779" t="inlineStr">
@@ -39654,10 +39654,10 @@
         <v>0</v>
       </c>
       <c r="J779" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K779" t="n">
-        <v>4</v>
+        <v>37</v>
       </c>
     </row>
     <row r="780">
@@ -39688,23 +39688,27 @@
       </c>
       <c r="F780" t="inlineStr">
         <is>
-          <t>FIN - CONTÁBIL</t>
+          <t>ESCRITA FISCAL (Outsourcing)</t>
         </is>
       </c>
       <c r="G780" t="inlineStr">
         <is>
-          <t>Daniele Faria</t>
-        </is>
-      </c>
-      <c r="H780" t="inlineStr"/>
+          <t>Regiane Santos</t>
+        </is>
+      </c>
+      <c r="H780" t="inlineStr">
+        <is>
+          <t>Larice Souza</t>
+        </is>
+      </c>
       <c r="I780" t="n">
         <v>0</v>
       </c>
       <c r="J780" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="K780" t="n">
-        <v>62</v>
+        <v>13</v>
       </c>
     </row>
     <row r="781">
@@ -39735,23 +39739,27 @@
       </c>
       <c r="F781" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>ESCRITA FISCAL (Outsourcing)</t>
         </is>
       </c>
       <c r="G781" t="inlineStr">
         <is>
-          <t>Ana Santana</t>
-        </is>
-      </c>
-      <c r="H781" t="inlineStr"/>
+          <t>Yasmim Oliveira</t>
+        </is>
+      </c>
+      <c r="H781" t="inlineStr">
+        <is>
+          <t>Larice Souza</t>
+        </is>
+      </c>
       <c r="I781" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="J781" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K781" t="n">
-        <v>397</v>
+        <v>4</v>
       </c>
     </row>
     <row r="782">
@@ -39782,12 +39790,12 @@
       </c>
       <c r="F782" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>FIN - CONTÁBIL</t>
         </is>
       </c>
       <c r="G782" t="inlineStr">
         <is>
-          <t>Andre Coelho</t>
+          <t>Daniele Faria</t>
         </is>
       </c>
       <c r="H782" t="inlineStr"/>
@@ -39795,10 +39803,10 @@
         <v>0</v>
       </c>
       <c r="J782" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K782" t="n">
-        <v>3</v>
+        <v>62</v>
       </c>
     </row>
     <row r="783">
@@ -39834,18 +39842,18 @@
       </c>
       <c r="G783" t="inlineStr">
         <is>
-          <t>Bianca Castro</t>
+          <t>Ana Santana</t>
         </is>
       </c>
       <c r="H783" t="inlineStr"/>
       <c r="I783" t="n">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="J783" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="K783" t="n">
-        <v>325</v>
+        <v>397</v>
       </c>
     </row>
     <row r="784">
@@ -39881,7 +39889,7 @@
       </c>
       <c r="G784" t="inlineStr">
         <is>
-          <t>Bruna Costa</t>
+          <t>Andre Coelho</t>
         </is>
       </c>
       <c r="H784" t="inlineStr"/>
@@ -39889,10 +39897,10 @@
         <v>0</v>
       </c>
       <c r="J784" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K784" t="n">
-        <v>34</v>
+        <v>3</v>
       </c>
     </row>
     <row r="785">
@@ -39928,18 +39936,18 @@
       </c>
       <c r="G785" t="inlineStr">
         <is>
-          <t>Daniela Silva</t>
+          <t>Bianca Castro</t>
         </is>
       </c>
       <c r="H785" t="inlineStr"/>
       <c r="I785" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J785" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K785" t="n">
-        <v>11</v>
+        <v>325</v>
       </c>
     </row>
     <row r="786">
@@ -39975,7 +39983,7 @@
       </c>
       <c r="G786" t="inlineStr">
         <is>
-          <t>Isabelli Afonso</t>
+          <t>Bruna Costa</t>
         </is>
       </c>
       <c r="H786" t="inlineStr"/>
@@ -39983,10 +39991,10 @@
         <v>0</v>
       </c>
       <c r="J786" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K786" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="787">
@@ -40022,18 +40030,18 @@
       </c>
       <c r="G787" t="inlineStr">
         <is>
-          <t>Jurema Damacena - SAC</t>
+          <t>Daniela Silva</t>
         </is>
       </c>
       <c r="H787" t="inlineStr"/>
       <c r="I787" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J787" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K787" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="788">
@@ -40069,18 +40077,18 @@
       </c>
       <c r="G788" t="inlineStr">
         <is>
-          <t>Leticia Queiroz</t>
+          <t>Isabelli Afonso</t>
         </is>
       </c>
       <c r="H788" t="inlineStr"/>
       <c r="I788" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J788" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K788" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
     </row>
     <row r="789">
@@ -40116,7 +40124,7 @@
       </c>
       <c r="G789" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Jurema Damacena - SAC</t>
         </is>
       </c>
       <c r="H789" t="inlineStr"/>
@@ -40127,7 +40135,7 @@
         <v>0</v>
       </c>
       <c r="K789" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="790">
@@ -40163,18 +40171,18 @@
       </c>
       <c r="G790" t="inlineStr">
         <is>
-          <t>Victoria Virgens</t>
+          <t>Leticia Queiroz</t>
         </is>
       </c>
       <c r="H790" t="inlineStr"/>
       <c r="I790" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J790" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K790" t="n">
-        <v>13</v>
+        <v>48</v>
       </c>
     </row>
     <row r="791">
@@ -40210,18 +40218,18 @@
       </c>
       <c r="G791" t="inlineStr">
         <is>
-          <t>Yasmin Peixoto</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="H791" t="inlineStr"/>
       <c r="I791" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J791" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K791" t="n">
-        <v>263</v>
+        <v>7</v>
       </c>
     </row>
     <row r="792">
@@ -40252,23 +40260,23 @@
       </c>
       <c r="F792" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="G792" t="inlineStr">
         <is>
-          <t>Andre Coelho</t>
+          <t>Victoria Virgens</t>
         </is>
       </c>
       <c r="H792" t="inlineStr"/>
       <c r="I792" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J792" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K792" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="793">
@@ -40299,23 +40307,23 @@
       </c>
       <c r="F793" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="G793" t="inlineStr">
         <is>
-          <t>Beatriz Rangel</t>
+          <t>Yasmin Peixoto</t>
         </is>
       </c>
       <c r="H793" t="inlineStr"/>
       <c r="I793" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J793" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="K793" t="n">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="794">
@@ -40351,7 +40359,7 @@
       </c>
       <c r="G794" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
+          <t>Andre Coelho</t>
         </is>
       </c>
       <c r="H794" t="inlineStr"/>
@@ -40359,10 +40367,10 @@
         <v>0</v>
       </c>
       <c r="J794" t="n">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="K794" t="n">
-        <v>279</v>
+        <v>4</v>
       </c>
     </row>
     <row r="795">
@@ -40398,18 +40406,18 @@
       </c>
       <c r="G795" t="inlineStr">
         <is>
-          <t>Cristiane Simões</t>
+          <t>Beatriz Rangel</t>
         </is>
       </c>
       <c r="H795" t="inlineStr"/>
       <c r="I795" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J795" t="n">
-        <v>133</v>
+        <v>4</v>
       </c>
       <c r="K795" t="n">
-        <v>305</v>
+        <v>266</v>
       </c>
     </row>
     <row r="796">
@@ -40445,7 +40453,7 @@
       </c>
       <c r="G796" t="inlineStr">
         <is>
-          <t>Daniel Oliveira</t>
+          <t>Bruno Contieri</t>
         </is>
       </c>
       <c r="H796" t="inlineStr"/>
@@ -40453,10 +40461,10 @@
         <v>0</v>
       </c>
       <c r="J796" t="n">
-        <v>116</v>
+        <v>139</v>
       </c>
       <c r="K796" t="n">
-        <v>176</v>
+        <v>279</v>
       </c>
     </row>
     <row r="797">
@@ -40492,18 +40500,18 @@
       </c>
       <c r="G797" t="inlineStr">
         <is>
-          <t>Diego Lima</t>
+          <t>Cristiane Simões</t>
         </is>
       </c>
       <c r="H797" t="inlineStr"/>
       <c r="I797" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J797" t="n">
-        <v>35</v>
+        <v>133</v>
       </c>
       <c r="K797" t="n">
-        <v>114</v>
+        <v>305</v>
       </c>
     </row>
     <row r="798">
@@ -40539,18 +40547,18 @@
       </c>
       <c r="G798" t="inlineStr">
         <is>
-          <t>Karine Gusmão</t>
+          <t>Daniel Oliveira</t>
         </is>
       </c>
       <c r="H798" t="inlineStr"/>
       <c r="I798" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J798" t="n">
-        <v>25</v>
+        <v>116</v>
       </c>
       <c r="K798" t="n">
-        <v>6</v>
+        <v>176</v>
       </c>
     </row>
     <row r="799">
@@ -40586,7 +40594,7 @@
       </c>
       <c r="G799" t="inlineStr">
         <is>
-          <t>Luiz Ferreira</t>
+          <t>Diego Lima</t>
         </is>
       </c>
       <c r="H799" t="inlineStr"/>
@@ -40594,10 +40602,10 @@
         <v>0</v>
       </c>
       <c r="J799" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="K799" t="n">
-        <v>14</v>
+        <v>114</v>
       </c>
     </row>
     <row r="800">
@@ -40633,7 +40641,7 @@
       </c>
       <c r="G800" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Karine Gusmão</t>
         </is>
       </c>
       <c r="H800" t="inlineStr"/>
@@ -40641,10 +40649,10 @@
         <v>0</v>
       </c>
       <c r="J800" t="n">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="K800" t="n">
-        <v>150</v>
+        <v>6</v>
       </c>
     </row>
     <row r="801">
@@ -40680,7 +40688,7 @@
       </c>
       <c r="G801" t="inlineStr">
         <is>
-          <t>Rodrigo Rego</t>
+          <t>Luiz Ferreira</t>
         </is>
       </c>
       <c r="H801" t="inlineStr"/>
@@ -40688,10 +40696,10 @@
         <v>0</v>
       </c>
       <c r="J801" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K801" t="n">
-        <v>177</v>
+        <v>14</v>
       </c>
     </row>
     <row r="802">
@@ -40727,18 +40735,18 @@
       </c>
       <c r="G802" t="inlineStr">
         <is>
-          <t>Rogerio Egidio</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="H802" t="inlineStr"/>
       <c r="I802" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J802" t="n">
-        <v>112</v>
+        <v>66</v>
       </c>
       <c r="K802" t="n">
-        <v>286</v>
+        <v>150</v>
       </c>
     </row>
     <row r="803">
@@ -40774,7 +40782,7 @@
       </c>
       <c r="G803" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Rodrigo Rego</t>
         </is>
       </c>
       <c r="H803" t="inlineStr"/>
@@ -40782,10 +40790,10 @@
         <v>0</v>
       </c>
       <c r="J803" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K803" t="n">
-        <v>34</v>
+        <v>177</v>
       </c>
     </row>
     <row r="804">
@@ -40821,18 +40829,18 @@
       </c>
       <c r="G804" t="inlineStr">
         <is>
-          <t>Simone Marques</t>
+          <t>Rogerio Egidio</t>
         </is>
       </c>
       <c r="H804" t="inlineStr"/>
       <c r="I804" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J804" t="n">
-        <v>68</v>
+        <v>112</v>
       </c>
       <c r="K804" t="n">
-        <v>179</v>
+        <v>286</v>
       </c>
     </row>
     <row r="805">
@@ -40868,18 +40876,18 @@
       </c>
       <c r="G805" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="H805" t="inlineStr"/>
       <c r="I805" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J805" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="K805" t="n">
-        <v>188</v>
+        <v>34</v>
       </c>
     </row>
     <row r="806">
@@ -40910,12 +40918,12 @@
       </c>
       <c r="F806" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="G806" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Simone Marques</t>
         </is>
       </c>
       <c r="H806" t="inlineStr"/>
@@ -40923,10 +40931,10 @@
         <v>0</v>
       </c>
       <c r="J806" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="K806" t="n">
-        <v>1</v>
+        <v>179</v>
       </c>
     </row>
     <row r="807">
@@ -40957,23 +40965,23 @@
       </c>
       <c r="F807" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="G807" t="inlineStr">
         <is>
-          <t>Jurema Damacena - SAC</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="H807" t="inlineStr"/>
       <c r="I807" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J807" t="n">
-        <v>23</v>
+        <v>72</v>
       </c>
       <c r="K807" t="n">
-        <v>42</v>
+        <v>188</v>
       </c>
     </row>
     <row r="808">
@@ -41004,20 +41012,20 @@
       </c>
       <c r="F808" t="inlineStr">
         <is>
-          <t>S.A.C</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="G808" t="inlineStr">
         <is>
-          <t>Ana Celia - SAC</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="H808" t="inlineStr"/>
       <c r="I808" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J808" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K808" t="n">
         <v>1</v>
@@ -41046,7 +41054,7 @@
       </c>
       <c r="E809" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F809" t="inlineStr">
@@ -41061,13 +41069,13 @@
       </c>
       <c r="H809" t="inlineStr"/>
       <c r="I809" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J809" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="K809" t="n">
-        <v>4</v>
+        <v>42</v>
       </c>
     </row>
     <row r="810">
@@ -41093,28 +41101,28 @@
       </c>
       <c r="E810" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F810" t="inlineStr">
         <is>
-          <t>SANTOS - ADM</t>
+          <t>S.A.C</t>
         </is>
       </c>
       <c r="G810" t="inlineStr">
         <is>
-          <t>Kauany Pereira</t>
+          <t>Ana Celia - SAC</t>
         </is>
       </c>
       <c r="H810" t="inlineStr"/>
       <c r="I810" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J810" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="K810" t="n">
-        <v>136</v>
+        <v>1</v>
       </c>
     </row>
     <row r="811">
@@ -41145,27 +41153,23 @@
       </c>
       <c r="F811" t="inlineStr">
         <is>
-          <t>SANTOS - CTB</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="G811" t="inlineStr">
         <is>
-          <t>Ivia Oliveira</t>
-        </is>
-      </c>
-      <c r="H811" t="inlineStr">
-        <is>
-          <t>Roberto Silva</t>
-        </is>
-      </c>
+          <t>Jurema Damacena - SAC</t>
+        </is>
+      </c>
+      <c r="H811" t="inlineStr"/>
       <c r="I811" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J811" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K811" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="812">
@@ -41196,27 +41200,23 @@
       </c>
       <c r="F812" t="inlineStr">
         <is>
-          <t>SANTOS - CTB</t>
+          <t>SANTOS - ADM</t>
         </is>
       </c>
       <c r="G812" t="inlineStr">
         <is>
-          <t>Nata Trindade</t>
-        </is>
-      </c>
-      <c r="H812" t="inlineStr">
-        <is>
-          <t>Roberto Silva</t>
-        </is>
-      </c>
+          <t>Kauany Pereira</t>
+        </is>
+      </c>
+      <c r="H812" t="inlineStr"/>
       <c r="I812" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J812" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="K812" t="n">
-        <v>26</v>
+        <v>136</v>
       </c>
     </row>
     <row r="813">
@@ -41252,22 +41252,22 @@
       </c>
       <c r="G813" t="inlineStr">
         <is>
+          <t>Ivia Oliveira</t>
+        </is>
+      </c>
+      <c r="H813" t="inlineStr">
+        <is>
           <t>Roberto Silva</t>
         </is>
       </c>
-      <c r="H813" t="inlineStr">
-        <is>
-          <t>Roberto Silva</t>
-        </is>
-      </c>
       <c r="I813" t="n">
+        <v>0</v>
+      </c>
+      <c r="J813" t="n">
         <v>1</v>
       </c>
-      <c r="J813" t="n">
-        <v>2</v>
-      </c>
       <c r="K813" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="814">
@@ -41303,7 +41303,7 @@
       </c>
       <c r="G814" t="inlineStr">
         <is>
-          <t>Thaina Rodrigues</t>
+          <t>Nata Trindade</t>
         </is>
       </c>
       <c r="H814" t="inlineStr">
@@ -41312,13 +41312,13 @@
         </is>
       </c>
       <c r="I814" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J814" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K814" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="815">
@@ -41349,27 +41349,27 @@
       </c>
       <c r="F815" t="inlineStr">
         <is>
-          <t>SANTOS - DP</t>
+          <t>SANTOS - CTB</t>
         </is>
       </c>
       <c r="G815" t="inlineStr">
         <is>
-          <t>Bruna Silva</t>
+          <t>Roberto Silva</t>
         </is>
       </c>
       <c r="H815" t="inlineStr">
         <is>
-          <t>Katia Valeria</t>
+          <t>Roberto Silva</t>
         </is>
       </c>
       <c r="I815" t="n">
+        <v>1</v>
+      </c>
+      <c r="J815" t="n">
         <v>2</v>
       </c>
-      <c r="J815" t="n">
-        <v>0</v>
-      </c>
       <c r="K815" t="n">
-        <v>14</v>
+        <v>37</v>
       </c>
     </row>
     <row r="816">
@@ -41400,27 +41400,27 @@
       </c>
       <c r="F816" t="inlineStr">
         <is>
-          <t>SANTOS - DP</t>
+          <t>SANTOS - CTB</t>
         </is>
       </c>
       <c r="G816" t="inlineStr">
         <is>
-          <t>Carliane Silva</t>
+          <t>Thaina Rodrigues</t>
         </is>
       </c>
       <c r="H816" t="inlineStr">
         <is>
-          <t>Katia Valeria</t>
+          <t>Roberto Silva</t>
         </is>
       </c>
       <c r="I816" t="n">
         <v>0</v>
       </c>
       <c r="J816" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="K816" t="n">
-        <v>177</v>
+        <v>29</v>
       </c>
     </row>
     <row r="817">
@@ -41456,7 +41456,7 @@
       </c>
       <c r="G817" t="inlineStr">
         <is>
-          <t>Cintia Andrade</t>
+          <t>Bruna Silva</t>
         </is>
       </c>
       <c r="H817" t="inlineStr">
@@ -41465,13 +41465,13 @@
         </is>
       </c>
       <c r="I817" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="J817" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="K817" t="n">
-        <v>152</v>
+        <v>14</v>
       </c>
     </row>
     <row r="818">
@@ -41507,7 +41507,7 @@
       </c>
       <c r="G818" t="inlineStr">
         <is>
-          <t>Katia Valeria</t>
+          <t>Carliane Silva</t>
         </is>
       </c>
       <c r="H818" t="inlineStr">
@@ -41519,10 +41519,10 @@
         <v>1</v>
       </c>
       <c r="J818" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="K818" t="n">
-        <v>229</v>
+        <v>194</v>
       </c>
     </row>
     <row r="819">
@@ -41553,27 +41553,27 @@
       </c>
       <c r="F819" t="inlineStr">
         <is>
-          <t>SANTOS - EF</t>
+          <t>SANTOS - DP</t>
         </is>
       </c>
       <c r="G819" t="inlineStr">
         <is>
-          <t>Jasmina Melo</t>
+          <t>Cintia Andrade</t>
         </is>
       </c>
       <c r="H819" t="inlineStr">
         <is>
-          <t>Lidia Tavares</t>
+          <t>Katia Valeria</t>
         </is>
       </c>
       <c r="I819" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="J819" t="n">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="K819" t="n">
-        <v>49</v>
+        <v>153</v>
       </c>
     </row>
     <row r="820">
@@ -41604,27 +41604,27 @@
       </c>
       <c r="F820" t="inlineStr">
         <is>
-          <t>SANTOS - EF</t>
+          <t>SANTOS - DP</t>
         </is>
       </c>
       <c r="G820" t="inlineStr">
         <is>
-          <t>Karen Saadi</t>
+          <t>Katia Valeria</t>
         </is>
       </c>
       <c r="H820" t="inlineStr">
         <is>
-          <t>Lidia Tavares</t>
+          <t>Katia Valeria</t>
         </is>
       </c>
       <c r="I820" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J820" t="n">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="K820" t="n">
-        <v>53</v>
+        <v>230</v>
       </c>
     </row>
     <row r="821">
@@ -41655,27 +41655,23 @@
       </c>
       <c r="F821" t="inlineStr">
         <is>
-          <t>SANTOS - EF</t>
+          <t>SANTOS - DP</t>
         </is>
       </c>
       <c r="G821" t="inlineStr">
         <is>
-          <t>Luckas Andrade</t>
-        </is>
-      </c>
-      <c r="H821" t="inlineStr">
-        <is>
-          <t>Lidia Tavares</t>
-        </is>
-      </c>
+          <t>Patricia Melo</t>
+        </is>
+      </c>
+      <c r="H821" t="inlineStr"/>
       <c r="I821" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="J821" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K821" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="822">
@@ -41711,7 +41707,7 @@
       </c>
       <c r="G822" t="inlineStr">
         <is>
-          <t>Mirian Rodrigues</t>
+          <t>Jasmina Melo</t>
         </is>
       </c>
       <c r="H822" t="inlineStr">
@@ -41720,13 +41716,13 @@
         </is>
       </c>
       <c r="I822" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="J822" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="K822" t="n">
-        <v>81</v>
+        <v>50</v>
       </c>
     </row>
     <row r="823">
@@ -41757,22 +41753,175 @@
       </c>
       <c r="F823" t="inlineStr">
         <is>
+          <t>SANTOS - EF</t>
+        </is>
+      </c>
+      <c r="G823" t="inlineStr">
+        <is>
+          <t>Karen Saadi</t>
+        </is>
+      </c>
+      <c r="H823" t="inlineStr">
+        <is>
+          <t>Lidia Tavares</t>
+        </is>
+      </c>
+      <c r="I823" t="n">
+        <v>5</v>
+      </c>
+      <c r="J823" t="n">
+        <v>19</v>
+      </c>
+      <c r="K823" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>Quarta</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D824" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E824" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="F824" t="inlineStr">
+        <is>
+          <t>SANTOS - EF</t>
+        </is>
+      </c>
+      <c r="G824" t="inlineStr">
+        <is>
+          <t>Luckas Andrade</t>
+        </is>
+      </c>
+      <c r="H824" t="inlineStr">
+        <is>
+          <t>Lidia Tavares</t>
+        </is>
+      </c>
+      <c r="I824" t="n">
+        <v>6</v>
+      </c>
+      <c r="J824" t="n">
+        <v>26</v>
+      </c>
+      <c r="K824" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>Quarta</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D825" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E825" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="F825" t="inlineStr">
+        <is>
+          <t>SANTOS - EF</t>
+        </is>
+      </c>
+      <c r="G825" t="inlineStr">
+        <is>
+          <t>Mirian Rodrigues</t>
+        </is>
+      </c>
+      <c r="H825" t="inlineStr">
+        <is>
+          <t>Lidia Tavares</t>
+        </is>
+      </c>
+      <c r="I825" t="n">
+        <v>17</v>
+      </c>
+      <c r="J825" t="n">
+        <v>28</v>
+      </c>
+      <c r="K825" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>Quarta</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D826" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E826" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="F826" t="inlineStr">
+        <is>
           <t>SANTOS - GC</t>
         </is>
       </c>
-      <c r="G823" t="inlineStr">
+      <c r="G826" t="inlineStr">
         <is>
           <t>Rafaella Massuia</t>
         </is>
       </c>
-      <c r="H823" t="inlineStr"/>
-      <c r="I823" t="n">
-        <v>0</v>
-      </c>
-      <c r="J823" t="n">
-        <v>0</v>
-      </c>
-      <c r="K823" t="n">
+      <c r="H826" t="inlineStr"/>
+      <c r="I826" t="n">
+        <v>0</v>
+      </c>
+      <c r="J826" t="n">
+        <v>0</v>
+      </c>
+      <c r="K826" t="n">
         <v>109</v>
       </c>
     </row>

--- a/data/historico/historico_baixas.xlsx
+++ b/data/historico/historico_baixas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K826"/>
+  <dimension ref="A1:K827"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -27911,13 +27911,13 @@
         </is>
       </c>
       <c r="I547" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J547" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K547" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="548">
@@ -28413,13 +28413,13 @@
         </is>
       </c>
       <c r="I557" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J557" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K557" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="558">
@@ -28464,13 +28464,13 @@
         </is>
       </c>
       <c r="I558" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J558" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K558" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="559">
@@ -28511,10 +28511,10 @@
       </c>
       <c r="H559" t="inlineStr"/>
       <c r="I559" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J559" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K559" t="n">
         <v>1</v>
@@ -28899,13 +28899,13 @@
         </is>
       </c>
       <c r="I567" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J567" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="K567" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="568">
@@ -29052,13 +29052,13 @@
         </is>
       </c>
       <c r="I570" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J570" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K570" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="571">
@@ -29103,13 +29103,13 @@
         </is>
       </c>
       <c r="I571" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="J571" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="K571" t="n">
-        <v>51</v>
+        <v>62</v>
       </c>
     </row>
     <row r="572">
@@ -29460,13 +29460,13 @@
         </is>
       </c>
       <c r="I578" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J578" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="K578" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="579">
@@ -29707,13 +29707,13 @@
         </is>
       </c>
       <c r="I583" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J583" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="K583" t="n">
-        <v>89</v>
+        <v>105</v>
       </c>
     </row>
     <row r="584">
@@ -29809,13 +29809,13 @@
         </is>
       </c>
       <c r="I585" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J585" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K585" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="586">
@@ -30013,13 +30013,13 @@
         </is>
       </c>
       <c r="I589" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J589" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K589" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="590">
@@ -30268,13 +30268,13 @@
         </is>
       </c>
       <c r="I594" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J594" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="K594" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
     </row>
     <row r="595">
@@ -30319,13 +30319,13 @@
         </is>
       </c>
       <c r="I595" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J595" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K595" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="596">
@@ -30472,10 +30472,10 @@
         </is>
       </c>
       <c r="I598" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J598" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K598" t="n">
         <v>163</v>
@@ -30574,13 +30574,13 @@
         </is>
       </c>
       <c r="I600" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="J600" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="K600" t="n">
-        <v>102</v>
+        <v>118</v>
       </c>
     </row>
     <row r="601">
@@ -30676,13 +30676,13 @@
         </is>
       </c>
       <c r="I602" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J602" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K602" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="603">
@@ -30727,13 +30727,13 @@
         </is>
       </c>
       <c r="I603" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J603" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K603" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="604">
@@ -30778,13 +30778,13 @@
         </is>
       </c>
       <c r="I604" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J604" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K604" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="605">
@@ -30829,13 +30829,13 @@
         </is>
       </c>
       <c r="I605" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J605" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="K605" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="606">
@@ -30880,13 +30880,13 @@
         </is>
       </c>
       <c r="I606" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="J606" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="K606" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
     </row>
     <row r="607">
@@ -30931,10 +30931,10 @@
         </is>
       </c>
       <c r="I607" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J607" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K607" t="n">
         <v>1</v>
@@ -30982,13 +30982,13 @@
         </is>
       </c>
       <c r="I608" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J608" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K608" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="609">
@@ -31084,13 +31084,13 @@
         </is>
       </c>
       <c r="I610" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J610" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="K610" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="611">
@@ -31135,13 +31135,13 @@
         </is>
       </c>
       <c r="I611" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J611" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="K611" t="n">
-        <v>97</v>
+        <v>104</v>
       </c>
     </row>
     <row r="612">
@@ -31237,13 +31237,13 @@
         </is>
       </c>
       <c r="I613" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J613" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="K613" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="614">
@@ -31331,7 +31331,7 @@
       </c>
       <c r="H615" t="inlineStr"/>
       <c r="I615" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J615" t="n">
         <v>5</v>
@@ -31425,13 +31425,13 @@
       </c>
       <c r="H617" t="inlineStr"/>
       <c r="I617" t="n">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="J617" t="n">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="K617" t="n">
-        <v>151</v>
+        <v>162</v>
       </c>
     </row>
     <row r="618">
@@ -31472,13 +31472,13 @@
       </c>
       <c r="H618" t="inlineStr"/>
       <c r="I618" t="n">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="J618" t="n">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="K618" t="n">
-        <v>303</v>
+        <v>333</v>
       </c>
     </row>
     <row r="619">
@@ -33092,13 +33092,13 @@
         </is>
       </c>
       <c r="I650" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J650" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="K650" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="651">
@@ -33245,13 +33245,13 @@
         </is>
       </c>
       <c r="I653" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J653" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K653" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="654">
@@ -33500,13 +33500,13 @@
         </is>
       </c>
       <c r="I658" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J658" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K658" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="659">
@@ -33755,13 +33755,13 @@
         </is>
       </c>
       <c r="I663" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J663" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K663" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="664">
@@ -33857,13 +33857,13 @@
         </is>
       </c>
       <c r="I665" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J665" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K665" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="666">
@@ -34771,13 +34771,13 @@
         </is>
       </c>
       <c r="I683" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J683" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K683" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="684">
@@ -34924,10 +34924,10 @@
         </is>
       </c>
       <c r="I686" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J686" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K686" t="n">
         <v>57</v>
@@ -35026,13 +35026,13 @@
         </is>
       </c>
       <c r="I688" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J688" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K688" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
     </row>
     <row r="689">
@@ -35185,7 +35185,7 @@
         <v>0</v>
       </c>
       <c r="K691" t="n">
-        <v>40</v>
+        <v>56</v>
       </c>
     </row>
     <row r="692">
@@ -35281,13 +35281,13 @@
         </is>
       </c>
       <c r="I693" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J693" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="K693" t="n">
-        <v>133</v>
+        <v>140</v>
       </c>
     </row>
     <row r="694">
@@ -35332,13 +35332,13 @@
         </is>
       </c>
       <c r="I694" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J694" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K694" t="n">
-        <v>110</v>
+        <v>129</v>
       </c>
     </row>
     <row r="695">
@@ -35383,13 +35383,13 @@
         </is>
       </c>
       <c r="I695" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J695" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K695" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="696">
@@ -35488,10 +35488,10 @@
         <v>1</v>
       </c>
       <c r="J697" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K697" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="698">
@@ -35638,13 +35638,13 @@
         </is>
       </c>
       <c r="I700" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J700" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="K700" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
     </row>
     <row r="701">
@@ -35791,10 +35791,10 @@
         </is>
       </c>
       <c r="I703" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="J703" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="K703" t="n">
         <v>1</v>
@@ -35893,13 +35893,13 @@
         </is>
       </c>
       <c r="I705" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J705" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K705" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="706">
@@ -35944,13 +35944,13 @@
         </is>
       </c>
       <c r="I706" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J706" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K706" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="707">
@@ -36144,13 +36144,13 @@
         </is>
       </c>
       <c r="I710" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J710" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K710" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="711">
@@ -36246,13 +36246,13 @@
         </is>
       </c>
       <c r="I712" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J712" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K712" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="713">
@@ -36348,13 +36348,13 @@
         </is>
       </c>
       <c r="I714" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="J714" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="K714" t="n">
-        <v>82</v>
+        <v>90</v>
       </c>
     </row>
     <row r="715">
@@ -36450,13 +36450,13 @@
         </is>
       </c>
       <c r="I716" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J716" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K716" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="717">
@@ -36603,13 +36603,13 @@
         </is>
       </c>
       <c r="I719" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="J719" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="K719" t="n">
-        <v>55</v>
+        <v>73</v>
       </c>
     </row>
     <row r="720">
@@ -36705,13 +36705,13 @@
         </is>
       </c>
       <c r="I721" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J721" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K721" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="722">
@@ -36854,13 +36854,13 @@
       </c>
       <c r="H724" t="inlineStr"/>
       <c r="I724" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J724" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K724" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="725">
@@ -36905,13 +36905,13 @@
         </is>
       </c>
       <c r="I725" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="J725" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="K725" t="n">
-        <v>101</v>
+        <v>112</v>
       </c>
     </row>
     <row r="726">
@@ -37007,13 +37007,13 @@
         </is>
       </c>
       <c r="I727" t="n">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="J727" t="n">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="K727" t="n">
-        <v>304</v>
+        <v>321</v>
       </c>
     </row>
     <row r="728">
@@ -37058,13 +37058,13 @@
         </is>
       </c>
       <c r="I728" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J728" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K728" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="729">
@@ -37109,13 +37109,13 @@
         </is>
       </c>
       <c r="I729" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J729" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="K729" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
     </row>
     <row r="730">
@@ -37163,10 +37163,10 @@
         <v>4</v>
       </c>
       <c r="J730" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K730" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="731">
@@ -37262,13 +37262,13 @@
         </is>
       </c>
       <c r="I732" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J732" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="K732" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
     </row>
     <row r="733">
@@ -37313,13 +37313,13 @@
         </is>
       </c>
       <c r="I733" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="J733" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="K733" t="n">
-        <v>167</v>
+        <v>180</v>
       </c>
     </row>
     <row r="734">
@@ -37364,13 +37364,13 @@
         </is>
       </c>
       <c r="I734" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J734" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K734" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="735">
@@ -37415,13 +37415,13 @@
         </is>
       </c>
       <c r="I735" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J735" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K735" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="736">
@@ -37466,13 +37466,13 @@
         </is>
       </c>
       <c r="I736" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J736" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="K736" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
     </row>
     <row r="737">
@@ -37517,13 +37517,13 @@
         </is>
       </c>
       <c r="I737" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J737" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K737" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="738">
@@ -37568,13 +37568,13 @@
         </is>
       </c>
       <c r="I738" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J738" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="K738" t="n">
-        <v>163</v>
+        <v>168</v>
       </c>
     </row>
     <row r="739">
@@ -37619,13 +37619,13 @@
         </is>
       </c>
       <c r="I739" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="J739" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="K739" t="n">
-        <v>83</v>
+        <v>92</v>
       </c>
     </row>
     <row r="740">
@@ -37721,13 +37721,13 @@
         </is>
       </c>
       <c r="I741" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J741" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K741" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="742">
@@ -37772,13 +37772,13 @@
         </is>
       </c>
       <c r="I742" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="J742" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="K742" t="n">
-        <v>77</v>
+        <v>91</v>
       </c>
     </row>
     <row r="743">
@@ -37823,13 +37823,13 @@
         </is>
       </c>
       <c r="I743" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J743" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K743" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="744">
@@ -37874,13 +37874,13 @@
         </is>
       </c>
       <c r="I744" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J744" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K744" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="745">
@@ -37925,13 +37925,13 @@
         </is>
       </c>
       <c r="I745" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J745" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K745" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="746">
@@ -37975,10 +37975,10 @@
         <v>0</v>
       </c>
       <c r="J746" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K746" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
     </row>
     <row r="747">
@@ -38026,10 +38026,10 @@
         <v>4</v>
       </c>
       <c r="J747" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K747" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="748">
@@ -38176,13 +38176,13 @@
         </is>
       </c>
       <c r="I750" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J750" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K750" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="751">
@@ -38278,13 +38278,13 @@
         </is>
       </c>
       <c r="I752" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J752" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="K752" t="n">
-        <v>73</v>
+        <v>83</v>
       </c>
     </row>
     <row r="753">
@@ -38329,13 +38329,13 @@
         </is>
       </c>
       <c r="I753" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="J753" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="K753" t="n">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="754">
@@ -38482,13 +38482,13 @@
         </is>
       </c>
       <c r="I756" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J756" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K756" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="757">
@@ -38533,7 +38533,7 @@
         </is>
       </c>
       <c r="I757" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J757" t="n">
         <v>0</v>
@@ -38635,13 +38635,13 @@
         </is>
       </c>
       <c r="I759" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J759" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K759" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="760">
@@ -38788,13 +38788,13 @@
         </is>
       </c>
       <c r="I762" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J762" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="K762" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="763">
@@ -38890,13 +38890,13 @@
         </is>
       </c>
       <c r="I764" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="J764" t="n">
-        <v>47</v>
+        <v>96</v>
       </c>
       <c r="K764" t="n">
-        <v>110</v>
+        <v>159</v>
       </c>
     </row>
     <row r="765">
@@ -38941,13 +38941,13 @@
         </is>
       </c>
       <c r="I765" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J765" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K765" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="766">
@@ -39196,13 +39196,13 @@
         </is>
       </c>
       <c r="I770" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J770" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K770" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="771">
@@ -39247,13 +39247,13 @@
         </is>
       </c>
       <c r="I771" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J771" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="K771" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
     </row>
     <row r="772">
@@ -39298,13 +39298,13 @@
         </is>
       </c>
       <c r="I772" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J772" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K772" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="773">
@@ -39498,13 +39498,13 @@
         </is>
       </c>
       <c r="I776" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J776" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="K776" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="777">
@@ -39651,13 +39651,13 @@
         </is>
       </c>
       <c r="I779" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J779" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="K779" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="780">
@@ -39753,13 +39753,13 @@
         </is>
       </c>
       <c r="I781" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J781" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K781" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="782">
@@ -39847,13 +39847,13 @@
       </c>
       <c r="H783" t="inlineStr"/>
       <c r="I783" t="n">
+        <v>32</v>
+      </c>
+      <c r="J783" t="n">
         <v>29</v>
       </c>
-      <c r="J783" t="n">
-        <v>26</v>
-      </c>
       <c r="K783" t="n">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="784">
@@ -39941,13 +39941,13 @@
       </c>
       <c r="H785" t="inlineStr"/>
       <c r="I785" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="J785" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="K785" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="786">
@@ -40176,7 +40176,7 @@
       </c>
       <c r="H790" t="inlineStr"/>
       <c r="I790" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J790" t="n">
         <v>9</v>
@@ -40270,13 +40270,13 @@
       </c>
       <c r="H792" t="inlineStr"/>
       <c r="I792" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="J792" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="K792" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="793">
@@ -40414,10 +40414,10 @@
         <v>0</v>
       </c>
       <c r="J795" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K795" t="n">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="796">
@@ -40558,7 +40558,7 @@
         <v>116</v>
       </c>
       <c r="K798" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="799">
@@ -40740,7 +40740,7 @@
       </c>
       <c r="H802" t="inlineStr"/>
       <c r="I802" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J802" t="n">
         <v>66</v>
@@ -40840,7 +40840,7 @@
         <v>112</v>
       </c>
       <c r="K804" t="n">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="805">
@@ -40931,7 +40931,7 @@
         <v>0</v>
       </c>
       <c r="J806" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K806" t="n">
         <v>179</v>
@@ -41148,28 +41148,32 @@
       </c>
       <c r="E811" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F811" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>SANTOS - DP</t>
         </is>
       </c>
       <c r="G811" t="inlineStr">
         <is>
-          <t>Jurema Damacena - SAC</t>
-        </is>
-      </c>
-      <c r="H811" t="inlineStr"/>
+          <t>Katia Valeria</t>
+        </is>
+      </c>
+      <c r="H811" t="inlineStr">
+        <is>
+          <t>Katia Valeria</t>
+        </is>
+      </c>
       <c r="I811" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J811" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K811" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="812">
@@ -41200,23 +41204,23 @@
       </c>
       <c r="F812" t="inlineStr">
         <is>
-          <t>SANTOS - ADM</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="G812" t="inlineStr">
         <is>
-          <t>Kauany Pereira</t>
+          <t>Jurema Damacena - SAC</t>
         </is>
       </c>
       <c r="H812" t="inlineStr"/>
       <c r="I812" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J812" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="K812" t="n">
-        <v>136</v>
+        <v>4</v>
       </c>
     </row>
     <row r="813">
@@ -41247,27 +41251,23 @@
       </c>
       <c r="F813" t="inlineStr">
         <is>
-          <t>SANTOS - CTB</t>
+          <t>SANTOS - ADM</t>
         </is>
       </c>
       <c r="G813" t="inlineStr">
         <is>
-          <t>Ivia Oliveira</t>
-        </is>
-      </c>
-      <c r="H813" t="inlineStr">
-        <is>
-          <t>Roberto Silva</t>
-        </is>
-      </c>
+          <t>Kauany Pereira</t>
+        </is>
+      </c>
+      <c r="H813" t="inlineStr"/>
       <c r="I813" t="n">
         <v>0</v>
       </c>
       <c r="J813" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="K813" t="n">
-        <v>9</v>
+        <v>136</v>
       </c>
     </row>
     <row r="814">
@@ -41303,7 +41303,7 @@
       </c>
       <c r="G814" t="inlineStr">
         <is>
-          <t>Nata Trindade</t>
+          <t>Ivia Oliveira</t>
         </is>
       </c>
       <c r="H814" t="inlineStr">
@@ -41312,13 +41312,13 @@
         </is>
       </c>
       <c r="I814" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J814" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K814" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
     </row>
     <row r="815">
@@ -41354,22 +41354,22 @@
       </c>
       <c r="G815" t="inlineStr">
         <is>
+          <t>Nata Trindade</t>
+        </is>
+      </c>
+      <c r="H815" t="inlineStr">
+        <is>
           <t>Roberto Silva</t>
         </is>
       </c>
-      <c r="H815" t="inlineStr">
-        <is>
-          <t>Roberto Silva</t>
-        </is>
-      </c>
       <c r="I815" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J815" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K815" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
     </row>
     <row r="816">
@@ -41405,7 +41405,7 @@
       </c>
       <c r="G816" t="inlineStr">
         <is>
-          <t>Thaina Rodrigues</t>
+          <t>Roberto Silva</t>
         </is>
       </c>
       <c r="H816" t="inlineStr">
@@ -41414,13 +41414,13 @@
         </is>
       </c>
       <c r="I816" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J816" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K816" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
     </row>
     <row r="817">
@@ -41451,27 +41451,27 @@
       </c>
       <c r="F817" t="inlineStr">
         <is>
-          <t>SANTOS - DP</t>
+          <t>SANTOS - CTB</t>
         </is>
       </c>
       <c r="G817" t="inlineStr">
         <is>
-          <t>Bruna Silva</t>
+          <t>Thaina Rodrigues</t>
         </is>
       </c>
       <c r="H817" t="inlineStr">
         <is>
-          <t>Katia Valeria</t>
+          <t>Roberto Silva</t>
         </is>
       </c>
       <c r="I817" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J817" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K817" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
     </row>
     <row r="818">
@@ -41507,7 +41507,7 @@
       </c>
       <c r="G818" t="inlineStr">
         <is>
-          <t>Carliane Silva</t>
+          <t>Bruna Silva</t>
         </is>
       </c>
       <c r="H818" t="inlineStr">
@@ -41516,13 +41516,13 @@
         </is>
       </c>
       <c r="I818" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J818" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K818" t="n">
-        <v>194</v>
+        <v>14</v>
       </c>
     </row>
     <row r="819">
@@ -41558,7 +41558,7 @@
       </c>
       <c r="G819" t="inlineStr">
         <is>
-          <t>Cintia Andrade</t>
+          <t>Carliane Silva</t>
         </is>
       </c>
       <c r="H819" t="inlineStr">
@@ -41567,13 +41567,13 @@
         </is>
       </c>
       <c r="I819" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J819" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="K819" t="n">
-        <v>153</v>
+        <v>197</v>
       </c>
     </row>
     <row r="820">
@@ -41609,22 +41609,22 @@
       </c>
       <c r="G820" t="inlineStr">
         <is>
+          <t>Cintia Andrade</t>
+        </is>
+      </c>
+      <c r="H820" t="inlineStr">
+        <is>
           <t>Katia Valeria</t>
         </is>
       </c>
-      <c r="H820" t="inlineStr">
-        <is>
-          <t>Katia Valeria</t>
-        </is>
-      </c>
       <c r="I820" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="J820" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="K820" t="n">
-        <v>230</v>
+        <v>169</v>
       </c>
     </row>
     <row r="821">
@@ -41660,18 +41660,22 @@
       </c>
       <c r="G821" t="inlineStr">
         <is>
-          <t>Patricia Melo</t>
-        </is>
-      </c>
-      <c r="H821" t="inlineStr"/>
+          <t>Katia Valeria</t>
+        </is>
+      </c>
+      <c r="H821" t="inlineStr">
+        <is>
+          <t>Katia Valeria</t>
+        </is>
+      </c>
       <c r="I821" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="J821" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="K821" t="n">
-        <v>0</v>
+        <v>241</v>
       </c>
     </row>
     <row r="822">
@@ -41702,27 +41706,23 @@
       </c>
       <c r="F822" t="inlineStr">
         <is>
-          <t>SANTOS - EF</t>
+          <t>SANTOS - DP</t>
         </is>
       </c>
       <c r="G822" t="inlineStr">
         <is>
-          <t>Jasmina Melo</t>
-        </is>
-      </c>
-      <c r="H822" t="inlineStr">
-        <is>
-          <t>Lidia Tavares</t>
-        </is>
-      </c>
+          <t>Patricia Melo</t>
+        </is>
+      </c>
+      <c r="H822" t="inlineStr"/>
       <c r="I822" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="J822" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K822" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="823">
@@ -41758,7 +41758,7 @@
       </c>
       <c r="G823" t="inlineStr">
         <is>
-          <t>Karen Saadi</t>
+          <t>Jasmina Melo</t>
         </is>
       </c>
       <c r="H823" t="inlineStr">
@@ -41767,13 +41767,13 @@
         </is>
       </c>
       <c r="I823" t="n">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="J823" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="K823" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="824">
@@ -41809,7 +41809,7 @@
       </c>
       <c r="G824" t="inlineStr">
         <is>
-          <t>Luckas Andrade</t>
+          <t>Karen Saadi</t>
         </is>
       </c>
       <c r="H824" t="inlineStr">
@@ -41818,13 +41818,13 @@
         </is>
       </c>
       <c r="I824" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J824" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K824" t="n">
-        <v>64</v>
+        <v>57</v>
       </c>
     </row>
     <row r="825">
@@ -41860,7 +41860,7 @@
       </c>
       <c r="G825" t="inlineStr">
         <is>
-          <t>Mirian Rodrigues</t>
+          <t>Luckas Andrade</t>
         </is>
       </c>
       <c r="H825" t="inlineStr">
@@ -41869,13 +41869,13 @@
         </is>
       </c>
       <c r="I825" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J825" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="K825" t="n">
-        <v>82</v>
+        <v>71</v>
       </c>
     </row>
     <row r="826">
@@ -41906,22 +41906,73 @@
       </c>
       <c r="F826" t="inlineStr">
         <is>
+          <t>SANTOS - EF</t>
+        </is>
+      </c>
+      <c r="G826" t="inlineStr">
+        <is>
+          <t>Mirian Rodrigues</t>
+        </is>
+      </c>
+      <c r="H826" t="inlineStr">
+        <is>
+          <t>Lidia Tavares</t>
+        </is>
+      </c>
+      <c r="I826" t="n">
+        <v>17</v>
+      </c>
+      <c r="J826" t="n">
+        <v>28</v>
+      </c>
+      <c r="K826" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>Quarta</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D827" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E827" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="F827" t="inlineStr">
+        <is>
           <t>SANTOS - GC</t>
         </is>
       </c>
-      <c r="G826" t="inlineStr">
+      <c r="G827" t="inlineStr">
         <is>
           <t>Rafaella Massuia</t>
         </is>
       </c>
-      <c r="H826" t="inlineStr"/>
-      <c r="I826" t="n">
-        <v>0</v>
-      </c>
-      <c r="J826" t="n">
-        <v>0</v>
-      </c>
-      <c r="K826" t="n">
+      <c r="H827" t="inlineStr"/>
+      <c r="I827" t="n">
+        <v>0</v>
+      </c>
+      <c r="J827" t="n">
+        <v>0</v>
+      </c>
+      <c r="K827" t="n">
         <v>109</v>
       </c>
     </row>

--- a/data/historico/historico_baixas.xlsx
+++ b/data/historico/historico_baixas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1111"/>
+  <dimension ref="A1:K1118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -42004,27 +42004,27 @@
       </c>
       <c r="F828" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="G828" t="inlineStr">
         <is>
-          <t>Eveny Silva</t>
+          <t>Emylle Souza</t>
         </is>
       </c>
       <c r="H828" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Erika Santana|Isabella Nascimento</t>
         </is>
       </c>
       <c r="I828" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J828" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K828" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="829">
@@ -42060,12 +42060,12 @@
       </c>
       <c r="G829" t="inlineStr">
         <is>
-          <t>Jackson Silva</t>
+          <t>Eveny Silva</t>
         </is>
       </c>
       <c r="H829" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Karina Santos</t>
         </is>
       </c>
       <c r="I829" t="n">
@@ -42075,7 +42075,7 @@
         <v>0</v>
       </c>
       <c r="K829" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="830">
@@ -42111,12 +42111,12 @@
       </c>
       <c r="G830" t="inlineStr">
         <is>
-          <t>Paulo Silva</t>
+          <t>Jackson Silva</t>
         </is>
       </c>
       <c r="H830" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I830" t="n">
@@ -42126,7 +42126,7 @@
         <v>0</v>
       </c>
       <c r="K830" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="831">
@@ -42157,17 +42157,17 @@
       </c>
       <c r="F831" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="G831" t="inlineStr">
         <is>
-          <t>Elaine Assis</t>
+          <t>Paulo Silva</t>
         </is>
       </c>
       <c r="H831" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="I831" t="n">
@@ -42177,7 +42177,7 @@
         <v>0</v>
       </c>
       <c r="K831" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="832">
@@ -42213,12 +42213,12 @@
       </c>
       <c r="G832" t="inlineStr">
         <is>
-          <t>Evellin Bispo</t>
+          <t>Elaine Assis</t>
         </is>
       </c>
       <c r="H832" t="inlineStr">
         <is>
-          <t>Leandro Matos</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I832" t="n">
@@ -42228,7 +42228,7 @@
         <v>0</v>
       </c>
       <c r="K832" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="833">
@@ -42264,22 +42264,22 @@
       </c>
       <c r="G833" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Evellin Bispo</t>
         </is>
       </c>
       <c r="H833" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Leandro Matos</t>
         </is>
       </c>
       <c r="I833" t="n">
         <v>0</v>
       </c>
       <c r="J833" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K833" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="834">
@@ -42315,22 +42315,22 @@
       </c>
       <c r="G834" t="inlineStr">
         <is>
-          <t>Jhenifer Tenorio</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="H834" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I834" t="n">
         <v>0</v>
       </c>
       <c r="J834" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K834" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
     </row>
     <row r="835">
@@ -42366,22 +42366,22 @@
       </c>
       <c r="G835" t="inlineStr">
         <is>
-          <t>Kaique Souza</t>
+          <t>Jhenifer Tenorio</t>
         </is>
       </c>
       <c r="H835" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I835" t="n">
         <v>0</v>
       </c>
       <c r="J835" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K835" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="836">
@@ -42417,22 +42417,22 @@
       </c>
       <c r="G836" t="inlineStr">
         <is>
-          <t>Mauricio Lermen</t>
+          <t>Kaique Souza</t>
         </is>
       </c>
       <c r="H836" t="inlineStr">
         <is>
-          <t>Mauricio Lermen</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I836" t="n">
         <v>0</v>
       </c>
       <c r="J836" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K836" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="837">
@@ -42468,18 +42468,22 @@
       </c>
       <c r="G837" t="inlineStr">
         <is>
-          <t>Mikael Teixeira</t>
-        </is>
-      </c>
-      <c r="H837" t="inlineStr"/>
+          <t>Mauricio Lermen</t>
+        </is>
+      </c>
+      <c r="H837" t="inlineStr">
+        <is>
+          <t>Mauricio Lermen</t>
+        </is>
+      </c>
       <c r="I837" t="n">
         <v>0</v>
       </c>
       <c r="J837" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K837" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="838">
@@ -42515,22 +42519,18 @@
       </c>
       <c r="G838" t="inlineStr">
         <is>
-          <t>Tania Luz</t>
-        </is>
-      </c>
-      <c r="H838" t="inlineStr">
-        <is>
-          <t>Sara Cavalheiro</t>
-        </is>
-      </c>
+          <t>Mikael Teixeira</t>
+        </is>
+      </c>
+      <c r="H838" t="inlineStr"/>
       <c r="I838" t="n">
         <v>0</v>
       </c>
       <c r="J838" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K838" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="839">
@@ -42566,12 +42566,12 @@
       </c>
       <c r="G839" t="inlineStr">
         <is>
-          <t>Vitor Guedes</t>
+          <t>Tania Luz</t>
         </is>
       </c>
       <c r="H839" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I839" t="n">
@@ -42581,7 +42581,7 @@
         <v>0</v>
       </c>
       <c r="K839" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="840">
@@ -42612,27 +42612,27 @@
       </c>
       <c r="F840" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="G840" t="inlineStr">
         <is>
-          <t>Cristiana Grizostomo</t>
+          <t>Vitor Guedes</t>
         </is>
       </c>
       <c r="H840" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I840" t="n">
         <v>0</v>
       </c>
       <c r="J840" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K840" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="841">
@@ -42668,18 +42668,22 @@
       </c>
       <c r="G841" t="inlineStr">
         <is>
-          <t>Denis Reis</t>
-        </is>
-      </c>
-      <c r="H841" t="inlineStr"/>
+          <t>Cristiana Grizostomo</t>
+        </is>
+      </c>
+      <c r="H841" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
       <c r="I841" t="n">
         <v>0</v>
       </c>
       <c r="J841" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K841" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="842">
@@ -42715,22 +42719,18 @@
       </c>
       <c r="G842" t="inlineStr">
         <is>
-          <t>Priscila Volpe</t>
-        </is>
-      </c>
-      <c r="H842" t="inlineStr">
-        <is>
-          <t>Nayara Oliveira</t>
-        </is>
-      </c>
+          <t>Denis Reis</t>
+        </is>
+      </c>
+      <c r="H842" t="inlineStr"/>
       <c r="I842" t="n">
         <v>0</v>
       </c>
       <c r="J842" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K842" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="843">
@@ -42766,7 +42766,7 @@
       </c>
       <c r="G843" t="inlineStr">
         <is>
-          <t>Rosilene Santos</t>
+          <t>Priscila Volpe</t>
         </is>
       </c>
       <c r="H843" t="inlineStr">
@@ -42778,10 +42778,10 @@
         <v>0</v>
       </c>
       <c r="J843" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K843" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="844">
@@ -42812,27 +42812,27 @@
       </c>
       <c r="F844" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="G844" t="inlineStr">
         <is>
-          <t>Cristina Leite</t>
+          <t>Rosilene Santos</t>
         </is>
       </c>
       <c r="H844" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
       <c r="I844" t="n">
         <v>0</v>
       </c>
       <c r="J844" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="K844" t="n">
-        <v>57</v>
+        <v>5</v>
       </c>
     </row>
     <row r="845">
@@ -42863,23 +42863,27 @@
       </c>
       <c r="F845" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="G845" t="inlineStr">
         <is>
-          <t>Victoria Virgens</t>
-        </is>
-      </c>
-      <c r="H845" t="inlineStr"/>
+          <t>Cristina Leite</t>
+        </is>
+      </c>
+      <c r="H845" t="inlineStr">
+        <is>
+          <t>Ricardo Fischer</t>
+        </is>
+      </c>
       <c r="I845" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J845" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="K845" t="n">
-        <v>1</v>
+        <v>59</v>
       </c>
     </row>
     <row r="846">
@@ -42910,20 +42914,20 @@
       </c>
       <c r="F846" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="G846" t="inlineStr">
         <is>
-          <t>Cristiane Simões</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="H846" t="inlineStr"/>
       <c r="I846" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J846" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K846" t="n">
         <v>2</v>
@@ -42957,23 +42961,23 @@
       </c>
       <c r="F847" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="G847" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Victoria Virgens</t>
         </is>
       </c>
       <c r="H847" t="inlineStr"/>
       <c r="I847" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J847" t="n">
+        <v>14</v>
+      </c>
+      <c r="K847" t="n">
         <v>13</v>
-      </c>
-      <c r="K847" t="n">
-        <v>31</v>
       </c>
     </row>
     <row r="848">
@@ -43009,18 +43013,18 @@
       </c>
       <c r="G848" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Cristiane Simões</t>
         </is>
       </c>
       <c r="H848" t="inlineStr"/>
       <c r="I848" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J848" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K848" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="849">
@@ -43056,18 +43060,18 @@
       </c>
       <c r="G849" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="H849" t="inlineStr"/>
       <c r="I849" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J849" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="K849" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
     <row r="850">
@@ -43093,28 +43097,28 @@
       </c>
       <c r="E850" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>GOIAS</t>
         </is>
       </c>
       <c r="F850" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="G850" t="inlineStr">
         <is>
-          <t>Caroline Alves</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="H850" t="inlineStr"/>
       <c r="I850" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J850" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K850" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="851">
@@ -43140,32 +43144,28 @@
       </c>
       <c r="E851" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>GOIAS</t>
         </is>
       </c>
       <c r="F851" t="inlineStr">
         <is>
-          <t>RJ - CTB</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="G851" t="inlineStr">
         <is>
-          <t>Crislaine Maia</t>
-        </is>
-      </c>
-      <c r="H851" t="inlineStr">
-        <is>
-          <t>Walace Gonçalves|Maicon Costa</t>
-        </is>
-      </c>
+          <t>Vander Silva</t>
+        </is>
+      </c>
+      <c r="H851" t="inlineStr"/>
       <c r="I851" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J851" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K851" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="852">
@@ -43196,27 +43196,23 @@
       </c>
       <c r="F852" t="inlineStr">
         <is>
-          <t>RJ - CTB</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="G852" t="inlineStr">
         <is>
-          <t>Gabriela Lopes</t>
-        </is>
-      </c>
-      <c r="H852" t="inlineStr">
-        <is>
-          <t>Walace Gonçalves|Maicon Costa</t>
-        </is>
-      </c>
+          <t>Caroline Alves</t>
+        </is>
+      </c>
+      <c r="H852" t="inlineStr"/>
       <c r="I852" t="n">
         <v>0</v>
       </c>
       <c r="J852" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K852" t="n">
-        <v>53</v>
+        <v>16</v>
       </c>
     </row>
     <row r="853">
@@ -43252,7 +43248,7 @@
       </c>
       <c r="G853" t="inlineStr">
         <is>
-          <t>Jeniffer Cristina</t>
+          <t>Crislaine Maia</t>
         </is>
       </c>
       <c r="H853" t="inlineStr">
@@ -43264,10 +43260,10 @@
         <v>0</v>
       </c>
       <c r="J853" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="K853" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="854">
@@ -43303,7 +43299,7 @@
       </c>
       <c r="G854" t="inlineStr">
         <is>
-          <t>Jessica Roque</t>
+          <t>Gabriela Lopes</t>
         </is>
       </c>
       <c r="H854" t="inlineStr">
@@ -43315,10 +43311,10 @@
         <v>0</v>
       </c>
       <c r="J854" t="n">
-        <v>55</v>
+        <v>2</v>
       </c>
       <c r="K854" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
     </row>
     <row r="855">
@@ -43354,7 +43350,7 @@
       </c>
       <c r="G855" t="inlineStr">
         <is>
-          <t>Kellem Freitas</t>
+          <t>Jeniffer Cristina</t>
         </is>
       </c>
       <c r="H855" t="inlineStr">
@@ -43363,13 +43359,13 @@
         </is>
       </c>
       <c r="I855" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J855" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="K855" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="856">
@@ -43405,7 +43401,7 @@
       </c>
       <c r="G856" t="inlineStr">
         <is>
-          <t>Leidiane Paulino</t>
+          <t>Jessica Roque</t>
         </is>
       </c>
       <c r="H856" t="inlineStr">
@@ -43417,10 +43413,10 @@
         <v>0</v>
       </c>
       <c r="J856" t="n">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="K856" t="n">
-        <v>21</v>
+        <v>60</v>
       </c>
     </row>
     <row r="857">
@@ -43456,7 +43452,7 @@
       </c>
       <c r="G857" t="inlineStr">
         <is>
-          <t>Leticia Barbosa</t>
+          <t>Kellem Freitas</t>
         </is>
       </c>
       <c r="H857" t="inlineStr">
@@ -43468,10 +43464,10 @@
         <v>0</v>
       </c>
       <c r="J857" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="K857" t="n">
-        <v>62</v>
+        <v>20</v>
       </c>
     </row>
     <row r="858">
@@ -43507,7 +43503,7 @@
       </c>
       <c r="G858" t="inlineStr">
         <is>
-          <t>Luis Junior</t>
+          <t>Leidiane Paulino</t>
         </is>
       </c>
       <c r="H858" t="inlineStr">
@@ -43519,10 +43515,10 @@
         <v>0</v>
       </c>
       <c r="J858" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K858" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="859">
@@ -43558,7 +43554,7 @@
       </c>
       <c r="G859" t="inlineStr">
         <is>
-          <t>Nicoly Rodrigues</t>
+          <t>Leticia Barbosa</t>
         </is>
       </c>
       <c r="H859" t="inlineStr">
@@ -43567,13 +43563,13 @@
         </is>
       </c>
       <c r="I859" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J859" t="n">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="K859" t="n">
-        <v>25</v>
+        <v>81</v>
       </c>
     </row>
     <row r="860">
@@ -43609,7 +43605,7 @@
       </c>
       <c r="G860" t="inlineStr">
         <is>
-          <t>Rafaella Silva</t>
+          <t>Luis Junior</t>
         </is>
       </c>
       <c r="H860" t="inlineStr">
@@ -43621,10 +43617,10 @@
         <v>0</v>
       </c>
       <c r="J860" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K860" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="861">
@@ -43660,7 +43656,7 @@
       </c>
       <c r="G861" t="inlineStr">
         <is>
-          <t>Rangel Rocha</t>
+          <t>Nicoly Rodrigues</t>
         </is>
       </c>
       <c r="H861" t="inlineStr">
@@ -43672,10 +43668,10 @@
         <v>0</v>
       </c>
       <c r="J861" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K861" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="862">
@@ -43711,7 +43707,7 @@
       </c>
       <c r="G862" t="inlineStr">
         <is>
-          <t>Simone Soares</t>
+          <t>Rafaella Silva</t>
         </is>
       </c>
       <c r="H862" t="inlineStr">
@@ -43720,13 +43716,13 @@
         </is>
       </c>
       <c r="I862" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J862" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K862" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="863">
@@ -43762,7 +43758,7 @@
       </c>
       <c r="G863" t="inlineStr">
         <is>
-          <t>Suzana Silva</t>
+          <t>Rangel Rocha</t>
         </is>
       </c>
       <c r="H863" t="inlineStr">
@@ -43774,10 +43770,10 @@
         <v>0</v>
       </c>
       <c r="J863" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K863" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="864">
@@ -43813,7 +43809,7 @@
       </c>
       <c r="G864" t="inlineStr">
         <is>
-          <t>Veronica Barbosa</t>
+          <t>Simone Soares</t>
         </is>
       </c>
       <c r="H864" t="inlineStr">
@@ -43825,10 +43821,10 @@
         <v>0</v>
       </c>
       <c r="J864" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="K864" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
     </row>
     <row r="865">
@@ -43864,7 +43860,7 @@
       </c>
       <c r="G865" t="inlineStr">
         <is>
-          <t>Vitor Monteiro</t>
+          <t>Suzana Silva</t>
         </is>
       </c>
       <c r="H865" t="inlineStr">
@@ -43876,10 +43872,10 @@
         <v>0</v>
       </c>
       <c r="J865" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K865" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="866">
@@ -43915,7 +43911,7 @@
       </c>
       <c r="G866" t="inlineStr">
         <is>
-          <t>Vitoria Silva</t>
+          <t>Veronica Barbosa</t>
         </is>
       </c>
       <c r="H866" t="inlineStr">
@@ -43924,13 +43920,13 @@
         </is>
       </c>
       <c r="I866" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J866" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="K866" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="867">
@@ -43966,7 +43962,7 @@
       </c>
       <c r="G867" t="inlineStr">
         <is>
-          <t>Walace Gonçalves</t>
+          <t>Vitor Monteiro</t>
         </is>
       </c>
       <c r="H867" t="inlineStr">
@@ -43978,10 +43974,10 @@
         <v>0</v>
       </c>
       <c r="J867" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K867" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="868">
@@ -44012,19 +44008,27 @@
       </c>
       <c r="F868" t="inlineStr">
         <is>
-          <t>RJ - DP</t>
-        </is>
-      </c>
-      <c r="G868" t="inlineStr"/>
-      <c r="H868" t="inlineStr"/>
+          <t>RJ - CTB</t>
+        </is>
+      </c>
+      <c r="G868" t="inlineStr">
+        <is>
+          <t>Vitoria Silva</t>
+        </is>
+      </c>
+      <c r="H868" t="inlineStr">
+        <is>
+          <t>Walace Gonçalves|Maicon Costa</t>
+        </is>
+      </c>
       <c r="I868" t="n">
         <v>0</v>
       </c>
       <c r="J868" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K868" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="869">
@@ -44055,27 +44059,27 @@
       </c>
       <c r="F869" t="inlineStr">
         <is>
-          <t>RJ - DP</t>
+          <t>RJ - CTB</t>
         </is>
       </c>
       <c r="G869" t="inlineStr">
         <is>
-          <t>Barbara Mello</t>
+          <t>Walace Gonçalves</t>
         </is>
       </c>
       <c r="H869" t="inlineStr">
         <is>
-          <t>Karina Oliveira|Liliane Costa</t>
+          <t>Walace Gonçalves|Maicon Costa</t>
         </is>
       </c>
       <c r="I869" t="n">
         <v>0</v>
       </c>
       <c r="J869" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="K869" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
     </row>
     <row r="870">
@@ -44109,24 +44113,16 @@
           <t>RJ - DP</t>
         </is>
       </c>
-      <c r="G870" t="inlineStr">
-        <is>
-          <t>Debora Nunes</t>
-        </is>
-      </c>
-      <c r="H870" t="inlineStr">
-        <is>
-          <t>Karina Oliveira|Liliane Costa</t>
-        </is>
-      </c>
+      <c r="G870" t="inlineStr"/>
+      <c r="H870" t="inlineStr"/>
       <c r="I870" t="n">
         <v>0</v>
       </c>
       <c r="J870" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K870" t="n">
-        <v>78</v>
+        <v>7</v>
       </c>
     </row>
     <row r="871">
@@ -44162,7 +44158,7 @@
       </c>
       <c r="G871" t="inlineStr">
         <is>
-          <t>Graziele Almeida</t>
+          <t>Barbara Mello</t>
         </is>
       </c>
       <c r="H871" t="inlineStr">
@@ -44171,13 +44167,13 @@
         </is>
       </c>
       <c r="I871" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J871" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="K871" t="n">
-        <v>84</v>
+        <v>105</v>
       </c>
     </row>
     <row r="872">
@@ -44213,7 +44209,7 @@
       </c>
       <c r="G872" t="inlineStr">
         <is>
-          <t>Janiele Ferreira</t>
+          <t>Debora Nunes</t>
         </is>
       </c>
       <c r="H872" t="inlineStr">
@@ -44225,10 +44221,10 @@
         <v>0</v>
       </c>
       <c r="J872" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K872" t="n">
-        <v>20</v>
+        <v>78</v>
       </c>
     </row>
     <row r="873">
@@ -44264,7 +44260,7 @@
       </c>
       <c r="G873" t="inlineStr">
         <is>
-          <t>Jefferson Barros</t>
+          <t>Graziele Almeida</t>
         </is>
       </c>
       <c r="H873" t="inlineStr">
@@ -44273,13 +44269,13 @@
         </is>
       </c>
       <c r="I873" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J873" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K873" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="874">
@@ -44315,7 +44311,7 @@
       </c>
       <c r="G874" t="inlineStr">
         <is>
-          <t>Karina Oliveira</t>
+          <t>Janiele Ferreira</t>
         </is>
       </c>
       <c r="H874" t="inlineStr">
@@ -44327,10 +44323,10 @@
         <v>0</v>
       </c>
       <c r="J874" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K874" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="875">
@@ -44366,7 +44362,7 @@
       </c>
       <c r="G875" t="inlineStr">
         <is>
-          <t>Leonardo Assunção</t>
+          <t>Jefferson Barros</t>
         </is>
       </c>
       <c r="H875" t="inlineStr">
@@ -44375,13 +44371,13 @@
         </is>
       </c>
       <c r="I875" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J875" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K875" t="n">
-        <v>32</v>
+        <v>99</v>
       </c>
     </row>
     <row r="876">
@@ -44417,7 +44413,7 @@
       </c>
       <c r="G876" t="inlineStr">
         <is>
-          <t>Liliane Costa</t>
+          <t>Karina Oliveira</t>
         </is>
       </c>
       <c r="H876" t="inlineStr">
@@ -44426,13 +44422,13 @@
         </is>
       </c>
       <c r="I876" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J876" t="n">
         <v>5</v>
       </c>
       <c r="K876" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="877">
@@ -44468,7 +44464,7 @@
       </c>
       <c r="G877" t="inlineStr">
         <is>
-          <t>Luciene Pimenta</t>
+          <t>Leonardo Assunção</t>
         </is>
       </c>
       <c r="H877" t="inlineStr">
@@ -44480,10 +44476,10 @@
         <v>0</v>
       </c>
       <c r="J877" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="K877" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
     </row>
     <row r="878">
@@ -44519,7 +44515,7 @@
       </c>
       <c r="G878" t="inlineStr">
         <is>
-          <t>Lucirene Souza</t>
+          <t>Liliane Costa</t>
         </is>
       </c>
       <c r="H878" t="inlineStr">
@@ -44531,10 +44527,10 @@
         <v>0</v>
       </c>
       <c r="J878" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="K878" t="n">
-        <v>84</v>
+        <v>16</v>
       </c>
     </row>
     <row r="879">
@@ -44570,7 +44566,7 @@
       </c>
       <c r="G879" t="inlineStr">
         <is>
-          <t>Marlon Silva</t>
+          <t>Luciene Pimenta</t>
         </is>
       </c>
       <c r="H879" t="inlineStr">
@@ -44582,10 +44578,10 @@
         <v>0</v>
       </c>
       <c r="J879" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K879" t="n">
-        <v>109</v>
+        <v>10</v>
       </c>
     </row>
     <row r="880">
@@ -44621,7 +44617,7 @@
       </c>
       <c r="G880" t="inlineStr">
         <is>
-          <t>Monique Britto</t>
+          <t>Lucirene Souza</t>
         </is>
       </c>
       <c r="H880" t="inlineStr">
@@ -44633,10 +44629,10 @@
         <v>0</v>
       </c>
       <c r="J880" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="K880" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="881">
@@ -44672,7 +44668,7 @@
       </c>
       <c r="G881" t="inlineStr">
         <is>
-          <t>Romulo Ferreira</t>
+          <t>Marlon Silva</t>
         </is>
       </c>
       <c r="H881" t="inlineStr">
@@ -44684,10 +44680,10 @@
         <v>0</v>
       </c>
       <c r="J881" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K881" t="n">
-        <v>306</v>
+        <v>109</v>
       </c>
     </row>
     <row r="882">
@@ -44723,7 +44719,7 @@
       </c>
       <c r="G882" t="inlineStr">
         <is>
-          <t>Rosilene Silva</t>
+          <t>Monique Britto</t>
         </is>
       </c>
       <c r="H882" t="inlineStr">
@@ -44732,13 +44728,13 @@
         </is>
       </c>
       <c r="I882" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J882" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="K882" t="n">
-        <v>18</v>
+        <v>91</v>
       </c>
     </row>
     <row r="883">
@@ -44774,7 +44770,7 @@
       </c>
       <c r="G883" t="inlineStr">
         <is>
-          <t>Thais Santos</t>
+          <t>Romulo Ferreira</t>
         </is>
       </c>
       <c r="H883" t="inlineStr">
@@ -44783,13 +44779,13 @@
         </is>
       </c>
       <c r="I883" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J883" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="K883" t="n">
-        <v>105</v>
+        <v>306</v>
       </c>
     </row>
     <row r="884">
@@ -44825,7 +44821,7 @@
       </c>
       <c r="G884" t="inlineStr">
         <is>
-          <t>Vitoria Tavares</t>
+          <t>Rosilene Silva</t>
         </is>
       </c>
       <c r="H884" t="inlineStr">
@@ -44834,13 +44830,13 @@
         </is>
       </c>
       <c r="I884" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J884" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K884" t="n">
-        <v>163</v>
+        <v>29</v>
       </c>
     </row>
     <row r="885">
@@ -44876,7 +44872,7 @@
       </c>
       <c r="G885" t="inlineStr">
         <is>
-          <t>Viviane Moura</t>
+          <t>Thais Santos</t>
         </is>
       </c>
       <c r="H885" t="inlineStr">
@@ -44885,13 +44881,13 @@
         </is>
       </c>
       <c r="I885" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J885" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="K885" t="n">
-        <v>74</v>
+        <v>107</v>
       </c>
     </row>
     <row r="886">
@@ -44927,7 +44923,7 @@
       </c>
       <c r="G886" t="inlineStr">
         <is>
-          <t>Yasmin Lopes</t>
+          <t>Vitoria Tavares</t>
         </is>
       </c>
       <c r="H886" t="inlineStr">
@@ -44939,10 +44935,10 @@
         <v>0</v>
       </c>
       <c r="J886" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="K886" t="n">
-        <v>118</v>
+        <v>163</v>
       </c>
     </row>
     <row r="887">
@@ -44973,27 +44969,27 @@
       </c>
       <c r="F887" t="inlineStr">
         <is>
-          <t>RJ - EF</t>
+          <t>RJ - DP</t>
         </is>
       </c>
       <c r="G887" t="inlineStr">
         <is>
-          <t>Altamir Nogueira</t>
+          <t>Viviane Moura</t>
         </is>
       </c>
       <c r="H887" t="inlineStr">
         <is>
-          <t>Julio Santos|Jessica Benjamin</t>
+          <t>Karina Oliveira|Liliane Costa</t>
         </is>
       </c>
       <c r="I887" t="n">
         <v>0</v>
       </c>
       <c r="J887" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="K887" t="n">
-        <v>103</v>
+        <v>74</v>
       </c>
     </row>
     <row r="888">
@@ -45024,27 +45020,27 @@
       </c>
       <c r="F888" t="inlineStr">
         <is>
-          <t>RJ - EF</t>
+          <t>RJ - DP</t>
         </is>
       </c>
       <c r="G888" t="inlineStr">
         <is>
-          <t>Beatriz Oliveira</t>
+          <t>Yasmin Lopes</t>
         </is>
       </c>
       <c r="H888" t="inlineStr">
         <is>
-          <t>Julio Santos|Jessica Benjamin</t>
+          <t>Karina Oliveira|Liliane Costa</t>
         </is>
       </c>
       <c r="I888" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J888" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="K888" t="n">
-        <v>45</v>
+        <v>118</v>
       </c>
     </row>
     <row r="889">
@@ -45080,7 +45076,7 @@
       </c>
       <c r="G889" t="inlineStr">
         <is>
-          <t>Glaucia Santos</t>
+          <t>Altamir Nogueira</t>
         </is>
       </c>
       <c r="H889" t="inlineStr">
@@ -45089,13 +45085,13 @@
         </is>
       </c>
       <c r="I889" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J889" t="n">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="K889" t="n">
-        <v>57</v>
+        <v>104</v>
       </c>
     </row>
     <row r="890">
@@ -45131,7 +45127,7 @@
       </c>
       <c r="G890" t="inlineStr">
         <is>
-          <t>Isabela Barbosa</t>
+          <t>Beatriz Oliveira</t>
         </is>
       </c>
       <c r="H890" t="inlineStr">
@@ -45143,10 +45139,10 @@
         <v>0</v>
       </c>
       <c r="J890" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="K890" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="891">
@@ -45182,7 +45178,7 @@
       </c>
       <c r="G891" t="inlineStr">
         <is>
-          <t>Jessica Benjamin</t>
+          <t>Glaucia Santos</t>
         </is>
       </c>
       <c r="H891" t="inlineStr">
@@ -45191,13 +45187,13 @@
         </is>
       </c>
       <c r="I891" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="J891" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="K891" t="n">
-        <v>69</v>
+        <v>91</v>
       </c>
     </row>
     <row r="892">
@@ -45233,7 +45229,7 @@
       </c>
       <c r="G892" t="inlineStr">
         <is>
-          <t>Juliana Perfeito</t>
+          <t>Isabela Barbosa</t>
         </is>
       </c>
       <c r="H892" t="inlineStr">
@@ -45242,13 +45238,13 @@
         </is>
       </c>
       <c r="I892" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J892" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="K892" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="893">
@@ -45284,7 +45280,7 @@
       </c>
       <c r="G893" t="inlineStr">
         <is>
-          <t>Julio Santos</t>
+          <t>Jessica Benjamin</t>
         </is>
       </c>
       <c r="H893" t="inlineStr">
@@ -45293,13 +45289,13 @@
         </is>
       </c>
       <c r="I893" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J893" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="K893" t="n">
-        <v>1</v>
+        <v>72</v>
       </c>
     </row>
     <row r="894">
@@ -45335,7 +45331,7 @@
       </c>
       <c r="G894" t="inlineStr">
         <is>
-          <t>Lais Catrine EF</t>
+          <t>Juliana Perfeito</t>
         </is>
       </c>
       <c r="H894" t="inlineStr">
@@ -45344,13 +45340,13 @@
         </is>
       </c>
       <c r="I894" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J894" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="K894" t="n">
-        <v>124</v>
+        <v>56</v>
       </c>
     </row>
     <row r="895">
@@ -45386,7 +45382,7 @@
       </c>
       <c r="G895" t="inlineStr">
         <is>
-          <t>Luana Meneses</t>
+          <t>Julio Santos</t>
         </is>
       </c>
       <c r="H895" t="inlineStr">
@@ -45398,10 +45394,10 @@
         <v>0</v>
       </c>
       <c r="J895" t="n">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="K895" t="n">
-        <v>96</v>
+        <v>1</v>
       </c>
     </row>
     <row r="896">
@@ -45437,7 +45433,7 @@
       </c>
       <c r="G896" t="inlineStr">
         <is>
-          <t>Otacilia Ferreira</t>
+          <t>Lais Catrine EF</t>
         </is>
       </c>
       <c r="H896" t="inlineStr">
@@ -45446,13 +45442,13 @@
         </is>
       </c>
       <c r="I896" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J896" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="K896" t="n">
-        <v>36</v>
+        <v>125</v>
       </c>
     </row>
     <row r="897">
@@ -45488,7 +45484,7 @@
       </c>
       <c r="G897" t="inlineStr">
         <is>
-          <t>Renata Paixão</t>
+          <t>Luana Meneses</t>
         </is>
       </c>
       <c r="H897" t="inlineStr">
@@ -45500,10 +45496,10 @@
         <v>0</v>
       </c>
       <c r="J897" t="n">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="K897" t="n">
-        <v>107</v>
+        <v>96</v>
       </c>
     </row>
     <row r="898">
@@ -45539,7 +45535,7 @@
       </c>
       <c r="G898" t="inlineStr">
         <is>
-          <t>Thamara Jordes</t>
+          <t>Otacilia Ferreira</t>
         </is>
       </c>
       <c r="H898" t="inlineStr">
@@ -45548,13 +45544,13 @@
         </is>
       </c>
       <c r="I898" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J898" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="K898" t="n">
-        <v>43</v>
+        <v>56</v>
       </c>
     </row>
     <row r="899">
@@ -45590,7 +45586,7 @@
       </c>
       <c r="G899" t="inlineStr">
         <is>
-          <t>Wellington Oliveira</t>
+          <t>Renata Paixão</t>
         </is>
       </c>
       <c r="H899" t="inlineStr">
@@ -45599,13 +45595,13 @@
         </is>
       </c>
       <c r="I899" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="J899" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="K899" t="n">
-        <v>108</v>
+        <v>138</v>
       </c>
     </row>
     <row r="900">
@@ -45636,23 +45632,27 @@
       </c>
       <c r="F900" t="inlineStr">
         <is>
-          <t>RJ - GC</t>
+          <t>RJ - EF</t>
         </is>
       </c>
       <c r="G900" t="inlineStr">
         <is>
-          <t>Bruno Mota</t>
-        </is>
-      </c>
-      <c r="H900" t="inlineStr"/>
+          <t>Thamara Jordes</t>
+        </is>
+      </c>
+      <c r="H900" t="inlineStr">
+        <is>
+          <t>Julio Santos|Jessica Benjamin</t>
+        </is>
+      </c>
       <c r="I900" t="n">
         <v>0</v>
       </c>
       <c r="J900" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="K900" t="n">
-        <v>136</v>
+        <v>43</v>
       </c>
     </row>
     <row r="901">
@@ -45683,23 +45683,27 @@
       </c>
       <c r="F901" t="inlineStr">
         <is>
-          <t>RJ - GC</t>
+          <t>RJ - EF</t>
         </is>
       </c>
       <c r="G901" t="inlineStr">
         <is>
-          <t>Cavalcante Peres</t>
-        </is>
-      </c>
-      <c r="H901" t="inlineStr"/>
+          <t>Wellington Oliveira</t>
+        </is>
+      </c>
+      <c r="H901" t="inlineStr">
+        <is>
+          <t>Julio Santos|Jessica Benjamin</t>
+        </is>
+      </c>
       <c r="I901" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J901" t="n">
-        <v>5</v>
+        <v>57</v>
       </c>
       <c r="K901" t="n">
-        <v>21</v>
+        <v>116</v>
       </c>
     </row>
     <row r="902">
@@ -45735,7 +45739,7 @@
       </c>
       <c r="G902" t="inlineStr">
         <is>
-          <t>Tiago Rodrigues</t>
+          <t>Bruno Mota</t>
         </is>
       </c>
       <c r="H902" t="inlineStr"/>
@@ -45743,10 +45747,10 @@
         <v>0</v>
       </c>
       <c r="J902" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="K902" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
     </row>
     <row r="903">
@@ -45777,12 +45781,12 @@
       </c>
       <c r="F903" t="inlineStr">
         <is>
-          <t>RJ - GC ADMINISTRATIVO</t>
+          <t>RJ - GC</t>
         </is>
       </c>
       <c r="G903" t="inlineStr">
         <is>
-          <t>Amanda Mesquita</t>
+          <t>Cavalcante Peres</t>
         </is>
       </c>
       <c r="H903" t="inlineStr"/>
@@ -45790,10 +45794,10 @@
         <v>0</v>
       </c>
       <c r="J903" t="n">
-        <v>180</v>
+        <v>5</v>
       </c>
       <c r="K903" t="n">
-        <v>215</v>
+        <v>21</v>
       </c>
     </row>
     <row r="904">
@@ -45824,12 +45828,12 @@
       </c>
       <c r="F904" t="inlineStr">
         <is>
-          <t>RJ - GC ADMINISTRATIVO</t>
+          <t>RJ - GC</t>
         </is>
       </c>
       <c r="G904" t="inlineStr">
         <is>
-          <t>Lohany Martins</t>
+          <t>Tiago Rodrigues</t>
         </is>
       </c>
       <c r="H904" t="inlineStr"/>
@@ -45837,10 +45841,10 @@
         <v>0</v>
       </c>
       <c r="J904" t="n">
-        <v>143</v>
+        <v>1</v>
       </c>
       <c r="K904" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
     </row>
     <row r="905">
@@ -45871,12 +45875,12 @@
       </c>
       <c r="F905" t="inlineStr">
         <is>
-          <t>S.A.C</t>
+          <t>RJ - GC ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="G905" t="inlineStr">
         <is>
-          <t>Milena Campos - SAC</t>
+          <t>Amanda Mesquita</t>
         </is>
       </c>
       <c r="H905" t="inlineStr"/>
@@ -45884,10 +45888,10 @@
         <v>0</v>
       </c>
       <c r="J905" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="K905" t="n">
-        <v>1</v>
+        <v>215</v>
       </c>
     </row>
     <row r="906">
@@ -45913,32 +45917,28 @@
       </c>
       <c r="E906" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F906" t="inlineStr">
         <is>
-          <t>CONTABILIDADE (Outsourcing)</t>
+          <t>RJ - GC ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="G906" t="inlineStr">
         <is>
-          <t>Aline Petrini</t>
-        </is>
-      </c>
-      <c r="H906" t="inlineStr">
-        <is>
-          <t>Fernanda Araujo</t>
-        </is>
-      </c>
+          <t>Lohany Martins</t>
+        </is>
+      </c>
+      <c r="H906" t="inlineStr"/>
       <c r="I906" t="n">
         <v>0</v>
       </c>
       <c r="J906" t="n">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="K906" t="n">
-        <v>1</v>
+        <v>345</v>
       </c>
     </row>
     <row r="907">
@@ -45964,24 +45964,20 @@
       </c>
       <c r="E907" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F907" t="inlineStr">
         <is>
-          <t>CONTABILIDADE (Outsourcing)</t>
+          <t>S.A.C</t>
         </is>
       </c>
       <c r="G907" t="inlineStr">
         <is>
-          <t>Daniele Leite</t>
-        </is>
-      </c>
-      <c r="H907" t="inlineStr">
-        <is>
-          <t>Edileide Dias</t>
-        </is>
-      </c>
+          <t>Milena Campos - SAC</t>
+        </is>
+      </c>
+      <c r="H907" t="inlineStr"/>
       <c r="I907" t="n">
         <v>0</v>
       </c>
@@ -46025,22 +46021,22 @@
       </c>
       <c r="G908" t="inlineStr">
         <is>
-          <t>Diogo Calazans</t>
+          <t>Aline Petrini</t>
         </is>
       </c>
       <c r="H908" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="I908" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J908" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K908" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="909">
@@ -46076,22 +46072,22 @@
       </c>
       <c r="G909" t="inlineStr">
         <is>
-          <t>Jaqueline Sousa</t>
+          <t>Daniele Leite</t>
         </is>
       </c>
       <c r="H909" t="inlineStr">
         <is>
-          <t>Lucas Fischer</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I909" t="n">
         <v>0</v>
       </c>
       <c r="J909" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K909" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="910">
@@ -46127,12 +46123,12 @@
       </c>
       <c r="G910" t="inlineStr">
         <is>
-          <t>Patricia Borges</t>
+          <t>Diogo Calazans</t>
         </is>
       </c>
       <c r="H910" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Karina Santos</t>
         </is>
       </c>
       <c r="I910" t="n">
@@ -46142,7 +46138,7 @@
         <v>0</v>
       </c>
       <c r="K910" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="911">
@@ -46178,19 +46174,19 @@
       </c>
       <c r="G911" t="inlineStr">
         <is>
-          <t>Rejane Coelho</t>
+          <t>Jaqueline Sousa</t>
         </is>
       </c>
       <c r="H911" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Lucas Fischer</t>
         </is>
       </c>
       <c r="I911" t="n">
         <v>0</v>
       </c>
       <c r="J911" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K911" t="n">
         <v>5</v>
@@ -46229,22 +46225,22 @@
       </c>
       <c r="G912" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Patricia Borges</t>
         </is>
       </c>
       <c r="H912" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I912" t="n">
         <v>0</v>
       </c>
       <c r="J912" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K912" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="913">
@@ -46280,7 +46276,7 @@
       </c>
       <c r="G913" t="inlineStr">
         <is>
-          <t>Thiago Ceconelli</t>
+          <t>Rejane Coelho</t>
         </is>
       </c>
       <c r="H913" t="inlineStr">
@@ -46295,7 +46291,7 @@
         <v>1</v>
       </c>
       <c r="K913" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="914">
@@ -46326,12 +46322,12 @@
       </c>
       <c r="F914" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL HOLDING</t>
+          <t>CONTABILIDADE (Outsourcing)</t>
         </is>
       </c>
       <c r="G914" t="inlineStr">
         <is>
-          <t>Ana Flavia Silva</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="H914" t="inlineStr">
@@ -46343,10 +46339,10 @@
         <v>0</v>
       </c>
       <c r="J914" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="K914" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="915">
@@ -46377,23 +46373,27 @@
       </c>
       <c r="F915" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL HOLDING</t>
+          <t>CONTABILIDADE (Outsourcing)</t>
         </is>
       </c>
       <c r="G915" t="inlineStr">
         <is>
-          <t>Daniele Faria</t>
-        </is>
-      </c>
-      <c r="H915" t="inlineStr"/>
+          <t>Thiago Ceconelli</t>
+        </is>
+      </c>
+      <c r="H915" t="inlineStr">
+        <is>
+          <t>Karina Santos</t>
+        </is>
+      </c>
       <c r="I915" t="n">
         <v>0</v>
       </c>
       <c r="J915" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K915" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="916">
@@ -46429,7 +46429,7 @@
       </c>
       <c r="G916" t="inlineStr">
         <is>
-          <t>Vitor de Souza</t>
+          <t>Ana Flavia Silva</t>
         </is>
       </c>
       <c r="H916" t="inlineStr">
@@ -46441,10 +46441,10 @@
         <v>0</v>
       </c>
       <c r="J916" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="K916" t="n">
-        <v>112</v>
+        <v>28</v>
       </c>
     </row>
     <row r="917">
@@ -46480,22 +46480,18 @@
       </c>
       <c r="G917" t="inlineStr">
         <is>
-          <t>Vitoria Regina</t>
-        </is>
-      </c>
-      <c r="H917" t="inlineStr">
-        <is>
-          <t>Tatiana Linardi</t>
-        </is>
-      </c>
+          <t>Daniele Faria</t>
+        </is>
+      </c>
+      <c r="H917" t="inlineStr"/>
       <c r="I917" t="n">
         <v>0</v>
       </c>
       <c r="J917" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K917" t="n">
-        <v>63</v>
+        <v>2</v>
       </c>
     </row>
     <row r="918">
@@ -46526,27 +46522,27 @@
       </c>
       <c r="F918" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL INDUSTRIA</t>
+          <t>CTB - CONTÁBIL HOLDING</t>
         </is>
       </c>
       <c r="G918" t="inlineStr">
         <is>
-          <t>Adriano Barros</t>
+          <t>Vitor de Souza</t>
         </is>
       </c>
       <c r="H918" t="inlineStr">
         <is>
-          <t>Erika Santana|Isabella Nascimento</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="I918" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J918" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K918" t="n">
-        <v>1</v>
+        <v>113</v>
       </c>
     </row>
     <row r="919">
@@ -46577,27 +46573,27 @@
       </c>
       <c r="F919" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL INDUSTRIA</t>
+          <t>CTB - CONTÁBIL HOLDING</t>
         </is>
       </c>
       <c r="G919" t="inlineStr">
         <is>
-          <t>Bianca Silva</t>
+          <t>Vitoria Regina</t>
         </is>
       </c>
       <c r="H919" t="inlineStr">
         <is>
-          <t>Erika Santana|Isabella Nascimento</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="I919" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J919" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K919" t="n">
-        <v>10</v>
+        <v>64</v>
       </c>
     </row>
     <row r="920">
@@ -46633,7 +46629,7 @@
       </c>
       <c r="G920" t="inlineStr">
         <is>
-          <t>Emylle Souza</t>
+          <t>Adriano Barros</t>
         </is>
       </c>
       <c r="H920" t="inlineStr">
@@ -46645,10 +46641,10 @@
         <v>0</v>
       </c>
       <c r="J920" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K920" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="921">
@@ -46684,7 +46680,7 @@
       </c>
       <c r="G921" t="inlineStr">
         <is>
-          <t>Fatima Rocha</t>
+          <t>Bianca Silva</t>
         </is>
       </c>
       <c r="H921" t="inlineStr">
@@ -46696,10 +46692,10 @@
         <v>0</v>
       </c>
       <c r="J921" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="K921" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="922">
@@ -46735,7 +46731,7 @@
       </c>
       <c r="G922" t="inlineStr">
         <is>
-          <t>Gabriel Correia</t>
+          <t>Emylle Souza</t>
         </is>
       </c>
       <c r="H922" t="inlineStr">
@@ -46747,10 +46743,10 @@
         <v>0</v>
       </c>
       <c r="J922" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K922" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="923">
@@ -46786,7 +46782,7 @@
       </c>
       <c r="G923" t="inlineStr">
         <is>
-          <t>Isabella Nascimento</t>
+          <t>Fatima Rocha</t>
         </is>
       </c>
       <c r="H923" t="inlineStr">
@@ -46798,10 +46794,10 @@
         <v>0</v>
       </c>
       <c r="J923" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K923" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="924">
@@ -46837,7 +46833,7 @@
       </c>
       <c r="G924" t="inlineStr">
         <is>
-          <t>Laisa Rocha</t>
+          <t>Gabriel Correia</t>
         </is>
       </c>
       <c r="H924" t="inlineStr">
@@ -46846,10 +46842,10 @@
         </is>
       </c>
       <c r="I924" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J924" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K924" t="n">
         <v>8</v>
@@ -46888,7 +46884,7 @@
       </c>
       <c r="G925" t="inlineStr">
         <is>
-          <t>Lucas Alves</t>
+          <t>Isabella Nascimento</t>
         </is>
       </c>
       <c r="H925" t="inlineStr">
@@ -46900,10 +46896,10 @@
         <v>0</v>
       </c>
       <c r="J925" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K925" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="926">
@@ -46939,7 +46935,7 @@
       </c>
       <c r="G926" t="inlineStr">
         <is>
-          <t>Luciana Silva</t>
+          <t>Laisa Rocha</t>
         </is>
       </c>
       <c r="H926" t="inlineStr">
@@ -46948,13 +46944,13 @@
         </is>
       </c>
       <c r="I926" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J926" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K926" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
     </row>
     <row r="927">
@@ -46990,18 +46986,22 @@
       </c>
       <c r="G927" t="inlineStr">
         <is>
-          <t>Luiz Ferreira</t>
-        </is>
-      </c>
-      <c r="H927" t="inlineStr"/>
+          <t>Lucas Alves</t>
+        </is>
+      </c>
+      <c r="H927" t="inlineStr">
+        <is>
+          <t>Erika Santana|Isabella Nascimento</t>
+        </is>
+      </c>
       <c r="I927" t="n">
         <v>0</v>
       </c>
       <c r="J927" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K927" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="928">
@@ -47037,7 +47037,7 @@
       </c>
       <c r="G928" t="inlineStr">
         <is>
-          <t>Marcus Oliveira</t>
+          <t>Luciana Silva</t>
         </is>
       </c>
       <c r="H928" t="inlineStr">
@@ -47049,10 +47049,10 @@
         <v>0</v>
       </c>
       <c r="J928" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K928" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
     </row>
     <row r="929">
@@ -47088,22 +47088,18 @@
       </c>
       <c r="G929" t="inlineStr">
         <is>
-          <t>Mariana Pires</t>
-        </is>
-      </c>
-      <c r="H929" t="inlineStr">
-        <is>
-          <t>Erika Santana|Isabella Nascimento</t>
-        </is>
-      </c>
+          <t>Luiz Ferreira</t>
+        </is>
+      </c>
+      <c r="H929" t="inlineStr"/>
       <c r="I929" t="n">
         <v>0</v>
       </c>
       <c r="J929" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K929" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="930">
@@ -47139,7 +47135,7 @@
       </c>
       <c r="G930" t="inlineStr">
         <is>
-          <t>Marta Souza</t>
+          <t>Marcus Oliveira</t>
         </is>
       </c>
       <c r="H930" t="inlineStr">
@@ -47151,10 +47147,10 @@
         <v>0</v>
       </c>
       <c r="J930" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K930" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="931">
@@ -47190,7 +47186,7 @@
       </c>
       <c r="G931" t="inlineStr">
         <is>
-          <t>Mateus Miranda</t>
+          <t>Mariana Pires</t>
         </is>
       </c>
       <c r="H931" t="inlineStr">
@@ -47202,10 +47198,10 @@
         <v>0</v>
       </c>
       <c r="J931" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K931" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="932">
@@ -47241,7 +47237,7 @@
       </c>
       <c r="G932" t="inlineStr">
         <is>
-          <t>Mirian Lima</t>
+          <t>Marta Souza</t>
         </is>
       </c>
       <c r="H932" t="inlineStr">
@@ -47253,10 +47249,10 @@
         <v>0</v>
       </c>
       <c r="J932" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K932" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="933">
@@ -47292,7 +47288,7 @@
       </c>
       <c r="G933" t="inlineStr">
         <is>
-          <t>Nathalia Lourenco</t>
+          <t>Mateus Miranda</t>
         </is>
       </c>
       <c r="H933" t="inlineStr">
@@ -47304,10 +47300,10 @@
         <v>0</v>
       </c>
       <c r="J933" t="n">
+        <v>0</v>
+      </c>
+      <c r="K933" t="n">
         <v>3</v>
-      </c>
-      <c r="K933" t="n">
-        <v>13</v>
       </c>
     </row>
     <row r="934">
@@ -47343,7 +47339,7 @@
       </c>
       <c r="G934" t="inlineStr">
         <is>
-          <t>Nicolas Dias</t>
+          <t>Mirian Lima</t>
         </is>
       </c>
       <c r="H934" t="inlineStr">
@@ -47352,13 +47348,13 @@
         </is>
       </c>
       <c r="I934" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J934" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K934" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="935">
@@ -47394,7 +47390,7 @@
       </c>
       <c r="G935" t="inlineStr">
         <is>
-          <t>Rodrigo Nunes</t>
+          <t>Nathalia Lourenco</t>
         </is>
       </c>
       <c r="H935" t="inlineStr">
@@ -47403,13 +47399,13 @@
         </is>
       </c>
       <c r="I935" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J935" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K935" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="936">
@@ -47445,7 +47441,7 @@
       </c>
       <c r="G936" t="inlineStr">
         <is>
-          <t>Thais Souza</t>
+          <t>Nicolas Dias</t>
         </is>
       </c>
       <c r="H936" t="inlineStr">
@@ -47454,13 +47450,13 @@
         </is>
       </c>
       <c r="I936" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J936" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="K936" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="937">
@@ -47491,27 +47487,27 @@
       </c>
       <c r="F937" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="G937" t="inlineStr">
         <is>
-          <t>Aline Petrini</t>
+          <t>Rodrigo Nunes</t>
         </is>
       </c>
       <c r="H937" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Erika Santana|Isabella Nascimento</t>
         </is>
       </c>
       <c r="I937" t="n">
         <v>0</v>
       </c>
       <c r="J937" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K937" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
     </row>
     <row r="938">
@@ -47542,27 +47538,27 @@
       </c>
       <c r="F938" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="G938" t="inlineStr">
         <is>
-          <t>Ana Barbosa</t>
+          <t>Thais Souza</t>
         </is>
       </c>
       <c r="H938" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Erika Santana|Isabella Nascimento</t>
         </is>
       </c>
       <c r="I938" t="n">
         <v>0</v>
       </c>
       <c r="J938" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K938" t="n">
-        <v>44</v>
+        <v>3</v>
       </c>
     </row>
     <row r="939">
@@ -47598,22 +47594,22 @@
       </c>
       <c r="G939" t="inlineStr">
         <is>
-          <t>Daniele Leite</t>
+          <t>Aline Petrini</t>
         </is>
       </c>
       <c r="H939" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="I939" t="n">
         <v>0</v>
       </c>
       <c r="J939" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="K939" t="n">
-        <v>4</v>
+        <v>29</v>
       </c>
     </row>
     <row r="940">
@@ -47649,22 +47645,22 @@
       </c>
       <c r="G940" t="inlineStr">
         <is>
-          <t>Danielle Silva</t>
+          <t>Ana Barbosa</t>
         </is>
       </c>
       <c r="H940" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I940" t="n">
         <v>0</v>
       </c>
       <c r="J940" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K940" t="n">
-        <v>65</v>
+        <v>44</v>
       </c>
     </row>
     <row r="941">
@@ -47700,22 +47696,22 @@
       </c>
       <c r="G941" t="inlineStr">
         <is>
-          <t>Danilo Oliveira</t>
+          <t>Daniele Leite</t>
         </is>
       </c>
       <c r="H941" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I941" t="n">
         <v>0</v>
       </c>
       <c r="J941" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K941" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="942">
@@ -47751,22 +47747,22 @@
       </c>
       <c r="G942" t="inlineStr">
         <is>
-          <t>Debora Silva</t>
+          <t>Danielle Silva</t>
         </is>
       </c>
       <c r="H942" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Karina Santos</t>
         </is>
       </c>
       <c r="I942" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J942" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="K942" t="n">
-        <v>18</v>
+        <v>69</v>
       </c>
     </row>
     <row r="943">
@@ -47802,7 +47798,7 @@
       </c>
       <c r="G943" t="inlineStr">
         <is>
-          <t>Diogo Calazans</t>
+          <t>Danilo Oliveira</t>
         </is>
       </c>
       <c r="H943" t="inlineStr">
@@ -47814,10 +47810,10 @@
         <v>0</v>
       </c>
       <c r="J943" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K943" t="n">
-        <v>79</v>
+        <v>18</v>
       </c>
     </row>
     <row r="944">
@@ -47853,7 +47849,7 @@
       </c>
       <c r="G944" t="inlineStr">
         <is>
-          <t>Eduardo Cruz</t>
+          <t>Debora Silva</t>
         </is>
       </c>
       <c r="H944" t="inlineStr">
@@ -47862,13 +47858,13 @@
         </is>
       </c>
       <c r="I944" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J944" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K944" t="n">
-        <v>75</v>
+        <v>19</v>
       </c>
     </row>
     <row r="945">
@@ -47904,7 +47900,7 @@
       </c>
       <c r="G945" t="inlineStr">
         <is>
-          <t>Eveny Silva</t>
+          <t>Diogo Calazans</t>
         </is>
       </c>
       <c r="H945" t="inlineStr">
@@ -47916,10 +47912,10 @@
         <v>0</v>
       </c>
       <c r="J945" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K945" t="n">
-        <v>35</v>
+        <v>79</v>
       </c>
     </row>
     <row r="946">
@@ -47955,7 +47951,7 @@
       </c>
       <c r="G946" t="inlineStr">
         <is>
-          <t>Everton Moura</t>
+          <t>Eduardo Cruz</t>
         </is>
       </c>
       <c r="H946" t="inlineStr">
@@ -47967,10 +47963,10 @@
         <v>0</v>
       </c>
       <c r="J946" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K946" t="n">
-        <v>9</v>
+        <v>75</v>
       </c>
     </row>
     <row r="947">
@@ -48006,22 +48002,22 @@
       </c>
       <c r="G947" t="inlineStr">
         <is>
-          <t>Guilherme Dantas</t>
+          <t>Eveny Silva</t>
         </is>
       </c>
       <c r="H947" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Karina Santos</t>
         </is>
       </c>
       <c r="I947" t="n">
         <v>0</v>
       </c>
       <c r="J947" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K947" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
     </row>
     <row r="948">
@@ -48057,7 +48053,7 @@
       </c>
       <c r="G948" t="inlineStr">
         <is>
-          <t>Isabela Lemos</t>
+          <t>Everton Moura</t>
         </is>
       </c>
       <c r="H948" t="inlineStr">
@@ -48069,10 +48065,10 @@
         <v>0</v>
       </c>
       <c r="J948" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K948" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="949">
@@ -48108,7 +48104,7 @@
       </c>
       <c r="G949" t="inlineStr">
         <is>
-          <t>Jackson Silva</t>
+          <t>Guilherme Dantas</t>
         </is>
       </c>
       <c r="H949" t="inlineStr">
@@ -48123,7 +48119,7 @@
         <v>0</v>
       </c>
       <c r="K949" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="950">
@@ -48159,22 +48155,22 @@
       </c>
       <c r="G950" t="inlineStr">
         <is>
-          <t>Jaqueline Sousa</t>
+          <t>Isabela Lemos</t>
         </is>
       </c>
       <c r="H950" t="inlineStr">
         <is>
-          <t>Lucas Fischer</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="I950" t="n">
         <v>0</v>
       </c>
       <c r="J950" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="K950" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="951">
@@ -48210,22 +48206,22 @@
       </c>
       <c r="G951" t="inlineStr">
         <is>
-          <t>Leticia Medeiros</t>
+          <t>Jackson Silva</t>
         </is>
       </c>
       <c r="H951" t="inlineStr">
         <is>
-          <t>Lucas Fischer</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I951" t="n">
         <v>0</v>
       </c>
       <c r="J951" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K951" t="n">
-        <v>59</v>
+        <v>20</v>
       </c>
     </row>
     <row r="952">
@@ -48261,22 +48257,22 @@
       </c>
       <c r="G952" t="inlineStr">
         <is>
-          <t>Monica Medeiros</t>
+          <t>Jaqueline Sousa</t>
         </is>
       </c>
       <c r="H952" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Lucas Fischer</t>
         </is>
       </c>
       <c r="I952" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J952" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="K952" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
     </row>
     <row r="953">
@@ -48312,7 +48308,7 @@
       </c>
       <c r="G953" t="inlineStr">
         <is>
-          <t>Naiara Dutra</t>
+          <t>Leticia Medeiros</t>
         </is>
       </c>
       <c r="H953" t="inlineStr">
@@ -48324,10 +48320,10 @@
         <v>0</v>
       </c>
       <c r="J953" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K953" t="n">
-        <v>24</v>
+        <v>59</v>
       </c>
     </row>
     <row r="954">
@@ -48363,7 +48359,7 @@
       </c>
       <c r="G954" t="inlineStr">
         <is>
-          <t>Patricia Borges</t>
+          <t>Monica Medeiros</t>
         </is>
       </c>
       <c r="H954" t="inlineStr">
@@ -48372,13 +48368,13 @@
         </is>
       </c>
       <c r="I954" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J954" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K954" t="n">
-        <v>30</v>
+        <v>47</v>
       </c>
     </row>
     <row r="955">
@@ -48414,22 +48410,22 @@
       </c>
       <c r="G955" t="inlineStr">
         <is>
-          <t>Paulo Silva</t>
+          <t>Naiara Dutra</t>
         </is>
       </c>
       <c r="H955" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Lucas Fischer</t>
         </is>
       </c>
       <c r="I955" t="n">
         <v>0</v>
       </c>
       <c r="J955" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="K955" t="n">
-        <v>58</v>
+        <v>24</v>
       </c>
     </row>
     <row r="956">
@@ -48465,7 +48461,7 @@
       </c>
       <c r="G956" t="inlineStr">
         <is>
-          <t>Rachel Lima</t>
+          <t>Patricia Borges</t>
         </is>
       </c>
       <c r="H956" t="inlineStr">
@@ -48477,10 +48473,10 @@
         <v>0</v>
       </c>
       <c r="J956" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="K956" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="957">
@@ -48516,22 +48512,22 @@
       </c>
       <c r="G957" t="inlineStr">
         <is>
-          <t>Raiane Barbosa</t>
+          <t>Paulo Silva</t>
         </is>
       </c>
       <c r="H957" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="I957" t="n">
         <v>0</v>
       </c>
       <c r="J957" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K957" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="958">
@@ -48567,22 +48563,22 @@
       </c>
       <c r="G958" t="inlineStr">
         <is>
-          <t>Rejane Coelho</t>
+          <t>Rachel Lima</t>
         </is>
       </c>
       <c r="H958" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I958" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J958" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K958" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
     </row>
     <row r="959">
@@ -48618,22 +48614,22 @@
       </c>
       <c r="G959" t="inlineStr">
         <is>
-          <t>Renata Alves - CTV</t>
+          <t>Raiane Barbosa</t>
         </is>
       </c>
       <c r="H959" t="inlineStr">
         <is>
-          <t>Lucas Fischer</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I959" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J959" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="K959" t="n">
-        <v>11</v>
+        <v>63</v>
       </c>
     </row>
     <row r="960">
@@ -48669,15 +48665,19 @@
       </c>
       <c r="G960" t="inlineStr">
         <is>
-          <t>Renata Cavalheiro</t>
-        </is>
-      </c>
-      <c r="H960" t="inlineStr"/>
+          <t>Rejane Coelho</t>
+        </is>
+      </c>
+      <c r="H960" t="inlineStr">
+        <is>
+          <t>Karina Santos</t>
+        </is>
+      </c>
       <c r="I960" t="n">
         <v>0</v>
       </c>
       <c r="J960" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K960" t="n">
         <v>1</v>
@@ -48716,22 +48716,22 @@
       </c>
       <c r="G961" t="inlineStr">
         <is>
-          <t>Ryan Godinho</t>
+          <t>Renata Alves - CTV</t>
         </is>
       </c>
       <c r="H961" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Lucas Fischer</t>
         </is>
       </c>
       <c r="I961" t="n">
         <v>0</v>
       </c>
       <c r="J961" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K961" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
     </row>
     <row r="962">
@@ -48767,14 +48767,10 @@
       </c>
       <c r="G962" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
-        </is>
-      </c>
-      <c r="H962" t="inlineStr">
-        <is>
-          <t>Tatiana Linardi</t>
-        </is>
-      </c>
+          <t>Renata Cavalheiro</t>
+        </is>
+      </c>
+      <c r="H962" t="inlineStr"/>
       <c r="I962" t="n">
         <v>0</v>
       </c>
@@ -48818,22 +48814,22 @@
       </c>
       <c r="G963" t="inlineStr">
         <is>
-          <t>Vitor Domingues</t>
+          <t>Ryan Godinho</t>
         </is>
       </c>
       <c r="H963" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Karina Santos</t>
         </is>
       </c>
       <c r="I963" t="n">
         <v>0</v>
       </c>
       <c r="J963" t="n">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="K963" t="n">
-        <v>66</v>
+        <v>29</v>
       </c>
     </row>
     <row r="964">
@@ -48864,27 +48860,27 @@
       </c>
       <c r="F964" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO PESSOAL (Outsourcing)</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="G964" t="inlineStr">
         <is>
-          <t>Bruna Santana</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="H964" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="I964" t="n">
         <v>0</v>
       </c>
       <c r="J964" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K964" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="965">
@@ -48915,27 +48911,27 @@
       </c>
       <c r="F965" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO PESSOAL (Outsourcing)</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="G965" t="inlineStr">
         <is>
-          <t>Camila Oliveira</t>
+          <t>Vitor Domingues</t>
         </is>
       </c>
       <c r="H965" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="I965" t="n">
         <v>0</v>
       </c>
       <c r="J965" t="n">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="K965" t="n">
-        <v>15</v>
+        <v>66</v>
       </c>
     </row>
     <row r="966">
@@ -48971,12 +48967,12 @@
       </c>
       <c r="G966" t="inlineStr">
         <is>
-          <t>Elaine Assis</t>
+          <t>Bruna Santana</t>
         </is>
       </c>
       <c r="H966" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I966" t="n">
@@ -48986,7 +48982,7 @@
         <v>0</v>
       </c>
       <c r="K966" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="967">
@@ -49022,22 +49018,22 @@
       </c>
       <c r="G967" t="inlineStr">
         <is>
-          <t>Fabiane Branco</t>
+          <t>Camila Oliveira</t>
         </is>
       </c>
       <c r="H967" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I967" t="n">
         <v>0</v>
       </c>
       <c r="J967" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K967" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="968">
@@ -49073,22 +49069,22 @@
       </c>
       <c r="G968" t="inlineStr">
         <is>
-          <t>Jonas Nunes</t>
+          <t>Elaine Assis</t>
         </is>
       </c>
       <c r="H968" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I968" t="n">
         <v>0</v>
       </c>
       <c r="J968" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K968" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="969">
@@ -49119,27 +49115,27 @@
       </c>
       <c r="F969" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>DEPARTAMENTO PESSOAL (Outsourcing)</t>
         </is>
       </c>
       <c r="G969" t="inlineStr">
         <is>
-          <t>Bruna Santana</t>
+          <t>Fabiane Branco</t>
         </is>
       </c>
       <c r="H969" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I969" t="n">
         <v>0</v>
       </c>
       <c r="J969" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K969" t="n">
-        <v>99</v>
+        <v>9</v>
       </c>
     </row>
     <row r="970">
@@ -49170,12 +49166,12 @@
       </c>
       <c r="F970" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>DEPARTAMENTO PESSOAL (Outsourcing)</t>
         </is>
       </c>
       <c r="G970" t="inlineStr">
         <is>
-          <t>Camila Oliveira</t>
+          <t>Jonas Nunes</t>
         </is>
       </c>
       <c r="H970" t="inlineStr">
@@ -49184,13 +49180,13 @@
         </is>
       </c>
       <c r="I970" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J970" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K970" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
     </row>
     <row r="971">
@@ -49226,22 +49222,22 @@
       </c>
       <c r="G971" t="inlineStr">
         <is>
-          <t>Daniel Moraes</t>
+          <t>Bruna Santana</t>
         </is>
       </c>
       <c r="H971" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I971" t="n">
         <v>0</v>
       </c>
       <c r="J971" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K971" t="n">
-        <v>41</v>
+        <v>99</v>
       </c>
     </row>
     <row r="972">
@@ -49277,22 +49273,22 @@
       </c>
       <c r="G972" t="inlineStr">
         <is>
-          <t>Danilo Xavier</t>
+          <t>Camila Oliveira</t>
         </is>
       </c>
       <c r="H972" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I972" t="n">
         <v>0</v>
       </c>
       <c r="J972" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="K972" t="n">
-        <v>156</v>
+        <v>32</v>
       </c>
     </row>
     <row r="973">
@@ -49328,7 +49324,7 @@
       </c>
       <c r="G973" t="inlineStr">
         <is>
-          <t>Elaine Assis</t>
+          <t>Daniel Moraes</t>
         </is>
       </c>
       <c r="H973" t="inlineStr">
@@ -49337,13 +49333,13 @@
         </is>
       </c>
       <c r="I973" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J973" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K973" t="n">
-        <v>57</v>
+        <v>45</v>
       </c>
     </row>
     <row r="974">
@@ -49379,22 +49375,22 @@
       </c>
       <c r="G974" t="inlineStr">
         <is>
-          <t>Eliene Lima</t>
+          <t>Danilo Xavier</t>
         </is>
       </c>
       <c r="H974" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I974" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J974" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="K974" t="n">
-        <v>44</v>
+        <v>157</v>
       </c>
     </row>
     <row r="975">
@@ -49430,7 +49426,7 @@
       </c>
       <c r="G975" t="inlineStr">
         <is>
-          <t>Erica Oliveira</t>
+          <t>Elaine Assis</t>
         </is>
       </c>
       <c r="H975" t="inlineStr">
@@ -49442,10 +49438,10 @@
         <v>0</v>
       </c>
       <c r="J975" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K975" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="976">
@@ -49481,12 +49477,12 @@
       </c>
       <c r="G976" t="inlineStr">
         <is>
-          <t>Evellin Bispo</t>
+          <t>Eliene Lima</t>
         </is>
       </c>
       <c r="H976" t="inlineStr">
         <is>
-          <t>Leandro Matos</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I976" t="n">
@@ -49496,7 +49492,7 @@
         <v>1</v>
       </c>
       <c r="K976" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
     </row>
     <row r="977">
@@ -49532,22 +49528,22 @@
       </c>
       <c r="G977" t="inlineStr">
         <is>
-          <t>Fabiane Branco</t>
+          <t>Erica Oliveira</t>
         </is>
       </c>
       <c r="H977" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I977" t="n">
         <v>0</v>
       </c>
       <c r="J977" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K977" t="n">
-        <v>125</v>
+        <v>47</v>
       </c>
     </row>
     <row r="978">
@@ -49583,22 +49579,22 @@
       </c>
       <c r="G978" t="inlineStr">
         <is>
-          <t>Franciele Alves</t>
+          <t>Evellin Bispo</t>
         </is>
       </c>
       <c r="H978" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Leandro Matos</t>
         </is>
       </c>
       <c r="I978" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J978" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K978" t="n">
-        <v>56</v>
+        <v>25</v>
       </c>
     </row>
     <row r="979">
@@ -49634,22 +49630,22 @@
       </c>
       <c r="G979" t="inlineStr">
         <is>
-          <t>Gabriela Peres</t>
+          <t>Fabiane Branco</t>
         </is>
       </c>
       <c r="H979" t="inlineStr">
         <is>
-          <t>Leandro Matos</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I979" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J979" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K979" t="n">
-        <v>12</v>
+        <v>128</v>
       </c>
     </row>
     <row r="980">
@@ -49685,22 +49681,22 @@
       </c>
       <c r="G980" t="inlineStr">
         <is>
-          <t>Grasiele Santos</t>
+          <t>Franciele Alves</t>
         </is>
       </c>
       <c r="H980" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I980" t="n">
         <v>0</v>
       </c>
       <c r="J980" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K980" t="n">
-        <v>141</v>
+        <v>56</v>
       </c>
     </row>
     <row r="981">
@@ -49736,22 +49732,22 @@
       </c>
       <c r="G981" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Gabriela Peres</t>
         </is>
       </c>
       <c r="H981" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Leandro Matos</t>
         </is>
       </c>
       <c r="I981" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J981" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="K981" t="n">
-        <v>127</v>
+        <v>14</v>
       </c>
     </row>
     <row r="982">
@@ -49787,7 +49783,7 @@
       </c>
       <c r="G982" t="inlineStr">
         <is>
-          <t>Janaina Rocha</t>
+          <t>Grasiele Santos</t>
         </is>
       </c>
       <c r="H982" t="inlineStr">
@@ -49796,13 +49792,13 @@
         </is>
       </c>
       <c r="I982" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J982" t="n">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="K982" t="n">
-        <v>90</v>
+        <v>143</v>
       </c>
     </row>
     <row r="983">
@@ -49838,22 +49834,22 @@
       </c>
       <c r="G983" t="inlineStr">
         <is>
-          <t>Jayne Tavares</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="H983" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I983" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J983" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="K983" t="n">
-        <v>127</v>
+        <v>142</v>
       </c>
     </row>
     <row r="984">
@@ -49889,7 +49885,7 @@
       </c>
       <c r="G984" t="inlineStr">
         <is>
-          <t>Jhenifer Tenorio</t>
+          <t>Janaina Rocha</t>
         </is>
       </c>
       <c r="H984" t="inlineStr">
@@ -49901,10 +49897,10 @@
         <v>0</v>
       </c>
       <c r="J984" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K984" t="n">
-        <v>115</v>
+        <v>90</v>
       </c>
     </row>
     <row r="985">
@@ -49940,22 +49936,22 @@
       </c>
       <c r="G985" t="inlineStr">
         <is>
-          <t>Jonas Nunes</t>
+          <t>Jayne Tavares</t>
         </is>
       </c>
       <c r="H985" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I985" t="n">
         <v>0</v>
       </c>
       <c r="J985" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="K985" t="n">
-        <v>91</v>
+        <v>127</v>
       </c>
     </row>
     <row r="986">
@@ -49991,22 +49987,22 @@
       </c>
       <c r="G986" t="inlineStr">
         <is>
-          <t>Kaique Souza</t>
+          <t>Jhenifer Tenorio</t>
         </is>
       </c>
       <c r="H986" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I986" t="n">
         <v>0</v>
       </c>
       <c r="J986" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="K986" t="n">
-        <v>79</v>
+        <v>115</v>
       </c>
     </row>
     <row r="987">
@@ -50042,22 +50038,22 @@
       </c>
       <c r="G987" t="inlineStr">
         <is>
-          <t>Karine Sousa</t>
+          <t>Jonas Nunes</t>
         </is>
       </c>
       <c r="H987" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I987" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J987" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="K987" t="n">
-        <v>65</v>
+        <v>112</v>
       </c>
     </row>
     <row r="988">
@@ -50093,22 +50089,22 @@
       </c>
       <c r="G988" t="inlineStr">
         <is>
-          <t>Laysla Alves</t>
+          <t>Kaique Souza</t>
         </is>
       </c>
       <c r="H988" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I988" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J988" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="K988" t="n">
-        <v>60</v>
+        <v>79</v>
       </c>
     </row>
     <row r="989">
@@ -50144,22 +50140,22 @@
       </c>
       <c r="G989" t="inlineStr">
         <is>
-          <t>Luana Marques</t>
+          <t>Karine Sousa</t>
         </is>
       </c>
       <c r="H989" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I989" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J989" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="K989" t="n">
-        <v>17</v>
+        <v>66</v>
       </c>
     </row>
     <row r="990">
@@ -50195,22 +50191,22 @@
       </c>
       <c r="G990" t="inlineStr">
         <is>
-          <t>Maria Pires</t>
+          <t>Laysla Alves</t>
         </is>
       </c>
       <c r="H990" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I990" t="n">
         <v>0</v>
       </c>
       <c r="J990" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="K990" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
     </row>
     <row r="991">
@@ -50246,22 +50242,22 @@
       </c>
       <c r="G991" t="inlineStr">
         <is>
-          <t>Mauricio Lermen</t>
+          <t>Luana Marques</t>
         </is>
       </c>
       <c r="H991" t="inlineStr">
         <is>
-          <t>Mauricio Lermen</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I991" t="n">
         <v>0</v>
       </c>
       <c r="J991" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K991" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="992">
@@ -50297,22 +50293,22 @@
       </c>
       <c r="G992" t="inlineStr">
         <is>
-          <t>Micaele Cordeiro</t>
+          <t>Maria Pires</t>
         </is>
       </c>
       <c r="H992" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I992" t="n">
         <v>0</v>
       </c>
       <c r="J992" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="K992" t="n">
-        <v>86</v>
+        <v>1</v>
       </c>
     </row>
     <row r="993">
@@ -50348,22 +50344,22 @@
       </c>
       <c r="G993" t="inlineStr">
         <is>
-          <t>Michele Silva</t>
+          <t>Mauricio Lermen</t>
         </is>
       </c>
       <c r="H993" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>Mauricio Lermen</t>
         </is>
       </c>
       <c r="I993" t="n">
         <v>0</v>
       </c>
       <c r="J993" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K993" t="n">
-        <v>70</v>
+        <v>14</v>
       </c>
     </row>
     <row r="994">
@@ -50399,18 +50395,22 @@
       </c>
       <c r="G994" t="inlineStr">
         <is>
-          <t>Mikael Teixeira</t>
-        </is>
-      </c>
-      <c r="H994" t="inlineStr"/>
+          <t>Micaele Cordeiro</t>
+        </is>
+      </c>
+      <c r="H994" t="inlineStr">
+        <is>
+          <t>Sara Cavalheiro</t>
+        </is>
+      </c>
       <c r="I994" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J994" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="K994" t="n">
-        <v>4</v>
+        <v>96</v>
       </c>
     </row>
     <row r="995">
@@ -50446,22 +50446,22 @@
       </c>
       <c r="G995" t="inlineStr">
         <is>
-          <t>Murilo Marques</t>
+          <t>Michele Silva</t>
         </is>
       </c>
       <c r="H995" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I995" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J995" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K995" t="n">
-        <v>42</v>
+        <v>80</v>
       </c>
     </row>
     <row r="996">
@@ -50497,22 +50497,18 @@
       </c>
       <c r="G996" t="inlineStr">
         <is>
-          <t>Natalia Batista</t>
-        </is>
-      </c>
-      <c r="H996" t="inlineStr">
-        <is>
-          <t>Edivaldo Veiga</t>
-        </is>
-      </c>
+          <t>Mikael Teixeira</t>
+        </is>
+      </c>
+      <c r="H996" t="inlineStr"/>
       <c r="I996" t="n">
         <v>0</v>
       </c>
       <c r="J996" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="K996" t="n">
-        <v>110</v>
+        <v>4</v>
       </c>
     </row>
     <row r="997">
@@ -50548,7 +50544,7 @@
       </c>
       <c r="G997" t="inlineStr">
         <is>
-          <t>Natalia Silva</t>
+          <t>Murilo Marques</t>
         </is>
       </c>
       <c r="H997" t="inlineStr">
@@ -50560,10 +50556,10 @@
         <v>0</v>
       </c>
       <c r="J997" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K997" t="n">
-        <v>107</v>
+        <v>42</v>
       </c>
     </row>
     <row r="998">
@@ -50599,22 +50595,22 @@
       </c>
       <c r="G998" t="inlineStr">
         <is>
-          <t>Oliene Mariano</t>
+          <t>Natalia Batista</t>
         </is>
       </c>
       <c r="H998" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I998" t="n">
         <v>0</v>
       </c>
       <c r="J998" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="K998" t="n">
-        <v>75</v>
+        <v>110</v>
       </c>
     </row>
     <row r="999">
@@ -50650,19 +50646,19 @@
       </c>
       <c r="G999" t="inlineStr">
         <is>
-          <t>Priscila Aguiar</t>
+          <t>Natalia Silva</t>
         </is>
       </c>
       <c r="H999" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I999" t="n">
         <v>0</v>
       </c>
       <c r="J999" t="n">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="K999" t="n">
         <v>107</v>
@@ -50701,22 +50697,22 @@
       </c>
       <c r="G1000" t="inlineStr">
         <is>
-          <t>Rebeca Ribeiro</t>
+          <t>Oliene Mariano</t>
         </is>
       </c>
       <c r="H1000" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I1000" t="n">
         <v>0</v>
       </c>
       <c r="J1000" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K1000" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
     </row>
     <row r="1001">
@@ -50752,7 +50748,7 @@
       </c>
       <c r="G1001" t="inlineStr">
         <is>
-          <t>Roberta Souza</t>
+          <t>Priscila Aguiar</t>
         </is>
       </c>
       <c r="H1001" t="inlineStr">
@@ -50761,13 +50757,13 @@
         </is>
       </c>
       <c r="I1001" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J1001" t="n">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="K1001" t="n">
-        <v>94</v>
+        <v>112</v>
       </c>
     </row>
     <row r="1002">
@@ -50803,7 +50799,7 @@
       </c>
       <c r="G1002" t="inlineStr">
         <is>
-          <t>Ronildo Santos</t>
+          <t>Rebeca Ribeiro</t>
         </is>
       </c>
       <c r="H1002" t="inlineStr">
@@ -50815,10 +50811,10 @@
         <v>0</v>
       </c>
       <c r="J1002" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K1002" t="n">
-        <v>6</v>
+        <v>66</v>
       </c>
     </row>
     <row r="1003">
@@ -50854,22 +50850,22 @@
       </c>
       <c r="G1003" t="inlineStr">
         <is>
-          <t>Rozania Santos</t>
+          <t>Roberta Souza</t>
         </is>
       </c>
       <c r="H1003" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I1003" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J1003" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="K1003" t="n">
-        <v>123</v>
+        <v>99</v>
       </c>
     </row>
     <row r="1004">
@@ -50905,22 +50901,22 @@
       </c>
       <c r="G1004" t="inlineStr">
         <is>
-          <t>Santos Karina</t>
+          <t>Ronildo Santos</t>
         </is>
       </c>
       <c r="H1004" t="inlineStr">
         <is>
-          <t>Leandro Matos</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I1004" t="n">
         <v>0</v>
       </c>
       <c r="J1004" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K1004" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1005">
@@ -50956,7 +50952,7 @@
       </c>
       <c r="G1005" t="inlineStr">
         <is>
-          <t>Sibelly Pereira</t>
+          <t>Rozania Santos</t>
         </is>
       </c>
       <c r="H1005" t="inlineStr">
@@ -50965,13 +50961,13 @@
         </is>
       </c>
       <c r="I1005" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J1005" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="K1005" t="n">
-        <v>64</v>
+        <v>126</v>
       </c>
     </row>
     <row r="1006">
@@ -51007,22 +51003,22 @@
       </c>
       <c r="G1006" t="inlineStr">
         <is>
-          <t>Tania Luz</t>
+          <t>Santos Karina</t>
         </is>
       </c>
       <c r="H1006" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>Leandro Matos</t>
         </is>
       </c>
       <c r="I1006" t="n">
         <v>0</v>
       </c>
       <c r="J1006" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K1006" t="n">
-        <v>72</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1007">
@@ -51058,7 +51054,7 @@
       </c>
       <c r="G1007" t="inlineStr">
         <is>
-          <t>Vitor Guedes</t>
+          <t>Sibelly Pereira</t>
         </is>
       </c>
       <c r="H1007" t="inlineStr">
@@ -51067,13 +51063,13 @@
         </is>
       </c>
       <c r="I1007" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J1007" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="K1007" t="n">
-        <v>134</v>
+        <v>69</v>
       </c>
     </row>
     <row r="1008">
@@ -51104,27 +51100,27 @@
       </c>
       <c r="F1008" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="G1008" t="inlineStr">
         <is>
-          <t>Andrea Medeiros</t>
+          <t>Tania Luz</t>
         </is>
       </c>
       <c r="H1008" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I1008" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J1008" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K1008" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="1009">
@@ -51155,27 +51151,27 @@
       </c>
       <c r="F1009" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="G1009" t="inlineStr">
         <is>
-          <t>Caroline Nascimento</t>
+          <t>Vitor Guedes</t>
         </is>
       </c>
       <c r="H1009" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I1009" t="n">
         <v>0</v>
       </c>
       <c r="J1009" t="n">
-        <v>88</v>
+        <v>5</v>
       </c>
       <c r="K1009" t="n">
-        <v>141</v>
+        <v>134</v>
       </c>
     </row>
     <row r="1010">
@@ -51211,7 +51207,7 @@
       </c>
       <c r="G1010" t="inlineStr">
         <is>
-          <t>Cristiana Grizostomo</t>
+          <t>Andrea Medeiros</t>
         </is>
       </c>
       <c r="H1010" t="inlineStr">
@@ -51223,10 +51219,10 @@
         <v>0</v>
       </c>
       <c r="J1010" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K1010" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="1011">
@@ -51262,18 +51258,22 @@
       </c>
       <c r="G1011" t="inlineStr">
         <is>
-          <t>Denis Reis</t>
-        </is>
-      </c>
-      <c r="H1011" t="inlineStr"/>
+          <t>Caroline Nascimento</t>
+        </is>
+      </c>
+      <c r="H1011" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
       <c r="I1011" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1011" t="n">
-        <v>22</v>
+        <v>89</v>
       </c>
       <c r="K1011" t="n">
-        <v>89</v>
+        <v>142</v>
       </c>
     </row>
     <row r="1012">
@@ -51309,7 +51309,7 @@
       </c>
       <c r="G1012" t="inlineStr">
         <is>
-          <t>Eliane Moreira</t>
+          <t>Cristiana Grizostomo</t>
         </is>
       </c>
       <c r="H1012" t="inlineStr">
@@ -51321,10 +51321,10 @@
         <v>0</v>
       </c>
       <c r="J1012" t="n">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="K1012" t="n">
-        <v>122</v>
+        <v>55</v>
       </c>
     </row>
     <row r="1013">
@@ -51360,22 +51360,18 @@
       </c>
       <c r="G1013" t="inlineStr">
         <is>
-          <t>Gustavo Tonan</t>
-        </is>
-      </c>
-      <c r="H1013" t="inlineStr">
-        <is>
-          <t>Nayara Oliveira</t>
-        </is>
-      </c>
+          <t>Denis Reis</t>
+        </is>
+      </c>
+      <c r="H1013" t="inlineStr"/>
       <c r="I1013" t="n">
         <v>0</v>
       </c>
       <c r="J1013" t="n">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="K1013" t="n">
-        <v>97</v>
+        <v>89</v>
       </c>
     </row>
     <row r="1014">
@@ -51411,7 +51407,7 @@
       </c>
       <c r="G1014" t="inlineStr">
         <is>
-          <t>Jonatan Hayashibara</t>
+          <t>Eliane Moreira</t>
         </is>
       </c>
       <c r="H1014" t="inlineStr">
@@ -51420,13 +51416,13 @@
         </is>
       </c>
       <c r="I1014" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J1014" t="n">
-        <v>279</v>
+        <v>64</v>
       </c>
       <c r="K1014" t="n">
-        <v>391</v>
+        <v>127</v>
       </c>
     </row>
     <row r="1015">
@@ -51462,7 +51458,7 @@
       </c>
       <c r="G1015" t="inlineStr">
         <is>
-          <t>Lais Arruda</t>
+          <t>Gustavo Tonan</t>
         </is>
       </c>
       <c r="H1015" t="inlineStr">
@@ -51474,10 +51470,10 @@
         <v>0</v>
       </c>
       <c r="J1015" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K1015" t="n">
-        <v>105</v>
+        <v>97</v>
       </c>
     </row>
     <row r="1016">
@@ -51513,7 +51509,7 @@
       </c>
       <c r="G1016" t="inlineStr">
         <is>
-          <t>Luan Batista</t>
+          <t>Jonatan Hayashibara</t>
         </is>
       </c>
       <c r="H1016" t="inlineStr">
@@ -51522,13 +51518,13 @@
         </is>
       </c>
       <c r="I1016" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="J1016" t="n">
-        <v>31</v>
+        <v>320</v>
       </c>
       <c r="K1016" t="n">
-        <v>69</v>
+        <v>432</v>
       </c>
     </row>
     <row r="1017">
@@ -51564,7 +51560,7 @@
       </c>
       <c r="G1017" t="inlineStr">
         <is>
-          <t>Maria Garcia</t>
+          <t>Lais Arruda</t>
         </is>
       </c>
       <c r="H1017" t="inlineStr">
@@ -51573,13 +51569,13 @@
         </is>
       </c>
       <c r="I1017" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1017" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="K1017" t="n">
-        <v>71</v>
+        <v>108</v>
       </c>
     </row>
     <row r="1018">
@@ -51615,7 +51611,7 @@
       </c>
       <c r="G1018" t="inlineStr">
         <is>
-          <t>Priscila Volpe</t>
+          <t>Luan Batista</t>
         </is>
       </c>
       <c r="H1018" t="inlineStr">
@@ -51624,13 +51620,13 @@
         </is>
       </c>
       <c r="I1018" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J1018" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="K1018" t="n">
-        <v>11</v>
+        <v>75</v>
       </c>
     </row>
     <row r="1019">
@@ -51666,7 +51662,7 @@
       </c>
       <c r="G1019" t="inlineStr">
         <is>
-          <t>Rodrigo Souza</t>
+          <t>Maria Garcia</t>
         </is>
       </c>
       <c r="H1019" t="inlineStr">
@@ -51678,10 +51674,10 @@
         <v>0</v>
       </c>
       <c r="J1019" t="n">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="K1019" t="n">
-        <v>83</v>
+        <v>72</v>
       </c>
     </row>
     <row r="1020">
@@ -51717,7 +51713,7 @@
       </c>
       <c r="G1020" t="inlineStr">
         <is>
-          <t>Romario Silva</t>
+          <t>Priscila Volpe</t>
         </is>
       </c>
       <c r="H1020" t="inlineStr">
@@ -51729,10 +51725,10 @@
         <v>0</v>
       </c>
       <c r="J1020" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="K1020" t="n">
-        <v>200</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1021">
@@ -51768,7 +51764,7 @@
       </c>
       <c r="G1021" t="inlineStr">
         <is>
-          <t>Rosilene Santos</t>
+          <t>Rodrigo Souza</t>
         </is>
       </c>
       <c r="H1021" t="inlineStr">
@@ -51780,10 +51776,10 @@
         <v>0</v>
       </c>
       <c r="J1021" t="n">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="K1021" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="1022">
@@ -51819,7 +51815,7 @@
       </c>
       <c r="G1022" t="inlineStr">
         <is>
-          <t>Suede Gomes</t>
+          <t>Romario Silva</t>
         </is>
       </c>
       <c r="H1022" t="inlineStr">
@@ -51828,13 +51824,13 @@
         </is>
       </c>
       <c r="I1022" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J1022" t="n">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="K1022" t="n">
-        <v>42</v>
+        <v>219</v>
       </c>
     </row>
     <row r="1023">
@@ -51870,7 +51866,7 @@
       </c>
       <c r="G1023" t="inlineStr">
         <is>
-          <t>Taina Silva</t>
+          <t>Rosilene Santos</t>
         </is>
       </c>
       <c r="H1023" t="inlineStr">
@@ -51885,7 +51881,7 @@
         <v>45</v>
       </c>
       <c r="K1023" t="n">
-        <v>61</v>
+        <v>80</v>
       </c>
     </row>
     <row r="1024">
@@ -51921,7 +51917,7 @@
       </c>
       <c r="G1024" t="inlineStr">
         <is>
-          <t>Thayna Melo</t>
+          <t>Suede Gomes</t>
         </is>
       </c>
       <c r="H1024" t="inlineStr">
@@ -51930,13 +51926,13 @@
         </is>
       </c>
       <c r="I1024" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1024" t="n">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="K1024" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
     </row>
     <row r="1025">
@@ -51972,7 +51968,7 @@
       </c>
       <c r="G1025" t="inlineStr">
         <is>
-          <t>Vanessa Santana</t>
+          <t>Taina Silva</t>
         </is>
       </c>
       <c r="H1025" t="inlineStr">
@@ -51981,13 +51977,13 @@
         </is>
       </c>
       <c r="I1025" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1025" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="K1025" t="n">
-        <v>168</v>
+        <v>63</v>
       </c>
     </row>
     <row r="1026">
@@ -52018,27 +52014,27 @@
       </c>
       <c r="F1026" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="G1026" t="inlineStr">
         <is>
-          <t>Alaine Neres</t>
+          <t>Thayna Melo</t>
         </is>
       </c>
       <c r="H1026" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
       <c r="I1026" t="n">
         <v>0</v>
       </c>
       <c r="J1026" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="K1026" t="n">
-        <v>93</v>
+        <v>51</v>
       </c>
     </row>
     <row r="1027">
@@ -52069,27 +52065,27 @@
       </c>
       <c r="F1027" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="G1027" t="inlineStr">
         <is>
-          <t>Andre Silva</t>
+          <t>Vanessa Santana</t>
         </is>
       </c>
       <c r="H1027" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
       <c r="I1027" t="n">
         <v>0</v>
       </c>
       <c r="J1027" t="n">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="K1027" t="n">
-        <v>64</v>
+        <v>168</v>
       </c>
     </row>
     <row r="1028">
@@ -52125,22 +52121,22 @@
       </c>
       <c r="G1028" t="inlineStr">
         <is>
-          <t>Anna Ramalho</t>
+          <t>Alaine Neres</t>
         </is>
       </c>
       <c r="H1028" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I1028" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="J1028" t="n">
-        <v>17</v>
+        <v>87</v>
       </c>
       <c r="K1028" t="n">
-        <v>73</v>
+        <v>144</v>
       </c>
     </row>
     <row r="1029">
@@ -52176,22 +52172,22 @@
       </c>
       <c r="G1029" t="inlineStr">
         <is>
-          <t>Beatriz Ferreira</t>
+          <t>Andre Silva</t>
         </is>
       </c>
       <c r="H1029" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I1029" t="n">
         <v>0</v>
       </c>
       <c r="J1029" t="n">
-        <v>61</v>
+        <v>7</v>
       </c>
       <c r="K1029" t="n">
-        <v>103</v>
+        <v>64</v>
       </c>
     </row>
     <row r="1030">
@@ -52227,22 +52223,22 @@
       </c>
       <c r="G1030" t="inlineStr">
         <is>
-          <t>Brenda Batista</t>
+          <t>Anna Ramalho</t>
         </is>
       </c>
       <c r="H1030" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="I1030" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1030" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="K1030" t="n">
-        <v>53</v>
+        <v>74</v>
       </c>
     </row>
     <row r="1031">
@@ -52278,22 +52274,22 @@
       </c>
       <c r="G1031" t="inlineStr">
         <is>
-          <t>Bruna Souza</t>
+          <t>Beatriz Ferreira</t>
         </is>
       </c>
       <c r="H1031" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="I1031" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J1031" t="n">
-        <v>28</v>
+        <v>71</v>
       </c>
       <c r="K1031" t="n">
-        <v>75</v>
+        <v>113</v>
       </c>
     </row>
     <row r="1032">
@@ -52329,22 +52325,22 @@
       </c>
       <c r="G1032" t="inlineStr">
         <is>
-          <t>Bruno Henrique</t>
+          <t>Brenda Batista</t>
         </is>
       </c>
       <c r="H1032" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I1032" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1032" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="K1032" t="n">
-        <v>104</v>
+        <v>54</v>
       </c>
     </row>
     <row r="1033">
@@ -52380,18 +52376,22 @@
       </c>
       <c r="G1033" t="inlineStr">
         <is>
-          <t>Claudineia Rodrigues</t>
-        </is>
-      </c>
-      <c r="H1033" t="inlineStr"/>
+          <t>Bruna Souza</t>
+        </is>
+      </c>
+      <c r="H1033" t="inlineStr">
+        <is>
+          <t>Thaiza Oliveira</t>
+        </is>
+      </c>
       <c r="I1033" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1033" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K1033" t="n">
-        <v>140</v>
+        <v>76</v>
       </c>
     </row>
     <row r="1034">
@@ -52427,22 +52427,22 @@
       </c>
       <c r="G1034" t="inlineStr">
         <is>
-          <t>Cristina Leite</t>
+          <t>Bruno Henrique</t>
         </is>
       </c>
       <c r="H1034" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I1034" t="n">
         <v>0</v>
       </c>
       <c r="J1034" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="K1034" t="n">
-        <v>130</v>
+        <v>104</v>
       </c>
     </row>
     <row r="1035">
@@ -52478,22 +52478,18 @@
       </c>
       <c r="G1035" t="inlineStr">
         <is>
-          <t>Davi Santos</t>
-        </is>
-      </c>
-      <c r="H1035" t="inlineStr">
-        <is>
-          <t>Thaiza Oliveira</t>
-        </is>
-      </c>
+          <t>Claudineia Rodrigues</t>
+        </is>
+      </c>
+      <c r="H1035" t="inlineStr"/>
       <c r="I1035" t="n">
         <v>0</v>
       </c>
       <c r="J1035" t="n">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="K1035" t="n">
-        <v>92</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1036">
@@ -52529,22 +52525,22 @@
       </c>
       <c r="G1036" t="inlineStr">
         <is>
-          <t>Deleia Oliveira</t>
+          <t>Cristina Leite</t>
         </is>
       </c>
       <c r="H1036" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="I1036" t="n">
         <v>0</v>
       </c>
       <c r="J1036" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="K1036" t="n">
-        <v>83</v>
+        <v>130</v>
       </c>
     </row>
     <row r="1037">
@@ -52580,7 +52576,7 @@
       </c>
       <c r="G1037" t="inlineStr">
         <is>
-          <t>Diego Pereira</t>
+          <t>Davi Santos</t>
         </is>
       </c>
       <c r="H1037" t="inlineStr">
@@ -52589,13 +52585,13 @@
         </is>
       </c>
       <c r="I1037" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1037" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="K1037" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
     </row>
     <row r="1038">
@@ -52631,22 +52627,22 @@
       </c>
       <c r="G1038" t="inlineStr">
         <is>
-          <t>Eduardo Lopes</t>
+          <t>Deleia Oliveira</t>
         </is>
       </c>
       <c r="H1038" t="inlineStr">
         <is>
-          <t>Idna Sousa</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I1038" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J1038" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="K1038" t="n">
-        <v>16</v>
+        <v>92</v>
       </c>
     </row>
     <row r="1039">
@@ -52682,22 +52678,22 @@
       </c>
       <c r="G1039" t="inlineStr">
         <is>
-          <t>Gislaine Lima</t>
+          <t>Diego Pereira</t>
         </is>
       </c>
       <c r="H1039" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I1039" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="J1039" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K1039" t="n">
-        <v>83</v>
+        <v>93</v>
       </c>
     </row>
     <row r="1040">
@@ -52733,22 +52729,22 @@
       </c>
       <c r="G1040" t="inlineStr">
         <is>
-          <t>Gustavo Santos</t>
+          <t>Eduardo Lopes</t>
         </is>
       </c>
       <c r="H1040" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Idna Sousa</t>
         </is>
       </c>
       <c r="I1040" t="n">
         <v>0</v>
       </c>
       <c r="J1040" t="n">
-        <v>75</v>
+        <v>3</v>
       </c>
       <c r="K1040" t="n">
-        <v>186</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1041">
@@ -52784,22 +52780,22 @@
       </c>
       <c r="G1041" t="inlineStr">
         <is>
-          <t>Igor Valezi</t>
+          <t>Gislaine Lima</t>
         </is>
       </c>
       <c r="H1041" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I1041" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J1041" t="n">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="K1041" t="n">
-        <v>74</v>
+        <v>89</v>
       </c>
     </row>
     <row r="1042">
@@ -52835,22 +52831,22 @@
       </c>
       <c r="G1042" t="inlineStr">
         <is>
-          <t>Izabely Araujo</t>
+          <t>Gustavo Santos</t>
         </is>
       </c>
       <c r="H1042" t="inlineStr">
         <is>
-          <t>Idna Sousa</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="I1042" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="J1042" t="n">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="K1042" t="n">
-        <v>7</v>
+        <v>217</v>
       </c>
     </row>
     <row r="1043">
@@ -52886,22 +52882,22 @@
       </c>
       <c r="G1043" t="inlineStr">
         <is>
-          <t>Joanna Costa</t>
+          <t>Igor Valezi</t>
         </is>
       </c>
       <c r="H1043" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I1043" t="n">
         <v>0</v>
       </c>
       <c r="J1043" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="K1043" t="n">
-        <v>19</v>
+        <v>74</v>
       </c>
     </row>
     <row r="1044">
@@ -52937,22 +52933,22 @@
       </c>
       <c r="G1044" t="inlineStr">
         <is>
-          <t>Jose Natan</t>
+          <t>Izabely Araujo</t>
         </is>
       </c>
       <c r="H1044" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Idna Sousa</t>
         </is>
       </c>
       <c r="I1044" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1044" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="K1044" t="n">
-        <v>98</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1045">
@@ -52988,22 +52984,22 @@
       </c>
       <c r="G1045" t="inlineStr">
         <is>
-          <t>João Oliveira</t>
+          <t>Joanna Costa</t>
         </is>
       </c>
       <c r="H1045" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I1045" t="n">
         <v>0</v>
       </c>
       <c r="J1045" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K1045" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1046">
@@ -53039,22 +53035,22 @@
       </c>
       <c r="G1046" t="inlineStr">
         <is>
-          <t>Juan Ribeiro</t>
+          <t>Jose Borges</t>
         </is>
       </c>
       <c r="H1046" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="I1046" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1046" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K1046" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1047">
@@ -53090,7 +53086,7 @@
       </c>
       <c r="G1047" t="inlineStr">
         <is>
-          <t>Juliana Valeria</t>
+          <t>Jose Natan</t>
         </is>
       </c>
       <c r="H1047" t="inlineStr">
@@ -53102,10 +53098,10 @@
         <v>0</v>
       </c>
       <c r="J1047" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K1047" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="1048">
@@ -53141,7 +53137,7 @@
       </c>
       <c r="G1048" t="inlineStr">
         <is>
-          <t>Juliane Vaz</t>
+          <t>João Oliveira</t>
         </is>
       </c>
       <c r="H1048" t="inlineStr">
@@ -53150,13 +53146,13 @@
         </is>
       </c>
       <c r="I1048" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1048" t="n">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="K1048" t="n">
-        <v>195</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1049">
@@ -53192,22 +53188,22 @@
       </c>
       <c r="G1049" t="inlineStr">
         <is>
-          <t>Katia Xavier</t>
+          <t>Juan Ribeiro</t>
         </is>
       </c>
       <c r="H1049" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I1049" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1049" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="K1049" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="1050">
@@ -53243,22 +53239,22 @@
       </c>
       <c r="G1050" t="inlineStr">
         <is>
-          <t>Larissa Félix</t>
+          <t>Juliana Valeria</t>
         </is>
       </c>
       <c r="H1050" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I1050" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1050" t="n">
-        <v>96</v>
+        <v>36</v>
       </c>
       <c r="K1050" t="n">
-        <v>159</v>
+        <v>98</v>
       </c>
     </row>
     <row r="1051">
@@ -53294,22 +53290,22 @@
       </c>
       <c r="G1051" t="inlineStr">
         <is>
-          <t>Léia de Oliveira</t>
+          <t>Juliane Vaz</t>
         </is>
       </c>
       <c r="H1051" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I1051" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1051" t="n">
-        <v>20</v>
+        <v>95</v>
       </c>
       <c r="K1051" t="n">
-        <v>107</v>
+        <v>195</v>
       </c>
     </row>
     <row r="1052">
@@ -53345,7 +53341,7 @@
       </c>
       <c r="G1052" t="inlineStr">
         <is>
-          <t>Maria Gualberto</t>
+          <t>Katia Xavier</t>
         </is>
       </c>
       <c r="H1052" t="inlineStr">
@@ -53354,13 +53350,13 @@
         </is>
       </c>
       <c r="I1052" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J1052" t="n">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="K1052" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="1053">
@@ -53396,22 +53392,22 @@
       </c>
       <c r="G1053" t="inlineStr">
         <is>
-          <t>Priscila Moreira</t>
+          <t>Larissa Félix</t>
         </is>
       </c>
       <c r="H1053" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I1053" t="n">
         <v>0</v>
       </c>
       <c r="J1053" t="n">
-        <v>15</v>
+        <v>96</v>
       </c>
       <c r="K1053" t="n">
-        <v>82</v>
+        <v>159</v>
       </c>
     </row>
     <row r="1054">
@@ -53447,22 +53443,22 @@
       </c>
       <c r="G1054" t="inlineStr">
         <is>
-          <t>Regiane Santos</t>
+          <t>Léia de Oliveira</t>
         </is>
       </c>
       <c r="H1054" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I1054" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J1054" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="K1054" t="n">
-        <v>52</v>
+        <v>113</v>
       </c>
     </row>
     <row r="1055">
@@ -53498,22 +53494,22 @@
       </c>
       <c r="G1055" t="inlineStr">
         <is>
-          <t>Shofia Gomes</t>
+          <t>Maria Gualberto</t>
         </is>
       </c>
       <c r="H1055" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I1055" t="n">
         <v>0</v>
       </c>
       <c r="J1055" t="n">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="K1055" t="n">
-        <v>120</v>
+        <v>96</v>
       </c>
     </row>
     <row r="1056">
@@ -53549,22 +53545,22 @@
       </c>
       <c r="G1056" t="inlineStr">
         <is>
-          <t>Vanessa Tavares</t>
+          <t>Nathany Silva</t>
         </is>
       </c>
       <c r="H1056" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I1056" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1056" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K1056" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1057">
@@ -53600,22 +53596,22 @@
       </c>
       <c r="G1057" t="inlineStr">
         <is>
-          <t>Willian Luz</t>
+          <t>Priscila Moreira</t>
         </is>
       </c>
       <c r="H1057" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="I1057" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="J1057" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K1057" t="n">
-        <v>67</v>
+        <v>84</v>
       </c>
     </row>
     <row r="1058">
@@ -53651,7 +53647,7 @@
       </c>
       <c r="G1058" t="inlineStr">
         <is>
-          <t>Yasmim Oliveira</t>
+          <t>Regiane Santos</t>
         </is>
       </c>
       <c r="H1058" t="inlineStr">
@@ -53660,13 +53656,13 @@
         </is>
       </c>
       <c r="I1058" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J1058" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K1058" t="n">
-        <v>34</v>
+        <v>57</v>
       </c>
     </row>
     <row r="1059">
@@ -53697,23 +53693,27 @@
       </c>
       <c r="F1059" t="inlineStr">
         <is>
-          <t>ESCRITA FISCAL (Outsourcing)</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="G1059" t="inlineStr">
         <is>
-          <t>Claudineia Rodrigues</t>
-        </is>
-      </c>
-      <c r="H1059" t="inlineStr"/>
+          <t>Shofia Gomes</t>
+        </is>
+      </c>
+      <c r="H1059" t="inlineStr">
+        <is>
+          <t>Ricardo Fischer</t>
+        </is>
+      </c>
       <c r="I1059" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1059" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K1059" t="n">
-        <v>4</v>
+        <v>121</v>
       </c>
     </row>
     <row r="1060">
@@ -53744,27 +53744,27 @@
       </c>
       <c r="F1060" t="inlineStr">
         <is>
-          <t>ESCRITA FISCAL (Outsourcing)</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="G1060" t="inlineStr">
         <is>
-          <t>Diego Pereira</t>
+          <t>Vanessa Tavares</t>
         </is>
       </c>
       <c r="H1060" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I1060" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J1060" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="K1060" t="n">
-        <v>6</v>
+        <v>65</v>
       </c>
     </row>
     <row r="1061">
@@ -53795,27 +53795,27 @@
       </c>
       <c r="F1061" t="inlineStr">
         <is>
-          <t>ESCRITA FISCAL (Outsourcing)</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="G1061" t="inlineStr">
         <is>
-          <t>Gislaine Lima</t>
+          <t>Willian Luz</t>
         </is>
       </c>
       <c r="H1061" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I1061" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J1061" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="K1061" t="n">
-        <v>32</v>
+        <v>71</v>
       </c>
     </row>
     <row r="1062">
@@ -53846,24 +53846,24 @@
       </c>
       <c r="F1062" t="inlineStr">
         <is>
-          <t>ESCRITA FISCAL (Outsourcing)</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="G1062" t="inlineStr">
         <is>
-          <t>Joanna Costa</t>
+          <t>Yasmim Oliveira</t>
         </is>
       </c>
       <c r="H1062" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I1062" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J1062" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="K1062" t="n">
         <v>40</v>
@@ -53902,22 +53902,18 @@
       </c>
       <c r="G1063" t="inlineStr">
         <is>
-          <t>Jonatan Hayashibara</t>
-        </is>
-      </c>
-      <c r="H1063" t="inlineStr">
-        <is>
-          <t>Nayara Oliveira</t>
-        </is>
-      </c>
+          <t>Claudineia Rodrigues</t>
+        </is>
+      </c>
+      <c r="H1063" t="inlineStr"/>
       <c r="I1063" t="n">
         <v>0</v>
       </c>
       <c r="J1063" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K1063" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1064">
@@ -53953,22 +53949,22 @@
       </c>
       <c r="G1064" t="inlineStr">
         <is>
-          <t>João Oliveira</t>
+          <t>Diego Pereira</t>
         </is>
       </c>
       <c r="H1064" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I1064" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1064" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="K1064" t="n">
-        <v>42</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1065">
@@ -54004,22 +54000,22 @@
       </c>
       <c r="G1065" t="inlineStr">
         <is>
-          <t>Regiane Santos</t>
+          <t>Gislaine Lima</t>
         </is>
       </c>
       <c r="H1065" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I1065" t="n">
         <v>0</v>
       </c>
       <c r="J1065" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K1065" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
     </row>
     <row r="1066">
@@ -54055,22 +54051,22 @@
       </c>
       <c r="G1066" t="inlineStr">
         <is>
-          <t>Yasmim Oliveira</t>
+          <t>Joanna Costa</t>
         </is>
       </c>
       <c r="H1066" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I1066" t="n">
         <v>0</v>
       </c>
       <c r="J1066" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="K1066" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="1067">
@@ -54101,23 +54097,27 @@
       </c>
       <c r="F1067" t="inlineStr">
         <is>
-          <t>FIN - CONTÁBIL</t>
+          <t>ESCRITA FISCAL (Outsourcing)</t>
         </is>
       </c>
       <c r="G1067" t="inlineStr">
         <is>
-          <t>Daniele Faria</t>
-        </is>
-      </c>
-      <c r="H1067" t="inlineStr"/>
+          <t>Jonatan Hayashibara</t>
+        </is>
+      </c>
+      <c r="H1067" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
       <c r="I1067" t="n">
         <v>0</v>
       </c>
       <c r="J1067" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="K1067" t="n">
-        <v>62</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1068">
@@ -54148,23 +54148,27 @@
       </c>
       <c r="F1068" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>ESCRITA FISCAL (Outsourcing)</t>
         </is>
       </c>
       <c r="G1068" t="inlineStr">
         <is>
-          <t>Ana Santana</t>
-        </is>
-      </c>
-      <c r="H1068" t="inlineStr"/>
+          <t>Jose Borges</t>
+        </is>
+      </c>
+      <c r="H1068" t="inlineStr">
+        <is>
+          <t>Ricardo Fischer</t>
+        </is>
+      </c>
       <c r="I1068" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1068" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K1068" t="n">
-        <v>401</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1069">
@@ -54195,23 +54199,27 @@
       </c>
       <c r="F1069" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>ESCRITA FISCAL (Outsourcing)</t>
         </is>
       </c>
       <c r="G1069" t="inlineStr">
         <is>
-          <t>Andre Coelho</t>
-        </is>
-      </c>
-      <c r="H1069" t="inlineStr"/>
+          <t>João Oliveira</t>
+        </is>
+      </c>
+      <c r="H1069" t="inlineStr">
+        <is>
+          <t>Larice Souza</t>
+        </is>
+      </c>
       <c r="I1069" t="n">
         <v>0</v>
       </c>
       <c r="J1069" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K1069" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1070">
@@ -54242,23 +54250,27 @@
       </c>
       <c r="F1070" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>ESCRITA FISCAL (Outsourcing)</t>
         </is>
       </c>
       <c r="G1070" t="inlineStr">
         <is>
-          <t>Bianca Castro</t>
-        </is>
-      </c>
-      <c r="H1070" t="inlineStr"/>
+          <t>Regiane Santos</t>
+        </is>
+      </c>
+      <c r="H1070" t="inlineStr">
+        <is>
+          <t>Larice Souza</t>
+        </is>
+      </c>
       <c r="I1070" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1070" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="K1070" t="n">
-        <v>327</v>
+        <v>15</v>
       </c>
     </row>
     <row r="1071">
@@ -54289,15 +54301,19 @@
       </c>
       <c r="F1071" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>ESCRITA FISCAL (Outsourcing)</t>
         </is>
       </c>
       <c r="G1071" t="inlineStr">
         <is>
-          <t>Bruna Costa</t>
-        </is>
-      </c>
-      <c r="H1071" t="inlineStr"/>
+          <t>Yasmim Oliveira</t>
+        </is>
+      </c>
+      <c r="H1071" t="inlineStr">
+        <is>
+          <t>Larice Souza</t>
+        </is>
+      </c>
       <c r="I1071" t="n">
         <v>0</v>
       </c>
@@ -54305,7 +54321,7 @@
         <v>1</v>
       </c>
       <c r="K1071" t="n">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1072">
@@ -54336,12 +54352,12 @@
       </c>
       <c r="F1072" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>FIN - CONTÁBIL</t>
         </is>
       </c>
       <c r="G1072" t="inlineStr">
         <is>
-          <t>Daniela Silva</t>
+          <t>Daniele Faria</t>
         </is>
       </c>
       <c r="H1072" t="inlineStr"/>
@@ -54349,10 +54365,10 @@
         <v>0</v>
       </c>
       <c r="J1072" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K1072" t="n">
-        <v>11</v>
+        <v>62</v>
       </c>
     </row>
     <row r="1073">
@@ -54388,18 +54404,18 @@
       </c>
       <c r="G1073" t="inlineStr">
         <is>
-          <t>Isabelli Afonso</t>
+          <t>Ana Santana</t>
         </is>
       </c>
       <c r="H1073" t="inlineStr"/>
       <c r="I1073" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="J1073" t="n">
-        <v>7</v>
+        <v>65</v>
       </c>
       <c r="K1073" t="n">
-        <v>29</v>
+        <v>418</v>
       </c>
     </row>
     <row r="1074">
@@ -54435,18 +54451,18 @@
       </c>
       <c r="G1074" t="inlineStr">
         <is>
-          <t>Jurema Damacena - SAC</t>
+          <t>Andre Coelho</t>
         </is>
       </c>
       <c r="H1074" t="inlineStr"/>
       <c r="I1074" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J1074" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K1074" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1075">
@@ -54482,18 +54498,18 @@
       </c>
       <c r="G1075" t="inlineStr">
         <is>
-          <t>Leticia Queiroz</t>
+          <t>Bianca Castro</t>
         </is>
       </c>
       <c r="H1075" t="inlineStr"/>
       <c r="I1075" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="J1075" t="n">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="K1075" t="n">
-        <v>48</v>
+        <v>338</v>
       </c>
     </row>
     <row r="1076">
@@ -54529,18 +54545,18 @@
       </c>
       <c r="G1076" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Bruna Costa</t>
         </is>
       </c>
       <c r="H1076" t="inlineStr"/>
       <c r="I1076" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J1076" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K1076" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
     </row>
     <row r="1077">
@@ -54576,18 +54592,18 @@
       </c>
       <c r="G1077" t="inlineStr">
         <is>
-          <t>Victoria Virgens</t>
+          <t>Daniela Silva</t>
         </is>
       </c>
       <c r="H1077" t="inlineStr"/>
       <c r="I1077" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="J1077" t="n">
-        <v>17</v>
+        <v>93</v>
       </c>
       <c r="K1077" t="n">
-        <v>17</v>
+        <v>89</v>
       </c>
     </row>
     <row r="1078">
@@ -54623,18 +54639,18 @@
       </c>
       <c r="G1078" t="inlineStr">
         <is>
-          <t>Yasmin Peixoto</t>
+          <t>Isabelli Afonso</t>
         </is>
       </c>
       <c r="H1078" t="inlineStr"/>
       <c r="I1078" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J1078" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K1078" t="n">
-        <v>265</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1079">
@@ -54665,12 +54681,12 @@
       </c>
       <c r="F1079" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="G1079" t="inlineStr">
         <is>
-          <t>Andre Coelho</t>
+          <t>Jurema Damacena - SAC</t>
         </is>
       </c>
       <c r="H1079" t="inlineStr"/>
@@ -54681,7 +54697,7 @@
         <v>0</v>
       </c>
       <c r="K1079" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1080">
@@ -54712,23 +54728,23 @@
       </c>
       <c r="F1080" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="G1080" t="inlineStr">
         <is>
-          <t>Beatriz Rangel</t>
+          <t>Leticia Queiroz</t>
         </is>
       </c>
       <c r="H1080" t="inlineStr"/>
       <c r="I1080" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="J1080" t="n">
-        <v>6</v>
+        <v>56</v>
       </c>
       <c r="K1080" t="n">
-        <v>266</v>
+        <v>92</v>
       </c>
     </row>
     <row r="1081">
@@ -54759,23 +54775,23 @@
       </c>
       <c r="F1081" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="G1081" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="H1081" t="inlineStr"/>
       <c r="I1081" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1081" t="n">
-        <v>139</v>
+        <v>2</v>
       </c>
       <c r="K1081" t="n">
-        <v>279</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1082">
@@ -54806,23 +54822,23 @@
       </c>
       <c r="F1082" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="G1082" t="inlineStr">
         <is>
-          <t>Cristiane Simões</t>
+          <t>Victoria Virgens</t>
         </is>
       </c>
       <c r="H1082" t="inlineStr"/>
       <c r="I1082" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="J1082" t="n">
-        <v>135</v>
+        <v>71</v>
       </c>
       <c r="K1082" t="n">
-        <v>307</v>
+        <v>71</v>
       </c>
     </row>
     <row r="1083">
@@ -54853,23 +54869,23 @@
       </c>
       <c r="F1083" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="G1083" t="inlineStr">
         <is>
-          <t>Daniel Oliveira</t>
+          <t>Yasmin Peixoto</t>
         </is>
       </c>
       <c r="H1083" t="inlineStr"/>
       <c r="I1083" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J1083" t="n">
-        <v>116</v>
+        <v>33</v>
       </c>
       <c r="K1083" t="n">
-        <v>174</v>
+        <v>276</v>
       </c>
     </row>
     <row r="1084">
@@ -54905,18 +54921,18 @@
       </c>
       <c r="G1084" t="inlineStr">
         <is>
-          <t>Diego Lima</t>
+          <t>Andre Coelho</t>
         </is>
       </c>
       <c r="H1084" t="inlineStr"/>
       <c r="I1084" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1084" t="n">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="K1084" t="n">
-        <v>114</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1085">
@@ -54952,18 +54968,18 @@
       </c>
       <c r="G1085" t="inlineStr">
         <is>
-          <t>Karine Gusmão</t>
+          <t>Beatriz Rangel</t>
         </is>
       </c>
       <c r="H1085" t="inlineStr"/>
       <c r="I1085" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J1085" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="K1085" t="n">
-        <v>6</v>
+        <v>269</v>
       </c>
     </row>
     <row r="1086">
@@ -54999,18 +55015,18 @@
       </c>
       <c r="G1086" t="inlineStr">
         <is>
-          <t>Luiz Ferreira</t>
+          <t>Bruno Contieri</t>
         </is>
       </c>
       <c r="H1086" t="inlineStr"/>
       <c r="I1086" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="J1086" t="n">
-        <v>8</v>
+        <v>216</v>
       </c>
       <c r="K1086" t="n">
-        <v>14</v>
+        <v>341</v>
       </c>
     </row>
     <row r="1087">
@@ -55046,18 +55062,18 @@
       </c>
       <c r="G1087" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Cristiane Simões</t>
         </is>
       </c>
       <c r="H1087" t="inlineStr"/>
       <c r="I1087" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1087" t="n">
-        <v>66</v>
+        <v>136</v>
       </c>
       <c r="K1087" t="n">
-        <v>150</v>
+        <v>302</v>
       </c>
     </row>
     <row r="1088">
@@ -55093,18 +55109,18 @@
       </c>
       <c r="G1088" t="inlineStr">
         <is>
-          <t>Rodrigo Rego</t>
+          <t>Daniel Oliveira</t>
         </is>
       </c>
       <c r="H1088" t="inlineStr"/>
       <c r="I1088" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J1088" t="n">
-        <v>4</v>
+        <v>135</v>
       </c>
       <c r="K1088" t="n">
-        <v>177</v>
+        <v>190</v>
       </c>
     </row>
     <row r="1089">
@@ -55140,18 +55156,18 @@
       </c>
       <c r="G1089" t="inlineStr">
         <is>
-          <t>Rogerio Egidio</t>
+          <t>Diego Lima</t>
         </is>
       </c>
       <c r="H1089" t="inlineStr"/>
       <c r="I1089" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J1089" t="n">
-        <v>114</v>
+        <v>42</v>
       </c>
       <c r="K1089" t="n">
-        <v>287</v>
+        <v>113</v>
       </c>
     </row>
     <row r="1090">
@@ -55187,18 +55203,18 @@
       </c>
       <c r="G1090" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Eduardo Aparicio</t>
         </is>
       </c>
       <c r="H1090" t="inlineStr"/>
       <c r="I1090" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1090" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1090" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1091">
@@ -55234,18 +55250,18 @@
       </c>
       <c r="G1091" t="inlineStr">
         <is>
-          <t>Simone Marques</t>
+          <t>Karine Gusmão</t>
         </is>
       </c>
       <c r="H1091" t="inlineStr"/>
       <c r="I1091" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J1091" t="n">
-        <v>69</v>
+        <v>28</v>
       </c>
       <c r="K1091" t="n">
-        <v>181</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1092">
@@ -55281,7 +55297,7 @@
       </c>
       <c r="G1092" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Luiz Ferreira</t>
         </is>
       </c>
       <c r="H1092" t="inlineStr"/>
@@ -55289,10 +55305,10 @@
         <v>0</v>
       </c>
       <c r="J1092" t="n">
-        <v>72</v>
+        <v>8</v>
       </c>
       <c r="K1092" t="n">
-        <v>188</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1093">
@@ -55323,23 +55339,23 @@
       </c>
       <c r="F1093" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="G1093" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="H1093" t="inlineStr"/>
       <c r="I1093" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="J1093" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="K1093" t="n">
-        <v>1</v>
+        <v>167</v>
       </c>
     </row>
     <row r="1094">
@@ -55370,23 +55386,23 @@
       </c>
       <c r="F1094" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="G1094" t="inlineStr">
         <is>
-          <t>Jurema Damacena - SAC</t>
+          <t>Rodrigo Rego</t>
         </is>
       </c>
       <c r="H1094" t="inlineStr"/>
       <c r="I1094" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="J1094" t="n">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="K1094" t="n">
-        <v>41</v>
+        <v>212</v>
       </c>
     </row>
     <row r="1095">
@@ -55417,23 +55433,23 @@
       </c>
       <c r="F1095" t="inlineStr">
         <is>
-          <t>S.A.C</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="G1095" t="inlineStr">
         <is>
-          <t>Ana Celia - SAC</t>
+          <t>Rogerio Egidio</t>
         </is>
       </c>
       <c r="H1095" t="inlineStr"/>
       <c r="I1095" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J1095" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="K1095" t="n">
-        <v>1</v>
+        <v>291</v>
       </c>
     </row>
     <row r="1096">
@@ -55464,27 +55480,23 @@
       </c>
       <c r="F1096" t="inlineStr">
         <is>
-          <t>SANTOS - DP</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="G1096" t="inlineStr">
         <is>
-          <t>Katia Valeria</t>
-        </is>
-      </c>
-      <c r="H1096" t="inlineStr">
-        <is>
-          <t>Katia Valeria</t>
-        </is>
-      </c>
+          <t>Sergio Fernandes</t>
+        </is>
+      </c>
+      <c r="H1096" t="inlineStr"/>
       <c r="I1096" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J1096" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="K1096" t="n">
-        <v>3</v>
+        <v>48</v>
       </c>
     </row>
     <row r="1097">
@@ -55510,28 +55522,28 @@
       </c>
       <c r="E1097" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F1097" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="G1097" t="inlineStr">
         <is>
-          <t>Jurema Damacena - SAC</t>
+          <t>Simone Marques</t>
         </is>
       </c>
       <c r="H1097" t="inlineStr"/>
       <c r="I1097" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="J1097" t="n">
-        <v>4</v>
+        <v>95</v>
       </c>
       <c r="K1097" t="n">
-        <v>4</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1098">
@@ -55557,28 +55569,28 @@
       </c>
       <c r="E1098" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F1098" t="inlineStr">
         <is>
-          <t>SANTOS - ADM</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="G1098" t="inlineStr">
         <is>
-          <t>Kauany Pereira</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="H1098" t="inlineStr"/>
       <c r="I1098" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J1098" t="n">
-        <v>32</v>
+        <v>97</v>
       </c>
       <c r="K1098" t="n">
-        <v>136</v>
+        <v>200</v>
       </c>
     </row>
     <row r="1099">
@@ -55604,32 +55616,28 @@
       </c>
       <c r="E1099" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F1099" t="inlineStr">
         <is>
-          <t>SANTOS - CTB</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="G1099" t="inlineStr">
         <is>
-          <t>Ivia Oliveira</t>
-        </is>
-      </c>
-      <c r="H1099" t="inlineStr">
-        <is>
-          <t>Roberto Silva</t>
-        </is>
-      </c>
+          <t>Edimir Santos</t>
+        </is>
+      </c>
+      <c r="H1099" t="inlineStr"/>
       <c r="I1099" t="n">
         <v>0</v>
       </c>
       <c r="J1099" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1099" t="n">
         <v>1</v>
-      </c>
-      <c r="K1099" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="1100">
@@ -55655,32 +55663,28 @@
       </c>
       <c r="E1100" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F1100" t="inlineStr">
         <is>
-          <t>SANTOS - CTB</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="G1100" t="inlineStr">
         <is>
-          <t>Nata Trindade</t>
-        </is>
-      </c>
-      <c r="H1100" t="inlineStr">
-        <is>
-          <t>Roberto Silva</t>
-        </is>
-      </c>
+          <t>Jurema Damacena - SAC</t>
+        </is>
+      </c>
+      <c r="H1100" t="inlineStr"/>
       <c r="I1100" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J1100" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="K1100" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1101">
@@ -55706,32 +55710,28 @@
       </c>
       <c r="E1101" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F1101" t="inlineStr">
         <is>
-          <t>SANTOS - CTB</t>
+          <t>S.A.C</t>
         </is>
       </c>
       <c r="G1101" t="inlineStr">
         <is>
-          <t>Roberto Silva</t>
-        </is>
-      </c>
-      <c r="H1101" t="inlineStr">
-        <is>
-          <t>Roberto Silva</t>
-        </is>
-      </c>
+          <t>Ana Celia - SAC</t>
+        </is>
+      </c>
+      <c r="H1101" t="inlineStr"/>
       <c r="I1101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1101" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K1101" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1102">
@@ -55757,32 +55757,32 @@
       </c>
       <c r="E1102" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F1102" t="inlineStr">
         <is>
-          <t>SANTOS - CTB</t>
+          <t>SANTOS - DP</t>
         </is>
       </c>
       <c r="G1102" t="inlineStr">
         <is>
-          <t>Thaina Rodrigues</t>
+          <t>Katia Valeria</t>
         </is>
       </c>
       <c r="H1102" t="inlineStr">
         <is>
-          <t>Roberto Silva</t>
+          <t>Katia Valeria</t>
         </is>
       </c>
       <c r="I1102" t="n">
         <v>0</v>
       </c>
       <c r="J1102" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="K1102" t="n">
-        <v>48</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1103">
@@ -55813,27 +55813,23 @@
       </c>
       <c r="F1103" t="inlineStr">
         <is>
-          <t>SANTOS - DP</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="G1103" t="inlineStr">
         <is>
-          <t>Bruna Silva</t>
-        </is>
-      </c>
-      <c r="H1103" t="inlineStr">
-        <is>
-          <t>Katia Valeria</t>
-        </is>
-      </c>
+          <t>Jurema Damacena - SAC</t>
+        </is>
+      </c>
+      <c r="H1103" t="inlineStr"/>
       <c r="I1103" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1103" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K1103" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1104">
@@ -55864,27 +55860,23 @@
       </c>
       <c r="F1104" t="inlineStr">
         <is>
-          <t>SANTOS - DP</t>
+          <t>SANTOS - ADM</t>
         </is>
       </c>
       <c r="G1104" t="inlineStr">
         <is>
-          <t>Carliane Silva</t>
-        </is>
-      </c>
-      <c r="H1104" t="inlineStr">
-        <is>
-          <t>Katia Valeria</t>
-        </is>
-      </c>
+          <t>Kauany Pereira</t>
+        </is>
+      </c>
+      <c r="H1104" t="inlineStr"/>
       <c r="I1104" t="n">
         <v>0</v>
       </c>
       <c r="J1104" t="n">
-        <v>125</v>
+        <v>32</v>
       </c>
       <c r="K1104" t="n">
-        <v>279</v>
+        <v>136</v>
       </c>
     </row>
     <row r="1105">
@@ -55915,27 +55907,27 @@
       </c>
       <c r="F1105" t="inlineStr">
         <is>
-          <t>SANTOS - DP</t>
+          <t>SANTOS - CTB</t>
         </is>
       </c>
       <c r="G1105" t="inlineStr">
         <is>
-          <t>Cintia Andrade</t>
+          <t>Ivia Oliveira</t>
         </is>
       </c>
       <c r="H1105" t="inlineStr">
         <is>
-          <t>Katia Valeria</t>
+          <t>Roberto Silva</t>
         </is>
       </c>
       <c r="I1105" t="n">
         <v>0</v>
       </c>
       <c r="J1105" t="n">
-        <v>95</v>
+        <v>1</v>
       </c>
       <c r="K1105" t="n">
-        <v>199</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1106">
@@ -55966,27 +55958,27 @@
       </c>
       <c r="F1106" t="inlineStr">
         <is>
-          <t>SANTOS - DP</t>
+          <t>SANTOS - CTB</t>
         </is>
       </c>
       <c r="G1106" t="inlineStr">
         <is>
-          <t>Katia Valeria</t>
+          <t>Nata Trindade</t>
         </is>
       </c>
       <c r="H1106" t="inlineStr">
         <is>
-          <t>Katia Valeria</t>
+          <t>Roberto Silva</t>
         </is>
       </c>
       <c r="I1106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1106" t="n">
-        <v>153</v>
+        <v>11</v>
       </c>
       <c r="K1106" t="n">
-        <v>333</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1107">
@@ -56017,27 +56009,27 @@
       </c>
       <c r="F1107" t="inlineStr">
         <is>
-          <t>SANTOS - EF</t>
+          <t>SANTOS - CTB</t>
         </is>
       </c>
       <c r="G1107" t="inlineStr">
         <is>
-          <t>Jasmina Melo</t>
+          <t>Roberto Silva</t>
         </is>
       </c>
       <c r="H1107" t="inlineStr">
         <is>
-          <t>Lidia Tavares</t>
+          <t>Roberto Silva</t>
         </is>
       </c>
       <c r="I1107" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J1107" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="K1107" t="n">
-        <v>54</v>
+        <v>41</v>
       </c>
     </row>
     <row r="1108">
@@ -56068,17 +56060,17 @@
       </c>
       <c r="F1108" t="inlineStr">
         <is>
-          <t>SANTOS - EF</t>
+          <t>SANTOS - CTB</t>
         </is>
       </c>
       <c r="G1108" t="inlineStr">
         <is>
-          <t>Karen Saadi</t>
+          <t>Thaina Rodrigues</t>
         </is>
       </c>
       <c r="H1108" t="inlineStr">
         <is>
-          <t>Lidia Tavares</t>
+          <t>Roberto Silva</t>
         </is>
       </c>
       <c r="I1108" t="n">
@@ -56088,7 +56080,7 @@
         <v>24</v>
       </c>
       <c r="K1108" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
     </row>
     <row r="1109">
@@ -56119,27 +56111,27 @@
       </c>
       <c r="F1109" t="inlineStr">
         <is>
-          <t>SANTOS - EF</t>
+          <t>SANTOS - DP</t>
         </is>
       </c>
       <c r="G1109" t="inlineStr">
         <is>
-          <t>Luckas Andrade</t>
+          <t>Bruna Silva</t>
         </is>
       </c>
       <c r="H1109" t="inlineStr">
         <is>
-          <t>Lidia Tavares</t>
+          <t>Katia Valeria</t>
         </is>
       </c>
       <c r="I1109" t="n">
         <v>0</v>
       </c>
       <c r="J1109" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K1109" t="n">
-        <v>71</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1110">
@@ -56170,27 +56162,27 @@
       </c>
       <c r="F1110" t="inlineStr">
         <is>
-          <t>SANTOS - EF</t>
+          <t>SANTOS - DP</t>
         </is>
       </c>
       <c r="G1110" t="inlineStr">
         <is>
-          <t>Mirian Rodrigues</t>
+          <t>Carliane Silva</t>
         </is>
       </c>
       <c r="H1110" t="inlineStr">
         <is>
-          <t>Lidia Tavares</t>
+          <t>Katia Valeria</t>
         </is>
       </c>
       <c r="I1110" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1110" t="n">
-        <v>28</v>
+        <v>127</v>
       </c>
       <c r="K1110" t="n">
-        <v>82</v>
+        <v>280</v>
       </c>
     </row>
     <row r="1111">
@@ -56221,22 +56213,375 @@
       </c>
       <c r="F1111" t="inlineStr">
         <is>
+          <t>SANTOS - DP</t>
+        </is>
+      </c>
+      <c r="G1111" t="inlineStr">
+        <is>
+          <t>Cintia Andrade</t>
+        </is>
+      </c>
+      <c r="H1111" t="inlineStr">
+        <is>
+          <t>Katia Valeria</t>
+        </is>
+      </c>
+      <c r="I1111" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1111" t="n">
+        <v>95</v>
+      </c>
+      <c r="K1111" t="n">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B1112" t="inlineStr">
+        <is>
+          <t>Quinta</t>
+        </is>
+      </c>
+      <c r="C1112" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D1112" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1112" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="F1112" t="inlineStr">
+        <is>
+          <t>SANTOS - DP</t>
+        </is>
+      </c>
+      <c r="G1112" t="inlineStr">
+        <is>
+          <t>Katia Valeria</t>
+        </is>
+      </c>
+      <c r="H1112" t="inlineStr">
+        <is>
+          <t>Katia Valeria</t>
+        </is>
+      </c>
+      <c r="I1112" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1112" t="n">
+        <v>155</v>
+      </c>
+      <c r="K1112" t="n">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B1113" t="inlineStr">
+        <is>
+          <t>Quinta</t>
+        </is>
+      </c>
+      <c r="C1113" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D1113" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1113" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="F1113" t="inlineStr">
+        <is>
+          <t>SANTOS - DP</t>
+        </is>
+      </c>
+      <c r="G1113" t="inlineStr">
+        <is>
+          <t>Patricia Melo</t>
+        </is>
+      </c>
+      <c r="H1113" t="inlineStr"/>
+      <c r="I1113" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B1114" t="inlineStr">
+        <is>
+          <t>Quinta</t>
+        </is>
+      </c>
+      <c r="C1114" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D1114" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1114" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="F1114" t="inlineStr">
+        <is>
+          <t>SANTOS - EF</t>
+        </is>
+      </c>
+      <c r="G1114" t="inlineStr">
+        <is>
+          <t>Jasmina Melo</t>
+        </is>
+      </c>
+      <c r="H1114" t="inlineStr">
+        <is>
+          <t>Lidia Tavares</t>
+        </is>
+      </c>
+      <c r="I1114" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1114" t="n">
+        <v>32</v>
+      </c>
+      <c r="K1114" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B1115" t="inlineStr">
+        <is>
+          <t>Quinta</t>
+        </is>
+      </c>
+      <c r="C1115" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D1115" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1115" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="F1115" t="inlineStr">
+        <is>
+          <t>SANTOS - EF</t>
+        </is>
+      </c>
+      <c r="G1115" t="inlineStr">
+        <is>
+          <t>Karen Saadi</t>
+        </is>
+      </c>
+      <c r="H1115" t="inlineStr">
+        <is>
+          <t>Lidia Tavares</t>
+        </is>
+      </c>
+      <c r="I1115" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1115" t="n">
+        <v>26</v>
+      </c>
+      <c r="K1115" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B1116" t="inlineStr">
+        <is>
+          <t>Quinta</t>
+        </is>
+      </c>
+      <c r="C1116" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D1116" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1116" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="F1116" t="inlineStr">
+        <is>
+          <t>SANTOS - EF</t>
+        </is>
+      </c>
+      <c r="G1116" t="inlineStr">
+        <is>
+          <t>Luckas Andrade</t>
+        </is>
+      </c>
+      <c r="H1116" t="inlineStr">
+        <is>
+          <t>Lidia Tavares</t>
+        </is>
+      </c>
+      <c r="I1116" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1116" t="n">
+        <v>36</v>
+      </c>
+      <c r="K1116" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B1117" t="inlineStr">
+        <is>
+          <t>Quinta</t>
+        </is>
+      </c>
+      <c r="C1117" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D1117" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1117" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="F1117" t="inlineStr">
+        <is>
+          <t>SANTOS - EF</t>
+        </is>
+      </c>
+      <c r="G1117" t="inlineStr">
+        <is>
+          <t>Mirian Rodrigues</t>
+        </is>
+      </c>
+      <c r="H1117" t="inlineStr">
+        <is>
+          <t>Lidia Tavares</t>
+        </is>
+      </c>
+      <c r="I1117" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1117" t="n">
+        <v>28</v>
+      </c>
+      <c r="K1117" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B1118" t="inlineStr">
+        <is>
+          <t>Quinta</t>
+        </is>
+      </c>
+      <c r="C1118" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D1118" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1118" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="F1118" t="inlineStr">
+        <is>
           <t>SANTOS - GC</t>
         </is>
       </c>
-      <c r="G1111" t="inlineStr">
+      <c r="G1118" t="inlineStr">
         <is>
           <t>Rafaella Massuia</t>
         </is>
       </c>
-      <c r="H1111" t="inlineStr"/>
-      <c r="I1111" t="n">
-        <v>0</v>
-      </c>
-      <c r="J1111" t="n">
-        <v>0</v>
-      </c>
-      <c r="K1111" t="n">
+      <c r="H1118" t="inlineStr"/>
+      <c r="I1118" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1118" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1118" t="n">
         <v>109</v>
       </c>
     </row>

--- a/data/historico/historico_baixas.xlsx
+++ b/data/historico/historico_baixas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1118"/>
+  <dimension ref="A1:K1120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -42222,13 +42222,13 @@
         </is>
       </c>
       <c r="I832" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J832" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K832" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="833">
@@ -42273,13 +42273,13 @@
         </is>
       </c>
       <c r="I833" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J833" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K833" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="834">
@@ -42971,13 +42971,13 @@
       </c>
       <c r="H847" t="inlineStr"/>
       <c r="I847" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J847" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="K847" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="848">
@@ -43065,13 +43065,13 @@
       </c>
       <c r="H849" t="inlineStr"/>
       <c r="I849" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="J849" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="K849" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
     </row>
     <row r="850">
@@ -43257,13 +43257,13 @@
         </is>
       </c>
       <c r="I853" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J853" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K853" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="854">
@@ -43563,13 +43563,13 @@
         </is>
       </c>
       <c r="I859" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J859" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K859" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="860">
@@ -43869,13 +43869,13 @@
         </is>
       </c>
       <c r="I865" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J865" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K865" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="866">
@@ -44218,13 +44218,13 @@
         </is>
       </c>
       <c r="I872" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J872" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K872" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="873">
@@ -44269,13 +44269,13 @@
         </is>
       </c>
       <c r="I873" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J873" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K873" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="874">
@@ -44626,7 +44626,7 @@
         </is>
       </c>
       <c r="I880" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J880" t="n">
         <v>15</v>
@@ -44932,13 +44932,13 @@
         </is>
       </c>
       <c r="I886" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J886" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="K886" t="n">
-        <v>163</v>
+        <v>171</v>
       </c>
     </row>
     <row r="887">
@@ -45238,13 +45238,13 @@
         </is>
       </c>
       <c r="I892" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J892" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K892" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="893">
@@ -45289,13 +45289,13 @@
         </is>
       </c>
       <c r="I893" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J893" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K893" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="894">
@@ -45442,13 +45442,13 @@
         </is>
       </c>
       <c r="I896" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J896" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K896" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="897">
@@ -45595,13 +45595,13 @@
         </is>
       </c>
       <c r="I899" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="J899" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="K899" t="n">
-        <v>138</v>
+        <v>145</v>
       </c>
     </row>
     <row r="900">
@@ -45697,13 +45697,13 @@
         </is>
       </c>
       <c r="I901" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J901" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="K901" t="n">
-        <v>116</v>
+        <v>123</v>
       </c>
     </row>
     <row r="902">
@@ -46536,13 +46536,13 @@
         </is>
       </c>
       <c r="I918" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J918" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K918" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="919">
@@ -47046,13 +47046,13 @@
         </is>
       </c>
       <c r="I928" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J928" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K928" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="929">
@@ -47399,13 +47399,13 @@
         </is>
       </c>
       <c r="I935" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J935" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K935" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="936">
@@ -47450,13 +47450,13 @@
         </is>
       </c>
       <c r="I936" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J936" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K936" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="937">
@@ -47552,13 +47552,13 @@
         </is>
       </c>
       <c r="I938" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J938" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K938" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="939">
@@ -47705,13 +47705,13 @@
         </is>
       </c>
       <c r="I941" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J941" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K941" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="942">
@@ -47756,13 +47756,13 @@
         </is>
       </c>
       <c r="I942" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J942" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K942" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="943">
@@ -47858,13 +47858,13 @@
         </is>
       </c>
       <c r="I944" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J944" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K944" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="945">
@@ -47909,13 +47909,13 @@
         </is>
       </c>
       <c r="I945" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J945" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K945" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="946">
@@ -47960,13 +47960,13 @@
         </is>
       </c>
       <c r="I946" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J946" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K946" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="947">
@@ -48011,13 +48011,13 @@
         </is>
       </c>
       <c r="I947" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J947" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K947" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="948">
@@ -48119,7 +48119,7 @@
         <v>0</v>
       </c>
       <c r="K949" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="950">
@@ -48215,13 +48215,13 @@
         </is>
       </c>
       <c r="I951" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J951" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K951" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="952">
@@ -48368,13 +48368,13 @@
         </is>
       </c>
       <c r="I954" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J954" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K954" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="955">
@@ -48623,13 +48623,13 @@
         </is>
       </c>
       <c r="I959" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J959" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K959" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="960">
@@ -48976,13 +48976,13 @@
         </is>
       </c>
       <c r="I966" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J966" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K966" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="967">
@@ -49027,10 +49027,10 @@
         </is>
       </c>
       <c r="I967" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J967" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K967" t="n">
         <v>15</v>
@@ -49078,13 +49078,13 @@
         </is>
       </c>
       <c r="I968" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J968" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K968" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="969">
@@ -49231,13 +49231,13 @@
         </is>
       </c>
       <c r="I971" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J971" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K971" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="972">
@@ -49282,10 +49282,10 @@
         </is>
       </c>
       <c r="I972" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J972" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K972" t="n">
         <v>32</v>
@@ -49333,13 +49333,13 @@
         </is>
       </c>
       <c r="I973" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J973" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K973" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="974">
@@ -49384,13 +49384,13 @@
         </is>
       </c>
       <c r="I974" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="J974" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="K974" t="n">
-        <v>157</v>
+        <v>176</v>
       </c>
     </row>
     <row r="975">
@@ -49435,13 +49435,13 @@
         </is>
       </c>
       <c r="I975" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J975" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K975" t="n">
-        <v>57</v>
+        <v>67</v>
       </c>
     </row>
     <row r="976">
@@ -49588,13 +49588,13 @@
         </is>
       </c>
       <c r="I978" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J978" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K978" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="979">
@@ -49696,7 +49696,7 @@
         <v>0</v>
       </c>
       <c r="K980" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="981">
@@ -49843,13 +49843,13 @@
         </is>
       </c>
       <c r="I983" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="J983" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="K983" t="n">
-        <v>142</v>
+        <v>151</v>
       </c>
     </row>
     <row r="984">
@@ -50251,13 +50251,13 @@
         </is>
       </c>
       <c r="I991" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J991" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K991" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="992">
@@ -50302,10 +50302,10 @@
         </is>
       </c>
       <c r="I992" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J992" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K992" t="n">
         <v>1</v>
@@ -50410,7 +50410,7 @@
         <v>15</v>
       </c>
       <c r="K994" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="995">
@@ -50455,7 +50455,7 @@
         </is>
       </c>
       <c r="I995" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J995" t="n">
         <v>20</v>
@@ -50553,13 +50553,13 @@
         </is>
       </c>
       <c r="I997" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J997" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K997" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
     </row>
     <row r="998">
@@ -51216,13 +51216,13 @@
         </is>
       </c>
       <c r="I1010" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1010" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K1010" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="1011">
@@ -51267,13 +51267,13 @@
         </is>
       </c>
       <c r="I1011" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J1011" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="K1011" t="n">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="1012">
@@ -51318,13 +51318,13 @@
         </is>
       </c>
       <c r="I1012" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1012" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K1012" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="1013">
@@ -51620,13 +51620,13 @@
         </is>
       </c>
       <c r="I1018" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J1018" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K1018" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="1019">
@@ -51671,13 +51671,13 @@
         </is>
       </c>
       <c r="I1019" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1019" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K1019" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="1020">
@@ -51773,13 +51773,13 @@
         </is>
       </c>
       <c r="I1021" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J1021" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="K1021" t="n">
-        <v>83</v>
+        <v>92</v>
       </c>
     </row>
     <row r="1022">
@@ -51824,13 +51824,13 @@
         </is>
       </c>
       <c r="I1022" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J1022" t="n">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="K1022" t="n">
-        <v>219</v>
+        <v>228</v>
       </c>
     </row>
     <row r="1023">
@@ -51977,13 +51977,13 @@
         </is>
       </c>
       <c r="I1025" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J1025" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K1025" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="1026">
@@ -52028,13 +52028,13 @@
         </is>
       </c>
       <c r="I1026" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1026" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K1026" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="1027">
@@ -52079,13 +52079,13 @@
         </is>
       </c>
       <c r="I1027" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J1027" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="K1027" t="n">
-        <v>168</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1028">
@@ -52130,13 +52130,13 @@
         </is>
       </c>
       <c r="I1028" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="J1028" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="K1028" t="n">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="1029">
@@ -52181,13 +52181,13 @@
         </is>
       </c>
       <c r="I1029" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1029" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K1029" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="1030">
@@ -52232,13 +52232,13 @@
         </is>
       </c>
       <c r="I1030" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J1030" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="K1030" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="1031">
@@ -52283,13 +52283,13 @@
         </is>
       </c>
       <c r="I1031" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="J1031" t="n">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="K1031" t="n">
-        <v>113</v>
+        <v>125</v>
       </c>
     </row>
     <row r="1032">
@@ -52334,13 +52334,13 @@
         </is>
       </c>
       <c r="I1032" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J1032" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K1032" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="1033">
@@ -52388,10 +52388,10 @@
         <v>1</v>
       </c>
       <c r="J1033" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K1033" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="1034">
@@ -52439,10 +52439,10 @@
         <v>0</v>
       </c>
       <c r="J1034" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K1034" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="1035">
@@ -52486,10 +52486,10 @@
         <v>0</v>
       </c>
       <c r="J1035" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K1035" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1036">
@@ -52534,13 +52534,13 @@
         </is>
       </c>
       <c r="I1036" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J1036" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="K1036" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="1037">
@@ -52588,10 +52588,10 @@
         <v>1</v>
       </c>
       <c r="J1037" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K1037" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="1038">
@@ -52636,13 +52636,13 @@
         </is>
       </c>
       <c r="I1038" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J1038" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K1038" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="1039">
@@ -52687,13 +52687,13 @@
         </is>
       </c>
       <c r="I1039" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J1039" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K1039" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="1040">
@@ -52789,13 +52789,13 @@
         </is>
       </c>
       <c r="I1041" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J1041" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K1041" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="1042">
@@ -52840,13 +52840,13 @@
         </is>
       </c>
       <c r="I1042" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J1042" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K1042" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="1043">
@@ -52942,13 +52942,13 @@
         </is>
       </c>
       <c r="I1044" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J1044" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K1044" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1045">
@@ -52996,10 +52996,10 @@
         <v>0</v>
       </c>
       <c r="J1045" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K1045" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1046">
@@ -53095,13 +53095,13 @@
         </is>
       </c>
       <c r="I1047" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1047" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K1047" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="1048">
@@ -53248,13 +53248,13 @@
         </is>
       </c>
       <c r="I1050" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J1050" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K1050" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="1051">
@@ -53299,13 +53299,13 @@
         </is>
       </c>
       <c r="I1051" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="J1051" t="n">
-        <v>95</v>
+        <v>135</v>
       </c>
       <c r="K1051" t="n">
-        <v>195</v>
+        <v>235</v>
       </c>
     </row>
     <row r="1052">
@@ -53350,13 +53350,13 @@
         </is>
       </c>
       <c r="I1052" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J1052" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K1052" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="1053">
@@ -53452,13 +53452,13 @@
         </is>
       </c>
       <c r="I1054" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J1054" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K1054" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="1055">
@@ -53503,13 +53503,13 @@
         </is>
       </c>
       <c r="I1055" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1055" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K1055" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="1056">
@@ -53554,7 +53554,7 @@
         </is>
       </c>
       <c r="I1056" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J1056" t="n">
         <v>0</v>
@@ -53605,7 +53605,7 @@
         </is>
       </c>
       <c r="I1057" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J1057" t="n">
         <v>17</v>
@@ -53707,13 +53707,13 @@
         </is>
       </c>
       <c r="I1059" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J1059" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K1059" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="1060">
@@ -53809,13 +53809,13 @@
         </is>
       </c>
       <c r="I1061" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J1061" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K1061" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="1062">
@@ -54060,13 +54060,13 @@
         </is>
       </c>
       <c r="I1066" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J1066" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="K1066" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1067">
@@ -54264,13 +54264,13 @@
         </is>
       </c>
       <c r="I1070" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J1070" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K1070" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1071">
@@ -54409,13 +54409,13 @@
       </c>
       <c r="H1073" t="inlineStr"/>
       <c r="I1073" t="n">
-        <v>36</v>
+        <v>148</v>
       </c>
       <c r="J1073" t="n">
-        <v>65</v>
+        <v>177</v>
       </c>
       <c r="K1073" t="n">
-        <v>418</v>
+        <v>446</v>
       </c>
     </row>
     <row r="1074">
@@ -54503,13 +54503,13 @@
       </c>
       <c r="H1075" t="inlineStr"/>
       <c r="I1075" t="n">
-        <v>22</v>
+        <v>114</v>
       </c>
       <c r="J1075" t="n">
-        <v>44</v>
+        <v>136</v>
       </c>
       <c r="K1075" t="n">
-        <v>338</v>
+        <v>368</v>
       </c>
     </row>
     <row r="1076">
@@ -54550,10 +54550,10 @@
       </c>
       <c r="H1076" t="inlineStr"/>
       <c r="I1076" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="J1076" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="K1076" t="n">
         <v>32</v>
@@ -54597,13 +54597,13 @@
       </c>
       <c r="H1077" t="inlineStr"/>
       <c r="I1077" t="n">
-        <v>89</v>
+        <v>185</v>
       </c>
       <c r="J1077" t="n">
-        <v>93</v>
+        <v>189</v>
       </c>
       <c r="K1077" t="n">
-        <v>89</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1078">
@@ -54644,13 +54644,13 @@
       </c>
       <c r="H1078" t="inlineStr"/>
       <c r="I1078" t="n">
-        <v>4</v>
+        <v>90</v>
       </c>
       <c r="J1078" t="n">
-        <v>11</v>
+        <v>97</v>
       </c>
       <c r="K1078" t="n">
-        <v>33</v>
+        <v>116</v>
       </c>
     </row>
     <row r="1079">
@@ -54738,13 +54738,13 @@
       </c>
       <c r="H1080" t="inlineStr"/>
       <c r="I1080" t="n">
-        <v>61</v>
+        <v>209</v>
       </c>
       <c r="J1080" t="n">
-        <v>56</v>
+        <v>204</v>
       </c>
       <c r="K1080" t="n">
-        <v>92</v>
+        <v>221</v>
       </c>
     </row>
     <row r="1081">
@@ -54832,13 +54832,13 @@
       </c>
       <c r="H1082" t="inlineStr"/>
       <c r="I1082" t="n">
-        <v>54</v>
+        <v>135</v>
       </c>
       <c r="J1082" t="n">
-        <v>71</v>
+        <v>152</v>
       </c>
       <c r="K1082" t="n">
-        <v>71</v>
+        <v>152</v>
       </c>
     </row>
     <row r="1083">
@@ -54879,13 +54879,13 @@
       </c>
       <c r="H1083" t="inlineStr"/>
       <c r="I1083" t="n">
-        <v>20</v>
+        <v>136</v>
       </c>
       <c r="J1083" t="n">
-        <v>33</v>
+        <v>149</v>
       </c>
       <c r="K1083" t="n">
-        <v>276</v>
+        <v>373</v>
       </c>
     </row>
     <row r="1084">
@@ -54926,10 +54926,10 @@
       </c>
       <c r="H1084" t="inlineStr"/>
       <c r="I1084" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J1084" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K1084" t="n">
         <v>4</v>
@@ -54973,13 +54973,13 @@
       </c>
       <c r="H1085" t="inlineStr"/>
       <c r="I1085" t="n">
-        <v>10</v>
+        <v>83</v>
       </c>
       <c r="J1085" t="n">
-        <v>15</v>
+        <v>88</v>
       </c>
       <c r="K1085" t="n">
-        <v>269</v>
+        <v>283</v>
       </c>
     </row>
     <row r="1086">
@@ -55020,13 +55020,13 @@
       </c>
       <c r="H1086" t="inlineStr"/>
       <c r="I1086" t="n">
-        <v>79</v>
+        <v>185</v>
       </c>
       <c r="J1086" t="n">
-        <v>216</v>
+        <v>311</v>
       </c>
       <c r="K1086" t="n">
-        <v>341</v>
+        <v>363</v>
       </c>
     </row>
     <row r="1087">
@@ -55067,13 +55067,13 @@
       </c>
       <c r="H1087" t="inlineStr"/>
       <c r="I1087" t="n">
-        <v>1</v>
+        <v>59</v>
       </c>
       <c r="J1087" t="n">
-        <v>136</v>
+        <v>194</v>
       </c>
       <c r="K1087" t="n">
-        <v>302</v>
+        <v>280</v>
       </c>
     </row>
     <row r="1088">
@@ -55114,13 +55114,13 @@
       </c>
       <c r="H1088" t="inlineStr"/>
       <c r="I1088" t="n">
-        <v>19</v>
+        <v>110</v>
       </c>
       <c r="J1088" t="n">
-        <v>135</v>
+        <v>223</v>
       </c>
       <c r="K1088" t="n">
-        <v>190</v>
+        <v>276</v>
       </c>
     </row>
     <row r="1089">
@@ -55161,13 +55161,13 @@
       </c>
       <c r="H1089" t="inlineStr"/>
       <c r="I1089" t="n">
-        <v>7</v>
+        <v>54</v>
       </c>
       <c r="J1089" t="n">
-        <v>42</v>
+        <v>86</v>
       </c>
       <c r="K1089" t="n">
-        <v>113</v>
+        <v>122</v>
       </c>
     </row>
     <row r="1090">
@@ -55255,13 +55255,13 @@
       </c>
       <c r="H1091" t="inlineStr"/>
       <c r="I1091" t="n">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="J1091" t="n">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="K1091" t="n">
-        <v>9</v>
+        <v>44</v>
       </c>
     </row>
     <row r="1092">
@@ -55302,13 +55302,13 @@
       </c>
       <c r="H1092" t="inlineStr"/>
       <c r="I1092" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1092" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K1092" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1093">
@@ -55349,13 +55349,13 @@
       </c>
       <c r="H1093" t="inlineStr"/>
       <c r="I1093" t="n">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="J1093" t="n">
-        <v>93</v>
+        <v>143</v>
       </c>
       <c r="K1093" t="n">
-        <v>167</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1094">
@@ -55396,13 +55396,13 @@
       </c>
       <c r="H1094" t="inlineStr"/>
       <c r="I1094" t="n">
-        <v>47</v>
+        <v>202</v>
       </c>
       <c r="J1094" t="n">
-        <v>51</v>
+        <v>199</v>
       </c>
       <c r="K1094" t="n">
-        <v>212</v>
+        <v>279</v>
       </c>
     </row>
     <row r="1095">
@@ -55443,13 +55443,13 @@
       </c>
       <c r="H1095" t="inlineStr"/>
       <c r="I1095" t="n">
-        <v>18</v>
+        <v>92</v>
       </c>
       <c r="J1095" t="n">
-        <v>129</v>
+        <v>201</v>
       </c>
       <c r="K1095" t="n">
-        <v>291</v>
+        <v>300</v>
       </c>
     </row>
     <row r="1096">
@@ -55490,10 +55490,10 @@
       </c>
       <c r="H1096" t="inlineStr"/>
       <c r="I1096" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J1096" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="K1096" t="n">
         <v>48</v>
@@ -55537,13 +55537,13 @@
       </c>
       <c r="H1097" t="inlineStr"/>
       <c r="I1097" t="n">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="J1097" t="n">
-        <v>95</v>
+        <v>137</v>
       </c>
       <c r="K1097" t="n">
-        <v>185</v>
+        <v>195</v>
       </c>
     </row>
     <row r="1098">
@@ -55584,13 +55584,13 @@
       </c>
       <c r="H1098" t="inlineStr"/>
       <c r="I1098" t="n">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="J1098" t="n">
-        <v>97</v>
+        <v>130</v>
       </c>
       <c r="K1098" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="1099">
@@ -55678,7 +55678,7 @@
       </c>
       <c r="H1100" t="inlineStr"/>
       <c r="I1100" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J1100" t="n">
         <v>30</v>
@@ -55715,23 +55715,19 @@
       </c>
       <c r="F1101" t="inlineStr">
         <is>
-          <t>S.A.C</t>
-        </is>
-      </c>
-      <c r="G1101" t="inlineStr">
-        <is>
-          <t>Ana Celia - SAC</t>
-        </is>
-      </c>
+          <t>MG CONTABIFÁCIL - CTB</t>
+        </is>
+      </c>
+      <c r="G1101" t="inlineStr"/>
       <c r="H1101" t="inlineStr"/>
       <c r="I1101" t="n">
         <v>1</v>
       </c>
       <c r="J1101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1102">
@@ -55762,27 +55758,23 @@
       </c>
       <c r="F1102" t="inlineStr">
         <is>
-          <t>SANTOS - DP</t>
+          <t>MG CONTABIFÁCIL - CTB</t>
         </is>
       </c>
       <c r="G1102" t="inlineStr">
         <is>
-          <t>Katia Valeria</t>
-        </is>
-      </c>
-      <c r="H1102" t="inlineStr">
-        <is>
-          <t>Katia Valeria</t>
-        </is>
-      </c>
+          <t>Guilherme Delecrodio</t>
+        </is>
+      </c>
+      <c r="H1102" t="inlineStr"/>
       <c r="I1102" t="n">
         <v>0</v>
       </c>
       <c r="J1102" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K1102" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1103">
@@ -55808,28 +55800,28 @@
       </c>
       <c r="E1103" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F1103" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>S.A.C</t>
         </is>
       </c>
       <c r="G1103" t="inlineStr">
         <is>
-          <t>Jurema Damacena - SAC</t>
+          <t>Ana Celia - SAC</t>
         </is>
       </c>
       <c r="H1103" t="inlineStr"/>
       <c r="I1103" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J1103" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K1103" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1104">
@@ -55855,28 +55847,32 @@
       </c>
       <c r="E1104" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F1104" t="inlineStr">
         <is>
-          <t>SANTOS - ADM</t>
+          <t>SANTOS - DP</t>
         </is>
       </c>
       <c r="G1104" t="inlineStr">
         <is>
-          <t>Kauany Pereira</t>
-        </is>
-      </c>
-      <c r="H1104" t="inlineStr"/>
+          <t>Katia Valeria</t>
+        </is>
+      </c>
+      <c r="H1104" t="inlineStr">
+        <is>
+          <t>Katia Valeria</t>
+        </is>
+      </c>
       <c r="I1104" t="n">
         <v>0</v>
       </c>
       <c r="J1104" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="K1104" t="n">
-        <v>136</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1105">
@@ -55907,27 +55903,23 @@
       </c>
       <c r="F1105" t="inlineStr">
         <is>
-          <t>SANTOS - CTB</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="G1105" t="inlineStr">
         <is>
-          <t>Ivia Oliveira</t>
-        </is>
-      </c>
-      <c r="H1105" t="inlineStr">
-        <is>
-          <t>Roberto Silva</t>
-        </is>
-      </c>
+          <t>Jurema Damacena - SAC</t>
+        </is>
+      </c>
+      <c r="H1105" t="inlineStr"/>
       <c r="I1105" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1105" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K1105" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1106">
@@ -55958,27 +55950,23 @@
       </c>
       <c r="F1106" t="inlineStr">
         <is>
-          <t>SANTOS - CTB</t>
+          <t>SANTOS - ADM</t>
         </is>
       </c>
       <c r="G1106" t="inlineStr">
         <is>
-          <t>Nata Trindade</t>
-        </is>
-      </c>
-      <c r="H1106" t="inlineStr">
-        <is>
-          <t>Roberto Silva</t>
-        </is>
-      </c>
+          <t>Kauany Pereira</t>
+        </is>
+      </c>
+      <c r="H1106" t="inlineStr"/>
       <c r="I1106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J1106" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="K1106" t="n">
-        <v>29</v>
+        <v>136</v>
       </c>
     </row>
     <row r="1107">
@@ -56014,22 +56002,22 @@
       </c>
       <c r="G1107" t="inlineStr">
         <is>
+          <t>Ivia Oliveira</t>
+        </is>
+      </c>
+      <c r="H1107" t="inlineStr">
+        <is>
           <t>Roberto Silva</t>
         </is>
       </c>
-      <c r="H1107" t="inlineStr">
-        <is>
-          <t>Roberto Silva</t>
-        </is>
-      </c>
       <c r="I1107" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="J1107" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K1107" t="n">
-        <v>41</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1108">
@@ -56065,7 +56053,7 @@
       </c>
       <c r="G1108" t="inlineStr">
         <is>
-          <t>Thaina Rodrigues</t>
+          <t>Nata Trindade</t>
         </is>
       </c>
       <c r="H1108" t="inlineStr">
@@ -56074,13 +56062,13 @@
         </is>
       </c>
       <c r="I1108" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1108" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="K1108" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1109">
@@ -56111,27 +56099,27 @@
       </c>
       <c r="F1109" t="inlineStr">
         <is>
-          <t>SANTOS - DP</t>
+          <t>SANTOS - CTB</t>
         </is>
       </c>
       <c r="G1109" t="inlineStr">
         <is>
-          <t>Bruna Silva</t>
+          <t>Roberto Silva</t>
         </is>
       </c>
       <c r="H1109" t="inlineStr">
         <is>
-          <t>Katia Valeria</t>
+          <t>Roberto Silva</t>
         </is>
       </c>
       <c r="I1109" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J1109" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K1109" t="n">
-        <v>14</v>
+        <v>41</v>
       </c>
     </row>
     <row r="1110">
@@ -56162,27 +56150,27 @@
       </c>
       <c r="F1110" t="inlineStr">
         <is>
-          <t>SANTOS - DP</t>
+          <t>SANTOS - CTB</t>
         </is>
       </c>
       <c r="G1110" t="inlineStr">
         <is>
-          <t>Carliane Silva</t>
+          <t>Thaina Rodrigues</t>
         </is>
       </c>
       <c r="H1110" t="inlineStr">
         <is>
-          <t>Katia Valeria</t>
+          <t>Roberto Silva</t>
         </is>
       </c>
       <c r="I1110" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J1110" t="n">
-        <v>127</v>
+        <v>24</v>
       </c>
       <c r="K1110" t="n">
-        <v>280</v>
+        <v>48</v>
       </c>
     </row>
     <row r="1111">
@@ -56218,7 +56206,7 @@
       </c>
       <c r="G1111" t="inlineStr">
         <is>
-          <t>Cintia Andrade</t>
+          <t>Bruna Silva</t>
         </is>
       </c>
       <c r="H1111" t="inlineStr">
@@ -56230,10 +56218,10 @@
         <v>0</v>
       </c>
       <c r="J1111" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="K1111" t="n">
-        <v>199</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1112">
@@ -56269,7 +56257,7 @@
       </c>
       <c r="G1112" t="inlineStr">
         <is>
-          <t>Katia Valeria</t>
+          <t>Carliane Silva</t>
         </is>
       </c>
       <c r="H1112" t="inlineStr">
@@ -56281,10 +56269,10 @@
         <v>2</v>
       </c>
       <c r="J1112" t="n">
-        <v>155</v>
+        <v>127</v>
       </c>
       <c r="K1112" t="n">
-        <v>335</v>
+        <v>280</v>
       </c>
     </row>
     <row r="1113">
@@ -56320,18 +56308,22 @@
       </c>
       <c r="G1113" t="inlineStr">
         <is>
-          <t>Patricia Melo</t>
-        </is>
-      </c>
-      <c r="H1113" t="inlineStr"/>
+          <t>Cintia Andrade</t>
+        </is>
+      </c>
+      <c r="H1113" t="inlineStr">
+        <is>
+          <t>Katia Valeria</t>
+        </is>
+      </c>
       <c r="I1113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J1113" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="K1113" t="n">
-        <v>0</v>
+        <v>199</v>
       </c>
     </row>
     <row r="1114">
@@ -56362,27 +56354,27 @@
       </c>
       <c r="F1114" t="inlineStr">
         <is>
-          <t>SANTOS - EF</t>
+          <t>SANTOS - DP</t>
         </is>
       </c>
       <c r="G1114" t="inlineStr">
         <is>
-          <t>Jasmina Melo</t>
+          <t>Katia Valeria</t>
         </is>
       </c>
       <c r="H1114" t="inlineStr">
         <is>
-          <t>Lidia Tavares</t>
+          <t>Katia Valeria</t>
         </is>
       </c>
       <c r="I1114" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J1114" t="n">
-        <v>32</v>
+        <v>155</v>
       </c>
       <c r="K1114" t="n">
-        <v>57</v>
+        <v>335</v>
       </c>
     </row>
     <row r="1115">
@@ -56413,27 +56405,23 @@
       </c>
       <c r="F1115" t="inlineStr">
         <is>
-          <t>SANTOS - EF</t>
+          <t>SANTOS - DP</t>
         </is>
       </c>
       <c r="G1115" t="inlineStr">
         <is>
-          <t>Karen Saadi</t>
-        </is>
-      </c>
-      <c r="H1115" t="inlineStr">
-        <is>
-          <t>Lidia Tavares</t>
-        </is>
-      </c>
+          <t>Patricia Melo</t>
+        </is>
+      </c>
+      <c r="H1115" t="inlineStr"/>
       <c r="I1115" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J1115" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K1115" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1116">
@@ -56469,7 +56457,7 @@
       </c>
       <c r="G1116" t="inlineStr">
         <is>
-          <t>Luckas Andrade</t>
+          <t>Jasmina Melo</t>
         </is>
       </c>
       <c r="H1116" t="inlineStr">
@@ -56481,10 +56469,10 @@
         <v>3</v>
       </c>
       <c r="J1116" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K1116" t="n">
-        <v>74</v>
+        <v>57</v>
       </c>
     </row>
     <row r="1117">
@@ -56520,7 +56508,7 @@
       </c>
       <c r="G1117" t="inlineStr">
         <is>
-          <t>Mirian Rodrigues</t>
+          <t>Karen Saadi</t>
         </is>
       </c>
       <c r="H1117" t="inlineStr">
@@ -56529,13 +56517,13 @@
         </is>
       </c>
       <c r="I1117" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1117" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K1117" t="n">
-        <v>82</v>
+        <v>60</v>
       </c>
     </row>
     <row r="1118">
@@ -56566,22 +56554,124 @@
       </c>
       <c r="F1118" t="inlineStr">
         <is>
+          <t>SANTOS - EF</t>
+        </is>
+      </c>
+      <c r="G1118" t="inlineStr">
+        <is>
+          <t>Luckas Andrade</t>
+        </is>
+      </c>
+      <c r="H1118" t="inlineStr">
+        <is>
+          <t>Lidia Tavares</t>
+        </is>
+      </c>
+      <c r="I1118" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1118" t="n">
+        <v>36</v>
+      </c>
+      <c r="K1118" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B1119" t="inlineStr">
+        <is>
+          <t>Quinta</t>
+        </is>
+      </c>
+      <c r="C1119" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D1119" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1119" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="F1119" t="inlineStr">
+        <is>
+          <t>SANTOS - EF</t>
+        </is>
+      </c>
+      <c r="G1119" t="inlineStr">
+        <is>
+          <t>Mirian Rodrigues</t>
+        </is>
+      </c>
+      <c r="H1119" t="inlineStr">
+        <is>
+          <t>Lidia Tavares</t>
+        </is>
+      </c>
+      <c r="I1119" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1119" t="n">
+        <v>28</v>
+      </c>
+      <c r="K1119" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B1120" t="inlineStr">
+        <is>
+          <t>Quinta</t>
+        </is>
+      </c>
+      <c r="C1120" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D1120" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1120" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="F1120" t="inlineStr">
+        <is>
           <t>SANTOS - GC</t>
         </is>
       </c>
-      <c r="G1118" t="inlineStr">
+      <c r="G1120" t="inlineStr">
         <is>
           <t>Rafaella Massuia</t>
         </is>
       </c>
-      <c r="H1118" t="inlineStr"/>
-      <c r="I1118" t="n">
-        <v>0</v>
-      </c>
-      <c r="J1118" t="n">
-        <v>0</v>
-      </c>
-      <c r="K1118" t="n">
+      <c r="H1120" t="inlineStr"/>
+      <c r="I1120" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1120" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1120" t="n">
         <v>109</v>
       </c>
     </row>

--- a/data/historico/historico_baixas.xlsx
+++ b/data/historico/historico_baixas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1120"/>
+  <dimension ref="A1:K1121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -42426,13 +42426,13 @@
         </is>
       </c>
       <c r="I836" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J836" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K836" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="837">
@@ -42880,10 +42880,10 @@
         <v>2</v>
       </c>
       <c r="J845" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K845" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="846">
@@ -42971,13 +42971,13 @@
       </c>
       <c r="H847" t="inlineStr"/>
       <c r="I847" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J847" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="K847" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="848">
@@ -43065,13 +43065,13 @@
       </c>
       <c r="H849" t="inlineStr"/>
       <c r="I849" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J849" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="K849" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="850">
@@ -43359,13 +43359,13 @@
         </is>
       </c>
       <c r="I855" t="n">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="J855" t="n">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="K855" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
     </row>
     <row r="856">
@@ -43614,13 +43614,13 @@
         </is>
       </c>
       <c r="I860" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J860" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K860" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="861">
@@ -43920,13 +43920,13 @@
         </is>
       </c>
       <c r="I866" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J866" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K866" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="867">
@@ -44218,13 +44218,13 @@
         </is>
       </c>
       <c r="I872" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J872" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="K872" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
     </row>
     <row r="873">
@@ -44626,13 +44626,13 @@
         </is>
       </c>
       <c r="I880" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J880" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K880" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="881">
@@ -44779,13 +44779,13 @@
         </is>
       </c>
       <c r="I883" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J883" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K883" t="n">
-        <v>306</v>
+        <v>311</v>
       </c>
     </row>
     <row r="884">
@@ -44881,10 +44881,10 @@
         </is>
       </c>
       <c r="I885" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J885" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K885" t="n">
         <v>107</v>
@@ -44932,13 +44932,13 @@
         </is>
       </c>
       <c r="I886" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J886" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K886" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="887">
@@ -45034,13 +45034,13 @@
         </is>
       </c>
       <c r="I888" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J888" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="K888" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
     </row>
     <row r="889">
@@ -45085,13 +45085,13 @@
         </is>
       </c>
       <c r="I889" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J889" t="n">
         <v>42</v>
       </c>
       <c r="K889" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="890">
@@ -45238,13 +45238,13 @@
         </is>
       </c>
       <c r="I892" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="J892" t="n">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="K892" t="n">
-        <v>55</v>
+        <v>71</v>
       </c>
     </row>
     <row r="893">
@@ -45442,13 +45442,13 @@
         </is>
       </c>
       <c r="I896" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J896" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K896" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="897">
@@ -45747,10 +45747,10 @@
         <v>0</v>
       </c>
       <c r="J902" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K902" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="903">
@@ -45885,13 +45885,13 @@
       </c>
       <c r="H905" t="inlineStr"/>
       <c r="I905" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J905" t="n">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="K905" t="n">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="906">
@@ -46438,13 +46438,13 @@
         </is>
       </c>
       <c r="I916" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J916" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K916" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="917">
@@ -46944,13 +46944,13 @@
         </is>
       </c>
       <c r="I926" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J926" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K926" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="927">
@@ -47046,13 +47046,13 @@
         </is>
       </c>
       <c r="I928" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J928" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K928" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="929">
@@ -47807,13 +47807,13 @@
         </is>
       </c>
       <c r="I943" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J943" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K943" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="944">
@@ -47960,13 +47960,13 @@
         </is>
       </c>
       <c r="I946" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J946" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K946" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="947">
@@ -48011,13 +48011,13 @@
         </is>
       </c>
       <c r="I947" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J947" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K947" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="948">
@@ -48164,13 +48164,13 @@
         </is>
       </c>
       <c r="I950" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J950" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K950" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="951">
@@ -48674,13 +48674,13 @@
         </is>
       </c>
       <c r="I960" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J960" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K960" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="961">
@@ -49027,13 +49027,13 @@
         </is>
       </c>
       <c r="I967" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J967" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K967" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="968">
@@ -49078,13 +49078,13 @@
         </is>
       </c>
       <c r="I968" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J968" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K968" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="969">
@@ -49129,13 +49129,13 @@
         </is>
       </c>
       <c r="I969" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J969" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K969" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="970">
@@ -49222,22 +49222,18 @@
       </c>
       <c r="G971" t="inlineStr">
         <is>
-          <t>Bruna Santana</t>
-        </is>
-      </c>
-      <c r="H971" t="inlineStr">
-        <is>
-          <t>Edivaldo Veiga</t>
-        </is>
-      </c>
+          <t>Andressa Miranda</t>
+        </is>
+      </c>
+      <c r="H971" t="inlineStr"/>
       <c r="I971" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J971" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K971" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
     </row>
     <row r="972">
@@ -49273,7 +49269,7 @@
       </c>
       <c r="G972" t="inlineStr">
         <is>
-          <t>Camila Oliveira</t>
+          <t>Bruna Santana</t>
         </is>
       </c>
       <c r="H972" t="inlineStr">
@@ -49282,13 +49278,13 @@
         </is>
       </c>
       <c r="I972" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="J972" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="K972" t="n">
-        <v>32</v>
+        <v>117</v>
       </c>
     </row>
     <row r="973">
@@ -49324,22 +49320,22 @@
       </c>
       <c r="G973" t="inlineStr">
         <is>
-          <t>Daniel Moraes</t>
+          <t>Camila Oliveira</t>
         </is>
       </c>
       <c r="H973" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I973" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J973" t="n">
         <v>9</v>
       </c>
       <c r="K973" t="n">
-        <v>47</v>
+        <v>32</v>
       </c>
     </row>
     <row r="974">
@@ -49375,7 +49371,7 @@
       </c>
       <c r="G974" t="inlineStr">
         <is>
-          <t>Danilo Xavier</t>
+          <t>Daniel Moraes</t>
         </is>
       </c>
       <c r="H974" t="inlineStr">
@@ -49384,13 +49380,13 @@
         </is>
       </c>
       <c r="I974" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="J974" t="n">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="K974" t="n">
-        <v>176</v>
+        <v>47</v>
       </c>
     </row>
     <row r="975">
@@ -49426,7 +49422,7 @@
       </c>
       <c r="G975" t="inlineStr">
         <is>
-          <t>Elaine Assis</t>
+          <t>Danilo Xavier</t>
         </is>
       </c>
       <c r="H975" t="inlineStr">
@@ -49435,13 +49431,13 @@
         </is>
       </c>
       <c r="I975" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J975" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="K975" t="n">
-        <v>67</v>
+        <v>176</v>
       </c>
     </row>
     <row r="976">
@@ -49477,22 +49473,22 @@
       </c>
       <c r="G976" t="inlineStr">
         <is>
-          <t>Eliene Lima</t>
+          <t>Elaine Assis</t>
         </is>
       </c>
       <c r="H976" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I976" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J976" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K976" t="n">
-        <v>44</v>
+        <v>67</v>
       </c>
     </row>
     <row r="977">
@@ -49528,22 +49524,22 @@
       </c>
       <c r="G977" t="inlineStr">
         <is>
-          <t>Erica Oliveira</t>
+          <t>Eliene Lima</t>
         </is>
       </c>
       <c r="H977" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I977" t="n">
         <v>0</v>
       </c>
       <c r="J977" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K977" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="978">
@@ -49579,22 +49575,22 @@
       </c>
       <c r="G978" t="inlineStr">
         <is>
-          <t>Evellin Bispo</t>
+          <t>Erica Oliveira</t>
         </is>
       </c>
       <c r="H978" t="inlineStr">
         <is>
-          <t>Leandro Matos</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I978" t="n">
+        <v>1</v>
+      </c>
+      <c r="J978" t="n">
         <v>7</v>
       </c>
-      <c r="J978" t="n">
-        <v>8</v>
-      </c>
       <c r="K978" t="n">
-        <v>31</v>
+        <v>47</v>
       </c>
     </row>
     <row r="979">
@@ -49630,22 +49626,22 @@
       </c>
       <c r="G979" t="inlineStr">
         <is>
-          <t>Fabiane Branco</t>
+          <t>Evellin Bispo</t>
         </is>
       </c>
       <c r="H979" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>Leandro Matos</t>
         </is>
       </c>
       <c r="I979" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J979" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K979" t="n">
-        <v>128</v>
+        <v>31</v>
       </c>
     </row>
     <row r="980">
@@ -49681,22 +49677,22 @@
       </c>
       <c r="G980" t="inlineStr">
         <is>
-          <t>Franciele Alves</t>
+          <t>Fabiane Branco</t>
         </is>
       </c>
       <c r="H980" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I980" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J980" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K980" t="n">
-        <v>57</v>
+        <v>134</v>
       </c>
     </row>
     <row r="981">
@@ -49732,22 +49728,22 @@
       </c>
       <c r="G981" t="inlineStr">
         <is>
-          <t>Gabriela Peres</t>
+          <t>Franciele Alves</t>
         </is>
       </c>
       <c r="H981" t="inlineStr">
         <is>
-          <t>Leandro Matos</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I981" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J981" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K981" t="n">
-        <v>14</v>
+        <v>57</v>
       </c>
     </row>
     <row r="982">
@@ -49783,22 +49779,22 @@
       </c>
       <c r="G982" t="inlineStr">
         <is>
-          <t>Grasiele Santos</t>
+          <t>Gabriela Peres</t>
         </is>
       </c>
       <c r="H982" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Leandro Matos</t>
         </is>
       </c>
       <c r="I982" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J982" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="K982" t="n">
-        <v>143</v>
+        <v>14</v>
       </c>
     </row>
     <row r="983">
@@ -49834,22 +49830,22 @@
       </c>
       <c r="G983" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Grasiele Santos</t>
         </is>
       </c>
       <c r="H983" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I983" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="J983" t="n">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="K983" t="n">
-        <v>151</v>
+        <v>143</v>
       </c>
     </row>
     <row r="984">
@@ -49885,22 +49881,22 @@
       </c>
       <c r="G984" t="inlineStr">
         <is>
-          <t>Janaina Rocha</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="H984" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I984" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="J984" t="n">
-        <v>9</v>
+        <v>62</v>
       </c>
       <c r="K984" t="n">
-        <v>90</v>
+        <v>168</v>
       </c>
     </row>
     <row r="985">
@@ -49936,22 +49932,22 @@
       </c>
       <c r="G985" t="inlineStr">
         <is>
-          <t>Jayne Tavares</t>
+          <t>Janaina Rocha</t>
         </is>
       </c>
       <c r="H985" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I985" t="n">
         <v>0</v>
       </c>
       <c r="J985" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K985" t="n">
-        <v>127</v>
+        <v>90</v>
       </c>
     </row>
     <row r="986">
@@ -49987,22 +49983,22 @@
       </c>
       <c r="G986" t="inlineStr">
         <is>
-          <t>Jhenifer Tenorio</t>
+          <t>Jayne Tavares</t>
         </is>
       </c>
       <c r="H986" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I986" t="n">
         <v>0</v>
       </c>
       <c r="J986" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="K986" t="n">
-        <v>115</v>
+        <v>127</v>
       </c>
     </row>
     <row r="987">
@@ -50038,7 +50034,7 @@
       </c>
       <c r="G987" t="inlineStr">
         <is>
-          <t>Jonas Nunes</t>
+          <t>Jhenifer Tenorio</t>
         </is>
       </c>
       <c r="H987" t="inlineStr">
@@ -50047,13 +50043,13 @@
         </is>
       </c>
       <c r="I987" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="J987" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="K987" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="988">
@@ -50089,22 +50085,22 @@
       </c>
       <c r="G988" t="inlineStr">
         <is>
-          <t>Kaique Souza</t>
+          <t>Jonas Nunes</t>
         </is>
       </c>
       <c r="H988" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I988" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="J988" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="K988" t="n">
-        <v>79</v>
+        <v>112</v>
       </c>
     </row>
     <row r="989">
@@ -50140,7 +50136,7 @@
       </c>
       <c r="G989" t="inlineStr">
         <is>
-          <t>Karine Sousa</t>
+          <t>Kaique Souza</t>
         </is>
       </c>
       <c r="H989" t="inlineStr">
@@ -50149,13 +50145,13 @@
         </is>
       </c>
       <c r="I989" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J989" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="K989" t="n">
-        <v>66</v>
+        <v>89</v>
       </c>
     </row>
     <row r="990">
@@ -50191,22 +50187,22 @@
       </c>
       <c r="G990" t="inlineStr">
         <is>
-          <t>Laysla Alves</t>
+          <t>Karine Sousa</t>
         </is>
       </c>
       <c r="H990" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I990" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J990" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="K990" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
     </row>
     <row r="991">
@@ -50242,22 +50238,22 @@
       </c>
       <c r="G991" t="inlineStr">
         <is>
-          <t>Luana Marques</t>
+          <t>Laysla Alves</t>
         </is>
       </c>
       <c r="H991" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I991" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J991" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K991" t="n">
-        <v>19</v>
+        <v>60</v>
       </c>
     </row>
     <row r="992">
@@ -50293,7 +50289,7 @@
       </c>
       <c r="G992" t="inlineStr">
         <is>
-          <t>Maria Pires</t>
+          <t>Luana Marques</t>
         </is>
       </c>
       <c r="H992" t="inlineStr">
@@ -50302,13 +50298,13 @@
         </is>
       </c>
       <c r="I992" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J992" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="K992" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="993">
@@ -50344,22 +50340,22 @@
       </c>
       <c r="G993" t="inlineStr">
         <is>
-          <t>Mauricio Lermen</t>
+          <t>Maria Pires</t>
         </is>
       </c>
       <c r="H993" t="inlineStr">
         <is>
-          <t>Mauricio Lermen</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I993" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J993" t="n">
+        <v>21</v>
+      </c>
+      <c r="K993" t="n">
         <v>1</v>
-      </c>
-      <c r="K993" t="n">
-        <v>14</v>
       </c>
     </row>
     <row r="994">
@@ -50395,22 +50391,22 @@
       </c>
       <c r="G994" t="inlineStr">
         <is>
-          <t>Micaele Cordeiro</t>
+          <t>Mauricio Lermen</t>
         </is>
       </c>
       <c r="H994" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>Mauricio Lermen</t>
         </is>
       </c>
       <c r="I994" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J994" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="K994" t="n">
-        <v>95</v>
+        <v>14</v>
       </c>
     </row>
     <row r="995">
@@ -50446,7 +50442,7 @@
       </c>
       <c r="G995" t="inlineStr">
         <is>
-          <t>Michele Silva</t>
+          <t>Micaele Cordeiro</t>
         </is>
       </c>
       <c r="H995" t="inlineStr">
@@ -50455,13 +50451,13 @@
         </is>
       </c>
       <c r="I995" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J995" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K995" t="n">
-        <v>80</v>
+        <v>102</v>
       </c>
     </row>
     <row r="996">
@@ -50497,18 +50493,22 @@
       </c>
       <c r="G996" t="inlineStr">
         <is>
-          <t>Mikael Teixeira</t>
-        </is>
-      </c>
-      <c r="H996" t="inlineStr"/>
+          <t>Michele Silva</t>
+        </is>
+      </c>
+      <c r="H996" t="inlineStr">
+        <is>
+          <t>Sara Cavalheiro</t>
+        </is>
+      </c>
       <c r="I996" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J996" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="K996" t="n">
-        <v>4</v>
+        <v>83</v>
       </c>
     </row>
     <row r="997">
@@ -50544,22 +50544,18 @@
       </c>
       <c r="G997" t="inlineStr">
         <is>
-          <t>Murilo Marques</t>
-        </is>
-      </c>
-      <c r="H997" t="inlineStr">
-        <is>
-          <t>David Bragança</t>
-        </is>
-      </c>
+          <t>Mikael Teixeira</t>
+        </is>
+      </c>
+      <c r="H997" t="inlineStr"/>
       <c r="I997" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J997" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K997" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
     </row>
     <row r="998">
@@ -50595,22 +50591,22 @@
       </c>
       <c r="G998" t="inlineStr">
         <is>
-          <t>Natalia Batista</t>
+          <t>Murilo Marques</t>
         </is>
       </c>
       <c r="H998" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I998" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J998" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="K998" t="n">
-        <v>110</v>
+        <v>53</v>
       </c>
     </row>
     <row r="999">
@@ -50646,22 +50642,22 @@
       </c>
       <c r="G999" t="inlineStr">
         <is>
-          <t>Natalia Silva</t>
+          <t>Natalia Batista</t>
         </is>
       </c>
       <c r="H999" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I999" t="n">
         <v>0</v>
       </c>
       <c r="J999" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="K999" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="1000">
@@ -50697,22 +50693,22 @@
       </c>
       <c r="G1000" t="inlineStr">
         <is>
-          <t>Oliene Mariano</t>
+          <t>Natalia Silva</t>
         </is>
       </c>
       <c r="H1000" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I1000" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1000" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="K1000" t="n">
-        <v>75</v>
+        <v>109</v>
       </c>
     </row>
     <row r="1001">
@@ -50748,22 +50744,22 @@
       </c>
       <c r="G1001" t="inlineStr">
         <is>
-          <t>Priscila Aguiar</t>
+          <t>Oliene Mariano</t>
         </is>
       </c>
       <c r="H1001" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I1001" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="J1001" t="n">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="K1001" t="n">
-        <v>112</v>
+        <v>97</v>
       </c>
     </row>
     <row r="1002">
@@ -50799,7 +50795,7 @@
       </c>
       <c r="G1002" t="inlineStr">
         <is>
-          <t>Rebeca Ribeiro</t>
+          <t>Priscila Aguiar</t>
         </is>
       </c>
       <c r="H1002" t="inlineStr">
@@ -50808,13 +50804,13 @@
         </is>
       </c>
       <c r="I1002" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J1002" t="n">
-        <v>6</v>
+        <v>59</v>
       </c>
       <c r="K1002" t="n">
-        <v>66</v>
+        <v>112</v>
       </c>
     </row>
     <row r="1003">
@@ -50850,7 +50846,7 @@
       </c>
       <c r="G1003" t="inlineStr">
         <is>
-          <t>Roberta Souza</t>
+          <t>Rebeca Ribeiro</t>
         </is>
       </c>
       <c r="H1003" t="inlineStr">
@@ -50859,13 +50855,13 @@
         </is>
       </c>
       <c r="I1003" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J1003" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="K1003" t="n">
-        <v>99</v>
+        <v>66</v>
       </c>
     </row>
     <row r="1004">
@@ -50901,7 +50897,7 @@
       </c>
       <c r="G1004" t="inlineStr">
         <is>
-          <t>Ronildo Santos</t>
+          <t>Roberta Souza</t>
         </is>
       </c>
       <c r="H1004" t="inlineStr">
@@ -50910,13 +50906,13 @@
         </is>
       </c>
       <c r="I1004" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J1004" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="K1004" t="n">
-        <v>6</v>
+        <v>99</v>
       </c>
     </row>
     <row r="1005">
@@ -50952,22 +50948,22 @@
       </c>
       <c r="G1005" t="inlineStr">
         <is>
-          <t>Rozania Santos</t>
+          <t>Ronildo Santos</t>
         </is>
       </c>
       <c r="H1005" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I1005" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J1005" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="K1005" t="n">
-        <v>126</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1006">
@@ -51003,22 +50999,22 @@
       </c>
       <c r="G1006" t="inlineStr">
         <is>
-          <t>Santos Karina</t>
+          <t>Rozania Santos</t>
         </is>
       </c>
       <c r="H1006" t="inlineStr">
         <is>
-          <t>Leandro Matos</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I1006" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="J1006" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="K1006" t="n">
-        <v>2</v>
+        <v>140</v>
       </c>
     </row>
     <row r="1007">
@@ -51054,22 +51050,22 @@
       </c>
       <c r="G1007" t="inlineStr">
         <is>
-          <t>Sibelly Pereira</t>
+          <t>Santos Karina</t>
         </is>
       </c>
       <c r="H1007" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Leandro Matos</t>
         </is>
       </c>
       <c r="I1007" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J1007" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K1007" t="n">
-        <v>69</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1008">
@@ -51105,22 +51101,22 @@
       </c>
       <c r="G1008" t="inlineStr">
         <is>
-          <t>Tania Luz</t>
+          <t>Sibelly Pereira</t>
         </is>
       </c>
       <c r="H1008" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I1008" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J1008" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K1008" t="n">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="1009">
@@ -51156,22 +51152,22 @@
       </c>
       <c r="G1009" t="inlineStr">
         <is>
-          <t>Vitor Guedes</t>
+          <t>Tania Luz</t>
         </is>
       </c>
       <c r="H1009" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I1009" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J1009" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="K1009" t="n">
-        <v>134</v>
+        <v>77</v>
       </c>
     </row>
     <row r="1010">
@@ -51202,27 +51198,27 @@
       </c>
       <c r="F1010" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="G1010" t="inlineStr">
         <is>
-          <t>Andrea Medeiros</t>
+          <t>Vitor Guedes</t>
         </is>
       </c>
       <c r="H1010" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I1010" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J1010" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="K1010" t="n">
-        <v>62</v>
+        <v>134</v>
       </c>
     </row>
     <row r="1011">
@@ -51258,7 +51254,7 @@
       </c>
       <c r="G1011" t="inlineStr">
         <is>
-          <t>Caroline Nascimento</t>
+          <t>Andrea Medeiros</t>
         </is>
       </c>
       <c r="H1011" t="inlineStr">
@@ -51267,13 +51263,13 @@
         </is>
       </c>
       <c r="I1011" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J1011" t="n">
-        <v>95</v>
+        <v>28</v>
       </c>
       <c r="K1011" t="n">
-        <v>148</v>
+        <v>66</v>
       </c>
     </row>
     <row r="1012">
@@ -51309,7 +51305,7 @@
       </c>
       <c r="G1012" t="inlineStr">
         <is>
-          <t>Cristiana Grizostomo</t>
+          <t>Caroline Nascimento</t>
         </is>
       </c>
       <c r="H1012" t="inlineStr">
@@ -51318,13 +51314,13 @@
         </is>
       </c>
       <c r="I1012" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J1012" t="n">
-        <v>24</v>
+        <v>95</v>
       </c>
       <c r="K1012" t="n">
-        <v>56</v>
+        <v>148</v>
       </c>
     </row>
     <row r="1013">
@@ -51360,18 +51356,22 @@
       </c>
       <c r="G1013" t="inlineStr">
         <is>
-          <t>Denis Reis</t>
-        </is>
-      </c>
-      <c r="H1013" t="inlineStr"/>
+          <t>Cristiana Grizostomo</t>
+        </is>
+      </c>
+      <c r="H1013" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
       <c r="I1013" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1013" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K1013" t="n">
-        <v>89</v>
+        <v>57</v>
       </c>
     </row>
     <row r="1014">
@@ -51407,22 +51407,18 @@
       </c>
       <c r="G1014" t="inlineStr">
         <is>
-          <t>Eliane Moreira</t>
-        </is>
-      </c>
-      <c r="H1014" t="inlineStr">
-        <is>
-          <t>Nayara Oliveira</t>
-        </is>
-      </c>
+          <t>Denis Reis</t>
+        </is>
+      </c>
+      <c r="H1014" t="inlineStr"/>
       <c r="I1014" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J1014" t="n">
-        <v>64</v>
+        <v>22</v>
       </c>
       <c r="K1014" t="n">
-        <v>127</v>
+        <v>89</v>
       </c>
     </row>
     <row r="1015">
@@ -51458,7 +51454,7 @@
       </c>
       <c r="G1015" t="inlineStr">
         <is>
-          <t>Gustavo Tonan</t>
+          <t>Eliane Moreira</t>
         </is>
       </c>
       <c r="H1015" t="inlineStr">
@@ -51467,13 +51463,13 @@
         </is>
       </c>
       <c r="I1015" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J1015" t="n">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="K1015" t="n">
-        <v>97</v>
+        <v>130</v>
       </c>
     </row>
     <row r="1016">
@@ -51509,7 +51505,7 @@
       </c>
       <c r="G1016" t="inlineStr">
         <is>
-          <t>Jonatan Hayashibara</t>
+          <t>Gustavo Tonan</t>
         </is>
       </c>
       <c r="H1016" t="inlineStr">
@@ -51518,13 +51514,13 @@
         </is>
       </c>
       <c r="I1016" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="J1016" t="n">
-        <v>320</v>
+        <v>47</v>
       </c>
       <c r="K1016" t="n">
-        <v>432</v>
+        <v>98</v>
       </c>
     </row>
     <row r="1017">
@@ -51560,7 +51556,7 @@
       </c>
       <c r="G1017" t="inlineStr">
         <is>
-          <t>Lais Arruda</t>
+          <t>Jonatan Hayashibara</t>
         </is>
       </c>
       <c r="H1017" t="inlineStr">
@@ -51569,13 +51565,13 @@
         </is>
       </c>
       <c r="I1017" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="J1017" t="n">
-        <v>50</v>
+        <v>320</v>
       </c>
       <c r="K1017" t="n">
-        <v>108</v>
+        <v>432</v>
       </c>
     </row>
     <row r="1018">
@@ -51611,7 +51607,7 @@
       </c>
       <c r="G1018" t="inlineStr">
         <is>
-          <t>Luan Batista</t>
+          <t>Lais Arruda</t>
         </is>
       </c>
       <c r="H1018" t="inlineStr">
@@ -51620,13 +51616,13 @@
         </is>
       </c>
       <c r="I1018" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J1018" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="K1018" t="n">
-        <v>79</v>
+        <v>110</v>
       </c>
     </row>
     <row r="1019">
@@ -51662,7 +51658,7 @@
       </c>
       <c r="G1019" t="inlineStr">
         <is>
-          <t>Maria Garcia</t>
+          <t>Luan Batista</t>
         </is>
       </c>
       <c r="H1019" t="inlineStr">
@@ -51671,13 +51667,13 @@
         </is>
       </c>
       <c r="I1019" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J1019" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K1019" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
     <row r="1020">
@@ -51713,7 +51709,7 @@
       </c>
       <c r="G1020" t="inlineStr">
         <is>
-          <t>Priscila Volpe</t>
+          <t>Maria Garcia</t>
         </is>
       </c>
       <c r="H1020" t="inlineStr">
@@ -51722,13 +51718,13 @@
         </is>
       </c>
       <c r="I1020" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J1020" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="K1020" t="n">
-        <v>11</v>
+        <v>78</v>
       </c>
     </row>
     <row r="1021">
@@ -51764,7 +51760,7 @@
       </c>
       <c r="G1021" t="inlineStr">
         <is>
-          <t>Rodrigo Souza</t>
+          <t>Priscila Volpe</t>
         </is>
       </c>
       <c r="H1021" t="inlineStr">
@@ -51773,13 +51769,13 @@
         </is>
       </c>
       <c r="I1021" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J1021" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="K1021" t="n">
-        <v>92</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1022">
@@ -51815,7 +51811,7 @@
       </c>
       <c r="G1022" t="inlineStr">
         <is>
-          <t>Romario Silva</t>
+          <t>Rodrigo Souza</t>
         </is>
       </c>
       <c r="H1022" t="inlineStr">
@@ -51824,13 +51820,13 @@
         </is>
       </c>
       <c r="I1022" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="J1022" t="n">
-        <v>103</v>
+        <v>68</v>
       </c>
       <c r="K1022" t="n">
-        <v>228</v>
+        <v>92</v>
       </c>
     </row>
     <row r="1023">
@@ -51866,7 +51862,7 @@
       </c>
       <c r="G1023" t="inlineStr">
         <is>
-          <t>Rosilene Santos</t>
+          <t>Romario Silva</t>
         </is>
       </c>
       <c r="H1023" t="inlineStr">
@@ -51875,13 +51871,13 @@
         </is>
       </c>
       <c r="I1023" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J1023" t="n">
-        <v>45</v>
+        <v>105</v>
       </c>
       <c r="K1023" t="n">
-        <v>80</v>
+        <v>230</v>
       </c>
     </row>
     <row r="1024">
@@ -51917,7 +51913,7 @@
       </c>
       <c r="G1024" t="inlineStr">
         <is>
-          <t>Suede Gomes</t>
+          <t>Rosilene Santos</t>
         </is>
       </c>
       <c r="H1024" t="inlineStr">
@@ -51926,13 +51922,13 @@
         </is>
       </c>
       <c r="I1024" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J1024" t="n">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="K1024" t="n">
-        <v>44</v>
+        <v>80</v>
       </c>
     </row>
     <row r="1025">
@@ -51968,7 +51964,7 @@
       </c>
       <c r="G1025" t="inlineStr">
         <is>
-          <t>Taina Silva</t>
+          <t>Suede Gomes</t>
         </is>
       </c>
       <c r="H1025" t="inlineStr">
@@ -51977,13 +51973,13 @@
         </is>
       </c>
       <c r="I1025" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J1025" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="K1025" t="n">
-        <v>64</v>
+        <v>44</v>
       </c>
     </row>
     <row r="1026">
@@ -52019,7 +52015,7 @@
       </c>
       <c r="G1026" t="inlineStr">
         <is>
-          <t>Thayna Melo</t>
+          <t>Taina Silva</t>
         </is>
       </c>
       <c r="H1026" t="inlineStr">
@@ -52028,13 +52024,13 @@
         </is>
       </c>
       <c r="I1026" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J1026" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K1026" t="n">
-        <v>53</v>
+        <v>64</v>
       </c>
     </row>
     <row r="1027">
@@ -52070,7 +52066,7 @@
       </c>
       <c r="G1027" t="inlineStr">
         <is>
-          <t>Vanessa Santana</t>
+          <t>Thayna Melo</t>
         </is>
       </c>
       <c r="H1027" t="inlineStr">
@@ -52079,13 +52075,13 @@
         </is>
       </c>
       <c r="I1027" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="J1027" t="n">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="K1027" t="n">
-        <v>179</v>
+        <v>53</v>
       </c>
     </row>
     <row r="1028">
@@ -52116,27 +52112,27 @@
       </c>
       <c r="F1028" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="G1028" t="inlineStr">
         <is>
-          <t>Alaine Neres</t>
+          <t>Vanessa Santana</t>
         </is>
       </c>
       <c r="H1028" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
       <c r="I1028" t="n">
-        <v>56</v>
+        <v>11</v>
       </c>
       <c r="J1028" t="n">
-        <v>91</v>
+        <v>61</v>
       </c>
       <c r="K1028" t="n">
-        <v>148</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1029">
@@ -52172,22 +52168,22 @@
       </c>
       <c r="G1029" t="inlineStr">
         <is>
-          <t>Andre Silva</t>
+          <t>Alaine Neres</t>
         </is>
       </c>
       <c r="H1029" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I1029" t="n">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="J1029" t="n">
-        <v>9</v>
+        <v>91</v>
       </c>
       <c r="K1029" t="n">
-        <v>66</v>
+        <v>148</v>
       </c>
     </row>
     <row r="1030">
@@ -52223,22 +52219,22 @@
       </c>
       <c r="G1030" t="inlineStr">
         <is>
-          <t>Anna Ramalho</t>
+          <t>Andre Silva</t>
         </is>
       </c>
       <c r="H1030" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I1030" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J1030" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="K1030" t="n">
-        <v>78</v>
+        <v>66</v>
       </c>
     </row>
     <row r="1031">
@@ -52274,7 +52270,7 @@
       </c>
       <c r="G1031" t="inlineStr">
         <is>
-          <t>Beatriz Ferreira</t>
+          <t>Anna Ramalho</t>
         </is>
       </c>
       <c r="H1031" t="inlineStr">
@@ -52283,13 +52279,13 @@
         </is>
       </c>
       <c r="I1031" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="J1031" t="n">
-        <v>86</v>
+        <v>23</v>
       </c>
       <c r="K1031" t="n">
-        <v>125</v>
+        <v>79</v>
       </c>
     </row>
     <row r="1032">
@@ -52325,22 +52321,22 @@
       </c>
       <c r="G1032" t="inlineStr">
         <is>
-          <t>Brenda Batista</t>
+          <t>Beatriz Ferreira</t>
         </is>
       </c>
       <c r="H1032" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="I1032" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J1032" t="n">
-        <v>28</v>
+        <v>86</v>
       </c>
       <c r="K1032" t="n">
-        <v>52</v>
+        <v>125</v>
       </c>
     </row>
     <row r="1033">
@@ -52376,22 +52372,22 @@
       </c>
       <c r="G1033" t="inlineStr">
         <is>
-          <t>Bruna Souza</t>
+          <t>Brenda Batista</t>
         </is>
       </c>
       <c r="H1033" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I1033" t="n">
         <v>1</v>
       </c>
       <c r="J1033" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K1033" t="n">
-        <v>75</v>
+        <v>53</v>
       </c>
     </row>
     <row r="1034">
@@ -52427,22 +52423,22 @@
       </c>
       <c r="G1034" t="inlineStr">
         <is>
-          <t>Bruno Henrique</t>
+          <t>Bruna Souza</t>
         </is>
       </c>
       <c r="H1034" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I1034" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1034" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="K1034" t="n">
-        <v>102</v>
+        <v>75</v>
       </c>
     </row>
     <row r="1035">
@@ -52478,18 +52474,22 @@
       </c>
       <c r="G1035" t="inlineStr">
         <is>
-          <t>Claudineia Rodrigues</t>
-        </is>
-      </c>
-      <c r="H1035" t="inlineStr"/>
+          <t>Bruno Henrique</t>
+        </is>
+      </c>
+      <c r="H1035" t="inlineStr">
+        <is>
+          <t>Lorrane Santos</t>
+        </is>
+      </c>
       <c r="I1035" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J1035" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="K1035" t="n">
-        <v>178</v>
+        <v>121</v>
       </c>
     </row>
     <row r="1036">
@@ -52525,22 +52525,18 @@
       </c>
       <c r="G1036" t="inlineStr">
         <is>
-          <t>Cristina Leite</t>
-        </is>
-      </c>
-      <c r="H1036" t="inlineStr">
-        <is>
-          <t>Ricardo Fischer</t>
-        </is>
-      </c>
+          <t>Claudineia Rodrigues</t>
+        </is>
+      </c>
+      <c r="H1036" t="inlineStr"/>
       <c r="I1036" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J1036" t="n">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="K1036" t="n">
-        <v>134</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1037">
@@ -52576,22 +52572,22 @@
       </c>
       <c r="G1037" t="inlineStr">
         <is>
-          <t>Davi Santos</t>
+          <t>Cristina Leite</t>
         </is>
       </c>
       <c r="H1037" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="I1037" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J1037" t="n">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="K1037" t="n">
-        <v>87</v>
+        <v>134</v>
       </c>
     </row>
     <row r="1038">
@@ -52627,22 +52623,22 @@
       </c>
       <c r="G1038" t="inlineStr">
         <is>
-          <t>Deleia Oliveira</t>
+          <t>Davi Santos</t>
         </is>
       </c>
       <c r="H1038" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I1038" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="J1038" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="K1038" t="n">
-        <v>95</v>
+        <v>82</v>
       </c>
     </row>
     <row r="1039">
@@ -52678,22 +52674,22 @@
       </c>
       <c r="G1039" t="inlineStr">
         <is>
-          <t>Diego Pereira</t>
+          <t>Deleia Oliveira</t>
         </is>
       </c>
       <c r="H1039" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I1039" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J1039" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="K1039" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="1040">
@@ -52729,22 +52725,22 @@
       </c>
       <c r="G1040" t="inlineStr">
         <is>
-          <t>Eduardo Lopes</t>
+          <t>Diego Pereira</t>
         </is>
       </c>
       <c r="H1040" t="inlineStr">
         <is>
-          <t>Idna Sousa</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I1040" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J1040" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="K1040" t="n">
-        <v>16</v>
+        <v>94</v>
       </c>
     </row>
     <row r="1041">
@@ -52780,22 +52776,22 @@
       </c>
       <c r="G1041" t="inlineStr">
         <is>
-          <t>Gislaine Lima</t>
+          <t>Eduardo Lopes</t>
         </is>
       </c>
       <c r="H1041" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Idna Sousa</t>
         </is>
       </c>
       <c r="I1041" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J1041" t="n">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="K1041" t="n">
-        <v>90</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1042">
@@ -52831,22 +52827,22 @@
       </c>
       <c r="G1042" t="inlineStr">
         <is>
-          <t>Gustavo Santos</t>
+          <t>Gislaine Lima</t>
         </is>
       </c>
       <c r="H1042" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I1042" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="J1042" t="n">
-        <v>110</v>
+        <v>51</v>
       </c>
       <c r="K1042" t="n">
-        <v>218</v>
+        <v>90</v>
       </c>
     </row>
     <row r="1043">
@@ -52882,22 +52878,22 @@
       </c>
       <c r="G1043" t="inlineStr">
         <is>
-          <t>Igor Valezi</t>
+          <t>Gustavo Santos</t>
         </is>
       </c>
       <c r="H1043" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="I1043" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="J1043" t="n">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="K1043" t="n">
-        <v>74</v>
+        <v>218</v>
       </c>
     </row>
     <row r="1044">
@@ -52933,22 +52929,22 @@
       </c>
       <c r="G1044" t="inlineStr">
         <is>
-          <t>Izabely Araujo</t>
+          <t>Igor Valezi</t>
         </is>
       </c>
       <c r="H1044" t="inlineStr">
         <is>
-          <t>Idna Sousa</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I1044" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="J1044" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="K1044" t="n">
-        <v>9</v>
+        <v>87</v>
       </c>
     </row>
     <row r="1045">
@@ -52984,22 +52980,22 @@
       </c>
       <c r="G1045" t="inlineStr">
         <is>
-          <t>Joanna Costa</t>
+          <t>Izabely Araujo</t>
         </is>
       </c>
       <c r="H1045" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Idna Sousa</t>
         </is>
       </c>
       <c r="I1045" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1045" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="K1045" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1046">
@@ -53035,22 +53031,22 @@
       </c>
       <c r="G1046" t="inlineStr">
         <is>
-          <t>Jose Borges</t>
+          <t>Joanna Costa</t>
         </is>
       </c>
       <c r="H1046" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I1046" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J1046" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K1046" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1047">
@@ -53086,22 +53082,22 @@
       </c>
       <c r="G1047" t="inlineStr">
         <is>
-          <t>Jose Natan</t>
+          <t>Jose Borges</t>
         </is>
       </c>
       <c r="H1047" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="I1047" t="n">
         <v>1</v>
       </c>
       <c r="J1047" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K1047" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1048">
@@ -53137,7 +53133,7 @@
       </c>
       <c r="G1048" t="inlineStr">
         <is>
-          <t>João Oliveira</t>
+          <t>Jose Natan</t>
         </is>
       </c>
       <c r="H1048" t="inlineStr">
@@ -53149,10 +53145,10 @@
         <v>2</v>
       </c>
       <c r="J1048" t="n">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="K1048" t="n">
-        <v>16</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1049">
@@ -53188,22 +53184,22 @@
       </c>
       <c r="G1049" t="inlineStr">
         <is>
-          <t>Juan Ribeiro</t>
+          <t>João Oliveira</t>
         </is>
       </c>
       <c r="H1049" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I1049" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J1049" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="K1049" t="n">
-        <v>84</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1050">
@@ -53239,22 +53235,22 @@
       </c>
       <c r="G1050" t="inlineStr">
         <is>
-          <t>Juliana Valeria</t>
+          <t>Juan Ribeiro</t>
         </is>
       </c>
       <c r="H1050" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I1050" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J1050" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K1050" t="n">
-        <v>99</v>
+        <v>84</v>
       </c>
     </row>
     <row r="1051">
@@ -53290,7 +53286,7 @@
       </c>
       <c r="G1051" t="inlineStr">
         <is>
-          <t>Juliane Vaz</t>
+          <t>Juliana Valeria</t>
         </is>
       </c>
       <c r="H1051" t="inlineStr">
@@ -53299,13 +53295,13 @@
         </is>
       </c>
       <c r="I1051" t="n">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="J1051" t="n">
-        <v>135</v>
+        <v>39</v>
       </c>
       <c r="K1051" t="n">
-        <v>235</v>
+        <v>101</v>
       </c>
     </row>
     <row r="1052">
@@ -53341,22 +53337,22 @@
       </c>
       <c r="G1052" t="inlineStr">
         <is>
-          <t>Katia Xavier</t>
+          <t>Juliane Vaz</t>
         </is>
       </c>
       <c r="H1052" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I1052" t="n">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="J1052" t="n">
-        <v>44</v>
+        <v>163</v>
       </c>
       <c r="K1052" t="n">
-        <v>95</v>
+        <v>263</v>
       </c>
     </row>
     <row r="1053">
@@ -53392,22 +53388,22 @@
       </c>
       <c r="G1053" t="inlineStr">
         <is>
-          <t>Larissa Félix</t>
+          <t>Katia Xavier</t>
         </is>
       </c>
       <c r="H1053" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I1053" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J1053" t="n">
-        <v>96</v>
+        <v>50</v>
       </c>
       <c r="K1053" t="n">
-        <v>159</v>
+        <v>101</v>
       </c>
     </row>
     <row r="1054">
@@ -53443,22 +53439,22 @@
       </c>
       <c r="G1054" t="inlineStr">
         <is>
-          <t>Léia de Oliveira</t>
+          <t>Larissa Félix</t>
         </is>
       </c>
       <c r="H1054" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I1054" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J1054" t="n">
-        <v>29</v>
+        <v>96</v>
       </c>
       <c r="K1054" t="n">
-        <v>116</v>
+        <v>159</v>
       </c>
     </row>
     <row r="1055">
@@ -53494,7 +53490,7 @@
       </c>
       <c r="G1055" t="inlineStr">
         <is>
-          <t>Maria Gualberto</t>
+          <t>Léia de Oliveira</t>
         </is>
       </c>
       <c r="H1055" t="inlineStr">
@@ -53503,13 +53499,13 @@
         </is>
       </c>
       <c r="I1055" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J1055" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="K1055" t="n">
-        <v>97</v>
+        <v>117</v>
       </c>
     </row>
     <row r="1056">
@@ -53545,22 +53541,22 @@
       </c>
       <c r="G1056" t="inlineStr">
         <is>
-          <t>Nathany Silva</t>
+          <t>Maria Gualberto</t>
         </is>
       </c>
       <c r="H1056" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I1056" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J1056" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K1056" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
     </row>
     <row r="1057">
@@ -53596,22 +53592,22 @@
       </c>
       <c r="G1057" t="inlineStr">
         <is>
-          <t>Priscila Moreira</t>
+          <t>Nathany Silva</t>
         </is>
       </c>
       <c r="H1057" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I1057" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="J1057" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K1057" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1058">
@@ -53647,22 +53643,22 @@
       </c>
       <c r="G1058" t="inlineStr">
         <is>
-          <t>Regiane Santos</t>
+          <t>Priscila Moreira</t>
         </is>
       </c>
       <c r="H1058" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="I1058" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="J1058" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="K1058" t="n">
-        <v>57</v>
+        <v>84</v>
       </c>
     </row>
     <row r="1059">
@@ -53698,22 +53694,22 @@
       </c>
       <c r="G1059" t="inlineStr">
         <is>
-          <t>Shofia Gomes</t>
+          <t>Regiane Santos</t>
         </is>
       </c>
       <c r="H1059" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I1059" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J1059" t="n">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="K1059" t="n">
-        <v>124</v>
+        <v>57</v>
       </c>
     </row>
     <row r="1060">
@@ -53749,22 +53745,22 @@
       </c>
       <c r="G1060" t="inlineStr">
         <is>
-          <t>Vanessa Tavares</t>
+          <t>Shofia Gomes</t>
         </is>
       </c>
       <c r="H1060" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="I1060" t="n">
         <v>5</v>
       </c>
       <c r="J1060" t="n">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="K1060" t="n">
-        <v>65</v>
+        <v>125</v>
       </c>
     </row>
     <row r="1061">
@@ -53800,7 +53796,7 @@
       </c>
       <c r="G1061" t="inlineStr">
         <is>
-          <t>Willian Luz</t>
+          <t>Vanessa Tavares</t>
         </is>
       </c>
       <c r="H1061" t="inlineStr">
@@ -53809,13 +53805,13 @@
         </is>
       </c>
       <c r="I1061" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J1061" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="K1061" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="1062">
@@ -53851,7 +53847,7 @@
       </c>
       <c r="G1062" t="inlineStr">
         <is>
-          <t>Yasmim Oliveira</t>
+          <t>Willian Luz</t>
         </is>
       </c>
       <c r="H1062" t="inlineStr">
@@ -53860,13 +53856,13 @@
         </is>
       </c>
       <c r="I1062" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J1062" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="K1062" t="n">
-        <v>40</v>
+        <v>75</v>
       </c>
     </row>
     <row r="1063">
@@ -53897,23 +53893,27 @@
       </c>
       <c r="F1063" t="inlineStr">
         <is>
-          <t>ESCRITA FISCAL (Outsourcing)</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="G1063" t="inlineStr">
         <is>
-          <t>Claudineia Rodrigues</t>
-        </is>
-      </c>
-      <c r="H1063" t="inlineStr"/>
+          <t>Yasmim Oliveira</t>
+        </is>
+      </c>
+      <c r="H1063" t="inlineStr">
+        <is>
+          <t>Larice Souza</t>
+        </is>
+      </c>
       <c r="I1063" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J1063" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K1063" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="1064">
@@ -53949,22 +53949,18 @@
       </c>
       <c r="G1064" t="inlineStr">
         <is>
-          <t>Diego Pereira</t>
-        </is>
-      </c>
-      <c r="H1064" t="inlineStr">
-        <is>
-          <t>Thaiza Oliveira</t>
-        </is>
-      </c>
+          <t>Claudineia Rodrigues</t>
+        </is>
+      </c>
+      <c r="H1064" t="inlineStr"/>
       <c r="I1064" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J1064" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K1064" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1065">
@@ -54000,22 +53996,22 @@
       </c>
       <c r="G1065" t="inlineStr">
         <is>
-          <t>Gislaine Lima</t>
+          <t>Diego Pereira</t>
         </is>
       </c>
       <c r="H1065" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I1065" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1065" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="K1065" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1066">
@@ -54051,7 +54047,7 @@
       </c>
       <c r="G1066" t="inlineStr">
         <is>
-          <t>Joanna Costa</t>
+          <t>Gislaine Lima</t>
         </is>
       </c>
       <c r="H1066" t="inlineStr">
@@ -54060,13 +54056,13 @@
         </is>
       </c>
       <c r="I1066" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J1066" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="K1066" t="n">
-        <v>47</v>
+        <v>32</v>
       </c>
     </row>
     <row r="1067">
@@ -54102,22 +54098,22 @@
       </c>
       <c r="G1067" t="inlineStr">
         <is>
-          <t>Jonatan Hayashibara</t>
+          <t>Joanna Costa</t>
         </is>
       </c>
       <c r="H1067" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I1067" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J1067" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="K1067" t="n">
-        <v>4</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1068">
@@ -54153,22 +54149,22 @@
       </c>
       <c r="G1068" t="inlineStr">
         <is>
-          <t>Jose Borges</t>
+          <t>Jonatan Hayashibara</t>
         </is>
       </c>
       <c r="H1068" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
       <c r="I1068" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J1068" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K1068" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1069">
@@ -54204,22 +54200,22 @@
       </c>
       <c r="G1069" t="inlineStr">
         <is>
-          <t>João Oliveira</t>
+          <t>Jose Borges</t>
         </is>
       </c>
       <c r="H1069" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="I1069" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1069" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K1069" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1070">
@@ -54255,7 +54251,7 @@
       </c>
       <c r="G1070" t="inlineStr">
         <is>
-          <t>Regiane Santos</t>
+          <t>João Oliveira</t>
         </is>
       </c>
       <c r="H1070" t="inlineStr">
@@ -54264,13 +54260,13 @@
         </is>
       </c>
       <c r="I1070" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J1070" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="K1070" t="n">
-        <v>16</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1071">
@@ -54306,7 +54302,7 @@
       </c>
       <c r="G1071" t="inlineStr">
         <is>
-          <t>Yasmim Oliveira</t>
+          <t>Regiane Santos</t>
         </is>
       </c>
       <c r="H1071" t="inlineStr">
@@ -54315,13 +54311,13 @@
         </is>
       </c>
       <c r="I1071" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1071" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K1071" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1072">
@@ -54352,23 +54348,27 @@
       </c>
       <c r="F1072" t="inlineStr">
         <is>
-          <t>FIN - CONTÁBIL</t>
+          <t>ESCRITA FISCAL (Outsourcing)</t>
         </is>
       </c>
       <c r="G1072" t="inlineStr">
         <is>
-          <t>Daniele Faria</t>
-        </is>
-      </c>
-      <c r="H1072" t="inlineStr"/>
+          <t>Yasmim Oliveira</t>
+        </is>
+      </c>
+      <c r="H1072" t="inlineStr">
+        <is>
+          <t>Larice Souza</t>
+        </is>
+      </c>
       <c r="I1072" t="n">
         <v>0</v>
       </c>
       <c r="J1072" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="K1072" t="n">
-        <v>62</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1073">
@@ -54399,23 +54399,23 @@
       </c>
       <c r="F1073" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>FIN - CONTÁBIL</t>
         </is>
       </c>
       <c r="G1073" t="inlineStr">
         <is>
-          <t>Ana Santana</t>
+          <t>Daniele Faria</t>
         </is>
       </c>
       <c r="H1073" t="inlineStr"/>
       <c r="I1073" t="n">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="J1073" t="n">
-        <v>177</v>
+        <v>20</v>
       </c>
       <c r="K1073" t="n">
-        <v>446</v>
+        <v>62</v>
       </c>
     </row>
     <row r="1074">
@@ -54451,18 +54451,18 @@
       </c>
       <c r="G1074" t="inlineStr">
         <is>
-          <t>Andre Coelho</t>
+          <t>Ana Santana</t>
         </is>
       </c>
       <c r="H1074" t="inlineStr"/>
       <c r="I1074" t="n">
-        <v>12</v>
+        <v>352</v>
       </c>
       <c r="J1074" t="n">
-        <v>12</v>
+        <v>381</v>
       </c>
       <c r="K1074" t="n">
-        <v>16</v>
+        <v>585</v>
       </c>
     </row>
     <row r="1075">
@@ -54498,18 +54498,18 @@
       </c>
       <c r="G1075" t="inlineStr">
         <is>
-          <t>Bianca Castro</t>
+          <t>Andre Coelho</t>
         </is>
       </c>
       <c r="H1075" t="inlineStr"/>
       <c r="I1075" t="n">
-        <v>114</v>
+        <v>12</v>
       </c>
       <c r="J1075" t="n">
-        <v>136</v>
+        <v>12</v>
       </c>
       <c r="K1075" t="n">
-        <v>368</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1076">
@@ -54545,18 +54545,18 @@
       </c>
       <c r="G1076" t="inlineStr">
         <is>
-          <t>Bruna Costa</t>
+          <t>Bianca Castro</t>
         </is>
       </c>
       <c r="H1076" t="inlineStr"/>
       <c r="I1076" t="n">
-        <v>21</v>
+        <v>243</v>
       </c>
       <c r="J1076" t="n">
-        <v>22</v>
+        <v>265</v>
       </c>
       <c r="K1076" t="n">
-        <v>32</v>
+        <v>459</v>
       </c>
     </row>
     <row r="1077">
@@ -54592,18 +54592,18 @@
       </c>
       <c r="G1077" t="inlineStr">
         <is>
-          <t>Daniela Silva</t>
+          <t>Bruna Costa</t>
         </is>
       </c>
       <c r="H1077" t="inlineStr"/>
       <c r="I1077" t="n">
-        <v>185</v>
+        <v>32</v>
       </c>
       <c r="J1077" t="n">
-        <v>189</v>
+        <v>33</v>
       </c>
       <c r="K1077" t="n">
-        <v>185</v>
+        <v>34</v>
       </c>
     </row>
     <row r="1078">
@@ -54639,18 +54639,18 @@
       </c>
       <c r="G1078" t="inlineStr">
         <is>
-          <t>Isabelli Afonso</t>
+          <t>Daniela Silva</t>
         </is>
       </c>
       <c r="H1078" t="inlineStr"/>
       <c r="I1078" t="n">
-        <v>90</v>
+        <v>301</v>
       </c>
       <c r="J1078" t="n">
-        <v>97</v>
+        <v>306</v>
       </c>
       <c r="K1078" t="n">
-        <v>116</v>
+        <v>302</v>
       </c>
     </row>
     <row r="1079">
@@ -54686,18 +54686,18 @@
       </c>
       <c r="G1079" t="inlineStr">
         <is>
-          <t>Jurema Damacena - SAC</t>
+          <t>Isabelli Afonso</t>
         </is>
       </c>
       <c r="H1079" t="inlineStr"/>
       <c r="I1079" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="J1079" t="n">
-        <v>0</v>
+        <v>217</v>
       </c>
       <c r="K1079" t="n">
-        <v>1</v>
+        <v>232</v>
       </c>
     </row>
     <row r="1080">
@@ -54733,18 +54733,18 @@
       </c>
       <c r="G1080" t="inlineStr">
         <is>
-          <t>Leticia Queiroz</t>
+          <t>Jurema Damacena - SAC</t>
         </is>
       </c>
       <c r="H1080" t="inlineStr"/>
       <c r="I1080" t="n">
-        <v>209</v>
+        <v>0</v>
       </c>
       <c r="J1080" t="n">
-        <v>204</v>
+        <v>0</v>
       </c>
       <c r="K1080" t="n">
-        <v>221</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1081">
@@ -54780,18 +54780,18 @@
       </c>
       <c r="G1081" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Leticia Queiroz</t>
         </is>
       </c>
       <c r="H1081" t="inlineStr"/>
       <c r="I1081" t="n">
-        <v>2</v>
+        <v>432</v>
       </c>
       <c r="J1081" t="n">
-        <v>2</v>
+        <v>424</v>
       </c>
       <c r="K1081" t="n">
-        <v>13</v>
+        <v>428</v>
       </c>
     </row>
     <row r="1082">
@@ -54827,18 +54827,18 @@
       </c>
       <c r="G1082" t="inlineStr">
         <is>
-          <t>Victoria Virgens</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="H1082" t="inlineStr"/>
       <c r="I1082" t="n">
-        <v>135</v>
+        <v>2</v>
       </c>
       <c r="J1082" t="n">
-        <v>152</v>
+        <v>2</v>
       </c>
       <c r="K1082" t="n">
-        <v>152</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1083">
@@ -54874,18 +54874,18 @@
       </c>
       <c r="G1083" t="inlineStr">
         <is>
-          <t>Yasmin Peixoto</t>
+          <t>Victoria Virgens</t>
         </is>
       </c>
       <c r="H1083" t="inlineStr"/>
       <c r="I1083" t="n">
-        <v>136</v>
+        <v>290</v>
       </c>
       <c r="J1083" t="n">
-        <v>149</v>
+        <v>307</v>
       </c>
       <c r="K1083" t="n">
-        <v>373</v>
+        <v>307</v>
       </c>
     </row>
     <row r="1084">
@@ -54916,23 +54916,23 @@
       </c>
       <c r="F1084" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="G1084" t="inlineStr">
         <is>
-          <t>Andre Coelho</t>
+          <t>Yasmin Peixoto</t>
         </is>
       </c>
       <c r="H1084" t="inlineStr"/>
       <c r="I1084" t="n">
-        <v>4</v>
+        <v>341</v>
       </c>
       <c r="J1084" t="n">
-        <v>4</v>
+        <v>354</v>
       </c>
       <c r="K1084" t="n">
-        <v>4</v>
+        <v>552</v>
       </c>
     </row>
     <row r="1085">
@@ -54968,18 +54968,18 @@
       </c>
       <c r="G1085" t="inlineStr">
         <is>
-          <t>Beatriz Rangel</t>
+          <t>Andre Coelho</t>
         </is>
       </c>
       <c r="H1085" t="inlineStr"/>
       <c r="I1085" t="n">
-        <v>83</v>
+        <v>4</v>
       </c>
       <c r="J1085" t="n">
-        <v>88</v>
+        <v>4</v>
       </c>
       <c r="K1085" t="n">
-        <v>283</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1086">
@@ -55015,18 +55015,18 @@
       </c>
       <c r="G1086" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
+          <t>Beatriz Rangel</t>
         </is>
       </c>
       <c r="H1086" t="inlineStr"/>
       <c r="I1086" t="n">
-        <v>185</v>
+        <v>217</v>
       </c>
       <c r="J1086" t="n">
-        <v>311</v>
+        <v>222</v>
       </c>
       <c r="K1086" t="n">
-        <v>363</v>
+        <v>372</v>
       </c>
     </row>
     <row r="1087">
@@ -55062,18 +55062,18 @@
       </c>
       <c r="G1087" t="inlineStr">
         <is>
-          <t>Cristiane Simões</t>
+          <t>Bruno Contieri</t>
         </is>
       </c>
       <c r="H1087" t="inlineStr"/>
       <c r="I1087" t="n">
-        <v>59</v>
+        <v>303</v>
       </c>
       <c r="J1087" t="n">
-        <v>194</v>
+        <v>429</v>
       </c>
       <c r="K1087" t="n">
-        <v>280</v>
+        <v>434</v>
       </c>
     </row>
     <row r="1088">
@@ -55109,18 +55109,18 @@
       </c>
       <c r="G1088" t="inlineStr">
         <is>
-          <t>Daniel Oliveira</t>
+          <t>Cristiane Simões</t>
         </is>
       </c>
       <c r="H1088" t="inlineStr"/>
       <c r="I1088" t="n">
-        <v>110</v>
+        <v>136</v>
       </c>
       <c r="J1088" t="n">
-        <v>223</v>
+        <v>271</v>
       </c>
       <c r="K1088" t="n">
-        <v>276</v>
+        <v>306</v>
       </c>
     </row>
     <row r="1089">
@@ -55156,18 +55156,18 @@
       </c>
       <c r="G1089" t="inlineStr">
         <is>
-          <t>Diego Lima</t>
+          <t>Daniel Oliveira</t>
         </is>
       </c>
       <c r="H1089" t="inlineStr"/>
       <c r="I1089" t="n">
-        <v>54</v>
+        <v>240</v>
       </c>
       <c r="J1089" t="n">
-        <v>86</v>
+        <v>353</v>
       </c>
       <c r="K1089" t="n">
-        <v>122</v>
+        <v>403</v>
       </c>
     </row>
     <row r="1090">
@@ -55203,18 +55203,18 @@
       </c>
       <c r="G1090" t="inlineStr">
         <is>
-          <t>Eduardo Aparicio</t>
+          <t>Diego Lima</t>
         </is>
       </c>
       <c r="H1090" t="inlineStr"/>
       <c r="I1090" t="n">
-        <v>1</v>
+        <v>123</v>
       </c>
       <c r="J1090" t="n">
-        <v>1</v>
+        <v>157</v>
       </c>
       <c r="K1090" t="n">
-        <v>1</v>
+        <v>164</v>
       </c>
     </row>
     <row r="1091">
@@ -55250,18 +55250,18 @@
       </c>
       <c r="G1091" t="inlineStr">
         <is>
-          <t>Karine Gusmão</t>
+          <t>Eduardo Aparicio</t>
         </is>
       </c>
       <c r="H1091" t="inlineStr"/>
       <c r="I1091" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="J1091" t="n">
-        <v>63</v>
+        <v>1</v>
       </c>
       <c r="K1091" t="n">
-        <v>44</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1092">
@@ -55297,18 +55297,18 @@
       </c>
       <c r="G1092" t="inlineStr">
         <is>
-          <t>Luiz Ferreira</t>
+          <t>Karine Gusmão</t>
         </is>
       </c>
       <c r="H1092" t="inlineStr"/>
       <c r="I1092" t="n">
-        <v>1</v>
+        <v>91</v>
       </c>
       <c r="J1092" t="n">
-        <v>9</v>
+        <v>112</v>
       </c>
       <c r="K1092" t="n">
-        <v>12</v>
+        <v>93</v>
       </c>
     </row>
     <row r="1093">
@@ -55344,18 +55344,18 @@
       </c>
       <c r="G1093" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Luiz Ferreira</t>
         </is>
       </c>
       <c r="H1093" t="inlineStr"/>
       <c r="I1093" t="n">
-        <v>79</v>
+        <v>10</v>
       </c>
       <c r="J1093" t="n">
-        <v>143</v>
+        <v>18</v>
       </c>
       <c r="K1093" t="n">
-        <v>180</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1094">
@@ -55391,18 +55391,18 @@
       </c>
       <c r="G1094" t="inlineStr">
         <is>
-          <t>Rodrigo Rego</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="H1094" t="inlineStr"/>
       <c r="I1094" t="n">
-        <v>202</v>
+        <v>146</v>
       </c>
       <c r="J1094" t="n">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="K1094" t="n">
-        <v>279</v>
+        <v>221</v>
       </c>
     </row>
     <row r="1095">
@@ -55438,18 +55438,18 @@
       </c>
       <c r="G1095" t="inlineStr">
         <is>
-          <t>Rogerio Egidio</t>
+          <t>Rodrigo Rego</t>
         </is>
       </c>
       <c r="H1095" t="inlineStr"/>
       <c r="I1095" t="n">
-        <v>92</v>
+        <v>424</v>
       </c>
       <c r="J1095" t="n">
-        <v>201</v>
+        <v>421</v>
       </c>
       <c r="K1095" t="n">
-        <v>300</v>
+        <v>460</v>
       </c>
     </row>
     <row r="1096">
@@ -55485,18 +55485,18 @@
       </c>
       <c r="G1096" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Rogerio Egidio</t>
         </is>
       </c>
       <c r="H1096" t="inlineStr"/>
       <c r="I1096" t="n">
-        <v>25</v>
+        <v>226</v>
       </c>
       <c r="J1096" t="n">
-        <v>22</v>
+        <v>335</v>
       </c>
       <c r="K1096" t="n">
-        <v>48</v>
+        <v>384</v>
       </c>
     </row>
     <row r="1097">
@@ -55532,18 +55532,18 @@
       </c>
       <c r="G1097" t="inlineStr">
         <is>
-          <t>Simone Marques</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="H1097" t="inlineStr"/>
       <c r="I1097" t="n">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="J1097" t="n">
-        <v>137</v>
+        <v>33</v>
       </c>
       <c r="K1097" t="n">
-        <v>195</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1098">
@@ -55579,18 +55579,18 @@
       </c>
       <c r="G1098" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Simone Marques</t>
         </is>
       </c>
       <c r="H1098" t="inlineStr"/>
       <c r="I1098" t="n">
-        <v>61</v>
+        <v>125</v>
       </c>
       <c r="J1098" t="n">
-        <v>130</v>
+        <v>197</v>
       </c>
       <c r="K1098" t="n">
-        <v>201</v>
+        <v>228</v>
       </c>
     </row>
     <row r="1099">
@@ -55621,23 +55621,23 @@
       </c>
       <c r="F1099" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="G1099" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="H1099" t="inlineStr"/>
       <c r="I1099" t="n">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="J1099" t="n">
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="K1099" t="n">
-        <v>1</v>
+        <v>268</v>
       </c>
     </row>
     <row r="1100">
@@ -55673,18 +55673,18 @@
       </c>
       <c r="G1100" t="inlineStr">
         <is>
-          <t>Jurema Damacena - SAC</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="H1100" t="inlineStr"/>
       <c r="I1100" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J1100" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K1100" t="n">
-        <v>46</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1101">
@@ -55715,19 +55715,23 @@
       </c>
       <c r="F1101" t="inlineStr">
         <is>
-          <t>MG CONTABIFÁCIL - CTB</t>
-        </is>
-      </c>
-      <c r="G1101" t="inlineStr"/>
+          <t>GERENCIA MASTER</t>
+        </is>
+      </c>
+      <c r="G1101" t="inlineStr">
+        <is>
+          <t>Jurema Damacena - SAC</t>
+        </is>
+      </c>
       <c r="H1101" t="inlineStr"/>
       <c r="I1101" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="J1101" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K1101" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1102">
@@ -55761,20 +55765,16 @@
           <t>MG CONTABIFÁCIL - CTB</t>
         </is>
       </c>
-      <c r="G1102" t="inlineStr">
-        <is>
-          <t>Guilherme Delecrodio</t>
-        </is>
-      </c>
+      <c r="G1102" t="inlineStr"/>
       <c r="H1102" t="inlineStr"/>
       <c r="I1102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1103">
@@ -55805,17 +55805,17 @@
       </c>
       <c r="F1103" t="inlineStr">
         <is>
-          <t>S.A.C</t>
+          <t>MG CONTABIFÁCIL - CTB</t>
         </is>
       </c>
       <c r="G1103" t="inlineStr">
         <is>
-          <t>Ana Celia - SAC</t>
+          <t>Guilherme Delecrodio</t>
         </is>
       </c>
       <c r="H1103" t="inlineStr"/>
       <c r="I1103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J1103" t="n">
         <v>1</v>
@@ -55852,27 +55852,23 @@
       </c>
       <c r="F1104" t="inlineStr">
         <is>
-          <t>SANTOS - DP</t>
+          <t>S.A.C</t>
         </is>
       </c>
       <c r="G1104" t="inlineStr">
         <is>
-          <t>Katia Valeria</t>
-        </is>
-      </c>
-      <c r="H1104" t="inlineStr">
-        <is>
-          <t>Katia Valeria</t>
-        </is>
-      </c>
+          <t>Ana Celia - SAC</t>
+        </is>
+      </c>
+      <c r="H1104" t="inlineStr"/>
       <c r="I1104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1104" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K1104" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1105">
@@ -55898,28 +55894,32 @@
       </c>
       <c r="E1105" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F1105" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>SANTOS - DP</t>
         </is>
       </c>
       <c r="G1105" t="inlineStr">
         <is>
-          <t>Jurema Damacena - SAC</t>
-        </is>
-      </c>
-      <c r="H1105" t="inlineStr"/>
+          <t>Katia Valeria</t>
+        </is>
+      </c>
+      <c r="H1105" t="inlineStr">
+        <is>
+          <t>Katia Valeria</t>
+        </is>
+      </c>
       <c r="I1105" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J1105" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K1105" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1106">
@@ -55950,23 +55950,23 @@
       </c>
       <c r="F1106" t="inlineStr">
         <is>
-          <t>SANTOS - ADM</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="G1106" t="inlineStr">
         <is>
-          <t>Kauany Pereira</t>
+          <t>Jurema Damacena - SAC</t>
         </is>
       </c>
       <c r="H1106" t="inlineStr"/>
       <c r="I1106" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1106" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="K1106" t="n">
-        <v>136</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1107">
@@ -55997,27 +55997,23 @@
       </c>
       <c r="F1107" t="inlineStr">
         <is>
-          <t>SANTOS - CTB</t>
+          <t>SANTOS - ADM</t>
         </is>
       </c>
       <c r="G1107" t="inlineStr">
         <is>
-          <t>Ivia Oliveira</t>
-        </is>
-      </c>
-      <c r="H1107" t="inlineStr">
-        <is>
-          <t>Roberto Silva</t>
-        </is>
-      </c>
+          <t>Kauany Pereira</t>
+        </is>
+      </c>
+      <c r="H1107" t="inlineStr"/>
       <c r="I1107" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J1107" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="K1107" t="n">
-        <v>20</v>
+        <v>136</v>
       </c>
     </row>
     <row r="1108">
@@ -56053,7 +56049,7 @@
       </c>
       <c r="G1108" t="inlineStr">
         <is>
-          <t>Nata Trindade</t>
+          <t>Ivia Oliveira</t>
         </is>
       </c>
       <c r="H1108" t="inlineStr">
@@ -56062,13 +56058,13 @@
         </is>
       </c>
       <c r="I1108" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="J1108" t="n">
         <v>12</v>
       </c>
       <c r="K1108" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1109">
@@ -56104,22 +56100,22 @@
       </c>
       <c r="G1109" t="inlineStr">
         <is>
+          <t>Nata Trindade</t>
+        </is>
+      </c>
+      <c r="H1109" t="inlineStr">
+        <is>
           <t>Roberto Silva</t>
         </is>
       </c>
-      <c r="H1109" t="inlineStr">
-        <is>
-          <t>Roberto Silva</t>
-        </is>
-      </c>
       <c r="I1109" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="J1109" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="K1109" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="1110">
@@ -56155,7 +56151,7 @@
       </c>
       <c r="G1110" t="inlineStr">
         <is>
-          <t>Thaina Rodrigues</t>
+          <t>Roberto Silva</t>
         </is>
       </c>
       <c r="H1110" t="inlineStr">
@@ -56164,13 +56160,13 @@
         </is>
       </c>
       <c r="I1110" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J1110" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="K1110" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
     </row>
     <row r="1111">
@@ -56201,27 +56197,27 @@
       </c>
       <c r="F1111" t="inlineStr">
         <is>
-          <t>SANTOS - DP</t>
+          <t>SANTOS - CTB</t>
         </is>
       </c>
       <c r="G1111" t="inlineStr">
         <is>
-          <t>Bruna Silva</t>
+          <t>Thaina Rodrigues</t>
         </is>
       </c>
       <c r="H1111" t="inlineStr">
         <is>
-          <t>Katia Valeria</t>
+          <t>Roberto Silva</t>
         </is>
       </c>
       <c r="I1111" t="n">
         <v>0</v>
       </c>
       <c r="J1111" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="K1111" t="n">
-        <v>14</v>
+        <v>48</v>
       </c>
     </row>
     <row r="1112">
@@ -56257,7 +56253,7 @@
       </c>
       <c r="G1112" t="inlineStr">
         <is>
-          <t>Carliane Silva</t>
+          <t>Bruna Silva</t>
         </is>
       </c>
       <c r="H1112" t="inlineStr">
@@ -56266,13 +56262,13 @@
         </is>
       </c>
       <c r="I1112" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J1112" t="n">
-        <v>127</v>
+        <v>0</v>
       </c>
       <c r="K1112" t="n">
-        <v>280</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1113">
@@ -56308,7 +56304,7 @@
       </c>
       <c r="G1113" t="inlineStr">
         <is>
-          <t>Cintia Andrade</t>
+          <t>Carliane Silva</t>
         </is>
       </c>
       <c r="H1113" t="inlineStr">
@@ -56317,13 +56313,13 @@
         </is>
       </c>
       <c r="I1113" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1113" t="n">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="K1113" t="n">
-        <v>199</v>
+        <v>280</v>
       </c>
     </row>
     <row r="1114">
@@ -56359,22 +56355,22 @@
       </c>
       <c r="G1114" t="inlineStr">
         <is>
+          <t>Cintia Andrade</t>
+        </is>
+      </c>
+      <c r="H1114" t="inlineStr">
+        <is>
           <t>Katia Valeria</t>
         </is>
       </c>
-      <c r="H1114" t="inlineStr">
-        <is>
-          <t>Katia Valeria</t>
-        </is>
-      </c>
       <c r="I1114" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J1114" t="n">
-        <v>155</v>
+        <v>95</v>
       </c>
       <c r="K1114" t="n">
-        <v>335</v>
+        <v>199</v>
       </c>
     </row>
     <row r="1115">
@@ -56410,18 +56406,22 @@
       </c>
       <c r="G1115" t="inlineStr">
         <is>
-          <t>Patricia Melo</t>
-        </is>
-      </c>
-      <c r="H1115" t="inlineStr"/>
+          <t>Katia Valeria</t>
+        </is>
+      </c>
+      <c r="H1115" t="inlineStr">
+        <is>
+          <t>Katia Valeria</t>
+        </is>
+      </c>
       <c r="I1115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J1115" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="K1115" t="n">
-        <v>0</v>
+        <v>335</v>
       </c>
     </row>
     <row r="1116">
@@ -56452,27 +56452,23 @@
       </c>
       <c r="F1116" t="inlineStr">
         <is>
-          <t>SANTOS - EF</t>
+          <t>SANTOS - DP</t>
         </is>
       </c>
       <c r="G1116" t="inlineStr">
         <is>
-          <t>Jasmina Melo</t>
-        </is>
-      </c>
-      <c r="H1116" t="inlineStr">
-        <is>
-          <t>Lidia Tavares</t>
-        </is>
-      </c>
+          <t>Patricia Melo</t>
+        </is>
+      </c>
+      <c r="H1116" t="inlineStr"/>
       <c r="I1116" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J1116" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K1116" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1117">
@@ -56508,7 +56504,7 @@
       </c>
       <c r="G1117" t="inlineStr">
         <is>
-          <t>Karen Saadi</t>
+          <t>Jasmina Melo</t>
         </is>
       </c>
       <c r="H1117" t="inlineStr">
@@ -56517,13 +56513,13 @@
         </is>
       </c>
       <c r="I1117" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J1117" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K1117" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="1118">
@@ -56559,7 +56555,7 @@
       </c>
       <c r="G1118" t="inlineStr">
         <is>
-          <t>Luckas Andrade</t>
+          <t>Karen Saadi</t>
         </is>
       </c>
       <c r="H1118" t="inlineStr">
@@ -56571,10 +56567,10 @@
         <v>3</v>
       </c>
       <c r="J1118" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="K1118" t="n">
-        <v>74</v>
+        <v>61</v>
       </c>
     </row>
     <row r="1119">
@@ -56610,7 +56606,7 @@
       </c>
       <c r="G1119" t="inlineStr">
         <is>
-          <t>Mirian Rodrigues</t>
+          <t>Luckas Andrade</t>
         </is>
       </c>
       <c r="H1119" t="inlineStr">
@@ -56619,13 +56615,13 @@
         </is>
       </c>
       <c r="I1119" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1119" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="K1119" t="n">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="1120">
@@ -56656,22 +56652,73 @@
       </c>
       <c r="F1120" t="inlineStr">
         <is>
+          <t>SANTOS - EF</t>
+        </is>
+      </c>
+      <c r="G1120" t="inlineStr">
+        <is>
+          <t>Mirian Rodrigues</t>
+        </is>
+      </c>
+      <c r="H1120" t="inlineStr">
+        <is>
+          <t>Lidia Tavares</t>
+        </is>
+      </c>
+      <c r="I1120" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1120" t="n">
+        <v>29</v>
+      </c>
+      <c r="K1120" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B1121" t="inlineStr">
+        <is>
+          <t>Quinta</t>
+        </is>
+      </c>
+      <c r="C1121" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D1121" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1121" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="F1121" t="inlineStr">
+        <is>
           <t>SANTOS - GC</t>
         </is>
       </c>
-      <c r="G1120" t="inlineStr">
+      <c r="G1121" t="inlineStr">
         <is>
           <t>Rafaella Massuia</t>
         </is>
       </c>
-      <c r="H1120" t="inlineStr"/>
-      <c r="I1120" t="n">
-        <v>0</v>
-      </c>
-      <c r="J1120" t="n">
-        <v>0</v>
-      </c>
-      <c r="K1120" t="n">
+      <c r="H1121" t="inlineStr"/>
+      <c r="I1121" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1121" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1121" t="n">
         <v>109</v>
       </c>
     </row>

--- a/data/historico/historico_baixas.xlsx
+++ b/data/historico/historico_baixas.xlsx
@@ -43359,13 +43359,13 @@
         </is>
       </c>
       <c r="I855" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J855" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K855" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="856">
@@ -44218,13 +44218,13 @@
         </is>
       </c>
       <c r="I872" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J872" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K872" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="873">
@@ -44881,10 +44881,10 @@
         </is>
       </c>
       <c r="I885" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J885" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K885" t="n">
         <v>107</v>
@@ -44932,10 +44932,10 @@
         </is>
       </c>
       <c r="I886" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J886" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K886" t="n">
         <v>172</v>
@@ -45187,13 +45187,13 @@
         </is>
       </c>
       <c r="I891" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J891" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K891" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="892">
@@ -45238,13 +45238,13 @@
         </is>
       </c>
       <c r="I892" t="n">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="J892" t="n">
-        <v>57</v>
+        <v>91</v>
       </c>
       <c r="K892" t="n">
-        <v>71</v>
+        <v>105</v>
       </c>
     </row>
     <row r="893">
@@ -45595,13 +45595,13 @@
         </is>
       </c>
       <c r="I899" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J899" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="K899" t="n">
-        <v>145</v>
+        <v>150</v>
       </c>
     </row>
     <row r="900">
@@ -45885,13 +45885,13 @@
       </c>
       <c r="H905" t="inlineStr"/>
       <c r="I905" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J905" t="n">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="K905" t="n">
-        <v>219</v>
+        <v>224</v>
       </c>
     </row>
     <row r="906">
@@ -46536,13 +46536,13 @@
         </is>
       </c>
       <c r="I918" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J918" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K918" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="919">
@@ -47046,13 +47046,13 @@
         </is>
       </c>
       <c r="I928" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J928" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K928" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="929">
@@ -47603,13 +47603,13 @@
         </is>
       </c>
       <c r="I939" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J939" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K939" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="940">
@@ -47756,13 +47756,13 @@
         </is>
       </c>
       <c r="I942" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J942" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K942" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="943">
@@ -48011,13 +48011,13 @@
         </is>
       </c>
       <c r="I947" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J947" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K947" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="948">
@@ -48164,13 +48164,13 @@
         </is>
       </c>
       <c r="I950" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J950" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K950" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="951">
@@ -48215,13 +48215,13 @@
         </is>
       </c>
       <c r="I951" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J951" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K951" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="952">
@@ -48572,13 +48572,13 @@
         </is>
       </c>
       <c r="I958" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J958" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K958" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="959">
@@ -48823,13 +48823,13 @@
         </is>
       </c>
       <c r="I963" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J963" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K963" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="964">
@@ -49890,13 +49890,13 @@
         </is>
       </c>
       <c r="I984" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J984" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K984" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="985">
@@ -51463,13 +51463,13 @@
         </is>
       </c>
       <c r="I1015" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="J1015" t="n">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="K1015" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
     </row>
     <row r="1016">
@@ -51616,13 +51616,13 @@
         </is>
       </c>
       <c r="I1018" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J1018" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K1018" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="1019">
@@ -51667,13 +51667,13 @@
         </is>
       </c>
       <c r="I1019" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J1019" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="K1019" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="1020">
@@ -51718,13 +51718,13 @@
         </is>
       </c>
       <c r="I1020" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J1020" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="K1020" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="1021">
@@ -51769,7 +51769,7 @@
         </is>
       </c>
       <c r="I1021" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1021" t="n">
         <v>0</v>
@@ -52126,13 +52126,13 @@
         </is>
       </c>
       <c r="I1028" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J1028" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="K1028" t="n">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1029">
@@ -52228,13 +52228,13 @@
         </is>
       </c>
       <c r="I1030" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J1030" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="K1030" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
     </row>
     <row r="1031">
@@ -52279,13 +52279,13 @@
         </is>
       </c>
       <c r="I1031" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1031" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K1031" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="1032">
@@ -52381,13 +52381,13 @@
         </is>
       </c>
       <c r="I1033" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J1033" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K1033" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="1034">
@@ -52483,13 +52483,13 @@
         </is>
       </c>
       <c r="I1035" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J1035" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K1035" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="1036">
@@ -52683,13 +52683,13 @@
         </is>
       </c>
       <c r="I1039" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J1039" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K1039" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="1040">
@@ -52887,13 +52887,13 @@
         </is>
       </c>
       <c r="I1043" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J1043" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="K1043" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="1044">
@@ -53142,13 +53142,13 @@
         </is>
       </c>
       <c r="I1048" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J1048" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K1048" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="1049">
@@ -53856,13 +53856,13 @@
         </is>
       </c>
       <c r="I1062" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J1062" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K1062" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="1063">
@@ -54932,7 +54932,7 @@
         <v>354</v>
       </c>
       <c r="K1084" t="n">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="1085">
@@ -55208,7 +55208,7 @@
       </c>
       <c r="H1090" t="inlineStr"/>
       <c r="I1090" t="n">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="J1090" t="n">
         <v>157</v>
@@ -55590,7 +55590,7 @@
         <v>197</v>
       </c>
       <c r="K1098" t="n">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="1099">
@@ -55725,13 +55725,13 @@
       </c>
       <c r="H1101" t="inlineStr"/>
       <c r="I1101" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J1101" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K1101" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="1102">
@@ -56007,13 +56007,13 @@
       </c>
       <c r="H1107" t="inlineStr"/>
       <c r="I1107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1107" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K1107" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="1108">
@@ -56109,13 +56109,13 @@
         </is>
       </c>
       <c r="I1109" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J1109" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K1109" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="1110">
@@ -56513,13 +56513,13 @@
         </is>
       </c>
       <c r="I1117" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J1117" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K1117" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="1118">

--- a/data/historico/historico_baixas.xlsx
+++ b/data/historico/historico_baixas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1409"/>
+  <dimension ref="A1:K1412"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -56801,24 +56801,24 @@
       </c>
       <c r="F1123" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="G1123" t="inlineStr">
         <is>
-          <t>Eveny Silva</t>
+          <t>Nathalia Lourenco</t>
         </is>
       </c>
       <c r="H1123" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Erika Santana|Isabella Nascimento</t>
         </is>
       </c>
       <c r="I1123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1123" t="n">
         <v>1</v>
@@ -56857,12 +56857,12 @@
       </c>
       <c r="G1124" t="inlineStr">
         <is>
-          <t>Jackson Silva</t>
+          <t>Eveny Silva</t>
         </is>
       </c>
       <c r="H1124" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Karina Santos</t>
         </is>
       </c>
       <c r="I1124" t="n">
@@ -56872,7 +56872,7 @@
         <v>0</v>
       </c>
       <c r="K1124" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1125">
@@ -56908,12 +56908,12 @@
       </c>
       <c r="G1125" t="inlineStr">
         <is>
-          <t>Paulo Silva</t>
+          <t>Jackson Silva</t>
         </is>
       </c>
       <c r="H1125" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I1125" t="n">
@@ -56923,7 +56923,7 @@
         <v>0</v>
       </c>
       <c r="K1125" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1126">
@@ -56954,27 +56954,27 @@
       </c>
       <c r="F1126" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="G1126" t="inlineStr">
         <is>
-          <t>Elaine Assis</t>
+          <t>Paulo Silva</t>
         </is>
       </c>
       <c r="H1126" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="I1126" t="n">
         <v>0</v>
       </c>
       <c r="J1126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1126" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1127">
@@ -57010,12 +57010,12 @@
       </c>
       <c r="G1127" t="inlineStr">
         <is>
-          <t>Evellin Bispo</t>
+          <t>Elaine Assis</t>
         </is>
       </c>
       <c r="H1127" t="inlineStr">
         <is>
-          <t>Leandro Matos</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I1127" t="n">
@@ -57025,7 +57025,7 @@
         <v>1</v>
       </c>
       <c r="K1127" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1128">
@@ -57061,22 +57061,22 @@
       </c>
       <c r="G1128" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Evellin Bispo</t>
         </is>
       </c>
       <c r="H1128" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Leandro Matos</t>
         </is>
       </c>
       <c r="I1128" t="n">
         <v>0</v>
       </c>
       <c r="J1128" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K1128" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1129">
@@ -57112,22 +57112,22 @@
       </c>
       <c r="G1129" t="inlineStr">
         <is>
-          <t>Jhenifer Tenorio</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="H1129" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I1129" t="n">
         <v>0</v>
       </c>
       <c r="J1129" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K1129" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1130">
@@ -57163,22 +57163,22 @@
       </c>
       <c r="G1130" t="inlineStr">
         <is>
-          <t>Kaique Souza</t>
+          <t>Jhenifer Tenorio</t>
         </is>
       </c>
       <c r="H1130" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I1130" t="n">
         <v>0</v>
       </c>
       <c r="J1130" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K1130" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1131">
@@ -57214,22 +57214,22 @@
       </c>
       <c r="G1131" t="inlineStr">
         <is>
-          <t>Mauricio Lermen</t>
+          <t>Kaique Souza</t>
         </is>
       </c>
       <c r="H1131" t="inlineStr">
         <is>
-          <t>Mauricio Lermen</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I1131" t="n">
         <v>0</v>
       </c>
       <c r="J1131" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K1131" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1132">
@@ -57265,18 +57265,22 @@
       </c>
       <c r="G1132" t="inlineStr">
         <is>
-          <t>Mikael Teixeira</t>
-        </is>
-      </c>
-      <c r="H1132" t="inlineStr"/>
+          <t>Mauricio Lermen</t>
+        </is>
+      </c>
+      <c r="H1132" t="inlineStr">
+        <is>
+          <t>Mauricio Lermen</t>
+        </is>
+      </c>
       <c r="I1132" t="n">
         <v>0</v>
       </c>
       <c r="J1132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1132" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1133">
@@ -57312,22 +57316,18 @@
       </c>
       <c r="G1133" t="inlineStr">
         <is>
-          <t>Tania Luz</t>
-        </is>
-      </c>
-      <c r="H1133" t="inlineStr">
-        <is>
-          <t>Sara Cavalheiro</t>
-        </is>
-      </c>
+          <t>Mikael Teixeira</t>
+        </is>
+      </c>
+      <c r="H1133" t="inlineStr"/>
       <c r="I1133" t="n">
         <v>0</v>
       </c>
       <c r="J1133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1133" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1134">
@@ -57363,12 +57363,12 @@
       </c>
       <c r="G1134" t="inlineStr">
         <is>
-          <t>Vitor Guedes</t>
+          <t>Tania Luz</t>
         </is>
       </c>
       <c r="H1134" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I1134" t="n">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="K1134" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1135">
@@ -57409,27 +57409,27 @@
       </c>
       <c r="F1135" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="G1135" t="inlineStr">
         <is>
-          <t>Cristiana Grizostomo</t>
+          <t>Vitor Guedes</t>
         </is>
       </c>
       <c r="H1135" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I1135" t="n">
         <v>0</v>
       </c>
       <c r="J1135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1135" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1136">
@@ -57465,18 +57465,22 @@
       </c>
       <c r="G1136" t="inlineStr">
         <is>
-          <t>Denis Reis</t>
-        </is>
-      </c>
-      <c r="H1136" t="inlineStr"/>
+          <t>Cristiana Grizostomo</t>
+        </is>
+      </c>
+      <c r="H1136" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
       <c r="I1136" t="n">
         <v>0</v>
       </c>
       <c r="J1136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1136" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1137">
@@ -57512,22 +57516,18 @@
       </c>
       <c r="G1137" t="inlineStr">
         <is>
-          <t>Priscila Volpe</t>
-        </is>
-      </c>
-      <c r="H1137" t="inlineStr">
-        <is>
-          <t>Nayara Oliveira</t>
-        </is>
-      </c>
+          <t>Denis Reis</t>
+        </is>
+      </c>
+      <c r="H1137" t="inlineStr"/>
       <c r="I1137" t="n">
         <v>0</v>
       </c>
       <c r="J1137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1137" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="1138">
@@ -57563,7 +57563,7 @@
       </c>
       <c r="G1138" t="inlineStr">
         <is>
-          <t>Rosilene Santos</t>
+          <t>Priscila Volpe</t>
         </is>
       </c>
       <c r="H1138" t="inlineStr">
@@ -57575,10 +57575,10 @@
         <v>0</v>
       </c>
       <c r="J1138" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K1138" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1139">
@@ -57609,27 +57609,27 @@
       </c>
       <c r="F1139" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="G1139" t="inlineStr">
         <is>
-          <t>Cristina Leite</t>
+          <t>Rosilene Santos</t>
         </is>
       </c>
       <c r="H1139" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
       <c r="I1139" t="n">
         <v>0</v>
       </c>
       <c r="J1139" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="K1139" t="n">
-        <v>64</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1140">
@@ -57660,23 +57660,27 @@
       </c>
       <c r="F1140" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="G1140" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
-        </is>
-      </c>
-      <c r="H1140" t="inlineStr"/>
+          <t>Cristina Leite</t>
+        </is>
+      </c>
+      <c r="H1140" t="inlineStr">
+        <is>
+          <t>Ricardo Fischer</t>
+        </is>
+      </c>
       <c r="I1140" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J1140" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="K1140" t="n">
-        <v>2</v>
+        <v>70</v>
       </c>
     </row>
     <row r="1141">
@@ -57712,7 +57716,7 @@
       </c>
       <c r="G1141" t="inlineStr">
         <is>
-          <t>Victoria Virgens</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="H1141" t="inlineStr"/>
@@ -57720,10 +57724,10 @@
         <v>0</v>
       </c>
       <c r="J1141" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="K1141" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1142">
@@ -57754,12 +57758,12 @@
       </c>
       <c r="F1142" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="G1142" t="inlineStr">
         <is>
-          <t>Cristiane Simões</t>
+          <t>Victoria Virgens</t>
         </is>
       </c>
       <c r="H1142" t="inlineStr"/>
@@ -57767,10 +57771,10 @@
         <v>0</v>
       </c>
       <c r="J1142" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="K1142" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1143">
@@ -57806,7 +57810,7 @@
       </c>
       <c r="G1143" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Cristiane Simões</t>
         </is>
       </c>
       <c r="H1143" t="inlineStr"/>
@@ -57814,10 +57818,10 @@
         <v>0</v>
       </c>
       <c r="J1143" t="n">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="K1143" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1144">
@@ -57853,7 +57857,7 @@
       </c>
       <c r="G1144" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="H1144" t="inlineStr"/>
@@ -57861,10 +57865,10 @@
         <v>0</v>
       </c>
       <c r="J1144" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="K1144" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
     </row>
     <row r="1145">
@@ -57900,7 +57904,7 @@
       </c>
       <c r="G1145" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="H1145" t="inlineStr"/>
@@ -57911,7 +57915,7 @@
         <v>3</v>
       </c>
       <c r="K1145" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1146">
@@ -57937,17 +57941,17 @@
       </c>
       <c r="E1146" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>GOIAS</t>
         </is>
       </c>
       <c r="F1146" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="G1146" t="inlineStr">
         <is>
-          <t>Caroline Alves</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="H1146" t="inlineStr"/>
@@ -57955,10 +57959,10 @@
         <v>0</v>
       </c>
       <c r="J1146" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K1146" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1147">
@@ -57989,27 +57993,23 @@
       </c>
       <c r="F1147" t="inlineStr">
         <is>
-          <t>RJ - CTB</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="G1147" t="inlineStr">
         <is>
-          <t>Crislaine Maia</t>
-        </is>
-      </c>
-      <c r="H1147" t="inlineStr">
-        <is>
-          <t>Walace Gonçalves|Maicon Costa</t>
-        </is>
-      </c>
+          <t>Caroline Alves</t>
+        </is>
+      </c>
+      <c r="H1147" t="inlineStr"/>
       <c r="I1147" t="n">
         <v>0</v>
       </c>
       <c r="J1147" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K1147" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1148">
@@ -58045,7 +58045,7 @@
       </c>
       <c r="G1148" t="inlineStr">
         <is>
-          <t>Gabriela Lopes</t>
+          <t>Crislaine Maia</t>
         </is>
       </c>
       <c r="H1148" t="inlineStr">
@@ -58054,13 +58054,13 @@
         </is>
       </c>
       <c r="I1148" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J1148" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="K1148" t="n">
-        <v>53</v>
+        <v>31</v>
       </c>
     </row>
     <row r="1149">
@@ -58096,7 +58096,7 @@
       </c>
       <c r="G1149" t="inlineStr">
         <is>
-          <t>Jeniffer Cristina</t>
+          <t>Gabriela Lopes</t>
         </is>
       </c>
       <c r="H1149" t="inlineStr">
@@ -58105,13 +58105,13 @@
         </is>
       </c>
       <c r="I1149" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J1149" t="n">
-        <v>67</v>
+        <v>15</v>
       </c>
       <c r="K1149" t="n">
-        <v>76</v>
+        <v>66</v>
       </c>
     </row>
     <row r="1150">
@@ -58147,7 +58147,7 @@
       </c>
       <c r="G1150" t="inlineStr">
         <is>
-          <t>Jessica Roque</t>
+          <t>Jeniffer Cristina</t>
         </is>
       </c>
       <c r="H1150" t="inlineStr">
@@ -58159,10 +58159,10 @@
         <v>0</v>
       </c>
       <c r="J1150" t="n">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="K1150" t="n">
-        <v>60</v>
+        <v>76</v>
       </c>
     </row>
     <row r="1151">
@@ -58198,7 +58198,7 @@
       </c>
       <c r="G1151" t="inlineStr">
         <is>
-          <t>Kellem Freitas</t>
+          <t>Jessica Roque</t>
         </is>
       </c>
       <c r="H1151" t="inlineStr">
@@ -58210,10 +58210,10 @@
         <v>0</v>
       </c>
       <c r="J1151" t="n">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="K1151" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
     </row>
     <row r="1152">
@@ -58249,7 +58249,7 @@
       </c>
       <c r="G1152" t="inlineStr">
         <is>
-          <t>Leidiane Paulino</t>
+          <t>Kellem Freitas</t>
         </is>
       </c>
       <c r="H1152" t="inlineStr">
@@ -58258,13 +58258,13 @@
         </is>
       </c>
       <c r="I1152" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1152" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K1152" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1153">
@@ -58300,7 +58300,7 @@
       </c>
       <c r="G1153" t="inlineStr">
         <is>
-          <t>Leticia Barbosa</t>
+          <t>Leidiane Paulino</t>
         </is>
       </c>
       <c r="H1153" t="inlineStr">
@@ -58312,10 +58312,10 @@
         <v>0</v>
       </c>
       <c r="J1153" t="n">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="K1153" t="n">
-        <v>83</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1154">
@@ -58351,7 +58351,7 @@
       </c>
       <c r="G1154" t="inlineStr">
         <is>
-          <t>Luis Junior</t>
+          <t>Leticia Barbosa</t>
         </is>
       </c>
       <c r="H1154" t="inlineStr">
@@ -58363,10 +58363,10 @@
         <v>0</v>
       </c>
       <c r="J1154" t="n">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="K1154" t="n">
-        <v>13</v>
+        <v>83</v>
       </c>
     </row>
     <row r="1155">
@@ -58402,7 +58402,7 @@
       </c>
       <c r="G1155" t="inlineStr">
         <is>
-          <t>Nicoly Rodrigues</t>
+          <t>Luis Junior</t>
         </is>
       </c>
       <c r="H1155" t="inlineStr">
@@ -58414,10 +58414,10 @@
         <v>0</v>
       </c>
       <c r="J1155" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K1155" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1156">
@@ -58453,7 +58453,7 @@
       </c>
       <c r="G1156" t="inlineStr">
         <is>
-          <t>Rafaella Silva</t>
+          <t>Nicoly Rodrigues</t>
         </is>
       </c>
       <c r="H1156" t="inlineStr">
@@ -58462,13 +58462,13 @@
         </is>
       </c>
       <c r="I1156" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1156" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="K1156" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1157">
@@ -58504,7 +58504,7 @@
       </c>
       <c r="G1157" t="inlineStr">
         <is>
-          <t>Rangel Rocha</t>
+          <t>Rafaella Silva</t>
         </is>
       </c>
       <c r="H1157" t="inlineStr">
@@ -58516,10 +58516,10 @@
         <v>0</v>
       </c>
       <c r="J1157" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K1157" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1158">
@@ -58555,7 +58555,7 @@
       </c>
       <c r="G1158" t="inlineStr">
         <is>
-          <t>Simone Soares</t>
+          <t>Rangel Rocha</t>
         </is>
       </c>
       <c r="H1158" t="inlineStr">
@@ -58564,13 +58564,13 @@
         </is>
       </c>
       <c r="I1158" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J1158" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="K1158" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1159">
@@ -58606,7 +58606,7 @@
       </c>
       <c r="G1159" t="inlineStr">
         <is>
-          <t>Suzana Silva</t>
+          <t>Simone Soares</t>
         </is>
       </c>
       <c r="H1159" t="inlineStr">
@@ -58615,13 +58615,13 @@
         </is>
       </c>
       <c r="I1159" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1159" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K1159" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="1160">
@@ -58657,7 +58657,7 @@
       </c>
       <c r="G1160" t="inlineStr">
         <is>
-          <t>Veronica Barbosa</t>
+          <t>Suzana Silva</t>
         </is>
       </c>
       <c r="H1160" t="inlineStr">
@@ -58666,13 +58666,13 @@
         </is>
       </c>
       <c r="I1160" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J1160" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K1160" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="1161">
@@ -58708,7 +58708,7 @@
       </c>
       <c r="G1161" t="inlineStr">
         <is>
-          <t>Vitor Monteiro</t>
+          <t>Veronica Barbosa</t>
         </is>
       </c>
       <c r="H1161" t="inlineStr">
@@ -58720,10 +58720,10 @@
         <v>0</v>
       </c>
       <c r="J1161" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="K1161" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1162">
@@ -58759,7 +58759,7 @@
       </c>
       <c r="G1162" t="inlineStr">
         <is>
-          <t>Vitoria Silva</t>
+          <t>Vitor Monteiro</t>
         </is>
       </c>
       <c r="H1162" t="inlineStr">
@@ -58768,13 +58768,13 @@
         </is>
       </c>
       <c r="I1162" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J1162" t="n">
         <v>7</v>
       </c>
       <c r="K1162" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1163">
@@ -58810,7 +58810,7 @@
       </c>
       <c r="G1163" t="inlineStr">
         <is>
-          <t>Walace Gonçalves</t>
+          <t>Vitoria Silva</t>
         </is>
       </c>
       <c r="H1163" t="inlineStr">
@@ -58819,13 +58819,13 @@
         </is>
       </c>
       <c r="I1163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1163" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K1163" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="1164">
@@ -58856,19 +58856,27 @@
       </c>
       <c r="F1164" t="inlineStr">
         <is>
-          <t>RJ - DP</t>
-        </is>
-      </c>
-      <c r="G1164" t="inlineStr"/>
-      <c r="H1164" t="inlineStr"/>
+          <t>RJ - CTB</t>
+        </is>
+      </c>
+      <c r="G1164" t="inlineStr">
+        <is>
+          <t>Walace Gonçalves</t>
+        </is>
+      </c>
+      <c r="H1164" t="inlineStr">
+        <is>
+          <t>Walace Gonçalves|Maicon Costa</t>
+        </is>
+      </c>
       <c r="I1164" t="n">
         <v>0</v>
       </c>
       <c r="J1164" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K1164" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1165">
@@ -58902,24 +58910,16 @@
           <t>RJ - DP</t>
         </is>
       </c>
-      <c r="G1165" t="inlineStr">
-        <is>
-          <t>Barbara Mello</t>
-        </is>
-      </c>
-      <c r="H1165" t="inlineStr">
-        <is>
-          <t>Karina Oliveira|Liliane Costa</t>
-        </is>
-      </c>
+      <c r="G1165" t="inlineStr"/>
+      <c r="H1165" t="inlineStr"/>
       <c r="I1165" t="n">
         <v>0</v>
       </c>
       <c r="J1165" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K1165" t="n">
-        <v>105</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1166">
@@ -58955,7 +58955,7 @@
       </c>
       <c r="G1166" t="inlineStr">
         <is>
-          <t>Debora Nunes</t>
+          <t>Barbara Mello</t>
         </is>
       </c>
       <c r="H1166" t="inlineStr">
@@ -58967,10 +58967,10 @@
         <v>0</v>
       </c>
       <c r="J1166" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="K1166" t="n">
-        <v>92</v>
+        <v>105</v>
       </c>
     </row>
     <row r="1167">
@@ -59006,7 +59006,7 @@
       </c>
       <c r="G1167" t="inlineStr">
         <is>
-          <t>Graziele Almeida</t>
+          <t>Debora Nunes</t>
         </is>
       </c>
       <c r="H1167" t="inlineStr">
@@ -59015,13 +59015,13 @@
         </is>
       </c>
       <c r="I1167" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J1167" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="K1167" t="n">
-        <v>88</v>
+        <v>99</v>
       </c>
     </row>
     <row r="1168">
@@ -59057,7 +59057,7 @@
       </c>
       <c r="G1168" t="inlineStr">
         <is>
-          <t>Janiele Ferreira</t>
+          <t>Graziele Almeida</t>
         </is>
       </c>
       <c r="H1168" t="inlineStr">
@@ -59069,10 +59069,10 @@
         <v>0</v>
       </c>
       <c r="J1168" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K1168" t="n">
-        <v>20</v>
+        <v>88</v>
       </c>
     </row>
     <row r="1169">
@@ -59108,7 +59108,7 @@
       </c>
       <c r="G1169" t="inlineStr">
         <is>
-          <t>Jefferson Barros</t>
+          <t>Janiele Ferreira</t>
         </is>
       </c>
       <c r="H1169" t="inlineStr">
@@ -59120,10 +59120,10 @@
         <v>0</v>
       </c>
       <c r="J1169" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K1169" t="n">
-        <v>99</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1170">
@@ -59159,7 +59159,7 @@
       </c>
       <c r="G1170" t="inlineStr">
         <is>
-          <t>Karina Oliveira</t>
+          <t>Jefferson Barros</t>
         </is>
       </c>
       <c r="H1170" t="inlineStr">
@@ -59171,10 +59171,10 @@
         <v>0</v>
       </c>
       <c r="J1170" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K1170" t="n">
-        <v>31</v>
+        <v>99</v>
       </c>
     </row>
     <row r="1171">
@@ -59210,7 +59210,7 @@
       </c>
       <c r="G1171" t="inlineStr">
         <is>
-          <t>Leonardo Assunção</t>
+          <t>Karina Oliveira</t>
         </is>
       </c>
       <c r="H1171" t="inlineStr">
@@ -59219,13 +59219,13 @@
         </is>
       </c>
       <c r="I1171" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1171" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="K1171" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="1172">
@@ -59261,7 +59261,7 @@
       </c>
       <c r="G1172" t="inlineStr">
         <is>
-          <t>Liliane Costa</t>
+          <t>Leonardo Assunção</t>
         </is>
       </c>
       <c r="H1172" t="inlineStr">
@@ -59270,13 +59270,13 @@
         </is>
       </c>
       <c r="I1172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1172" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="K1172" t="n">
-        <v>16</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1173">
@@ -59312,7 +59312,7 @@
       </c>
       <c r="G1173" t="inlineStr">
         <is>
-          <t>Luciene Pimenta</t>
+          <t>Liliane Costa</t>
         </is>
       </c>
       <c r="H1173" t="inlineStr">
@@ -59324,10 +59324,10 @@
         <v>0</v>
       </c>
       <c r="J1173" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K1173" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1174">
@@ -59363,7 +59363,7 @@
       </c>
       <c r="G1174" t="inlineStr">
         <is>
-          <t>Lucirene Souza</t>
+          <t>Luciene Pimenta</t>
         </is>
       </c>
       <c r="H1174" t="inlineStr">
@@ -59375,10 +59375,10 @@
         <v>0</v>
       </c>
       <c r="J1174" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K1174" t="n">
-        <v>85</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1175">
@@ -59414,7 +59414,7 @@
       </c>
       <c r="G1175" t="inlineStr">
         <is>
-          <t>Marlon Silva</t>
+          <t>Lucirene Souza</t>
         </is>
       </c>
       <c r="H1175" t="inlineStr">
@@ -59426,10 +59426,10 @@
         <v>0</v>
       </c>
       <c r="J1175" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="K1175" t="n">
-        <v>109</v>
+        <v>85</v>
       </c>
     </row>
     <row r="1176">
@@ -59465,7 +59465,7 @@
       </c>
       <c r="G1176" t="inlineStr">
         <is>
-          <t>Monique Britto</t>
+          <t>Marlon Silva</t>
         </is>
       </c>
       <c r="H1176" t="inlineStr">
@@ -59477,10 +59477,10 @@
         <v>0</v>
       </c>
       <c r="J1176" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="K1176" t="n">
-        <v>94</v>
+        <v>109</v>
       </c>
     </row>
     <row r="1177">
@@ -59516,7 +59516,7 @@
       </c>
       <c r="G1177" t="inlineStr">
         <is>
-          <t>Romulo Ferreira</t>
+          <t>Monique Britto</t>
         </is>
       </c>
       <c r="H1177" t="inlineStr">
@@ -59528,10 +59528,10 @@
         <v>0</v>
       </c>
       <c r="J1177" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="K1177" t="n">
-        <v>314</v>
+        <v>94</v>
       </c>
     </row>
     <row r="1178">
@@ -59567,7 +59567,7 @@
       </c>
       <c r="G1178" t="inlineStr">
         <is>
-          <t>Rosilene Silva</t>
+          <t>Romulo Ferreira</t>
         </is>
       </c>
       <c r="H1178" t="inlineStr">
@@ -59576,13 +59576,13 @@
         </is>
       </c>
       <c r="I1178" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1178" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="K1178" t="n">
-        <v>29</v>
+        <v>315</v>
       </c>
     </row>
     <row r="1179">
@@ -59618,7 +59618,7 @@
       </c>
       <c r="G1179" t="inlineStr">
         <is>
-          <t>Thais Santos</t>
+          <t>Rosilene Silva</t>
         </is>
       </c>
       <c r="H1179" t="inlineStr">
@@ -59630,10 +59630,10 @@
         <v>0</v>
       </c>
       <c r="J1179" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K1179" t="n">
-        <v>107</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1180">
@@ -59669,7 +59669,7 @@
       </c>
       <c r="G1180" t="inlineStr">
         <is>
-          <t>Vitoria Tavares</t>
+          <t>Thais Santos</t>
         </is>
       </c>
       <c r="H1180" t="inlineStr">
@@ -59678,13 +59678,13 @@
         </is>
       </c>
       <c r="I1180" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J1180" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K1180" t="n">
-        <v>172</v>
+        <v>113</v>
       </c>
     </row>
     <row r="1181">
@@ -59720,7 +59720,7 @@
       </c>
       <c r="G1181" t="inlineStr">
         <is>
-          <t>Viviane Moura</t>
+          <t>Vitoria Tavares</t>
         </is>
       </c>
       <c r="H1181" t="inlineStr">
@@ -59729,13 +59729,13 @@
         </is>
       </c>
       <c r="I1181" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J1181" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K1181" t="n">
-        <v>74</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1182">
@@ -59771,7 +59771,7 @@
       </c>
       <c r="G1182" t="inlineStr">
         <is>
-          <t>Yasmin Lopes</t>
+          <t>Viviane Moura</t>
         </is>
       </c>
       <c r="H1182" t="inlineStr">
@@ -59783,10 +59783,10 @@
         <v>0</v>
       </c>
       <c r="J1182" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="K1182" t="n">
-        <v>123</v>
+        <v>74</v>
       </c>
     </row>
     <row r="1183">
@@ -59817,27 +59817,27 @@
       </c>
       <c r="F1183" t="inlineStr">
         <is>
-          <t>RJ - EF</t>
+          <t>RJ - DP</t>
         </is>
       </c>
       <c r="G1183" t="inlineStr">
         <is>
-          <t>Altamir Nogueira</t>
+          <t>Yasmin Lopes</t>
         </is>
       </c>
       <c r="H1183" t="inlineStr">
         <is>
-          <t>Julio Santos|Jessica Benjamin</t>
+          <t>Karina Oliveira|Liliane Costa</t>
         </is>
       </c>
       <c r="I1183" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1183" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K1183" t="n">
-        <v>104</v>
+        <v>123</v>
       </c>
     </row>
     <row r="1184">
@@ -59873,7 +59873,7 @@
       </c>
       <c r="G1184" t="inlineStr">
         <is>
-          <t>Beatriz Oliveira</t>
+          <t>Altamir Nogueira</t>
         </is>
       </c>
       <c r="H1184" t="inlineStr">
@@ -59882,13 +59882,13 @@
         </is>
       </c>
       <c r="I1184" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="J1184" t="n">
-        <v>26</v>
+        <v>81</v>
       </c>
       <c r="K1184" t="n">
-        <v>45</v>
+        <v>143</v>
       </c>
     </row>
     <row r="1185">
@@ -59924,7 +59924,7 @@
       </c>
       <c r="G1185" t="inlineStr">
         <is>
-          <t>Glaucia Santos</t>
+          <t>Beatriz Oliveira</t>
         </is>
       </c>
       <c r="H1185" t="inlineStr">
@@ -59933,13 +59933,13 @@
         </is>
       </c>
       <c r="I1185" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="J1185" t="n">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="K1185" t="n">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="1186">
@@ -59975,7 +59975,7 @@
       </c>
       <c r="G1186" t="inlineStr">
         <is>
-          <t>Isabela Barbosa</t>
+          <t>Glaucia Santos</t>
         </is>
       </c>
       <c r="H1186" t="inlineStr">
@@ -59984,13 +59984,13 @@
         </is>
       </c>
       <c r="I1186" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="J1186" t="n">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="K1186" t="n">
-        <v>115</v>
+        <v>127</v>
       </c>
     </row>
     <row r="1187">
@@ -60026,7 +60026,7 @@
       </c>
       <c r="G1187" t="inlineStr">
         <is>
-          <t>Jessica Benjamin</t>
+          <t>Isabela Barbosa</t>
         </is>
       </c>
       <c r="H1187" t="inlineStr">
@@ -60035,13 +60035,13 @@
         </is>
       </c>
       <c r="I1187" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J1187" t="n">
-        <v>15</v>
+        <v>115</v>
       </c>
       <c r="K1187" t="n">
-        <v>73</v>
+        <v>129</v>
       </c>
     </row>
     <row r="1188">
@@ -60077,7 +60077,7 @@
       </c>
       <c r="G1188" t="inlineStr">
         <is>
-          <t>Juliana Perfeito</t>
+          <t>Jessica Benjamin</t>
         </is>
       </c>
       <c r="H1188" t="inlineStr">
@@ -60086,13 +60086,13 @@
         </is>
       </c>
       <c r="I1188" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="J1188" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="K1188" t="n">
-        <v>56</v>
+        <v>108</v>
       </c>
     </row>
     <row r="1189">
@@ -60128,7 +60128,7 @@
       </c>
       <c r="G1189" t="inlineStr">
         <is>
-          <t>Julio Santos</t>
+          <t>Juliana Perfeito</t>
         </is>
       </c>
       <c r="H1189" t="inlineStr">
@@ -60137,13 +60137,13 @@
         </is>
       </c>
       <c r="I1189" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J1189" t="n">
-        <v>4</v>
+        <v>53</v>
       </c>
       <c r="K1189" t="n">
-        <v>1</v>
+        <v>77</v>
       </c>
     </row>
     <row r="1190">
@@ -60179,7 +60179,7 @@
       </c>
       <c r="G1190" t="inlineStr">
         <is>
-          <t>Lais Catrine EF</t>
+          <t>Julio Santos</t>
         </is>
       </c>
       <c r="H1190" t="inlineStr">
@@ -60191,10 +60191,10 @@
         <v>0</v>
       </c>
       <c r="J1190" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="K1190" t="n">
-        <v>129</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1191">
@@ -60230,7 +60230,7 @@
       </c>
       <c r="G1191" t="inlineStr">
         <is>
-          <t>Luana Meneses</t>
+          <t>Lais Catrine EF</t>
         </is>
       </c>
       <c r="H1191" t="inlineStr">
@@ -60239,13 +60239,13 @@
         </is>
       </c>
       <c r="I1191" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="J1191" t="n">
-        <v>54</v>
+        <v>95</v>
       </c>
       <c r="K1191" t="n">
-        <v>96</v>
+        <v>209</v>
       </c>
     </row>
     <row r="1192">
@@ -60281,7 +60281,7 @@
       </c>
       <c r="G1192" t="inlineStr">
         <is>
-          <t>Otacilia Ferreira</t>
+          <t>Luana Meneses</t>
         </is>
       </c>
       <c r="H1192" t="inlineStr">
@@ -60290,13 +60290,13 @@
         </is>
       </c>
       <c r="I1192" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="J1192" t="n">
-        <v>42</v>
+        <v>91</v>
       </c>
       <c r="K1192" t="n">
-        <v>61</v>
+        <v>133</v>
       </c>
     </row>
     <row r="1193">
@@ -60332,7 +60332,7 @@
       </c>
       <c r="G1193" t="inlineStr">
         <is>
-          <t>Renata Paixão</t>
+          <t>Otacilia Ferreira</t>
         </is>
       </c>
       <c r="H1193" t="inlineStr">
@@ -60341,13 +60341,13 @@
         </is>
       </c>
       <c r="I1193" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="J1193" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="K1193" t="n">
-        <v>150</v>
+        <v>97</v>
       </c>
     </row>
     <row r="1194">
@@ -60383,7 +60383,7 @@
       </c>
       <c r="G1194" t="inlineStr">
         <is>
-          <t>Thamara Jordes</t>
+          <t>Renata Paixão</t>
         </is>
       </c>
       <c r="H1194" t="inlineStr">
@@ -60392,13 +60392,13 @@
         </is>
       </c>
       <c r="I1194" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1194" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="K1194" t="n">
-        <v>43</v>
+        <v>152</v>
       </c>
     </row>
     <row r="1195">
@@ -60434,7 +60434,7 @@
       </c>
       <c r="G1195" t="inlineStr">
         <is>
-          <t>Wellington Oliveira</t>
+          <t>Thamara Jordes</t>
         </is>
       </c>
       <c r="H1195" t="inlineStr">
@@ -60443,13 +60443,13 @@
         </is>
       </c>
       <c r="I1195" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="J1195" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K1195" t="n">
-        <v>124</v>
+        <v>110</v>
       </c>
     </row>
     <row r="1196">
@@ -60480,23 +60480,27 @@
       </c>
       <c r="F1196" t="inlineStr">
         <is>
-          <t>RJ - GC</t>
+          <t>RJ - EF</t>
         </is>
       </c>
       <c r="G1196" t="inlineStr">
         <is>
-          <t>Bruno Mota</t>
-        </is>
-      </c>
-      <c r="H1196" t="inlineStr"/>
+          <t>Wellington Oliveira</t>
+        </is>
+      </c>
+      <c r="H1196" t="inlineStr">
+        <is>
+          <t>Julio Santos|Jessica Benjamin</t>
+        </is>
+      </c>
       <c r="I1196" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="J1196" t="n">
-        <v>70</v>
+        <v>114</v>
       </c>
       <c r="K1196" t="n">
-        <v>155</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1197">
@@ -60532,7 +60536,7 @@
       </c>
       <c r="G1197" t="inlineStr">
         <is>
-          <t>Cavalcante Peres</t>
+          <t>Bruno Mota</t>
         </is>
       </c>
       <c r="H1197" t="inlineStr"/>
@@ -60540,10 +60544,10 @@
         <v>0</v>
       </c>
       <c r="J1197" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="K1197" t="n">
-        <v>81</v>
+        <v>155</v>
       </c>
     </row>
     <row r="1198">
@@ -60579,18 +60583,18 @@
       </c>
       <c r="G1198" t="inlineStr">
         <is>
-          <t>Tiago Rodrigues</t>
+          <t>Cavalcante Peres</t>
         </is>
       </c>
       <c r="H1198" t="inlineStr"/>
       <c r="I1198" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1198" t="n">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="K1198" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
     </row>
     <row r="1199">
@@ -60621,12 +60625,12 @@
       </c>
       <c r="F1199" t="inlineStr">
         <is>
-          <t>RJ - GC ADMINISTRATIVO</t>
+          <t>RJ - GC</t>
         </is>
       </c>
       <c r="G1199" t="inlineStr">
         <is>
-          <t>Amanda Mesquita</t>
+          <t>Tiago Rodrigues</t>
         </is>
       </c>
       <c r="H1199" t="inlineStr"/>
@@ -60634,10 +60638,10 @@
         <v>0</v>
       </c>
       <c r="J1199" t="n">
-        <v>189</v>
+        <v>1</v>
       </c>
       <c r="K1199" t="n">
-        <v>224</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1200">
@@ -60673,7 +60677,7 @@
       </c>
       <c r="G1200" t="inlineStr">
         <is>
-          <t>Lohany Martins</t>
+          <t>Amanda Mesquita</t>
         </is>
       </c>
       <c r="H1200" t="inlineStr"/>
@@ -60681,10 +60685,10 @@
         <v>0</v>
       </c>
       <c r="J1200" t="n">
-        <v>144</v>
+        <v>189</v>
       </c>
       <c r="K1200" t="n">
-        <v>346</v>
+        <v>224</v>
       </c>
     </row>
     <row r="1201">
@@ -60715,23 +60719,23 @@
       </c>
       <c r="F1201" t="inlineStr">
         <is>
-          <t>S.A.C</t>
+          <t>RJ - GC ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="G1201" t="inlineStr">
         <is>
-          <t>Milena Campos - SAC</t>
+          <t>Lohany Martins</t>
         </is>
       </c>
       <c r="H1201" t="inlineStr"/>
       <c r="I1201" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1201" t="n">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="K1201" t="n">
-        <v>1</v>
+        <v>347</v>
       </c>
     </row>
     <row r="1202">
@@ -60757,32 +60761,28 @@
       </c>
       <c r="E1202" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F1202" t="inlineStr">
         <is>
-          <t>CONTABILIDADE (Outsourcing)</t>
+          <t>S.A.C</t>
         </is>
       </c>
       <c r="G1202" t="inlineStr">
         <is>
-          <t>Aline Petrini</t>
-        </is>
-      </c>
-      <c r="H1202" t="inlineStr">
-        <is>
-          <t>Fernanda Araujo</t>
-        </is>
-      </c>
+          <t>Milena Campos - SAC</t>
+        </is>
+      </c>
+      <c r="H1202" t="inlineStr"/>
       <c r="I1202" t="n">
         <v>0</v>
       </c>
       <c r="J1202" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1202" t="n">
         <v>1</v>
-      </c>
-      <c r="K1202" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="1203">
@@ -60818,22 +60818,22 @@
       </c>
       <c r="G1203" t="inlineStr">
         <is>
-          <t>Daniele Leite</t>
+          <t>Aline Petrini</t>
         </is>
       </c>
       <c r="H1203" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="I1203" t="n">
         <v>0</v>
       </c>
       <c r="J1203" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1203" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1204">
@@ -60869,12 +60869,12 @@
       </c>
       <c r="G1204" t="inlineStr">
         <is>
-          <t>Diogo Calazans</t>
+          <t>Daniele Leite</t>
         </is>
       </c>
       <c r="H1204" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I1204" t="n">
@@ -60920,22 +60920,22 @@
       </c>
       <c r="G1205" t="inlineStr">
         <is>
-          <t>Jaqueline Sousa</t>
+          <t>Diogo Calazans</t>
         </is>
       </c>
       <c r="H1205" t="inlineStr">
         <is>
-          <t>Lucas Fischer</t>
+          <t>Karina Santos</t>
         </is>
       </c>
       <c r="I1205" t="n">
         <v>0</v>
       </c>
       <c r="J1205" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K1205" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1206">
@@ -60971,19 +60971,19 @@
       </c>
       <c r="G1206" t="inlineStr">
         <is>
-          <t>Patricia Borges</t>
+          <t>Jaqueline Sousa</t>
         </is>
       </c>
       <c r="H1206" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Lucas Fischer</t>
         </is>
       </c>
       <c r="I1206" t="n">
         <v>0</v>
       </c>
       <c r="J1206" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K1206" t="n">
         <v>5</v>
@@ -61022,19 +61022,19 @@
       </c>
       <c r="G1207" t="inlineStr">
         <is>
-          <t>Rejane Coelho</t>
+          <t>Patricia Borges</t>
         </is>
       </c>
       <c r="H1207" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I1207" t="n">
         <v>0</v>
       </c>
       <c r="J1207" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1207" t="n">
         <v>5</v>
@@ -61073,12 +61073,12 @@
       </c>
       <c r="G1208" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Rejane Coelho</t>
         </is>
       </c>
       <c r="H1208" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Karina Santos</t>
         </is>
       </c>
       <c r="I1208" t="n">
@@ -61088,7 +61088,7 @@
         <v>1</v>
       </c>
       <c r="K1208" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1209">
@@ -61124,12 +61124,12 @@
       </c>
       <c r="G1209" t="inlineStr">
         <is>
-          <t>Thiago Ceconelli</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="H1209" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="I1209" t="n">
@@ -61139,7 +61139,7 @@
         <v>1</v>
       </c>
       <c r="K1209" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1210">
@@ -61170,27 +61170,27 @@
       </c>
       <c r="F1210" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL HOLDING</t>
+          <t>CONTABILIDADE (Outsourcing)</t>
         </is>
       </c>
       <c r="G1210" t="inlineStr">
         <is>
-          <t>Ana Flavia Silva</t>
+          <t>Thiago Ceconelli</t>
         </is>
       </c>
       <c r="H1210" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Karina Santos</t>
         </is>
       </c>
       <c r="I1210" t="n">
         <v>0</v>
       </c>
       <c r="J1210" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="K1210" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1211">
@@ -61226,18 +61226,22 @@
       </c>
       <c r="G1211" t="inlineStr">
         <is>
-          <t>Daniele Faria</t>
-        </is>
-      </c>
-      <c r="H1211" t="inlineStr"/>
+          <t>Ana Flavia Silva</t>
+        </is>
+      </c>
+      <c r="H1211" t="inlineStr">
+        <is>
+          <t>Tatiana Linardi</t>
+        </is>
+      </c>
       <c r="I1211" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="J1211" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="K1211" t="n">
-        <v>2</v>
+        <v>60</v>
       </c>
     </row>
     <row r="1212">
@@ -61273,22 +61277,18 @@
       </c>
       <c r="G1212" t="inlineStr">
         <is>
-          <t>Vitor de Souza</t>
-        </is>
-      </c>
-      <c r="H1212" t="inlineStr">
-        <is>
-          <t>Tatiana Linardi</t>
-        </is>
-      </c>
+          <t>Daniele Faria</t>
+        </is>
+      </c>
+      <c r="H1212" t="inlineStr"/>
       <c r="I1212" t="n">
         <v>0</v>
       </c>
       <c r="J1212" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="K1212" t="n">
-        <v>118</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1213">
@@ -61324,7 +61324,7 @@
       </c>
       <c r="G1213" t="inlineStr">
         <is>
-          <t>Vitoria Regina</t>
+          <t>Vitor de Souza</t>
         </is>
       </c>
       <c r="H1213" t="inlineStr">
@@ -61333,13 +61333,13 @@
         </is>
       </c>
       <c r="I1213" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="J1213" t="n">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="K1213" t="n">
-        <v>64</v>
+        <v>141</v>
       </c>
     </row>
     <row r="1214">
@@ -61370,27 +61370,27 @@
       </c>
       <c r="F1214" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL INDUSTRIA</t>
+          <t>CTB - CONTÁBIL HOLDING</t>
         </is>
       </c>
       <c r="G1214" t="inlineStr">
         <is>
-          <t>Adriano Barros</t>
+          <t>Vitoria Regina</t>
         </is>
       </c>
       <c r="H1214" t="inlineStr">
         <is>
-          <t>Erika Santana|Isabella Nascimento</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="I1214" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="J1214" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="K1214" t="n">
-        <v>1</v>
+        <v>143</v>
       </c>
     </row>
     <row r="1215">
@@ -61426,7 +61426,7 @@
       </c>
       <c r="G1215" t="inlineStr">
         <is>
-          <t>Bianca Silva</t>
+          <t>Adriano Barros</t>
         </is>
       </c>
       <c r="H1215" t="inlineStr">
@@ -61435,13 +61435,13 @@
         </is>
       </c>
       <c r="I1215" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J1215" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="K1215" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1216">
@@ -61477,7 +61477,7 @@
       </c>
       <c r="G1216" t="inlineStr">
         <is>
-          <t>Emylle Souza</t>
+          <t>Bianca Silva</t>
         </is>
       </c>
       <c r="H1216" t="inlineStr">
@@ -61486,13 +61486,13 @@
         </is>
       </c>
       <c r="I1216" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J1216" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="K1216" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1217">
@@ -61528,7 +61528,7 @@
       </c>
       <c r="G1217" t="inlineStr">
         <is>
-          <t>Fatima Rocha</t>
+          <t>Emylle Souza</t>
         </is>
       </c>
       <c r="H1217" t="inlineStr">
@@ -61537,13 +61537,13 @@
         </is>
       </c>
       <c r="I1217" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J1217" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K1217" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1218">
@@ -61579,7 +61579,7 @@
       </c>
       <c r="G1218" t="inlineStr">
         <is>
-          <t>Gabriel Correia</t>
+          <t>Fatima Rocha</t>
         </is>
       </c>
       <c r="H1218" t="inlineStr">
@@ -61588,13 +61588,13 @@
         </is>
       </c>
       <c r="I1218" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J1218" t="n">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="K1218" t="n">
-        <v>8</v>
+        <v>39</v>
       </c>
     </row>
     <row r="1219">
@@ -61630,7 +61630,7 @@
       </c>
       <c r="G1219" t="inlineStr">
         <is>
-          <t>Isabella Nascimento</t>
+          <t>Gabriel Correia</t>
         </is>
       </c>
       <c r="H1219" t="inlineStr">
@@ -61639,13 +61639,13 @@
         </is>
       </c>
       <c r="I1219" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J1219" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K1219" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1220">
@@ -61681,7 +61681,7 @@
       </c>
       <c r="G1220" t="inlineStr">
         <is>
-          <t>Laisa Rocha</t>
+          <t>Isabella Nascimento</t>
         </is>
       </c>
       <c r="H1220" t="inlineStr">
@@ -61693,10 +61693,10 @@
         <v>0</v>
       </c>
       <c r="J1220" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K1220" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1221">
@@ -61732,7 +61732,7 @@
       </c>
       <c r="G1221" t="inlineStr">
         <is>
-          <t>Lucas Alves</t>
+          <t>Laisa Rocha</t>
         </is>
       </c>
       <c r="H1221" t="inlineStr">
@@ -61741,13 +61741,13 @@
         </is>
       </c>
       <c r="I1221" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J1221" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="K1221" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1222">
@@ -61783,7 +61783,7 @@
       </c>
       <c r="G1222" t="inlineStr">
         <is>
-          <t>Luciana Silva</t>
+          <t>Lucas Alves</t>
         </is>
       </c>
       <c r="H1222" t="inlineStr">
@@ -61792,13 +61792,13 @@
         </is>
       </c>
       <c r="I1222" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1222" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="K1222" t="n">
-        <v>33</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1223">
@@ -61834,18 +61834,22 @@
       </c>
       <c r="G1223" t="inlineStr">
         <is>
-          <t>Luiz Ferreira</t>
-        </is>
-      </c>
-      <c r="H1223" t="inlineStr"/>
+          <t>Luciana Silva</t>
+        </is>
+      </c>
+      <c r="H1223" t="inlineStr">
+        <is>
+          <t>Erika Santana|Isabella Nascimento</t>
+        </is>
+      </c>
       <c r="I1223" t="n">
         <v>0</v>
       </c>
       <c r="J1223" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K1223" t="n">
-        <v>4</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1224">
@@ -61881,22 +61885,18 @@
       </c>
       <c r="G1224" t="inlineStr">
         <is>
-          <t>Marcus Oliveira</t>
-        </is>
-      </c>
-      <c r="H1224" t="inlineStr">
-        <is>
-          <t>Erika Santana|Isabella Nascimento</t>
-        </is>
-      </c>
+          <t>Luiz Ferreira</t>
+        </is>
+      </c>
+      <c r="H1224" t="inlineStr"/>
       <c r="I1224" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1224" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K1224" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1225">
@@ -61932,7 +61932,7 @@
       </c>
       <c r="G1225" t="inlineStr">
         <is>
-          <t>Mariana Pires</t>
+          <t>Marcus Oliveira</t>
         </is>
       </c>
       <c r="H1225" t="inlineStr">
@@ -61941,13 +61941,13 @@
         </is>
       </c>
       <c r="I1225" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J1225" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="K1225" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1226">
@@ -61983,7 +61983,7 @@
       </c>
       <c r="G1226" t="inlineStr">
         <is>
-          <t>Marta Souza</t>
+          <t>Mariana Pires</t>
         </is>
       </c>
       <c r="H1226" t="inlineStr">
@@ -61992,13 +61992,13 @@
         </is>
       </c>
       <c r="I1226" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J1226" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="K1226" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1227">
@@ -62034,7 +62034,7 @@
       </c>
       <c r="G1227" t="inlineStr">
         <is>
-          <t>Mateus Miranda</t>
+          <t>Marta Souza</t>
         </is>
       </c>
       <c r="H1227" t="inlineStr">
@@ -62043,13 +62043,13 @@
         </is>
       </c>
       <c r="I1227" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J1227" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K1227" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1228">
@@ -62085,7 +62085,7 @@
       </c>
       <c r="G1228" t="inlineStr">
         <is>
-          <t>Mirian Lima</t>
+          <t>Mateus Miranda</t>
         </is>
       </c>
       <c r="H1228" t="inlineStr">
@@ -62094,13 +62094,13 @@
         </is>
       </c>
       <c r="I1228" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J1228" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K1228" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1229">
@@ -62136,7 +62136,7 @@
       </c>
       <c r="G1229" t="inlineStr">
         <is>
-          <t>Nathalia Lourenco</t>
+          <t>Mirian Lima</t>
         </is>
       </c>
       <c r="H1229" t="inlineStr">
@@ -62145,13 +62145,13 @@
         </is>
       </c>
       <c r="I1229" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J1229" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K1229" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1230">
@@ -62187,7 +62187,7 @@
       </c>
       <c r="G1230" t="inlineStr">
         <is>
-          <t>Nicolas Dias</t>
+          <t>Nathalia Lourenco</t>
         </is>
       </c>
       <c r="H1230" t="inlineStr">
@@ -62196,13 +62196,13 @@
         </is>
       </c>
       <c r="I1230" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J1230" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K1230" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1231">
@@ -62238,7 +62238,7 @@
       </c>
       <c r="G1231" t="inlineStr">
         <is>
-          <t>Rodrigo Nunes</t>
+          <t>Nicolas Dias</t>
         </is>
       </c>
       <c r="H1231" t="inlineStr">
@@ -62247,13 +62247,13 @@
         </is>
       </c>
       <c r="I1231" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J1231" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="K1231" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1232">
@@ -62289,7 +62289,7 @@
       </c>
       <c r="G1232" t="inlineStr">
         <is>
-          <t>Thais Souza</t>
+          <t>Rodrigo Nunes</t>
         </is>
       </c>
       <c r="H1232" t="inlineStr">
@@ -62301,10 +62301,10 @@
         <v>0</v>
       </c>
       <c r="J1232" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K1232" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1233">
@@ -62335,27 +62335,27 @@
       </c>
       <c r="F1233" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="G1233" t="inlineStr">
         <is>
-          <t>Aline Petrini</t>
+          <t>Thais Souza</t>
         </is>
       </c>
       <c r="H1233" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Erika Santana|Isabella Nascimento</t>
         </is>
       </c>
       <c r="I1233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1233" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="K1233" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1234">
@@ -62386,27 +62386,27 @@
       </c>
       <c r="F1234" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="G1234" t="inlineStr">
         <is>
-          <t>Ana Barbosa</t>
+          <t>Viviane Guedes</t>
         </is>
       </c>
       <c r="H1234" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Erika Santana|Isabella Nascimento</t>
         </is>
       </c>
       <c r="I1234" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1234" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K1234" t="n">
-        <v>44</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1235">
@@ -62442,22 +62442,22 @@
       </c>
       <c r="G1235" t="inlineStr">
         <is>
-          <t>Daniele Leite</t>
+          <t>Aline Petrini</t>
         </is>
       </c>
       <c r="H1235" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="I1235" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J1235" t="n">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="K1235" t="n">
-        <v>6</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1236">
@@ -62493,22 +62493,22 @@
       </c>
       <c r="G1236" t="inlineStr">
         <is>
-          <t>Danielle Silva</t>
+          <t>Ana Barbosa</t>
         </is>
       </c>
       <c r="H1236" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I1236" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1236" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="K1236" t="n">
-        <v>71</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1237">
@@ -62544,22 +62544,22 @@
       </c>
       <c r="G1237" t="inlineStr">
         <is>
-          <t>Danilo Oliveira</t>
+          <t>Daniele Leite</t>
         </is>
       </c>
       <c r="H1237" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I1237" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J1237" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="K1237" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1238">
@@ -62595,22 +62595,22 @@
       </c>
       <c r="G1238" t="inlineStr">
         <is>
-          <t>Debora Silva</t>
+          <t>Danielle Silva</t>
         </is>
       </c>
       <c r="H1238" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Karina Santos</t>
         </is>
       </c>
       <c r="I1238" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J1238" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="K1238" t="n">
-        <v>22</v>
+        <v>77</v>
       </c>
     </row>
     <row r="1239">
@@ -62646,7 +62646,7 @@
       </c>
       <c r="G1239" t="inlineStr">
         <is>
-          <t>Diogo Calazans</t>
+          <t>Danilo Oliveira</t>
         </is>
       </c>
       <c r="H1239" t="inlineStr">
@@ -62655,13 +62655,13 @@
         </is>
       </c>
       <c r="I1239" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J1239" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="K1239" t="n">
-        <v>80</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1240">
@@ -62697,7 +62697,7 @@
       </c>
       <c r="G1240" t="inlineStr">
         <is>
-          <t>Eduardo Cruz</t>
+          <t>Debora Silva</t>
         </is>
       </c>
       <c r="H1240" t="inlineStr">
@@ -62706,13 +62706,13 @@
         </is>
       </c>
       <c r="I1240" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J1240" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="K1240" t="n">
-        <v>77</v>
+        <v>31</v>
       </c>
     </row>
     <row r="1241">
@@ -62748,7 +62748,7 @@
       </c>
       <c r="G1241" t="inlineStr">
         <is>
-          <t>Eveny Silva</t>
+          <t>Diogo Calazans</t>
         </is>
       </c>
       <c r="H1241" t="inlineStr">
@@ -62757,13 +62757,13 @@
         </is>
       </c>
       <c r="I1241" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J1241" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K1241" t="n">
-        <v>41</v>
+        <v>93</v>
       </c>
     </row>
     <row r="1242">
@@ -62799,7 +62799,7 @@
       </c>
       <c r="G1242" t="inlineStr">
         <is>
-          <t>Everton Moura</t>
+          <t>Eduardo Cruz</t>
         </is>
       </c>
       <c r="H1242" t="inlineStr">
@@ -62808,13 +62808,13 @@
         </is>
       </c>
       <c r="I1242" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1242" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K1242" t="n">
-        <v>9</v>
+        <v>80</v>
       </c>
     </row>
     <row r="1243">
@@ -62850,22 +62850,22 @@
       </c>
       <c r="G1243" t="inlineStr">
         <is>
-          <t>Guilherme Dantas</t>
+          <t>Eveny Silva</t>
         </is>
       </c>
       <c r="H1243" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Karina Santos</t>
         </is>
       </c>
       <c r="I1243" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J1243" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="K1243" t="n">
-        <v>22</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1244">
@@ -62901,7 +62901,7 @@
       </c>
       <c r="G1244" t="inlineStr">
         <is>
-          <t>Isabela Lemos</t>
+          <t>Everton Moura</t>
         </is>
       </c>
       <c r="H1244" t="inlineStr">
@@ -62916,7 +62916,7 @@
         <v>7</v>
       </c>
       <c r="K1244" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1245">
@@ -62952,7 +62952,7 @@
       </c>
       <c r="G1245" t="inlineStr">
         <is>
-          <t>Jackson Silva</t>
+          <t>Guilherme Dantas</t>
         </is>
       </c>
       <c r="H1245" t="inlineStr">
@@ -62964,10 +62964,10 @@
         <v>0</v>
       </c>
       <c r="J1245" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K1245" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1246">
@@ -63003,22 +63003,22 @@
       </c>
       <c r="G1246" t="inlineStr">
         <is>
-          <t>Jaqueline Sousa</t>
+          <t>Isabela Lemos</t>
         </is>
       </c>
       <c r="H1246" t="inlineStr">
         <is>
-          <t>Lucas Fischer</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="I1246" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J1246" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="K1246" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1247">
@@ -63054,22 +63054,22 @@
       </c>
       <c r="G1247" t="inlineStr">
         <is>
-          <t>Leticia Medeiros</t>
+          <t>Jackson Silva</t>
         </is>
       </c>
       <c r="H1247" t="inlineStr">
         <is>
-          <t>Lucas Fischer</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I1247" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J1247" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K1247" t="n">
-        <v>61</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1248">
@@ -63105,22 +63105,22 @@
       </c>
       <c r="G1248" t="inlineStr">
         <is>
-          <t>Monica Medeiros</t>
+          <t>Jaqueline Sousa</t>
         </is>
       </c>
       <c r="H1248" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Lucas Fischer</t>
         </is>
       </c>
       <c r="I1248" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1248" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="K1248" t="n">
-        <v>49</v>
+        <v>31</v>
       </c>
     </row>
     <row r="1249">
@@ -63156,7 +63156,7 @@
       </c>
       <c r="G1249" t="inlineStr">
         <is>
-          <t>Naiara Dutra</t>
+          <t>Leticia Medeiros</t>
         </is>
       </c>
       <c r="H1249" t="inlineStr">
@@ -63165,13 +63165,13 @@
         </is>
       </c>
       <c r="I1249" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J1249" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K1249" t="n">
-        <v>25</v>
+        <v>66</v>
       </c>
     </row>
     <row r="1250">
@@ -63207,7 +63207,7 @@
       </c>
       <c r="G1250" t="inlineStr">
         <is>
-          <t>Patricia Borges</t>
+          <t>Monica Medeiros</t>
         </is>
       </c>
       <c r="H1250" t="inlineStr">
@@ -63216,13 +63216,13 @@
         </is>
       </c>
       <c r="I1250" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1250" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K1250" t="n">
-        <v>34</v>
+        <v>52</v>
       </c>
     </row>
     <row r="1251">
@@ -63258,22 +63258,22 @@
       </c>
       <c r="G1251" t="inlineStr">
         <is>
-          <t>Paulo Silva</t>
+          <t>Naiara Dutra</t>
         </is>
       </c>
       <c r="H1251" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Lucas Fischer</t>
         </is>
       </c>
       <c r="I1251" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1251" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="K1251" t="n">
-        <v>58</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1252">
@@ -63309,7 +63309,7 @@
       </c>
       <c r="G1252" t="inlineStr">
         <is>
-          <t>Rachel Lima</t>
+          <t>Patricia Borges</t>
         </is>
       </c>
       <c r="H1252" t="inlineStr">
@@ -63318,13 +63318,13 @@
         </is>
       </c>
       <c r="I1252" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J1252" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="K1252" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="1253">
@@ -63360,22 +63360,22 @@
       </c>
       <c r="G1253" t="inlineStr">
         <is>
-          <t>Raiane Barbosa</t>
+          <t>Paulo Silva</t>
         </is>
       </c>
       <c r="H1253" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="I1253" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1253" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="K1253" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
     </row>
     <row r="1254">
@@ -63411,22 +63411,22 @@
       </c>
       <c r="G1254" t="inlineStr">
         <is>
-          <t>Rejane Coelho</t>
+          <t>Rachel Lima</t>
         </is>
       </c>
       <c r="H1254" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I1254" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J1254" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="K1254" t="n">
-        <v>2</v>
+        <v>64</v>
       </c>
     </row>
     <row r="1255">
@@ -63462,22 +63462,22 @@
       </c>
       <c r="G1255" t="inlineStr">
         <is>
-          <t>Renata Alves - CTV</t>
+          <t>Raiane Barbosa</t>
         </is>
       </c>
       <c r="H1255" t="inlineStr">
         <is>
-          <t>Lucas Fischer</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I1255" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J1255" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="K1255" t="n">
-        <v>11</v>
+        <v>71</v>
       </c>
     </row>
     <row r="1256">
@@ -63513,10 +63513,14 @@
       </c>
       <c r="G1256" t="inlineStr">
         <is>
-          <t>Renata Cavalheiro</t>
-        </is>
-      </c>
-      <c r="H1256" t="inlineStr"/>
+          <t>Rejane Coelho</t>
+        </is>
+      </c>
+      <c r="H1256" t="inlineStr">
+        <is>
+          <t>Karina Santos</t>
+        </is>
+      </c>
       <c r="I1256" t="n">
         <v>0</v>
       </c>
@@ -63524,7 +63528,7 @@
         <v>1</v>
       </c>
       <c r="K1256" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1257">
@@ -63560,22 +63564,22 @@
       </c>
       <c r="G1257" t="inlineStr">
         <is>
-          <t>Ryan Godinho</t>
+          <t>Renata Alves - CTV</t>
         </is>
       </c>
       <c r="H1257" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Lucas Fischer</t>
         </is>
       </c>
       <c r="I1257" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J1257" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="K1257" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1258">
@@ -63611,16 +63615,12 @@
       </c>
       <c r="G1258" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
-        </is>
-      </c>
-      <c r="H1258" t="inlineStr">
-        <is>
-          <t>Tatiana Linardi</t>
-        </is>
-      </c>
+          <t>Renata Cavalheiro</t>
+        </is>
+      </c>
+      <c r="H1258" t="inlineStr"/>
       <c r="I1258" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1258" t="n">
         <v>1</v>
@@ -63662,22 +63662,22 @@
       </c>
       <c r="G1259" t="inlineStr">
         <is>
-          <t>Vitor Domingues</t>
+          <t>Ryan Godinho</t>
         </is>
       </c>
       <c r="H1259" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Karina Santos</t>
         </is>
       </c>
       <c r="I1259" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1259" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="K1259" t="n">
-        <v>66</v>
+        <v>32</v>
       </c>
     </row>
     <row r="1260">
@@ -63708,24 +63708,24 @@
       </c>
       <c r="F1260" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO PESSOAL (Outsourcing)</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="G1260" t="inlineStr">
         <is>
-          <t>Bruna Santana</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="H1260" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="I1260" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1260" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K1260" t="n">
         <v>4</v>
@@ -63759,27 +63759,27 @@
       </c>
       <c r="F1261" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO PESSOAL (Outsourcing)</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="G1261" t="inlineStr">
         <is>
-          <t>Camila Oliveira</t>
+          <t>Vitor Domingues</t>
         </is>
       </c>
       <c r="H1261" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="I1261" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J1261" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="K1261" t="n">
-        <v>16</v>
+        <v>70</v>
       </c>
     </row>
     <row r="1262">
@@ -63815,22 +63815,22 @@
       </c>
       <c r="G1262" t="inlineStr">
         <is>
-          <t>Elaine Assis</t>
+          <t>Bruna Santana</t>
         </is>
       </c>
       <c r="H1262" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I1262" t="n">
         <v>0</v>
       </c>
       <c r="J1262" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K1262" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1263">
@@ -63866,22 +63866,22 @@
       </c>
       <c r="G1263" t="inlineStr">
         <is>
-          <t>Fabiane Branco</t>
+          <t>Camila Oliveira</t>
         </is>
       </c>
       <c r="H1263" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I1263" t="n">
         <v>0</v>
       </c>
       <c r="J1263" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K1263" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1264">
@@ -63917,22 +63917,22 @@
       </c>
       <c r="G1264" t="inlineStr">
         <is>
-          <t>Jonas Nunes</t>
+          <t>Elaine Assis</t>
         </is>
       </c>
       <c r="H1264" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I1264" t="n">
         <v>0</v>
       </c>
       <c r="J1264" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K1264" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1265">
@@ -63963,27 +63963,27 @@
       </c>
       <c r="F1265" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>DEPARTAMENTO PESSOAL (Outsourcing)</t>
         </is>
       </c>
       <c r="G1265" t="inlineStr">
         <is>
-          <t>Bruna Santana</t>
+          <t>Fabiane Branco</t>
         </is>
       </c>
       <c r="H1265" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I1265" t="n">
         <v>0</v>
       </c>
       <c r="J1265" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="K1265" t="n">
-        <v>117</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1266">
@@ -64014,12 +64014,12 @@
       </c>
       <c r="F1266" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>DEPARTAMENTO PESSOAL (Outsourcing)</t>
         </is>
       </c>
       <c r="G1266" t="inlineStr">
         <is>
-          <t>Camila Oliveira</t>
+          <t>Jonas Nunes</t>
         </is>
       </c>
       <c r="H1266" t="inlineStr">
@@ -64028,13 +64028,13 @@
         </is>
       </c>
       <c r="I1266" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1266" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K1266" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1267">
@@ -64070,22 +64070,22 @@
       </c>
       <c r="G1267" t="inlineStr">
         <is>
-          <t>Daniel Moraes</t>
+          <t>Bruna Santana</t>
         </is>
       </c>
       <c r="H1267" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I1267" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J1267" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="K1267" t="n">
-        <v>47</v>
+        <v>122</v>
       </c>
     </row>
     <row r="1268">
@@ -64121,22 +64121,22 @@
       </c>
       <c r="G1268" t="inlineStr">
         <is>
-          <t>Danilo Xavier</t>
+          <t>Camila Oliveira</t>
         </is>
       </c>
       <c r="H1268" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I1268" t="n">
         <v>0</v>
       </c>
       <c r="J1268" t="n">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="K1268" t="n">
-        <v>176</v>
+        <v>32</v>
       </c>
     </row>
     <row r="1269">
@@ -64172,7 +64172,7 @@
       </c>
       <c r="G1269" t="inlineStr">
         <is>
-          <t>Elaine Assis</t>
+          <t>Daniel Moraes</t>
         </is>
       </c>
       <c r="H1269" t="inlineStr">
@@ -64184,10 +64184,10 @@
         <v>0</v>
       </c>
       <c r="J1269" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K1269" t="n">
-        <v>67</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1270">
@@ -64223,22 +64223,22 @@
       </c>
       <c r="G1270" t="inlineStr">
         <is>
-          <t>Eliene Lima</t>
+          <t>Danilo Xavier</t>
         </is>
       </c>
       <c r="H1270" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I1270" t="n">
         <v>0</v>
       </c>
       <c r="J1270" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="K1270" t="n">
-        <v>44</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1271">
@@ -64274,7 +64274,7 @@
       </c>
       <c r="G1271" t="inlineStr">
         <is>
-          <t>Erica Oliveira</t>
+          <t>Elaine Assis</t>
         </is>
       </c>
       <c r="H1271" t="inlineStr">
@@ -64283,13 +64283,13 @@
         </is>
       </c>
       <c r="I1271" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1271" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="K1271" t="n">
-        <v>47</v>
+        <v>67</v>
       </c>
     </row>
     <row r="1272">
@@ -64325,22 +64325,22 @@
       </c>
       <c r="G1272" t="inlineStr">
         <is>
-          <t>Evellin Bispo</t>
+          <t>Eliene Lima</t>
         </is>
       </c>
       <c r="H1272" t="inlineStr">
         <is>
-          <t>Leandro Matos</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I1272" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1272" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K1272" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
     </row>
     <row r="1273">
@@ -64376,22 +64376,22 @@
       </c>
       <c r="G1273" t="inlineStr">
         <is>
-          <t>Fabiane Branco</t>
+          <t>Erica Oliveira</t>
         </is>
       </c>
       <c r="H1273" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I1273" t="n">
         <v>0</v>
       </c>
       <c r="J1273" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="K1273" t="n">
-        <v>134</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1274">
@@ -64427,22 +64427,22 @@
       </c>
       <c r="G1274" t="inlineStr">
         <is>
-          <t>Franciele Alves</t>
+          <t>Evellin Bispo</t>
         </is>
       </c>
       <c r="H1274" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Leandro Matos</t>
         </is>
       </c>
       <c r="I1274" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1274" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K1274" t="n">
-        <v>57</v>
+        <v>32</v>
       </c>
     </row>
     <row r="1275">
@@ -64478,22 +64478,22 @@
       </c>
       <c r="G1275" t="inlineStr">
         <is>
-          <t>Gabriela Peres</t>
+          <t>Fabiane Branco</t>
         </is>
       </c>
       <c r="H1275" t="inlineStr">
         <is>
-          <t>Leandro Matos</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I1275" t="n">
         <v>0</v>
       </c>
       <c r="J1275" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="K1275" t="n">
-        <v>14</v>
+        <v>134</v>
       </c>
     </row>
     <row r="1276">
@@ -64529,22 +64529,22 @@
       </c>
       <c r="G1276" t="inlineStr">
         <is>
-          <t>Grasiele Santos</t>
+          <t>Franciele Alves</t>
         </is>
       </c>
       <c r="H1276" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I1276" t="n">
         <v>0</v>
       </c>
       <c r="J1276" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K1276" t="n">
-        <v>143</v>
+        <v>84</v>
       </c>
     </row>
     <row r="1277">
@@ -64580,22 +64580,22 @@
       </c>
       <c r="G1277" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Gabriela Peres</t>
         </is>
       </c>
       <c r="H1277" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Leandro Matos</t>
         </is>
       </c>
       <c r="I1277" t="n">
         <v>0</v>
       </c>
       <c r="J1277" t="n">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="K1277" t="n">
-        <v>169</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1278">
@@ -64631,7 +64631,7 @@
       </c>
       <c r="G1278" t="inlineStr">
         <is>
-          <t>Janaina Rocha</t>
+          <t>Grasiele Santos</t>
         </is>
       </c>
       <c r="H1278" t="inlineStr">
@@ -64643,10 +64643,10 @@
         <v>0</v>
       </c>
       <c r="J1278" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="K1278" t="n">
-        <v>106</v>
+        <v>143</v>
       </c>
     </row>
     <row r="1279">
@@ -64682,22 +64682,22 @@
       </c>
       <c r="G1279" t="inlineStr">
         <is>
-          <t>Jayne Tavares</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="H1279" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I1279" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="J1279" t="n">
-        <v>2</v>
+        <v>91</v>
       </c>
       <c r="K1279" t="n">
-        <v>127</v>
+        <v>190</v>
       </c>
     </row>
     <row r="1280">
@@ -64733,7 +64733,7 @@
       </c>
       <c r="G1280" t="inlineStr">
         <is>
-          <t>Jhenifer Tenorio</t>
+          <t>Janaina Rocha</t>
         </is>
       </c>
       <c r="H1280" t="inlineStr">
@@ -64745,10 +64745,10 @@
         <v>0</v>
       </c>
       <c r="J1280" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="K1280" t="n">
-        <v>115</v>
+        <v>106</v>
       </c>
     </row>
     <row r="1281">
@@ -64784,22 +64784,22 @@
       </c>
       <c r="G1281" t="inlineStr">
         <is>
-          <t>Jonas Nunes</t>
+          <t>Jayne Tavares</t>
         </is>
       </c>
       <c r="H1281" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I1281" t="n">
         <v>0</v>
       </c>
       <c r="J1281" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="K1281" t="n">
-        <v>112</v>
+        <v>127</v>
       </c>
     </row>
     <row r="1282">
@@ -64835,22 +64835,22 @@
       </c>
       <c r="G1282" t="inlineStr">
         <is>
-          <t>Kaique Souza</t>
+          <t>Jhenifer Tenorio</t>
         </is>
       </c>
       <c r="H1282" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I1282" t="n">
         <v>0</v>
       </c>
       <c r="J1282" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="K1282" t="n">
-        <v>89</v>
+        <v>115</v>
       </c>
     </row>
     <row r="1283">
@@ -64886,22 +64886,22 @@
       </c>
       <c r="G1283" t="inlineStr">
         <is>
-          <t>Karine Sousa</t>
+          <t>Jonas Nunes</t>
         </is>
       </c>
       <c r="H1283" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I1283" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1283" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="K1283" t="n">
-        <v>66</v>
+        <v>114</v>
       </c>
     </row>
     <row r="1284">
@@ -64937,22 +64937,22 @@
       </c>
       <c r="G1284" t="inlineStr">
         <is>
-          <t>Laysla Alves</t>
+          <t>Kaique Souza</t>
         </is>
       </c>
       <c r="H1284" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I1284" t="n">
         <v>0</v>
       </c>
       <c r="J1284" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="K1284" t="n">
-        <v>60</v>
+        <v>89</v>
       </c>
     </row>
     <row r="1285">
@@ -64988,22 +64988,22 @@
       </c>
       <c r="G1285" t="inlineStr">
         <is>
-          <t>Luana Marques</t>
+          <t>Karine Sousa</t>
         </is>
       </c>
       <c r="H1285" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I1285" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1285" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="K1285" t="n">
-        <v>19</v>
+        <v>68</v>
       </c>
     </row>
     <row r="1286">
@@ -65039,22 +65039,22 @@
       </c>
       <c r="G1286" t="inlineStr">
         <is>
-          <t>Maria Pires</t>
+          <t>Laysla Alves</t>
         </is>
       </c>
       <c r="H1286" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I1286" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1286" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="K1286" t="n">
-        <v>1</v>
+        <v>63</v>
       </c>
     </row>
     <row r="1287">
@@ -65090,22 +65090,22 @@
       </c>
       <c r="G1287" t="inlineStr">
         <is>
-          <t>Mauricio Lermen</t>
+          <t>Luana Marques</t>
         </is>
       </c>
       <c r="H1287" t="inlineStr">
         <is>
-          <t>Mauricio Lermen</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I1287" t="n">
         <v>0</v>
       </c>
       <c r="J1287" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1287" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1288">
@@ -65141,22 +65141,22 @@
       </c>
       <c r="G1288" t="inlineStr">
         <is>
-          <t>Micaele Cordeiro</t>
+          <t>Maria Pires</t>
         </is>
       </c>
       <c r="H1288" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I1288" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="J1288" t="n">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="K1288" t="n">
-        <v>102</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1289">
@@ -65192,22 +65192,22 @@
       </c>
       <c r="G1289" t="inlineStr">
         <is>
-          <t>Michele Silva</t>
+          <t>Mauricio Lermen</t>
         </is>
       </c>
       <c r="H1289" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>Mauricio Lermen</t>
         </is>
       </c>
       <c r="I1289" t="n">
         <v>0</v>
       </c>
       <c r="J1289" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="K1289" t="n">
-        <v>83</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1290">
@@ -65243,18 +65243,22 @@
       </c>
       <c r="G1290" t="inlineStr">
         <is>
-          <t>Mikael Teixeira</t>
-        </is>
-      </c>
-      <c r="H1290" t="inlineStr"/>
+          <t>Micaele Cordeiro</t>
+        </is>
+      </c>
+      <c r="H1290" t="inlineStr">
+        <is>
+          <t>Sara Cavalheiro</t>
+        </is>
+      </c>
       <c r="I1290" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J1290" t="n">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="K1290" t="n">
-        <v>4</v>
+        <v>120</v>
       </c>
     </row>
     <row r="1291">
@@ -65290,22 +65294,22 @@
       </c>
       <c r="G1291" t="inlineStr">
         <is>
-          <t>Murilo Marques</t>
+          <t>Michele Silva</t>
         </is>
       </c>
       <c r="H1291" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I1291" t="n">
         <v>0</v>
       </c>
       <c r="J1291" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="K1291" t="n">
-        <v>61</v>
+        <v>83</v>
       </c>
     </row>
     <row r="1292">
@@ -65341,22 +65345,18 @@
       </c>
       <c r="G1292" t="inlineStr">
         <is>
-          <t>Natalia Batista</t>
-        </is>
-      </c>
-      <c r="H1292" t="inlineStr">
-        <is>
-          <t>Edivaldo Veiga</t>
-        </is>
-      </c>
+          <t>Mikael Teixeira</t>
+        </is>
+      </c>
+      <c r="H1292" t="inlineStr"/>
       <c r="I1292" t="n">
         <v>0</v>
       </c>
       <c r="J1292" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="K1292" t="n">
-        <v>110</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1293">
@@ -65392,7 +65392,7 @@
       </c>
       <c r="G1293" t="inlineStr">
         <is>
-          <t>Natalia Silva</t>
+          <t>Murilo Marques</t>
         </is>
       </c>
       <c r="H1293" t="inlineStr">
@@ -65407,7 +65407,7 @@
         <v>19</v>
       </c>
       <c r="K1293" t="n">
-        <v>113</v>
+        <v>61</v>
       </c>
     </row>
     <row r="1294">
@@ -65443,12 +65443,12 @@
       </c>
       <c r="G1294" t="inlineStr">
         <is>
-          <t>Oliene Mariano</t>
+          <t>Natalia Batista</t>
         </is>
       </c>
       <c r="H1294" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I1294" t="n">
@@ -65458,7 +65458,7 @@
         <v>23</v>
       </c>
       <c r="K1294" t="n">
-        <v>97</v>
+        <v>110</v>
       </c>
     </row>
     <row r="1295">
@@ -65494,22 +65494,22 @@
       </c>
       <c r="G1295" t="inlineStr">
         <is>
-          <t>Priscila Aguiar</t>
+          <t>Natalia Silva</t>
         </is>
       </c>
       <c r="H1295" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I1295" t="n">
         <v>0</v>
       </c>
       <c r="J1295" t="n">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="K1295" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="1296">
@@ -65545,22 +65545,22 @@
       </c>
       <c r="G1296" t="inlineStr">
         <is>
-          <t>Rebeca Ribeiro</t>
+          <t>Oliene Mariano</t>
         </is>
       </c>
       <c r="H1296" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I1296" t="n">
         <v>0</v>
       </c>
       <c r="J1296" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="K1296" t="n">
-        <v>66</v>
+        <v>97</v>
       </c>
     </row>
     <row r="1297">
@@ -65596,7 +65596,7 @@
       </c>
       <c r="G1297" t="inlineStr">
         <is>
-          <t>Roberta Souza</t>
+          <t>Priscila Aguiar</t>
         </is>
       </c>
       <c r="H1297" t="inlineStr">
@@ -65605,13 +65605,13 @@
         </is>
       </c>
       <c r="I1297" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1297" t="n">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="K1297" t="n">
-        <v>99</v>
+        <v>112</v>
       </c>
     </row>
     <row r="1298">
@@ -65647,7 +65647,7 @@
       </c>
       <c r="G1298" t="inlineStr">
         <is>
-          <t>Ronildo Santos</t>
+          <t>Rebeca Ribeiro</t>
         </is>
       </c>
       <c r="H1298" t="inlineStr">
@@ -65659,10 +65659,10 @@
         <v>0</v>
       </c>
       <c r="J1298" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K1298" t="n">
-        <v>6</v>
+        <v>66</v>
       </c>
     </row>
     <row r="1299">
@@ -65698,22 +65698,22 @@
       </c>
       <c r="G1299" t="inlineStr">
         <is>
-          <t>Rozania Santos</t>
+          <t>Roberta Souza</t>
         </is>
       </c>
       <c r="H1299" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I1299" t="n">
         <v>0</v>
       </c>
       <c r="J1299" t="n">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="K1299" t="n">
-        <v>139</v>
+        <v>99</v>
       </c>
     </row>
     <row r="1300">
@@ -65749,22 +65749,22 @@
       </c>
       <c r="G1300" t="inlineStr">
         <is>
-          <t>Santos Karina</t>
+          <t>Ronildo Santos</t>
         </is>
       </c>
       <c r="H1300" t="inlineStr">
         <is>
-          <t>Leandro Matos</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I1300" t="n">
         <v>0</v>
       </c>
       <c r="J1300" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K1300" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1301">
@@ -65800,7 +65800,7 @@
       </c>
       <c r="G1301" t="inlineStr">
         <is>
-          <t>Sibelly Pereira</t>
+          <t>Rozania Santos</t>
         </is>
       </c>
       <c r="H1301" t="inlineStr">
@@ -65809,13 +65809,13 @@
         </is>
       </c>
       <c r="I1301" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1301" t="n">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="K1301" t="n">
-        <v>64</v>
+        <v>141</v>
       </c>
     </row>
     <row r="1302">
@@ -65851,22 +65851,22 @@
       </c>
       <c r="G1302" t="inlineStr">
         <is>
-          <t>Tania Luz</t>
+          <t>Santos Karina</t>
         </is>
       </c>
       <c r="H1302" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>Leandro Matos</t>
         </is>
       </c>
       <c r="I1302" t="n">
         <v>0</v>
       </c>
       <c r="J1302" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K1302" t="n">
-        <v>77</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1303">
@@ -65902,7 +65902,7 @@
       </c>
       <c r="G1303" t="inlineStr">
         <is>
-          <t>Vitor Guedes</t>
+          <t>Sibelly Pereira</t>
         </is>
       </c>
       <c r="H1303" t="inlineStr">
@@ -65911,13 +65911,13 @@
         </is>
       </c>
       <c r="I1303" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J1303" t="n">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="K1303" t="n">
-        <v>134</v>
+        <v>94</v>
       </c>
     </row>
     <row r="1304">
@@ -65948,27 +65948,27 @@
       </c>
       <c r="F1304" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="G1304" t="inlineStr">
         <is>
-          <t>Andrea Medeiros</t>
+          <t>Tania Luz</t>
         </is>
       </c>
       <c r="H1304" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I1304" t="n">
         <v>0</v>
       </c>
       <c r="J1304" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K1304" t="n">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="1305">
@@ -65999,27 +65999,27 @@
       </c>
       <c r="F1305" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="G1305" t="inlineStr">
         <is>
-          <t>Caroline Nascimento</t>
+          <t>Vitor Guedes</t>
         </is>
       </c>
       <c r="H1305" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I1305" t="n">
         <v>0</v>
       </c>
       <c r="J1305" t="n">
-        <v>98</v>
+        <v>5</v>
       </c>
       <c r="K1305" t="n">
-        <v>151</v>
+        <v>134</v>
       </c>
     </row>
     <row r="1306">
@@ -66055,7 +66055,7 @@
       </c>
       <c r="G1306" t="inlineStr">
         <is>
-          <t>Cristiana Grizostomo</t>
+          <t>Andrea Medeiros</t>
         </is>
       </c>
       <c r="H1306" t="inlineStr">
@@ -66067,10 +66067,10 @@
         <v>0</v>
       </c>
       <c r="J1306" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K1306" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
     </row>
     <row r="1307">
@@ -66106,18 +66106,22 @@
       </c>
       <c r="G1307" t="inlineStr">
         <is>
-          <t>Denis Reis</t>
-        </is>
-      </c>
-      <c r="H1307" t="inlineStr"/>
+          <t>Caroline Nascimento</t>
+        </is>
+      </c>
+      <c r="H1307" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
       <c r="I1307" t="n">
         <v>0</v>
       </c>
       <c r="J1307" t="n">
-        <v>22</v>
+        <v>98</v>
       </c>
       <c r="K1307" t="n">
-        <v>89</v>
+        <v>151</v>
       </c>
     </row>
     <row r="1308">
@@ -66153,7 +66157,7 @@
       </c>
       <c r="G1308" t="inlineStr">
         <is>
-          <t>Eliane Moreira</t>
+          <t>Cristiana Grizostomo</t>
         </is>
       </c>
       <c r="H1308" t="inlineStr">
@@ -66162,13 +66166,13 @@
         </is>
       </c>
       <c r="I1308" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J1308" t="n">
-        <v>77</v>
+        <v>30</v>
       </c>
       <c r="K1308" t="n">
-        <v>140</v>
+        <v>63</v>
       </c>
     </row>
     <row r="1309">
@@ -66204,22 +66208,18 @@
       </c>
       <c r="G1309" t="inlineStr">
         <is>
-          <t>Gustavo Tonan</t>
-        </is>
-      </c>
-      <c r="H1309" t="inlineStr">
-        <is>
-          <t>Nayara Oliveira</t>
-        </is>
-      </c>
+          <t>Denis Reis</t>
+        </is>
+      </c>
+      <c r="H1309" t="inlineStr"/>
       <c r="I1309" t="n">
         <v>0</v>
       </c>
       <c r="J1309" t="n">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="K1309" t="n">
-        <v>101</v>
+        <v>89</v>
       </c>
     </row>
     <row r="1310">
@@ -66255,7 +66255,7 @@
       </c>
       <c r="G1310" t="inlineStr">
         <is>
-          <t>Jonatan Hayashibara</t>
+          <t>Eliane Moreira</t>
         </is>
       </c>
       <c r="H1310" t="inlineStr">
@@ -66264,13 +66264,13 @@
         </is>
       </c>
       <c r="I1310" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1310" t="n">
-        <v>490</v>
+        <v>79</v>
       </c>
       <c r="K1310" t="n">
-        <v>602</v>
+        <v>143</v>
       </c>
     </row>
     <row r="1311">
@@ -66306,7 +66306,7 @@
       </c>
       <c r="G1311" t="inlineStr">
         <is>
-          <t>Lais Arruda</t>
+          <t>Gustavo Tonan</t>
         </is>
       </c>
       <c r="H1311" t="inlineStr">
@@ -66315,13 +66315,13 @@
         </is>
       </c>
       <c r="I1311" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="J1311" t="n">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="K1311" t="n">
-        <v>111</v>
+        <v>122</v>
       </c>
     </row>
     <row r="1312">
@@ -66357,7 +66357,7 @@
       </c>
       <c r="G1312" t="inlineStr">
         <is>
-          <t>Luan Batista</t>
+          <t>Jonatan Hayashibara</t>
         </is>
       </c>
       <c r="H1312" t="inlineStr">
@@ -66366,13 +66366,13 @@
         </is>
       </c>
       <c r="I1312" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J1312" t="n">
-        <v>48</v>
+        <v>514</v>
       </c>
       <c r="K1312" t="n">
-        <v>85</v>
+        <v>626</v>
       </c>
     </row>
     <row r="1313">
@@ -66408,7 +66408,7 @@
       </c>
       <c r="G1313" t="inlineStr">
         <is>
-          <t>Maria Garcia</t>
+          <t>Lais Arruda</t>
         </is>
       </c>
       <c r="H1313" t="inlineStr">
@@ -66417,13 +66417,13 @@
         </is>
       </c>
       <c r="I1313" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1313" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="K1313" t="n">
-        <v>82</v>
+        <v>112</v>
       </c>
     </row>
     <row r="1314">
@@ -66459,7 +66459,7 @@
       </c>
       <c r="G1314" t="inlineStr">
         <is>
-          <t>Priscila Volpe</t>
+          <t>Luan Batista</t>
         </is>
       </c>
       <c r="H1314" t="inlineStr">
@@ -66468,13 +66468,13 @@
         </is>
       </c>
       <c r="I1314" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1314" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K1314" t="n">
-        <v>11</v>
+        <v>87</v>
       </c>
     </row>
     <row r="1315">
@@ -66510,7 +66510,7 @@
       </c>
       <c r="G1315" t="inlineStr">
         <is>
-          <t>Rodrigo Souza</t>
+          <t>Maria Garcia</t>
         </is>
       </c>
       <c r="H1315" t="inlineStr">
@@ -66519,13 +66519,13 @@
         </is>
       </c>
       <c r="I1315" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J1315" t="n">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="K1315" t="n">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="1316">
@@ -66561,7 +66561,7 @@
       </c>
       <c r="G1316" t="inlineStr">
         <is>
-          <t>Romario Silva</t>
+          <t>Priscila Volpe</t>
         </is>
       </c>
       <c r="H1316" t="inlineStr">
@@ -66573,10 +66573,10 @@
         <v>0</v>
       </c>
       <c r="J1316" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="K1316" t="n">
-        <v>230</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1317">
@@ -66612,7 +66612,7 @@
       </c>
       <c r="G1317" t="inlineStr">
         <is>
-          <t>Rosilene Santos</t>
+          <t>Rodrigo Souza</t>
         </is>
       </c>
       <c r="H1317" t="inlineStr">
@@ -66621,13 +66621,13 @@
         </is>
       </c>
       <c r="I1317" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J1317" t="n">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="K1317" t="n">
-        <v>81</v>
+        <v>99</v>
       </c>
     </row>
     <row r="1318">
@@ -66663,7 +66663,7 @@
       </c>
       <c r="G1318" t="inlineStr">
         <is>
-          <t>Suede Gomes</t>
+          <t>Romario Silva</t>
         </is>
       </c>
       <c r="H1318" t="inlineStr">
@@ -66672,13 +66672,13 @@
         </is>
       </c>
       <c r="I1318" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J1318" t="n">
-        <v>24</v>
+        <v>111</v>
       </c>
       <c r="K1318" t="n">
-        <v>52</v>
+        <v>236</v>
       </c>
     </row>
     <row r="1319">
@@ -66714,7 +66714,7 @@
       </c>
       <c r="G1319" t="inlineStr">
         <is>
-          <t>Taina Silva</t>
+          <t>Rosilene Santos</t>
         </is>
       </c>
       <c r="H1319" t="inlineStr">
@@ -66726,10 +66726,10 @@
         <v>0</v>
       </c>
       <c r="J1319" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="K1319" t="n">
-        <v>64</v>
+        <v>81</v>
       </c>
     </row>
     <row r="1320">
@@ -66765,7 +66765,7 @@
       </c>
       <c r="G1320" t="inlineStr">
         <is>
-          <t>Thayna Melo</t>
+          <t>Suede Gomes</t>
         </is>
       </c>
       <c r="H1320" t="inlineStr">
@@ -66774,13 +66774,13 @@
         </is>
       </c>
       <c r="I1320" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1320" t="n">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="K1320" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="1321">
@@ -66816,7 +66816,7 @@
       </c>
       <c r="G1321" t="inlineStr">
         <is>
-          <t>Vanessa Santana</t>
+          <t>Taina Silva</t>
         </is>
       </c>
       <c r="H1321" t="inlineStr">
@@ -66825,13 +66825,13 @@
         </is>
       </c>
       <c r="I1321" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1321" t="n">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="K1321" t="n">
-        <v>181</v>
+        <v>66</v>
       </c>
     </row>
     <row r="1322">
@@ -66862,27 +66862,27 @@
       </c>
       <c r="F1322" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="G1322" t="inlineStr">
         <is>
-          <t>Alaine Neres</t>
+          <t>Thayna Melo</t>
         </is>
       </c>
       <c r="H1322" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
       <c r="I1322" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J1322" t="n">
-        <v>91</v>
+        <v>50</v>
       </c>
       <c r="K1322" t="n">
-        <v>148</v>
+        <v>58</v>
       </c>
     </row>
     <row r="1323">
@@ -66913,27 +66913,27 @@
       </c>
       <c r="F1323" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="G1323" t="inlineStr">
         <is>
-          <t>Andre Silva</t>
+          <t>Vanessa Santana</t>
         </is>
       </c>
       <c r="H1323" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
       <c r="I1323" t="n">
         <v>0</v>
       </c>
       <c r="J1323" t="n">
-        <v>16</v>
+        <v>63</v>
       </c>
       <c r="K1323" t="n">
-        <v>73</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1324">
@@ -66969,22 +66969,22 @@
       </c>
       <c r="G1324" t="inlineStr">
         <is>
-          <t>Anna Ramalho</t>
+          <t>Alaine Neres</t>
         </is>
       </c>
       <c r="H1324" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I1324" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J1324" t="n">
-        <v>24</v>
+        <v>112</v>
       </c>
       <c r="K1324" t="n">
-        <v>80</v>
+        <v>169</v>
       </c>
     </row>
     <row r="1325">
@@ -67020,22 +67020,22 @@
       </c>
       <c r="G1325" t="inlineStr">
         <is>
-          <t>Beatriz Ferreira</t>
+          <t>Andre Silva</t>
         </is>
       </c>
       <c r="H1325" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I1325" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1325" t="n">
-        <v>102</v>
+        <v>17</v>
       </c>
       <c r="K1325" t="n">
-        <v>141</v>
+        <v>74</v>
       </c>
     </row>
     <row r="1326">
@@ -67071,22 +67071,22 @@
       </c>
       <c r="G1326" t="inlineStr">
         <is>
-          <t>Brenda Batista</t>
+          <t>Anna Ramalho</t>
         </is>
       </c>
       <c r="H1326" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="I1326" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1326" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="K1326" t="n">
-        <v>54</v>
+        <v>82</v>
       </c>
     </row>
     <row r="1327">
@@ -67122,22 +67122,22 @@
       </c>
       <c r="G1327" t="inlineStr">
         <is>
-          <t>Bruna Souza</t>
+          <t>Beatriz Ferreira</t>
         </is>
       </c>
       <c r="H1327" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="I1327" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1327" t="n">
-        <v>28</v>
+        <v>103</v>
       </c>
       <c r="K1327" t="n">
-        <v>75</v>
+        <v>142</v>
       </c>
     </row>
     <row r="1328">
@@ -67173,22 +67173,22 @@
       </c>
       <c r="G1328" t="inlineStr">
         <is>
-          <t>Bruno Henrique</t>
+          <t>Brenda Batista</t>
         </is>
       </c>
       <c r="H1328" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I1328" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1328" t="n">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="K1328" t="n">
-        <v>122</v>
+        <v>53</v>
       </c>
     </row>
     <row r="1329">
@@ -67224,18 +67224,22 @@
       </c>
       <c r="G1329" t="inlineStr">
         <is>
-          <t>Claudineia Rodrigues</t>
-        </is>
-      </c>
-      <c r="H1329" t="inlineStr"/>
+          <t>Bruna Souza</t>
+        </is>
+      </c>
+      <c r="H1329" t="inlineStr">
+        <is>
+          <t>Thaiza Oliveira</t>
+        </is>
+      </c>
       <c r="I1329" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1329" t="n">
-        <v>67</v>
+        <v>29</v>
       </c>
       <c r="K1329" t="n">
-        <v>185</v>
+        <v>76</v>
       </c>
     </row>
     <row r="1330">
@@ -67271,22 +67275,22 @@
       </c>
       <c r="G1330" t="inlineStr">
         <is>
-          <t>Cristina Leite</t>
+          <t>Bruno Henrique</t>
         </is>
       </c>
       <c r="H1330" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I1330" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J1330" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="K1330" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
     </row>
     <row r="1331">
@@ -67322,22 +67326,18 @@
       </c>
       <c r="G1331" t="inlineStr">
         <is>
-          <t>Davi Santos</t>
-        </is>
-      </c>
-      <c r="H1331" t="inlineStr">
-        <is>
-          <t>Thaiza Oliveira</t>
-        </is>
-      </c>
+          <t>Claudineia Rodrigues</t>
+        </is>
+      </c>
+      <c r="H1331" t="inlineStr"/>
       <c r="I1331" t="n">
         <v>0</v>
       </c>
       <c r="J1331" t="n">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="K1331" t="n">
-        <v>82</v>
+        <v>186</v>
       </c>
     </row>
     <row r="1332">
@@ -67373,22 +67373,22 @@
       </c>
       <c r="G1332" t="inlineStr">
         <is>
-          <t>Deleia Oliveira</t>
+          <t>Cristina Leite</t>
         </is>
       </c>
       <c r="H1332" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="I1332" t="n">
         <v>0</v>
       </c>
       <c r="J1332" t="n">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="K1332" t="n">
-        <v>97</v>
+        <v>150</v>
       </c>
     </row>
     <row r="1333">
@@ -67424,7 +67424,7 @@
       </c>
       <c r="G1333" t="inlineStr">
         <is>
-          <t>Diego Pereira</t>
+          <t>Davi Santos</t>
         </is>
       </c>
       <c r="H1333" t="inlineStr">
@@ -67433,13 +67433,13 @@
         </is>
       </c>
       <c r="I1333" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J1333" t="n">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="K1333" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="1334">
@@ -67475,22 +67475,22 @@
       </c>
       <c r="G1334" t="inlineStr">
         <is>
-          <t>Eduardo Lopes</t>
+          <t>Deleia Oliveira</t>
         </is>
       </c>
       <c r="H1334" t="inlineStr">
         <is>
-          <t>Idna Sousa</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I1334" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J1334" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="K1334" t="n">
-        <v>17</v>
+        <v>111</v>
       </c>
     </row>
     <row r="1335">
@@ -67526,22 +67526,22 @@
       </c>
       <c r="G1335" t="inlineStr">
         <is>
-          <t>Gislaine Lima</t>
+          <t>Diego Pereira</t>
         </is>
       </c>
       <c r="H1335" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I1335" t="n">
         <v>0</v>
       </c>
       <c r="J1335" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K1335" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
     </row>
     <row r="1336">
@@ -67577,22 +67577,22 @@
       </c>
       <c r="G1336" t="inlineStr">
         <is>
-          <t>Gustavo Santos</t>
+          <t>Eduardo Lopes</t>
         </is>
       </c>
       <c r="H1336" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Idna Sousa</t>
         </is>
       </c>
       <c r="I1336" t="n">
         <v>0</v>
       </c>
       <c r="J1336" t="n">
-        <v>113</v>
+        <v>4</v>
       </c>
       <c r="K1336" t="n">
-        <v>221</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1337">
@@ -67628,22 +67628,22 @@
       </c>
       <c r="G1337" t="inlineStr">
         <is>
-          <t>Igor Valezi</t>
+          <t>Gislaine Lima</t>
         </is>
       </c>
       <c r="H1337" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I1337" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J1337" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="K1337" t="n">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="1338">
@@ -67679,22 +67679,22 @@
       </c>
       <c r="G1338" t="inlineStr">
         <is>
-          <t>Izabely Araujo</t>
+          <t>Gustavo Santos</t>
         </is>
       </c>
       <c r="H1338" t="inlineStr">
         <is>
-          <t>Idna Sousa</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="I1338" t="n">
         <v>0</v>
       </c>
       <c r="J1338" t="n">
-        <v>6</v>
+        <v>111</v>
       </c>
       <c r="K1338" t="n">
-        <v>10</v>
+        <v>219</v>
       </c>
     </row>
     <row r="1339">
@@ -67730,22 +67730,22 @@
       </c>
       <c r="G1339" t="inlineStr">
         <is>
-          <t>Joanna Costa</t>
+          <t>Igor Valezi</t>
         </is>
       </c>
       <c r="H1339" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I1339" t="n">
         <v>0</v>
       </c>
       <c r="J1339" t="n">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="K1339" t="n">
-        <v>25</v>
+        <v>101</v>
       </c>
     </row>
     <row r="1340">
@@ -67781,22 +67781,22 @@
       </c>
       <c r="G1340" t="inlineStr">
         <is>
-          <t>Jose Natan</t>
+          <t>Izabely Araujo</t>
         </is>
       </c>
       <c r="H1340" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Idna Sousa</t>
         </is>
       </c>
       <c r="I1340" t="n">
         <v>0</v>
       </c>
       <c r="J1340" t="n">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="K1340" t="n">
-        <v>101</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1341">
@@ -67832,22 +67832,22 @@
       </c>
       <c r="G1341" t="inlineStr">
         <is>
-          <t>João Oliveira</t>
+          <t>Joanna Costa</t>
         </is>
       </c>
       <c r="H1341" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I1341" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1341" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="K1341" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1342">
@@ -67883,22 +67883,22 @@
       </c>
       <c r="G1342" t="inlineStr">
         <is>
-          <t>Juan Ribeiro</t>
+          <t>Jose Natan</t>
         </is>
       </c>
       <c r="H1342" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I1342" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1342" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K1342" t="n">
-        <v>85</v>
+        <v>102</v>
       </c>
     </row>
     <row r="1343">
@@ -67934,7 +67934,7 @@
       </c>
       <c r="G1343" t="inlineStr">
         <is>
-          <t>Juliana Valeria</t>
+          <t>João Oliveira</t>
         </is>
       </c>
       <c r="H1343" t="inlineStr">
@@ -67946,10 +67946,10 @@
         <v>0</v>
       </c>
       <c r="J1343" t="n">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="K1343" t="n">
-        <v>101</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1344">
@@ -67985,22 +67985,22 @@
       </c>
       <c r="G1344" t="inlineStr">
         <is>
-          <t>Juliane Vaz</t>
+          <t>Juan Ribeiro</t>
         </is>
       </c>
       <c r="H1344" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I1344" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1344" t="n">
-        <v>164</v>
+        <v>42</v>
       </c>
       <c r="K1344" t="n">
-        <v>264</v>
+        <v>86</v>
       </c>
     </row>
     <row r="1345">
@@ -68036,22 +68036,22 @@
       </c>
       <c r="G1345" t="inlineStr">
         <is>
-          <t>Katia Xavier</t>
+          <t>Juliana Valeria</t>
         </is>
       </c>
       <c r="H1345" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I1345" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J1345" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="K1345" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
     </row>
     <row r="1346">
@@ -68087,22 +68087,22 @@
       </c>
       <c r="G1346" t="inlineStr">
         <is>
-          <t>Larissa Félix</t>
+          <t>Juliane Vaz</t>
         </is>
       </c>
       <c r="H1346" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I1346" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J1346" t="n">
-        <v>123</v>
+        <v>174</v>
       </c>
       <c r="K1346" t="n">
-        <v>186</v>
+        <v>274</v>
       </c>
     </row>
     <row r="1347">
@@ -68138,7 +68138,7 @@
       </c>
       <c r="G1347" t="inlineStr">
         <is>
-          <t>Léia de Oliveira</t>
+          <t>Katia Xavier</t>
         </is>
       </c>
       <c r="H1347" t="inlineStr">
@@ -68147,13 +68147,13 @@
         </is>
       </c>
       <c r="I1347" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J1347" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="K1347" t="n">
-        <v>117</v>
+        <v>106</v>
       </c>
     </row>
     <row r="1348">
@@ -68189,22 +68189,22 @@
       </c>
       <c r="G1348" t="inlineStr">
         <is>
-          <t>Maria Gualberto</t>
+          <t>Larissa Félix</t>
         </is>
       </c>
       <c r="H1348" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I1348" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J1348" t="n">
-        <v>20</v>
+        <v>147</v>
       </c>
       <c r="K1348" t="n">
-        <v>101</v>
+        <v>210</v>
       </c>
     </row>
     <row r="1349">
@@ -68240,22 +68240,22 @@
       </c>
       <c r="G1349" t="inlineStr">
         <is>
-          <t>Priscila Moreira</t>
+          <t>Léia de Oliveira</t>
         </is>
       </c>
       <c r="H1349" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I1349" t="n">
         <v>0</v>
       </c>
       <c r="J1349" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="K1349" t="n">
-        <v>84</v>
+        <v>117</v>
       </c>
     </row>
     <row r="1350">
@@ -68291,22 +68291,22 @@
       </c>
       <c r="G1350" t="inlineStr">
         <is>
-          <t>Regiane Santos</t>
+          <t>Maria Gualberto</t>
         </is>
       </c>
       <c r="H1350" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I1350" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1350" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="K1350" t="n">
-        <v>57</v>
+        <v>103</v>
       </c>
     </row>
     <row r="1351">
@@ -68342,22 +68342,22 @@
       </c>
       <c r="G1351" t="inlineStr">
         <is>
-          <t>Shofia Gomes</t>
+          <t>Nathany Silva</t>
         </is>
       </c>
       <c r="H1351" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I1351" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1351" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="K1351" t="n">
-        <v>125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1352">
@@ -68393,22 +68393,22 @@
       </c>
       <c r="G1352" t="inlineStr">
         <is>
-          <t>Vanessa Tavares</t>
+          <t>Priscila Moreira</t>
         </is>
       </c>
       <c r="H1352" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="I1352" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J1352" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="K1352" t="n">
-        <v>83</v>
+        <v>97</v>
       </c>
     </row>
     <row r="1353">
@@ -68444,7 +68444,7 @@
       </c>
       <c r="G1353" t="inlineStr">
         <is>
-          <t>Willian Luz</t>
+          <t>Regiane Santos</t>
         </is>
       </c>
       <c r="H1353" t="inlineStr">
@@ -68453,13 +68453,13 @@
         </is>
       </c>
       <c r="I1353" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J1353" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="K1353" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
     </row>
     <row r="1354">
@@ -68495,22 +68495,22 @@
       </c>
       <c r="G1354" t="inlineStr">
         <is>
-          <t>Yasmim Oliveira</t>
+          <t>Shofia Gomes</t>
         </is>
       </c>
       <c r="H1354" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="I1354" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1354" t="n">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="K1354" t="n">
-        <v>40</v>
+        <v>126</v>
       </c>
     </row>
     <row r="1355">
@@ -68541,23 +68541,27 @@
       </c>
       <c r="F1355" t="inlineStr">
         <is>
-          <t>ESCRITA FISCAL (Outsourcing)</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="G1355" t="inlineStr">
         <is>
-          <t>Claudineia Rodrigues</t>
-        </is>
-      </c>
-      <c r="H1355" t="inlineStr"/>
+          <t>Vanessa Tavares</t>
+        </is>
+      </c>
+      <c r="H1355" t="inlineStr">
+        <is>
+          <t>Larice Souza</t>
+        </is>
+      </c>
       <c r="I1355" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J1355" t="n">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="K1355" t="n">
-        <v>5</v>
+        <v>89</v>
       </c>
     </row>
     <row r="1356">
@@ -68588,27 +68592,27 @@
       </c>
       <c r="F1356" t="inlineStr">
         <is>
-          <t>ESCRITA FISCAL (Outsourcing)</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="G1356" t="inlineStr">
         <is>
-          <t>Diego Pereira</t>
+          <t>Willian Luz</t>
         </is>
       </c>
       <c r="H1356" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I1356" t="n">
         <v>0</v>
       </c>
       <c r="J1356" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="K1356" t="n">
-        <v>8</v>
+        <v>77</v>
       </c>
     </row>
     <row r="1357">
@@ -68639,27 +68643,27 @@
       </c>
       <c r="F1357" t="inlineStr">
         <is>
-          <t>ESCRITA FISCAL (Outsourcing)</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="G1357" t="inlineStr">
         <is>
-          <t>Gislaine Lima</t>
+          <t>Yasmim Oliveira</t>
         </is>
       </c>
       <c r="H1357" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I1357" t="n">
         <v>0</v>
       </c>
       <c r="J1357" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="K1357" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
     </row>
     <row r="1358">
@@ -68695,22 +68699,18 @@
       </c>
       <c r="G1358" t="inlineStr">
         <is>
-          <t>Joanna Costa</t>
-        </is>
-      </c>
-      <c r="H1358" t="inlineStr">
-        <is>
-          <t>Lorrane Santos</t>
-        </is>
-      </c>
+          <t>Claudineia Rodrigues</t>
+        </is>
+      </c>
+      <c r="H1358" t="inlineStr"/>
       <c r="I1358" t="n">
         <v>0</v>
       </c>
       <c r="J1358" t="n">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="K1358" t="n">
-        <v>51</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1359">
@@ -68746,12 +68746,12 @@
       </c>
       <c r="G1359" t="inlineStr">
         <is>
-          <t>Jonatan Hayashibara</t>
+          <t>Diego Pereira</t>
         </is>
       </c>
       <c r="H1359" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I1359" t="n">
@@ -68761,7 +68761,7 @@
         <v>4</v>
       </c>
       <c r="K1359" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1360">
@@ -68797,22 +68797,22 @@
       </c>
       <c r="G1360" t="inlineStr">
         <is>
-          <t>João Oliveira</t>
+          <t>Gislaine Lima</t>
         </is>
       </c>
       <c r="H1360" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I1360" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1360" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K1360" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1361">
@@ -68848,22 +68848,22 @@
       </c>
       <c r="G1361" t="inlineStr">
         <is>
-          <t>Regiane Santos</t>
+          <t>Joanna Costa</t>
         </is>
       </c>
       <c r="H1361" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I1361" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J1361" t="n">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="K1361" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
     </row>
     <row r="1362">
@@ -68899,22 +68899,22 @@
       </c>
       <c r="G1362" t="inlineStr">
         <is>
-          <t>Yasmim Oliveira</t>
+          <t>Jonatan Hayashibara</t>
         </is>
       </c>
       <c r="H1362" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
       <c r="I1362" t="n">
         <v>0</v>
       </c>
       <c r="J1362" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K1362" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1363">
@@ -68945,23 +68945,27 @@
       </c>
       <c r="F1363" t="inlineStr">
         <is>
-          <t>FIN - CONTÁBIL</t>
+          <t>ESCRITA FISCAL (Outsourcing)</t>
         </is>
       </c>
       <c r="G1363" t="inlineStr">
         <is>
-          <t>Daniele Faria</t>
-        </is>
-      </c>
-      <c r="H1363" t="inlineStr"/>
+          <t>João Oliveira</t>
+        </is>
+      </c>
+      <c r="H1363" t="inlineStr">
+        <is>
+          <t>Larice Souza</t>
+        </is>
+      </c>
       <c r="I1363" t="n">
         <v>0</v>
       </c>
       <c r="J1363" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="K1363" t="n">
-        <v>62</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1364">
@@ -68992,23 +68996,27 @@
       </c>
       <c r="F1364" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>ESCRITA FISCAL (Outsourcing)</t>
         </is>
       </c>
       <c r="G1364" t="inlineStr">
         <is>
-          <t>Ana Santana</t>
-        </is>
-      </c>
-      <c r="H1364" t="inlineStr"/>
+          <t>Regiane Santos</t>
+        </is>
+      </c>
+      <c r="H1364" t="inlineStr">
+        <is>
+          <t>Larice Souza</t>
+        </is>
+      </c>
       <c r="I1364" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1364" t="n">
-        <v>382</v>
+        <v>8</v>
       </c>
       <c r="K1364" t="n">
-        <v>585</v>
+        <v>18</v>
       </c>
     </row>
     <row r="1365">
@@ -69039,23 +69047,27 @@
       </c>
       <c r="F1365" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>ESCRITA FISCAL (Outsourcing)</t>
         </is>
       </c>
       <c r="G1365" t="inlineStr">
         <is>
-          <t>Andre Coelho</t>
-        </is>
-      </c>
-      <c r="H1365" t="inlineStr"/>
+          <t>Yasmim Oliveira</t>
+        </is>
+      </c>
+      <c r="H1365" t="inlineStr">
+        <is>
+          <t>Larice Souza</t>
+        </is>
+      </c>
       <c r="I1365" t="n">
         <v>0</v>
       </c>
       <c r="J1365" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K1365" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1366">
@@ -69086,12 +69098,12 @@
       </c>
       <c r="F1366" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>FIN - CONTÁBIL</t>
         </is>
       </c>
       <c r="G1366" t="inlineStr">
         <is>
-          <t>Bianca Castro</t>
+          <t>Daniele Faria</t>
         </is>
       </c>
       <c r="H1366" t="inlineStr"/>
@@ -69099,10 +69111,10 @@
         <v>0</v>
       </c>
       <c r="J1366" t="n">
-        <v>265</v>
+        <v>20</v>
       </c>
       <c r="K1366" t="n">
-        <v>459</v>
+        <v>62</v>
       </c>
     </row>
     <row r="1367">
@@ -69138,18 +69150,18 @@
       </c>
       <c r="G1367" t="inlineStr">
         <is>
-          <t>Bruna Costa</t>
+          <t>Ana Santana</t>
         </is>
       </c>
       <c r="H1367" t="inlineStr"/>
       <c r="I1367" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1367" t="n">
-        <v>33</v>
+        <v>384</v>
       </c>
       <c r="K1367" t="n">
-        <v>34</v>
+        <v>587</v>
       </c>
     </row>
     <row r="1368">
@@ -69185,7 +69197,7 @@
       </c>
       <c r="G1368" t="inlineStr">
         <is>
-          <t>Daniela Silva</t>
+          <t>Andre Coelho</t>
         </is>
       </c>
       <c r="H1368" t="inlineStr"/>
@@ -69193,10 +69205,10 @@
         <v>0</v>
       </c>
       <c r="J1368" t="n">
-        <v>306</v>
+        <v>12</v>
       </c>
       <c r="K1368" t="n">
-        <v>302</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1369">
@@ -69232,18 +69244,18 @@
       </c>
       <c r="G1369" t="inlineStr">
         <is>
-          <t>Isabelli Afonso</t>
+          <t>Bianca Castro</t>
         </is>
       </c>
       <c r="H1369" t="inlineStr"/>
       <c r="I1369" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1369" t="n">
-        <v>217</v>
+        <v>265</v>
       </c>
       <c r="K1369" t="n">
-        <v>232</v>
+        <v>459</v>
       </c>
     </row>
     <row r="1370">
@@ -69279,7 +69291,7 @@
       </c>
       <c r="G1370" t="inlineStr">
         <is>
-          <t>Jurema Damacena - SAC</t>
+          <t>Bruna Costa</t>
         </is>
       </c>
       <c r="H1370" t="inlineStr"/>
@@ -69287,10 +69299,10 @@
         <v>0</v>
       </c>
       <c r="J1370" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="K1370" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
     </row>
     <row r="1371">
@@ -69326,7 +69338,7 @@
       </c>
       <c r="G1371" t="inlineStr">
         <is>
-          <t>Leticia Queiroz</t>
+          <t>Daniela Silva</t>
         </is>
       </c>
       <c r="H1371" t="inlineStr"/>
@@ -69334,10 +69346,10 @@
         <v>0</v>
       </c>
       <c r="J1371" t="n">
-        <v>424</v>
+        <v>306</v>
       </c>
       <c r="K1371" t="n">
-        <v>428</v>
+        <v>302</v>
       </c>
     </row>
     <row r="1372">
@@ -69373,18 +69385,18 @@
       </c>
       <c r="G1372" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Isabelli Afonso</t>
         </is>
       </c>
       <c r="H1372" t="inlineStr"/>
       <c r="I1372" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J1372" t="n">
-        <v>2</v>
+        <v>217</v>
       </c>
       <c r="K1372" t="n">
-        <v>13</v>
+        <v>234</v>
       </c>
     </row>
     <row r="1373">
@@ -69420,7 +69432,7 @@
       </c>
       <c r="G1373" t="inlineStr">
         <is>
-          <t>Victoria Virgens</t>
+          <t>Jurema Damacena - SAC</t>
         </is>
       </c>
       <c r="H1373" t="inlineStr"/>
@@ -69428,10 +69440,10 @@
         <v>0</v>
       </c>
       <c r="J1373" t="n">
-        <v>308</v>
+        <v>0</v>
       </c>
       <c r="K1373" t="n">
-        <v>308</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1374">
@@ -69467,7 +69479,7 @@
       </c>
       <c r="G1374" t="inlineStr">
         <is>
-          <t>Yasmin Peixoto</t>
+          <t>Leticia Queiroz</t>
         </is>
       </c>
       <c r="H1374" t="inlineStr"/>
@@ -69475,10 +69487,10 @@
         <v>0</v>
       </c>
       <c r="J1374" t="n">
-        <v>354</v>
+        <v>424</v>
       </c>
       <c r="K1374" t="n">
-        <v>551</v>
+        <v>428</v>
       </c>
     </row>
     <row r="1375">
@@ -69509,12 +69521,12 @@
       </c>
       <c r="F1375" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="G1375" t="inlineStr">
         <is>
-          <t>Andre Coelho</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="H1375" t="inlineStr"/>
@@ -69522,10 +69534,10 @@
         <v>0</v>
       </c>
       <c r="J1375" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K1375" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1376">
@@ -69556,12 +69568,12 @@
       </c>
       <c r="F1376" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="G1376" t="inlineStr">
         <is>
-          <t>Beatriz Rangel</t>
+          <t>Victoria Virgens</t>
         </is>
       </c>
       <c r="H1376" t="inlineStr"/>
@@ -69569,10 +69581,10 @@
         <v>0</v>
       </c>
       <c r="J1376" t="n">
-        <v>222</v>
+        <v>308</v>
       </c>
       <c r="K1376" t="n">
-        <v>372</v>
+        <v>308</v>
       </c>
     </row>
     <row r="1377">
@@ -69603,12 +69615,12 @@
       </c>
       <c r="F1377" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="G1377" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
+          <t>Yasmin Peixoto</t>
         </is>
       </c>
       <c r="H1377" t="inlineStr"/>
@@ -69616,10 +69628,10 @@
         <v>0</v>
       </c>
       <c r="J1377" t="n">
-        <v>429</v>
+        <v>354</v>
       </c>
       <c r="K1377" t="n">
-        <v>434</v>
+        <v>551</v>
       </c>
     </row>
     <row r="1378">
@@ -69655,7 +69667,7 @@
       </c>
       <c r="G1378" t="inlineStr">
         <is>
-          <t>Cristiane Simões</t>
+          <t>Andre Coelho</t>
         </is>
       </c>
       <c r="H1378" t="inlineStr"/>
@@ -69663,10 +69675,10 @@
         <v>0</v>
       </c>
       <c r="J1378" t="n">
-        <v>271</v>
+        <v>4</v>
       </c>
       <c r="K1378" t="n">
-        <v>306</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1379">
@@ -69702,18 +69714,18 @@
       </c>
       <c r="G1379" t="inlineStr">
         <is>
-          <t>Daniel Oliveira</t>
+          <t>Beatriz Rangel</t>
         </is>
       </c>
       <c r="H1379" t="inlineStr"/>
       <c r="I1379" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J1379" t="n">
-        <v>353</v>
+        <v>222</v>
       </c>
       <c r="K1379" t="n">
-        <v>403</v>
+        <v>372</v>
       </c>
     </row>
     <row r="1380">
@@ -69749,7 +69761,7 @@
       </c>
       <c r="G1380" t="inlineStr">
         <is>
-          <t>Diego Lima</t>
+          <t>Bruno Contieri</t>
         </is>
       </c>
       <c r="H1380" t="inlineStr"/>
@@ -69757,10 +69769,10 @@
         <v>0</v>
       </c>
       <c r="J1380" t="n">
-        <v>172</v>
+        <v>429</v>
       </c>
       <c r="K1380" t="n">
-        <v>164</v>
+        <v>434</v>
       </c>
     </row>
     <row r="1381">
@@ -69796,7 +69808,7 @@
       </c>
       <c r="G1381" t="inlineStr">
         <is>
-          <t>Eduardo Aparicio</t>
+          <t>Cristiane Simões</t>
         </is>
       </c>
       <c r="H1381" t="inlineStr"/>
@@ -69804,10 +69816,10 @@
         <v>0</v>
       </c>
       <c r="J1381" t="n">
-        <v>1</v>
+        <v>271</v>
       </c>
       <c r="K1381" t="n">
-        <v>1</v>
+        <v>306</v>
       </c>
     </row>
     <row r="1382">
@@ -69843,18 +69855,18 @@
       </c>
       <c r="G1382" t="inlineStr">
         <is>
-          <t>Karine Gusmão</t>
+          <t>Daniel Oliveira</t>
         </is>
       </c>
       <c r="H1382" t="inlineStr"/>
       <c r="I1382" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1382" t="n">
-        <v>112</v>
+        <v>353</v>
       </c>
       <c r="K1382" t="n">
-        <v>93</v>
+        <v>403</v>
       </c>
     </row>
     <row r="1383">
@@ -69890,7 +69902,7 @@
       </c>
       <c r="G1383" t="inlineStr">
         <is>
-          <t>Luiz Ferreira</t>
+          <t>Diego Lima</t>
         </is>
       </c>
       <c r="H1383" t="inlineStr"/>
@@ -69898,10 +69910,10 @@
         <v>0</v>
       </c>
       <c r="J1383" t="n">
-        <v>18</v>
+        <v>172</v>
       </c>
       <c r="K1383" t="n">
-        <v>17</v>
+        <v>164</v>
       </c>
     </row>
     <row r="1384">
@@ -69937,7 +69949,7 @@
       </c>
       <c r="G1384" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Eduardo Aparicio</t>
         </is>
       </c>
       <c r="H1384" t="inlineStr"/>
@@ -69945,10 +69957,10 @@
         <v>0</v>
       </c>
       <c r="J1384" t="n">
-        <v>210</v>
+        <v>1</v>
       </c>
       <c r="K1384" t="n">
-        <v>221</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1385">
@@ -69984,18 +69996,18 @@
       </c>
       <c r="G1385" t="inlineStr">
         <is>
-          <t>Rodrigo Rego</t>
+          <t>Karine Gusmão</t>
         </is>
       </c>
       <c r="H1385" t="inlineStr"/>
       <c r="I1385" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1385" t="n">
-        <v>421</v>
+        <v>112</v>
       </c>
       <c r="K1385" t="n">
-        <v>460</v>
+        <v>93</v>
       </c>
     </row>
     <row r="1386">
@@ -70031,7 +70043,7 @@
       </c>
       <c r="G1386" t="inlineStr">
         <is>
-          <t>Rogerio Egidio</t>
+          <t>Luiz Ferreira</t>
         </is>
       </c>
       <c r="H1386" t="inlineStr"/>
@@ -70039,10 +70051,10 @@
         <v>0</v>
       </c>
       <c r="J1386" t="n">
-        <v>335</v>
+        <v>18</v>
       </c>
       <c r="K1386" t="n">
-        <v>384</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1387">
@@ -70078,7 +70090,7 @@
       </c>
       <c r="G1387" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="H1387" t="inlineStr"/>
@@ -70086,10 +70098,10 @@
         <v>0</v>
       </c>
       <c r="J1387" t="n">
-        <v>33</v>
+        <v>210</v>
       </c>
       <c r="K1387" t="n">
-        <v>50</v>
+        <v>221</v>
       </c>
     </row>
     <row r="1388">
@@ -70125,18 +70137,18 @@
       </c>
       <c r="G1388" t="inlineStr">
         <is>
-          <t>Simone Marques</t>
+          <t>Rodrigo Rego</t>
         </is>
       </c>
       <c r="H1388" t="inlineStr"/>
       <c r="I1388" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1388" t="n">
-        <v>197</v>
+        <v>420</v>
       </c>
       <c r="K1388" t="n">
-        <v>227</v>
+        <v>460</v>
       </c>
     </row>
     <row r="1389">
@@ -70172,7 +70184,7 @@
       </c>
       <c r="G1389" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Rogerio Egidio</t>
         </is>
       </c>
       <c r="H1389" t="inlineStr"/>
@@ -70180,10 +70192,10 @@
         <v>0</v>
       </c>
       <c r="J1389" t="n">
-        <v>216</v>
+        <v>335</v>
       </c>
       <c r="K1389" t="n">
-        <v>268</v>
+        <v>384</v>
       </c>
     </row>
     <row r="1390">
@@ -70214,12 +70226,12 @@
       </c>
       <c r="F1390" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="G1390" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="H1390" t="inlineStr"/>
@@ -70227,10 +70239,10 @@
         <v>0</v>
       </c>
       <c r="J1390" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="K1390" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1391">
@@ -70261,23 +70273,23 @@
       </c>
       <c r="F1391" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="G1391" t="inlineStr">
         <is>
-          <t>Jurema Damacena - SAC</t>
+          <t>Simone Marques</t>
         </is>
       </c>
       <c r="H1391" t="inlineStr"/>
       <c r="I1391" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1391" t="n">
-        <v>29</v>
+        <v>197</v>
       </c>
       <c r="K1391" t="n">
-        <v>45</v>
+        <v>227</v>
       </c>
     </row>
     <row r="1392">
@@ -70308,12 +70320,12 @@
       </c>
       <c r="F1392" t="inlineStr">
         <is>
-          <t>MG CONTABIFÁCIL - CTB</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="G1392" t="inlineStr">
         <is>
-          <t>Guilherme Delecrodio</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="H1392" t="inlineStr"/>
@@ -70321,10 +70333,10 @@
         <v>0</v>
       </c>
       <c r="J1392" t="n">
-        <v>1</v>
+        <v>214</v>
       </c>
       <c r="K1392" t="n">
-        <v>1</v>
+        <v>267</v>
       </c>
     </row>
     <row r="1393">
@@ -70355,12 +70367,12 @@
       </c>
       <c r="F1393" t="inlineStr">
         <is>
-          <t>S.A.C</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="G1393" t="inlineStr">
         <is>
-          <t>Ana Celia - SAC</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="H1393" t="inlineStr"/>
@@ -70368,7 +70380,7 @@
         <v>0</v>
       </c>
       <c r="J1393" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1393" t="n">
         <v>1</v>
@@ -70402,27 +70414,23 @@
       </c>
       <c r="F1394" t="inlineStr">
         <is>
-          <t>SANTOS - DP</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="G1394" t="inlineStr">
         <is>
-          <t>Katia Valeria</t>
-        </is>
-      </c>
-      <c r="H1394" t="inlineStr">
-        <is>
-          <t>Katia Valeria</t>
-        </is>
-      </c>
+          <t>Jurema Damacena - SAC</t>
+        </is>
+      </c>
+      <c r="H1394" t="inlineStr"/>
       <c r="I1394" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J1394" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="K1394" t="n">
-        <v>3</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1395">
@@ -70448,17 +70456,17 @@
       </c>
       <c r="E1395" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F1395" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>MG CONTABIFÁCIL - CTB</t>
         </is>
       </c>
       <c r="G1395" t="inlineStr">
         <is>
-          <t>Jurema Damacena - SAC</t>
+          <t>Guilherme Delecrodio</t>
         </is>
       </c>
       <c r="H1395" t="inlineStr"/>
@@ -70466,10 +70474,10 @@
         <v>0</v>
       </c>
       <c r="J1395" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K1395" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1396">
@@ -70495,17 +70503,17 @@
       </c>
       <c r="E1396" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F1396" t="inlineStr">
         <is>
-          <t>SANTOS - ADM</t>
+          <t>S.A.C</t>
         </is>
       </c>
       <c r="G1396" t="inlineStr">
         <is>
-          <t>Kauany Pereira</t>
+          <t>Ana Celia - SAC</t>
         </is>
       </c>
       <c r="H1396" t="inlineStr"/>
@@ -70513,10 +70521,10 @@
         <v>0</v>
       </c>
       <c r="J1396" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="K1396" t="n">
-        <v>136</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1397">
@@ -70542,32 +70550,32 @@
       </c>
       <c r="E1397" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F1397" t="inlineStr">
         <is>
-          <t>SANTOS - CTB</t>
+          <t>SANTOS - DP</t>
         </is>
       </c>
       <c r="G1397" t="inlineStr">
         <is>
-          <t>Ivia Oliveira</t>
+          <t>Katia Valeria</t>
         </is>
       </c>
       <c r="H1397" t="inlineStr">
         <is>
-          <t>Roberto Silva</t>
+          <t>Katia Valeria</t>
         </is>
       </c>
       <c r="I1397" t="n">
         <v>0</v>
       </c>
       <c r="J1397" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="K1397" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1398">
@@ -70598,27 +70606,23 @@
       </c>
       <c r="F1398" t="inlineStr">
         <is>
-          <t>SANTOS - CTB</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="G1398" t="inlineStr">
         <is>
-          <t>Nata Trindade</t>
-        </is>
-      </c>
-      <c r="H1398" t="inlineStr">
-        <is>
-          <t>Roberto Silva</t>
-        </is>
-      </c>
+          <t>Jurema Damacena - SAC</t>
+        </is>
+      </c>
+      <c r="H1398" t="inlineStr"/>
       <c r="I1398" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1398" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="K1398" t="n">
-        <v>40</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1399">
@@ -70649,27 +70653,23 @@
       </c>
       <c r="F1399" t="inlineStr">
         <is>
-          <t>SANTOS - CTB</t>
+          <t>SANTOS - ADM</t>
         </is>
       </c>
       <c r="G1399" t="inlineStr">
         <is>
-          <t>Roberto Silva</t>
-        </is>
-      </c>
-      <c r="H1399" t="inlineStr">
-        <is>
-          <t>Roberto Silva</t>
-        </is>
-      </c>
+          <t>Kauany Pereira</t>
+        </is>
+      </c>
+      <c r="H1399" t="inlineStr"/>
       <c r="I1399" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1399" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="K1399" t="n">
-        <v>41</v>
+        <v>138</v>
       </c>
     </row>
     <row r="1400">
@@ -70705,7 +70705,7 @@
       </c>
       <c r="G1400" t="inlineStr">
         <is>
-          <t>Thaina Rodrigues</t>
+          <t>Ivia Oliveira</t>
         </is>
       </c>
       <c r="H1400" t="inlineStr">
@@ -70717,10 +70717,10 @@
         <v>0</v>
       </c>
       <c r="J1400" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="K1400" t="n">
-        <v>48</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1401">
@@ -70751,27 +70751,27 @@
       </c>
       <c r="F1401" t="inlineStr">
         <is>
-          <t>SANTOS - DP</t>
+          <t>SANTOS - CTB</t>
         </is>
       </c>
       <c r="G1401" t="inlineStr">
         <is>
-          <t>Bruna Silva</t>
+          <t>Nata Trindade</t>
         </is>
       </c>
       <c r="H1401" t="inlineStr">
         <is>
-          <t>Katia Valeria</t>
+          <t>Roberto Silva</t>
         </is>
       </c>
       <c r="I1401" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1401" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="K1401" t="n">
-        <v>14</v>
+        <v>41</v>
       </c>
     </row>
     <row r="1402">
@@ -70802,27 +70802,27 @@
       </c>
       <c r="F1402" t="inlineStr">
         <is>
-          <t>SANTOS - DP</t>
+          <t>SANTOS - CTB</t>
         </is>
       </c>
       <c r="G1402" t="inlineStr">
         <is>
-          <t>Carliane Silva</t>
+          <t>Roberto Silva</t>
         </is>
       </c>
       <c r="H1402" t="inlineStr">
         <is>
-          <t>Katia Valeria</t>
+          <t>Roberto Silva</t>
         </is>
       </c>
       <c r="I1402" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1402" t="n">
-        <v>131</v>
+        <v>7</v>
       </c>
       <c r="K1402" t="n">
-        <v>284</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1403">
@@ -70853,27 +70853,27 @@
       </c>
       <c r="F1403" t="inlineStr">
         <is>
-          <t>SANTOS - DP</t>
+          <t>SANTOS - CTB</t>
         </is>
       </c>
       <c r="G1403" t="inlineStr">
         <is>
-          <t>Cintia Andrade</t>
+          <t>Thaina Rodrigues</t>
         </is>
       </c>
       <c r="H1403" t="inlineStr">
         <is>
-          <t>Katia Valeria</t>
+          <t>Roberto Silva</t>
         </is>
       </c>
       <c r="I1403" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1403" t="n">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="K1403" t="n">
-        <v>203</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1404">
@@ -70909,22 +70909,22 @@
       </c>
       <c r="G1404" t="inlineStr">
         <is>
+          <t>Bruna Silva</t>
+        </is>
+      </c>
+      <c r="H1404" t="inlineStr">
+        <is>
           <t>Katia Valeria</t>
         </is>
       </c>
-      <c r="H1404" t="inlineStr">
-        <is>
-          <t>Katia Valeria</t>
-        </is>
-      </c>
       <c r="I1404" t="n">
         <v>0</v>
       </c>
       <c r="J1404" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="K1404" t="n">
-        <v>336</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1405">
@@ -70955,27 +70955,27 @@
       </c>
       <c r="F1405" t="inlineStr">
         <is>
-          <t>SANTOS - EF</t>
+          <t>SANTOS - DP</t>
         </is>
       </c>
       <c r="G1405" t="inlineStr">
         <is>
-          <t>Jasmina Melo</t>
+          <t>Carliane Silva</t>
         </is>
       </c>
       <c r="H1405" t="inlineStr">
         <is>
-          <t>Lidia Tavares</t>
+          <t>Katia Valeria</t>
         </is>
       </c>
       <c r="I1405" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J1405" t="n">
-        <v>39</v>
+        <v>131</v>
       </c>
       <c r="K1405" t="n">
-        <v>63</v>
+        <v>284</v>
       </c>
     </row>
     <row r="1406">
@@ -71006,27 +71006,27 @@
       </c>
       <c r="F1406" t="inlineStr">
         <is>
-          <t>SANTOS - EF</t>
+          <t>SANTOS - DP</t>
         </is>
       </c>
       <c r="G1406" t="inlineStr">
         <is>
-          <t>Karen Saadi</t>
+          <t>Cintia Andrade</t>
         </is>
       </c>
       <c r="H1406" t="inlineStr">
         <is>
-          <t>Lidia Tavares</t>
+          <t>Katia Valeria</t>
         </is>
       </c>
       <c r="I1406" t="n">
         <v>0</v>
       </c>
       <c r="J1406" t="n">
-        <v>27</v>
+        <v>103</v>
       </c>
       <c r="K1406" t="n">
-        <v>61</v>
+        <v>207</v>
       </c>
     </row>
     <row r="1407">
@@ -71057,27 +71057,27 @@
       </c>
       <c r="F1407" t="inlineStr">
         <is>
-          <t>SANTOS - EF</t>
+          <t>SANTOS - DP</t>
         </is>
       </c>
       <c r="G1407" t="inlineStr">
         <is>
-          <t>Luckas Andrade</t>
+          <t>Katia Valeria</t>
         </is>
       </c>
       <c r="H1407" t="inlineStr">
         <is>
-          <t>Lidia Tavares</t>
+          <t>Katia Valeria</t>
         </is>
       </c>
       <c r="I1407" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1407" t="n">
-        <v>36</v>
+        <v>157</v>
       </c>
       <c r="K1407" t="n">
-        <v>74</v>
+        <v>337</v>
       </c>
     </row>
     <row r="1408">
@@ -71113,7 +71113,7 @@
       </c>
       <c r="G1408" t="inlineStr">
         <is>
-          <t>Mirian Rodrigues</t>
+          <t>Jasmina Melo</t>
         </is>
       </c>
       <c r="H1408" t="inlineStr">
@@ -71122,13 +71122,13 @@
         </is>
       </c>
       <c r="I1408" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1408" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="K1408" t="n">
-        <v>84</v>
+        <v>65</v>
       </c>
     </row>
     <row r="1409">
@@ -71159,22 +71159,175 @@
       </c>
       <c r="F1409" t="inlineStr">
         <is>
+          <t>SANTOS - EF</t>
+        </is>
+      </c>
+      <c r="G1409" t="inlineStr">
+        <is>
+          <t>Karen Saadi</t>
+        </is>
+      </c>
+      <c r="H1409" t="inlineStr">
+        <is>
+          <t>Lidia Tavares</t>
+        </is>
+      </c>
+      <c r="I1409" t="n">
+        <v>18</v>
+      </c>
+      <c r="J1409" t="n">
+        <v>43</v>
+      </c>
+      <c r="K1409" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="1410">
+      <c r="A1410" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B1410" t="inlineStr">
+        <is>
+          <t>Sexta</t>
+        </is>
+      </c>
+      <c r="C1410" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D1410" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1410" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="F1410" t="inlineStr">
+        <is>
+          <t>SANTOS - EF</t>
+        </is>
+      </c>
+      <c r="G1410" t="inlineStr">
+        <is>
+          <t>Luckas Andrade</t>
+        </is>
+      </c>
+      <c r="H1410" t="inlineStr">
+        <is>
+          <t>Lidia Tavares</t>
+        </is>
+      </c>
+      <c r="I1410" t="n">
+        <v>30</v>
+      </c>
+      <c r="J1410" t="n">
+        <v>66</v>
+      </c>
+      <c r="K1410" t="n">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1411">
+      <c r="A1411" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B1411" t="inlineStr">
+        <is>
+          <t>Sexta</t>
+        </is>
+      </c>
+      <c r="C1411" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D1411" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1411" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="F1411" t="inlineStr">
+        <is>
+          <t>SANTOS - EF</t>
+        </is>
+      </c>
+      <c r="G1411" t="inlineStr">
+        <is>
+          <t>Mirian Rodrigues</t>
+        </is>
+      </c>
+      <c r="H1411" t="inlineStr">
+        <is>
+          <t>Lidia Tavares</t>
+        </is>
+      </c>
+      <c r="I1411" t="n">
+        <v>11</v>
+      </c>
+      <c r="J1411" t="n">
+        <v>38</v>
+      </c>
+      <c r="K1411" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="1412">
+      <c r="A1412" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B1412" t="inlineStr">
+        <is>
+          <t>Sexta</t>
+        </is>
+      </c>
+      <c r="C1412" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D1412" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1412" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="F1412" t="inlineStr">
+        <is>
           <t>SANTOS - GC</t>
         </is>
       </c>
-      <c r="G1409" t="inlineStr">
+      <c r="G1412" t="inlineStr">
         <is>
           <t>Rafaella Massuia</t>
         </is>
       </c>
-      <c r="H1409" t="inlineStr"/>
-      <c r="I1409" t="n">
-        <v>0</v>
-      </c>
-      <c r="J1409" t="n">
-        <v>0</v>
-      </c>
-      <c r="K1409" t="n">
+      <c r="H1412" t="inlineStr"/>
+      <c r="I1412" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1412" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1412" t="n">
         <v>109</v>
       </c>
     </row>

--- a/data/historico/historico_baixas.xlsx
+++ b/data/historico/historico_baixas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1412"/>
+  <dimension ref="A1:K1415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -56852,24 +56852,24 @@
       </c>
       <c r="F1124" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="G1124" t="inlineStr">
         <is>
-          <t>Eveny Silva</t>
+          <t>Thais Souza</t>
         </is>
       </c>
       <c r="H1124" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Erika Santana|Isabella Nascimento</t>
         </is>
       </c>
       <c r="I1124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1124" t="n">
         <v>1</v>
@@ -56908,12 +56908,12 @@
       </c>
       <c r="G1125" t="inlineStr">
         <is>
-          <t>Jackson Silva</t>
+          <t>Eveny Silva</t>
         </is>
       </c>
       <c r="H1125" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Karina Santos</t>
         </is>
       </c>
       <c r="I1125" t="n">
@@ -56923,7 +56923,7 @@
         <v>0</v>
       </c>
       <c r="K1125" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1126">
@@ -56959,12 +56959,12 @@
       </c>
       <c r="G1126" t="inlineStr">
         <is>
-          <t>Paulo Silva</t>
+          <t>Jackson Silva</t>
         </is>
       </c>
       <c r="H1126" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I1126" t="n">
@@ -56974,7 +56974,7 @@
         <v>0</v>
       </c>
       <c r="K1126" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1127">
@@ -57005,27 +57005,27 @@
       </c>
       <c r="F1127" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="G1127" t="inlineStr">
         <is>
-          <t>Elaine Assis</t>
+          <t>Paulo Silva</t>
         </is>
       </c>
       <c r="H1127" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="I1127" t="n">
         <v>0</v>
       </c>
       <c r="J1127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1127" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1128">
@@ -57061,12 +57061,12 @@
       </c>
       <c r="G1128" t="inlineStr">
         <is>
-          <t>Evellin Bispo</t>
+          <t>Elaine Assis</t>
         </is>
       </c>
       <c r="H1128" t="inlineStr">
         <is>
-          <t>Leandro Matos</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I1128" t="n">
@@ -57076,7 +57076,7 @@
         <v>1</v>
       </c>
       <c r="K1128" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1129">
@@ -57112,22 +57112,22 @@
       </c>
       <c r="G1129" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Evellin Bispo</t>
         </is>
       </c>
       <c r="H1129" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Leandro Matos</t>
         </is>
       </c>
       <c r="I1129" t="n">
         <v>0</v>
       </c>
       <c r="J1129" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K1129" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1130">
@@ -57163,22 +57163,22 @@
       </c>
       <c r="G1130" t="inlineStr">
         <is>
-          <t>Jhenifer Tenorio</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="H1130" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I1130" t="n">
         <v>0</v>
       </c>
       <c r="J1130" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K1130" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1131">
@@ -57214,22 +57214,22 @@
       </c>
       <c r="G1131" t="inlineStr">
         <is>
-          <t>Kaique Souza</t>
+          <t>Jhenifer Tenorio</t>
         </is>
       </c>
       <c r="H1131" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I1131" t="n">
         <v>0</v>
       </c>
       <c r="J1131" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K1131" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1132">
@@ -57265,22 +57265,22 @@
       </c>
       <c r="G1132" t="inlineStr">
         <is>
-          <t>Mauricio Lermen</t>
+          <t>Kaique Souza</t>
         </is>
       </c>
       <c r="H1132" t="inlineStr">
         <is>
-          <t>Mauricio Lermen</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I1132" t="n">
         <v>0</v>
       </c>
       <c r="J1132" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K1132" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1133">
@@ -57316,18 +57316,22 @@
       </c>
       <c r="G1133" t="inlineStr">
         <is>
-          <t>Mikael Teixeira</t>
-        </is>
-      </c>
-      <c r="H1133" t="inlineStr"/>
+          <t>Mauricio Lermen</t>
+        </is>
+      </c>
+      <c r="H1133" t="inlineStr">
+        <is>
+          <t>Mauricio Lermen</t>
+        </is>
+      </c>
       <c r="I1133" t="n">
         <v>0</v>
       </c>
       <c r="J1133" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K1133" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1134">
@@ -57363,22 +57367,18 @@
       </c>
       <c r="G1134" t="inlineStr">
         <is>
-          <t>Tania Luz</t>
-        </is>
-      </c>
-      <c r="H1134" t="inlineStr">
-        <is>
-          <t>Sara Cavalheiro</t>
-        </is>
-      </c>
+          <t>Mikael Teixeira</t>
+        </is>
+      </c>
+      <c r="H1134" t="inlineStr"/>
       <c r="I1134" t="n">
         <v>0</v>
       </c>
       <c r="J1134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1134" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1135">
@@ -57414,22 +57414,22 @@
       </c>
       <c r="G1135" t="inlineStr">
         <is>
-          <t>Vitor Guedes</t>
+          <t>Santos Karina</t>
         </is>
       </c>
       <c r="H1135" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Leandro Matos</t>
         </is>
       </c>
       <c r="I1135" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1135" t="n">
         <v>0</v>
       </c>
       <c r="K1135" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1136">
@@ -57460,27 +57460,27 @@
       </c>
       <c r="F1136" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="G1136" t="inlineStr">
         <is>
-          <t>Cristiana Grizostomo</t>
+          <t>Tania Luz</t>
         </is>
       </c>
       <c r="H1136" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I1136" t="n">
         <v>0</v>
       </c>
       <c r="J1136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1136" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1137">
@@ -57511,15 +57511,19 @@
       </c>
       <c r="F1137" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="G1137" t="inlineStr">
         <is>
-          <t>Denis Reis</t>
-        </is>
-      </c>
-      <c r="H1137" t="inlineStr"/>
+          <t>Vitor Guedes</t>
+        </is>
+      </c>
+      <c r="H1137" t="inlineStr">
+        <is>
+          <t>David Bragança</t>
+        </is>
+      </c>
       <c r="I1137" t="n">
         <v>0</v>
       </c>
@@ -57527,7 +57531,7 @@
         <v>0</v>
       </c>
       <c r="K1137" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1138">
@@ -57563,7 +57567,7 @@
       </c>
       <c r="G1138" t="inlineStr">
         <is>
-          <t>Priscila Volpe</t>
+          <t>Cristiana Grizostomo</t>
         </is>
       </c>
       <c r="H1138" t="inlineStr">
@@ -57578,7 +57582,7 @@
         <v>1</v>
       </c>
       <c r="K1138" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1139">
@@ -57614,22 +57618,18 @@
       </c>
       <c r="G1139" t="inlineStr">
         <is>
-          <t>Rosilene Santos</t>
-        </is>
-      </c>
-      <c r="H1139" t="inlineStr">
-        <is>
-          <t>Nayara Oliveira</t>
-        </is>
-      </c>
+          <t>Denis Reis</t>
+        </is>
+      </c>
+      <c r="H1139" t="inlineStr"/>
       <c r="I1139" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1139" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K1139" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1140">
@@ -57660,27 +57660,27 @@
       </c>
       <c r="F1140" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="G1140" t="inlineStr">
         <is>
-          <t>Cristina Leite</t>
+          <t>Priscila Volpe</t>
         </is>
       </c>
       <c r="H1140" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
       <c r="I1140" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J1140" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="K1140" t="n">
-        <v>70</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1141">
@@ -57711,23 +57711,27 @@
       </c>
       <c r="F1141" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="G1141" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
-        </is>
-      </c>
-      <c r="H1141" t="inlineStr"/>
+          <t>Rosilene Santos</t>
+        </is>
+      </c>
+      <c r="H1141" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
       <c r="I1141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1141" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1141" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1142">
@@ -57758,23 +57762,27 @@
       </c>
       <c r="F1142" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="G1142" t="inlineStr">
         <is>
-          <t>Victoria Virgens</t>
-        </is>
-      </c>
-      <c r="H1142" t="inlineStr"/>
+          <t>Cristina Leite</t>
+        </is>
+      </c>
+      <c r="H1142" t="inlineStr">
+        <is>
+          <t>Ricardo Fischer</t>
+        </is>
+      </c>
       <c r="I1142" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J1142" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="K1142" t="n">
-        <v>29</v>
+        <v>70</v>
       </c>
     </row>
     <row r="1143">
@@ -57805,12 +57813,12 @@
       </c>
       <c r="F1143" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="G1143" t="inlineStr">
         <is>
-          <t>Cristiane Simões</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="H1143" t="inlineStr"/>
@@ -57821,7 +57829,7 @@
         <v>2</v>
       </c>
       <c r="K1143" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1144">
@@ -57852,12 +57860,12 @@
       </c>
       <c r="F1144" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="G1144" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Victoria Virgens</t>
         </is>
       </c>
       <c r="H1144" t="inlineStr"/>
@@ -57865,10 +57873,10 @@
         <v>0</v>
       </c>
       <c r="J1144" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="K1144" t="n">
-        <v>41</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1145">
@@ -57904,7 +57912,7 @@
       </c>
       <c r="G1145" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Cristiane Simões</t>
         </is>
       </c>
       <c r="H1145" t="inlineStr"/>
@@ -57912,10 +57920,10 @@
         <v>0</v>
       </c>
       <c r="J1145" t="n">
+        <v>2</v>
+      </c>
+      <c r="K1145" t="n">
         <v>3</v>
-      </c>
-      <c r="K1145" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="1146">
@@ -57951,18 +57959,18 @@
       </c>
       <c r="G1146" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="H1146" t="inlineStr"/>
       <c r="I1146" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1146" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="K1146" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
     </row>
     <row r="1147">
@@ -57988,17 +57996,17 @@
       </c>
       <c r="E1147" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>GOIAS</t>
         </is>
       </c>
       <c r="F1147" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="G1147" t="inlineStr">
         <is>
-          <t>Caroline Alves</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="H1147" t="inlineStr"/>
@@ -58006,10 +58014,10 @@
         <v>0</v>
       </c>
       <c r="J1147" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K1147" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1148">
@@ -58035,32 +58043,28 @@
       </c>
       <c r="E1148" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>GOIAS</t>
         </is>
       </c>
       <c r="F1148" t="inlineStr">
         <is>
-          <t>RJ - CTB</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="G1148" t="inlineStr">
         <is>
-          <t>Crislaine Maia</t>
-        </is>
-      </c>
-      <c r="H1148" t="inlineStr">
-        <is>
-          <t>Walace Gonçalves|Maicon Costa</t>
-        </is>
-      </c>
+          <t>Vander Silva</t>
+        </is>
+      </c>
+      <c r="H1148" t="inlineStr"/>
       <c r="I1148" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J1148" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="K1148" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1149">
@@ -58091,27 +58095,23 @@
       </c>
       <c r="F1149" t="inlineStr">
         <is>
-          <t>RJ - CTB</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="G1149" t="inlineStr">
         <is>
-          <t>Gabriela Lopes</t>
-        </is>
-      </c>
-      <c r="H1149" t="inlineStr">
-        <is>
-          <t>Walace Gonçalves|Maicon Costa</t>
-        </is>
-      </c>
+          <t>Caroline Alves</t>
+        </is>
+      </c>
+      <c r="H1149" t="inlineStr"/>
       <c r="I1149" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J1149" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="K1149" t="n">
-        <v>66</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1150">
@@ -58147,7 +58147,7 @@
       </c>
       <c r="G1150" t="inlineStr">
         <is>
-          <t>Jeniffer Cristina</t>
+          <t>Crislaine Maia</t>
         </is>
       </c>
       <c r="H1150" t="inlineStr">
@@ -58156,13 +58156,13 @@
         </is>
       </c>
       <c r="I1150" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J1150" t="n">
-        <v>67</v>
+        <v>19</v>
       </c>
       <c r="K1150" t="n">
-        <v>76</v>
+        <v>31</v>
       </c>
     </row>
     <row r="1151">
@@ -58198,7 +58198,7 @@
       </c>
       <c r="G1151" t="inlineStr">
         <is>
-          <t>Jessica Roque</t>
+          <t>Gabriela Lopes</t>
         </is>
       </c>
       <c r="H1151" t="inlineStr">
@@ -58207,13 +58207,13 @@
         </is>
       </c>
       <c r="I1151" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J1151" t="n">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="K1151" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
     </row>
     <row r="1152">
@@ -58249,7 +58249,7 @@
       </c>
       <c r="G1152" t="inlineStr">
         <is>
-          <t>Kellem Freitas</t>
+          <t>Jeniffer Cristina</t>
         </is>
       </c>
       <c r="H1152" t="inlineStr">
@@ -58258,13 +58258,13 @@
         </is>
       </c>
       <c r="I1152" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J1152" t="n">
-        <v>4</v>
+        <v>67</v>
       </c>
       <c r="K1152" t="n">
-        <v>23</v>
+        <v>76</v>
       </c>
     </row>
     <row r="1153">
@@ -58300,7 +58300,7 @@
       </c>
       <c r="G1153" t="inlineStr">
         <is>
-          <t>Leidiane Paulino</t>
+          <t>Jessica Roque</t>
         </is>
       </c>
       <c r="H1153" t="inlineStr">
@@ -58312,10 +58312,10 @@
         <v>0</v>
       </c>
       <c r="J1153" t="n">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="K1153" t="n">
-        <v>21</v>
+        <v>60</v>
       </c>
     </row>
     <row r="1154">
@@ -58351,7 +58351,7 @@
       </c>
       <c r="G1154" t="inlineStr">
         <is>
-          <t>Leticia Barbosa</t>
+          <t>Kellem Freitas</t>
         </is>
       </c>
       <c r="H1154" t="inlineStr">
@@ -58360,13 +58360,13 @@
         </is>
       </c>
       <c r="I1154" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1154" t="n">
-        <v>49</v>
+        <v>4</v>
       </c>
       <c r="K1154" t="n">
-        <v>83</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1155">
@@ -58402,7 +58402,7 @@
       </c>
       <c r="G1155" t="inlineStr">
         <is>
-          <t>Luis Junior</t>
+          <t>Leidiane Paulino</t>
         </is>
       </c>
       <c r="H1155" t="inlineStr">
@@ -58414,10 +58414,10 @@
         <v>0</v>
       </c>
       <c r="J1155" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K1155" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1156">
@@ -58453,7 +58453,7 @@
       </c>
       <c r="G1156" t="inlineStr">
         <is>
-          <t>Nicoly Rodrigues</t>
+          <t>Leticia Barbosa</t>
         </is>
       </c>
       <c r="H1156" t="inlineStr">
@@ -58462,13 +58462,13 @@
         </is>
       </c>
       <c r="I1156" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J1156" t="n">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="K1156" t="n">
-        <v>28</v>
+        <v>83</v>
       </c>
     </row>
     <row r="1157">
@@ -58504,7 +58504,7 @@
       </c>
       <c r="G1157" t="inlineStr">
         <is>
-          <t>Rafaella Silva</t>
+          <t>Luis Junior</t>
         </is>
       </c>
       <c r="H1157" t="inlineStr">
@@ -58555,7 +58555,7 @@
       </c>
       <c r="G1158" t="inlineStr">
         <is>
-          <t>Rangel Rocha</t>
+          <t>Nicoly Rodrigues</t>
         </is>
       </c>
       <c r="H1158" t="inlineStr">
@@ -58564,13 +58564,13 @@
         </is>
       </c>
       <c r="I1158" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="J1158" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="K1158" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1159">
@@ -58606,7 +58606,7 @@
       </c>
       <c r="G1159" t="inlineStr">
         <is>
-          <t>Simone Soares</t>
+          <t>Rafaella Silva</t>
         </is>
       </c>
       <c r="H1159" t="inlineStr">
@@ -58615,13 +58615,13 @@
         </is>
       </c>
       <c r="I1159" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J1159" t="n">
+        <v>8</v>
+      </c>
+      <c r="K1159" t="n">
         <v>13</v>
-      </c>
-      <c r="K1159" t="n">
-        <v>18</v>
       </c>
     </row>
     <row r="1160">
@@ -58657,7 +58657,7 @@
       </c>
       <c r="G1160" t="inlineStr">
         <is>
-          <t>Suzana Silva</t>
+          <t>Rangel Rocha</t>
         </is>
       </c>
       <c r="H1160" t="inlineStr">
@@ -58666,13 +58666,13 @@
         </is>
       </c>
       <c r="I1160" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J1160" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K1160" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1161">
@@ -58708,7 +58708,7 @@
       </c>
       <c r="G1161" t="inlineStr">
         <is>
-          <t>Veronica Barbosa</t>
+          <t>Simone Soares</t>
         </is>
       </c>
       <c r="H1161" t="inlineStr">
@@ -58717,13 +58717,13 @@
         </is>
       </c>
       <c r="I1161" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1161" t="n">
+        <v>13</v>
+      </c>
+      <c r="K1161" t="n">
         <v>18</v>
-      </c>
-      <c r="K1161" t="n">
-        <v>27</v>
       </c>
     </row>
     <row r="1162">
@@ -58759,7 +58759,7 @@
       </c>
       <c r="G1162" t="inlineStr">
         <is>
-          <t>Vitor Monteiro</t>
+          <t>Suzana Silva</t>
         </is>
       </c>
       <c r="H1162" t="inlineStr">
@@ -58768,13 +58768,13 @@
         </is>
       </c>
       <c r="I1162" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="J1162" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="K1162" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="1163">
@@ -58810,7 +58810,7 @@
       </c>
       <c r="G1163" t="inlineStr">
         <is>
-          <t>Vitoria Silva</t>
+          <t>Veronica Barbosa</t>
         </is>
       </c>
       <c r="H1163" t="inlineStr">
@@ -58819,13 +58819,13 @@
         </is>
       </c>
       <c r="I1163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J1163" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="K1163" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1164">
@@ -58861,7 +58861,7 @@
       </c>
       <c r="G1164" t="inlineStr">
         <is>
-          <t>Walace Gonçalves</t>
+          <t>Vitor Monteiro</t>
         </is>
       </c>
       <c r="H1164" t="inlineStr">
@@ -58870,13 +58870,13 @@
         </is>
       </c>
       <c r="I1164" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J1164" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K1164" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1165">
@@ -58907,19 +58907,27 @@
       </c>
       <c r="F1165" t="inlineStr">
         <is>
-          <t>RJ - DP</t>
-        </is>
-      </c>
-      <c r="G1165" t="inlineStr"/>
-      <c r="H1165" t="inlineStr"/>
+          <t>RJ - CTB</t>
+        </is>
+      </c>
+      <c r="G1165" t="inlineStr">
+        <is>
+          <t>Vitoria Silva</t>
+        </is>
+      </c>
+      <c r="H1165" t="inlineStr">
+        <is>
+          <t>Walace Gonçalves|Maicon Costa</t>
+        </is>
+      </c>
       <c r="I1165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1165" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K1165" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="1166">
@@ -58950,27 +58958,27 @@
       </c>
       <c r="F1166" t="inlineStr">
         <is>
-          <t>RJ - DP</t>
+          <t>RJ - CTB</t>
         </is>
       </c>
       <c r="G1166" t="inlineStr">
         <is>
-          <t>Barbara Mello</t>
+          <t>Walace Gonçalves</t>
         </is>
       </c>
       <c r="H1166" t="inlineStr">
         <is>
-          <t>Karina Oliveira|Liliane Costa</t>
+          <t>Walace Gonçalves|Maicon Costa</t>
         </is>
       </c>
       <c r="I1166" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1166" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="K1166" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1167">
@@ -59004,24 +59012,16 @@
           <t>RJ - DP</t>
         </is>
       </c>
-      <c r="G1167" t="inlineStr">
-        <is>
-          <t>Debora Nunes</t>
-        </is>
-      </c>
-      <c r="H1167" t="inlineStr">
-        <is>
-          <t>Karina Oliveira|Liliane Costa</t>
-        </is>
-      </c>
+      <c r="G1167" t="inlineStr"/>
+      <c r="H1167" t="inlineStr"/>
       <c r="I1167" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1167" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1167" t="n">
         <v>7</v>
-      </c>
-      <c r="J1167" t="n">
-        <v>25</v>
-      </c>
-      <c r="K1167" t="n">
-        <v>99</v>
       </c>
     </row>
     <row r="1168">
@@ -59057,7 +59057,7 @@
       </c>
       <c r="G1168" t="inlineStr">
         <is>
-          <t>Graziele Almeida</t>
+          <t>Barbara Mello</t>
         </is>
       </c>
       <c r="H1168" t="inlineStr">
@@ -59069,10 +59069,10 @@
         <v>0</v>
       </c>
       <c r="J1168" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="K1168" t="n">
-        <v>88</v>
+        <v>105</v>
       </c>
     </row>
     <row r="1169">
@@ -59108,7 +59108,7 @@
       </c>
       <c r="G1169" t="inlineStr">
         <is>
-          <t>Janiele Ferreira</t>
+          <t>Debora Nunes</t>
         </is>
       </c>
       <c r="H1169" t="inlineStr">
@@ -59117,13 +59117,13 @@
         </is>
       </c>
       <c r="I1169" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J1169" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="K1169" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1170">
@@ -59159,7 +59159,7 @@
       </c>
       <c r="G1170" t="inlineStr">
         <is>
-          <t>Jefferson Barros</t>
+          <t>Graziele Almeida</t>
         </is>
       </c>
       <c r="H1170" t="inlineStr">
@@ -59171,10 +59171,10 @@
         <v>0</v>
       </c>
       <c r="J1170" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="K1170" t="n">
-        <v>99</v>
+        <v>88</v>
       </c>
     </row>
     <row r="1171">
@@ -59210,7 +59210,7 @@
       </c>
       <c r="G1171" t="inlineStr">
         <is>
-          <t>Karina Oliveira</t>
+          <t>Janiele Ferreira</t>
         </is>
       </c>
       <c r="H1171" t="inlineStr">
@@ -59219,13 +59219,13 @@
         </is>
       </c>
       <c r="I1171" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J1171" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K1171" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1172">
@@ -59261,7 +59261,7 @@
       </c>
       <c r="G1172" t="inlineStr">
         <is>
-          <t>Leonardo Assunção</t>
+          <t>Jefferson Barros</t>
         </is>
       </c>
       <c r="H1172" t="inlineStr">
@@ -59270,13 +59270,13 @@
         </is>
       </c>
       <c r="I1172" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J1172" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K1172" t="n">
-        <v>33</v>
+        <v>102</v>
       </c>
     </row>
     <row r="1173">
@@ -59312,7 +59312,7 @@
       </c>
       <c r="G1173" t="inlineStr">
         <is>
-          <t>Liliane Costa</t>
+          <t>Karina Oliveira</t>
         </is>
       </c>
       <c r="H1173" t="inlineStr">
@@ -59321,13 +59321,13 @@
         </is>
       </c>
       <c r="I1173" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1173" t="n">
         <v>6</v>
       </c>
       <c r="K1173" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
     </row>
     <row r="1174">
@@ -59363,7 +59363,7 @@
       </c>
       <c r="G1174" t="inlineStr">
         <is>
-          <t>Luciene Pimenta</t>
+          <t>Leonardo Assunção</t>
         </is>
       </c>
       <c r="H1174" t="inlineStr">
@@ -59372,13 +59372,13 @@
         </is>
       </c>
       <c r="I1174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1174" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K1174" t="n">
-        <v>11</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1175">
@@ -59414,7 +59414,7 @@
       </c>
       <c r="G1175" t="inlineStr">
         <is>
-          <t>Lucirene Souza</t>
+          <t>Liliane Costa</t>
         </is>
       </c>
       <c r="H1175" t="inlineStr">
@@ -59423,13 +59423,13 @@
         </is>
       </c>
       <c r="I1175" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1175" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="K1175" t="n">
-        <v>85</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1176">
@@ -59465,7 +59465,7 @@
       </c>
       <c r="G1176" t="inlineStr">
         <is>
-          <t>Marlon Silva</t>
+          <t>Luciene Pimenta</t>
         </is>
       </c>
       <c r="H1176" t="inlineStr">
@@ -59477,10 +59477,10 @@
         <v>0</v>
       </c>
       <c r="J1176" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K1176" t="n">
-        <v>109</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1177">
@@ -59516,7 +59516,7 @@
       </c>
       <c r="G1177" t="inlineStr">
         <is>
-          <t>Monique Britto</t>
+          <t>Lucirene Souza</t>
         </is>
       </c>
       <c r="H1177" t="inlineStr">
@@ -59528,10 +59528,10 @@
         <v>0</v>
       </c>
       <c r="J1177" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="K1177" t="n">
-        <v>94</v>
+        <v>85</v>
       </c>
     </row>
     <row r="1178">
@@ -59567,7 +59567,7 @@
       </c>
       <c r="G1178" t="inlineStr">
         <is>
-          <t>Romulo Ferreira</t>
+          <t>Marlon Silva</t>
         </is>
       </c>
       <c r="H1178" t="inlineStr">
@@ -59576,13 +59576,13 @@
         </is>
       </c>
       <c r="I1178" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J1178" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="K1178" t="n">
-        <v>315</v>
+        <v>109</v>
       </c>
     </row>
     <row r="1179">
@@ -59618,7 +59618,7 @@
       </c>
       <c r="G1179" t="inlineStr">
         <is>
-          <t>Rosilene Silva</t>
+          <t>Monique Britto</t>
         </is>
       </c>
       <c r="H1179" t="inlineStr">
@@ -59630,10 +59630,10 @@
         <v>0</v>
       </c>
       <c r="J1179" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="K1179" t="n">
-        <v>29</v>
+        <v>94</v>
       </c>
     </row>
     <row r="1180">
@@ -59669,7 +59669,7 @@
       </c>
       <c r="G1180" t="inlineStr">
         <is>
-          <t>Thais Santos</t>
+          <t>Romulo Ferreira</t>
         </is>
       </c>
       <c r="H1180" t="inlineStr">
@@ -59678,13 +59678,13 @@
         </is>
       </c>
       <c r="I1180" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J1180" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="K1180" t="n">
-        <v>113</v>
+        <v>315</v>
       </c>
     </row>
     <row r="1181">
@@ -59720,7 +59720,7 @@
       </c>
       <c r="G1181" t="inlineStr">
         <is>
-          <t>Vitoria Tavares</t>
+          <t>Rosilene Silva</t>
         </is>
       </c>
       <c r="H1181" t="inlineStr">
@@ -59729,13 +59729,13 @@
         </is>
       </c>
       <c r="I1181" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J1181" t="n">
+        <v>16</v>
+      </c>
+      <c r="K1181" t="n">
         <v>29</v>
-      </c>
-      <c r="K1181" t="n">
-        <v>178</v>
       </c>
     </row>
     <row r="1182">
@@ -59771,7 +59771,7 @@
       </c>
       <c r="G1182" t="inlineStr">
         <is>
-          <t>Viviane Moura</t>
+          <t>Thais Santos</t>
         </is>
       </c>
       <c r="H1182" t="inlineStr">
@@ -59780,13 +59780,13 @@
         </is>
       </c>
       <c r="I1182" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J1182" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K1182" t="n">
-        <v>74</v>
+        <v>113</v>
       </c>
     </row>
     <row r="1183">
@@ -59822,7 +59822,7 @@
       </c>
       <c r="G1183" t="inlineStr">
         <is>
-          <t>Yasmin Lopes</t>
+          <t>Vitoria Tavares</t>
         </is>
       </c>
       <c r="H1183" t="inlineStr">
@@ -59831,13 +59831,13 @@
         </is>
       </c>
       <c r="I1183" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J1183" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="K1183" t="n">
-        <v>123</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1184">
@@ -59868,27 +59868,27 @@
       </c>
       <c r="F1184" t="inlineStr">
         <is>
-          <t>RJ - EF</t>
+          <t>RJ - DP</t>
         </is>
       </c>
       <c r="G1184" t="inlineStr">
         <is>
-          <t>Altamir Nogueira</t>
+          <t>Viviane Moura</t>
         </is>
       </c>
       <c r="H1184" t="inlineStr">
         <is>
-          <t>Julio Santos|Jessica Benjamin</t>
+          <t>Karina Oliveira|Liliane Costa</t>
         </is>
       </c>
       <c r="I1184" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="J1184" t="n">
-        <v>81</v>
+        <v>30</v>
       </c>
       <c r="K1184" t="n">
-        <v>143</v>
+        <v>74</v>
       </c>
     </row>
     <row r="1185">
@@ -59919,27 +59919,27 @@
       </c>
       <c r="F1185" t="inlineStr">
         <is>
-          <t>RJ - EF</t>
+          <t>RJ - DP</t>
         </is>
       </c>
       <c r="G1185" t="inlineStr">
         <is>
-          <t>Beatriz Oliveira</t>
+          <t>Yasmin Lopes</t>
         </is>
       </c>
       <c r="H1185" t="inlineStr">
         <is>
-          <t>Julio Santos|Jessica Benjamin</t>
+          <t>Karina Oliveira|Liliane Costa</t>
         </is>
       </c>
       <c r="I1185" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="J1185" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="K1185" t="n">
-        <v>74</v>
+        <v>123</v>
       </c>
     </row>
     <row r="1186">
@@ -59975,7 +59975,7 @@
       </c>
       <c r="G1186" t="inlineStr">
         <is>
-          <t>Glaucia Santos</t>
+          <t>Altamir Nogueira</t>
         </is>
       </c>
       <c r="H1186" t="inlineStr">
@@ -59984,13 +59984,13 @@
         </is>
       </c>
       <c r="I1186" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="J1186" t="n">
-        <v>76</v>
+        <v>107</v>
       </c>
       <c r="K1186" t="n">
-        <v>127</v>
+        <v>169</v>
       </c>
     </row>
     <row r="1187">
@@ -60026,7 +60026,7 @@
       </c>
       <c r="G1187" t="inlineStr">
         <is>
-          <t>Isabela Barbosa</t>
+          <t>Beatriz Oliveira</t>
         </is>
       </c>
       <c r="H1187" t="inlineStr">
@@ -60035,13 +60035,13 @@
         </is>
       </c>
       <c r="I1187" t="n">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="J1187" t="n">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="K1187" t="n">
-        <v>129</v>
+        <v>112</v>
       </c>
     </row>
     <row r="1188">
@@ -60077,7 +60077,7 @@
       </c>
       <c r="G1188" t="inlineStr">
         <is>
-          <t>Jessica Benjamin</t>
+          <t>Glaucia Santos</t>
         </is>
       </c>
       <c r="H1188" t="inlineStr">
@@ -60086,13 +60086,13 @@
         </is>
       </c>
       <c r="I1188" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="J1188" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="K1188" t="n">
-        <v>108</v>
+        <v>129</v>
       </c>
     </row>
     <row r="1189">
@@ -60128,7 +60128,7 @@
       </c>
       <c r="G1189" t="inlineStr">
         <is>
-          <t>Juliana Perfeito</t>
+          <t>Isabela Barbosa</t>
         </is>
       </c>
       <c r="H1189" t="inlineStr">
@@ -60137,13 +60137,13 @@
         </is>
       </c>
       <c r="I1189" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="J1189" t="n">
-        <v>53</v>
+        <v>134</v>
       </c>
       <c r="K1189" t="n">
-        <v>77</v>
+        <v>148</v>
       </c>
     </row>
     <row r="1190">
@@ -60179,7 +60179,7 @@
       </c>
       <c r="G1190" t="inlineStr">
         <is>
-          <t>Julio Santos</t>
+          <t>Jessica Benjamin</t>
         </is>
       </c>
       <c r="H1190" t="inlineStr">
@@ -60188,13 +60188,13 @@
         </is>
       </c>
       <c r="I1190" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="J1190" t="n">
-        <v>4</v>
+        <v>64</v>
       </c>
       <c r="K1190" t="n">
-        <v>1</v>
+        <v>122</v>
       </c>
     </row>
     <row r="1191">
@@ -60230,7 +60230,7 @@
       </c>
       <c r="G1191" t="inlineStr">
         <is>
-          <t>Lais Catrine EF</t>
+          <t>Juliana Perfeito</t>
         </is>
       </c>
       <c r="H1191" t="inlineStr">
@@ -60239,13 +60239,13 @@
         </is>
       </c>
       <c r="I1191" t="n">
-        <v>82</v>
+        <v>35</v>
       </c>
       <c r="J1191" t="n">
-        <v>95</v>
+        <v>67</v>
       </c>
       <c r="K1191" t="n">
-        <v>209</v>
+        <v>91</v>
       </c>
     </row>
     <row r="1192">
@@ -60281,7 +60281,7 @@
       </c>
       <c r="G1192" t="inlineStr">
         <is>
-          <t>Luana Meneses</t>
+          <t>Julio Santos</t>
         </is>
       </c>
       <c r="H1192" t="inlineStr">
@@ -60290,13 +60290,13 @@
         </is>
       </c>
       <c r="I1192" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="J1192" t="n">
-        <v>91</v>
+        <v>4</v>
       </c>
       <c r="K1192" t="n">
-        <v>133</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1193">
@@ -60332,7 +60332,7 @@
       </c>
       <c r="G1193" t="inlineStr">
         <is>
-          <t>Otacilia Ferreira</t>
+          <t>Lais Catrine EF</t>
         </is>
       </c>
       <c r="H1193" t="inlineStr">
@@ -60341,13 +60341,13 @@
         </is>
       </c>
       <c r="I1193" t="n">
-        <v>36</v>
+        <v>83</v>
       </c>
       <c r="J1193" t="n">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="K1193" t="n">
-        <v>97</v>
+        <v>210</v>
       </c>
     </row>
     <row r="1194">
@@ -60383,7 +60383,7 @@
       </c>
       <c r="G1194" t="inlineStr">
         <is>
-          <t>Renata Paixão</t>
+          <t>Luana Meneses</t>
         </is>
       </c>
       <c r="H1194" t="inlineStr">
@@ -60392,13 +60392,13 @@
         </is>
       </c>
       <c r="I1194" t="n">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="J1194" t="n">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="K1194" t="n">
-        <v>152</v>
+        <v>133</v>
       </c>
     </row>
     <row r="1195">
@@ -60434,7 +60434,7 @@
       </c>
       <c r="G1195" t="inlineStr">
         <is>
-          <t>Thamara Jordes</t>
+          <t>Otacilia Ferreira</t>
         </is>
       </c>
       <c r="H1195" t="inlineStr">
@@ -60443,13 +60443,13 @@
         </is>
       </c>
       <c r="I1195" t="n">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="J1195" t="n">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="K1195" t="n">
-        <v>110</v>
+        <v>104</v>
       </c>
     </row>
     <row r="1196">
@@ -60485,7 +60485,7 @@
       </c>
       <c r="G1196" t="inlineStr">
         <is>
-          <t>Wellington Oliveira</t>
+          <t>Renata Paixão</t>
         </is>
       </c>
       <c r="H1196" t="inlineStr">
@@ -60494,13 +60494,13 @@
         </is>
       </c>
       <c r="I1196" t="n">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="J1196" t="n">
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="K1196" t="n">
-        <v>173</v>
+        <v>162</v>
       </c>
     </row>
     <row r="1197">
@@ -60531,23 +60531,27 @@
       </c>
       <c r="F1197" t="inlineStr">
         <is>
-          <t>RJ - GC</t>
+          <t>RJ - EF</t>
         </is>
       </c>
       <c r="G1197" t="inlineStr">
         <is>
-          <t>Bruno Mota</t>
-        </is>
-      </c>
-      <c r="H1197" t="inlineStr"/>
+          <t>Thamara Jordes</t>
+        </is>
+      </c>
+      <c r="H1197" t="inlineStr">
+        <is>
+          <t>Julio Santos|Jessica Benjamin</t>
+        </is>
+      </c>
       <c r="I1197" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="J1197" t="n">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="K1197" t="n">
-        <v>155</v>
+        <v>126</v>
       </c>
     </row>
     <row r="1198">
@@ -60578,23 +60582,27 @@
       </c>
       <c r="F1198" t="inlineStr">
         <is>
-          <t>RJ - GC</t>
+          <t>RJ - EF</t>
         </is>
       </c>
       <c r="G1198" t="inlineStr">
         <is>
-          <t>Cavalcante Peres</t>
-        </is>
-      </c>
-      <c r="H1198" t="inlineStr"/>
+          <t>Wellington Oliveira</t>
+        </is>
+      </c>
+      <c r="H1198" t="inlineStr">
+        <is>
+          <t>Julio Santos|Jessica Benjamin</t>
+        </is>
+      </c>
       <c r="I1198" t="n">
-        <v>3</v>
+        <v>63</v>
       </c>
       <c r="J1198" t="n">
-        <v>65</v>
+        <v>128</v>
       </c>
       <c r="K1198" t="n">
-        <v>81</v>
+        <v>187</v>
       </c>
     </row>
     <row r="1199">
@@ -60630,7 +60638,7 @@
       </c>
       <c r="G1199" t="inlineStr">
         <is>
-          <t>Tiago Rodrigues</t>
+          <t>Bruno Mota</t>
         </is>
       </c>
       <c r="H1199" t="inlineStr"/>
@@ -60638,10 +60646,10 @@
         <v>0</v>
       </c>
       <c r="J1199" t="n">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="K1199" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
     </row>
     <row r="1200">
@@ -60672,23 +60680,23 @@
       </c>
       <c r="F1200" t="inlineStr">
         <is>
-          <t>RJ - GC ADMINISTRATIVO</t>
+          <t>RJ - GC</t>
         </is>
       </c>
       <c r="G1200" t="inlineStr">
         <is>
-          <t>Amanda Mesquita</t>
+          <t>Cavalcante Peres</t>
         </is>
       </c>
       <c r="H1200" t="inlineStr"/>
       <c r="I1200" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1200" t="n">
-        <v>189</v>
+        <v>65</v>
       </c>
       <c r="K1200" t="n">
-        <v>224</v>
+        <v>81</v>
       </c>
     </row>
     <row r="1201">
@@ -60719,23 +60727,23 @@
       </c>
       <c r="F1201" t="inlineStr">
         <is>
-          <t>RJ - GC ADMINISTRATIVO</t>
+          <t>RJ - GC</t>
         </is>
       </c>
       <c r="G1201" t="inlineStr">
         <is>
-          <t>Lohany Martins</t>
+          <t>Tiago Rodrigues</t>
         </is>
       </c>
       <c r="H1201" t="inlineStr"/>
       <c r="I1201" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1201" t="n">
         <v>1</v>
       </c>
-      <c r="J1201" t="n">
-        <v>145</v>
-      </c>
       <c r="K1201" t="n">
-        <v>347</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1202">
@@ -60766,12 +60774,12 @@
       </c>
       <c r="F1202" t="inlineStr">
         <is>
-          <t>S.A.C</t>
+          <t>RJ - GC ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="G1202" t="inlineStr">
         <is>
-          <t>Milena Campos - SAC</t>
+          <t>Amanda Mesquita</t>
         </is>
       </c>
       <c r="H1202" t="inlineStr"/>
@@ -60779,10 +60787,10 @@
         <v>0</v>
       </c>
       <c r="J1202" t="n">
-        <v>0</v>
+        <v>189</v>
       </c>
       <c r="K1202" t="n">
-        <v>1</v>
+        <v>224</v>
       </c>
     </row>
     <row r="1203">
@@ -60808,32 +60816,28 @@
       </c>
       <c r="E1203" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F1203" t="inlineStr">
         <is>
-          <t>CONTABILIDADE (Outsourcing)</t>
+          <t>RJ - GC ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="G1203" t="inlineStr">
         <is>
-          <t>Aline Petrini</t>
-        </is>
-      </c>
-      <c r="H1203" t="inlineStr">
-        <is>
-          <t>Fernanda Araujo</t>
-        </is>
-      </c>
+          <t>Lohany Martins</t>
+        </is>
+      </c>
+      <c r="H1203" t="inlineStr"/>
       <c r="I1203" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1203" t="n">
-        <v>1</v>
+        <v>145</v>
       </c>
       <c r="K1203" t="n">
-        <v>2</v>
+        <v>347</v>
       </c>
     </row>
     <row r="1204">
@@ -60859,24 +60863,20 @@
       </c>
       <c r="E1204" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F1204" t="inlineStr">
         <is>
-          <t>CONTABILIDADE (Outsourcing)</t>
+          <t>S.A.C</t>
         </is>
       </c>
       <c r="G1204" t="inlineStr">
         <is>
-          <t>Daniele Leite</t>
-        </is>
-      </c>
-      <c r="H1204" t="inlineStr">
-        <is>
-          <t>Edileide Dias</t>
-        </is>
-      </c>
+          <t>Milena Campos - SAC</t>
+        </is>
+      </c>
+      <c r="H1204" t="inlineStr"/>
       <c r="I1204" t="n">
         <v>0</v>
       </c>
@@ -60920,22 +60920,22 @@
       </c>
       <c r="G1205" t="inlineStr">
         <is>
-          <t>Diogo Calazans</t>
+          <t>Aline Petrini</t>
         </is>
       </c>
       <c r="H1205" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="I1205" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1205" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1205" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1206">
@@ -60971,22 +60971,22 @@
       </c>
       <c r="G1206" t="inlineStr">
         <is>
-          <t>Jaqueline Sousa</t>
+          <t>Daniele Leite</t>
         </is>
       </c>
       <c r="H1206" t="inlineStr">
         <is>
-          <t>Lucas Fischer</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I1206" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1206" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K1206" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1207">
@@ -61022,12 +61022,12 @@
       </c>
       <c r="G1207" t="inlineStr">
         <is>
-          <t>Patricia Borges</t>
+          <t>Diogo Calazans</t>
         </is>
       </c>
       <c r="H1207" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Karina Santos</t>
         </is>
       </c>
       <c r="I1207" t="n">
@@ -61037,7 +61037,7 @@
         <v>0</v>
       </c>
       <c r="K1207" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1208">
@@ -61073,19 +61073,19 @@
       </c>
       <c r="G1208" t="inlineStr">
         <is>
-          <t>Rejane Coelho</t>
+          <t>Jaqueline Sousa</t>
         </is>
       </c>
       <c r="H1208" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Lucas Fischer</t>
         </is>
       </c>
       <c r="I1208" t="n">
         <v>0</v>
       </c>
       <c r="J1208" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K1208" t="n">
         <v>5</v>
@@ -61124,22 +61124,22 @@
       </c>
       <c r="G1209" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Patricia Borges</t>
         </is>
       </c>
       <c r="H1209" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I1209" t="n">
         <v>0</v>
       </c>
       <c r="J1209" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1209" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1210">
@@ -61175,7 +61175,7 @@
       </c>
       <c r="G1210" t="inlineStr">
         <is>
-          <t>Thiago Ceconelli</t>
+          <t>Rejane Coelho</t>
         </is>
       </c>
       <c r="H1210" t="inlineStr">
@@ -61190,7 +61190,7 @@
         <v>1</v>
       </c>
       <c r="K1210" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1211">
@@ -61221,12 +61221,12 @@
       </c>
       <c r="F1211" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL HOLDING</t>
+          <t>CONTABILIDADE (Outsourcing)</t>
         </is>
       </c>
       <c r="G1211" t="inlineStr">
         <is>
-          <t>Ana Flavia Silva</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="H1211" t="inlineStr">
@@ -61235,13 +61235,13 @@
         </is>
       </c>
       <c r="I1211" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="J1211" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="K1211" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1212">
@@ -61272,23 +61272,27 @@
       </c>
       <c r="F1212" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL HOLDING</t>
+          <t>CONTABILIDADE (Outsourcing)</t>
         </is>
       </c>
       <c r="G1212" t="inlineStr">
         <is>
-          <t>Daniele Faria</t>
-        </is>
-      </c>
-      <c r="H1212" t="inlineStr"/>
+          <t>Thiago Ceconelli</t>
+        </is>
+      </c>
+      <c r="H1212" t="inlineStr">
+        <is>
+          <t>Karina Santos</t>
+        </is>
+      </c>
       <c r="I1212" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1212" t="n">
         <v>2</v>
       </c>
       <c r="K1212" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1213">
@@ -61324,7 +61328,7 @@
       </c>
       <c r="G1213" t="inlineStr">
         <is>
-          <t>Vitor de Souza</t>
+          <t>Ana Flavia Silva</t>
         </is>
       </c>
       <c r="H1213" t="inlineStr">
@@ -61333,13 +61337,13 @@
         </is>
       </c>
       <c r="I1213" t="n">
-        <v>23</v>
+        <v>73</v>
       </c>
       <c r="J1213" t="n">
-        <v>39</v>
+        <v>92</v>
       </c>
       <c r="K1213" t="n">
-        <v>141</v>
+        <v>104</v>
       </c>
     </row>
     <row r="1214">
@@ -61375,22 +61379,18 @@
       </c>
       <c r="G1214" t="inlineStr">
         <is>
-          <t>Vitoria Regina</t>
-        </is>
-      </c>
-      <c r="H1214" t="inlineStr">
-        <is>
-          <t>Tatiana Linardi</t>
-        </is>
-      </c>
+          <t>Daniele Faria</t>
+        </is>
+      </c>
+      <c r="H1214" t="inlineStr"/>
       <c r="I1214" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="J1214" t="n">
-        <v>88</v>
+        <v>2</v>
       </c>
       <c r="K1214" t="n">
-        <v>143</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1215">
@@ -61421,27 +61421,27 @@
       </c>
       <c r="F1215" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL INDUSTRIA</t>
+          <t>CTB - CONTÁBIL HOLDING</t>
         </is>
       </c>
       <c r="G1215" t="inlineStr">
         <is>
-          <t>Adriano Barros</t>
+          <t>Vitor de Souza</t>
         </is>
       </c>
       <c r="H1215" t="inlineStr">
         <is>
-          <t>Erika Santana|Isabella Nascimento</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="I1215" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="J1215" t="n">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="K1215" t="n">
-        <v>12</v>
+        <v>141</v>
       </c>
     </row>
     <row r="1216">
@@ -61472,27 +61472,27 @@
       </c>
       <c r="F1216" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL INDUSTRIA</t>
+          <t>CTB - CONTÁBIL HOLDING</t>
         </is>
       </c>
       <c r="G1216" t="inlineStr">
         <is>
-          <t>Bianca Silva</t>
+          <t>Vitoria Regina</t>
         </is>
       </c>
       <c r="H1216" t="inlineStr">
         <is>
-          <t>Erika Santana|Isabella Nascimento</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="I1216" t="n">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="J1216" t="n">
-        <v>17</v>
+        <v>89</v>
       </c>
       <c r="K1216" t="n">
-        <v>22</v>
+        <v>144</v>
       </c>
     </row>
     <row r="1217">
@@ -61528,7 +61528,7 @@
       </c>
       <c r="G1217" t="inlineStr">
         <is>
-          <t>Emylle Souza</t>
+          <t>Adriano Barros</t>
         </is>
       </c>
       <c r="H1217" t="inlineStr">
@@ -61537,13 +61537,13 @@
         </is>
       </c>
       <c r="I1217" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="J1217" t="n">
+        <v>11</v>
+      </c>
+      <c r="K1217" t="n">
         <v>12</v>
-      </c>
-      <c r="K1217" t="n">
-        <v>17</v>
       </c>
     </row>
     <row r="1218">
@@ -61579,7 +61579,7 @@
       </c>
       <c r="G1218" t="inlineStr">
         <is>
-          <t>Fatima Rocha</t>
+          <t>Bianca Silva</t>
         </is>
       </c>
       <c r="H1218" t="inlineStr">
@@ -61588,13 +61588,13 @@
         </is>
       </c>
       <c r="I1218" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="J1218" t="n">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="K1218" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1219">
@@ -61630,7 +61630,7 @@
       </c>
       <c r="G1219" t="inlineStr">
         <is>
-          <t>Gabriel Correia</t>
+          <t>Emylle Souza</t>
         </is>
       </c>
       <c r="H1219" t="inlineStr">
@@ -61639,13 +61639,13 @@
         </is>
       </c>
       <c r="I1219" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J1219" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K1219" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1220">
@@ -61681,7 +61681,7 @@
       </c>
       <c r="G1220" t="inlineStr">
         <is>
-          <t>Isabella Nascimento</t>
+          <t>Fatima Rocha</t>
         </is>
       </c>
       <c r="H1220" t="inlineStr">
@@ -61690,13 +61690,13 @@
         </is>
       </c>
       <c r="I1220" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="J1220" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="K1220" t="n">
-        <v>2</v>
+        <v>54</v>
       </c>
     </row>
     <row r="1221">
@@ -61732,7 +61732,7 @@
       </c>
       <c r="G1221" t="inlineStr">
         <is>
-          <t>Laisa Rocha</t>
+          <t>Gabriel Correia</t>
         </is>
       </c>
       <c r="H1221" t="inlineStr">
@@ -61741,13 +61741,13 @@
         </is>
       </c>
       <c r="I1221" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J1221" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="K1221" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1222">
@@ -61783,7 +61783,7 @@
       </c>
       <c r="G1222" t="inlineStr">
         <is>
-          <t>Lucas Alves</t>
+          <t>Isabella Nascimento</t>
         </is>
       </c>
       <c r="H1222" t="inlineStr">
@@ -61792,13 +61792,13 @@
         </is>
       </c>
       <c r="I1222" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1222" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1222" t="n">
         <v>2</v>
-      </c>
-      <c r="J1222" t="n">
-        <v>6</v>
-      </c>
-      <c r="K1222" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="1223">
@@ -61834,7 +61834,7 @@
       </c>
       <c r="G1223" t="inlineStr">
         <is>
-          <t>Luciana Silva</t>
+          <t>Laisa Rocha</t>
         </is>
       </c>
       <c r="H1223" t="inlineStr">
@@ -61843,13 +61843,13 @@
         </is>
       </c>
       <c r="I1223" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J1223" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K1223" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1224">
@@ -61885,18 +61885,22 @@
       </c>
       <c r="G1224" t="inlineStr">
         <is>
-          <t>Luiz Ferreira</t>
-        </is>
-      </c>
-      <c r="H1224" t="inlineStr"/>
+          <t>Lucas Alves</t>
+        </is>
+      </c>
+      <c r="H1224" t="inlineStr">
+        <is>
+          <t>Erika Santana|Isabella Nascimento</t>
+        </is>
+      </c>
       <c r="I1224" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J1224" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K1224" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1225">
@@ -61932,7 +61936,7 @@
       </c>
       <c r="G1225" t="inlineStr">
         <is>
-          <t>Marcus Oliveira</t>
+          <t>Luciana Silva</t>
         </is>
       </c>
       <c r="H1225" t="inlineStr">
@@ -61941,13 +61945,13 @@
         </is>
       </c>
       <c r="I1225" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1225" t="n">
         <v>19</v>
       </c>
-      <c r="J1225" t="n">
-        <v>27</v>
-      </c>
       <c r="K1225" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="1226">
@@ -61983,22 +61987,18 @@
       </c>
       <c r="G1226" t="inlineStr">
         <is>
-          <t>Mariana Pires</t>
-        </is>
-      </c>
-      <c r="H1226" t="inlineStr">
-        <is>
-          <t>Erika Santana|Isabella Nascimento</t>
-        </is>
-      </c>
+          <t>Luiz Ferreira</t>
+        </is>
+      </c>
+      <c r="H1226" t="inlineStr"/>
       <c r="I1226" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J1226" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="K1226" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1227">
@@ -62034,7 +62034,7 @@
       </c>
       <c r="G1227" t="inlineStr">
         <is>
-          <t>Marta Souza</t>
+          <t>Marcus Oliveira</t>
         </is>
       </c>
       <c r="H1227" t="inlineStr">
@@ -62043,13 +62043,13 @@
         </is>
       </c>
       <c r="I1227" t="n">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="J1227" t="n">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="K1227" t="n">
-        <v>8</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1228">
@@ -62085,7 +62085,7 @@
       </c>
       <c r="G1228" t="inlineStr">
         <is>
-          <t>Mateus Miranda</t>
+          <t>Mariana Pires</t>
         </is>
       </c>
       <c r="H1228" t="inlineStr">
@@ -62094,13 +62094,13 @@
         </is>
       </c>
       <c r="I1228" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="J1228" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="K1228" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
     </row>
     <row r="1229">
@@ -62136,7 +62136,7 @@
       </c>
       <c r="G1229" t="inlineStr">
         <is>
-          <t>Mirian Lima</t>
+          <t>Marta Souza</t>
         </is>
       </c>
       <c r="H1229" t="inlineStr">
@@ -62145,13 +62145,13 @@
         </is>
       </c>
       <c r="I1229" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="J1229" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="K1229" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1230">
@@ -62187,7 +62187,7 @@
       </c>
       <c r="G1230" t="inlineStr">
         <is>
-          <t>Nathalia Lourenco</t>
+          <t>Mateus Miranda</t>
         </is>
       </c>
       <c r="H1230" t="inlineStr">
@@ -62196,13 +62196,13 @@
         </is>
       </c>
       <c r="I1230" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="J1230" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="K1230" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1231">
@@ -62238,7 +62238,7 @@
       </c>
       <c r="G1231" t="inlineStr">
         <is>
-          <t>Nicolas Dias</t>
+          <t>Mirian Lima</t>
         </is>
       </c>
       <c r="H1231" t="inlineStr">
@@ -62247,13 +62247,13 @@
         </is>
       </c>
       <c r="I1231" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J1231" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="K1231" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1232">
@@ -62289,7 +62289,7 @@
       </c>
       <c r="G1232" t="inlineStr">
         <is>
-          <t>Rodrigo Nunes</t>
+          <t>Nathalia Lourenco</t>
         </is>
       </c>
       <c r="H1232" t="inlineStr">
@@ -62298,13 +62298,13 @@
         </is>
       </c>
       <c r="I1232" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J1232" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K1232" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1233">
@@ -62340,7 +62340,7 @@
       </c>
       <c r="G1233" t="inlineStr">
         <is>
-          <t>Thais Souza</t>
+          <t>Nicolas Dias</t>
         </is>
       </c>
       <c r="H1233" t="inlineStr">
@@ -62349,13 +62349,13 @@
         </is>
       </c>
       <c r="I1233" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="J1233" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="K1233" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1234">
@@ -62391,7 +62391,7 @@
       </c>
       <c r="G1234" t="inlineStr">
         <is>
-          <t>Viviane Guedes</t>
+          <t>Rodrigo Nunes</t>
         </is>
       </c>
       <c r="H1234" t="inlineStr">
@@ -62400,13 +62400,13 @@
         </is>
       </c>
       <c r="I1234" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J1234" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1234" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1235">
@@ -62437,27 +62437,27 @@
       </c>
       <c r="F1235" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="G1235" t="inlineStr">
         <is>
-          <t>Aline Petrini</t>
+          <t>Thais Souza</t>
         </is>
       </c>
       <c r="H1235" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Erika Santana|Isabella Nascimento</t>
         </is>
       </c>
       <c r="I1235" t="n">
         <v>6</v>
       </c>
       <c r="J1235" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="K1235" t="n">
-        <v>46</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1236">
@@ -62488,27 +62488,27 @@
       </c>
       <c r="F1236" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="G1236" t="inlineStr">
         <is>
-          <t>Ana Barbosa</t>
+          <t>Viviane Guedes</t>
         </is>
       </c>
       <c r="H1236" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Erika Santana|Isabella Nascimento</t>
         </is>
       </c>
       <c r="I1236" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J1236" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K1236" t="n">
-        <v>46</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1237">
@@ -62544,22 +62544,22 @@
       </c>
       <c r="G1237" t="inlineStr">
         <is>
-          <t>Daniele Leite</t>
+          <t>Aline Petrini</t>
         </is>
       </c>
       <c r="H1237" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="I1237" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J1237" t="n">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="K1237" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1238">
@@ -62595,22 +62595,22 @@
       </c>
       <c r="G1238" t="inlineStr">
         <is>
-          <t>Danielle Silva</t>
+          <t>Ana Barbosa</t>
         </is>
       </c>
       <c r="H1238" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I1238" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J1238" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="K1238" t="n">
-        <v>77</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1239">
@@ -62646,22 +62646,22 @@
       </c>
       <c r="G1239" t="inlineStr">
         <is>
-          <t>Danilo Oliveira</t>
+          <t>Daniele Leite</t>
         </is>
       </c>
       <c r="H1239" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I1239" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J1239" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="K1239" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1240">
@@ -62697,22 +62697,22 @@
       </c>
       <c r="G1240" t="inlineStr">
         <is>
-          <t>Debora Silva</t>
+          <t>Danielle Silva</t>
         </is>
       </c>
       <c r="H1240" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Karina Santos</t>
         </is>
       </c>
       <c r="I1240" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J1240" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="K1240" t="n">
-        <v>31</v>
+        <v>78</v>
       </c>
     </row>
     <row r="1241">
@@ -62748,7 +62748,7 @@
       </c>
       <c r="G1241" t="inlineStr">
         <is>
-          <t>Diogo Calazans</t>
+          <t>Danilo Oliveira</t>
         </is>
       </c>
       <c r="H1241" t="inlineStr">
@@ -62757,13 +62757,13 @@
         </is>
       </c>
       <c r="I1241" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J1241" t="n">
         <v>17</v>
       </c>
       <c r="K1241" t="n">
-        <v>93</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1242">
@@ -62799,7 +62799,7 @@
       </c>
       <c r="G1242" t="inlineStr">
         <is>
-          <t>Eduardo Cruz</t>
+          <t>Debora Silva</t>
         </is>
       </c>
       <c r="H1242" t="inlineStr">
@@ -62808,13 +62808,13 @@
         </is>
       </c>
       <c r="I1242" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J1242" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="K1242" t="n">
-        <v>80</v>
+        <v>31</v>
       </c>
     </row>
     <row r="1243">
@@ -62850,7 +62850,7 @@
       </c>
       <c r="G1243" t="inlineStr">
         <is>
-          <t>Eveny Silva</t>
+          <t>Diogo Calazans</t>
         </is>
       </c>
       <c r="H1243" t="inlineStr">
@@ -62859,13 +62859,13 @@
         </is>
       </c>
       <c r="I1243" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J1243" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="K1243" t="n">
-        <v>49</v>
+        <v>93</v>
       </c>
     </row>
     <row r="1244">
@@ -62901,7 +62901,7 @@
       </c>
       <c r="G1244" t="inlineStr">
         <is>
-          <t>Everton Moura</t>
+          <t>Eduardo Cruz</t>
         </is>
       </c>
       <c r="H1244" t="inlineStr">
@@ -62910,13 +62910,13 @@
         </is>
       </c>
       <c r="I1244" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J1244" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K1244" t="n">
-        <v>9</v>
+        <v>83</v>
       </c>
     </row>
     <row r="1245">
@@ -62952,22 +62952,22 @@
       </c>
       <c r="G1245" t="inlineStr">
         <is>
-          <t>Guilherme Dantas</t>
+          <t>Eveny Silva</t>
         </is>
       </c>
       <c r="H1245" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Karina Santos</t>
         </is>
       </c>
       <c r="I1245" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J1245" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="K1245" t="n">
-        <v>28</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1246">
@@ -63003,7 +63003,7 @@
       </c>
       <c r="G1246" t="inlineStr">
         <is>
-          <t>Isabela Lemos</t>
+          <t>Everton Moura</t>
         </is>
       </c>
       <c r="H1246" t="inlineStr">
@@ -63012,13 +63012,13 @@
         </is>
       </c>
       <c r="I1246" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J1246" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="K1246" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1247">
@@ -63054,7 +63054,7 @@
       </c>
       <c r="G1247" t="inlineStr">
         <is>
-          <t>Jackson Silva</t>
+          <t>Guilherme Dantas</t>
         </is>
       </c>
       <c r="H1247" t="inlineStr">
@@ -63063,10 +63063,10 @@
         </is>
       </c>
       <c r="I1247" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J1247" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K1247" t="n">
         <v>28</v>
@@ -63105,22 +63105,22 @@
       </c>
       <c r="G1248" t="inlineStr">
         <is>
-          <t>Jaqueline Sousa</t>
+          <t>Isabela Lemos</t>
         </is>
       </c>
       <c r="H1248" t="inlineStr">
         <is>
-          <t>Lucas Fischer</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="I1248" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J1248" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="K1248" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1249">
@@ -63156,22 +63156,22 @@
       </c>
       <c r="G1249" t="inlineStr">
         <is>
-          <t>Leticia Medeiros</t>
+          <t>Jackson Silva</t>
         </is>
       </c>
       <c r="H1249" t="inlineStr">
         <is>
-          <t>Lucas Fischer</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I1249" t="n">
         <v>5</v>
       </c>
       <c r="J1249" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="K1249" t="n">
-        <v>66</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1250">
@@ -63207,22 +63207,22 @@
       </c>
       <c r="G1250" t="inlineStr">
         <is>
-          <t>Monica Medeiros</t>
+          <t>Jaqueline Sousa</t>
         </is>
       </c>
       <c r="H1250" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Lucas Fischer</t>
         </is>
       </c>
       <c r="I1250" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J1250" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="K1250" t="n">
-        <v>52</v>
+        <v>31</v>
       </c>
     </row>
     <row r="1251">
@@ -63258,7 +63258,7 @@
       </c>
       <c r="G1251" t="inlineStr">
         <is>
-          <t>Naiara Dutra</t>
+          <t>Leticia Medeiros</t>
         </is>
       </c>
       <c r="H1251" t="inlineStr">
@@ -63267,13 +63267,13 @@
         </is>
       </c>
       <c r="I1251" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J1251" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="K1251" t="n">
-        <v>26</v>
+        <v>71</v>
       </c>
     </row>
     <row r="1252">
@@ -63309,7 +63309,7 @@
       </c>
       <c r="G1252" t="inlineStr">
         <is>
-          <t>Patricia Borges</t>
+          <t>Monica Medeiros</t>
         </is>
       </c>
       <c r="H1252" t="inlineStr">
@@ -63321,10 +63321,10 @@
         <v>4</v>
       </c>
       <c r="J1252" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K1252" t="n">
-        <v>38</v>
+        <v>53</v>
       </c>
     </row>
     <row r="1253">
@@ -63360,22 +63360,22 @@
       </c>
       <c r="G1253" t="inlineStr">
         <is>
-          <t>Paulo Silva</t>
+          <t>Naiara Dutra</t>
         </is>
       </c>
       <c r="H1253" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Lucas Fischer</t>
         </is>
       </c>
       <c r="I1253" t="n">
         <v>1</v>
       </c>
       <c r="J1253" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="K1253" t="n">
-        <v>59</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1254">
@@ -63411,7 +63411,7 @@
       </c>
       <c r="G1254" t="inlineStr">
         <is>
-          <t>Rachel Lima</t>
+          <t>Patricia Borges</t>
         </is>
       </c>
       <c r="H1254" t="inlineStr">
@@ -63420,13 +63420,13 @@
         </is>
       </c>
       <c r="I1254" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="J1254" t="n">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="K1254" t="n">
-        <v>64</v>
+        <v>38</v>
       </c>
     </row>
     <row r="1255">
@@ -63462,22 +63462,22 @@
       </c>
       <c r="G1255" t="inlineStr">
         <is>
-          <t>Raiane Barbosa</t>
+          <t>Paulo Silva</t>
         </is>
       </c>
       <c r="H1255" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="I1255" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J1255" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="K1255" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
     </row>
     <row r="1256">
@@ -63513,22 +63513,22 @@
       </c>
       <c r="G1256" t="inlineStr">
         <is>
-          <t>Rejane Coelho</t>
+          <t>Rachel Lima</t>
         </is>
       </c>
       <c r="H1256" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I1256" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="J1256" t="n">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="K1256" t="n">
-        <v>2</v>
+        <v>65</v>
       </c>
     </row>
     <row r="1257">
@@ -63564,22 +63564,22 @@
       </c>
       <c r="G1257" t="inlineStr">
         <is>
-          <t>Renata Alves - CTV</t>
+          <t>Raiane Barbosa</t>
         </is>
       </c>
       <c r="H1257" t="inlineStr">
         <is>
-          <t>Lucas Fischer</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I1257" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J1257" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="K1257" t="n">
-        <v>22</v>
+        <v>72</v>
       </c>
     </row>
     <row r="1258">
@@ -63615,18 +63615,22 @@
       </c>
       <c r="G1258" t="inlineStr">
         <is>
-          <t>Renata Cavalheiro</t>
-        </is>
-      </c>
-      <c r="H1258" t="inlineStr"/>
+          <t>Rejane Coelho</t>
+        </is>
+      </c>
+      <c r="H1258" t="inlineStr">
+        <is>
+          <t>Karina Santos</t>
+        </is>
+      </c>
       <c r="I1258" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J1258" t="n">
         <v>1</v>
       </c>
       <c r="K1258" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1259">
@@ -63662,22 +63666,22 @@
       </c>
       <c r="G1259" t="inlineStr">
         <is>
-          <t>Ryan Godinho</t>
+          <t>Renata Alves - CTV</t>
         </is>
       </c>
       <c r="H1259" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Lucas Fischer</t>
         </is>
       </c>
       <c r="I1259" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="J1259" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K1259" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1260">
@@ -63713,22 +63717,18 @@
       </c>
       <c r="G1260" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
-        </is>
-      </c>
-      <c r="H1260" t="inlineStr">
-        <is>
-          <t>Tatiana Linardi</t>
-        </is>
-      </c>
+          <t>Renata Cavalheiro</t>
+        </is>
+      </c>
+      <c r="H1260" t="inlineStr"/>
       <c r="I1260" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J1260" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K1260" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1261">
@@ -63764,22 +63764,22 @@
       </c>
       <c r="G1261" t="inlineStr">
         <is>
-          <t>Vitor Domingues</t>
+          <t>Ryan Godinho</t>
         </is>
       </c>
       <c r="H1261" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Karina Santos</t>
         </is>
       </c>
       <c r="I1261" t="n">
         <v>4</v>
       </c>
       <c r="J1261" t="n">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="K1261" t="n">
-        <v>70</v>
+        <v>34</v>
       </c>
     </row>
     <row r="1262">
@@ -63810,24 +63810,24 @@
       </c>
       <c r="F1262" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO PESSOAL (Outsourcing)</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="G1262" t="inlineStr">
         <is>
-          <t>Bruna Santana</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="H1262" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="I1262" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J1262" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K1262" t="n">
         <v>4</v>
@@ -63861,27 +63861,27 @@
       </c>
       <c r="F1263" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO PESSOAL (Outsourcing)</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="G1263" t="inlineStr">
         <is>
-          <t>Camila Oliveira</t>
+          <t>Vitor Domingues</t>
         </is>
       </c>
       <c r="H1263" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="I1263" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J1263" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="K1263" t="n">
-        <v>16</v>
+        <v>70</v>
       </c>
     </row>
     <row r="1264">
@@ -63917,22 +63917,22 @@
       </c>
       <c r="G1264" t="inlineStr">
         <is>
-          <t>Elaine Assis</t>
+          <t>Bruna Santana</t>
         </is>
       </c>
       <c r="H1264" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I1264" t="n">
         <v>0</v>
       </c>
       <c r="J1264" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K1264" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1265">
@@ -63968,22 +63968,22 @@
       </c>
       <c r="G1265" t="inlineStr">
         <is>
-          <t>Fabiane Branco</t>
+          <t>Camila Oliveira</t>
         </is>
       </c>
       <c r="H1265" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I1265" t="n">
         <v>0</v>
       </c>
       <c r="J1265" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K1265" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1266">
@@ -64019,22 +64019,22 @@
       </c>
       <c r="G1266" t="inlineStr">
         <is>
-          <t>Jonas Nunes</t>
+          <t>Elaine Assis</t>
         </is>
       </c>
       <c r="H1266" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I1266" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J1266" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K1266" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1267">
@@ -64065,27 +64065,27 @@
       </c>
       <c r="F1267" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>DEPARTAMENTO PESSOAL (Outsourcing)</t>
         </is>
       </c>
       <c r="G1267" t="inlineStr">
         <is>
-          <t>Bruna Santana</t>
+          <t>Fabiane Branco</t>
         </is>
       </c>
       <c r="H1267" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I1267" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J1267" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="K1267" t="n">
-        <v>122</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1268">
@@ -64116,12 +64116,12 @@
       </c>
       <c r="F1268" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>DEPARTAMENTO PESSOAL (Outsourcing)</t>
         </is>
       </c>
       <c r="G1268" t="inlineStr">
         <is>
-          <t>Camila Oliveira</t>
+          <t>Jonas Nunes</t>
         </is>
       </c>
       <c r="H1268" t="inlineStr">
@@ -64130,13 +64130,13 @@
         </is>
       </c>
       <c r="I1268" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1268" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K1268" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1269">
@@ -64172,22 +64172,18 @@
       </c>
       <c r="G1269" t="inlineStr">
         <is>
-          <t>Daniel Moraes</t>
-        </is>
-      </c>
-      <c r="H1269" t="inlineStr">
-        <is>
-          <t>David Bragança</t>
-        </is>
-      </c>
+          <t>Andressa Miranda</t>
+        </is>
+      </c>
+      <c r="H1269" t="inlineStr"/>
       <c r="I1269" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1269" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K1269" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1270">
@@ -64223,22 +64219,22 @@
       </c>
       <c r="G1270" t="inlineStr">
         <is>
-          <t>Danilo Xavier</t>
+          <t>Bruna Santana</t>
         </is>
       </c>
       <c r="H1270" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I1270" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J1270" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="K1270" t="n">
-        <v>176</v>
+        <v>125</v>
       </c>
     </row>
     <row r="1271">
@@ -64274,22 +64270,22 @@
       </c>
       <c r="G1271" t="inlineStr">
         <is>
-          <t>Elaine Assis</t>
+          <t>Camila Oliveira</t>
         </is>
       </c>
       <c r="H1271" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I1271" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J1271" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K1271" t="n">
-        <v>67</v>
+        <v>32</v>
       </c>
     </row>
     <row r="1272">
@@ -64325,22 +64321,22 @@
       </c>
       <c r="G1272" t="inlineStr">
         <is>
-          <t>Eliene Lima</t>
+          <t>Daniel Moraes</t>
         </is>
       </c>
       <c r="H1272" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I1272" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J1272" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K1272" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1273">
@@ -64376,7 +64372,7 @@
       </c>
       <c r="G1273" t="inlineStr">
         <is>
-          <t>Erica Oliveira</t>
+          <t>Danilo Xavier</t>
         </is>
       </c>
       <c r="H1273" t="inlineStr">
@@ -64388,10 +64384,10 @@
         <v>0</v>
       </c>
       <c r="J1273" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="K1273" t="n">
-        <v>47</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1274">
@@ -64427,22 +64423,22 @@
       </c>
       <c r="G1274" t="inlineStr">
         <is>
-          <t>Evellin Bispo</t>
+          <t>Elaine Assis</t>
         </is>
       </c>
       <c r="H1274" t="inlineStr">
         <is>
-          <t>Leandro Matos</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I1274" t="n">
         <v>1</v>
       </c>
       <c r="J1274" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K1274" t="n">
-        <v>32</v>
+        <v>67</v>
       </c>
     </row>
     <row r="1275">
@@ -64478,7 +64474,7 @@
       </c>
       <c r="G1275" t="inlineStr">
         <is>
-          <t>Fabiane Branco</t>
+          <t>Eliene Lima</t>
         </is>
       </c>
       <c r="H1275" t="inlineStr">
@@ -64487,13 +64483,13 @@
         </is>
       </c>
       <c r="I1275" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1275" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="K1275" t="n">
-        <v>134</v>
+        <v>44</v>
       </c>
     </row>
     <row r="1276">
@@ -64529,7 +64525,7 @@
       </c>
       <c r="G1276" t="inlineStr">
         <is>
-          <t>Franciele Alves</t>
+          <t>Erica Oliveira</t>
         </is>
       </c>
       <c r="H1276" t="inlineStr">
@@ -64541,10 +64537,10 @@
         <v>0</v>
       </c>
       <c r="J1276" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K1276" t="n">
-        <v>84</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1277">
@@ -64580,7 +64576,7 @@
       </c>
       <c r="G1277" t="inlineStr">
         <is>
-          <t>Gabriela Peres</t>
+          <t>Evellin Bispo</t>
         </is>
       </c>
       <c r="H1277" t="inlineStr">
@@ -64589,13 +64585,13 @@
         </is>
       </c>
       <c r="I1277" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J1277" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="K1277" t="n">
-        <v>14</v>
+        <v>39</v>
       </c>
     </row>
     <row r="1278">
@@ -64631,22 +64627,22 @@
       </c>
       <c r="G1278" t="inlineStr">
         <is>
-          <t>Grasiele Santos</t>
+          <t>Fabiane Branco</t>
         </is>
       </c>
       <c r="H1278" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I1278" t="n">
         <v>0</v>
       </c>
       <c r="J1278" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="K1278" t="n">
-        <v>143</v>
+        <v>134</v>
       </c>
     </row>
     <row r="1279">
@@ -64682,7 +64678,7 @@
       </c>
       <c r="G1279" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Franciele Alves</t>
         </is>
       </c>
       <c r="H1279" t="inlineStr">
@@ -64691,13 +64687,13 @@
         </is>
       </c>
       <c r="I1279" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="J1279" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="K1279" t="n">
-        <v>190</v>
+        <v>85</v>
       </c>
     </row>
     <row r="1280">
@@ -64733,22 +64729,22 @@
       </c>
       <c r="G1280" t="inlineStr">
         <is>
-          <t>Janaina Rocha</t>
+          <t>Gabriela Peres</t>
         </is>
       </c>
       <c r="H1280" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Leandro Matos</t>
         </is>
       </c>
       <c r="I1280" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1280" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="K1280" t="n">
-        <v>106</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1281">
@@ -64784,22 +64780,22 @@
       </c>
       <c r="G1281" t="inlineStr">
         <is>
-          <t>Jayne Tavares</t>
+          <t>Grasiele Santos</t>
         </is>
       </c>
       <c r="H1281" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I1281" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1281" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="K1281" t="n">
-        <v>127</v>
+        <v>143</v>
       </c>
     </row>
     <row r="1282">
@@ -64835,22 +64831,22 @@
       </c>
       <c r="G1282" t="inlineStr">
         <is>
-          <t>Jhenifer Tenorio</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="H1282" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I1282" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="J1282" t="n">
-        <v>10</v>
+        <v>108</v>
       </c>
       <c r="K1282" t="n">
-        <v>115</v>
+        <v>207</v>
       </c>
     </row>
     <row r="1283">
@@ -64886,7 +64882,7 @@
       </c>
       <c r="G1283" t="inlineStr">
         <is>
-          <t>Jonas Nunes</t>
+          <t>Janaina Rocha</t>
         </is>
       </c>
       <c r="H1283" t="inlineStr">
@@ -64895,13 +64891,13 @@
         </is>
       </c>
       <c r="I1283" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J1283" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="K1283" t="n">
-        <v>114</v>
+        <v>106</v>
       </c>
     </row>
     <row r="1284">
@@ -64937,7 +64933,7 @@
       </c>
       <c r="G1284" t="inlineStr">
         <is>
-          <t>Kaique Souza</t>
+          <t>Jayne Tavares</t>
         </is>
       </c>
       <c r="H1284" t="inlineStr">
@@ -64949,10 +64945,10 @@
         <v>0</v>
       </c>
       <c r="J1284" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="K1284" t="n">
-        <v>89</v>
+        <v>127</v>
       </c>
     </row>
     <row r="1285">
@@ -64988,22 +64984,22 @@
       </c>
       <c r="G1285" t="inlineStr">
         <is>
-          <t>Karine Sousa</t>
+          <t>Jhenifer Tenorio</t>
         </is>
       </c>
       <c r="H1285" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I1285" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J1285" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="K1285" t="n">
-        <v>68</v>
+        <v>115</v>
       </c>
     </row>
     <row r="1286">
@@ -65039,7 +65035,7 @@
       </c>
       <c r="G1286" t="inlineStr">
         <is>
-          <t>Laysla Alves</t>
+          <t>Jonas Nunes</t>
         </is>
       </c>
       <c r="H1286" t="inlineStr">
@@ -65048,13 +65044,13 @@
         </is>
       </c>
       <c r="I1286" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J1286" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="K1286" t="n">
-        <v>63</v>
+        <v>114</v>
       </c>
     </row>
     <row r="1287">
@@ -65090,22 +65086,22 @@
       </c>
       <c r="G1287" t="inlineStr">
         <is>
-          <t>Luana Marques</t>
+          <t>Kaique Souza</t>
         </is>
       </c>
       <c r="H1287" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I1287" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J1287" t="n">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="K1287" t="n">
-        <v>19</v>
+        <v>99</v>
       </c>
     </row>
     <row r="1288">
@@ -65141,22 +65137,22 @@
       </c>
       <c r="G1288" t="inlineStr">
         <is>
-          <t>Maria Pires</t>
+          <t>Karine Sousa</t>
         </is>
       </c>
       <c r="H1288" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I1288" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="J1288" t="n">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="K1288" t="n">
-        <v>1</v>
+        <v>76</v>
       </c>
     </row>
     <row r="1289">
@@ -65192,22 +65188,22 @@
       </c>
       <c r="G1289" t="inlineStr">
         <is>
-          <t>Mauricio Lermen</t>
+          <t>Laysla Alves</t>
         </is>
       </c>
       <c r="H1289" t="inlineStr">
         <is>
-          <t>Mauricio Lermen</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I1289" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J1289" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="K1289" t="n">
-        <v>14</v>
+        <v>79</v>
       </c>
     </row>
     <row r="1290">
@@ -65243,22 +65239,22 @@
       </c>
       <c r="G1290" t="inlineStr">
         <is>
-          <t>Micaele Cordeiro</t>
+          <t>Luana Marques</t>
         </is>
       </c>
       <c r="H1290" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I1290" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J1290" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="K1290" t="n">
-        <v>120</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1291">
@@ -65294,22 +65290,22 @@
       </c>
       <c r="G1291" t="inlineStr">
         <is>
-          <t>Michele Silva</t>
+          <t>Maria Pires</t>
         </is>
       </c>
       <c r="H1291" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I1291" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="J1291" t="n">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="K1291" t="n">
-        <v>83</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1292">
@@ -65345,18 +65341,22 @@
       </c>
       <c r="G1292" t="inlineStr">
         <is>
-          <t>Mikael Teixeira</t>
-        </is>
-      </c>
-      <c r="H1292" t="inlineStr"/>
+          <t>Mauricio Lermen</t>
+        </is>
+      </c>
+      <c r="H1292" t="inlineStr">
+        <is>
+          <t>Mauricio Lermen</t>
+        </is>
+      </c>
       <c r="I1292" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1292" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K1292" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1293">
@@ -65392,22 +65392,22 @@
       </c>
       <c r="G1293" t="inlineStr">
         <is>
-          <t>Murilo Marques</t>
+          <t>Micaele Cordeiro</t>
         </is>
       </c>
       <c r="H1293" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I1293" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J1293" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="K1293" t="n">
-        <v>61</v>
+        <v>120</v>
       </c>
     </row>
     <row r="1294">
@@ -65443,22 +65443,22 @@
       </c>
       <c r="G1294" t="inlineStr">
         <is>
-          <t>Natalia Batista</t>
+          <t>Michele Silva</t>
         </is>
       </c>
       <c r="H1294" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I1294" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1294" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K1294" t="n">
-        <v>110</v>
+        <v>84</v>
       </c>
     </row>
     <row r="1295">
@@ -65494,22 +65494,18 @@
       </c>
       <c r="G1295" t="inlineStr">
         <is>
-          <t>Natalia Silva</t>
-        </is>
-      </c>
-      <c r="H1295" t="inlineStr">
-        <is>
-          <t>David Bragança</t>
-        </is>
-      </c>
+          <t>Mikael Teixeira</t>
+        </is>
+      </c>
+      <c r="H1295" t="inlineStr"/>
       <c r="I1295" t="n">
         <v>0</v>
       </c>
       <c r="J1295" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="K1295" t="n">
-        <v>113</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1296">
@@ -65545,22 +65541,22 @@
       </c>
       <c r="G1296" t="inlineStr">
         <is>
-          <t>Oliene Mariano</t>
+          <t>Murilo Marques</t>
         </is>
       </c>
       <c r="H1296" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I1296" t="n">
         <v>0</v>
       </c>
       <c r="J1296" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="K1296" t="n">
-        <v>97</v>
+        <v>61</v>
       </c>
     </row>
     <row r="1297">
@@ -65596,7 +65592,7 @@
       </c>
       <c r="G1297" t="inlineStr">
         <is>
-          <t>Priscila Aguiar</t>
+          <t>Natalia Batista</t>
         </is>
       </c>
       <c r="H1297" t="inlineStr">
@@ -65605,13 +65601,13 @@
         </is>
       </c>
       <c r="I1297" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J1297" t="n">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="K1297" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="1298">
@@ -65647,22 +65643,22 @@
       </c>
       <c r="G1298" t="inlineStr">
         <is>
-          <t>Rebeca Ribeiro</t>
+          <t>Natalia Silva</t>
         </is>
       </c>
       <c r="H1298" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I1298" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J1298" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="K1298" t="n">
-        <v>66</v>
+        <v>118</v>
       </c>
     </row>
     <row r="1299">
@@ -65698,22 +65694,22 @@
       </c>
       <c r="G1299" t="inlineStr">
         <is>
-          <t>Roberta Souza</t>
+          <t>Oliene Mariano</t>
         </is>
       </c>
       <c r="H1299" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I1299" t="n">
         <v>0</v>
       </c>
       <c r="J1299" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K1299" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="1300">
@@ -65749,7 +65745,7 @@
       </c>
       <c r="G1300" t="inlineStr">
         <is>
-          <t>Ronildo Santos</t>
+          <t>Priscila Aguiar</t>
         </is>
       </c>
       <c r="H1300" t="inlineStr">
@@ -65758,13 +65754,13 @@
         </is>
       </c>
       <c r="I1300" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1300" t="n">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c r="K1300" t="n">
-        <v>6</v>
+        <v>112</v>
       </c>
     </row>
     <row r="1301">
@@ -65800,22 +65796,22 @@
       </c>
       <c r="G1301" t="inlineStr">
         <is>
-          <t>Rozania Santos</t>
+          <t>Rebeca Ribeiro</t>
         </is>
       </c>
       <c r="H1301" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I1301" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J1301" t="n">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="K1301" t="n">
-        <v>141</v>
+        <v>66</v>
       </c>
     </row>
     <row r="1302">
@@ -65851,22 +65847,22 @@
       </c>
       <c r="G1302" t="inlineStr">
         <is>
-          <t>Santos Karina</t>
+          <t>Roberta Souza</t>
         </is>
       </c>
       <c r="H1302" t="inlineStr">
         <is>
-          <t>Leandro Matos</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I1302" t="n">
         <v>0</v>
       </c>
       <c r="J1302" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="K1302" t="n">
-        <v>2</v>
+        <v>99</v>
       </c>
     </row>
     <row r="1303">
@@ -65902,22 +65898,22 @@
       </c>
       <c r="G1303" t="inlineStr">
         <is>
-          <t>Sibelly Pereira</t>
+          <t>Ronildo Santos</t>
         </is>
       </c>
       <c r="H1303" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I1303" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J1303" t="n">
-        <v>53</v>
+        <v>3</v>
       </c>
       <c r="K1303" t="n">
-        <v>94</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1304">
@@ -65953,22 +65949,22 @@
       </c>
       <c r="G1304" t="inlineStr">
         <is>
-          <t>Tania Luz</t>
+          <t>Rozania Santos</t>
         </is>
       </c>
       <c r="H1304" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I1304" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J1304" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="K1304" t="n">
-        <v>77</v>
+        <v>147</v>
       </c>
     </row>
     <row r="1305">
@@ -66004,22 +66000,22 @@
       </c>
       <c r="G1305" t="inlineStr">
         <is>
-          <t>Vitor Guedes</t>
+          <t>Santos Karina</t>
         </is>
       </c>
       <c r="H1305" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Leandro Matos</t>
         </is>
       </c>
       <c r="I1305" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1305" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K1305" t="n">
-        <v>134</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1306">
@@ -66050,27 +66046,27 @@
       </c>
       <c r="F1306" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="G1306" t="inlineStr">
         <is>
-          <t>Andrea Medeiros</t>
+          <t>Sibelly Pereira</t>
         </is>
       </c>
       <c r="H1306" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I1306" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="J1306" t="n">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="K1306" t="n">
-        <v>66</v>
+        <v>107</v>
       </c>
     </row>
     <row r="1307">
@@ -66101,27 +66097,27 @@
       </c>
       <c r="F1307" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="G1307" t="inlineStr">
         <is>
-          <t>Caroline Nascimento</t>
+          <t>Tania Luz</t>
         </is>
       </c>
       <c r="H1307" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I1307" t="n">
         <v>0</v>
       </c>
       <c r="J1307" t="n">
-        <v>98</v>
+        <v>29</v>
       </c>
       <c r="K1307" t="n">
-        <v>151</v>
+        <v>77</v>
       </c>
     </row>
     <row r="1308">
@@ -66152,27 +66148,27 @@
       </c>
       <c r="F1308" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="G1308" t="inlineStr">
         <is>
-          <t>Cristiana Grizostomo</t>
+          <t>Vitor Guedes</t>
         </is>
       </c>
       <c r="H1308" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I1308" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1308" t="n">
         <v>5</v>
       </c>
-      <c r="J1308" t="n">
-        <v>30</v>
-      </c>
       <c r="K1308" t="n">
-        <v>63</v>
+        <v>134</v>
       </c>
     </row>
     <row r="1309">
@@ -66208,18 +66204,22 @@
       </c>
       <c r="G1309" t="inlineStr">
         <is>
-          <t>Denis Reis</t>
-        </is>
-      </c>
-      <c r="H1309" t="inlineStr"/>
+          <t>Andrea Medeiros</t>
+        </is>
+      </c>
+      <c r="H1309" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
       <c r="I1309" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1309" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="K1309" t="n">
-        <v>89</v>
+        <v>68</v>
       </c>
     </row>
     <row r="1310">
@@ -66255,7 +66255,7 @@
       </c>
       <c r="G1310" t="inlineStr">
         <is>
-          <t>Eliane Moreira</t>
+          <t>Caroline Nascimento</t>
         </is>
       </c>
       <c r="H1310" t="inlineStr">
@@ -66264,13 +66264,13 @@
         </is>
       </c>
       <c r="I1310" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J1310" t="n">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="K1310" t="n">
-        <v>143</v>
+        <v>157</v>
       </c>
     </row>
     <row r="1311">
@@ -66306,7 +66306,7 @@
       </c>
       <c r="G1311" t="inlineStr">
         <is>
-          <t>Gustavo Tonan</t>
+          <t>Cristiana Grizostomo</t>
         </is>
       </c>
       <c r="H1311" t="inlineStr">
@@ -66315,13 +66315,13 @@
         </is>
       </c>
       <c r="I1311" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="J1311" t="n">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="K1311" t="n">
-        <v>122</v>
+        <v>71</v>
       </c>
     </row>
     <row r="1312">
@@ -66357,22 +66357,18 @@
       </c>
       <c r="G1312" t="inlineStr">
         <is>
-          <t>Jonatan Hayashibara</t>
-        </is>
-      </c>
-      <c r="H1312" t="inlineStr">
-        <is>
-          <t>Nayara Oliveira</t>
-        </is>
-      </c>
+          <t>Denis Reis</t>
+        </is>
+      </c>
+      <c r="H1312" t="inlineStr"/>
       <c r="I1312" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="J1312" t="n">
-        <v>514</v>
+        <v>31</v>
       </c>
       <c r="K1312" t="n">
-        <v>626</v>
+        <v>97</v>
       </c>
     </row>
     <row r="1313">
@@ -66408,7 +66404,7 @@
       </c>
       <c r="G1313" t="inlineStr">
         <is>
-          <t>Lais Arruda</t>
+          <t>Eliane Moreira</t>
         </is>
       </c>
       <c r="H1313" t="inlineStr">
@@ -66417,13 +66413,13 @@
         </is>
       </c>
       <c r="I1313" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J1313" t="n">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="K1313" t="n">
-        <v>112</v>
+        <v>151</v>
       </c>
     </row>
     <row r="1314">
@@ -66459,7 +66455,7 @@
       </c>
       <c r="G1314" t="inlineStr">
         <is>
-          <t>Luan Batista</t>
+          <t>Gustavo Tonan</t>
         </is>
       </c>
       <c r="H1314" t="inlineStr">
@@ -66468,13 +66464,13 @@
         </is>
       </c>
       <c r="I1314" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="J1314" t="n">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="K1314" t="n">
-        <v>87</v>
+        <v>124</v>
       </c>
     </row>
     <row r="1315">
@@ -66510,7 +66506,7 @@
       </c>
       <c r="G1315" t="inlineStr">
         <is>
-          <t>Maria Garcia</t>
+          <t>Jonatan Hayashibara</t>
         </is>
       </c>
       <c r="H1315" t="inlineStr">
@@ -66519,13 +66515,13 @@
         </is>
       </c>
       <c r="I1315" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="J1315" t="n">
-        <v>57</v>
+        <v>515</v>
       </c>
       <c r="K1315" t="n">
-        <v>89</v>
+        <v>627</v>
       </c>
     </row>
     <row r="1316">
@@ -66561,7 +66557,7 @@
       </c>
       <c r="G1316" t="inlineStr">
         <is>
-          <t>Priscila Volpe</t>
+          <t>Lais Arruda</t>
         </is>
       </c>
       <c r="H1316" t="inlineStr">
@@ -66570,13 +66566,13 @@
         </is>
       </c>
       <c r="I1316" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J1316" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="K1316" t="n">
-        <v>11</v>
+        <v>118</v>
       </c>
     </row>
     <row r="1317">
@@ -66612,7 +66608,7 @@
       </c>
       <c r="G1317" t="inlineStr">
         <is>
-          <t>Rodrigo Souza</t>
+          <t>Luan Batista</t>
         </is>
       </c>
       <c r="H1317" t="inlineStr">
@@ -66621,13 +66617,13 @@
         </is>
       </c>
       <c r="I1317" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="J1317" t="n">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="K1317" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1318">
@@ -66663,7 +66659,7 @@
       </c>
       <c r="G1318" t="inlineStr">
         <is>
-          <t>Romario Silva</t>
+          <t>Maria Garcia</t>
         </is>
       </c>
       <c r="H1318" t="inlineStr">
@@ -66672,13 +66668,13 @@
         </is>
       </c>
       <c r="I1318" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J1318" t="n">
-        <v>111</v>
+        <v>60</v>
       </c>
       <c r="K1318" t="n">
-        <v>236</v>
+        <v>92</v>
       </c>
     </row>
     <row r="1319">
@@ -66714,7 +66710,7 @@
       </c>
       <c r="G1319" t="inlineStr">
         <is>
-          <t>Rosilene Santos</t>
+          <t>Priscila Volpe</t>
         </is>
       </c>
       <c r="H1319" t="inlineStr">
@@ -66723,13 +66719,13 @@
         </is>
       </c>
       <c r="I1319" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1319" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="K1319" t="n">
-        <v>81</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1320">
@@ -66765,7 +66761,7 @@
       </c>
       <c r="G1320" t="inlineStr">
         <is>
-          <t>Suede Gomes</t>
+          <t>Rodrigo Souza</t>
         </is>
       </c>
       <c r="H1320" t="inlineStr">
@@ -66774,13 +66770,13 @@
         </is>
       </c>
       <c r="I1320" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J1320" t="n">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="K1320" t="n">
-        <v>55</v>
+        <v>103</v>
       </c>
     </row>
     <row r="1321">
@@ -66816,7 +66812,7 @@
       </c>
       <c r="G1321" t="inlineStr">
         <is>
-          <t>Taina Silva</t>
+          <t>Romario Silva</t>
         </is>
       </c>
       <c r="H1321" t="inlineStr">
@@ -66825,13 +66821,13 @@
         </is>
       </c>
       <c r="I1321" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="J1321" t="n">
-        <v>51</v>
+        <v>136</v>
       </c>
       <c r="K1321" t="n">
-        <v>66</v>
+        <v>261</v>
       </c>
     </row>
     <row r="1322">
@@ -66867,7 +66863,7 @@
       </c>
       <c r="G1322" t="inlineStr">
         <is>
-          <t>Thayna Melo</t>
+          <t>Rosilene Santos</t>
         </is>
       </c>
       <c r="H1322" t="inlineStr">
@@ -66876,13 +66872,13 @@
         </is>
       </c>
       <c r="I1322" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J1322" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="K1322" t="n">
-        <v>58</v>
+        <v>82</v>
       </c>
     </row>
     <row r="1323">
@@ -66918,7 +66914,7 @@
       </c>
       <c r="G1323" t="inlineStr">
         <is>
-          <t>Vanessa Santana</t>
+          <t>Suede Gomes</t>
         </is>
       </c>
       <c r="H1323" t="inlineStr">
@@ -66927,13 +66923,13 @@
         </is>
       </c>
       <c r="I1323" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J1323" t="n">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="K1323" t="n">
-        <v>181</v>
+        <v>62</v>
       </c>
     </row>
     <row r="1324">
@@ -66964,27 +66960,27 @@
       </c>
       <c r="F1324" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="G1324" t="inlineStr">
         <is>
-          <t>Alaine Neres</t>
+          <t>Taina Silva</t>
         </is>
       </c>
       <c r="H1324" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
       <c r="I1324" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="J1324" t="n">
-        <v>112</v>
+        <v>53</v>
       </c>
       <c r="K1324" t="n">
-        <v>169</v>
+        <v>68</v>
       </c>
     </row>
     <row r="1325">
@@ -67015,27 +67011,27 @@
       </c>
       <c r="F1325" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="G1325" t="inlineStr">
         <is>
-          <t>Andre Silva</t>
+          <t>Thayna Melo</t>
         </is>
       </c>
       <c r="H1325" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
       <c r="I1325" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="J1325" t="n">
-        <v>17</v>
+        <v>59</v>
       </c>
       <c r="K1325" t="n">
-        <v>74</v>
+        <v>67</v>
       </c>
     </row>
     <row r="1326">
@@ -67066,27 +67062,27 @@
       </c>
       <c r="F1326" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="G1326" t="inlineStr">
         <is>
-          <t>Anna Ramalho</t>
+          <t>Vanessa Santana</t>
         </is>
       </c>
       <c r="H1326" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
       <c r="I1326" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J1326" t="n">
-        <v>26</v>
+        <v>68</v>
       </c>
       <c r="K1326" t="n">
-        <v>82</v>
+        <v>186</v>
       </c>
     </row>
     <row r="1327">
@@ -67122,22 +67118,22 @@
       </c>
       <c r="G1327" t="inlineStr">
         <is>
-          <t>Beatriz Ferreira</t>
+          <t>Alaine Neres</t>
         </is>
       </c>
       <c r="H1327" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I1327" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="J1327" t="n">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="K1327" t="n">
-        <v>142</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1328">
@@ -67173,7 +67169,7 @@
       </c>
       <c r="G1328" t="inlineStr">
         <is>
-          <t>Brenda Batista</t>
+          <t>Andre Silva</t>
         </is>
       </c>
       <c r="H1328" t="inlineStr">
@@ -67182,13 +67178,13 @@
         </is>
       </c>
       <c r="I1328" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J1328" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K1328" t="n">
-        <v>53</v>
+        <v>85</v>
       </c>
     </row>
     <row r="1329">
@@ -67224,22 +67220,22 @@
       </c>
       <c r="G1329" t="inlineStr">
         <is>
-          <t>Bruna Souza</t>
+          <t>Anna Ramalho</t>
         </is>
       </c>
       <c r="H1329" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="I1329" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J1329" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K1329" t="n">
-        <v>76</v>
+        <v>88</v>
       </c>
     </row>
     <row r="1330">
@@ -67275,22 +67271,22 @@
       </c>
       <c r="G1330" t="inlineStr">
         <is>
-          <t>Bruno Henrique</t>
+          <t>Beatriz Ferreira</t>
         </is>
       </c>
       <c r="H1330" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="I1330" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J1330" t="n">
-        <v>60</v>
+        <v>104</v>
       </c>
       <c r="K1330" t="n">
-        <v>130</v>
+        <v>143</v>
       </c>
     </row>
     <row r="1331">
@@ -67326,18 +67322,22 @@
       </c>
       <c r="G1331" t="inlineStr">
         <is>
-          <t>Claudineia Rodrigues</t>
-        </is>
-      </c>
-      <c r="H1331" t="inlineStr"/>
+          <t>Brenda Batista</t>
+        </is>
+      </c>
+      <c r="H1331" t="inlineStr">
+        <is>
+          <t>Larice Souza</t>
+        </is>
+      </c>
       <c r="I1331" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J1331" t="n">
-        <v>68</v>
+        <v>32</v>
       </c>
       <c r="K1331" t="n">
-        <v>186</v>
+        <v>56</v>
       </c>
     </row>
     <row r="1332">
@@ -67373,22 +67373,22 @@
       </c>
       <c r="G1332" t="inlineStr">
         <is>
-          <t>Cristina Leite</t>
+          <t>Bruna Souza</t>
         </is>
       </c>
       <c r="H1332" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I1332" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1332" t="n">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="K1332" t="n">
-        <v>150</v>
+        <v>78</v>
       </c>
     </row>
     <row r="1333">
@@ -67424,22 +67424,22 @@
       </c>
       <c r="G1333" t="inlineStr">
         <is>
-          <t>Davi Santos</t>
+          <t>Bruno Henrique</t>
         </is>
       </c>
       <c r="H1333" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I1333" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="J1333" t="n">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="K1333" t="n">
-        <v>94</v>
+        <v>140</v>
       </c>
     </row>
     <row r="1334">
@@ -67475,22 +67475,18 @@
       </c>
       <c r="G1334" t="inlineStr">
         <is>
-          <t>Deleia Oliveira</t>
-        </is>
-      </c>
-      <c r="H1334" t="inlineStr">
-        <is>
-          <t>Lorrane Santos</t>
-        </is>
-      </c>
+          <t>Claudineia Rodrigues</t>
+        </is>
+      </c>
+      <c r="H1334" t="inlineStr"/>
       <c r="I1334" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J1334" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="K1334" t="n">
-        <v>111</v>
+        <v>186</v>
       </c>
     </row>
     <row r="1335">
@@ -67526,22 +67522,22 @@
       </c>
       <c r="G1335" t="inlineStr">
         <is>
-          <t>Diego Pereira</t>
+          <t>Cristina Leite</t>
         </is>
       </c>
       <c r="H1335" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="I1335" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1335" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="K1335" t="n">
-        <v>97</v>
+        <v>151</v>
       </c>
     </row>
     <row r="1336">
@@ -67577,22 +67573,22 @@
       </c>
       <c r="G1336" t="inlineStr">
         <is>
-          <t>Eduardo Lopes</t>
+          <t>Davi Santos</t>
         </is>
       </c>
       <c r="H1336" t="inlineStr">
         <is>
-          <t>Idna Sousa</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I1336" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J1336" t="n">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="K1336" t="n">
-        <v>17</v>
+        <v>98</v>
       </c>
     </row>
     <row r="1337">
@@ -67628,7 +67624,7 @@
       </c>
       <c r="G1337" t="inlineStr">
         <is>
-          <t>Gislaine Lima</t>
+          <t>Deleia Oliveira</t>
         </is>
       </c>
       <c r="H1337" t="inlineStr">
@@ -67637,13 +67633,13 @@
         </is>
       </c>
       <c r="I1337" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="J1337" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="K1337" t="n">
-        <v>94</v>
+        <v>124</v>
       </c>
     </row>
     <row r="1338">
@@ -67679,22 +67675,22 @@
       </c>
       <c r="G1338" t="inlineStr">
         <is>
-          <t>Gustavo Santos</t>
+          <t>Diego Pereira</t>
         </is>
       </c>
       <c r="H1338" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I1338" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J1338" t="n">
-        <v>111</v>
+        <v>64</v>
       </c>
       <c r="K1338" t="n">
-        <v>219</v>
+        <v>108</v>
       </c>
     </row>
     <row r="1339">
@@ -67730,22 +67726,22 @@
       </c>
       <c r="G1339" t="inlineStr">
         <is>
-          <t>Igor Valezi</t>
+          <t>Eduardo Lopes</t>
         </is>
       </c>
       <c r="H1339" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Idna Sousa</t>
         </is>
       </c>
       <c r="I1339" t="n">
         <v>0</v>
       </c>
       <c r="J1339" t="n">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="K1339" t="n">
-        <v>101</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1340">
@@ -67781,22 +67777,22 @@
       </c>
       <c r="G1340" t="inlineStr">
         <is>
-          <t>Izabely Araujo</t>
+          <t>Gislaine Lima</t>
         </is>
       </c>
       <c r="H1340" t="inlineStr">
         <is>
-          <t>Idna Sousa</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I1340" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J1340" t="n">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="K1340" t="n">
-        <v>10</v>
+        <v>102</v>
       </c>
     </row>
     <row r="1341">
@@ -67832,22 +67828,22 @@
       </c>
       <c r="G1341" t="inlineStr">
         <is>
-          <t>Joanna Costa</t>
+          <t>Gustavo Santos</t>
         </is>
       </c>
       <c r="H1341" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="I1341" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J1341" t="n">
-        <v>14</v>
+        <v>114</v>
       </c>
       <c r="K1341" t="n">
-        <v>27</v>
+        <v>222</v>
       </c>
     </row>
     <row r="1342">
@@ -67883,7 +67879,7 @@
       </c>
       <c r="G1342" t="inlineStr">
         <is>
-          <t>Jose Natan</t>
+          <t>Igor Valezi</t>
         </is>
       </c>
       <c r="H1342" t="inlineStr">
@@ -67892,13 +67888,13 @@
         </is>
       </c>
       <c r="I1342" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J1342" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K1342" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="1343">
@@ -67934,22 +67930,22 @@
       </c>
       <c r="G1343" t="inlineStr">
         <is>
-          <t>João Oliveira</t>
+          <t>Izabely Araujo</t>
         </is>
       </c>
       <c r="H1343" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Idna Sousa</t>
         </is>
       </c>
       <c r="I1343" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="J1343" t="n">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="K1343" t="n">
-        <v>16</v>
+        <v>52</v>
       </c>
     </row>
     <row r="1344">
@@ -67985,7 +67981,7 @@
       </c>
       <c r="G1344" t="inlineStr">
         <is>
-          <t>Juan Ribeiro</t>
+          <t>Joanna Costa</t>
         </is>
       </c>
       <c r="H1344" t="inlineStr">
@@ -67994,13 +67990,13 @@
         </is>
       </c>
       <c r="I1344" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J1344" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="K1344" t="n">
-        <v>86</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1345">
@@ -68036,7 +68032,7 @@
       </c>
       <c r="G1345" t="inlineStr">
         <is>
-          <t>Juliana Valeria</t>
+          <t>Jose Natan</t>
         </is>
       </c>
       <c r="H1345" t="inlineStr">
@@ -68045,13 +68041,13 @@
         </is>
       </c>
       <c r="I1345" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J1345" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="K1345" t="n">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="1346">
@@ -68087,7 +68083,7 @@
       </c>
       <c r="G1346" t="inlineStr">
         <is>
-          <t>Juliane Vaz</t>
+          <t>João Oliveira</t>
         </is>
       </c>
       <c r="H1346" t="inlineStr">
@@ -68096,13 +68092,13 @@
         </is>
       </c>
       <c r="I1346" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="J1346" t="n">
-        <v>174</v>
+        <v>10</v>
       </c>
       <c r="K1346" t="n">
-        <v>274</v>
+        <v>18</v>
       </c>
     </row>
     <row r="1347">
@@ -68138,22 +68134,22 @@
       </c>
       <c r="G1347" t="inlineStr">
         <is>
-          <t>Katia Xavier</t>
+          <t>Juan Ribeiro</t>
         </is>
       </c>
       <c r="H1347" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I1347" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J1347" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="K1347" t="n">
-        <v>106</v>
+        <v>87</v>
       </c>
     </row>
     <row r="1348">
@@ -68189,22 +68185,22 @@
       </c>
       <c r="G1348" t="inlineStr">
         <is>
-          <t>Larissa Félix</t>
+          <t>Juliana Valeria</t>
         </is>
       </c>
       <c r="H1348" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I1348" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="J1348" t="n">
-        <v>147</v>
+        <v>47</v>
       </c>
       <c r="K1348" t="n">
-        <v>210</v>
+        <v>109</v>
       </c>
     </row>
     <row r="1349">
@@ -68240,22 +68236,22 @@
       </c>
       <c r="G1349" t="inlineStr">
         <is>
-          <t>Léia de Oliveira</t>
+          <t>Juliane Vaz</t>
         </is>
       </c>
       <c r="H1349" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I1349" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J1349" t="n">
-        <v>30</v>
+        <v>175</v>
       </c>
       <c r="K1349" t="n">
-        <v>117</v>
+        <v>275</v>
       </c>
     </row>
     <row r="1350">
@@ -68291,7 +68287,7 @@
       </c>
       <c r="G1350" t="inlineStr">
         <is>
-          <t>Maria Gualberto</t>
+          <t>Katia Xavier</t>
         </is>
       </c>
       <c r="H1350" t="inlineStr">
@@ -68300,13 +68296,13 @@
         </is>
       </c>
       <c r="I1350" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J1350" t="n">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="K1350" t="n">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
     <row r="1351">
@@ -68342,7 +68338,7 @@
       </c>
       <c r="G1351" t="inlineStr">
         <is>
-          <t>Nathany Silva</t>
+          <t>Larissa Félix</t>
         </is>
       </c>
       <c r="H1351" t="inlineStr">
@@ -68351,13 +68347,13 @@
         </is>
       </c>
       <c r="I1351" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="J1351" t="n">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="K1351" t="n">
-        <v>0</v>
+        <v>212</v>
       </c>
     </row>
     <row r="1352">
@@ -68393,22 +68389,22 @@
       </c>
       <c r="G1352" t="inlineStr">
         <is>
-          <t>Priscila Moreira</t>
+          <t>Léia de Oliveira</t>
         </is>
       </c>
       <c r="H1352" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I1352" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J1352" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="K1352" t="n">
-        <v>97</v>
+        <v>126</v>
       </c>
     </row>
     <row r="1353">
@@ -68444,22 +68440,22 @@
       </c>
       <c r="G1353" t="inlineStr">
         <is>
-          <t>Regiane Santos</t>
+          <t>Maria Gualberto</t>
         </is>
       </c>
       <c r="H1353" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I1353" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J1353" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="K1353" t="n">
-        <v>66</v>
+        <v>105</v>
       </c>
     </row>
     <row r="1354">
@@ -68495,22 +68491,22 @@
       </c>
       <c r="G1354" t="inlineStr">
         <is>
-          <t>Shofia Gomes</t>
+          <t>Nathany Silva</t>
         </is>
       </c>
       <c r="H1354" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I1354" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J1354" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="K1354" t="n">
-        <v>126</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1355">
@@ -68546,22 +68542,22 @@
       </c>
       <c r="G1355" t="inlineStr">
         <is>
-          <t>Vanessa Tavares</t>
+          <t>Priscila Moreira</t>
         </is>
       </c>
       <c r="H1355" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="I1355" t="n">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="J1355" t="n">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="K1355" t="n">
-        <v>89</v>
+        <v>135</v>
       </c>
     </row>
     <row r="1356">
@@ -68597,7 +68593,7 @@
       </c>
       <c r="G1356" t="inlineStr">
         <is>
-          <t>Willian Luz</t>
+          <t>Regiane Santos</t>
         </is>
       </c>
       <c r="H1356" t="inlineStr">
@@ -68606,13 +68602,13 @@
         </is>
       </c>
       <c r="I1356" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J1356" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="K1356" t="n">
-        <v>77</v>
+        <v>67</v>
       </c>
     </row>
     <row r="1357">
@@ -68648,22 +68644,22 @@
       </c>
       <c r="G1357" t="inlineStr">
         <is>
-          <t>Yasmim Oliveira</t>
+          <t>Shofia Gomes</t>
         </is>
       </c>
       <c r="H1357" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="I1357" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1357" t="n">
-        <v>7</v>
+        <v>46</v>
       </c>
       <c r="K1357" t="n">
-        <v>40</v>
+        <v>127</v>
       </c>
     </row>
     <row r="1358">
@@ -68694,23 +68690,27 @@
       </c>
       <c r="F1358" t="inlineStr">
         <is>
-          <t>ESCRITA FISCAL (Outsourcing)</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="G1358" t="inlineStr">
         <is>
-          <t>Claudineia Rodrigues</t>
-        </is>
-      </c>
-      <c r="H1358" t="inlineStr"/>
+          <t>Vanessa Tavares</t>
+        </is>
+      </c>
+      <c r="H1358" t="inlineStr">
+        <is>
+          <t>Larice Souza</t>
+        </is>
+      </c>
       <c r="I1358" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J1358" t="n">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="K1358" t="n">
-        <v>5</v>
+        <v>89</v>
       </c>
     </row>
     <row r="1359">
@@ -68741,27 +68741,27 @@
       </c>
       <c r="F1359" t="inlineStr">
         <is>
-          <t>ESCRITA FISCAL (Outsourcing)</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="G1359" t="inlineStr">
         <is>
-          <t>Diego Pereira</t>
+          <t>Willian Luz</t>
         </is>
       </c>
       <c r="H1359" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I1359" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1359" t="n">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="K1359" t="n">
-        <v>8</v>
+        <v>80</v>
       </c>
     </row>
     <row r="1360">
@@ -68792,27 +68792,27 @@
       </c>
       <c r="F1360" t="inlineStr">
         <is>
-          <t>ESCRITA FISCAL (Outsourcing)</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="G1360" t="inlineStr">
         <is>
-          <t>Gislaine Lima</t>
+          <t>Yasmim Oliveira</t>
         </is>
       </c>
       <c r="H1360" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I1360" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J1360" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K1360" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
     </row>
     <row r="1361">
@@ -68848,22 +68848,18 @@
       </c>
       <c r="G1361" t="inlineStr">
         <is>
-          <t>Joanna Costa</t>
-        </is>
-      </c>
-      <c r="H1361" t="inlineStr">
-        <is>
-          <t>Lorrane Santos</t>
-        </is>
-      </c>
+          <t>Claudineia Rodrigues</t>
+        </is>
+      </c>
+      <c r="H1361" t="inlineStr"/>
       <c r="I1361" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J1361" t="n">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="K1361" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1362">
@@ -68899,22 +68895,22 @@
       </c>
       <c r="G1362" t="inlineStr">
         <is>
-          <t>Jonatan Hayashibara</t>
+          <t>Diego Pereira</t>
         </is>
       </c>
       <c r="H1362" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I1362" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1362" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K1362" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1363">
@@ -68950,22 +68946,22 @@
       </c>
       <c r="G1363" t="inlineStr">
         <is>
-          <t>João Oliveira</t>
+          <t>Gislaine Lima</t>
         </is>
       </c>
       <c r="H1363" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I1363" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1363" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K1363" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1364">
@@ -69001,22 +68997,22 @@
       </c>
       <c r="G1364" t="inlineStr">
         <is>
-          <t>Regiane Santos</t>
+          <t>Joanna Costa</t>
         </is>
       </c>
       <c r="H1364" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I1364" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J1364" t="n">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="K1364" t="n">
-        <v>18</v>
+        <v>60</v>
       </c>
     </row>
     <row r="1365">
@@ -69052,22 +69048,22 @@
       </c>
       <c r="G1365" t="inlineStr">
         <is>
-          <t>Yasmim Oliveira</t>
+          <t>Jonatan Hayashibara</t>
         </is>
       </c>
       <c r="H1365" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
       <c r="I1365" t="n">
         <v>0</v>
       </c>
       <c r="J1365" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K1365" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1366">
@@ -69098,23 +69094,27 @@
       </c>
       <c r="F1366" t="inlineStr">
         <is>
-          <t>FIN - CONTÁBIL</t>
+          <t>ESCRITA FISCAL (Outsourcing)</t>
         </is>
       </c>
       <c r="G1366" t="inlineStr">
         <is>
-          <t>Daniele Faria</t>
-        </is>
-      </c>
-      <c r="H1366" t="inlineStr"/>
+          <t>João Oliveira</t>
+        </is>
+      </c>
+      <c r="H1366" t="inlineStr">
+        <is>
+          <t>Larice Souza</t>
+        </is>
+      </c>
       <c r="I1366" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J1366" t="n">
         <v>20</v>
       </c>
       <c r="K1366" t="n">
-        <v>62</v>
+        <v>51</v>
       </c>
     </row>
     <row r="1367">
@@ -69145,23 +69145,27 @@
       </c>
       <c r="F1367" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>ESCRITA FISCAL (Outsourcing)</t>
         </is>
       </c>
       <c r="G1367" t="inlineStr">
         <is>
-          <t>Ana Santana</t>
-        </is>
-      </c>
-      <c r="H1367" t="inlineStr"/>
+          <t>Regiane Santos</t>
+        </is>
+      </c>
+      <c r="H1367" t="inlineStr">
+        <is>
+          <t>Larice Souza</t>
+        </is>
+      </c>
       <c r="I1367" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J1367" t="n">
-        <v>384</v>
+        <v>8</v>
       </c>
       <c r="K1367" t="n">
-        <v>587</v>
+        <v>18</v>
       </c>
     </row>
     <row r="1368">
@@ -69192,23 +69196,27 @@
       </c>
       <c r="F1368" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>ESCRITA FISCAL (Outsourcing)</t>
         </is>
       </c>
       <c r="G1368" t="inlineStr">
         <is>
-          <t>Andre Coelho</t>
-        </is>
-      </c>
-      <c r="H1368" t="inlineStr"/>
+          <t>Yasmim Oliveira</t>
+        </is>
+      </c>
+      <c r="H1368" t="inlineStr">
+        <is>
+          <t>Larice Souza</t>
+        </is>
+      </c>
       <c r="I1368" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1368" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="K1368" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1369">
@@ -69239,23 +69247,23 @@
       </c>
       <c r="F1369" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>FIN - CONTÁBIL</t>
         </is>
       </c>
       <c r="G1369" t="inlineStr">
         <is>
-          <t>Bianca Castro</t>
+          <t>Daniele Faria</t>
         </is>
       </c>
       <c r="H1369" t="inlineStr"/>
       <c r="I1369" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J1369" t="n">
-        <v>265</v>
+        <v>20</v>
       </c>
       <c r="K1369" t="n">
-        <v>459</v>
+        <v>62</v>
       </c>
     </row>
     <row r="1370">
@@ -69291,18 +69299,18 @@
       </c>
       <c r="G1370" t="inlineStr">
         <is>
-          <t>Bruna Costa</t>
+          <t>Ana Santana</t>
         </is>
       </c>
       <c r="H1370" t="inlineStr"/>
       <c r="I1370" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1370" t="n">
-        <v>33</v>
+        <v>384</v>
       </c>
       <c r="K1370" t="n">
-        <v>34</v>
+        <v>587</v>
       </c>
     </row>
     <row r="1371">
@@ -69338,7 +69346,7 @@
       </c>
       <c r="G1371" t="inlineStr">
         <is>
-          <t>Daniela Silva</t>
+          <t>Andre Coelho</t>
         </is>
       </c>
       <c r="H1371" t="inlineStr"/>
@@ -69346,10 +69354,10 @@
         <v>0</v>
       </c>
       <c r="J1371" t="n">
-        <v>306</v>
+        <v>12</v>
       </c>
       <c r="K1371" t="n">
-        <v>302</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1372">
@@ -69385,18 +69393,18 @@
       </c>
       <c r="G1372" t="inlineStr">
         <is>
-          <t>Isabelli Afonso</t>
+          <t>Bianca Castro</t>
         </is>
       </c>
       <c r="H1372" t="inlineStr"/>
       <c r="I1372" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J1372" t="n">
-        <v>217</v>
+        <v>265</v>
       </c>
       <c r="K1372" t="n">
-        <v>234</v>
+        <v>459</v>
       </c>
     </row>
     <row r="1373">
@@ -69432,18 +69440,18 @@
       </c>
       <c r="G1373" t="inlineStr">
         <is>
-          <t>Jurema Damacena - SAC</t>
+          <t>Bruna Costa</t>
         </is>
       </c>
       <c r="H1373" t="inlineStr"/>
       <c r="I1373" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1373" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="K1373" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
     </row>
     <row r="1374">
@@ -69479,7 +69487,7 @@
       </c>
       <c r="G1374" t="inlineStr">
         <is>
-          <t>Leticia Queiroz</t>
+          <t>Daniela Silva</t>
         </is>
       </c>
       <c r="H1374" t="inlineStr"/>
@@ -69487,10 +69495,10 @@
         <v>0</v>
       </c>
       <c r="J1374" t="n">
-        <v>424</v>
+        <v>306</v>
       </c>
       <c r="K1374" t="n">
-        <v>428</v>
+        <v>302</v>
       </c>
     </row>
     <row r="1375">
@@ -69526,18 +69534,18 @@
       </c>
       <c r="G1375" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Isabelli Afonso</t>
         </is>
       </c>
       <c r="H1375" t="inlineStr"/>
       <c r="I1375" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J1375" t="n">
-        <v>2</v>
+        <v>217</v>
       </c>
       <c r="K1375" t="n">
-        <v>13</v>
+        <v>234</v>
       </c>
     </row>
     <row r="1376">
@@ -69573,7 +69581,7 @@
       </c>
       <c r="G1376" t="inlineStr">
         <is>
-          <t>Victoria Virgens</t>
+          <t>Jurema Damacena - SAC</t>
         </is>
       </c>
       <c r="H1376" t="inlineStr"/>
@@ -69581,10 +69589,10 @@
         <v>0</v>
       </c>
       <c r="J1376" t="n">
-        <v>308</v>
+        <v>0</v>
       </c>
       <c r="K1376" t="n">
-        <v>308</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1377">
@@ -69620,7 +69628,7 @@
       </c>
       <c r="G1377" t="inlineStr">
         <is>
-          <t>Yasmin Peixoto</t>
+          <t>Leticia Queiroz</t>
         </is>
       </c>
       <c r="H1377" t="inlineStr"/>
@@ -69628,10 +69636,10 @@
         <v>0</v>
       </c>
       <c r="J1377" t="n">
-        <v>354</v>
+        <v>424</v>
       </c>
       <c r="K1377" t="n">
-        <v>551</v>
+        <v>428</v>
       </c>
     </row>
     <row r="1378">
@@ -69662,12 +69670,12 @@
       </c>
       <c r="F1378" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="G1378" t="inlineStr">
         <is>
-          <t>Andre Coelho</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="H1378" t="inlineStr"/>
@@ -69675,10 +69683,10 @@
         <v>0</v>
       </c>
       <c r="J1378" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K1378" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1379">
@@ -69709,23 +69717,23 @@
       </c>
       <c r="F1379" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="G1379" t="inlineStr">
         <is>
-          <t>Beatriz Rangel</t>
+          <t>Victoria Virgens</t>
         </is>
       </c>
       <c r="H1379" t="inlineStr"/>
       <c r="I1379" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J1379" t="n">
-        <v>222</v>
+        <v>308</v>
       </c>
       <c r="K1379" t="n">
-        <v>372</v>
+        <v>308</v>
       </c>
     </row>
     <row r="1380">
@@ -69756,12 +69764,12 @@
       </c>
       <c r="F1380" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="G1380" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
+          <t>Yasmin Peixoto</t>
         </is>
       </c>
       <c r="H1380" t="inlineStr"/>
@@ -69769,10 +69777,10 @@
         <v>0</v>
       </c>
       <c r="J1380" t="n">
-        <v>429</v>
+        <v>354</v>
       </c>
       <c r="K1380" t="n">
-        <v>434</v>
+        <v>551</v>
       </c>
     </row>
     <row r="1381">
@@ -69808,7 +69816,7 @@
       </c>
       <c r="G1381" t="inlineStr">
         <is>
-          <t>Cristiane Simões</t>
+          <t>Andre Coelho</t>
         </is>
       </c>
       <c r="H1381" t="inlineStr"/>
@@ -69816,10 +69824,10 @@
         <v>0</v>
       </c>
       <c r="J1381" t="n">
-        <v>271</v>
+        <v>4</v>
       </c>
       <c r="K1381" t="n">
-        <v>306</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1382">
@@ -69855,18 +69863,18 @@
       </c>
       <c r="G1382" t="inlineStr">
         <is>
-          <t>Daniel Oliveira</t>
+          <t>Beatriz Rangel</t>
         </is>
       </c>
       <c r="H1382" t="inlineStr"/>
       <c r="I1382" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="J1382" t="n">
-        <v>353</v>
+        <v>222</v>
       </c>
       <c r="K1382" t="n">
-        <v>403</v>
+        <v>371</v>
       </c>
     </row>
     <row r="1383">
@@ -69902,7 +69910,7 @@
       </c>
       <c r="G1383" t="inlineStr">
         <is>
-          <t>Diego Lima</t>
+          <t>Bruno Contieri</t>
         </is>
       </c>
       <c r="H1383" t="inlineStr"/>
@@ -69910,10 +69918,10 @@
         <v>0</v>
       </c>
       <c r="J1383" t="n">
-        <v>172</v>
+        <v>428</v>
       </c>
       <c r="K1383" t="n">
-        <v>164</v>
+        <v>434</v>
       </c>
     </row>
     <row r="1384">
@@ -69949,7 +69957,7 @@
       </c>
       <c r="G1384" t="inlineStr">
         <is>
-          <t>Eduardo Aparicio</t>
+          <t>Cristiane Simões</t>
         </is>
       </c>
       <c r="H1384" t="inlineStr"/>
@@ -69957,10 +69965,10 @@
         <v>0</v>
       </c>
       <c r="J1384" t="n">
-        <v>1</v>
+        <v>271</v>
       </c>
       <c r="K1384" t="n">
-        <v>1</v>
+        <v>305</v>
       </c>
     </row>
     <row r="1385">
@@ -69996,18 +70004,18 @@
       </c>
       <c r="G1385" t="inlineStr">
         <is>
-          <t>Karine Gusmão</t>
+          <t>Daniel Oliveira</t>
         </is>
       </c>
       <c r="H1385" t="inlineStr"/>
       <c r="I1385" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J1385" t="n">
-        <v>112</v>
+        <v>353</v>
       </c>
       <c r="K1385" t="n">
-        <v>93</v>
+        <v>403</v>
       </c>
     </row>
     <row r="1386">
@@ -70043,18 +70051,18 @@
       </c>
       <c r="G1386" t="inlineStr">
         <is>
-          <t>Luiz Ferreira</t>
+          <t>Diego Lima</t>
         </is>
       </c>
       <c r="H1386" t="inlineStr"/>
       <c r="I1386" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J1386" t="n">
-        <v>18</v>
+        <v>174</v>
       </c>
       <c r="K1386" t="n">
-        <v>17</v>
+        <v>164</v>
       </c>
     </row>
     <row r="1387">
@@ -70090,7 +70098,7 @@
       </c>
       <c r="G1387" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Eduardo Aparicio</t>
         </is>
       </c>
       <c r="H1387" t="inlineStr"/>
@@ -70098,10 +70106,10 @@
         <v>0</v>
       </c>
       <c r="J1387" t="n">
-        <v>210</v>
+        <v>1</v>
       </c>
       <c r="K1387" t="n">
-        <v>221</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1388">
@@ -70137,18 +70145,18 @@
       </c>
       <c r="G1388" t="inlineStr">
         <is>
-          <t>Rodrigo Rego</t>
+          <t>Karine Gusmão</t>
         </is>
       </c>
       <c r="H1388" t="inlineStr"/>
       <c r="I1388" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J1388" t="n">
-        <v>420</v>
+        <v>112</v>
       </c>
       <c r="K1388" t="n">
-        <v>460</v>
+        <v>93</v>
       </c>
     </row>
     <row r="1389">
@@ -70184,7 +70192,7 @@
       </c>
       <c r="G1389" t="inlineStr">
         <is>
-          <t>Rogerio Egidio</t>
+          <t>Luiz Ferreira</t>
         </is>
       </c>
       <c r="H1389" t="inlineStr"/>
@@ -70192,10 +70200,10 @@
         <v>0</v>
       </c>
       <c r="J1389" t="n">
-        <v>335</v>
+        <v>18</v>
       </c>
       <c r="K1389" t="n">
-        <v>384</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1390">
@@ -70231,18 +70239,18 @@
       </c>
       <c r="G1390" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="H1390" t="inlineStr"/>
       <c r="I1390" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1390" t="n">
-        <v>33</v>
+        <v>210</v>
       </c>
       <c r="K1390" t="n">
-        <v>50</v>
+        <v>221</v>
       </c>
     </row>
     <row r="1391">
@@ -70278,18 +70286,18 @@
       </c>
       <c r="G1391" t="inlineStr">
         <is>
-          <t>Simone Marques</t>
+          <t>Rodrigo Rego</t>
         </is>
       </c>
       <c r="H1391" t="inlineStr"/>
       <c r="I1391" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J1391" t="n">
-        <v>197</v>
+        <v>420</v>
       </c>
       <c r="K1391" t="n">
-        <v>227</v>
+        <v>460</v>
       </c>
     </row>
     <row r="1392">
@@ -70325,7 +70333,7 @@
       </c>
       <c r="G1392" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Rogerio Egidio</t>
         </is>
       </c>
       <c r="H1392" t="inlineStr"/>
@@ -70333,10 +70341,10 @@
         <v>0</v>
       </c>
       <c r="J1392" t="n">
-        <v>214</v>
+        <v>335</v>
       </c>
       <c r="K1392" t="n">
-        <v>267</v>
+        <v>382</v>
       </c>
     </row>
     <row r="1393">
@@ -70367,12 +70375,12 @@
       </c>
       <c r="F1393" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="G1393" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="H1393" t="inlineStr"/>
@@ -70380,10 +70388,10 @@
         <v>0</v>
       </c>
       <c r="J1393" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="K1393" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1394">
@@ -70414,23 +70422,23 @@
       </c>
       <c r="F1394" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="G1394" t="inlineStr">
         <is>
-          <t>Jurema Damacena - SAC</t>
+          <t>Simone Marques</t>
         </is>
       </c>
       <c r="H1394" t="inlineStr"/>
       <c r="I1394" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J1394" t="n">
-        <v>35</v>
+        <v>197</v>
       </c>
       <c r="K1394" t="n">
-        <v>49</v>
+        <v>228</v>
       </c>
     </row>
     <row r="1395">
@@ -70461,12 +70469,12 @@
       </c>
       <c r="F1395" t="inlineStr">
         <is>
-          <t>MG CONTABIFÁCIL - CTB</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="G1395" t="inlineStr">
         <is>
-          <t>Guilherme Delecrodio</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="H1395" t="inlineStr"/>
@@ -70474,10 +70482,10 @@
         <v>0</v>
       </c>
       <c r="J1395" t="n">
-        <v>1</v>
+        <v>214</v>
       </c>
       <c r="K1395" t="n">
-        <v>1</v>
+        <v>267</v>
       </c>
     </row>
     <row r="1396">
@@ -70508,12 +70516,12 @@
       </c>
       <c r="F1396" t="inlineStr">
         <is>
-          <t>S.A.C</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="G1396" t="inlineStr">
         <is>
-          <t>Ana Celia - SAC</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="H1396" t="inlineStr"/>
@@ -70521,7 +70529,7 @@
         <v>0</v>
       </c>
       <c r="J1396" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1396" t="n">
         <v>1</v>
@@ -70555,27 +70563,23 @@
       </c>
       <c r="F1397" t="inlineStr">
         <is>
-          <t>SANTOS - DP</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="G1397" t="inlineStr">
         <is>
-          <t>Katia Valeria</t>
-        </is>
-      </c>
-      <c r="H1397" t="inlineStr">
-        <is>
-          <t>Katia Valeria</t>
-        </is>
-      </c>
+          <t>Jurema Damacena - SAC</t>
+        </is>
+      </c>
+      <c r="H1397" t="inlineStr"/>
       <c r="I1397" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J1397" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="K1397" t="n">
-        <v>3</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1398">
@@ -70601,28 +70605,28 @@
       </c>
       <c r="E1398" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F1398" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>MG CONTABIFÁCIL - CTB</t>
         </is>
       </c>
       <c r="G1398" t="inlineStr">
         <is>
-          <t>Jurema Damacena - SAC</t>
+          <t>Guilherme Delecrodio</t>
         </is>
       </c>
       <c r="H1398" t="inlineStr"/>
       <c r="I1398" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1398" t="n">
         <v>1</v>
       </c>
-      <c r="J1398" t="n">
-        <v>7</v>
-      </c>
       <c r="K1398" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1399">
@@ -70648,28 +70652,28 @@
       </c>
       <c r="E1399" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F1399" t="inlineStr">
         <is>
-          <t>SANTOS - ADM</t>
+          <t>S.A.C</t>
         </is>
       </c>
       <c r="G1399" t="inlineStr">
         <is>
-          <t>Kauany Pereira</t>
+          <t>Ana Celia - SAC</t>
         </is>
       </c>
       <c r="H1399" t="inlineStr"/>
       <c r="I1399" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J1399" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="K1399" t="n">
-        <v>138</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1400">
@@ -70695,32 +70699,32 @@
       </c>
       <c r="E1400" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F1400" t="inlineStr">
         <is>
-          <t>SANTOS - CTB</t>
+          <t>SANTOS - DP</t>
         </is>
       </c>
       <c r="G1400" t="inlineStr">
         <is>
-          <t>Ivia Oliveira</t>
+          <t>Katia Valeria</t>
         </is>
       </c>
       <c r="H1400" t="inlineStr">
         <is>
-          <t>Roberto Silva</t>
+          <t>Katia Valeria</t>
         </is>
       </c>
       <c r="I1400" t="n">
         <v>0</v>
       </c>
       <c r="J1400" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="K1400" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1401">
@@ -70751,27 +70755,23 @@
       </c>
       <c r="F1401" t="inlineStr">
         <is>
-          <t>SANTOS - CTB</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="G1401" t="inlineStr">
         <is>
-          <t>Nata Trindade</t>
-        </is>
-      </c>
-      <c r="H1401" t="inlineStr">
-        <is>
-          <t>Roberto Silva</t>
-        </is>
-      </c>
+          <t>Jurema Damacena - SAC</t>
+        </is>
+      </c>
+      <c r="H1401" t="inlineStr"/>
       <c r="I1401" t="n">
         <v>1</v>
       </c>
       <c r="J1401" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="K1401" t="n">
-        <v>41</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1402">
@@ -70802,27 +70802,23 @@
       </c>
       <c r="F1402" t="inlineStr">
         <is>
-          <t>SANTOS - CTB</t>
+          <t>SANTOS - ADM</t>
         </is>
       </c>
       <c r="G1402" t="inlineStr">
         <is>
-          <t>Roberto Silva</t>
-        </is>
-      </c>
-      <c r="H1402" t="inlineStr">
-        <is>
-          <t>Roberto Silva</t>
-        </is>
-      </c>
+          <t>Kauany Pereira</t>
+        </is>
+      </c>
+      <c r="H1402" t="inlineStr"/>
       <c r="I1402" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J1402" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="K1402" t="n">
-        <v>42</v>
+        <v>138</v>
       </c>
     </row>
     <row r="1403">
@@ -70858,7 +70854,7 @@
       </c>
       <c r="G1403" t="inlineStr">
         <is>
-          <t>Thaina Rodrigues</t>
+          <t>Ivia Oliveira</t>
         </is>
       </c>
       <c r="H1403" t="inlineStr">
@@ -70867,13 +70863,13 @@
         </is>
       </c>
       <c r="I1403" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J1403" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="K1403" t="n">
-        <v>49</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1404">
@@ -70904,27 +70900,27 @@
       </c>
       <c r="F1404" t="inlineStr">
         <is>
-          <t>SANTOS - DP</t>
+          <t>SANTOS - CTB</t>
         </is>
       </c>
       <c r="G1404" t="inlineStr">
         <is>
-          <t>Bruna Silva</t>
+          <t>Nata Trindade</t>
         </is>
       </c>
       <c r="H1404" t="inlineStr">
         <is>
-          <t>Katia Valeria</t>
+          <t>Roberto Silva</t>
         </is>
       </c>
       <c r="I1404" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1404" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="K1404" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1405">
@@ -70955,27 +70951,27 @@
       </c>
       <c r="F1405" t="inlineStr">
         <is>
-          <t>SANTOS - DP</t>
+          <t>SANTOS - CTB</t>
         </is>
       </c>
       <c r="G1405" t="inlineStr">
         <is>
-          <t>Carliane Silva</t>
+          <t>Roberto Silva</t>
         </is>
       </c>
       <c r="H1405" t="inlineStr">
         <is>
-          <t>Katia Valeria</t>
+          <t>Roberto Silva</t>
         </is>
       </c>
       <c r="I1405" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J1405" t="n">
-        <v>131</v>
+        <v>8</v>
       </c>
       <c r="K1405" t="n">
-        <v>284</v>
+        <v>43</v>
       </c>
     </row>
     <row r="1406">
@@ -71006,27 +71002,27 @@
       </c>
       <c r="F1406" t="inlineStr">
         <is>
-          <t>SANTOS - DP</t>
+          <t>SANTOS - CTB</t>
         </is>
       </c>
       <c r="G1406" t="inlineStr">
         <is>
-          <t>Cintia Andrade</t>
+          <t>Thaina Rodrigues</t>
         </is>
       </c>
       <c r="H1406" t="inlineStr">
         <is>
-          <t>Katia Valeria</t>
+          <t>Roberto Silva</t>
         </is>
       </c>
       <c r="I1406" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1406" t="n">
-        <v>103</v>
+        <v>25</v>
       </c>
       <c r="K1406" t="n">
-        <v>207</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1407">
@@ -71062,22 +71058,22 @@
       </c>
       <c r="G1407" t="inlineStr">
         <is>
+          <t>Bruna Silva</t>
+        </is>
+      </c>
+      <c r="H1407" t="inlineStr">
+        <is>
           <t>Katia Valeria</t>
         </is>
       </c>
-      <c r="H1407" t="inlineStr">
-        <is>
-          <t>Katia Valeria</t>
-        </is>
-      </c>
       <c r="I1407" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J1407" t="n">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="K1407" t="n">
-        <v>337</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1408">
@@ -71108,27 +71104,27 @@
       </c>
       <c r="F1408" t="inlineStr">
         <is>
-          <t>SANTOS - EF</t>
+          <t>SANTOS - DP</t>
         </is>
       </c>
       <c r="G1408" t="inlineStr">
         <is>
-          <t>Jasmina Melo</t>
+          <t>Carliane Silva</t>
         </is>
       </c>
       <c r="H1408" t="inlineStr">
         <is>
-          <t>Lidia Tavares</t>
+          <t>Katia Valeria</t>
         </is>
       </c>
       <c r="I1408" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="J1408" t="n">
-        <v>41</v>
+        <v>132</v>
       </c>
       <c r="K1408" t="n">
-        <v>65</v>
+        <v>285</v>
       </c>
     </row>
     <row r="1409">
@@ -71159,27 +71155,27 @@
       </c>
       <c r="F1409" t="inlineStr">
         <is>
-          <t>SANTOS - EF</t>
+          <t>SANTOS - DP</t>
         </is>
       </c>
       <c r="G1409" t="inlineStr">
         <is>
-          <t>Karen Saadi</t>
+          <t>Cintia Andrade</t>
         </is>
       </c>
       <c r="H1409" t="inlineStr">
         <is>
-          <t>Lidia Tavares</t>
+          <t>Katia Valeria</t>
         </is>
       </c>
       <c r="I1409" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J1409" t="n">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="K1409" t="n">
-        <v>77</v>
+        <v>207</v>
       </c>
     </row>
     <row r="1410">
@@ -71210,27 +71206,27 @@
       </c>
       <c r="F1410" t="inlineStr">
         <is>
-          <t>SANTOS - EF</t>
+          <t>SANTOS - DP</t>
         </is>
       </c>
       <c r="G1410" t="inlineStr">
         <is>
-          <t>Luckas Andrade</t>
+          <t>Katia Valeria</t>
         </is>
       </c>
       <c r="H1410" t="inlineStr">
         <is>
-          <t>Lidia Tavares</t>
+          <t>Katia Valeria</t>
         </is>
       </c>
       <c r="I1410" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="J1410" t="n">
-        <v>66</v>
+        <v>166</v>
       </c>
       <c r="K1410" t="n">
-        <v>104</v>
+        <v>346</v>
       </c>
     </row>
     <row r="1411">
@@ -71266,7 +71262,7 @@
       </c>
       <c r="G1411" t="inlineStr">
         <is>
-          <t>Mirian Rodrigues</t>
+          <t>Jasmina Melo</t>
         </is>
       </c>
       <c r="H1411" t="inlineStr">
@@ -71275,13 +71271,13 @@
         </is>
       </c>
       <c r="I1411" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="J1411" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="K1411" t="n">
-        <v>93</v>
+        <v>78</v>
       </c>
     </row>
     <row r="1412">
@@ -71312,22 +71308,175 @@
       </c>
       <c r="F1412" t="inlineStr">
         <is>
+          <t>SANTOS - EF</t>
+        </is>
+      </c>
+      <c r="G1412" t="inlineStr">
+        <is>
+          <t>Karen Saadi</t>
+        </is>
+      </c>
+      <c r="H1412" t="inlineStr">
+        <is>
+          <t>Lidia Tavares</t>
+        </is>
+      </c>
+      <c r="I1412" t="n">
+        <v>18</v>
+      </c>
+      <c r="J1412" t="n">
+        <v>43</v>
+      </c>
+      <c r="K1412" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="1413">
+      <c r="A1413" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B1413" t="inlineStr">
+        <is>
+          <t>Sexta</t>
+        </is>
+      </c>
+      <c r="C1413" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D1413" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1413" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="F1413" t="inlineStr">
+        <is>
+          <t>SANTOS - EF</t>
+        </is>
+      </c>
+      <c r="G1413" t="inlineStr">
+        <is>
+          <t>Luckas Andrade</t>
+        </is>
+      </c>
+      <c r="H1413" t="inlineStr">
+        <is>
+          <t>Lidia Tavares</t>
+        </is>
+      </c>
+      <c r="I1413" t="n">
+        <v>35</v>
+      </c>
+      <c r="J1413" t="n">
+        <v>71</v>
+      </c>
+      <c r="K1413" t="n">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="1414">
+      <c r="A1414" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B1414" t="inlineStr">
+        <is>
+          <t>Sexta</t>
+        </is>
+      </c>
+      <c r="C1414" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D1414" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1414" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="F1414" t="inlineStr">
+        <is>
+          <t>SANTOS - EF</t>
+        </is>
+      </c>
+      <c r="G1414" t="inlineStr">
+        <is>
+          <t>Mirian Rodrigues</t>
+        </is>
+      </c>
+      <c r="H1414" t="inlineStr">
+        <is>
+          <t>Lidia Tavares</t>
+        </is>
+      </c>
+      <c r="I1414" t="n">
+        <v>23</v>
+      </c>
+      <c r="J1414" t="n">
+        <v>50</v>
+      </c>
+      <c r="K1414" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="1415">
+      <c r="A1415" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B1415" t="inlineStr">
+        <is>
+          <t>Sexta</t>
+        </is>
+      </c>
+      <c r="C1415" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D1415" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1415" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="F1415" t="inlineStr">
+        <is>
           <t>SANTOS - GC</t>
         </is>
       </c>
-      <c r="G1412" t="inlineStr">
+      <c r="G1415" t="inlineStr">
         <is>
           <t>Rafaella Massuia</t>
         </is>
       </c>
-      <c r="H1412" t="inlineStr"/>
-      <c r="I1412" t="n">
+      <c r="H1415" t="inlineStr"/>
+      <c r="I1415" t="n">
         <v>2</v>
       </c>
-      <c r="J1412" t="n">
+      <c r="J1415" t="n">
         <v>1</v>
       </c>
-      <c r="K1412" t="n">
+      <c r="K1415" t="n">
         <v>109</v>
       </c>
     </row>

--- a/data/historico/historico_baixas.xlsx
+++ b/data/historico/historico_baixas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1415"/>
+  <dimension ref="A1:K1416"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -56968,13 +56968,13 @@
         </is>
       </c>
       <c r="I1126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1126" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1127">
@@ -57172,13 +57172,13 @@
         </is>
       </c>
       <c r="I1130" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J1130" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="K1130" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1131">
@@ -57274,13 +57274,13 @@
         </is>
       </c>
       <c r="I1132" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1132" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K1132" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="1133">
@@ -57525,13 +57525,13 @@
         </is>
       </c>
       <c r="I1137" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1137" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1137" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1138">
@@ -57776,13 +57776,13 @@
         </is>
       </c>
       <c r="I1142" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J1142" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="K1142" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="1143">
@@ -58207,13 +58207,13 @@
         </is>
       </c>
       <c r="I1151" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J1151" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K1151" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="1152">
@@ -58819,13 +58819,13 @@
         </is>
       </c>
       <c r="I1163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1163" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K1163" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1164">
@@ -59984,13 +59984,13 @@
         </is>
       </c>
       <c r="I1186" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="J1186" t="n">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="K1186" t="n">
-        <v>169</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1187">
@@ -60035,13 +60035,13 @@
         </is>
       </c>
       <c r="I1187" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="J1187" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="K1187" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="1188">
@@ -60086,13 +60086,13 @@
         </is>
       </c>
       <c r="I1188" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="J1188" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="K1188" t="n">
-        <v>129</v>
+        <v>139</v>
       </c>
     </row>
     <row r="1189">
@@ -60137,13 +60137,13 @@
         </is>
       </c>
       <c r="I1189" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J1189" t="n">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="K1189" t="n">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="1190">
@@ -60188,13 +60188,13 @@
         </is>
       </c>
       <c r="I1190" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="J1190" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K1190" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="1191">
@@ -60239,13 +60239,13 @@
         </is>
       </c>
       <c r="I1191" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J1191" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K1191" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="1192">
@@ -60392,13 +60392,13 @@
         </is>
       </c>
       <c r="I1194" t="n">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="J1194" t="n">
-        <v>91</v>
+        <v>162</v>
       </c>
       <c r="K1194" t="n">
-        <v>133</v>
+        <v>204</v>
       </c>
     </row>
     <row r="1195">
@@ -60494,13 +60494,13 @@
         </is>
       </c>
       <c r="I1196" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J1196" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K1196" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="1197">
@@ -60545,13 +60545,13 @@
         </is>
       </c>
       <c r="I1197" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J1197" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K1197" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="1198">
@@ -60596,13 +60596,13 @@
         </is>
       </c>
       <c r="I1198" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="J1198" t="n">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="K1198" t="n">
-        <v>187</v>
+        <v>194</v>
       </c>
     </row>
     <row r="1199">
@@ -60643,7 +60643,7 @@
       </c>
       <c r="H1199" t="inlineStr"/>
       <c r="I1199" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1199" t="n">
         <v>70</v>
@@ -61337,13 +61337,13 @@
         </is>
       </c>
       <c r="I1213" t="n">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="J1213" t="n">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="K1213" t="n">
-        <v>104</v>
+        <v>120</v>
       </c>
     </row>
     <row r="1214">
@@ -61690,13 +61690,13 @@
         </is>
       </c>
       <c r="I1220" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="J1220" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K1220" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="1221">
@@ -62043,13 +62043,13 @@
         </is>
       </c>
       <c r="I1227" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J1227" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K1227" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="1228">
@@ -62094,13 +62094,13 @@
         </is>
       </c>
       <c r="I1228" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J1228" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K1228" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="1229">
@@ -62145,13 +62145,13 @@
         </is>
       </c>
       <c r="I1229" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="J1229" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="K1229" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
     </row>
     <row r="1230">
@@ -62196,13 +62196,13 @@
         </is>
       </c>
       <c r="I1230" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="J1230" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="K1230" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1231">
@@ -62349,13 +62349,13 @@
         </is>
       </c>
       <c r="I1233" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J1233" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K1233" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="1234">
@@ -62400,13 +62400,13 @@
         </is>
       </c>
       <c r="I1234" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1234" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1234" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1235">
@@ -62451,13 +62451,13 @@
         </is>
       </c>
       <c r="I1235" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J1235" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K1235" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1236">
@@ -63165,13 +63165,13 @@
         </is>
       </c>
       <c r="I1249" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="J1249" t="n">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="K1249" t="n">
-        <v>28</v>
+        <v>54</v>
       </c>
     </row>
     <row r="1250">
@@ -63267,13 +63267,13 @@
         </is>
       </c>
       <c r="I1251" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J1251" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K1251" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="1252">
@@ -63318,13 +63318,13 @@
         </is>
       </c>
       <c r="I1252" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J1252" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K1252" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="1253">
@@ -63773,13 +63773,13 @@
         </is>
       </c>
       <c r="I1261" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J1261" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K1261" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1262">
@@ -64228,13 +64228,13 @@
         </is>
       </c>
       <c r="I1270" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J1270" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K1270" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="1271">
@@ -64330,13 +64330,13 @@
         </is>
       </c>
       <c r="I1272" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1272" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K1272" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1273">
@@ -64381,13 +64381,13 @@
         </is>
       </c>
       <c r="I1273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1273" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K1273" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1274">
@@ -64585,13 +64585,13 @@
         </is>
       </c>
       <c r="I1277" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J1277" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K1277" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1278">
@@ -64840,13 +64840,13 @@
         </is>
       </c>
       <c r="I1282" t="n">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="J1282" t="n">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="K1282" t="n">
-        <v>207</v>
+        <v>229</v>
       </c>
     </row>
     <row r="1283">
@@ -64993,13 +64993,13 @@
         </is>
       </c>
       <c r="I1285" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J1285" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="K1285" t="n">
-        <v>115</v>
+        <v>133</v>
       </c>
     </row>
     <row r="1286">
@@ -65095,13 +65095,13 @@
         </is>
       </c>
       <c r="I1287" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J1287" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K1287" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="1288">
@@ -65652,13 +65652,13 @@
         </is>
       </c>
       <c r="I1298" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J1298" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K1298" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="1299">
@@ -66060,13 +66060,13 @@
         </is>
       </c>
       <c r="I1306" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="J1306" t="n">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="K1306" t="n">
-        <v>107</v>
+        <v>118</v>
       </c>
     </row>
     <row r="1307">
@@ -66162,13 +66162,13 @@
         </is>
       </c>
       <c r="I1308" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="J1308" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="K1308" t="n">
-        <v>134</v>
+        <v>158</v>
       </c>
     </row>
     <row r="1309">
@@ -66213,13 +66213,13 @@
         </is>
       </c>
       <c r="I1309" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J1309" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="K1309" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
     </row>
     <row r="1310">
@@ -66264,13 +66264,13 @@
         </is>
       </c>
       <c r="I1310" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J1310" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="K1310" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="1311">
@@ -66315,13 +66315,13 @@
         </is>
       </c>
       <c r="I1311" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="J1311" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="K1311" t="n">
-        <v>71</v>
+        <v>89</v>
       </c>
     </row>
     <row r="1312">
@@ -66365,10 +66365,10 @@
         <v>9</v>
       </c>
       <c r="J1312" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="K1312" t="n">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="1313">
@@ -66413,13 +66413,13 @@
         </is>
       </c>
       <c r="I1313" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J1313" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="K1313" t="n">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="1314">
@@ -66464,13 +66464,13 @@
         </is>
       </c>
       <c r="I1314" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J1314" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="K1314" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="1315">
@@ -66515,13 +66515,13 @@
         </is>
       </c>
       <c r="I1315" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J1315" t="n">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="K1315" t="n">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="1316">
@@ -66566,13 +66566,13 @@
         </is>
       </c>
       <c r="I1316" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J1316" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K1316" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="1317">
@@ -66617,13 +66617,13 @@
         </is>
       </c>
       <c r="I1317" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J1317" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K1317" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="1318">
@@ -66668,13 +66668,13 @@
         </is>
       </c>
       <c r="I1318" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="J1318" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="K1318" t="n">
-        <v>92</v>
+        <v>99</v>
       </c>
     </row>
     <row r="1319">
@@ -66725,7 +66725,7 @@
         <v>0</v>
       </c>
       <c r="K1319" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1320">
@@ -66770,13 +66770,13 @@
         </is>
       </c>
       <c r="I1320" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="J1320" t="n">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="K1320" t="n">
-        <v>103</v>
+        <v>126</v>
       </c>
     </row>
     <row r="1321">
@@ -66821,13 +66821,13 @@
         </is>
       </c>
       <c r="I1321" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="J1321" t="n">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="K1321" t="n">
-        <v>261</v>
+        <v>270</v>
       </c>
     </row>
     <row r="1322">
@@ -66923,13 +66923,13 @@
         </is>
       </c>
       <c r="I1323" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J1323" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K1323" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="1324">
@@ -66974,13 +66974,13 @@
         </is>
       </c>
       <c r="I1324" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J1324" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K1324" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="1325">
@@ -67025,13 +67025,13 @@
         </is>
       </c>
       <c r="I1325" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="J1325" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="K1325" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="1326">
@@ -67127,13 +67127,13 @@
         </is>
       </c>
       <c r="I1327" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J1327" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K1327" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1328">
@@ -67178,13 +67178,13 @@
         </is>
       </c>
       <c r="I1328" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J1328" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K1328" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="1329">
@@ -67229,13 +67229,13 @@
         </is>
       </c>
       <c r="I1329" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J1329" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K1329" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="1330">
@@ -67331,13 +67331,13 @@
         </is>
       </c>
       <c r="I1331" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="J1331" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="K1331" t="n">
-        <v>56</v>
+        <v>64</v>
       </c>
     </row>
     <row r="1332">
@@ -67382,13 +67382,13 @@
         </is>
       </c>
       <c r="I1332" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J1332" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="K1332" t="n">
-        <v>78</v>
+        <v>85</v>
       </c>
     </row>
     <row r="1333">
@@ -67433,13 +67433,13 @@
         </is>
       </c>
       <c r="I1333" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J1333" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="K1333" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="1334">
@@ -67483,10 +67483,10 @@
         <v>0</v>
       </c>
       <c r="J1334" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="K1334" t="n">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="1335">
@@ -67531,13 +67531,13 @@
         </is>
       </c>
       <c r="I1335" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J1335" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="K1335" t="n">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="1336">
@@ -67633,13 +67633,13 @@
         </is>
       </c>
       <c r="I1337" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="J1337" t="n">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="K1337" t="n">
-        <v>124</v>
+        <v>139</v>
       </c>
     </row>
     <row r="1338">
@@ -67684,13 +67684,13 @@
         </is>
       </c>
       <c r="I1338" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J1338" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K1338" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="1339">
@@ -67735,13 +67735,13 @@
         </is>
       </c>
       <c r="I1339" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="J1339" t="n">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="K1339" t="n">
-        <v>17</v>
+        <v>55</v>
       </c>
     </row>
     <row r="1340">
@@ -67786,13 +67786,13 @@
         </is>
       </c>
       <c r="I1340" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J1340" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K1340" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="1341">
@@ -67837,13 +67837,13 @@
         </is>
       </c>
       <c r="I1341" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J1341" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="K1341" t="n">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="1342">
@@ -67939,13 +67939,13 @@
         </is>
       </c>
       <c r="I1343" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J1343" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K1343" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="1344">
@@ -67990,13 +67990,13 @@
         </is>
       </c>
       <c r="I1344" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J1344" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K1344" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1345">
@@ -68032,22 +68032,22 @@
       </c>
       <c r="G1345" t="inlineStr">
         <is>
-          <t>Jose Natan</t>
+          <t>Jose Borges</t>
         </is>
       </c>
       <c r="H1345" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="I1345" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J1345" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K1345" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1346">
@@ -68083,7 +68083,7 @@
       </c>
       <c r="G1346" t="inlineStr">
         <is>
-          <t>João Oliveira</t>
+          <t>Jose Natan</t>
         </is>
       </c>
       <c r="H1346" t="inlineStr">
@@ -68092,13 +68092,13 @@
         </is>
       </c>
       <c r="I1346" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J1346" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="K1346" t="n">
-        <v>18</v>
+        <v>107</v>
       </c>
     </row>
     <row r="1347">
@@ -68134,22 +68134,22 @@
       </c>
       <c r="G1347" t="inlineStr">
         <is>
-          <t>Juan Ribeiro</t>
+          <t>João Oliveira</t>
         </is>
       </c>
       <c r="H1347" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I1347" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J1347" t="n">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="K1347" t="n">
-        <v>87</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1348">
@@ -68185,22 +68185,22 @@
       </c>
       <c r="G1348" t="inlineStr">
         <is>
-          <t>Juliana Valeria</t>
+          <t>Juan Ribeiro</t>
         </is>
       </c>
       <c r="H1348" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I1348" t="n">
         <v>8</v>
       </c>
       <c r="J1348" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K1348" t="n">
-        <v>109</v>
+        <v>92</v>
       </c>
     </row>
     <row r="1349">
@@ -68236,7 +68236,7 @@
       </c>
       <c r="G1349" t="inlineStr">
         <is>
-          <t>Juliane Vaz</t>
+          <t>Juliana Valeria</t>
         </is>
       </c>
       <c r="H1349" t="inlineStr">
@@ -68245,13 +68245,13 @@
         </is>
       </c>
       <c r="I1349" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="J1349" t="n">
-        <v>175</v>
+        <v>70</v>
       </c>
       <c r="K1349" t="n">
-        <v>275</v>
+        <v>132</v>
       </c>
     </row>
     <row r="1350">
@@ -68287,22 +68287,22 @@
       </c>
       <c r="G1350" t="inlineStr">
         <is>
-          <t>Katia Xavier</t>
+          <t>Juliane Vaz</t>
         </is>
       </c>
       <c r="H1350" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I1350" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="J1350" t="n">
-        <v>58</v>
+        <v>186</v>
       </c>
       <c r="K1350" t="n">
-        <v>109</v>
+        <v>286</v>
       </c>
     </row>
     <row r="1351">
@@ -68338,22 +68338,22 @@
       </c>
       <c r="G1351" t="inlineStr">
         <is>
-          <t>Larissa Félix</t>
+          <t>Katia Xavier</t>
         </is>
       </c>
       <c r="H1351" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I1351" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="J1351" t="n">
-        <v>149</v>
+        <v>58</v>
       </c>
       <c r="K1351" t="n">
-        <v>212</v>
+        <v>109</v>
       </c>
     </row>
     <row r="1352">
@@ -68389,22 +68389,22 @@
       </c>
       <c r="G1352" t="inlineStr">
         <is>
-          <t>Léia de Oliveira</t>
+          <t>Larissa Félix</t>
         </is>
       </c>
       <c r="H1352" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I1352" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="J1352" t="n">
-        <v>39</v>
+        <v>150</v>
       </c>
       <c r="K1352" t="n">
-        <v>126</v>
+        <v>213</v>
       </c>
     </row>
     <row r="1353">
@@ -68440,7 +68440,7 @@
       </c>
       <c r="G1353" t="inlineStr">
         <is>
-          <t>Maria Gualberto</t>
+          <t>Léia de Oliveira</t>
         </is>
       </c>
       <c r="H1353" t="inlineStr">
@@ -68449,13 +68449,13 @@
         </is>
       </c>
       <c r="I1353" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="J1353" t="n">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="K1353" t="n">
-        <v>105</v>
+        <v>130</v>
       </c>
     </row>
     <row r="1354">
@@ -68491,22 +68491,22 @@
       </c>
       <c r="G1354" t="inlineStr">
         <is>
-          <t>Nathany Silva</t>
+          <t>Maria Gualberto</t>
         </is>
       </c>
       <c r="H1354" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I1354" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J1354" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="K1354" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
     </row>
     <row r="1355">
@@ -68542,22 +68542,22 @@
       </c>
       <c r="G1355" t="inlineStr">
         <is>
-          <t>Priscila Moreira</t>
+          <t>Nathany Silva</t>
         </is>
       </c>
       <c r="H1355" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I1355" t="n">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="J1355" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="K1355" t="n">
-        <v>135</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1356">
@@ -68593,22 +68593,22 @@
       </c>
       <c r="G1356" t="inlineStr">
         <is>
-          <t>Regiane Santos</t>
+          <t>Priscila Moreira</t>
         </is>
       </c>
       <c r="H1356" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="I1356" t="n">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="J1356" t="n">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="K1356" t="n">
-        <v>67</v>
+        <v>142</v>
       </c>
     </row>
     <row r="1357">
@@ -68644,22 +68644,22 @@
       </c>
       <c r="G1357" t="inlineStr">
         <is>
-          <t>Shofia Gomes</t>
+          <t>Regiane Santos</t>
         </is>
       </c>
       <c r="H1357" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I1357" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J1357" t="n">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="K1357" t="n">
-        <v>127</v>
+        <v>67</v>
       </c>
     </row>
     <row r="1358">
@@ -68695,22 +68695,22 @@
       </c>
       <c r="G1358" t="inlineStr">
         <is>
-          <t>Vanessa Tavares</t>
+          <t>Shofia Gomes</t>
         </is>
       </c>
       <c r="H1358" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="I1358" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J1358" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="K1358" t="n">
-        <v>89</v>
+        <v>131</v>
       </c>
     </row>
     <row r="1359">
@@ -68746,7 +68746,7 @@
       </c>
       <c r="G1359" t="inlineStr">
         <is>
-          <t>Willian Luz</t>
+          <t>Vanessa Tavares</t>
         </is>
       </c>
       <c r="H1359" t="inlineStr">
@@ -68755,13 +68755,13 @@
         </is>
       </c>
       <c r="I1359" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J1359" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="K1359" t="n">
-        <v>80</v>
+        <v>89</v>
       </c>
     </row>
     <row r="1360">
@@ -68797,7 +68797,7 @@
       </c>
       <c r="G1360" t="inlineStr">
         <is>
-          <t>Yasmim Oliveira</t>
+          <t>Willian Luz</t>
         </is>
       </c>
       <c r="H1360" t="inlineStr">
@@ -68806,13 +68806,13 @@
         </is>
       </c>
       <c r="I1360" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J1360" t="n">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="K1360" t="n">
-        <v>45</v>
+        <v>84</v>
       </c>
     </row>
     <row r="1361">
@@ -68843,23 +68843,27 @@
       </c>
       <c r="F1361" t="inlineStr">
         <is>
-          <t>ESCRITA FISCAL (Outsourcing)</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="G1361" t="inlineStr">
         <is>
-          <t>Claudineia Rodrigues</t>
-        </is>
-      </c>
-      <c r="H1361" t="inlineStr"/>
+          <t>Yasmim Oliveira</t>
+        </is>
+      </c>
+      <c r="H1361" t="inlineStr">
+        <is>
+          <t>Larice Souza</t>
+        </is>
+      </c>
       <c r="I1361" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J1361" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="K1361" t="n">
-        <v>5</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1362">
@@ -68895,22 +68899,18 @@
       </c>
       <c r="G1362" t="inlineStr">
         <is>
-          <t>Diego Pereira</t>
-        </is>
-      </c>
-      <c r="H1362" t="inlineStr">
-        <is>
-          <t>Thaiza Oliveira</t>
-        </is>
-      </c>
+          <t>Claudineia Rodrigues</t>
+        </is>
+      </c>
+      <c r="H1362" t="inlineStr"/>
       <c r="I1362" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J1362" t="n">
+        <v>3</v>
+      </c>
+      <c r="K1362" t="n">
         <v>5</v>
-      </c>
-      <c r="K1362" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="1363">
@@ -68946,22 +68946,22 @@
       </c>
       <c r="G1363" t="inlineStr">
         <is>
-          <t>Gislaine Lima</t>
+          <t>Diego Pereira</t>
         </is>
       </c>
       <c r="H1363" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I1363" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J1363" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="K1363" t="n">
-        <v>35</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1364">
@@ -68997,7 +68997,7 @@
       </c>
       <c r="G1364" t="inlineStr">
         <is>
-          <t>Joanna Costa</t>
+          <t>Gislaine Lima</t>
         </is>
       </c>
       <c r="H1364" t="inlineStr">
@@ -69006,13 +69006,13 @@
         </is>
       </c>
       <c r="I1364" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J1364" t="n">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="K1364" t="n">
-        <v>60</v>
+        <v>37</v>
       </c>
     </row>
     <row r="1365">
@@ -69048,22 +69048,22 @@
       </c>
       <c r="G1365" t="inlineStr">
         <is>
-          <t>Jonatan Hayashibara</t>
+          <t>Joanna Costa</t>
         </is>
       </c>
       <c r="H1365" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I1365" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J1365" t="n">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="K1365" t="n">
-        <v>4</v>
+        <v>60</v>
       </c>
     </row>
     <row r="1366">
@@ -69099,22 +69099,22 @@
       </c>
       <c r="G1366" t="inlineStr">
         <is>
-          <t>João Oliveira</t>
+          <t>Jonatan Hayashibara</t>
         </is>
       </c>
       <c r="H1366" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
       <c r="I1366" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J1366" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="K1366" t="n">
-        <v>51</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1367">
@@ -69150,7 +69150,7 @@
       </c>
       <c r="G1367" t="inlineStr">
         <is>
-          <t>Regiane Santos</t>
+          <t>João Oliveira</t>
         </is>
       </c>
       <c r="H1367" t="inlineStr">
@@ -69159,13 +69159,13 @@
         </is>
       </c>
       <c r="I1367" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="J1367" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="K1367" t="n">
-        <v>18</v>
+        <v>53</v>
       </c>
     </row>
     <row r="1368">
@@ -69201,7 +69201,7 @@
       </c>
       <c r="G1368" t="inlineStr">
         <is>
-          <t>Yasmim Oliveira</t>
+          <t>Regiane Santos</t>
         </is>
       </c>
       <c r="H1368" t="inlineStr">
@@ -69210,13 +69210,13 @@
         </is>
       </c>
       <c r="I1368" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J1368" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K1368" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="1369">
@@ -69247,23 +69247,27 @@
       </c>
       <c r="F1369" t="inlineStr">
         <is>
-          <t>FIN - CONTÁBIL</t>
+          <t>ESCRITA FISCAL (Outsourcing)</t>
         </is>
       </c>
       <c r="G1369" t="inlineStr">
         <is>
-          <t>Daniele Faria</t>
-        </is>
-      </c>
-      <c r="H1369" t="inlineStr"/>
+          <t>Yasmim Oliveira</t>
+        </is>
+      </c>
+      <c r="H1369" t="inlineStr">
+        <is>
+          <t>Larice Souza</t>
+        </is>
+      </c>
       <c r="I1369" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1369" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="K1369" t="n">
-        <v>62</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1370">
@@ -69294,23 +69298,23 @@
       </c>
       <c r="F1370" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>FIN - CONTÁBIL</t>
         </is>
       </c>
       <c r="G1370" t="inlineStr">
         <is>
-          <t>Ana Santana</t>
+          <t>Daniele Faria</t>
         </is>
       </c>
       <c r="H1370" t="inlineStr"/>
       <c r="I1370" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J1370" t="n">
-        <v>384</v>
+        <v>20</v>
       </c>
       <c r="K1370" t="n">
-        <v>587</v>
+        <v>62</v>
       </c>
     </row>
     <row r="1371">
@@ -69346,18 +69350,18 @@
       </c>
       <c r="G1371" t="inlineStr">
         <is>
-          <t>Andre Coelho</t>
+          <t>Ana Santana</t>
         </is>
       </c>
       <c r="H1371" t="inlineStr"/>
       <c r="I1371" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1371" t="n">
-        <v>12</v>
+        <v>384</v>
       </c>
       <c r="K1371" t="n">
-        <v>16</v>
+        <v>587</v>
       </c>
     </row>
     <row r="1372">
@@ -69393,7 +69397,7 @@
       </c>
       <c r="G1372" t="inlineStr">
         <is>
-          <t>Bianca Castro</t>
+          <t>Andre Coelho</t>
         </is>
       </c>
       <c r="H1372" t="inlineStr"/>
@@ -69401,10 +69405,10 @@
         <v>0</v>
       </c>
       <c r="J1372" t="n">
-        <v>265</v>
+        <v>12</v>
       </c>
       <c r="K1372" t="n">
-        <v>459</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1373">
@@ -69440,18 +69444,18 @@
       </c>
       <c r="G1373" t="inlineStr">
         <is>
-          <t>Bruna Costa</t>
+          <t>Bianca Castro</t>
         </is>
       </c>
       <c r="H1373" t="inlineStr"/>
       <c r="I1373" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J1373" t="n">
-        <v>34</v>
+        <v>265</v>
       </c>
       <c r="K1373" t="n">
-        <v>34</v>
+        <v>459</v>
       </c>
     </row>
     <row r="1374">
@@ -69487,18 +69491,18 @@
       </c>
       <c r="G1374" t="inlineStr">
         <is>
-          <t>Daniela Silva</t>
+          <t>Bruna Costa</t>
         </is>
       </c>
       <c r="H1374" t="inlineStr"/>
       <c r="I1374" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1374" t="n">
-        <v>306</v>
+        <v>34</v>
       </c>
       <c r="K1374" t="n">
-        <v>302</v>
+        <v>34</v>
       </c>
     </row>
     <row r="1375">
@@ -69534,18 +69538,18 @@
       </c>
       <c r="G1375" t="inlineStr">
         <is>
-          <t>Isabelli Afonso</t>
+          <t>Daniela Silva</t>
         </is>
       </c>
       <c r="H1375" t="inlineStr"/>
       <c r="I1375" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J1375" t="n">
-        <v>217</v>
+        <v>306</v>
       </c>
       <c r="K1375" t="n">
-        <v>234</v>
+        <v>302</v>
       </c>
     </row>
     <row r="1376">
@@ -69581,18 +69585,18 @@
       </c>
       <c r="G1376" t="inlineStr">
         <is>
-          <t>Jurema Damacena - SAC</t>
+          <t>Isabelli Afonso</t>
         </is>
       </c>
       <c r="H1376" t="inlineStr"/>
       <c r="I1376" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J1376" t="n">
-        <v>0</v>
+        <v>217</v>
       </c>
       <c r="K1376" t="n">
-        <v>1</v>
+        <v>234</v>
       </c>
     </row>
     <row r="1377">
@@ -69628,7 +69632,7 @@
       </c>
       <c r="G1377" t="inlineStr">
         <is>
-          <t>Leticia Queiroz</t>
+          <t>Jurema Damacena - SAC</t>
         </is>
       </c>
       <c r="H1377" t="inlineStr"/>
@@ -69636,10 +69640,10 @@
         <v>0</v>
       </c>
       <c r="J1377" t="n">
-        <v>424</v>
+        <v>0</v>
       </c>
       <c r="K1377" t="n">
-        <v>428</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1378">
@@ -69675,7 +69679,7 @@
       </c>
       <c r="G1378" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Leticia Queiroz</t>
         </is>
       </c>
       <c r="H1378" t="inlineStr"/>
@@ -69683,10 +69687,10 @@
         <v>0</v>
       </c>
       <c r="J1378" t="n">
-        <v>2</v>
+        <v>424</v>
       </c>
       <c r="K1378" t="n">
-        <v>13</v>
+        <v>428</v>
       </c>
     </row>
     <row r="1379">
@@ -69722,7 +69726,7 @@
       </c>
       <c r="G1379" t="inlineStr">
         <is>
-          <t>Victoria Virgens</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="H1379" t="inlineStr"/>
@@ -69730,10 +69734,10 @@
         <v>0</v>
       </c>
       <c r="J1379" t="n">
-        <v>308</v>
+        <v>2</v>
       </c>
       <c r="K1379" t="n">
-        <v>308</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1380">
@@ -69769,18 +69773,18 @@
       </c>
       <c r="G1380" t="inlineStr">
         <is>
-          <t>Yasmin Peixoto</t>
+          <t>Victoria Virgens</t>
         </is>
       </c>
       <c r="H1380" t="inlineStr"/>
       <c r="I1380" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J1380" t="n">
-        <v>354</v>
+        <v>311</v>
       </c>
       <c r="K1380" t="n">
-        <v>551</v>
+        <v>308</v>
       </c>
     </row>
     <row r="1381">
@@ -69811,12 +69815,12 @@
       </c>
       <c r="F1381" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="G1381" t="inlineStr">
         <is>
-          <t>Andre Coelho</t>
+          <t>Yasmin Peixoto</t>
         </is>
       </c>
       <c r="H1381" t="inlineStr"/>
@@ -69824,10 +69828,10 @@
         <v>0</v>
       </c>
       <c r="J1381" t="n">
-        <v>4</v>
+        <v>354</v>
       </c>
       <c r="K1381" t="n">
-        <v>4</v>
+        <v>551</v>
       </c>
     </row>
     <row r="1382">
@@ -69863,18 +69867,18 @@
       </c>
       <c r="G1382" t="inlineStr">
         <is>
-          <t>Beatriz Rangel</t>
+          <t>Andre Coelho</t>
         </is>
       </c>
       <c r="H1382" t="inlineStr"/>
       <c r="I1382" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J1382" t="n">
-        <v>222</v>
+        <v>4</v>
       </c>
       <c r="K1382" t="n">
-        <v>371</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1383">
@@ -69910,18 +69914,18 @@
       </c>
       <c r="G1383" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
+          <t>Beatriz Rangel</t>
         </is>
       </c>
       <c r="H1383" t="inlineStr"/>
       <c r="I1383" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J1383" t="n">
-        <v>428</v>
+        <v>222</v>
       </c>
       <c r="K1383" t="n">
-        <v>434</v>
+        <v>371</v>
       </c>
     </row>
     <row r="1384">
@@ -69957,7 +69961,7 @@
       </c>
       <c r="G1384" t="inlineStr">
         <is>
-          <t>Cristiane Simões</t>
+          <t>Bruno Contieri</t>
         </is>
       </c>
       <c r="H1384" t="inlineStr"/>
@@ -69965,10 +69969,10 @@
         <v>0</v>
       </c>
       <c r="J1384" t="n">
-        <v>271</v>
+        <v>429</v>
       </c>
       <c r="K1384" t="n">
-        <v>305</v>
+        <v>434</v>
       </c>
     </row>
     <row r="1385">
@@ -70004,18 +70008,18 @@
       </c>
       <c r="G1385" t="inlineStr">
         <is>
-          <t>Daniel Oliveira</t>
+          <t>Cristiane Simões</t>
         </is>
       </c>
       <c r="H1385" t="inlineStr"/>
       <c r="I1385" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J1385" t="n">
-        <v>353</v>
+        <v>271</v>
       </c>
       <c r="K1385" t="n">
-        <v>403</v>
+        <v>305</v>
       </c>
     </row>
     <row r="1386">
@@ -70051,18 +70055,18 @@
       </c>
       <c r="G1386" t="inlineStr">
         <is>
-          <t>Diego Lima</t>
+          <t>Daniel Oliveira</t>
         </is>
       </c>
       <c r="H1386" t="inlineStr"/>
       <c r="I1386" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J1386" t="n">
-        <v>174</v>
+        <v>353</v>
       </c>
       <c r="K1386" t="n">
-        <v>164</v>
+        <v>403</v>
       </c>
     </row>
     <row r="1387">
@@ -70098,18 +70102,18 @@
       </c>
       <c r="G1387" t="inlineStr">
         <is>
-          <t>Eduardo Aparicio</t>
+          <t>Diego Lima</t>
         </is>
       </c>
       <c r="H1387" t="inlineStr"/>
       <c r="I1387" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J1387" t="n">
-        <v>1</v>
+        <v>174</v>
       </c>
       <c r="K1387" t="n">
-        <v>1</v>
+        <v>164</v>
       </c>
     </row>
     <row r="1388">
@@ -70145,18 +70149,18 @@
       </c>
       <c r="G1388" t="inlineStr">
         <is>
-          <t>Karine Gusmão</t>
+          <t>Eduardo Aparicio</t>
         </is>
       </c>
       <c r="H1388" t="inlineStr"/>
       <c r="I1388" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1388" t="n">
         <v>1</v>
       </c>
-      <c r="J1388" t="n">
-        <v>112</v>
-      </c>
       <c r="K1388" t="n">
-        <v>93</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1389">
@@ -70192,18 +70196,18 @@
       </c>
       <c r="G1389" t="inlineStr">
         <is>
-          <t>Luiz Ferreira</t>
+          <t>Karine Gusmão</t>
         </is>
       </c>
       <c r="H1389" t="inlineStr"/>
       <c r="I1389" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1389" t="n">
-        <v>18</v>
+        <v>112</v>
       </c>
       <c r="K1389" t="n">
-        <v>17</v>
+        <v>93</v>
       </c>
     </row>
     <row r="1390">
@@ -70239,18 +70243,18 @@
       </c>
       <c r="G1390" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Luiz Ferreira</t>
         </is>
       </c>
       <c r="H1390" t="inlineStr"/>
       <c r="I1390" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J1390" t="n">
-        <v>210</v>
+        <v>18</v>
       </c>
       <c r="K1390" t="n">
-        <v>221</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1391">
@@ -70286,7 +70290,7 @@
       </c>
       <c r="G1391" t="inlineStr">
         <is>
-          <t>Rodrigo Rego</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="H1391" t="inlineStr"/>
@@ -70294,10 +70298,10 @@
         <v>4</v>
       </c>
       <c r="J1391" t="n">
-        <v>420</v>
+        <v>210</v>
       </c>
       <c r="K1391" t="n">
-        <v>460</v>
+        <v>221</v>
       </c>
     </row>
     <row r="1392">
@@ -70333,18 +70337,18 @@
       </c>
       <c r="G1392" t="inlineStr">
         <is>
-          <t>Rogerio Egidio</t>
+          <t>Rodrigo Rego</t>
         </is>
       </c>
       <c r="H1392" t="inlineStr"/>
       <c r="I1392" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J1392" t="n">
-        <v>335</v>
+        <v>421</v>
       </c>
       <c r="K1392" t="n">
-        <v>382</v>
+        <v>460</v>
       </c>
     </row>
     <row r="1393">
@@ -70380,18 +70384,18 @@
       </c>
       <c r="G1393" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Rogerio Egidio</t>
         </is>
       </c>
       <c r="H1393" t="inlineStr"/>
       <c r="I1393" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1393" t="n">
-        <v>33</v>
+        <v>336</v>
       </c>
       <c r="K1393" t="n">
-        <v>50</v>
+        <v>383</v>
       </c>
     </row>
     <row r="1394">
@@ -70427,7 +70431,7 @@
       </c>
       <c r="G1394" t="inlineStr">
         <is>
-          <t>Simone Marques</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="H1394" t="inlineStr"/>
@@ -70435,10 +70439,10 @@
         <v>2</v>
       </c>
       <c r="J1394" t="n">
-        <v>197</v>
+        <v>33</v>
       </c>
       <c r="K1394" t="n">
-        <v>228</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1395">
@@ -70474,18 +70478,18 @@
       </c>
       <c r="G1395" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Simone Marques</t>
         </is>
       </c>
       <c r="H1395" t="inlineStr"/>
       <c r="I1395" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1395" t="n">
-        <v>214</v>
+        <v>197</v>
       </c>
       <c r="K1395" t="n">
-        <v>267</v>
+        <v>228</v>
       </c>
     </row>
     <row r="1396">
@@ -70516,12 +70520,12 @@
       </c>
       <c r="F1396" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="G1396" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="H1396" t="inlineStr"/>
@@ -70529,10 +70533,10 @@
         <v>0</v>
       </c>
       <c r="J1396" t="n">
-        <v>0</v>
+        <v>214</v>
       </c>
       <c r="K1396" t="n">
-        <v>1</v>
+        <v>267</v>
       </c>
     </row>
     <row r="1397">
@@ -70568,18 +70572,18 @@
       </c>
       <c r="G1397" t="inlineStr">
         <is>
-          <t>Jurema Damacena - SAC</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="H1397" t="inlineStr"/>
       <c r="I1397" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J1397" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K1397" t="n">
-        <v>49</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1398">
@@ -70610,23 +70614,23 @@
       </c>
       <c r="F1398" t="inlineStr">
         <is>
-          <t>MG CONTABIFÁCIL - CTB</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="G1398" t="inlineStr">
         <is>
-          <t>Guilherme Delecrodio</t>
+          <t>Jurema Damacena - SAC</t>
         </is>
       </c>
       <c r="H1398" t="inlineStr"/>
       <c r="I1398" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J1398" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="K1398" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
     </row>
     <row r="1399">
@@ -70657,12 +70661,12 @@
       </c>
       <c r="F1399" t="inlineStr">
         <is>
-          <t>S.A.C</t>
+          <t>MG CONTABIFÁCIL - CTB</t>
         </is>
       </c>
       <c r="G1399" t="inlineStr">
         <is>
-          <t>Ana Celia - SAC</t>
+          <t>Guilherme Delecrodio</t>
         </is>
       </c>
       <c r="H1399" t="inlineStr"/>
@@ -70704,27 +70708,23 @@
       </c>
       <c r="F1400" t="inlineStr">
         <is>
-          <t>SANTOS - DP</t>
+          <t>S.A.C</t>
         </is>
       </c>
       <c r="G1400" t="inlineStr">
         <is>
-          <t>Katia Valeria</t>
-        </is>
-      </c>
-      <c r="H1400" t="inlineStr">
-        <is>
-          <t>Katia Valeria</t>
-        </is>
-      </c>
+          <t>Ana Celia - SAC</t>
+        </is>
+      </c>
+      <c r="H1400" t="inlineStr"/>
       <c r="I1400" t="n">
         <v>0</v>
       </c>
       <c r="J1400" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K1400" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1401">
@@ -70750,28 +70750,32 @@
       </c>
       <c r="E1401" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F1401" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>SANTOS - DP</t>
         </is>
       </c>
       <c r="G1401" t="inlineStr">
         <is>
-          <t>Jurema Damacena - SAC</t>
-        </is>
-      </c>
-      <c r="H1401" t="inlineStr"/>
+          <t>Katia Valeria</t>
+        </is>
+      </c>
+      <c r="H1401" t="inlineStr">
+        <is>
+          <t>Katia Valeria</t>
+        </is>
+      </c>
       <c r="I1401" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J1401" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K1401" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1402">
@@ -70802,23 +70806,23 @@
       </c>
       <c r="F1402" t="inlineStr">
         <is>
-          <t>SANTOS - ADM</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="G1402" t="inlineStr">
         <is>
-          <t>Kauany Pereira</t>
+          <t>Jurema Damacena - SAC</t>
         </is>
       </c>
       <c r="H1402" t="inlineStr"/>
       <c r="I1402" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J1402" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="K1402" t="n">
-        <v>138</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1403">
@@ -70849,27 +70853,23 @@
       </c>
       <c r="F1403" t="inlineStr">
         <is>
-          <t>SANTOS - CTB</t>
+          <t>SANTOS - ADM</t>
         </is>
       </c>
       <c r="G1403" t="inlineStr">
         <is>
-          <t>Ivia Oliveira</t>
-        </is>
-      </c>
-      <c r="H1403" t="inlineStr">
-        <is>
-          <t>Roberto Silva</t>
-        </is>
-      </c>
+          <t>Kauany Pereira</t>
+        </is>
+      </c>
+      <c r="H1403" t="inlineStr"/>
       <c r="I1403" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1403" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="K1403" t="n">
-        <v>20</v>
+        <v>138</v>
       </c>
     </row>
     <row r="1404">
@@ -70905,7 +70905,7 @@
       </c>
       <c r="G1404" t="inlineStr">
         <is>
-          <t>Nata Trindade</t>
+          <t>Ivia Oliveira</t>
         </is>
       </c>
       <c r="H1404" t="inlineStr">
@@ -70914,13 +70914,13 @@
         </is>
       </c>
       <c r="I1404" t="n">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="J1404" t="n">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="K1404" t="n">
-        <v>42</v>
+        <v>57</v>
       </c>
     </row>
     <row r="1405">
@@ -70956,22 +70956,22 @@
       </c>
       <c r="G1405" t="inlineStr">
         <is>
+          <t>Nata Trindade</t>
+        </is>
+      </c>
+      <c r="H1405" t="inlineStr">
+        <is>
           <t>Roberto Silva</t>
         </is>
       </c>
-      <c r="H1405" t="inlineStr">
-        <is>
-          <t>Roberto Silva</t>
-        </is>
-      </c>
       <c r="I1405" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="J1405" t="n">
-        <v>8</v>
+        <v>64</v>
       </c>
       <c r="K1405" t="n">
-        <v>43</v>
+        <v>82</v>
       </c>
     </row>
     <row r="1406">
@@ -71007,7 +71007,7 @@
       </c>
       <c r="G1406" t="inlineStr">
         <is>
-          <t>Thaina Rodrigues</t>
+          <t>Roberto Silva</t>
         </is>
       </c>
       <c r="H1406" t="inlineStr">
@@ -71016,13 +71016,13 @@
         </is>
       </c>
       <c r="I1406" t="n">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="J1406" t="n">
-        <v>25</v>
+        <v>76</v>
       </c>
       <c r="K1406" t="n">
-        <v>49</v>
+        <v>111</v>
       </c>
     </row>
     <row r="1407">
@@ -71053,27 +71053,27 @@
       </c>
       <c r="F1407" t="inlineStr">
         <is>
-          <t>SANTOS - DP</t>
+          <t>SANTOS - CTB</t>
         </is>
       </c>
       <c r="G1407" t="inlineStr">
         <is>
-          <t>Bruna Silva</t>
+          <t>Thaina Rodrigues</t>
         </is>
       </c>
       <c r="H1407" t="inlineStr">
         <is>
-          <t>Katia Valeria</t>
+          <t>Roberto Silva</t>
         </is>
       </c>
       <c r="I1407" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="J1407" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="K1407" t="n">
-        <v>14</v>
+        <v>94</v>
       </c>
     </row>
     <row r="1408">
@@ -71109,7 +71109,7 @@
       </c>
       <c r="G1408" t="inlineStr">
         <is>
-          <t>Carliane Silva</t>
+          <t>Bruna Silva</t>
         </is>
       </c>
       <c r="H1408" t="inlineStr">
@@ -71118,13 +71118,13 @@
         </is>
       </c>
       <c r="I1408" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1408" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1408" t="n">
         <v>14</v>
-      </c>
-      <c r="J1408" t="n">
-        <v>132</v>
-      </c>
-      <c r="K1408" t="n">
-        <v>285</v>
       </c>
     </row>
     <row r="1409">
@@ -71160,7 +71160,7 @@
       </c>
       <c r="G1409" t="inlineStr">
         <is>
-          <t>Cintia Andrade</t>
+          <t>Carliane Silva</t>
         </is>
       </c>
       <c r="H1409" t="inlineStr">
@@ -71169,13 +71169,13 @@
         </is>
       </c>
       <c r="I1409" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J1409" t="n">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="K1409" t="n">
-        <v>207</v>
+        <v>285</v>
       </c>
     </row>
     <row r="1410">
@@ -71211,22 +71211,22 @@
       </c>
       <c r="G1410" t="inlineStr">
         <is>
+          <t>Cintia Andrade</t>
+        </is>
+      </c>
+      <c r="H1410" t="inlineStr">
+        <is>
           <t>Katia Valeria</t>
         </is>
       </c>
-      <c r="H1410" t="inlineStr">
-        <is>
-          <t>Katia Valeria</t>
-        </is>
-      </c>
       <c r="I1410" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J1410" t="n">
-        <v>166</v>
+        <v>103</v>
       </c>
       <c r="K1410" t="n">
-        <v>346</v>
+        <v>207</v>
       </c>
     </row>
     <row r="1411">
@@ -71257,27 +71257,27 @@
       </c>
       <c r="F1411" t="inlineStr">
         <is>
-          <t>SANTOS - EF</t>
+          <t>SANTOS - DP</t>
         </is>
       </c>
       <c r="G1411" t="inlineStr">
         <is>
-          <t>Jasmina Melo</t>
+          <t>Katia Valeria</t>
         </is>
       </c>
       <c r="H1411" t="inlineStr">
         <is>
-          <t>Lidia Tavares</t>
+          <t>Katia Valeria</t>
         </is>
       </c>
       <c r="I1411" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="J1411" t="n">
-        <v>55</v>
+        <v>168</v>
       </c>
       <c r="K1411" t="n">
-        <v>78</v>
+        <v>348</v>
       </c>
     </row>
     <row r="1412">
@@ -71313,7 +71313,7 @@
       </c>
       <c r="G1412" t="inlineStr">
         <is>
-          <t>Karen Saadi</t>
+          <t>Jasmina Melo</t>
         </is>
       </c>
       <c r="H1412" t="inlineStr">
@@ -71322,13 +71322,13 @@
         </is>
       </c>
       <c r="I1412" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J1412" t="n">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="K1412" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
     </row>
     <row r="1413">
@@ -71364,7 +71364,7 @@
       </c>
       <c r="G1413" t="inlineStr">
         <is>
-          <t>Luckas Andrade</t>
+          <t>Karen Saadi</t>
         </is>
       </c>
       <c r="H1413" t="inlineStr">
@@ -71373,13 +71373,13 @@
         </is>
       </c>
       <c r="I1413" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="J1413" t="n">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="K1413" t="n">
-        <v>109</v>
+        <v>77</v>
       </c>
     </row>
     <row r="1414">
@@ -71415,7 +71415,7 @@
       </c>
       <c r="G1414" t="inlineStr">
         <is>
-          <t>Mirian Rodrigues</t>
+          <t>Luckas Andrade</t>
         </is>
       </c>
       <c r="H1414" t="inlineStr">
@@ -71424,13 +71424,13 @@
         </is>
       </c>
       <c r="I1414" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="J1414" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="K1414" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="1415">
@@ -71461,22 +71461,73 @@
       </c>
       <c r="F1415" t="inlineStr">
         <is>
+          <t>SANTOS - EF</t>
+        </is>
+      </c>
+      <c r="G1415" t="inlineStr">
+        <is>
+          <t>Mirian Rodrigues</t>
+        </is>
+      </c>
+      <c r="H1415" t="inlineStr">
+        <is>
+          <t>Lidia Tavares</t>
+        </is>
+      </c>
+      <c r="I1415" t="n">
+        <v>26</v>
+      </c>
+      <c r="J1415" t="n">
+        <v>53</v>
+      </c>
+      <c r="K1415" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="1416">
+      <c r="A1416" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B1416" t="inlineStr">
+        <is>
+          <t>Sexta</t>
+        </is>
+      </c>
+      <c r="C1416" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D1416" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1416" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="F1416" t="inlineStr">
+        <is>
           <t>SANTOS - GC</t>
         </is>
       </c>
-      <c r="G1415" t="inlineStr">
+      <c r="G1416" t="inlineStr">
         <is>
           <t>Rafaella Massuia</t>
         </is>
       </c>
-      <c r="H1415" t="inlineStr"/>
-      <c r="I1415" t="n">
-        <v>2</v>
-      </c>
-      <c r="J1415" t="n">
+      <c r="H1416" t="inlineStr"/>
+      <c r="I1416" t="n">
         <v>1</v>
       </c>
-      <c r="K1415" t="n">
+      <c r="J1416" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1416" t="n">
         <v>109</v>
       </c>
     </row>

--- a/data/historico/historico_baixas.xlsx
+++ b/data/historico/historico_baixas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1705"/>
+  <dimension ref="A1:K1711"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -71768,22 +71768,22 @@
       </c>
       <c r="G1421" t="inlineStr">
         <is>
-          <t>Jackson Silva</t>
+          <t>Isabela Lemos</t>
         </is>
       </c>
       <c r="H1421" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="I1421" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1421" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1421" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1422">
@@ -71819,12 +71819,12 @@
       </c>
       <c r="G1422" t="inlineStr">
         <is>
-          <t>Paulo Silva</t>
+          <t>Jackson Silva</t>
         </is>
       </c>
       <c r="H1422" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I1422" t="n">
@@ -71865,17 +71865,17 @@
       </c>
       <c r="F1423" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="G1423" t="inlineStr">
         <is>
-          <t>Elaine Assis</t>
+          <t>Paulo Silva</t>
         </is>
       </c>
       <c r="H1423" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="I1423" t="n">
@@ -71885,7 +71885,7 @@
         <v>0</v>
       </c>
       <c r="K1423" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1424">
@@ -71921,12 +71921,12 @@
       </c>
       <c r="G1424" t="inlineStr">
         <is>
-          <t>Evellin Bispo</t>
+          <t>Elaine Assis</t>
         </is>
       </c>
       <c r="H1424" t="inlineStr">
         <is>
-          <t>Leandro Matos</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I1424" t="n">
@@ -71936,7 +71936,7 @@
         <v>0</v>
       </c>
       <c r="K1424" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1425">
@@ -71972,12 +71972,12 @@
       </c>
       <c r="G1425" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Evellin Bispo</t>
         </is>
       </c>
       <c r="H1425" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Leandro Matos</t>
         </is>
       </c>
       <c r="I1425" t="n">
@@ -71987,7 +71987,7 @@
         <v>0</v>
       </c>
       <c r="K1425" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1426">
@@ -72023,12 +72023,12 @@
       </c>
       <c r="G1426" t="inlineStr">
         <is>
-          <t>Jhenifer Tenorio</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="H1426" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I1426" t="n">
@@ -72038,7 +72038,7 @@
         <v>0</v>
       </c>
       <c r="K1426" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1427">
@@ -72074,12 +72074,12 @@
       </c>
       <c r="G1427" t="inlineStr">
         <is>
-          <t>Kaique Souza</t>
+          <t>Jhenifer Tenorio</t>
         </is>
       </c>
       <c r="H1427" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I1427" t="n">
@@ -72089,7 +72089,7 @@
         <v>0</v>
       </c>
       <c r="K1427" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1428">
@@ -72125,12 +72125,12 @@
       </c>
       <c r="G1428" t="inlineStr">
         <is>
-          <t>Mauricio Lermen</t>
+          <t>Kaique Souza</t>
         </is>
       </c>
       <c r="H1428" t="inlineStr">
         <is>
-          <t>Mauricio Lermen</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I1428" t="n">
@@ -72140,7 +72140,7 @@
         <v>0</v>
       </c>
       <c r="K1428" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="1429">
@@ -72176,10 +72176,14 @@
       </c>
       <c r="G1429" t="inlineStr">
         <is>
-          <t>Mikael Teixeira</t>
-        </is>
-      </c>
-      <c r="H1429" t="inlineStr"/>
+          <t>Mauricio Lermen</t>
+        </is>
+      </c>
+      <c r="H1429" t="inlineStr">
+        <is>
+          <t>Mauricio Lermen</t>
+        </is>
+      </c>
       <c r="I1429" t="n">
         <v>0</v>
       </c>
@@ -72187,7 +72191,7 @@
         <v>0</v>
       </c>
       <c r="K1429" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1430">
@@ -72223,14 +72227,10 @@
       </c>
       <c r="G1430" t="inlineStr">
         <is>
-          <t>Tania Luz</t>
-        </is>
-      </c>
-      <c r="H1430" t="inlineStr">
-        <is>
-          <t>Sara Cavalheiro</t>
-        </is>
-      </c>
+          <t>Mikael Teixeira</t>
+        </is>
+      </c>
+      <c r="H1430" t="inlineStr"/>
       <c r="I1430" t="n">
         <v>0</v>
       </c>
@@ -72238,7 +72238,7 @@
         <v>0</v>
       </c>
       <c r="K1430" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1431">
@@ -72274,22 +72274,22 @@
       </c>
       <c r="G1431" t="inlineStr">
         <is>
-          <t>Vitor Guedes</t>
+          <t>Tania Luz</t>
         </is>
       </c>
       <c r="H1431" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I1431" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J1431" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K1431" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1432">
@@ -72320,17 +72320,17 @@
       </c>
       <c r="F1432" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="G1432" t="inlineStr">
         <is>
-          <t>Cristiana Grizostomo</t>
+          <t>Vitor Guedes</t>
         </is>
       </c>
       <c r="H1432" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I1432" t="n">
@@ -72340,7 +72340,7 @@
         <v>0</v>
       </c>
       <c r="K1432" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1433">
@@ -72376,18 +72376,22 @@
       </c>
       <c r="G1433" t="inlineStr">
         <is>
-          <t>Denis Reis</t>
-        </is>
-      </c>
-      <c r="H1433" t="inlineStr"/>
+          <t>Cristiana Grizostomo</t>
+        </is>
+      </c>
+      <c r="H1433" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
       <c r="I1433" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1433" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1433" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1434">
@@ -72423,22 +72427,18 @@
       </c>
       <c r="G1434" t="inlineStr">
         <is>
-          <t>Priscila Volpe</t>
-        </is>
-      </c>
-      <c r="H1434" t="inlineStr">
-        <is>
-          <t>Nayara Oliveira</t>
-        </is>
-      </c>
+          <t>Denis Reis</t>
+        </is>
+      </c>
+      <c r="H1434" t="inlineStr"/>
       <c r="I1434" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1434" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1434" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1435">
@@ -72474,7 +72474,7 @@
       </c>
       <c r="G1435" t="inlineStr">
         <is>
-          <t>Rosilene Santos</t>
+          <t>Priscila Volpe</t>
         </is>
       </c>
       <c r="H1435" t="inlineStr">
@@ -72489,7 +72489,7 @@
         <v>0</v>
       </c>
       <c r="K1435" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1436">
@@ -72520,17 +72520,17 @@
       </c>
       <c r="F1436" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="G1436" t="inlineStr">
         <is>
-          <t>Cristina Leite</t>
+          <t>Rosilene Santos</t>
         </is>
       </c>
       <c r="H1436" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
       <c r="I1436" t="n">
@@ -72540,7 +72540,7 @@
         <v>0</v>
       </c>
       <c r="K1436" t="n">
-        <v>75</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1437">
@@ -72571,23 +72571,27 @@
       </c>
       <c r="F1437" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="G1437" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
-        </is>
-      </c>
-      <c r="H1437" t="inlineStr"/>
+          <t>Cristina Leite</t>
+        </is>
+      </c>
+      <c r="H1437" t="inlineStr">
+        <is>
+          <t>Ricardo Fischer</t>
+        </is>
+      </c>
       <c r="I1437" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1437" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1437" t="n">
-        <v>2</v>
+        <v>77</v>
       </c>
     </row>
     <row r="1438">
@@ -72623,7 +72627,7 @@
       </c>
       <c r="G1438" t="inlineStr">
         <is>
-          <t>Victoria Virgens</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="H1438" t="inlineStr"/>
@@ -72634,7 +72638,7 @@
         <v>0</v>
       </c>
       <c r="K1438" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1439">
@@ -72665,12 +72669,12 @@
       </c>
       <c r="F1439" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="G1439" t="inlineStr">
         <is>
-          <t>Cristiane Simões</t>
+          <t>Victoria Virgens</t>
         </is>
       </c>
       <c r="H1439" t="inlineStr"/>
@@ -72681,7 +72685,7 @@
         <v>0</v>
       </c>
       <c r="K1439" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1440">
@@ -72717,7 +72721,7 @@
       </c>
       <c r="G1440" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Cristiane Simões</t>
         </is>
       </c>
       <c r="H1440" t="inlineStr"/>
@@ -72728,7 +72732,7 @@
         <v>0</v>
       </c>
       <c r="K1440" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1441">
@@ -72764,7 +72768,7 @@
       </c>
       <c r="G1441" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="H1441" t="inlineStr"/>
@@ -72775,7 +72779,7 @@
         <v>0</v>
       </c>
       <c r="K1441" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
     </row>
     <row r="1442">
@@ -72811,7 +72815,7 @@
       </c>
       <c r="G1442" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="H1442" t="inlineStr"/>
@@ -72822,7 +72826,7 @@
         <v>0</v>
       </c>
       <c r="K1442" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1443">
@@ -72848,17 +72852,17 @@
       </c>
       <c r="E1443" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>GOIAS</t>
         </is>
       </c>
       <c r="F1443" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="G1443" t="inlineStr">
         <is>
-          <t>Caroline Alves</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="H1443" t="inlineStr"/>
@@ -72869,7 +72873,7 @@
         <v>0</v>
       </c>
       <c r="K1443" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1444">
@@ -72900,19 +72904,15 @@
       </c>
       <c r="F1444" t="inlineStr">
         <is>
-          <t>RJ - CTB</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="G1444" t="inlineStr">
         <is>
-          <t>Crislaine Maia</t>
-        </is>
-      </c>
-      <c r="H1444" t="inlineStr">
-        <is>
-          <t>Walace Gonçalves|Maicon Costa</t>
-        </is>
-      </c>
+          <t>Caroline Alves</t>
+        </is>
+      </c>
+      <c r="H1444" t="inlineStr"/>
       <c r="I1444" t="n">
         <v>0</v>
       </c>
@@ -72920,7 +72920,7 @@
         <v>0</v>
       </c>
       <c r="K1444" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1445">
@@ -72956,7 +72956,7 @@
       </c>
       <c r="G1445" t="inlineStr">
         <is>
-          <t>Gabriela Lopes</t>
+          <t>Crislaine Maia</t>
         </is>
       </c>
       <c r="H1445" t="inlineStr">
@@ -72971,7 +72971,7 @@
         <v>0</v>
       </c>
       <c r="K1445" t="n">
-        <v>70</v>
+        <v>31</v>
       </c>
     </row>
     <row r="1446">
@@ -73007,7 +73007,7 @@
       </c>
       <c r="G1446" t="inlineStr">
         <is>
-          <t>Jeniffer Cristina</t>
+          <t>Gabriela Lopes</t>
         </is>
       </c>
       <c r="H1446" t="inlineStr">
@@ -73022,7 +73022,7 @@
         <v>0</v>
       </c>
       <c r="K1446" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="1447">
@@ -73058,7 +73058,7 @@
       </c>
       <c r="G1447" t="inlineStr">
         <is>
-          <t>Jessica Roque</t>
+          <t>Jeniffer Cristina</t>
         </is>
       </c>
       <c r="H1447" t="inlineStr">
@@ -73073,7 +73073,7 @@
         <v>0</v>
       </c>
       <c r="K1447" t="n">
-        <v>60</v>
+        <v>76</v>
       </c>
     </row>
     <row r="1448">
@@ -73109,7 +73109,7 @@
       </c>
       <c r="G1448" t="inlineStr">
         <is>
-          <t>Kellem Freitas</t>
+          <t>Jessica Roque</t>
         </is>
       </c>
       <c r="H1448" t="inlineStr">
@@ -73118,13 +73118,13 @@
         </is>
       </c>
       <c r="I1448" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J1448" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K1448" t="n">
-        <v>23</v>
+        <v>64</v>
       </c>
     </row>
     <row r="1449">
@@ -73160,7 +73160,7 @@
       </c>
       <c r="G1449" t="inlineStr">
         <is>
-          <t>Leidiane Paulino</t>
+          <t>Kellem Freitas</t>
         </is>
       </c>
       <c r="H1449" t="inlineStr">
@@ -73175,7 +73175,7 @@
         <v>0</v>
       </c>
       <c r="K1449" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1450">
@@ -73211,7 +73211,7 @@
       </c>
       <c r="G1450" t="inlineStr">
         <is>
-          <t>Leticia Barbosa</t>
+          <t>Leidiane Paulino</t>
         </is>
       </c>
       <c r="H1450" t="inlineStr">
@@ -73226,7 +73226,7 @@
         <v>0</v>
       </c>
       <c r="K1450" t="n">
-        <v>83</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1451">
@@ -73262,7 +73262,7 @@
       </c>
       <c r="G1451" t="inlineStr">
         <is>
-          <t>Luis Junior</t>
+          <t>Leticia Barbosa</t>
         </is>
       </c>
       <c r="H1451" t="inlineStr">
@@ -73277,7 +73277,7 @@
         <v>0</v>
       </c>
       <c r="K1451" t="n">
-        <v>14</v>
+        <v>83</v>
       </c>
     </row>
     <row r="1452">
@@ -73313,7 +73313,7 @@
       </c>
       <c r="G1452" t="inlineStr">
         <is>
-          <t>Nicoly Rodrigues</t>
+          <t>Luis Junior</t>
         </is>
       </c>
       <c r="H1452" t="inlineStr">
@@ -73328,7 +73328,7 @@
         <v>0</v>
       </c>
       <c r="K1452" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1453">
@@ -73364,7 +73364,7 @@
       </c>
       <c r="G1453" t="inlineStr">
         <is>
-          <t>Rafaella Silva</t>
+          <t>Nicoly Rodrigues</t>
         </is>
       </c>
       <c r="H1453" t="inlineStr">
@@ -73379,7 +73379,7 @@
         <v>0</v>
       </c>
       <c r="K1453" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1454">
@@ -73415,7 +73415,7 @@
       </c>
       <c r="G1454" t="inlineStr">
         <is>
-          <t>Rangel Rocha</t>
+          <t>Rafaella Silva</t>
         </is>
       </c>
       <c r="H1454" t="inlineStr">
@@ -73430,7 +73430,7 @@
         <v>0</v>
       </c>
       <c r="K1454" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1455">
@@ -73466,7 +73466,7 @@
       </c>
       <c r="G1455" t="inlineStr">
         <is>
-          <t>Simone Soares</t>
+          <t>Rangel Rocha</t>
         </is>
       </c>
       <c r="H1455" t="inlineStr">
@@ -73481,7 +73481,7 @@
         <v>0</v>
       </c>
       <c r="K1455" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1456">
@@ -73517,7 +73517,7 @@
       </c>
       <c r="G1456" t="inlineStr">
         <is>
-          <t>Suzana Silva</t>
+          <t>Simone Soares</t>
         </is>
       </c>
       <c r="H1456" t="inlineStr">
@@ -73526,13 +73526,13 @@
         </is>
       </c>
       <c r="I1456" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J1456" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K1456" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1457">
@@ -73568,7 +73568,7 @@
       </c>
       <c r="G1457" t="inlineStr">
         <is>
-          <t>Veronica Barbosa</t>
+          <t>Suzana Silva</t>
         </is>
       </c>
       <c r="H1457" t="inlineStr">
@@ -73583,7 +73583,7 @@
         <v>0</v>
       </c>
       <c r="K1457" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="1458">
@@ -73619,7 +73619,7 @@
       </c>
       <c r="G1458" t="inlineStr">
         <is>
-          <t>Vitor Monteiro</t>
+          <t>Veronica Barbosa</t>
         </is>
       </c>
       <c r="H1458" t="inlineStr">
@@ -73628,13 +73628,13 @@
         </is>
       </c>
       <c r="I1458" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J1458" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K1458" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="1459">
@@ -73670,7 +73670,7 @@
       </c>
       <c r="G1459" t="inlineStr">
         <is>
-          <t>Vitoria Silva</t>
+          <t>Vitor Monteiro</t>
         </is>
       </c>
       <c r="H1459" t="inlineStr">
@@ -73685,7 +73685,7 @@
         <v>0</v>
       </c>
       <c r="K1459" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1460">
@@ -73716,11 +73716,19 @@
       </c>
       <c r="F1460" t="inlineStr">
         <is>
-          <t>RJ - DP</t>
-        </is>
-      </c>
-      <c r="G1460" t="inlineStr"/>
-      <c r="H1460" t="inlineStr"/>
+          <t>RJ - CTB</t>
+        </is>
+      </c>
+      <c r="G1460" t="inlineStr">
+        <is>
+          <t>Vitoria Silva</t>
+        </is>
+      </c>
+      <c r="H1460" t="inlineStr">
+        <is>
+          <t>Walace Gonçalves|Maicon Costa</t>
+        </is>
+      </c>
       <c r="I1460" t="n">
         <v>0</v>
       </c>
@@ -73728,7 +73736,7 @@
         <v>0</v>
       </c>
       <c r="K1460" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="1461">
@@ -73762,16 +73770,8 @@
           <t>RJ - DP</t>
         </is>
       </c>
-      <c r="G1461" t="inlineStr">
-        <is>
-          <t>Barbara Mello</t>
-        </is>
-      </c>
-      <c r="H1461" t="inlineStr">
-        <is>
-          <t>Karina Oliveira|Liliane Costa</t>
-        </is>
-      </c>
+      <c r="G1461" t="inlineStr"/>
+      <c r="H1461" t="inlineStr"/>
       <c r="I1461" t="n">
         <v>0</v>
       </c>
@@ -73779,7 +73779,7 @@
         <v>0</v>
       </c>
       <c r="K1461" t="n">
-        <v>105</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1462">
@@ -73815,7 +73815,7 @@
       </c>
       <c r="G1462" t="inlineStr">
         <is>
-          <t>Debora Nunes</t>
+          <t>Barbara Mello</t>
         </is>
       </c>
       <c r="H1462" t="inlineStr">
@@ -73830,7 +73830,7 @@
         <v>0</v>
       </c>
       <c r="K1462" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="1463">
@@ -73866,7 +73866,7 @@
       </c>
       <c r="G1463" t="inlineStr">
         <is>
-          <t>Graziele Almeida</t>
+          <t>Debora Nunes</t>
         </is>
       </c>
       <c r="H1463" t="inlineStr">
@@ -73881,7 +73881,7 @@
         <v>0</v>
       </c>
       <c r="K1463" t="n">
-        <v>88</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1464">
@@ -73917,7 +73917,7 @@
       </c>
       <c r="G1464" t="inlineStr">
         <is>
-          <t>Janiele Ferreira</t>
+          <t>Graziele Almeida</t>
         </is>
       </c>
       <c r="H1464" t="inlineStr">
@@ -73932,7 +73932,7 @@
         <v>0</v>
       </c>
       <c r="K1464" t="n">
-        <v>22</v>
+        <v>88</v>
       </c>
     </row>
     <row r="1465">
@@ -73968,7 +73968,7 @@
       </c>
       <c r="G1465" t="inlineStr">
         <is>
-          <t>Jefferson Barros</t>
+          <t>Janiele Ferreira</t>
         </is>
       </c>
       <c r="H1465" t="inlineStr">
@@ -73983,7 +73983,7 @@
         <v>0</v>
       </c>
       <c r="K1465" t="n">
-        <v>102</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1466">
@@ -74019,7 +74019,7 @@
       </c>
       <c r="G1466" t="inlineStr">
         <is>
-          <t>Karina Oliveira</t>
+          <t>Jefferson Barros</t>
         </is>
       </c>
       <c r="H1466" t="inlineStr">
@@ -74028,13 +74028,13 @@
         </is>
       </c>
       <c r="I1466" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1466" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1466" t="n">
-        <v>31</v>
+        <v>102</v>
       </c>
     </row>
     <row r="1467">
@@ -74070,7 +74070,7 @@
       </c>
       <c r="G1467" t="inlineStr">
         <is>
-          <t>Leonardo Assunção</t>
+          <t>Karina Oliveira</t>
         </is>
       </c>
       <c r="H1467" t="inlineStr">
@@ -74079,13 +74079,13 @@
         </is>
       </c>
       <c r="I1467" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1467" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1467" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="1468">
@@ -74121,7 +74121,7 @@
       </c>
       <c r="G1468" t="inlineStr">
         <is>
-          <t>Liliane Costa</t>
+          <t>Leonardo Assunção</t>
         </is>
       </c>
       <c r="H1468" t="inlineStr">
@@ -74136,7 +74136,7 @@
         <v>0</v>
       </c>
       <c r="K1468" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1469">
@@ -74172,7 +74172,7 @@
       </c>
       <c r="G1469" t="inlineStr">
         <is>
-          <t>Luciene Pimenta</t>
+          <t>Liliane Costa</t>
         </is>
       </c>
       <c r="H1469" t="inlineStr">
@@ -74187,7 +74187,7 @@
         <v>0</v>
       </c>
       <c r="K1469" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1470">
@@ -74223,7 +74223,7 @@
       </c>
       <c r="G1470" t="inlineStr">
         <is>
-          <t>Lucirene Souza</t>
+          <t>Luciene Pimenta</t>
         </is>
       </c>
       <c r="H1470" t="inlineStr">
@@ -74238,7 +74238,7 @@
         <v>0</v>
       </c>
       <c r="K1470" t="n">
-        <v>85</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1471">
@@ -74274,7 +74274,7 @@
       </c>
       <c r="G1471" t="inlineStr">
         <is>
-          <t>Marlon Silva</t>
+          <t>Lucirene Souza</t>
         </is>
       </c>
       <c r="H1471" t="inlineStr">
@@ -74283,13 +74283,13 @@
         </is>
       </c>
       <c r="I1471" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1471" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K1471" t="n">
-        <v>109</v>
+        <v>85</v>
       </c>
     </row>
     <row r="1472">
@@ -74325,7 +74325,7 @@
       </c>
       <c r="G1472" t="inlineStr">
         <is>
-          <t>Monique Britto</t>
+          <t>Marlon Silva</t>
         </is>
       </c>
       <c r="H1472" t="inlineStr">
@@ -74340,7 +74340,7 @@
         <v>0</v>
       </c>
       <c r="K1472" t="n">
-        <v>94</v>
+        <v>109</v>
       </c>
     </row>
     <row r="1473">
@@ -74376,7 +74376,7 @@
       </c>
       <c r="G1473" t="inlineStr">
         <is>
-          <t>Romulo Ferreira</t>
+          <t>Monique Britto</t>
         </is>
       </c>
       <c r="H1473" t="inlineStr">
@@ -74391,7 +74391,7 @@
         <v>0</v>
       </c>
       <c r="K1473" t="n">
-        <v>315</v>
+        <v>94</v>
       </c>
     </row>
     <row r="1474">
@@ -74427,7 +74427,7 @@
       </c>
       <c r="G1474" t="inlineStr">
         <is>
-          <t>Rosilene Silva</t>
+          <t>Romulo Ferreira</t>
         </is>
       </c>
       <c r="H1474" t="inlineStr">
@@ -74442,7 +74442,7 @@
         <v>0</v>
       </c>
       <c r="K1474" t="n">
-        <v>29</v>
+        <v>315</v>
       </c>
     </row>
     <row r="1475">
@@ -74478,7 +74478,7 @@
       </c>
       <c r="G1475" t="inlineStr">
         <is>
-          <t>Thais Santos</t>
+          <t>Rosilene Silva</t>
         </is>
       </c>
       <c r="H1475" t="inlineStr">
@@ -74493,7 +74493,7 @@
         <v>0</v>
       </c>
       <c r="K1475" t="n">
-        <v>113</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1476">
@@ -74529,7 +74529,7 @@
       </c>
       <c r="G1476" t="inlineStr">
         <is>
-          <t>Vitoria Tavares</t>
+          <t>Thais Santos</t>
         </is>
       </c>
       <c r="H1476" t="inlineStr">
@@ -74538,13 +74538,13 @@
         </is>
       </c>
       <c r="I1476" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1476" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1476" t="n">
-        <v>180</v>
+        <v>113</v>
       </c>
     </row>
     <row r="1477">
@@ -74580,7 +74580,7 @@
       </c>
       <c r="G1477" t="inlineStr">
         <is>
-          <t>Viviane Moura</t>
+          <t>Vitoria Tavares</t>
         </is>
       </c>
       <c r="H1477" t="inlineStr">
@@ -74595,7 +74595,7 @@
         <v>0</v>
       </c>
       <c r="K1477" t="n">
-        <v>74</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1478">
@@ -74631,7 +74631,7 @@
       </c>
       <c r="G1478" t="inlineStr">
         <is>
-          <t>Yasmin Lopes</t>
+          <t>Viviane Moura</t>
         </is>
       </c>
       <c r="H1478" t="inlineStr">
@@ -74646,7 +74646,7 @@
         <v>0</v>
       </c>
       <c r="K1478" t="n">
-        <v>123</v>
+        <v>74</v>
       </c>
     </row>
     <row r="1479">
@@ -74677,17 +74677,17 @@
       </c>
       <c r="F1479" t="inlineStr">
         <is>
-          <t>RJ - EF</t>
+          <t>RJ - DP</t>
         </is>
       </c>
       <c r="G1479" t="inlineStr">
         <is>
-          <t>Altamir Nogueira</t>
+          <t>Yasmin Lopes</t>
         </is>
       </c>
       <c r="H1479" t="inlineStr">
         <is>
-          <t>Julio Santos|Jessica Benjamin</t>
+          <t>Karina Oliveira|Liliane Costa</t>
         </is>
       </c>
       <c r="I1479" t="n">
@@ -74697,7 +74697,7 @@
         <v>0</v>
       </c>
       <c r="K1479" t="n">
-        <v>187</v>
+        <v>123</v>
       </c>
     </row>
     <row r="1480">
@@ -74733,7 +74733,7 @@
       </c>
       <c r="G1480" t="inlineStr">
         <is>
-          <t>Beatriz Oliveira</t>
+          <t>Altamir Nogueira</t>
         </is>
       </c>
       <c r="H1480" t="inlineStr">
@@ -74742,13 +74742,13 @@
         </is>
       </c>
       <c r="I1480" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J1480" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="K1480" t="n">
-        <v>116</v>
+        <v>208</v>
       </c>
     </row>
     <row r="1481">
@@ -74784,7 +74784,7 @@
       </c>
       <c r="G1481" t="inlineStr">
         <is>
-          <t>Glaucia Santos</t>
+          <t>Beatriz Oliveira</t>
         </is>
       </c>
       <c r="H1481" t="inlineStr">
@@ -74793,13 +74793,13 @@
         </is>
       </c>
       <c r="I1481" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J1481" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K1481" t="n">
-        <v>144</v>
+        <v>122</v>
       </c>
     </row>
     <row r="1482">
@@ -74835,7 +74835,7 @@
       </c>
       <c r="G1482" t="inlineStr">
         <is>
-          <t>Isabela Barbosa</t>
+          <t>Glaucia Santos</t>
         </is>
       </c>
       <c r="H1482" t="inlineStr">
@@ -74844,13 +74844,13 @@
         </is>
       </c>
       <c r="I1482" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J1482" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K1482" t="n">
-        <v>155</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1483">
@@ -74886,7 +74886,7 @@
       </c>
       <c r="G1483" t="inlineStr">
         <is>
-          <t>Jessica Benjamin</t>
+          <t>Isabela Barbosa</t>
         </is>
       </c>
       <c r="H1483" t="inlineStr">
@@ -74895,13 +74895,13 @@
         </is>
       </c>
       <c r="I1483" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1483" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1483" t="n">
-        <v>125</v>
+        <v>157</v>
       </c>
     </row>
     <row r="1484">
@@ -74937,7 +74937,7 @@
       </c>
       <c r="G1484" t="inlineStr">
         <is>
-          <t>Juliana Perfeito</t>
+          <t>Jessica Benjamin</t>
         </is>
       </c>
       <c r="H1484" t="inlineStr">
@@ -74946,13 +74946,13 @@
         </is>
       </c>
       <c r="I1484" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J1484" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K1484" t="n">
-        <v>92</v>
+        <v>129</v>
       </c>
     </row>
     <row r="1485">
@@ -74988,7 +74988,7 @@
       </c>
       <c r="G1485" t="inlineStr">
         <is>
-          <t>Julio Santos</t>
+          <t>Juliana Perfeito</t>
         </is>
       </c>
       <c r="H1485" t="inlineStr">
@@ -74997,13 +74997,13 @@
         </is>
       </c>
       <c r="I1485" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J1485" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K1485" t="n">
-        <v>1</v>
+        <v>99</v>
       </c>
     </row>
     <row r="1486">
@@ -75039,7 +75039,7 @@
       </c>
       <c r="G1486" t="inlineStr">
         <is>
-          <t>Lais Catrine EF</t>
+          <t>Julio Santos</t>
         </is>
       </c>
       <c r="H1486" t="inlineStr">
@@ -75054,7 +75054,7 @@
         <v>0</v>
       </c>
       <c r="K1486" t="n">
-        <v>210</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1487">
@@ -75090,7 +75090,7 @@
       </c>
       <c r="G1487" t="inlineStr">
         <is>
-          <t>Luana Meneses</t>
+          <t>Lais Catrine EF</t>
         </is>
       </c>
       <c r="H1487" t="inlineStr">
@@ -75099,13 +75099,13 @@
         </is>
       </c>
       <c r="I1487" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J1487" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K1487" t="n">
-        <v>204</v>
+        <v>221</v>
       </c>
     </row>
     <row r="1488">
@@ -75141,7 +75141,7 @@
       </c>
       <c r="G1488" t="inlineStr">
         <is>
-          <t>Otacilia Ferreira</t>
+          <t>Luana Meneses</t>
         </is>
       </c>
       <c r="H1488" t="inlineStr">
@@ -75150,13 +75150,13 @@
         </is>
       </c>
       <c r="I1488" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J1488" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K1488" t="n">
-        <v>104</v>
+        <v>218</v>
       </c>
     </row>
     <row r="1489">
@@ -75192,7 +75192,7 @@
       </c>
       <c r="G1489" t="inlineStr">
         <is>
-          <t>Renata Paixão</t>
+          <t>Otacilia Ferreira</t>
         </is>
       </c>
       <c r="H1489" t="inlineStr">
@@ -75201,13 +75201,13 @@
         </is>
       </c>
       <c r="I1489" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J1489" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K1489" t="n">
-        <v>164</v>
+        <v>113</v>
       </c>
     </row>
     <row r="1490">
@@ -75243,7 +75243,7 @@
       </c>
       <c r="G1490" t="inlineStr">
         <is>
-          <t>Thamara Jordes</t>
+          <t>Renata Paixão</t>
         </is>
       </c>
       <c r="H1490" t="inlineStr">
@@ -75258,7 +75258,7 @@
         <v>0</v>
       </c>
       <c r="K1490" t="n">
-        <v>138</v>
+        <v>164</v>
       </c>
     </row>
     <row r="1491">
@@ -75294,7 +75294,7 @@
       </c>
       <c r="G1491" t="inlineStr">
         <is>
-          <t>Wellington Oliveira</t>
+          <t>Thamara Jordes</t>
         </is>
       </c>
       <c r="H1491" t="inlineStr">
@@ -75303,13 +75303,13 @@
         </is>
       </c>
       <c r="I1491" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1491" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K1491" t="n">
-        <v>202</v>
+        <v>141</v>
       </c>
     </row>
     <row r="1492">
@@ -75340,23 +75340,27 @@
       </c>
       <c r="F1492" t="inlineStr">
         <is>
-          <t>RJ - GC</t>
+          <t>RJ - EF</t>
         </is>
       </c>
       <c r="G1492" t="inlineStr">
         <is>
-          <t>Bruno Mota</t>
-        </is>
-      </c>
-      <c r="H1492" t="inlineStr"/>
+          <t>Wellington Oliveira</t>
+        </is>
+      </c>
+      <c r="H1492" t="inlineStr">
+        <is>
+          <t>Julio Santos|Jessica Benjamin</t>
+        </is>
+      </c>
       <c r="I1492" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1492" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1492" t="n">
-        <v>155</v>
+        <v>204</v>
       </c>
     </row>
     <row r="1493">
@@ -75392,18 +75396,18 @@
       </c>
       <c r="G1493" t="inlineStr">
         <is>
-          <t>Cavalcante Peres</t>
+          <t>Bruno Mota</t>
         </is>
       </c>
       <c r="H1493" t="inlineStr"/>
       <c r="I1493" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1493" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1493" t="n">
-        <v>81</v>
+        <v>155</v>
       </c>
     </row>
     <row r="1494">
@@ -75434,23 +75438,23 @@
       </c>
       <c r="F1494" t="inlineStr">
         <is>
-          <t>RJ - GC ADMINISTRATIVO</t>
+          <t>RJ - GC</t>
         </is>
       </c>
       <c r="G1494" t="inlineStr">
         <is>
-          <t>Amanda Mesquita</t>
+          <t>Cavalcante Peres</t>
         </is>
       </c>
       <c r="H1494" t="inlineStr"/>
       <c r="I1494" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J1494" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K1494" t="n">
-        <v>230</v>
+        <v>87</v>
       </c>
     </row>
     <row r="1495">
@@ -75486,7 +75490,7 @@
       </c>
       <c r="G1495" t="inlineStr">
         <is>
-          <t>Lohany Martins</t>
+          <t>Amanda Mesquita</t>
         </is>
       </c>
       <c r="H1495" t="inlineStr"/>
@@ -75497,7 +75501,7 @@
         <v>0</v>
       </c>
       <c r="K1495" t="n">
-        <v>347</v>
+        <v>230</v>
       </c>
     </row>
     <row r="1496">
@@ -75528,12 +75532,12 @@
       </c>
       <c r="F1496" t="inlineStr">
         <is>
-          <t>S.A.C</t>
+          <t>RJ - GC ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="G1496" t="inlineStr">
         <is>
-          <t>Milena Campos - SAC</t>
+          <t>Lohany Martins</t>
         </is>
       </c>
       <c r="H1496" t="inlineStr"/>
@@ -75544,7 +75548,7 @@
         <v>0</v>
       </c>
       <c r="K1496" t="n">
-        <v>1</v>
+        <v>347</v>
       </c>
     </row>
     <row r="1497">
@@ -75570,24 +75574,20 @@
       </c>
       <c r="E1497" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F1497" t="inlineStr">
         <is>
-          <t>CONTABILIDADE (Outsourcing)</t>
+          <t>S.A.C</t>
         </is>
       </c>
       <c r="G1497" t="inlineStr">
         <is>
-          <t>Aline Petrini</t>
-        </is>
-      </c>
-      <c r="H1497" t="inlineStr">
-        <is>
-          <t>Fernanda Araujo</t>
-        </is>
-      </c>
+          <t>Milena Campos - SAC</t>
+        </is>
+      </c>
+      <c r="H1497" t="inlineStr"/>
       <c r="I1497" t="n">
         <v>0</v>
       </c>
@@ -75595,7 +75595,7 @@
         <v>0</v>
       </c>
       <c r="K1497" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1498">
@@ -75631,12 +75631,12 @@
       </c>
       <c r="G1498" t="inlineStr">
         <is>
-          <t>Daniele Leite</t>
+          <t>Aline Petrini</t>
         </is>
       </c>
       <c r="H1498" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="I1498" t="n">
@@ -75646,7 +75646,7 @@
         <v>0</v>
       </c>
       <c r="K1498" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1499">
@@ -75682,12 +75682,12 @@
       </c>
       <c r="G1499" t="inlineStr">
         <is>
-          <t>Diogo Calazans</t>
+          <t>Daniele Leite</t>
         </is>
       </c>
       <c r="H1499" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I1499" t="n">
@@ -75697,7 +75697,7 @@
         <v>0</v>
       </c>
       <c r="K1499" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1500">
@@ -75733,12 +75733,12 @@
       </c>
       <c r="G1500" t="inlineStr">
         <is>
-          <t>Jaqueline Sousa</t>
+          <t>Diogo Calazans</t>
         </is>
       </c>
       <c r="H1500" t="inlineStr">
         <is>
-          <t>Lucas Fischer</t>
+          <t>Karina Santos</t>
         </is>
       </c>
       <c r="I1500" t="n">
@@ -75748,7 +75748,7 @@
         <v>0</v>
       </c>
       <c r="K1500" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1501">
@@ -75784,12 +75784,12 @@
       </c>
       <c r="G1501" t="inlineStr">
         <is>
-          <t>Patricia Borges</t>
+          <t>Jaqueline Sousa</t>
         </is>
       </c>
       <c r="H1501" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Lucas Fischer</t>
         </is>
       </c>
       <c r="I1501" t="n">
@@ -75835,22 +75835,22 @@
       </c>
       <c r="G1502" t="inlineStr">
         <is>
-          <t>Rejane Coelho</t>
+          <t>Leticia Medeiros</t>
         </is>
       </c>
       <c r="H1502" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Lucas Fischer</t>
         </is>
       </c>
       <c r="I1502" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1502" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1502" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1503">
@@ -75886,12 +75886,12 @@
       </c>
       <c r="G1503" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Patricia Borges</t>
         </is>
       </c>
       <c r="H1503" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I1503" t="n">
@@ -75901,7 +75901,7 @@
         <v>0</v>
       </c>
       <c r="K1503" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1504">
@@ -75937,7 +75937,7 @@
       </c>
       <c r="G1504" t="inlineStr">
         <is>
-          <t>Thiago Ceconelli</t>
+          <t>Rejane Coelho</t>
         </is>
       </c>
       <c r="H1504" t="inlineStr">
@@ -75946,13 +75946,13 @@
         </is>
       </c>
       <c r="I1504" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J1504" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K1504" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1505">
@@ -75983,12 +75983,12 @@
       </c>
       <c r="F1505" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL HOLDING</t>
+          <t>CONTABILIDADE (Outsourcing)</t>
         </is>
       </c>
       <c r="G1505" t="inlineStr">
         <is>
-          <t>Ana Flavia Silva</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="H1505" t="inlineStr">
@@ -76003,7 +76003,7 @@
         <v>0</v>
       </c>
       <c r="K1505" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1506">
@@ -76034,15 +76034,19 @@
       </c>
       <c r="F1506" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL HOLDING</t>
+          <t>CONTABILIDADE (Outsourcing)</t>
         </is>
       </c>
       <c r="G1506" t="inlineStr">
         <is>
-          <t>Daniele Faria</t>
-        </is>
-      </c>
-      <c r="H1506" t="inlineStr"/>
+          <t>Thiago Ceconelli</t>
+        </is>
+      </c>
+      <c r="H1506" t="inlineStr">
+        <is>
+          <t>Karina Santos</t>
+        </is>
+      </c>
       <c r="I1506" t="n">
         <v>0</v>
       </c>
@@ -76050,7 +76054,7 @@
         <v>0</v>
       </c>
       <c r="K1506" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1507">
@@ -76086,7 +76090,7 @@
       </c>
       <c r="G1507" t="inlineStr">
         <is>
-          <t>Vitor de Souza</t>
+          <t>Ana Flavia Silva</t>
         </is>
       </c>
       <c r="H1507" t="inlineStr">
@@ -76095,13 +76099,13 @@
         </is>
       </c>
       <c r="I1507" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J1507" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="K1507" t="n">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="1508">
@@ -76137,14 +76141,10 @@
       </c>
       <c r="G1508" t="inlineStr">
         <is>
-          <t>Vitoria Regina</t>
-        </is>
-      </c>
-      <c r="H1508" t="inlineStr">
-        <is>
-          <t>Tatiana Linardi</t>
-        </is>
-      </c>
+          <t>Daniele Faria</t>
+        </is>
+      </c>
+      <c r="H1508" t="inlineStr"/>
       <c r="I1508" t="n">
         <v>0</v>
       </c>
@@ -76152,7 +76152,7 @@
         <v>0</v>
       </c>
       <c r="K1508" t="n">
-        <v>144</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1509">
@@ -76183,27 +76183,27 @@
       </c>
       <c r="F1509" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL INDUSTRIA</t>
+          <t>CTB - CONTÁBIL HOLDING</t>
         </is>
       </c>
       <c r="G1509" t="inlineStr">
         <is>
-          <t>Adriano Barros</t>
+          <t>Vitor de Souza</t>
         </is>
       </c>
       <c r="H1509" t="inlineStr">
         <is>
-          <t>Erika Santana|Isabella Nascimento</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="I1509" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="J1509" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="K1509" t="n">
-        <v>12</v>
+        <v>206</v>
       </c>
     </row>
     <row r="1510">
@@ -76234,27 +76234,27 @@
       </c>
       <c r="F1510" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL INDUSTRIA</t>
+          <t>CTB - CONTÁBIL HOLDING</t>
         </is>
       </c>
       <c r="G1510" t="inlineStr">
         <is>
-          <t>Bianca Silva</t>
+          <t>Vitoria Regina</t>
         </is>
       </c>
       <c r="H1510" t="inlineStr">
         <is>
-          <t>Erika Santana|Isabella Nascimento</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="I1510" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="J1510" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="K1510" t="n">
-        <v>22</v>
+        <v>219</v>
       </c>
     </row>
     <row r="1511">
@@ -76290,7 +76290,7 @@
       </c>
       <c r="G1511" t="inlineStr">
         <is>
-          <t>Emylle Souza</t>
+          <t>Adriano Barros</t>
         </is>
       </c>
       <c r="H1511" t="inlineStr">
@@ -76305,7 +76305,7 @@
         <v>0</v>
       </c>
       <c r="K1511" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1512">
@@ -76341,7 +76341,7 @@
       </c>
       <c r="G1512" t="inlineStr">
         <is>
-          <t>Fatima Rocha</t>
+          <t>Bianca Silva</t>
         </is>
       </c>
       <c r="H1512" t="inlineStr">
@@ -76350,13 +76350,13 @@
         </is>
       </c>
       <c r="I1512" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J1512" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="K1512" t="n">
-        <v>58</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1513">
@@ -76392,7 +76392,7 @@
       </c>
       <c r="G1513" t="inlineStr">
         <is>
-          <t>Gabriel Correia</t>
+          <t>Emylle Souza</t>
         </is>
       </c>
       <c r="H1513" t="inlineStr">
@@ -76407,7 +76407,7 @@
         <v>0</v>
       </c>
       <c r="K1513" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1514">
@@ -76443,7 +76443,7 @@
       </c>
       <c r="G1514" t="inlineStr">
         <is>
-          <t>Isabella Nascimento</t>
+          <t>Fatima Rocha</t>
         </is>
       </c>
       <c r="H1514" t="inlineStr">
@@ -76458,7 +76458,7 @@
         <v>0</v>
       </c>
       <c r="K1514" t="n">
-        <v>2</v>
+        <v>58</v>
       </c>
     </row>
     <row r="1515">
@@ -76494,7 +76494,7 @@
       </c>
       <c r="G1515" t="inlineStr">
         <is>
-          <t>Laisa Rocha</t>
+          <t>Gabriel Correia</t>
         </is>
       </c>
       <c r="H1515" t="inlineStr">
@@ -76503,13 +76503,13 @@
         </is>
       </c>
       <c r="I1515" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1515" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1515" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="1516">
@@ -76545,7 +76545,7 @@
       </c>
       <c r="G1516" t="inlineStr">
         <is>
-          <t>Lucas Alves</t>
+          <t>Isabella Nascimento</t>
         </is>
       </c>
       <c r="H1516" t="inlineStr">
@@ -76560,7 +76560,7 @@
         <v>0</v>
       </c>
       <c r="K1516" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1517">
@@ -76596,7 +76596,7 @@
       </c>
       <c r="G1517" t="inlineStr">
         <is>
-          <t>Luciana Silva</t>
+          <t>Laisa Rocha</t>
         </is>
       </c>
       <c r="H1517" t="inlineStr">
@@ -76605,13 +76605,13 @@
         </is>
       </c>
       <c r="I1517" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J1517" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K1517" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="1518">
@@ -76647,18 +76647,22 @@
       </c>
       <c r="G1518" t="inlineStr">
         <is>
-          <t>Luiz Ferreira</t>
-        </is>
-      </c>
-      <c r="H1518" t="inlineStr"/>
+          <t>Lucas Alves</t>
+        </is>
+      </c>
+      <c r="H1518" t="inlineStr">
+        <is>
+          <t>Erika Santana|Isabella Nascimento</t>
+        </is>
+      </c>
       <c r="I1518" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1518" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1518" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1519">
@@ -76694,7 +76698,7 @@
       </c>
       <c r="G1519" t="inlineStr">
         <is>
-          <t>Marcus Oliveira</t>
+          <t>Luciana Silva</t>
         </is>
       </c>
       <c r="H1519" t="inlineStr">
@@ -76709,7 +76713,7 @@
         <v>0</v>
       </c>
       <c r="K1519" t="n">
-        <v>58</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1520">
@@ -76745,14 +76749,10 @@
       </c>
       <c r="G1520" t="inlineStr">
         <is>
-          <t>Mariana Pires</t>
-        </is>
-      </c>
-      <c r="H1520" t="inlineStr">
-        <is>
-          <t>Erika Santana|Isabella Nascimento</t>
-        </is>
-      </c>
+          <t>Luiz Ferreira</t>
+        </is>
+      </c>
+      <c r="H1520" t="inlineStr"/>
       <c r="I1520" t="n">
         <v>0</v>
       </c>
@@ -76760,7 +76760,7 @@
         <v>0</v>
       </c>
       <c r="K1520" t="n">
-        <v>36</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1521">
@@ -76796,7 +76796,7 @@
       </c>
       <c r="G1521" t="inlineStr">
         <is>
-          <t>Marta Souza</t>
+          <t>Marcus Oliveira</t>
         </is>
       </c>
       <c r="H1521" t="inlineStr">
@@ -76805,13 +76805,13 @@
         </is>
       </c>
       <c r="I1521" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1521" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1521" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
     </row>
     <row r="1522">
@@ -76847,7 +76847,7 @@
       </c>
       <c r="G1522" t="inlineStr">
         <is>
-          <t>Mateus Miranda</t>
+          <t>Mariana Pires</t>
         </is>
       </c>
       <c r="H1522" t="inlineStr">
@@ -76862,7 +76862,7 @@
         <v>0</v>
       </c>
       <c r="K1522" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
     </row>
     <row r="1523">
@@ -76898,7 +76898,7 @@
       </c>
       <c r="G1523" t="inlineStr">
         <is>
-          <t>Mirian Lima</t>
+          <t>Marta Souza</t>
         </is>
       </c>
       <c r="H1523" t="inlineStr">
@@ -76907,13 +76907,13 @@
         </is>
       </c>
       <c r="I1523" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1523" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1523" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1524">
@@ -76949,7 +76949,7 @@
       </c>
       <c r="G1524" t="inlineStr">
         <is>
-          <t>Nathalia Lourenco</t>
+          <t>Mateus Miranda</t>
         </is>
       </c>
       <c r="H1524" t="inlineStr">
@@ -76964,7 +76964,7 @@
         <v>0</v>
       </c>
       <c r="K1524" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1525">
@@ -77000,7 +77000,7 @@
       </c>
       <c r="G1525" t="inlineStr">
         <is>
-          <t>Nicolas Dias</t>
+          <t>Mirian Lima</t>
         </is>
       </c>
       <c r="H1525" t="inlineStr">
@@ -77015,7 +77015,7 @@
         <v>0</v>
       </c>
       <c r="K1525" t="n">
-        <v>42</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1526">
@@ -77051,7 +77051,7 @@
       </c>
       <c r="G1526" t="inlineStr">
         <is>
-          <t>Rodrigo Nunes</t>
+          <t>Nathalia Lourenco</t>
         </is>
       </c>
       <c r="H1526" t="inlineStr">
@@ -77060,13 +77060,13 @@
         </is>
       </c>
       <c r="I1526" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J1526" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K1526" t="n">
-        <v>12</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1527">
@@ -77102,7 +77102,7 @@
       </c>
       <c r="G1527" t="inlineStr">
         <is>
-          <t>Thais Souza</t>
+          <t>Nicolas Dias</t>
         </is>
       </c>
       <c r="H1527" t="inlineStr">
@@ -77111,13 +77111,13 @@
         </is>
       </c>
       <c r="I1527" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1527" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1527" t="n">
-        <v>13</v>
+        <v>43</v>
       </c>
     </row>
     <row r="1528">
@@ -77153,7 +77153,7 @@
       </c>
       <c r="G1528" t="inlineStr">
         <is>
-          <t>Viviane Guedes</t>
+          <t>Rodrigo Nunes</t>
         </is>
       </c>
       <c r="H1528" t="inlineStr">
@@ -77162,13 +77162,13 @@
         </is>
       </c>
       <c r="I1528" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1528" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1528" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1529">
@@ -77199,17 +77199,17 @@
       </c>
       <c r="F1529" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="G1529" t="inlineStr">
         <is>
-          <t>Aline Petrini</t>
+          <t>Thais Souza</t>
         </is>
       </c>
       <c r="H1529" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Erika Santana|Isabella Nascimento</t>
         </is>
       </c>
       <c r="I1529" t="n">
@@ -77219,7 +77219,7 @@
         <v>0</v>
       </c>
       <c r="K1529" t="n">
-        <v>50</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1530">
@@ -77250,17 +77250,17 @@
       </c>
       <c r="F1530" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="G1530" t="inlineStr">
         <is>
-          <t>Ana Barbosa</t>
+          <t>Viviane Guedes</t>
         </is>
       </c>
       <c r="H1530" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Erika Santana|Isabella Nascimento</t>
         </is>
       </c>
       <c r="I1530" t="n">
@@ -77270,7 +77270,7 @@
         <v>0</v>
       </c>
       <c r="K1530" t="n">
-        <v>46</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1531">
@@ -77306,22 +77306,22 @@
       </c>
       <c r="G1531" t="inlineStr">
         <is>
-          <t>Daniele Leite</t>
+          <t>Aline Petrini</t>
         </is>
       </c>
       <c r="H1531" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="I1531" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1531" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1531" t="n">
-        <v>11</v>
+        <v>51</v>
       </c>
     </row>
     <row r="1532">
@@ -77357,22 +77357,22 @@
       </c>
       <c r="G1532" t="inlineStr">
         <is>
-          <t>Danielle Silva</t>
+          <t>Ana Barbosa</t>
         </is>
       </c>
       <c r="H1532" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I1532" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J1532" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="K1532" t="n">
-        <v>78</v>
+        <v>63</v>
       </c>
     </row>
     <row r="1533">
@@ -77408,22 +77408,22 @@
       </c>
       <c r="G1533" t="inlineStr">
         <is>
-          <t>Danilo Oliveira</t>
+          <t>Daniele Leite</t>
         </is>
       </c>
       <c r="H1533" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I1533" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1533" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1533" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1534">
@@ -77459,22 +77459,22 @@
       </c>
       <c r="G1534" t="inlineStr">
         <is>
-          <t>Debora Silva</t>
+          <t>Danielle Silva</t>
         </is>
       </c>
       <c r="H1534" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Karina Santos</t>
         </is>
       </c>
       <c r="I1534" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1534" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1534" t="n">
-        <v>31</v>
+        <v>79</v>
       </c>
     </row>
     <row r="1535">
@@ -77510,7 +77510,7 @@
       </c>
       <c r="G1535" t="inlineStr">
         <is>
-          <t>Diogo Calazans</t>
+          <t>Danilo Oliveira</t>
         </is>
       </c>
       <c r="H1535" t="inlineStr">
@@ -77519,13 +77519,13 @@
         </is>
       </c>
       <c r="I1535" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1535" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1535" t="n">
-        <v>93</v>
+        <v>37</v>
       </c>
     </row>
     <row r="1536">
@@ -77561,7 +77561,7 @@
       </c>
       <c r="G1536" t="inlineStr">
         <is>
-          <t>Eduardo Cruz</t>
+          <t>Debora Silva</t>
         </is>
       </c>
       <c r="H1536" t="inlineStr">
@@ -77570,13 +77570,13 @@
         </is>
       </c>
       <c r="I1536" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1536" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1536" t="n">
-        <v>83</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1537">
@@ -77612,7 +77612,7 @@
       </c>
       <c r="G1537" t="inlineStr">
         <is>
-          <t>Eveny Silva</t>
+          <t>Diogo Calazans</t>
         </is>
       </c>
       <c r="H1537" t="inlineStr">
@@ -77627,7 +77627,7 @@
         <v>0</v>
       </c>
       <c r="K1537" t="n">
-        <v>49</v>
+        <v>93</v>
       </c>
     </row>
     <row r="1538">
@@ -77663,7 +77663,7 @@
       </c>
       <c r="G1538" t="inlineStr">
         <is>
-          <t>Everton Moura</t>
+          <t>Eduardo Cruz</t>
         </is>
       </c>
       <c r="H1538" t="inlineStr">
@@ -77672,13 +77672,13 @@
         </is>
       </c>
       <c r="I1538" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="J1538" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="K1538" t="n">
-        <v>9</v>
+        <v>118</v>
       </c>
     </row>
     <row r="1539">
@@ -77714,22 +77714,22 @@
       </c>
       <c r="G1539" t="inlineStr">
         <is>
-          <t>Guilherme Dantas</t>
+          <t>Eveny Silva</t>
         </is>
       </c>
       <c r="H1539" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Karina Santos</t>
         </is>
       </c>
       <c r="I1539" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1539" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1539" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1540">
@@ -77765,7 +77765,7 @@
       </c>
       <c r="G1540" t="inlineStr">
         <is>
-          <t>Isabela Lemos</t>
+          <t>Everton Moura</t>
         </is>
       </c>
       <c r="H1540" t="inlineStr">
@@ -77780,7 +77780,7 @@
         <v>0</v>
       </c>
       <c r="K1540" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1541">
@@ -77816,7 +77816,7 @@
       </c>
       <c r="G1541" t="inlineStr">
         <is>
-          <t>Jackson Silva</t>
+          <t>Guilherme Dantas</t>
         </is>
       </c>
       <c r="H1541" t="inlineStr">
@@ -77831,7 +77831,7 @@
         <v>0</v>
       </c>
       <c r="K1541" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1542">
@@ -77867,22 +77867,22 @@
       </c>
       <c r="G1542" t="inlineStr">
         <is>
-          <t>Jaqueline Sousa</t>
+          <t>Isabela Lemos</t>
         </is>
       </c>
       <c r="H1542" t="inlineStr">
         <is>
-          <t>Lucas Fischer</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="I1542" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1542" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1542" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1543">
@@ -77918,22 +77918,22 @@
       </c>
       <c r="G1543" t="inlineStr">
         <is>
-          <t>Leticia Medeiros</t>
+          <t>Jackson Silva</t>
         </is>
       </c>
       <c r="H1543" t="inlineStr">
         <is>
-          <t>Lucas Fischer</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I1543" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1543" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1543" t="n">
-        <v>77</v>
+        <v>56</v>
       </c>
     </row>
     <row r="1544">
@@ -77969,22 +77969,22 @@
       </c>
       <c r="G1544" t="inlineStr">
         <is>
-          <t>Monica Medeiros</t>
+          <t>Jaqueline Sousa</t>
         </is>
       </c>
       <c r="H1544" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Lucas Fischer</t>
         </is>
       </c>
       <c r="I1544" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1544" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1544" t="n">
-        <v>54</v>
+        <v>32</v>
       </c>
     </row>
     <row r="1545">
@@ -78020,7 +78020,7 @@
       </c>
       <c r="G1545" t="inlineStr">
         <is>
-          <t>Naiara Dutra</t>
+          <t>Leticia Medeiros</t>
         </is>
       </c>
       <c r="H1545" t="inlineStr">
@@ -78029,13 +78029,13 @@
         </is>
       </c>
       <c r="I1545" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J1545" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K1545" t="n">
-        <v>26</v>
+        <v>117</v>
       </c>
     </row>
     <row r="1546">
@@ -78071,7 +78071,7 @@
       </c>
       <c r="G1546" t="inlineStr">
         <is>
-          <t>Patricia Borges</t>
+          <t>Monica Medeiros</t>
         </is>
       </c>
       <c r="H1546" t="inlineStr">
@@ -78086,7 +78086,7 @@
         <v>0</v>
       </c>
       <c r="K1546" t="n">
-        <v>38</v>
+        <v>54</v>
       </c>
     </row>
     <row r="1547">
@@ -78122,12 +78122,12 @@
       </c>
       <c r="G1547" t="inlineStr">
         <is>
-          <t>Paulo Silva</t>
+          <t>Naiara Dutra</t>
         </is>
       </c>
       <c r="H1547" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Lucas Fischer</t>
         </is>
       </c>
       <c r="I1547" t="n">
@@ -78137,7 +78137,7 @@
         <v>0</v>
       </c>
       <c r="K1547" t="n">
-        <v>60</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1548">
@@ -78173,7 +78173,7 @@
       </c>
       <c r="G1548" t="inlineStr">
         <is>
-          <t>Rachel Lima</t>
+          <t>Patricia Borges</t>
         </is>
       </c>
       <c r="H1548" t="inlineStr">
@@ -78188,7 +78188,7 @@
         <v>0</v>
       </c>
       <c r="K1548" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
     </row>
     <row r="1549">
@@ -78224,22 +78224,22 @@
       </c>
       <c r="G1549" t="inlineStr">
         <is>
-          <t>Raiane Barbosa</t>
+          <t>Paulo Silva</t>
         </is>
       </c>
       <c r="H1549" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="I1549" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J1549" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K1549" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
     </row>
     <row r="1550">
@@ -78275,12 +78275,12 @@
       </c>
       <c r="G1550" t="inlineStr">
         <is>
-          <t>Rejane Coelho</t>
+          <t>Rachel Lima</t>
         </is>
       </c>
       <c r="H1550" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I1550" t="n">
@@ -78290,7 +78290,7 @@
         <v>0</v>
       </c>
       <c r="K1550" t="n">
-        <v>2</v>
+        <v>65</v>
       </c>
     </row>
     <row r="1551">
@@ -78326,22 +78326,22 @@
       </c>
       <c r="G1551" t="inlineStr">
         <is>
-          <t>Renata Alves - CTV</t>
+          <t>Raiane Barbosa</t>
         </is>
       </c>
       <c r="H1551" t="inlineStr">
         <is>
-          <t>Lucas Fischer</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I1551" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J1551" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K1551" t="n">
-        <v>22</v>
+        <v>115</v>
       </c>
     </row>
     <row r="1552">
@@ -78377,18 +78377,22 @@
       </c>
       <c r="G1552" t="inlineStr">
         <is>
-          <t>Renata Cavalheiro</t>
-        </is>
-      </c>
-      <c r="H1552" t="inlineStr"/>
+          <t>Rejane Coelho</t>
+        </is>
+      </c>
+      <c r="H1552" t="inlineStr">
+        <is>
+          <t>Karina Santos</t>
+        </is>
+      </c>
       <c r="I1552" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J1552" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K1552" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1553">
@@ -78424,12 +78428,12 @@
       </c>
       <c r="G1553" t="inlineStr">
         <is>
-          <t>Ryan Godinho</t>
+          <t>Renata Alves - CTV</t>
         </is>
       </c>
       <c r="H1553" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Lucas Fischer</t>
         </is>
       </c>
       <c r="I1553" t="n">
@@ -78439,7 +78443,7 @@
         <v>0</v>
       </c>
       <c r="K1553" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1554">
@@ -78475,14 +78479,10 @@
       </c>
       <c r="G1554" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
-        </is>
-      </c>
-      <c r="H1554" t="inlineStr">
-        <is>
-          <t>Tatiana Linardi</t>
-        </is>
-      </c>
+          <t>Renata Cavalheiro</t>
+        </is>
+      </c>
+      <c r="H1554" t="inlineStr"/>
       <c r="I1554" t="n">
         <v>0</v>
       </c>
@@ -78490,7 +78490,7 @@
         <v>0</v>
       </c>
       <c r="K1554" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1555">
@@ -78526,12 +78526,12 @@
       </c>
       <c r="G1555" t="inlineStr">
         <is>
-          <t>Vitor Domingues</t>
+          <t>Ryan Godinho</t>
         </is>
       </c>
       <c r="H1555" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Karina Santos</t>
         </is>
       </c>
       <c r="I1555" t="n">
@@ -78541,7 +78541,7 @@
         <v>0</v>
       </c>
       <c r="K1555" t="n">
-        <v>71</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1556">
@@ -78572,24 +78572,24 @@
       </c>
       <c r="F1556" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO PESSOAL (Outsourcing)</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="G1556" t="inlineStr">
         <is>
-          <t>Bruna Santana</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="H1556" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="I1556" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1556" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1556" t="n">
         <v>4</v>
@@ -78623,17 +78623,17 @@
       </c>
       <c r="F1557" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO PESSOAL (Outsourcing)</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="G1557" t="inlineStr">
         <is>
-          <t>Camila Oliveira</t>
+          <t>Vitor Domingues</t>
         </is>
       </c>
       <c r="H1557" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="I1557" t="n">
@@ -78643,7 +78643,7 @@
         <v>0</v>
       </c>
       <c r="K1557" t="n">
-        <v>16</v>
+        <v>71</v>
       </c>
     </row>
     <row r="1558">
@@ -78679,12 +78679,12 @@
       </c>
       <c r="G1558" t="inlineStr">
         <is>
-          <t>Elaine Assis</t>
+          <t>Bruna Santana</t>
         </is>
       </c>
       <c r="H1558" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I1558" t="n">
@@ -78694,7 +78694,7 @@
         <v>0</v>
       </c>
       <c r="K1558" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1559">
@@ -78730,12 +78730,12 @@
       </c>
       <c r="G1559" t="inlineStr">
         <is>
-          <t>Fabiane Branco</t>
+          <t>Camila Oliveira</t>
         </is>
       </c>
       <c r="H1559" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I1559" t="n">
@@ -78745,7 +78745,7 @@
         <v>0</v>
       </c>
       <c r="K1559" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1560">
@@ -78781,12 +78781,12 @@
       </c>
       <c r="G1560" t="inlineStr">
         <is>
-          <t>Jonas Nunes</t>
+          <t>Elaine Assis</t>
         </is>
       </c>
       <c r="H1560" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I1560" t="n">
@@ -78796,7 +78796,7 @@
         <v>0</v>
       </c>
       <c r="K1560" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1561">
@@ -78827,17 +78827,17 @@
       </c>
       <c r="F1561" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>DEPARTAMENTO PESSOAL (Outsourcing)</t>
         </is>
       </c>
       <c r="G1561" t="inlineStr">
         <is>
-          <t>Bruna Santana</t>
+          <t>Fabiane Branco</t>
         </is>
       </c>
       <c r="H1561" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I1561" t="n">
@@ -78847,7 +78847,7 @@
         <v>0</v>
       </c>
       <c r="K1561" t="n">
-        <v>129</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1562">
@@ -78878,12 +78878,12 @@
       </c>
       <c r="F1562" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>DEPARTAMENTO PESSOAL (Outsourcing)</t>
         </is>
       </c>
       <c r="G1562" t="inlineStr">
         <is>
-          <t>Camila Oliveira</t>
+          <t>Jonas Nunes</t>
         </is>
       </c>
       <c r="H1562" t="inlineStr">
@@ -78898,7 +78898,7 @@
         <v>0</v>
       </c>
       <c r="K1562" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1563">
@@ -78934,12 +78934,12 @@
       </c>
       <c r="G1563" t="inlineStr">
         <is>
-          <t>Daniel Moraes</t>
+          <t>Aline Pereira</t>
         </is>
       </c>
       <c r="H1563" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I1563" t="n">
@@ -78949,7 +78949,7 @@
         <v>0</v>
       </c>
       <c r="K1563" t="n">
-        <v>55</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1564">
@@ -78985,12 +78985,12 @@
       </c>
       <c r="G1564" t="inlineStr">
         <is>
-          <t>Danilo Xavier</t>
+          <t>Bruna Santana</t>
         </is>
       </c>
       <c r="H1564" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I1564" t="n">
@@ -79000,7 +79000,7 @@
         <v>0</v>
       </c>
       <c r="K1564" t="n">
-        <v>177</v>
+        <v>129</v>
       </c>
     </row>
     <row r="1565">
@@ -79036,12 +79036,12 @@
       </c>
       <c r="G1565" t="inlineStr">
         <is>
-          <t>Elaine Assis</t>
+          <t>Camila Oliveira</t>
         </is>
       </c>
       <c r="H1565" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I1565" t="n">
@@ -79051,7 +79051,7 @@
         <v>0</v>
       </c>
       <c r="K1565" t="n">
-        <v>67</v>
+        <v>32</v>
       </c>
     </row>
     <row r="1566">
@@ -79087,22 +79087,22 @@
       </c>
       <c r="G1566" t="inlineStr">
         <is>
-          <t>Eliene Lima</t>
+          <t>Daniel Moraes</t>
         </is>
       </c>
       <c r="H1566" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I1566" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J1566" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K1566" t="n">
-        <v>44</v>
+        <v>58</v>
       </c>
     </row>
     <row r="1567">
@@ -79138,7 +79138,7 @@
       </c>
       <c r="G1567" t="inlineStr">
         <is>
-          <t>Erica Oliveira</t>
+          <t>Danilo Xavier</t>
         </is>
       </c>
       <c r="H1567" t="inlineStr">
@@ -79153,7 +79153,7 @@
         <v>0</v>
       </c>
       <c r="K1567" t="n">
-        <v>47</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1568">
@@ -79189,12 +79189,12 @@
       </c>
       <c r="G1568" t="inlineStr">
         <is>
-          <t>Evellin Bispo</t>
+          <t>Elaine Assis</t>
         </is>
       </c>
       <c r="H1568" t="inlineStr">
         <is>
-          <t>Leandro Matos</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I1568" t="n">
@@ -79204,7 +79204,7 @@
         <v>0</v>
       </c>
       <c r="K1568" t="n">
-        <v>42</v>
+        <v>67</v>
       </c>
     </row>
     <row r="1569">
@@ -79240,7 +79240,7 @@
       </c>
       <c r="G1569" t="inlineStr">
         <is>
-          <t>Fabiane Branco</t>
+          <t>Eliene Lima</t>
         </is>
       </c>
       <c r="H1569" t="inlineStr">
@@ -79255,7 +79255,7 @@
         <v>0</v>
       </c>
       <c r="K1569" t="n">
-        <v>134</v>
+        <v>44</v>
       </c>
     </row>
     <row r="1570">
@@ -79291,7 +79291,7 @@
       </c>
       <c r="G1570" t="inlineStr">
         <is>
-          <t>Franciele Alves</t>
+          <t>Erica Oliveira</t>
         </is>
       </c>
       <c r="H1570" t="inlineStr">
@@ -79306,7 +79306,7 @@
         <v>0</v>
       </c>
       <c r="K1570" t="n">
-        <v>85</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1571">
@@ -79342,7 +79342,7 @@
       </c>
       <c r="G1571" t="inlineStr">
         <is>
-          <t>Gabriela Peres</t>
+          <t>Evellin Bispo</t>
         </is>
       </c>
       <c r="H1571" t="inlineStr">
@@ -79351,13 +79351,13 @@
         </is>
       </c>
       <c r="I1571" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J1571" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K1571" t="n">
-        <v>14</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1572">
@@ -79393,22 +79393,22 @@
       </c>
       <c r="G1572" t="inlineStr">
         <is>
-          <t>Grasiele Santos</t>
+          <t>Fabiane Branco</t>
         </is>
       </c>
       <c r="H1572" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I1572" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J1572" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K1572" t="n">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="1573">
@@ -79444,7 +79444,7 @@
       </c>
       <c r="G1573" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Franciele Alves</t>
         </is>
       </c>
       <c r="H1573" t="inlineStr">
@@ -79459,7 +79459,7 @@
         <v>0</v>
       </c>
       <c r="K1573" t="n">
-        <v>230</v>
+        <v>86</v>
       </c>
     </row>
     <row r="1574">
@@ -79495,12 +79495,12 @@
       </c>
       <c r="G1574" t="inlineStr">
         <is>
-          <t>Janaina Rocha</t>
+          <t>Gabriela Peres</t>
         </is>
       </c>
       <c r="H1574" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Leandro Matos</t>
         </is>
       </c>
       <c r="I1574" t="n">
@@ -79510,7 +79510,7 @@
         <v>0</v>
       </c>
       <c r="K1574" t="n">
-        <v>106</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1575">
@@ -79546,12 +79546,12 @@
       </c>
       <c r="G1575" t="inlineStr">
         <is>
-          <t>Jayne Tavares</t>
+          <t>Grasiele Santos</t>
         </is>
       </c>
       <c r="H1575" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I1575" t="n">
@@ -79561,7 +79561,7 @@
         <v>0</v>
       </c>
       <c r="K1575" t="n">
-        <v>127</v>
+        <v>143</v>
       </c>
     </row>
     <row r="1576">
@@ -79597,12 +79597,12 @@
       </c>
       <c r="G1576" t="inlineStr">
         <is>
-          <t>Jhenifer Tenorio</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="H1576" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I1576" t="n">
@@ -79612,7 +79612,7 @@
         <v>0</v>
       </c>
       <c r="K1576" t="n">
-        <v>133</v>
+        <v>230</v>
       </c>
     </row>
     <row r="1577">
@@ -79648,7 +79648,7 @@
       </c>
       <c r="G1577" t="inlineStr">
         <is>
-          <t>Jonas Nunes</t>
+          <t>Janaina Rocha</t>
         </is>
       </c>
       <c r="H1577" t="inlineStr">
@@ -79663,7 +79663,7 @@
         <v>0</v>
       </c>
       <c r="K1577" t="n">
-        <v>114</v>
+        <v>106</v>
       </c>
     </row>
     <row r="1578">
@@ -79699,7 +79699,7 @@
       </c>
       <c r="G1578" t="inlineStr">
         <is>
-          <t>Kaique Souza</t>
+          <t>Jayne Tavares</t>
         </is>
       </c>
       <c r="H1578" t="inlineStr">
@@ -79714,7 +79714,7 @@
         <v>0</v>
       </c>
       <c r="K1578" t="n">
-        <v>106</v>
+        <v>127</v>
       </c>
     </row>
     <row r="1579">
@@ -79750,12 +79750,12 @@
       </c>
       <c r="G1579" t="inlineStr">
         <is>
-          <t>Karine Sousa</t>
+          <t>Jhenifer Tenorio</t>
         </is>
       </c>
       <c r="H1579" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I1579" t="n">
@@ -79765,7 +79765,7 @@
         <v>0</v>
       </c>
       <c r="K1579" t="n">
-        <v>77</v>
+        <v>133</v>
       </c>
     </row>
     <row r="1580">
@@ -79801,7 +79801,7 @@
       </c>
       <c r="G1580" t="inlineStr">
         <is>
-          <t>Laysla Alves</t>
+          <t>Jonas Nunes</t>
         </is>
       </c>
       <c r="H1580" t="inlineStr">
@@ -79816,7 +79816,7 @@
         <v>0</v>
       </c>
       <c r="K1580" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="1581">
@@ -79852,22 +79852,22 @@
       </c>
       <c r="G1581" t="inlineStr">
         <is>
-          <t>Luana Marques</t>
+          <t>Kaique Souza</t>
         </is>
       </c>
       <c r="H1581" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I1581" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="J1581" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="K1581" t="n">
-        <v>19</v>
+        <v>132</v>
       </c>
     </row>
     <row r="1582">
@@ -79903,22 +79903,22 @@
       </c>
       <c r="G1582" t="inlineStr">
         <is>
-          <t>Maria Pires</t>
+          <t>Karine Sousa</t>
         </is>
       </c>
       <c r="H1582" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I1582" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J1582" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K1582" t="n">
-        <v>1</v>
+        <v>81</v>
       </c>
     </row>
     <row r="1583">
@@ -79954,12 +79954,12 @@
       </c>
       <c r="G1583" t="inlineStr">
         <is>
-          <t>Mauricio Lermen</t>
+          <t>Laysla Alves</t>
         </is>
       </c>
       <c r="H1583" t="inlineStr">
         <is>
-          <t>Mauricio Lermen</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I1583" t="n">
@@ -79969,7 +79969,7 @@
         <v>0</v>
       </c>
       <c r="K1583" t="n">
-        <v>14</v>
+        <v>79</v>
       </c>
     </row>
     <row r="1584">
@@ -80005,12 +80005,12 @@
       </c>
       <c r="G1584" t="inlineStr">
         <is>
-          <t>Micaele Cordeiro</t>
+          <t>Luana Marques</t>
         </is>
       </c>
       <c r="H1584" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I1584" t="n">
@@ -80020,7 +80020,7 @@
         <v>0</v>
       </c>
       <c r="K1584" t="n">
-        <v>120</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1585">
@@ -80056,22 +80056,22 @@
       </c>
       <c r="G1585" t="inlineStr">
         <is>
-          <t>Michele Silva</t>
+          <t>Maria Pires</t>
         </is>
       </c>
       <c r="H1585" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I1585" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1585" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1585" t="n">
-        <v>84</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1586">
@@ -80107,10 +80107,14 @@
       </c>
       <c r="G1586" t="inlineStr">
         <is>
-          <t>Mikael Teixeira</t>
-        </is>
-      </c>
-      <c r="H1586" t="inlineStr"/>
+          <t>Mauricio Lermen</t>
+        </is>
+      </c>
+      <c r="H1586" t="inlineStr">
+        <is>
+          <t>Mauricio Lermen</t>
+        </is>
+      </c>
       <c r="I1586" t="n">
         <v>0</v>
       </c>
@@ -80118,7 +80122,7 @@
         <v>0</v>
       </c>
       <c r="K1586" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1587">
@@ -80154,22 +80158,22 @@
       </c>
       <c r="G1587" t="inlineStr">
         <is>
-          <t>Murilo Marques</t>
+          <t>Micaele Cordeiro</t>
         </is>
       </c>
       <c r="H1587" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I1587" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J1587" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K1587" t="n">
-        <v>61</v>
+        <v>134</v>
       </c>
     </row>
     <row r="1588">
@@ -80205,12 +80209,12 @@
       </c>
       <c r="G1588" t="inlineStr">
         <is>
-          <t>Natalia Batista</t>
+          <t>Michele Silva</t>
         </is>
       </c>
       <c r="H1588" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I1588" t="n">
@@ -80220,7 +80224,7 @@
         <v>0</v>
       </c>
       <c r="K1588" t="n">
-        <v>110</v>
+        <v>84</v>
       </c>
     </row>
     <row r="1589">
@@ -80256,14 +80260,10 @@
       </c>
       <c r="G1589" t="inlineStr">
         <is>
-          <t>Natalia Silva</t>
-        </is>
-      </c>
-      <c r="H1589" t="inlineStr">
-        <is>
-          <t>David Bragança</t>
-        </is>
-      </c>
+          <t>Mikael Teixeira</t>
+        </is>
+      </c>
+      <c r="H1589" t="inlineStr"/>
       <c r="I1589" t="n">
         <v>0</v>
       </c>
@@ -80271,7 +80271,7 @@
         <v>0</v>
       </c>
       <c r="K1589" t="n">
-        <v>121</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1590">
@@ -80307,12 +80307,12 @@
       </c>
       <c r="G1590" t="inlineStr">
         <is>
-          <t>Oliene Mariano</t>
+          <t>Murilo Marques</t>
         </is>
       </c>
       <c r="H1590" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I1590" t="n">
@@ -80322,7 +80322,7 @@
         <v>0</v>
       </c>
       <c r="K1590" t="n">
-        <v>97</v>
+        <v>61</v>
       </c>
     </row>
     <row r="1591">
@@ -80358,7 +80358,7 @@
       </c>
       <c r="G1591" t="inlineStr">
         <is>
-          <t>Priscila Aguiar</t>
+          <t>Natalia Batista</t>
         </is>
       </c>
       <c r="H1591" t="inlineStr">
@@ -80367,13 +80367,13 @@
         </is>
       </c>
       <c r="I1591" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J1591" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K1591" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="1592">
@@ -80409,22 +80409,22 @@
       </c>
       <c r="G1592" t="inlineStr">
         <is>
-          <t>Rebeca Ribeiro</t>
+          <t>Natalia Silva</t>
         </is>
       </c>
       <c r="H1592" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I1592" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1592" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1592" t="n">
-        <v>66</v>
+        <v>122</v>
       </c>
     </row>
     <row r="1593">
@@ -80460,12 +80460,12 @@
       </c>
       <c r="G1593" t="inlineStr">
         <is>
-          <t>Roberta Souza</t>
+          <t>Oliene Mariano</t>
         </is>
       </c>
       <c r="H1593" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I1593" t="n">
@@ -80475,7 +80475,7 @@
         <v>0</v>
       </c>
       <c r="K1593" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="1594">
@@ -80511,7 +80511,7 @@
       </c>
       <c r="G1594" t="inlineStr">
         <is>
-          <t>Ronildo Santos</t>
+          <t>Priscila Aguiar</t>
         </is>
       </c>
       <c r="H1594" t="inlineStr">
@@ -80526,7 +80526,7 @@
         <v>0</v>
       </c>
       <c r="K1594" t="n">
-        <v>6</v>
+        <v>112</v>
       </c>
     </row>
     <row r="1595">
@@ -80562,12 +80562,12 @@
       </c>
       <c r="G1595" t="inlineStr">
         <is>
-          <t>Rozania Santos</t>
+          <t>Rebeca Ribeiro</t>
         </is>
       </c>
       <c r="H1595" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I1595" t="n">
@@ -80577,7 +80577,7 @@
         <v>0</v>
       </c>
       <c r="K1595" t="n">
-        <v>147</v>
+        <v>66</v>
       </c>
     </row>
     <row r="1596">
@@ -80613,22 +80613,22 @@
       </c>
       <c r="G1596" t="inlineStr">
         <is>
-          <t>Santos Karina</t>
+          <t>Roberta Souza</t>
         </is>
       </c>
       <c r="H1596" t="inlineStr">
         <is>
-          <t>Leandro Matos</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I1596" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1596" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1596" t="n">
-        <v>3</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1597">
@@ -80664,12 +80664,12 @@
       </c>
       <c r="G1597" t="inlineStr">
         <is>
-          <t>Sibelly Pereira</t>
+          <t>Ronildo Santos</t>
         </is>
       </c>
       <c r="H1597" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I1597" t="n">
@@ -80679,7 +80679,7 @@
         <v>0</v>
       </c>
       <c r="K1597" t="n">
-        <v>118</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1598">
@@ -80715,12 +80715,12 @@
       </c>
       <c r="G1598" t="inlineStr">
         <is>
-          <t>Tania Luz</t>
+          <t>Rozania Santos</t>
         </is>
       </c>
       <c r="H1598" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I1598" t="n">
@@ -80730,7 +80730,7 @@
         <v>0</v>
       </c>
       <c r="K1598" t="n">
-        <v>77</v>
+        <v>147</v>
       </c>
     </row>
     <row r="1599">
@@ -80766,12 +80766,12 @@
       </c>
       <c r="G1599" t="inlineStr">
         <is>
-          <t>Vitor Guedes</t>
+          <t>Santos Karina</t>
         </is>
       </c>
       <c r="H1599" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Leandro Matos</t>
         </is>
       </c>
       <c r="I1599" t="n">
@@ -80781,7 +80781,7 @@
         <v>0</v>
       </c>
       <c r="K1599" t="n">
-        <v>159</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1600">
@@ -80812,27 +80812,27 @@
       </c>
       <c r="F1600" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="G1600" t="inlineStr">
         <is>
-          <t>Andrea Medeiros</t>
+          <t>Sibelly Pereira</t>
         </is>
       </c>
       <c r="H1600" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I1600" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J1600" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K1600" t="n">
-        <v>74</v>
+        <v>121</v>
       </c>
     </row>
     <row r="1601">
@@ -80863,27 +80863,27 @@
       </c>
       <c r="F1601" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="G1601" t="inlineStr">
         <is>
-          <t>Caroline Nascimento</t>
+          <t>Tania Luz</t>
         </is>
       </c>
       <c r="H1601" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I1601" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="J1601" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="K1601" t="n">
-        <v>169</v>
+        <v>125</v>
       </c>
     </row>
     <row r="1602">
@@ -80914,17 +80914,17 @@
       </c>
       <c r="F1602" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="G1602" t="inlineStr">
         <is>
-          <t>Cristiana Grizostomo</t>
+          <t>Vitor Guedes</t>
         </is>
       </c>
       <c r="H1602" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I1602" t="n">
@@ -80934,7 +80934,7 @@
         <v>0</v>
       </c>
       <c r="K1602" t="n">
-        <v>89</v>
+        <v>159</v>
       </c>
     </row>
     <row r="1603">
@@ -80970,18 +80970,22 @@
       </c>
       <c r="G1603" t="inlineStr">
         <is>
-          <t>Denis Reis</t>
-        </is>
-      </c>
-      <c r="H1603" t="inlineStr"/>
+          <t>Andrea Medeiros</t>
+        </is>
+      </c>
+      <c r="H1603" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
       <c r="I1603" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J1603" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K1603" t="n">
-        <v>97</v>
+        <v>78</v>
       </c>
     </row>
     <row r="1604">
@@ -81017,7 +81021,7 @@
       </c>
       <c r="G1604" t="inlineStr">
         <is>
-          <t>Eliane Moreira</t>
+          <t>Caroline Nascimento</t>
         </is>
       </c>
       <c r="H1604" t="inlineStr">
@@ -81032,7 +81036,7 @@
         <v>0</v>
       </c>
       <c r="K1604" t="n">
-        <v>155</v>
+        <v>169</v>
       </c>
     </row>
     <row r="1605">
@@ -81068,7 +81072,7 @@
       </c>
       <c r="G1605" t="inlineStr">
         <is>
-          <t>Gustavo Tonan</t>
+          <t>Cristiana Grizostomo</t>
         </is>
       </c>
       <c r="H1605" t="inlineStr">
@@ -81083,7 +81087,7 @@
         <v>0</v>
       </c>
       <c r="K1605" t="n">
-        <v>127</v>
+        <v>89</v>
       </c>
     </row>
     <row r="1606">
@@ -81119,22 +81123,18 @@
       </c>
       <c r="G1606" t="inlineStr">
         <is>
-          <t>Jonatan Hayashibara</t>
-        </is>
-      </c>
-      <c r="H1606" t="inlineStr">
-        <is>
-          <t>Nayara Oliveira</t>
-        </is>
-      </c>
+          <t>Denis Reis</t>
+        </is>
+      </c>
+      <c r="H1606" t="inlineStr"/>
       <c r="I1606" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J1606" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K1606" t="n">
-        <v>628</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1607">
@@ -81170,7 +81170,7 @@
       </c>
       <c r="G1607" t="inlineStr">
         <is>
-          <t>Lais Arruda</t>
+          <t>Eliane Moreira</t>
         </is>
       </c>
       <c r="H1607" t="inlineStr">
@@ -81179,13 +81179,13 @@
         </is>
       </c>
       <c r="I1607" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1607" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1607" t="n">
-        <v>125</v>
+        <v>155</v>
       </c>
     </row>
     <row r="1608">
@@ -81221,7 +81221,7 @@
       </c>
       <c r="G1608" t="inlineStr">
         <is>
-          <t>Luan Batista</t>
+          <t>Gustavo Tonan</t>
         </is>
       </c>
       <c r="H1608" t="inlineStr">
@@ -81230,13 +81230,13 @@
         </is>
       </c>
       <c r="I1608" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1608" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1608" t="n">
-        <v>104</v>
+        <v>129</v>
       </c>
     </row>
     <row r="1609">
@@ -81272,7 +81272,7 @@
       </c>
       <c r="G1609" t="inlineStr">
         <is>
-          <t>Maria Garcia</t>
+          <t>Jonatan Hayashibara</t>
         </is>
       </c>
       <c r="H1609" t="inlineStr">
@@ -81281,13 +81281,13 @@
         </is>
       </c>
       <c r="I1609" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1609" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1609" t="n">
-        <v>99</v>
+        <v>630</v>
       </c>
     </row>
     <row r="1610">
@@ -81323,7 +81323,7 @@
       </c>
       <c r="G1610" t="inlineStr">
         <is>
-          <t>Priscila Volpe</t>
+          <t>Lais Arruda</t>
         </is>
       </c>
       <c r="H1610" t="inlineStr">
@@ -81332,13 +81332,13 @@
         </is>
       </c>
       <c r="I1610" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J1610" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K1610" t="n">
-        <v>18</v>
+        <v>135</v>
       </c>
     </row>
     <row r="1611">
@@ -81374,7 +81374,7 @@
       </c>
       <c r="G1611" t="inlineStr">
         <is>
-          <t>Rodrigo Souza</t>
+          <t>Luan Batista</t>
         </is>
       </c>
       <c r="H1611" t="inlineStr">
@@ -81383,13 +81383,13 @@
         </is>
       </c>
       <c r="I1611" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1611" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1611" t="n">
-        <v>135</v>
+        <v>106</v>
       </c>
     </row>
     <row r="1612">
@@ -81425,7 +81425,7 @@
       </c>
       <c r="G1612" t="inlineStr">
         <is>
-          <t>Romario Silva</t>
+          <t>Maria Garcia</t>
         </is>
       </c>
       <c r="H1612" t="inlineStr">
@@ -81434,13 +81434,13 @@
         </is>
       </c>
       <c r="I1612" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1612" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K1612" t="n">
-        <v>271</v>
+        <v>101</v>
       </c>
     </row>
     <row r="1613">
@@ -81476,7 +81476,7 @@
       </c>
       <c r="G1613" t="inlineStr">
         <is>
-          <t>Rosilene Santos</t>
+          <t>Priscila Volpe</t>
         </is>
       </c>
       <c r="H1613" t="inlineStr">
@@ -81491,7 +81491,7 @@
         <v>0</v>
       </c>
       <c r="K1613" t="n">
-        <v>82</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1614">
@@ -81527,7 +81527,7 @@
       </c>
       <c r="G1614" t="inlineStr">
         <is>
-          <t>Suede Gomes</t>
+          <t>Rodrigo Souza</t>
         </is>
       </c>
       <c r="H1614" t="inlineStr">
@@ -81542,7 +81542,7 @@
         <v>0</v>
       </c>
       <c r="K1614" t="n">
-        <v>64</v>
+        <v>135</v>
       </c>
     </row>
     <row r="1615">
@@ -81578,7 +81578,7 @@
       </c>
       <c r="G1615" t="inlineStr">
         <is>
-          <t>Taina Silva</t>
+          <t>Romario Silva</t>
         </is>
       </c>
       <c r="H1615" t="inlineStr">
@@ -81587,13 +81587,13 @@
         </is>
       </c>
       <c r="I1615" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1615" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1615" t="n">
-        <v>71</v>
+        <v>272</v>
       </c>
     </row>
     <row r="1616">
@@ -81629,7 +81629,7 @@
       </c>
       <c r="G1616" t="inlineStr">
         <is>
-          <t>Thayna Melo</t>
+          <t>Rosilene Santos</t>
         </is>
       </c>
       <c r="H1616" t="inlineStr">
@@ -81644,7 +81644,7 @@
         <v>0</v>
       </c>
       <c r="K1616" t="n">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="1617">
@@ -81680,7 +81680,7 @@
       </c>
       <c r="G1617" t="inlineStr">
         <is>
-          <t>Vanessa Santana</t>
+          <t>Suede Gomes</t>
         </is>
       </c>
       <c r="H1617" t="inlineStr">
@@ -81695,7 +81695,7 @@
         <v>0</v>
       </c>
       <c r="K1617" t="n">
-        <v>195</v>
+        <v>64</v>
       </c>
     </row>
     <row r="1618">
@@ -81726,17 +81726,17 @@
       </c>
       <c r="F1618" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="G1618" t="inlineStr">
         <is>
-          <t>Alaine Neres</t>
+          <t>Taina Silva</t>
         </is>
       </c>
       <c r="H1618" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
       <c r="I1618" t="n">
@@ -81746,7 +81746,7 @@
         <v>0</v>
       </c>
       <c r="K1618" t="n">
-        <v>173</v>
+        <v>71</v>
       </c>
     </row>
     <row r="1619">
@@ -81777,17 +81777,17 @@
       </c>
       <c r="F1619" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="G1619" t="inlineStr">
         <is>
-          <t>Andre Silva</t>
+          <t>Thayna Melo</t>
         </is>
       </c>
       <c r="H1619" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
       <c r="I1619" t="n">
@@ -81797,7 +81797,7 @@
         <v>0</v>
       </c>
       <c r="K1619" t="n">
-        <v>88</v>
+        <v>72</v>
       </c>
     </row>
     <row r="1620">
@@ -81828,17 +81828,17 @@
       </c>
       <c r="F1620" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="G1620" t="inlineStr">
         <is>
-          <t>Anna Ramalho</t>
+          <t>Vanessa Santana</t>
         </is>
       </c>
       <c r="H1620" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
       <c r="I1620" t="n">
@@ -81848,7 +81848,7 @@
         <v>0</v>
       </c>
       <c r="K1620" t="n">
-        <v>95</v>
+        <v>195</v>
       </c>
     </row>
     <row r="1621">
@@ -81884,22 +81884,22 @@
       </c>
       <c r="G1621" t="inlineStr">
         <is>
-          <t>Beatriz Ferreira</t>
+          <t>Alaine Neres</t>
         </is>
       </c>
       <c r="H1621" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I1621" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J1621" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K1621" t="n">
-        <v>160</v>
+        <v>190</v>
       </c>
     </row>
     <row r="1622">
@@ -81935,7 +81935,7 @@
       </c>
       <c r="G1622" t="inlineStr">
         <is>
-          <t>Brenda Batista</t>
+          <t>Andre Silva</t>
         </is>
       </c>
       <c r="H1622" t="inlineStr">
@@ -81944,13 +81944,13 @@
         </is>
       </c>
       <c r="I1622" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J1622" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K1622" t="n">
-        <v>66</v>
+        <v>105</v>
       </c>
     </row>
     <row r="1623">
@@ -81986,22 +81986,22 @@
       </c>
       <c r="G1623" t="inlineStr">
         <is>
-          <t>Bruna Souza</t>
+          <t>Anna Ramalho</t>
         </is>
       </c>
       <c r="H1623" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="I1623" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1623" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1623" t="n">
-        <v>85</v>
+        <v>96</v>
       </c>
     </row>
     <row r="1624">
@@ -82037,22 +82037,22 @@
       </c>
       <c r="G1624" t="inlineStr">
         <is>
-          <t>Bruno Henrique</t>
+          <t>Beatriz Ferreira</t>
         </is>
       </c>
       <c r="H1624" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="I1624" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1624" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1624" t="n">
-        <v>144</v>
+        <v>160</v>
       </c>
     </row>
     <row r="1625">
@@ -82088,18 +82088,22 @@
       </c>
       <c r="G1625" t="inlineStr">
         <is>
-          <t>Claudineia Rodrigues</t>
-        </is>
-      </c>
-      <c r="H1625" t="inlineStr"/>
+          <t>Brenda Batista</t>
+        </is>
+      </c>
+      <c r="H1625" t="inlineStr">
+        <is>
+          <t>Larice Souza</t>
+        </is>
+      </c>
       <c r="I1625" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1625" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1625" t="n">
-        <v>200</v>
+        <v>66</v>
       </c>
     </row>
     <row r="1626">
@@ -82135,22 +82139,22 @@
       </c>
       <c r="G1626" t="inlineStr">
         <is>
-          <t>Cristina Leite</t>
+          <t>Bruna Souza</t>
         </is>
       </c>
       <c r="H1626" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I1626" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1626" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1626" t="n">
-        <v>157</v>
+        <v>87</v>
       </c>
     </row>
     <row r="1627">
@@ -82186,22 +82190,22 @@
       </c>
       <c r="G1627" t="inlineStr">
         <is>
-          <t>Davi Santos</t>
+          <t>Bruno Henrique</t>
         </is>
       </c>
       <c r="H1627" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I1627" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J1627" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K1627" t="n">
-        <v>103</v>
+        <v>149</v>
       </c>
     </row>
     <row r="1628">
@@ -82237,14 +82241,10 @@
       </c>
       <c r="G1628" t="inlineStr">
         <is>
-          <t>Deleia Oliveira</t>
-        </is>
-      </c>
-      <c r="H1628" t="inlineStr">
-        <is>
-          <t>Lorrane Santos</t>
-        </is>
-      </c>
+          <t>Claudineia Rodrigues</t>
+        </is>
+      </c>
+      <c r="H1628" t="inlineStr"/>
       <c r="I1628" t="n">
         <v>0</v>
       </c>
@@ -82252,7 +82252,7 @@
         <v>0</v>
       </c>
       <c r="K1628" t="n">
-        <v>139</v>
+        <v>202</v>
       </c>
     </row>
     <row r="1629">
@@ -82288,22 +82288,22 @@
       </c>
       <c r="G1629" t="inlineStr">
         <is>
-          <t>Diego Pereira</t>
+          <t>Cristina Leite</t>
         </is>
       </c>
       <c r="H1629" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="I1629" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1629" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1629" t="n">
-        <v>110</v>
+        <v>159</v>
       </c>
     </row>
     <row r="1630">
@@ -82339,22 +82339,22 @@
       </c>
       <c r="G1630" t="inlineStr">
         <is>
-          <t>Eduardo Lopes</t>
+          <t>Davi Santos</t>
         </is>
       </c>
       <c r="H1630" t="inlineStr">
         <is>
-          <t>Idna Sousa</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I1630" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="J1630" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="K1630" t="n">
-        <v>57</v>
+        <v>130</v>
       </c>
     </row>
     <row r="1631">
@@ -82390,7 +82390,7 @@
       </c>
       <c r="G1631" t="inlineStr">
         <is>
-          <t>Gislaine Lima</t>
+          <t>Deleia Oliveira</t>
         </is>
       </c>
       <c r="H1631" t="inlineStr">
@@ -82399,13 +82399,13 @@
         </is>
       </c>
       <c r="I1631" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J1631" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K1631" t="n">
-        <v>103</v>
+        <v>143</v>
       </c>
     </row>
     <row r="1632">
@@ -82441,22 +82441,22 @@
       </c>
       <c r="G1632" t="inlineStr">
         <is>
-          <t>Gustavo Santos</t>
+          <t>Diego Pereira</t>
         </is>
       </c>
       <c r="H1632" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I1632" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1632" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1632" t="n">
-        <v>232</v>
+        <v>112</v>
       </c>
     </row>
     <row r="1633">
@@ -82492,22 +82492,22 @@
       </c>
       <c r="G1633" t="inlineStr">
         <is>
-          <t>Igor Valezi</t>
+          <t>Eduardo Lopes</t>
         </is>
       </c>
       <c r="H1633" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Idna Sousa</t>
         </is>
       </c>
       <c r="I1633" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1633" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1633" t="n">
-        <v>101</v>
+        <v>58</v>
       </c>
     </row>
     <row r="1634">
@@ -82543,22 +82543,22 @@
       </c>
       <c r="G1634" t="inlineStr">
         <is>
-          <t>Izabely Araujo</t>
+          <t>Gislaine Lima</t>
         </is>
       </c>
       <c r="H1634" t="inlineStr">
         <is>
-          <t>Idna Sousa</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I1634" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1634" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1634" t="n">
-        <v>55</v>
+        <v>105</v>
       </c>
     </row>
     <row r="1635">
@@ -82594,22 +82594,22 @@
       </c>
       <c r="G1635" t="inlineStr">
         <is>
-          <t>Joanna Costa</t>
+          <t>Gustavo Santos</t>
         </is>
       </c>
       <c r="H1635" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="I1635" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="J1635" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="K1635" t="n">
-        <v>31</v>
+        <v>265</v>
       </c>
     </row>
     <row r="1636">
@@ -82645,7 +82645,7 @@
       </c>
       <c r="G1636" t="inlineStr">
         <is>
-          <t>Jose Natan</t>
+          <t>Igor Valezi</t>
         </is>
       </c>
       <c r="H1636" t="inlineStr">
@@ -82660,7 +82660,7 @@
         <v>0</v>
       </c>
       <c r="K1636" t="n">
-        <v>108</v>
+        <v>101</v>
       </c>
     </row>
     <row r="1637">
@@ -82696,22 +82696,22 @@
       </c>
       <c r="G1637" t="inlineStr">
         <is>
-          <t>João Oliveira</t>
+          <t>Izabely Araujo</t>
         </is>
       </c>
       <c r="H1637" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Idna Sousa</t>
         </is>
       </c>
       <c r="I1637" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1637" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1637" t="n">
-        <v>21</v>
+        <v>57</v>
       </c>
     </row>
     <row r="1638">
@@ -82747,7 +82747,7 @@
       </c>
       <c r="G1638" t="inlineStr">
         <is>
-          <t>Juan Ribeiro</t>
+          <t>Joanna Costa</t>
         </is>
       </c>
       <c r="H1638" t="inlineStr">
@@ -82762,7 +82762,7 @@
         <v>0</v>
       </c>
       <c r="K1638" t="n">
-        <v>94</v>
+        <v>32</v>
       </c>
     </row>
     <row r="1639">
@@ -82798,7 +82798,7 @@
       </c>
       <c r="G1639" t="inlineStr">
         <is>
-          <t>Juliana Valeria</t>
+          <t>Jose Natan</t>
         </is>
       </c>
       <c r="H1639" t="inlineStr">
@@ -82807,13 +82807,13 @@
         </is>
       </c>
       <c r="I1639" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J1639" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K1639" t="n">
-        <v>137</v>
+        <v>123</v>
       </c>
     </row>
     <row r="1640">
@@ -82849,7 +82849,7 @@
       </c>
       <c r="G1640" t="inlineStr">
         <is>
-          <t>Juliane Vaz</t>
+          <t>João Oliveira</t>
         </is>
       </c>
       <c r="H1640" t="inlineStr">
@@ -82864,7 +82864,7 @@
         <v>0</v>
       </c>
       <c r="K1640" t="n">
-        <v>290</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1641">
@@ -82900,22 +82900,22 @@
       </c>
       <c r="G1641" t="inlineStr">
         <is>
-          <t>Katia Xavier</t>
+          <t>Juan Ribeiro</t>
         </is>
       </c>
       <c r="H1641" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I1641" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1641" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1641" t="n">
-        <v>112</v>
+        <v>96</v>
       </c>
     </row>
     <row r="1642">
@@ -82951,22 +82951,22 @@
       </c>
       <c r="G1642" t="inlineStr">
         <is>
-          <t>Larissa Félix</t>
+          <t>Juliana Valeria</t>
         </is>
       </c>
       <c r="H1642" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I1642" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J1642" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K1642" t="n">
-        <v>215</v>
+        <v>143</v>
       </c>
     </row>
     <row r="1643">
@@ -83002,22 +83002,22 @@
       </c>
       <c r="G1643" t="inlineStr">
         <is>
-          <t>Léia de Oliveira</t>
+          <t>Juliane Vaz</t>
         </is>
       </c>
       <c r="H1643" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I1643" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1643" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1643" t="n">
-        <v>130</v>
+        <v>292</v>
       </c>
     </row>
     <row r="1644">
@@ -83053,7 +83053,7 @@
       </c>
       <c r="G1644" t="inlineStr">
         <is>
-          <t>Maria Gualberto</t>
+          <t>Katia Xavier</t>
         </is>
       </c>
       <c r="H1644" t="inlineStr">
@@ -83062,13 +83062,13 @@
         </is>
       </c>
       <c r="I1644" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1644" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1644" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="1645">
@@ -83104,22 +83104,22 @@
       </c>
       <c r="G1645" t="inlineStr">
         <is>
-          <t>Priscila Moreira</t>
+          <t>Larissa Félix</t>
         </is>
       </c>
       <c r="H1645" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I1645" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1645" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1645" t="n">
-        <v>143</v>
+        <v>216</v>
       </c>
     </row>
     <row r="1646">
@@ -83155,22 +83155,22 @@
       </c>
       <c r="G1646" t="inlineStr">
         <is>
-          <t>Regiane Santos</t>
+          <t>Léia de Oliveira</t>
         </is>
       </c>
       <c r="H1646" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I1646" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1646" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1646" t="n">
-        <v>67</v>
+        <v>132</v>
       </c>
     </row>
     <row r="1647">
@@ -83206,12 +83206,12 @@
       </c>
       <c r="G1647" t="inlineStr">
         <is>
-          <t>Shofia Gomes</t>
+          <t>Maria Gualberto</t>
         </is>
       </c>
       <c r="H1647" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I1647" t="n">
@@ -83221,7 +83221,7 @@
         <v>0</v>
       </c>
       <c r="K1647" t="n">
-        <v>135</v>
+        <v>110</v>
       </c>
     </row>
     <row r="1648">
@@ -83257,22 +83257,22 @@
       </c>
       <c r="G1648" t="inlineStr">
         <is>
-          <t>Vanessa Tavares</t>
+          <t>Nathany Silva</t>
         </is>
       </c>
       <c r="H1648" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I1648" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1648" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K1648" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1649">
@@ -83308,22 +83308,22 @@
       </c>
       <c r="G1649" t="inlineStr">
         <is>
-          <t>Willian Luz</t>
+          <t>Priscila Moreira</t>
         </is>
       </c>
       <c r="H1649" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="I1649" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1649" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1649" t="n">
-        <v>88</v>
+        <v>144</v>
       </c>
     </row>
     <row r="1650">
@@ -83359,7 +83359,7 @@
       </c>
       <c r="G1650" t="inlineStr">
         <is>
-          <t>Yasmim Oliveira</t>
+          <t>Regiane Santos</t>
         </is>
       </c>
       <c r="H1650" t="inlineStr">
@@ -83368,13 +83368,13 @@
         </is>
       </c>
       <c r="I1650" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1650" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1650" t="n">
-        <v>46</v>
+        <v>68</v>
       </c>
     </row>
     <row r="1651">
@@ -83405,15 +83405,19 @@
       </c>
       <c r="F1651" t="inlineStr">
         <is>
-          <t>ESCRITA FISCAL (Outsourcing)</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="G1651" t="inlineStr">
         <is>
-          <t>Claudineia Rodrigues</t>
-        </is>
-      </c>
-      <c r="H1651" t="inlineStr"/>
+          <t>Shofia Gomes</t>
+        </is>
+      </c>
+      <c r="H1651" t="inlineStr">
+        <is>
+          <t>Ricardo Fischer</t>
+        </is>
+      </c>
       <c r="I1651" t="n">
         <v>0</v>
       </c>
@@ -83421,7 +83425,7 @@
         <v>0</v>
       </c>
       <c r="K1651" t="n">
-        <v>5</v>
+        <v>135</v>
       </c>
     </row>
     <row r="1652">
@@ -83452,17 +83456,17 @@
       </c>
       <c r="F1652" t="inlineStr">
         <is>
-          <t>ESCRITA FISCAL (Outsourcing)</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="G1652" t="inlineStr">
         <is>
-          <t>Diego Pereira</t>
+          <t>Vanessa Tavares</t>
         </is>
       </c>
       <c r="H1652" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I1652" t="n">
@@ -83472,7 +83476,7 @@
         <v>0</v>
       </c>
       <c r="K1652" t="n">
-        <v>9</v>
+        <v>88</v>
       </c>
     </row>
     <row r="1653">
@@ -83503,27 +83507,27 @@
       </c>
       <c r="F1653" t="inlineStr">
         <is>
-          <t>ESCRITA FISCAL (Outsourcing)</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="G1653" t="inlineStr">
         <is>
-          <t>Gislaine Lima</t>
+          <t>Willian Luz</t>
         </is>
       </c>
       <c r="H1653" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I1653" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1653" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1653" t="n">
-        <v>37</v>
+        <v>89</v>
       </c>
     </row>
     <row r="1654">
@@ -83554,17 +83558,17 @@
       </c>
       <c r="F1654" t="inlineStr">
         <is>
-          <t>ESCRITA FISCAL (Outsourcing)</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="G1654" t="inlineStr">
         <is>
-          <t>Joanna Costa</t>
+          <t>Yasmim Oliveira</t>
         </is>
       </c>
       <c r="H1654" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I1654" t="n">
@@ -83574,7 +83578,7 @@
         <v>0</v>
       </c>
       <c r="K1654" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1655">
@@ -83610,14 +83614,10 @@
       </c>
       <c r="G1655" t="inlineStr">
         <is>
-          <t>Jonatan Hayashibara</t>
-        </is>
-      </c>
-      <c r="H1655" t="inlineStr">
-        <is>
-          <t>Nayara Oliveira</t>
-        </is>
-      </c>
+          <t>Claudineia Rodrigues</t>
+        </is>
+      </c>
+      <c r="H1655" t="inlineStr"/>
       <c r="I1655" t="n">
         <v>0</v>
       </c>
@@ -83625,7 +83625,7 @@
         <v>0</v>
       </c>
       <c r="K1655" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1656">
@@ -83661,12 +83661,12 @@
       </c>
       <c r="G1656" t="inlineStr">
         <is>
-          <t>João Oliveira</t>
+          <t>Diego Pereira</t>
         </is>
       </c>
       <c r="H1656" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I1656" t="n">
@@ -83676,7 +83676,7 @@
         <v>0</v>
       </c>
       <c r="K1656" t="n">
-        <v>55</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1657">
@@ -83712,12 +83712,12 @@
       </c>
       <c r="G1657" t="inlineStr">
         <is>
-          <t>Regiane Santos</t>
+          <t>Gislaine Lima</t>
         </is>
       </c>
       <c r="H1657" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I1657" t="n">
@@ -83727,7 +83727,7 @@
         <v>0</v>
       </c>
       <c r="K1657" t="n">
-        <v>18</v>
+        <v>37</v>
       </c>
     </row>
     <row r="1658">
@@ -83763,12 +83763,12 @@
       </c>
       <c r="G1658" t="inlineStr">
         <is>
-          <t>Yasmim Oliveira</t>
+          <t>Joanna Costa</t>
         </is>
       </c>
       <c r="H1658" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I1658" t="n">
@@ -83778,7 +83778,7 @@
         <v>0</v>
       </c>
       <c r="K1658" t="n">
-        <v>7</v>
+        <v>60</v>
       </c>
     </row>
     <row r="1659">
@@ -83809,15 +83809,19 @@
       </c>
       <c r="F1659" t="inlineStr">
         <is>
-          <t>FIN - CONTÁBIL</t>
+          <t>ESCRITA FISCAL (Outsourcing)</t>
         </is>
       </c>
       <c r="G1659" t="inlineStr">
         <is>
-          <t>Daniele Faria</t>
-        </is>
-      </c>
-      <c r="H1659" t="inlineStr"/>
+          <t>Jonatan Hayashibara</t>
+        </is>
+      </c>
+      <c r="H1659" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
       <c r="I1659" t="n">
         <v>0</v>
       </c>
@@ -83825,7 +83829,7 @@
         <v>0</v>
       </c>
       <c r="K1659" t="n">
-        <v>77</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1660">
@@ -83856,23 +83860,27 @@
       </c>
       <c r="F1660" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>ESCRITA FISCAL (Outsourcing)</t>
         </is>
       </c>
       <c r="G1660" t="inlineStr">
         <is>
-          <t>Ana Santana</t>
-        </is>
-      </c>
-      <c r="H1660" t="inlineStr"/>
+          <t>João Oliveira</t>
+        </is>
+      </c>
+      <c r="H1660" t="inlineStr">
+        <is>
+          <t>Larice Souza</t>
+        </is>
+      </c>
       <c r="I1660" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J1660" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K1660" t="n">
-        <v>588</v>
+        <v>70</v>
       </c>
     </row>
     <row r="1661">
@@ -83903,23 +83911,27 @@
       </c>
       <c r="F1661" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>ESCRITA FISCAL (Outsourcing)</t>
         </is>
       </c>
       <c r="G1661" t="inlineStr">
         <is>
-          <t>Andre Coelho</t>
-        </is>
-      </c>
-      <c r="H1661" t="inlineStr"/>
+          <t>Regiane Santos</t>
+        </is>
+      </c>
+      <c r="H1661" t="inlineStr">
+        <is>
+          <t>Larice Souza</t>
+        </is>
+      </c>
       <c r="I1661" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1661" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1661" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1662">
@@ -83950,15 +83962,19 @@
       </c>
       <c r="F1662" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>ESCRITA FISCAL (Outsourcing)</t>
         </is>
       </c>
       <c r="G1662" t="inlineStr">
         <is>
-          <t>Bianca Castro</t>
-        </is>
-      </c>
-      <c r="H1662" t="inlineStr"/>
+          <t>Yasmim Oliveira</t>
+        </is>
+      </c>
+      <c r="H1662" t="inlineStr">
+        <is>
+          <t>Larice Souza</t>
+        </is>
+      </c>
       <c r="I1662" t="n">
         <v>0</v>
       </c>
@@ -83966,7 +83982,7 @@
         <v>0</v>
       </c>
       <c r="K1662" t="n">
-        <v>459</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1663">
@@ -83997,12 +84013,12 @@
       </c>
       <c r="F1663" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>FIN - CONTÁBIL</t>
         </is>
       </c>
       <c r="G1663" t="inlineStr">
         <is>
-          <t>Bruna Costa</t>
+          <t>Daniele Faria</t>
         </is>
       </c>
       <c r="H1663" t="inlineStr"/>
@@ -84013,7 +84029,7 @@
         <v>0</v>
       </c>
       <c r="K1663" t="n">
-        <v>34</v>
+        <v>77</v>
       </c>
     </row>
     <row r="1664">
@@ -84049,7 +84065,7 @@
       </c>
       <c r="G1664" t="inlineStr">
         <is>
-          <t>Daniela Silva</t>
+          <t>Ana Santana</t>
         </is>
       </c>
       <c r="H1664" t="inlineStr"/>
@@ -84060,7 +84076,7 @@
         <v>0</v>
       </c>
       <c r="K1664" t="n">
-        <v>302</v>
+        <v>588</v>
       </c>
     </row>
     <row r="1665">
@@ -84096,7 +84112,7 @@
       </c>
       <c r="G1665" t="inlineStr">
         <is>
-          <t>Isabelli Afonso</t>
+          <t>Andre Coelho</t>
         </is>
       </c>
       <c r="H1665" t="inlineStr"/>
@@ -84107,7 +84123,7 @@
         <v>0</v>
       </c>
       <c r="K1665" t="n">
-        <v>234</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1666">
@@ -84143,18 +84159,18 @@
       </c>
       <c r="G1666" t="inlineStr">
         <is>
-          <t>Jurema Damacena - SAC</t>
+          <t>Bianca Castro</t>
         </is>
       </c>
       <c r="H1666" t="inlineStr"/>
       <c r="I1666" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J1666" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K1666" t="n">
-        <v>1</v>
+        <v>459</v>
       </c>
     </row>
     <row r="1667">
@@ -84190,7 +84206,7 @@
       </c>
       <c r="G1667" t="inlineStr">
         <is>
-          <t>Leticia Queiroz</t>
+          <t>Bruna Costa</t>
         </is>
       </c>
       <c r="H1667" t="inlineStr"/>
@@ -84201,7 +84217,7 @@
         <v>0</v>
       </c>
       <c r="K1667" t="n">
-        <v>428</v>
+        <v>34</v>
       </c>
     </row>
     <row r="1668">
@@ -84237,18 +84253,18 @@
       </c>
       <c r="G1668" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Daniela Silva</t>
         </is>
       </c>
       <c r="H1668" t="inlineStr"/>
       <c r="I1668" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="J1668" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="K1668" t="n">
-        <v>13</v>
+        <v>302</v>
       </c>
     </row>
     <row r="1669">
@@ -84284,18 +84300,18 @@
       </c>
       <c r="G1669" t="inlineStr">
         <is>
-          <t>Victoria Virgens</t>
+          <t>Isabelli Afonso</t>
         </is>
       </c>
       <c r="H1669" t="inlineStr"/>
       <c r="I1669" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1669" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1669" t="n">
-        <v>309</v>
+        <v>234</v>
       </c>
     </row>
     <row r="1670">
@@ -84331,7 +84347,7 @@
       </c>
       <c r="G1670" t="inlineStr">
         <is>
-          <t>Yasmin Peixoto</t>
+          <t>Jurema Damacena - SAC</t>
         </is>
       </c>
       <c r="H1670" t="inlineStr"/>
@@ -84342,7 +84358,7 @@
         <v>0</v>
       </c>
       <c r="K1670" t="n">
-        <v>551</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1671">
@@ -84373,23 +84389,23 @@
       </c>
       <c r="F1671" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="G1671" t="inlineStr">
         <is>
-          <t>Andre Coelho</t>
+          <t>Leticia Queiroz</t>
         </is>
       </c>
       <c r="H1671" t="inlineStr"/>
       <c r="I1671" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1671" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K1671" t="n">
-        <v>4</v>
+        <v>428</v>
       </c>
     </row>
     <row r="1672">
@@ -84420,23 +84436,23 @@
       </c>
       <c r="F1672" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="G1672" t="inlineStr">
         <is>
-          <t>Beatriz Rangel</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="H1672" t="inlineStr"/>
       <c r="I1672" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1672" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1672" t="n">
-        <v>372</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1673">
@@ -84467,12 +84483,12 @@
       </c>
       <c r="F1673" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="G1673" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
+          <t>Victoria Virgens</t>
         </is>
       </c>
       <c r="H1673" t="inlineStr"/>
@@ -84483,7 +84499,7 @@
         <v>0</v>
       </c>
       <c r="K1673" t="n">
-        <v>434</v>
+        <v>309</v>
       </c>
     </row>
     <row r="1674">
@@ -84514,23 +84530,23 @@
       </c>
       <c r="F1674" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="G1674" t="inlineStr">
         <is>
-          <t>Cristiane Simões</t>
+          <t>Yasmin Peixoto</t>
         </is>
       </c>
       <c r="H1674" t="inlineStr"/>
       <c r="I1674" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J1674" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K1674" t="n">
-        <v>305</v>
+        <v>552</v>
       </c>
     </row>
     <row r="1675">
@@ -84566,7 +84582,7 @@
       </c>
       <c r="G1675" t="inlineStr">
         <is>
-          <t>Daniel Oliveira</t>
+          <t>Andre Coelho</t>
         </is>
       </c>
       <c r="H1675" t="inlineStr"/>
@@ -84577,7 +84593,7 @@
         <v>0</v>
       </c>
       <c r="K1675" t="n">
-        <v>403</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1676">
@@ -84613,18 +84629,18 @@
       </c>
       <c r="G1676" t="inlineStr">
         <is>
-          <t>Diego Lima</t>
+          <t>Beatriz Rangel</t>
         </is>
       </c>
       <c r="H1676" t="inlineStr"/>
       <c r="I1676" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1676" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1676" t="n">
-        <v>164</v>
+        <v>373</v>
       </c>
     </row>
     <row r="1677">
@@ -84660,18 +84676,18 @@
       </c>
       <c r="G1677" t="inlineStr">
         <is>
-          <t>Eduardo Aparicio</t>
+          <t>Bruno Contieri</t>
         </is>
       </c>
       <c r="H1677" t="inlineStr"/>
       <c r="I1677" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="J1677" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="K1677" t="n">
-        <v>1</v>
+        <v>434</v>
       </c>
     </row>
     <row r="1678">
@@ -84707,7 +84723,7 @@
       </c>
       <c r="G1678" t="inlineStr">
         <is>
-          <t>Karine Gusmão</t>
+          <t>Cristiane Simões</t>
         </is>
       </c>
       <c r="H1678" t="inlineStr"/>
@@ -84718,7 +84734,7 @@
         <v>0</v>
       </c>
       <c r="K1678" t="n">
-        <v>93</v>
+        <v>305</v>
       </c>
     </row>
     <row r="1679">
@@ -84754,18 +84770,18 @@
       </c>
       <c r="G1679" t="inlineStr">
         <is>
-          <t>Luiz Ferreira</t>
+          <t>Daniel Oliveira</t>
         </is>
       </c>
       <c r="H1679" t="inlineStr"/>
       <c r="I1679" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1679" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1679" t="n">
-        <v>17</v>
+        <v>403</v>
       </c>
     </row>
     <row r="1680">
@@ -84801,7 +84817,7 @@
       </c>
       <c r="G1680" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Diego Lima</t>
         </is>
       </c>
       <c r="H1680" t="inlineStr"/>
@@ -84812,7 +84828,7 @@
         <v>0</v>
       </c>
       <c r="K1680" t="n">
-        <v>221</v>
+        <v>164</v>
       </c>
     </row>
     <row r="1681">
@@ -84848,18 +84864,18 @@
       </c>
       <c r="G1681" t="inlineStr">
         <is>
-          <t>Rodrigo Rego</t>
+          <t>Eduardo Aparicio</t>
         </is>
       </c>
       <c r="H1681" t="inlineStr"/>
       <c r="I1681" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1681" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1681" t="n">
-        <v>460</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1682">
@@ -84895,7 +84911,7 @@
       </c>
       <c r="G1682" t="inlineStr">
         <is>
-          <t>Rogerio Egidio</t>
+          <t>Karine Gusmão</t>
         </is>
       </c>
       <c r="H1682" t="inlineStr"/>
@@ -84906,7 +84922,7 @@
         <v>0</v>
       </c>
       <c r="K1682" t="n">
-        <v>383</v>
+        <v>93</v>
       </c>
     </row>
     <row r="1683">
@@ -84942,7 +84958,7 @@
       </c>
       <c r="G1683" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Luiz Ferreira</t>
         </is>
       </c>
       <c r="H1683" t="inlineStr"/>
@@ -84953,7 +84969,7 @@
         <v>0</v>
       </c>
       <c r="K1683" t="n">
-        <v>50</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1684">
@@ -84989,7 +85005,7 @@
       </c>
       <c r="G1684" t="inlineStr">
         <is>
-          <t>Simone Marques</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="H1684" t="inlineStr"/>
@@ -85000,7 +85016,7 @@
         <v>0</v>
       </c>
       <c r="K1684" t="n">
-        <v>228</v>
+        <v>221</v>
       </c>
     </row>
     <row r="1685">
@@ -85036,7 +85052,7 @@
       </c>
       <c r="G1685" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Rodrigo Rego</t>
         </is>
       </c>
       <c r="H1685" t="inlineStr"/>
@@ -85047,7 +85063,7 @@
         <v>0</v>
       </c>
       <c r="K1685" t="n">
-        <v>267</v>
+        <v>460</v>
       </c>
     </row>
     <row r="1686">
@@ -85078,12 +85094,12 @@
       </c>
       <c r="F1686" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="G1686" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Rogerio Egidio</t>
         </is>
       </c>
       <c r="H1686" t="inlineStr"/>
@@ -85094,7 +85110,7 @@
         <v>0</v>
       </c>
       <c r="K1686" t="n">
-        <v>1</v>
+        <v>383</v>
       </c>
     </row>
     <row r="1687">
@@ -85125,23 +85141,23 @@
       </c>
       <c r="F1687" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="G1687" t="inlineStr">
         <is>
-          <t>Jurema Damacena - SAC</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="H1687" t="inlineStr"/>
       <c r="I1687" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1687" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1687" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1688">
@@ -85172,12 +85188,12 @@
       </c>
       <c r="F1688" t="inlineStr">
         <is>
-          <t>MG CONTABIFÁCIL - CTB</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="G1688" t="inlineStr">
         <is>
-          <t>Guilherme Delecrodio</t>
+          <t>Simone Marques</t>
         </is>
       </c>
       <c r="H1688" t="inlineStr"/>
@@ -85188,7 +85204,7 @@
         <v>0</v>
       </c>
       <c r="K1688" t="n">
-        <v>1</v>
+        <v>228</v>
       </c>
     </row>
     <row r="1689">
@@ -85219,12 +85235,12 @@
       </c>
       <c r="F1689" t="inlineStr">
         <is>
-          <t>S.A.C</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="G1689" t="inlineStr">
         <is>
-          <t>Ana Celia - SAC</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="H1689" t="inlineStr"/>
@@ -85235,7 +85251,7 @@
         <v>0</v>
       </c>
       <c r="K1689" t="n">
-        <v>1</v>
+        <v>267</v>
       </c>
     </row>
     <row r="1690">
@@ -85266,19 +85282,15 @@
       </c>
       <c r="F1690" t="inlineStr">
         <is>
-          <t>SANTOS - DP</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="G1690" t="inlineStr">
         <is>
-          <t>Katia Valeria</t>
-        </is>
-      </c>
-      <c r="H1690" t="inlineStr">
-        <is>
-          <t>Katia Valeria</t>
-        </is>
-      </c>
+          <t>Edimir Santos</t>
+        </is>
+      </c>
+      <c r="H1690" t="inlineStr"/>
       <c r="I1690" t="n">
         <v>0</v>
       </c>
@@ -85286,7 +85298,7 @@
         <v>0</v>
       </c>
       <c r="K1690" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1691">
@@ -85312,7 +85324,7 @@
       </c>
       <c r="E1691" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F1691" t="inlineStr">
@@ -85327,13 +85339,13 @@
       </c>
       <c r="H1691" t="inlineStr"/>
       <c r="I1691" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J1691" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K1691" t="n">
-        <v>7</v>
+        <v>52</v>
       </c>
     </row>
     <row r="1692">
@@ -85359,17 +85371,17 @@
       </c>
       <c r="E1692" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F1692" t="inlineStr">
         <is>
-          <t>SANTOS - ADM</t>
+          <t>MG CONTABIFÁCIL - CTB</t>
         </is>
       </c>
       <c r="G1692" t="inlineStr">
         <is>
-          <t>Kauany Pereira</t>
+          <t>Guilherme Delecrodio</t>
         </is>
       </c>
       <c r="H1692" t="inlineStr"/>
@@ -85380,7 +85392,7 @@
         <v>0</v>
       </c>
       <c r="K1692" t="n">
-        <v>138</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1693">
@@ -85406,32 +85418,24 @@
       </c>
       <c r="E1693" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F1693" t="inlineStr">
         <is>
-          <t>SANTOS - CTB</t>
-        </is>
-      </c>
-      <c r="G1693" t="inlineStr">
-        <is>
-          <t>Ivia Oliveira</t>
-        </is>
-      </c>
-      <c r="H1693" t="inlineStr">
-        <is>
-          <t>Roberto Silva</t>
-        </is>
-      </c>
+          <t>MG EXPRESS - CTB</t>
+        </is>
+      </c>
+      <c r="G1693" t="inlineStr"/>
+      <c r="H1693" t="inlineStr"/>
       <c r="I1693" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J1693" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K1693" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1694">
@@ -85457,24 +85461,20 @@
       </c>
       <c r="E1694" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F1694" t="inlineStr">
         <is>
-          <t>SANTOS - CTB</t>
+          <t>MG EXPRESS - CTB</t>
         </is>
       </c>
       <c r="G1694" t="inlineStr">
         <is>
-          <t>Nata Trindade</t>
-        </is>
-      </c>
-      <c r="H1694" t="inlineStr">
-        <is>
-          <t>Roberto Silva</t>
-        </is>
-      </c>
+          <t>Guilherme Delecrodio</t>
+        </is>
+      </c>
+      <c r="H1694" t="inlineStr"/>
       <c r="I1694" t="n">
         <v>0</v>
       </c>
@@ -85482,7 +85482,7 @@
         <v>0</v>
       </c>
       <c r="K1694" t="n">
-        <v>82</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1695">
@@ -85508,24 +85508,20 @@
       </c>
       <c r="E1695" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F1695" t="inlineStr">
         <is>
-          <t>SANTOS - CTB</t>
+          <t>S.A.C</t>
         </is>
       </c>
       <c r="G1695" t="inlineStr">
         <is>
-          <t>Roberto Silva</t>
-        </is>
-      </c>
-      <c r="H1695" t="inlineStr">
-        <is>
-          <t>Roberto Silva</t>
-        </is>
-      </c>
+          <t>Ana Celia - SAC</t>
+        </is>
+      </c>
+      <c r="H1695" t="inlineStr"/>
       <c r="I1695" t="n">
         <v>0</v>
       </c>
@@ -85533,7 +85529,7 @@
         <v>0</v>
       </c>
       <c r="K1695" t="n">
-        <v>111</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1696">
@@ -85559,22 +85555,22 @@
       </c>
       <c r="E1696" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F1696" t="inlineStr">
         <is>
-          <t>SANTOS - CTB</t>
+          <t>SANTOS - DP</t>
         </is>
       </c>
       <c r="G1696" t="inlineStr">
         <is>
-          <t>Thaina Rodrigues</t>
+          <t>Katia Valeria</t>
         </is>
       </c>
       <c r="H1696" t="inlineStr">
         <is>
-          <t>Roberto Silva</t>
+          <t>Katia Valeria</t>
         </is>
       </c>
       <c r="I1696" t="n">
@@ -85584,7 +85580,7 @@
         <v>0</v>
       </c>
       <c r="K1696" t="n">
-        <v>94</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1697">
@@ -85615,27 +85611,23 @@
       </c>
       <c r="F1697" t="inlineStr">
         <is>
-          <t>SANTOS - DP</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="G1697" t="inlineStr">
         <is>
-          <t>Bruna Silva</t>
-        </is>
-      </c>
-      <c r="H1697" t="inlineStr">
-        <is>
-          <t>Katia Valeria</t>
-        </is>
-      </c>
+          <t>Jurema Damacena - SAC</t>
+        </is>
+      </c>
+      <c r="H1697" t="inlineStr"/>
       <c r="I1697" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1697" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1697" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1698">
@@ -85666,19 +85658,15 @@
       </c>
       <c r="F1698" t="inlineStr">
         <is>
-          <t>SANTOS - DP</t>
+          <t>SANTOS - ADM</t>
         </is>
       </c>
       <c r="G1698" t="inlineStr">
         <is>
-          <t>Carliane Silva</t>
-        </is>
-      </c>
-      <c r="H1698" t="inlineStr">
-        <is>
-          <t>Katia Valeria</t>
-        </is>
-      </c>
+          <t>Kauany Pereira</t>
+        </is>
+      </c>
+      <c r="H1698" t="inlineStr"/>
       <c r="I1698" t="n">
         <v>0</v>
       </c>
@@ -85686,7 +85674,7 @@
         <v>0</v>
       </c>
       <c r="K1698" t="n">
-        <v>285</v>
+        <v>138</v>
       </c>
     </row>
     <row r="1699">
@@ -85717,17 +85705,17 @@
       </c>
       <c r="F1699" t="inlineStr">
         <is>
-          <t>SANTOS - DP</t>
+          <t>SANTOS - CTB</t>
         </is>
       </c>
       <c r="G1699" t="inlineStr">
         <is>
-          <t>Cintia Andrade</t>
+          <t>Ivia Oliveira</t>
         </is>
       </c>
       <c r="H1699" t="inlineStr">
         <is>
-          <t>Katia Valeria</t>
+          <t>Roberto Silva</t>
         </is>
       </c>
       <c r="I1699" t="n">
@@ -85737,7 +85725,7 @@
         <v>0</v>
       </c>
       <c r="K1699" t="n">
-        <v>210</v>
+        <v>57</v>
       </c>
     </row>
     <row r="1700">
@@ -85768,27 +85756,27 @@
       </c>
       <c r="F1700" t="inlineStr">
         <is>
-          <t>SANTOS - DP</t>
+          <t>SANTOS - CTB</t>
         </is>
       </c>
       <c r="G1700" t="inlineStr">
         <is>
-          <t>Katia Valeria</t>
+          <t>Nata Trindade</t>
         </is>
       </c>
       <c r="H1700" t="inlineStr">
         <is>
-          <t>Katia Valeria</t>
+          <t>Roberto Silva</t>
         </is>
       </c>
       <c r="I1700" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1700" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1700" t="n">
-        <v>349</v>
+        <v>84</v>
       </c>
     </row>
     <row r="1701">
@@ -85819,17 +85807,17 @@
       </c>
       <c r="F1701" t="inlineStr">
         <is>
-          <t>SANTOS - EF</t>
+          <t>SANTOS - CTB</t>
         </is>
       </c>
       <c r="G1701" t="inlineStr">
         <is>
-          <t>Jasmina Melo</t>
+          <t>Roberto Silva</t>
         </is>
       </c>
       <c r="H1701" t="inlineStr">
         <is>
-          <t>Lidia Tavares</t>
+          <t>Roberto Silva</t>
         </is>
       </c>
       <c r="I1701" t="n">
@@ -85839,7 +85827,7 @@
         <v>0</v>
       </c>
       <c r="K1701" t="n">
-        <v>82</v>
+        <v>111</v>
       </c>
     </row>
     <row r="1702">
@@ -85870,17 +85858,17 @@
       </c>
       <c r="F1702" t="inlineStr">
         <is>
-          <t>SANTOS - EF</t>
+          <t>SANTOS - CTB</t>
         </is>
       </c>
       <c r="G1702" t="inlineStr">
         <is>
-          <t>Karen Saadi</t>
+          <t>Thaina Rodrigues</t>
         </is>
       </c>
       <c r="H1702" t="inlineStr">
         <is>
-          <t>Lidia Tavares</t>
+          <t>Roberto Silva</t>
         </is>
       </c>
       <c r="I1702" t="n">
@@ -85890,7 +85878,7 @@
         <v>0</v>
       </c>
       <c r="K1702" t="n">
-        <v>78</v>
+        <v>94</v>
       </c>
     </row>
     <row r="1703">
@@ -85921,27 +85909,27 @@
       </c>
       <c r="F1703" t="inlineStr">
         <is>
-          <t>SANTOS - EF</t>
+          <t>SANTOS - DP</t>
         </is>
       </c>
       <c r="G1703" t="inlineStr">
         <is>
-          <t>Luckas Andrade</t>
+          <t>Bruna Silva</t>
         </is>
       </c>
       <c r="H1703" t="inlineStr">
         <is>
-          <t>Lidia Tavares</t>
+          <t>Katia Valeria</t>
         </is>
       </c>
       <c r="I1703" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J1703" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K1703" t="n">
-        <v>108</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1704">
@@ -85972,27 +85960,27 @@
       </c>
       <c r="F1704" t="inlineStr">
         <is>
-          <t>SANTOS - EF</t>
+          <t>SANTOS - DP</t>
         </is>
       </c>
       <c r="G1704" t="inlineStr">
         <is>
-          <t>Mirian Rodrigues</t>
+          <t>Carliane Silva</t>
         </is>
       </c>
       <c r="H1704" t="inlineStr">
         <is>
-          <t>Lidia Tavares</t>
+          <t>Katia Valeria</t>
         </is>
       </c>
       <c r="I1704" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1704" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1704" t="n">
-        <v>111</v>
+        <v>288</v>
       </c>
     </row>
     <row r="1705">
@@ -86023,22 +86011,328 @@
       </c>
       <c r="F1705" t="inlineStr">
         <is>
+          <t>SANTOS - DP</t>
+        </is>
+      </c>
+      <c r="G1705" t="inlineStr">
+        <is>
+          <t>Cintia Andrade</t>
+        </is>
+      </c>
+      <c r="H1705" t="inlineStr">
+        <is>
+          <t>Katia Valeria</t>
+        </is>
+      </c>
+      <c r="I1705" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1705" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1705" t="n">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="1706">
+      <c r="A1706" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B1706" t="inlineStr">
+        <is>
+          <t>Segunda</t>
+        </is>
+      </c>
+      <c r="C1706" t="inlineStr">
+        <is>
+          <t>2026-W25</t>
+        </is>
+      </c>
+      <c r="D1706" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1706" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="F1706" t="inlineStr">
+        <is>
+          <t>SANTOS - DP</t>
+        </is>
+      </c>
+      <c r="G1706" t="inlineStr">
+        <is>
+          <t>Katia Valeria</t>
+        </is>
+      </c>
+      <c r="H1706" t="inlineStr">
+        <is>
+          <t>Katia Valeria</t>
+        </is>
+      </c>
+      <c r="I1706" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1706" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1706" t="n">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="1707">
+      <c r="A1707" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B1707" t="inlineStr">
+        <is>
+          <t>Segunda</t>
+        </is>
+      </c>
+      <c r="C1707" t="inlineStr">
+        <is>
+          <t>2026-W25</t>
+        </is>
+      </c>
+      <c r="D1707" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1707" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="F1707" t="inlineStr">
+        <is>
+          <t>SANTOS - EF</t>
+        </is>
+      </c>
+      <c r="G1707" t="inlineStr">
+        <is>
+          <t>Jasmina Melo</t>
+        </is>
+      </c>
+      <c r="H1707" t="inlineStr">
+        <is>
+          <t>Lidia Tavares</t>
+        </is>
+      </c>
+      <c r="I1707" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1707" t="n">
+        <v>2</v>
+      </c>
+      <c r="K1707" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="1708">
+      <c r="A1708" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B1708" t="inlineStr">
+        <is>
+          <t>Segunda</t>
+        </is>
+      </c>
+      <c r="C1708" t="inlineStr">
+        <is>
+          <t>2026-W25</t>
+        </is>
+      </c>
+      <c r="D1708" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1708" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="F1708" t="inlineStr">
+        <is>
+          <t>SANTOS - EF</t>
+        </is>
+      </c>
+      <c r="G1708" t="inlineStr">
+        <is>
+          <t>Karen Saadi</t>
+        </is>
+      </c>
+      <c r="H1708" t="inlineStr">
+        <is>
+          <t>Lidia Tavares</t>
+        </is>
+      </c>
+      <c r="I1708" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1708" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1708" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="1709">
+      <c r="A1709" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B1709" t="inlineStr">
+        <is>
+          <t>Segunda</t>
+        </is>
+      </c>
+      <c r="C1709" t="inlineStr">
+        <is>
+          <t>2026-W25</t>
+        </is>
+      </c>
+      <c r="D1709" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1709" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="F1709" t="inlineStr">
+        <is>
+          <t>SANTOS - EF</t>
+        </is>
+      </c>
+      <c r="G1709" t="inlineStr">
+        <is>
+          <t>Luckas Andrade</t>
+        </is>
+      </c>
+      <c r="H1709" t="inlineStr">
+        <is>
+          <t>Lidia Tavares</t>
+        </is>
+      </c>
+      <c r="I1709" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1709" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1709" t="n">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="1710">
+      <c r="A1710" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B1710" t="inlineStr">
+        <is>
+          <t>Segunda</t>
+        </is>
+      </c>
+      <c r="C1710" t="inlineStr">
+        <is>
+          <t>2026-W25</t>
+        </is>
+      </c>
+      <c r="D1710" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1710" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="F1710" t="inlineStr">
+        <is>
+          <t>SANTOS - EF</t>
+        </is>
+      </c>
+      <c r="G1710" t="inlineStr">
+        <is>
+          <t>Mirian Rodrigues</t>
+        </is>
+      </c>
+      <c r="H1710" t="inlineStr">
+        <is>
+          <t>Lidia Tavares</t>
+        </is>
+      </c>
+      <c r="I1710" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1710" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1710" t="n">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="1711">
+      <c r="A1711" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B1711" t="inlineStr">
+        <is>
+          <t>Segunda</t>
+        </is>
+      </c>
+      <c r="C1711" t="inlineStr">
+        <is>
+          <t>2026-W25</t>
+        </is>
+      </c>
+      <c r="D1711" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1711" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="F1711" t="inlineStr">
+        <is>
           <t>SANTOS - GC</t>
         </is>
       </c>
-      <c r="G1705" t="inlineStr">
+      <c r="G1711" t="inlineStr">
         <is>
           <t>Rafaella Massuia</t>
         </is>
       </c>
-      <c r="H1705" t="inlineStr"/>
-      <c r="I1705" t="n">
-        <v>0</v>
-      </c>
-      <c r="J1705" t="n">
-        <v>0</v>
-      </c>
-      <c r="K1705" t="n">
+      <c r="H1711" t="inlineStr"/>
+      <c r="I1711" t="n">
+        <v>5</v>
+      </c>
+      <c r="J1711" t="n">
+        <v>5</v>
+      </c>
+      <c r="K1711" t="n">
         <v>109</v>
       </c>
     </row>

--- a/data/historico/historico_baixas.xlsx
+++ b/data/historico/historico_baixas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1711"/>
+  <dimension ref="A1:K1712"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -71777,13 +71777,13 @@
         </is>
       </c>
       <c r="I1421" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J1421" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1421" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1422">
@@ -71828,13 +71828,13 @@
         </is>
       </c>
       <c r="I1422" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1422" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1422" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1423">
@@ -71879,13 +71879,13 @@
         </is>
       </c>
       <c r="I1423" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1423" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K1423" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1424">
@@ -72432,13 +72432,13 @@
       </c>
       <c r="H1434" t="inlineStr"/>
       <c r="I1434" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J1434" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1434" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="1435">
@@ -72585,13 +72585,13 @@
         </is>
       </c>
       <c r="I1437" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J1437" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1437" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="1438">
@@ -72773,13 +72773,13 @@
       </c>
       <c r="H1441" t="inlineStr"/>
       <c r="I1441" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1441" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1441" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1442">
@@ -72914,10 +72914,10 @@
       </c>
       <c r="H1444" t="inlineStr"/>
       <c r="I1444" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1444" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1444" t="n">
         <v>16</v>
@@ -72965,13 +72965,13 @@
         </is>
       </c>
       <c r="I1445" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J1445" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K1445" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="1446">
@@ -73016,13 +73016,13 @@
         </is>
       </c>
       <c r="I1446" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1446" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1446" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="1447">
@@ -73169,13 +73169,13 @@
         </is>
       </c>
       <c r="I1449" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J1449" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K1449" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1450">
@@ -73526,13 +73526,13 @@
         </is>
       </c>
       <c r="I1456" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J1456" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K1456" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1457">
@@ -73628,13 +73628,13 @@
         </is>
       </c>
       <c r="I1458" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J1458" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K1458" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="1459">
@@ -73679,13 +73679,13 @@
         </is>
       </c>
       <c r="I1459" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J1459" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K1459" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="1460">
@@ -73824,13 +73824,13 @@
         </is>
       </c>
       <c r="I1462" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J1462" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K1462" t="n">
-        <v>105</v>
+        <v>113</v>
       </c>
     </row>
     <row r="1463">
@@ -74028,13 +74028,13 @@
         </is>
       </c>
       <c r="I1466" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J1466" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1466" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="1467">
@@ -74130,13 +74130,13 @@
         </is>
       </c>
       <c r="I1468" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1468" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K1468" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="1469">
@@ -74283,13 +74283,13 @@
         </is>
       </c>
       <c r="I1471" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J1471" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K1471" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="1472">
@@ -74436,13 +74436,13 @@
         </is>
       </c>
       <c r="I1474" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1474" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1474" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="1475">
@@ -74487,13 +74487,13 @@
         </is>
       </c>
       <c r="I1475" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1475" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1475" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1476">
@@ -74538,13 +74538,13 @@
         </is>
       </c>
       <c r="I1476" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J1476" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1476" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="1477">
@@ -74589,13 +74589,13 @@
         </is>
       </c>
       <c r="I1477" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1477" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1477" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1478">
@@ -74691,10 +74691,10 @@
         </is>
       </c>
       <c r="I1479" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1479" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K1479" t="n">
         <v>123</v>
@@ -74742,13 +74742,13 @@
         </is>
       </c>
       <c r="I1480" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="J1480" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="K1480" t="n">
-        <v>208</v>
+        <v>217</v>
       </c>
     </row>
     <row r="1481">
@@ -74844,13 +74844,13 @@
         </is>
       </c>
       <c r="I1482" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J1482" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="K1482" t="n">
-        <v>163</v>
+        <v>169</v>
       </c>
     </row>
     <row r="1483">
@@ -74895,13 +74895,13 @@
         </is>
       </c>
       <c r="I1483" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J1483" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K1483" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="1484">
@@ -74997,13 +74997,13 @@
         </is>
       </c>
       <c r="I1485" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1485" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K1485" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1486">
@@ -75099,13 +75099,13 @@
         </is>
       </c>
       <c r="I1487" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="J1487" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="K1487" t="n">
-        <v>221</v>
+        <v>226</v>
       </c>
     </row>
     <row r="1488">
@@ -75150,13 +75150,13 @@
         </is>
       </c>
       <c r="I1488" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="J1488" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="K1488" t="n">
-        <v>218</v>
+        <v>233</v>
       </c>
     </row>
     <row r="1489">
@@ -75303,13 +75303,13 @@
         </is>
       </c>
       <c r="I1491" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J1491" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="K1491" t="n">
-        <v>141</v>
+        <v>147</v>
       </c>
     </row>
     <row r="1492">
@@ -75895,13 +75895,13 @@
         </is>
       </c>
       <c r="I1503" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1503" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K1503" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1504">
@@ -75946,13 +75946,13 @@
         </is>
       </c>
       <c r="I1504" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J1504" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K1504" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1505">
@@ -76099,13 +76099,13 @@
         </is>
       </c>
       <c r="I1507" t="n">
-        <v>18</v>
+        <v>73</v>
       </c>
       <c r="J1507" t="n">
-        <v>18</v>
+        <v>73</v>
       </c>
       <c r="K1507" t="n">
-        <v>138</v>
+        <v>192</v>
       </c>
     </row>
     <row r="1508">
@@ -76146,13 +76146,13 @@
       </c>
       <c r="H1508" t="inlineStr"/>
       <c r="I1508" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1508" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K1508" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1509">
@@ -76197,13 +76197,13 @@
         </is>
       </c>
       <c r="I1509" t="n">
-        <v>65</v>
+        <v>141</v>
       </c>
       <c r="J1509" t="n">
-        <v>65</v>
+        <v>141</v>
       </c>
       <c r="K1509" t="n">
-        <v>206</v>
+        <v>282</v>
       </c>
     </row>
     <row r="1510">
@@ -76299,13 +76299,13 @@
         </is>
       </c>
       <c r="I1511" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J1511" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K1511" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1512">
@@ -76503,13 +76503,13 @@
         </is>
       </c>
       <c r="I1515" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J1515" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1515" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1516">
@@ -76707,13 +76707,13 @@
         </is>
       </c>
       <c r="I1519" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="J1519" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="K1519" t="n">
-        <v>35</v>
+        <v>74</v>
       </c>
     </row>
     <row r="1520">
@@ -77009,13 +77009,13 @@
         </is>
       </c>
       <c r="I1525" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="J1525" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K1525" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="1526">
@@ -77060,13 +77060,13 @@
         </is>
       </c>
       <c r="I1526" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J1526" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K1526" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="1527">
@@ -77315,13 +77315,13 @@
         </is>
       </c>
       <c r="I1531" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J1531" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K1531" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="1532">
@@ -77366,13 +77366,13 @@
         </is>
       </c>
       <c r="I1532" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J1532" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="K1532" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="1533">
@@ -77417,13 +77417,13 @@
         </is>
       </c>
       <c r="I1533" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J1533" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K1533" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1534">
@@ -77468,13 +77468,13 @@
         </is>
       </c>
       <c r="I1534" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J1534" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K1534" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="1535">
@@ -77519,13 +77519,13 @@
         </is>
       </c>
       <c r="I1535" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J1535" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1535" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="1536">
@@ -77570,13 +77570,13 @@
         </is>
       </c>
       <c r="I1536" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J1536" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K1536" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="1537">
@@ -77723,13 +77723,13 @@
         </is>
       </c>
       <c r="I1539" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="J1539" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="K1539" t="n">
-        <v>50</v>
+        <v>79</v>
       </c>
     </row>
     <row r="1540">
@@ -77774,13 +77774,13 @@
         </is>
       </c>
       <c r="I1540" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1540" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1540" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1541">
@@ -77831,7 +77831,7 @@
         <v>0</v>
       </c>
       <c r="K1541" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
     <row r="1542">
@@ -77876,13 +77876,13 @@
         </is>
       </c>
       <c r="I1542" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J1542" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1542" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1543">
@@ -77927,13 +77927,13 @@
         </is>
       </c>
       <c r="I1543" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J1543" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K1543" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="1544">
@@ -77978,13 +77978,13 @@
         </is>
       </c>
       <c r="I1544" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J1544" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="K1544" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1545">
@@ -78029,13 +78029,13 @@
         </is>
       </c>
       <c r="I1545" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="J1545" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="K1545" t="n">
-        <v>117</v>
+        <v>139</v>
       </c>
     </row>
     <row r="1546">
@@ -78131,13 +78131,13 @@
         </is>
       </c>
       <c r="I1547" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J1547" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="K1547" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="1548">
@@ -78182,13 +78182,13 @@
         </is>
       </c>
       <c r="I1548" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J1548" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K1548" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
     </row>
     <row r="1549">
@@ -78233,13 +78233,13 @@
         </is>
       </c>
       <c r="I1549" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="J1549" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="K1549" t="n">
-        <v>65</v>
+        <v>83</v>
       </c>
     </row>
     <row r="1550">
@@ -78335,13 +78335,13 @@
         </is>
       </c>
       <c r="I1551" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="J1551" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K1551" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="1552">
@@ -78386,13 +78386,13 @@
         </is>
       </c>
       <c r="I1552" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J1552" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K1552" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1553">
@@ -78535,13 +78535,13 @@
         </is>
       </c>
       <c r="I1555" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J1555" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K1555" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="1556">
@@ -79096,13 +79096,13 @@
         </is>
       </c>
       <c r="I1566" t="n">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="J1566" t="n">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="K1566" t="n">
-        <v>58</v>
+        <v>90</v>
       </c>
     </row>
     <row r="1567">
@@ -79147,13 +79147,13 @@
         </is>
       </c>
       <c r="I1567" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1567" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1567" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1568">
@@ -79198,13 +79198,13 @@
         </is>
       </c>
       <c r="I1568" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J1568" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K1568" t="n">
-        <v>67</v>
+        <v>84</v>
       </c>
     </row>
     <row r="1569">
@@ -79402,10 +79402,10 @@
         </is>
       </c>
       <c r="I1572" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J1572" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K1572" t="n">
         <v>141</v>
@@ -79459,7 +79459,7 @@
         <v>0</v>
       </c>
       <c r="K1573" t="n">
-        <v>86</v>
+        <v>117</v>
       </c>
     </row>
     <row r="1574">
@@ -79504,10 +79504,10 @@
         </is>
       </c>
       <c r="I1574" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1574" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1574" t="n">
         <v>14</v>
@@ -79555,13 +79555,13 @@
         </is>
       </c>
       <c r="I1575" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J1575" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K1575" t="n">
-        <v>143</v>
+        <v>149</v>
       </c>
     </row>
     <row r="1576">
@@ -79708,13 +79708,13 @@
         </is>
       </c>
       <c r="I1578" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J1578" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K1578" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="1579">
@@ -79861,13 +79861,13 @@
         </is>
       </c>
       <c r="I1581" t="n">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="J1581" t="n">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="K1581" t="n">
-        <v>132</v>
+        <v>154</v>
       </c>
     </row>
     <row r="1582">
@@ -79912,13 +79912,13 @@
         </is>
       </c>
       <c r="I1582" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="J1582" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="K1582" t="n">
-        <v>81</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1583">
@@ -79963,13 +79963,13 @@
         </is>
       </c>
       <c r="I1583" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J1583" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K1583" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="1584">
@@ -80065,10 +80065,10 @@
         </is>
       </c>
       <c r="I1585" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="J1585" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="K1585" t="n">
         <v>1</v>
@@ -80167,13 +80167,13 @@
         </is>
       </c>
       <c r="I1587" t="n">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="J1587" t="n">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="K1587" t="n">
-        <v>134</v>
+        <v>164</v>
       </c>
     </row>
     <row r="1588">
@@ -80367,13 +80367,13 @@
         </is>
       </c>
       <c r="I1591" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J1591" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K1591" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="1592">
@@ -80469,13 +80469,13 @@
         </is>
       </c>
       <c r="I1593" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J1593" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K1593" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="1594">
@@ -80520,13 +80520,13 @@
         </is>
       </c>
       <c r="I1594" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J1594" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K1594" t="n">
-        <v>112</v>
+        <v>119</v>
       </c>
     </row>
     <row r="1595">
@@ -80622,13 +80622,13 @@
         </is>
       </c>
       <c r="I1596" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="J1596" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="K1596" t="n">
-        <v>100</v>
+        <v>112</v>
       </c>
     </row>
     <row r="1597">
@@ -80775,13 +80775,13 @@
         </is>
       </c>
       <c r="I1599" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1599" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1599" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1600">
@@ -80826,13 +80826,13 @@
         </is>
       </c>
       <c r="I1600" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J1600" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="K1600" t="n">
-        <v>121</v>
+        <v>127</v>
       </c>
     </row>
     <row r="1601">
@@ -80928,13 +80928,13 @@
         </is>
       </c>
       <c r="I1602" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J1602" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K1602" t="n">
-        <v>159</v>
+        <v>170</v>
       </c>
     </row>
     <row r="1603">
@@ -80979,13 +80979,13 @@
         </is>
       </c>
       <c r="I1603" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J1603" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K1603" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="1604">
@@ -81030,13 +81030,13 @@
         </is>
       </c>
       <c r="I1604" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1604" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1604" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="1605">
@@ -81081,13 +81081,13 @@
         </is>
       </c>
       <c r="I1605" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1605" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1605" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="1606">
@@ -81128,13 +81128,13 @@
       </c>
       <c r="H1606" t="inlineStr"/>
       <c r="I1606" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="J1606" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="K1606" t="n">
-        <v>100</v>
+        <v>109</v>
       </c>
     </row>
     <row r="1607">
@@ -81179,13 +81179,13 @@
         </is>
       </c>
       <c r="I1607" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="J1607" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="K1607" t="n">
-        <v>155</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1608">
@@ -81230,13 +81230,13 @@
         </is>
       </c>
       <c r="I1608" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J1608" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K1608" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="1609">
@@ -81281,13 +81281,13 @@
         </is>
       </c>
       <c r="I1609" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J1609" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K1609" t="n">
-        <v>630</v>
+        <v>637</v>
       </c>
     </row>
     <row r="1610">
@@ -81332,13 +81332,13 @@
         </is>
       </c>
       <c r="I1610" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J1610" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K1610" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="1611">
@@ -81383,13 +81383,13 @@
         </is>
       </c>
       <c r="I1611" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J1611" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K1611" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
     </row>
     <row r="1612">
@@ -81434,13 +81434,13 @@
         </is>
       </c>
       <c r="I1612" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="J1612" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="K1612" t="n">
-        <v>101</v>
+        <v>110</v>
       </c>
     </row>
     <row r="1613">
@@ -81491,7 +81491,7 @@
         <v>0</v>
       </c>
       <c r="K1613" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1614">
@@ -81536,13 +81536,13 @@
         </is>
       </c>
       <c r="I1614" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J1614" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K1614" t="n">
-        <v>135</v>
+        <v>142</v>
       </c>
     </row>
     <row r="1615">
@@ -81587,13 +81587,13 @@
         </is>
       </c>
       <c r="I1615" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J1615" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K1615" t="n">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="1616">
@@ -81689,13 +81689,13 @@
         </is>
       </c>
       <c r="I1617" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1617" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1617" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="1618">
@@ -81893,13 +81893,13 @@
         </is>
       </c>
       <c r="I1621" t="n">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="J1621" t="n">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="K1621" t="n">
-        <v>190</v>
+        <v>212</v>
       </c>
     </row>
     <row r="1622">
@@ -81944,13 +81944,13 @@
         </is>
       </c>
       <c r="I1622" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J1622" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K1622" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="1623">
@@ -81995,13 +81995,13 @@
         </is>
       </c>
       <c r="I1623" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J1623" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K1623" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="1624">
@@ -82046,13 +82046,13 @@
         </is>
       </c>
       <c r="I1624" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J1624" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1624" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="1625">
@@ -82097,13 +82097,13 @@
         </is>
       </c>
       <c r="I1625" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="J1625" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="K1625" t="n">
-        <v>66</v>
+        <v>88</v>
       </c>
     </row>
     <row r="1626">
@@ -82148,10 +82148,10 @@
         </is>
       </c>
       <c r="I1626" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J1626" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1626" t="n">
         <v>87</v>
@@ -82199,13 +82199,13 @@
         </is>
       </c>
       <c r="I1627" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J1627" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K1627" t="n">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="1628">
@@ -82252,7 +82252,7 @@
         <v>0</v>
       </c>
       <c r="K1628" t="n">
-        <v>202</v>
+        <v>207</v>
       </c>
     </row>
     <row r="1629">
@@ -82297,13 +82297,13 @@
         </is>
       </c>
       <c r="I1629" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J1629" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K1629" t="n">
-        <v>159</v>
+        <v>167</v>
       </c>
     </row>
     <row r="1630">
@@ -82348,13 +82348,13 @@
         </is>
       </c>
       <c r="I1630" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="J1630" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="K1630" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="1631">
@@ -82399,13 +82399,13 @@
         </is>
       </c>
       <c r="I1631" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="J1631" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="K1631" t="n">
-        <v>143</v>
+        <v>164</v>
       </c>
     </row>
     <row r="1632">
@@ -82501,13 +82501,13 @@
         </is>
       </c>
       <c r="I1633" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="J1633" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="K1633" t="n">
-        <v>58</v>
+        <v>71</v>
       </c>
     </row>
     <row r="1634">
@@ -82552,13 +82552,13 @@
         </is>
       </c>
       <c r="I1634" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J1634" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K1634" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
     </row>
     <row r="1635">
@@ -82603,13 +82603,13 @@
         </is>
       </c>
       <c r="I1635" t="n">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="J1635" t="n">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="K1635" t="n">
-        <v>265</v>
+        <v>243</v>
       </c>
     </row>
     <row r="1636">
@@ -82705,13 +82705,13 @@
         </is>
       </c>
       <c r="I1637" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="J1637" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="K1637" t="n">
-        <v>57</v>
+        <v>78</v>
       </c>
     </row>
     <row r="1638">
@@ -82756,13 +82756,13 @@
         </is>
       </c>
       <c r="I1638" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J1638" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K1638" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
     </row>
     <row r="1639">
@@ -82807,13 +82807,13 @@
         </is>
       </c>
       <c r="I1639" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="J1639" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="K1639" t="n">
-        <v>123</v>
+        <v>136</v>
       </c>
     </row>
     <row r="1640">
@@ -82960,13 +82960,13 @@
         </is>
       </c>
       <c r="I1642" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J1642" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K1642" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="1643">
@@ -83011,13 +83011,13 @@
         </is>
       </c>
       <c r="I1643" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J1643" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K1643" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="1644">
@@ -83062,13 +83062,13 @@
         </is>
       </c>
       <c r="I1644" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J1644" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K1644" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="1645">
@@ -83113,13 +83113,13 @@
         </is>
       </c>
       <c r="I1645" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J1645" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1645" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="1646">
@@ -83164,13 +83164,13 @@
         </is>
       </c>
       <c r="I1646" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J1646" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K1646" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="1647">
@@ -83215,13 +83215,13 @@
         </is>
       </c>
       <c r="I1647" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1647" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1647" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="1648">
@@ -83266,10 +83266,10 @@
         </is>
       </c>
       <c r="I1648" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J1648" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K1648" t="n">
         <v>0</v>
@@ -83317,13 +83317,13 @@
         </is>
       </c>
       <c r="I1649" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J1649" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K1649" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="1650">
@@ -83419,13 +83419,13 @@
         </is>
       </c>
       <c r="I1651" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1651" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1651" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="1652">
@@ -83470,13 +83470,13 @@
         </is>
       </c>
       <c r="I1652" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1652" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1652" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="1653">
@@ -83521,13 +83521,13 @@
         </is>
       </c>
       <c r="I1653" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J1653" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K1653" t="n">
-        <v>89</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1654">
@@ -83572,13 +83572,13 @@
         </is>
       </c>
       <c r="I1654" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J1654" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K1654" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
     </row>
     <row r="1655">
@@ -83721,13 +83721,13 @@
         </is>
       </c>
       <c r="I1657" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1657" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1657" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="1658">
@@ -83772,13 +83772,13 @@
         </is>
       </c>
       <c r="I1658" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1658" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1658" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="1659">
@@ -83976,13 +83976,13 @@
         </is>
       </c>
       <c r="I1662" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1662" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1662" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1663">
@@ -84023,13 +84023,13 @@
       </c>
       <c r="H1663" t="inlineStr"/>
       <c r="I1663" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="J1663" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="K1663" t="n">
-        <v>77</v>
+        <v>108</v>
       </c>
     </row>
     <row r="1664">
@@ -84076,7 +84076,7 @@
         <v>0</v>
       </c>
       <c r="K1664" t="n">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="1665">
@@ -84540,10 +84540,10 @@
       </c>
       <c r="H1674" t="inlineStr"/>
       <c r="I1674" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J1674" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K1674" t="n">
         <v>552</v>
@@ -84634,13 +84634,13 @@
       </c>
       <c r="H1676" t="inlineStr"/>
       <c r="I1676" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J1676" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K1676" t="n">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="1677">
@@ -84781,7 +84781,7 @@
         <v>1</v>
       </c>
       <c r="K1679" t="n">
-        <v>403</v>
+        <v>399</v>
       </c>
     </row>
     <row r="1680">
@@ -84822,10 +84822,10 @@
       </c>
       <c r="H1680" t="inlineStr"/>
       <c r="I1680" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1680" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1680" t="n">
         <v>164</v>
@@ -85104,10 +85104,10 @@
       </c>
       <c r="H1686" t="inlineStr"/>
       <c r="I1686" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J1686" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K1686" t="n">
         <v>383</v>
@@ -85198,10 +85198,10 @@
       </c>
       <c r="H1688" t="inlineStr"/>
       <c r="I1688" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1688" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1688" t="n">
         <v>228</v>
@@ -85668,13 +85668,13 @@
       </c>
       <c r="H1698" t="inlineStr"/>
       <c r="I1698" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J1698" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K1698" t="n">
-        <v>138</v>
+        <v>228</v>
       </c>
     </row>
     <row r="1699">
@@ -85770,13 +85770,13 @@
         </is>
       </c>
       <c r="I1700" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J1700" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K1700" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="1701">
@@ -85923,10 +85923,10 @@
         </is>
       </c>
       <c r="I1703" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J1703" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K1703" t="n">
         <v>14</v>
@@ -85974,10 +85974,10 @@
         </is>
       </c>
       <c r="I1704" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J1704" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1704" t="n">
         <v>288</v>
@@ -86031,7 +86031,7 @@
         <v>0</v>
       </c>
       <c r="K1705" t="n">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="1706">
@@ -86076,13 +86076,13 @@
         </is>
       </c>
       <c r="I1706" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1706" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1706" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="1707">
@@ -86113,27 +86113,23 @@
       </c>
       <c r="F1707" t="inlineStr">
         <is>
-          <t>SANTOS - EF</t>
+          <t>SANTOS - DP</t>
         </is>
       </c>
       <c r="G1707" t="inlineStr">
         <is>
-          <t>Jasmina Melo</t>
-        </is>
-      </c>
-      <c r="H1707" t="inlineStr">
-        <is>
-          <t>Lidia Tavares</t>
-        </is>
-      </c>
+          <t>Patricia Melo</t>
+        </is>
+      </c>
+      <c r="H1707" t="inlineStr"/>
       <c r="I1707" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J1707" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K1707" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1708">
@@ -86169,7 +86165,7 @@
       </c>
       <c r="G1708" t="inlineStr">
         <is>
-          <t>Karen Saadi</t>
+          <t>Jasmina Melo</t>
         </is>
       </c>
       <c r="H1708" t="inlineStr">
@@ -86178,13 +86174,13 @@
         </is>
       </c>
       <c r="I1708" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J1708" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="K1708" t="n">
-        <v>76</v>
+        <v>94</v>
       </c>
     </row>
     <row r="1709">
@@ -86220,7 +86216,7 @@
       </c>
       <c r="G1709" t="inlineStr">
         <is>
-          <t>Luckas Andrade</t>
+          <t>Karen Saadi</t>
         </is>
       </c>
       <c r="H1709" t="inlineStr">
@@ -86229,13 +86225,13 @@
         </is>
       </c>
       <c r="I1709" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J1709" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K1709" t="n">
-        <v>107</v>
+        <v>79</v>
       </c>
     </row>
     <row r="1710">
@@ -86271,7 +86267,7 @@
       </c>
       <c r="G1710" t="inlineStr">
         <is>
-          <t>Mirian Rodrigues</t>
+          <t>Luckas Andrade</t>
         </is>
       </c>
       <c r="H1710" t="inlineStr">
@@ -86280,13 +86276,13 @@
         </is>
       </c>
       <c r="I1710" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1710" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1710" t="n">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="1711">
@@ -86317,22 +86313,73 @@
       </c>
       <c r="F1711" t="inlineStr">
         <is>
+          <t>SANTOS - EF</t>
+        </is>
+      </c>
+      <c r="G1711" t="inlineStr">
+        <is>
+          <t>Mirian Rodrigues</t>
+        </is>
+      </c>
+      <c r="H1711" t="inlineStr">
+        <is>
+          <t>Lidia Tavares</t>
+        </is>
+      </c>
+      <c r="I1711" t="n">
+        <v>4</v>
+      </c>
+      <c r="J1711" t="n">
+        <v>4</v>
+      </c>
+      <c r="K1711" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="1712">
+      <c r="A1712" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B1712" t="inlineStr">
+        <is>
+          <t>Segunda</t>
+        </is>
+      </c>
+      <c r="C1712" t="inlineStr">
+        <is>
+          <t>2026-W25</t>
+        </is>
+      </c>
+      <c r="D1712" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1712" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="F1712" t="inlineStr">
+        <is>
           <t>SANTOS - GC</t>
         </is>
       </c>
-      <c r="G1711" t="inlineStr">
+      <c r="G1712" t="inlineStr">
         <is>
           <t>Rafaella Massuia</t>
         </is>
       </c>
-      <c r="H1711" t="inlineStr"/>
-      <c r="I1711" t="n">
-        <v>5</v>
-      </c>
-      <c r="J1711" t="n">
-        <v>5</v>
-      </c>
-      <c r="K1711" t="n">
+      <c r="H1712" t="inlineStr"/>
+      <c r="I1712" t="n">
+        <v>14</v>
+      </c>
+      <c r="J1712" t="n">
+        <v>14</v>
+      </c>
+      <c r="K1712" t="n">
         <v>109</v>
       </c>
     </row>

--- a/data/historico/historico_baixas.xlsx
+++ b/data/historico/historico_baixas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1712"/>
+  <dimension ref="A1:K1714"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -71624,13 +71624,13 @@
         </is>
       </c>
       <c r="I1418" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1418" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1418" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1419">
@@ -71726,13 +71726,13 @@
         </is>
       </c>
       <c r="I1420" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1420" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1420" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1421">
@@ -72232,13 +72232,13 @@
       </c>
       <c r="H1430" t="inlineStr"/>
       <c r="I1430" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1430" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1430" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1431">
@@ -72432,13 +72432,13 @@
       </c>
       <c r="H1434" t="inlineStr"/>
       <c r="I1434" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J1434" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1434" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1435">
@@ -72914,13 +72914,13 @@
       </c>
       <c r="H1444" t="inlineStr"/>
       <c r="I1444" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J1444" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K1444" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1445">
@@ -72965,13 +72965,13 @@
         </is>
       </c>
       <c r="I1445" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J1445" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="K1445" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1446">
@@ -73118,13 +73118,13 @@
         </is>
       </c>
       <c r="I1448" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J1448" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K1448" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="1449">
@@ -73220,13 +73220,13 @@
         </is>
       </c>
       <c r="I1450" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1450" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1450" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1451">
@@ -73475,13 +73475,13 @@
         </is>
       </c>
       <c r="I1455" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J1455" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K1455" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
     </row>
     <row r="1456">
@@ -73526,13 +73526,13 @@
         </is>
       </c>
       <c r="I1456" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J1456" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K1456" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1457">
@@ -73577,13 +73577,13 @@
         </is>
       </c>
       <c r="I1457" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1457" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K1457" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1458">
@@ -73824,10 +73824,10 @@
         </is>
       </c>
       <c r="I1462" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J1462" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K1462" t="n">
         <v>113</v>
@@ -74538,13 +74538,13 @@
         </is>
       </c>
       <c r="I1476" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J1476" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K1476" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="1477">
@@ -74589,10 +74589,10 @@
         </is>
       </c>
       <c r="I1477" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J1477" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1477" t="n">
         <v>181</v>
@@ -74691,10 +74691,10 @@
         </is>
       </c>
       <c r="I1479" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J1479" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K1479" t="n">
         <v>123</v>
@@ -74742,13 +74742,13 @@
         </is>
       </c>
       <c r="I1480" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J1480" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K1480" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="1481">
@@ -74793,13 +74793,13 @@
         </is>
       </c>
       <c r="I1481" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J1481" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="K1481" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
     </row>
     <row r="1482">
@@ -74844,13 +74844,13 @@
         </is>
       </c>
       <c r="I1482" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="J1482" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="K1482" t="n">
-        <v>169</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1483">
@@ -74997,13 +74997,13 @@
         </is>
       </c>
       <c r="I1485" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J1485" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K1485" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="1486">
@@ -75099,13 +75099,13 @@
         </is>
       </c>
       <c r="I1487" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J1487" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="K1487" t="n">
-        <v>226</v>
+        <v>235</v>
       </c>
     </row>
     <row r="1488">
@@ -75150,13 +75150,13 @@
         </is>
       </c>
       <c r="I1488" t="n">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="J1488" t="n">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="K1488" t="n">
-        <v>233</v>
+        <v>247</v>
       </c>
     </row>
     <row r="1489">
@@ -75542,13 +75542,13 @@
       </c>
       <c r="H1496" t="inlineStr"/>
       <c r="I1496" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="J1496" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="K1496" t="n">
-        <v>347</v>
+        <v>401</v>
       </c>
     </row>
     <row r="1497">
@@ -75895,13 +75895,13 @@
         </is>
       </c>
       <c r="I1503" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J1503" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K1503" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1504">
@@ -76248,13 +76248,13 @@
         </is>
       </c>
       <c r="I1510" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J1510" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K1510" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="1511">
@@ -76299,13 +76299,13 @@
         </is>
       </c>
       <c r="I1511" t="n">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="J1511" t="n">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K1511" t="n">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="1512">
@@ -76707,13 +76707,13 @@
         </is>
       </c>
       <c r="I1519" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J1519" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K1519" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="1520">
@@ -77009,13 +77009,13 @@
         </is>
       </c>
       <c r="I1525" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J1525" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K1525" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="1526">
@@ -77060,13 +77060,13 @@
         </is>
       </c>
       <c r="I1526" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J1526" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="K1526" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
     </row>
     <row r="1527">
@@ -77111,13 +77111,13 @@
         </is>
       </c>
       <c r="I1527" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="J1527" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="K1527" t="n">
-        <v>43</v>
+        <v>59</v>
       </c>
     </row>
     <row r="1528">
@@ -77570,13 +77570,13 @@
         </is>
       </c>
       <c r="I1536" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J1536" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="K1536" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
     </row>
     <row r="1537">
@@ -77723,13 +77723,13 @@
         </is>
       </c>
       <c r="I1539" t="n">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="J1539" t="n">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="K1539" t="n">
-        <v>79</v>
+        <v>103</v>
       </c>
     </row>
     <row r="1540">
@@ -77774,13 +77774,13 @@
         </is>
       </c>
       <c r="I1540" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J1540" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K1540" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1541">
@@ -77978,13 +77978,13 @@
         </is>
       </c>
       <c r="I1544" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="J1544" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="K1544" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1545">
@@ -78029,13 +78029,13 @@
         </is>
       </c>
       <c r="I1545" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="J1545" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K1545" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="1546">
@@ -78131,13 +78131,13 @@
         </is>
       </c>
       <c r="I1547" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="J1547" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="K1547" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1548">
@@ -78182,13 +78182,13 @@
         </is>
       </c>
       <c r="I1548" t="n">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="J1548" t="n">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="K1548" t="n">
-        <v>45</v>
+        <v>71</v>
       </c>
     </row>
     <row r="1549">
@@ -78335,13 +78335,13 @@
         </is>
       </c>
       <c r="I1551" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J1551" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K1551" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="1552">
@@ -78437,13 +78437,13 @@
         </is>
       </c>
       <c r="I1553" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J1553" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="K1553" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
     </row>
     <row r="1554">
@@ -78535,13 +78535,13 @@
         </is>
       </c>
       <c r="I1555" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J1555" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K1555" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="1556">
@@ -78637,13 +78637,13 @@
         </is>
       </c>
       <c r="I1557" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J1557" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K1557" t="n">
-        <v>71</v>
+        <v>78</v>
       </c>
     </row>
     <row r="1558">
@@ -78739,10 +78739,10 @@
         </is>
       </c>
       <c r="I1559" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1559" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1559" t="n">
         <v>16</v>
@@ -79045,10 +79045,10 @@
         </is>
       </c>
       <c r="I1565" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J1565" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K1565" t="n">
         <v>32</v>
@@ -79096,13 +79096,13 @@
         </is>
       </c>
       <c r="I1566" t="n">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="J1566" t="n">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="K1566" t="n">
-        <v>90</v>
+        <v>103</v>
       </c>
     </row>
     <row r="1567">
@@ -79300,13 +79300,13 @@
         </is>
       </c>
       <c r="I1570" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="J1570" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="K1570" t="n">
-        <v>47</v>
+        <v>86</v>
       </c>
     </row>
     <row r="1571">
@@ -79351,13 +79351,13 @@
         </is>
       </c>
       <c r="I1571" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J1571" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K1571" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="1572">
@@ -79708,13 +79708,13 @@
         </is>
       </c>
       <c r="I1578" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J1578" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="K1578" t="n">
-        <v>131</v>
+        <v>140</v>
       </c>
     </row>
     <row r="1579">
@@ -79759,13 +79759,13 @@
         </is>
       </c>
       <c r="I1579" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1579" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1579" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="1580">
@@ -79912,13 +79912,13 @@
         </is>
       </c>
       <c r="I1582" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="J1582" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="K1582" t="n">
-        <v>100</v>
+        <v>114</v>
       </c>
     </row>
     <row r="1583">
@@ -79963,13 +79963,13 @@
         </is>
       </c>
       <c r="I1583" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J1583" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K1583" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="1584">
@@ -80116,13 +80116,13 @@
         </is>
       </c>
       <c r="I1586" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J1586" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K1586" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1587">
@@ -80218,13 +80218,13 @@
         </is>
       </c>
       <c r="I1588" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J1588" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K1588" t="n">
-        <v>84</v>
+        <v>101</v>
       </c>
     </row>
     <row r="1589">
@@ -80265,13 +80265,13 @@
       </c>
       <c r="H1589" t="inlineStr"/>
       <c r="I1589" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J1589" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K1589" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1590">
@@ -80316,13 +80316,13 @@
         </is>
       </c>
       <c r="I1590" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1590" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K1590" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="1591">
@@ -80367,13 +80367,13 @@
         </is>
       </c>
       <c r="I1591" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="J1591" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="K1591" t="n">
-        <v>116</v>
+        <v>129</v>
       </c>
     </row>
     <row r="1592">
@@ -80418,10 +80418,10 @@
         </is>
       </c>
       <c r="I1592" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J1592" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1592" t="n">
         <v>122</v>
@@ -80469,13 +80469,13 @@
         </is>
       </c>
       <c r="I1593" t="n">
-        <v>4</v>
+        <v>73</v>
       </c>
       <c r="J1593" t="n">
-        <v>4</v>
+        <v>73</v>
       </c>
       <c r="K1593" t="n">
-        <v>101</v>
+        <v>169</v>
       </c>
     </row>
     <row r="1594">
@@ -80520,13 +80520,13 @@
         </is>
       </c>
       <c r="I1594" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="J1594" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="K1594" t="n">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="1595">
@@ -80571,10 +80571,10 @@
         </is>
       </c>
       <c r="I1595" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1595" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1595" t="n">
         <v>66</v>
@@ -80622,13 +80622,13 @@
         </is>
       </c>
       <c r="I1596" t="n">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="J1596" t="n">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="K1596" t="n">
-        <v>112</v>
+        <v>142</v>
       </c>
     </row>
     <row r="1597">
@@ -80724,13 +80724,13 @@
         </is>
       </c>
       <c r="I1598" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J1598" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K1598" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="1599">
@@ -80826,13 +80826,13 @@
         </is>
       </c>
       <c r="I1600" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J1600" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K1600" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="1601">
@@ -81030,13 +81030,13 @@
         </is>
       </c>
       <c r="I1604" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J1604" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K1604" t="n">
-        <v>170</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1605">
@@ -81128,13 +81128,13 @@
       </c>
       <c r="H1606" t="inlineStr"/>
       <c r="I1606" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="J1606" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="K1606" t="n">
-        <v>109</v>
+        <v>119</v>
       </c>
     </row>
     <row r="1607">
@@ -81179,13 +81179,13 @@
         </is>
       </c>
       <c r="I1607" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J1607" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K1607" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1608">
@@ -81230,13 +81230,13 @@
         </is>
       </c>
       <c r="I1608" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J1608" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="K1608" t="n">
-        <v>132</v>
+        <v>138</v>
       </c>
     </row>
     <row r="1609">
@@ -81281,13 +81281,13 @@
         </is>
       </c>
       <c r="I1609" t="n">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="J1609" t="n">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="K1609" t="n">
-        <v>637</v>
+        <v>666</v>
       </c>
     </row>
     <row r="1610">
@@ -81332,13 +81332,13 @@
         </is>
       </c>
       <c r="I1610" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J1610" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K1610" t="n">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="1611">
@@ -81383,13 +81383,13 @@
         </is>
       </c>
       <c r="I1611" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J1611" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K1611" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="1612">
@@ -81491,7 +81491,7 @@
         <v>0</v>
       </c>
       <c r="K1613" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1614">
@@ -81536,13 +81536,13 @@
         </is>
       </c>
       <c r="I1614" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J1614" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="K1614" t="n">
-        <v>142</v>
+        <v>149</v>
       </c>
     </row>
     <row r="1615">
@@ -81587,13 +81587,13 @@
         </is>
       </c>
       <c r="I1615" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J1615" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K1615" t="n">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="1616">
@@ -81689,13 +81689,13 @@
         </is>
       </c>
       <c r="I1617" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J1617" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1617" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="1618">
@@ -81842,13 +81842,13 @@
         </is>
       </c>
       <c r="I1620" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J1620" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K1620" t="n">
-        <v>195</v>
+        <v>200</v>
       </c>
     </row>
     <row r="1621">
@@ -81893,13 +81893,13 @@
         </is>
       </c>
       <c r="I1621" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J1621" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K1621" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="1622">
@@ -81944,13 +81944,13 @@
         </is>
       </c>
       <c r="I1622" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="J1622" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="K1622" t="n">
-        <v>106</v>
+        <v>117</v>
       </c>
     </row>
     <row r="1623">
@@ -81995,13 +81995,13 @@
         </is>
       </c>
       <c r="I1623" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="J1623" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="K1623" t="n">
-        <v>99</v>
+        <v>107</v>
       </c>
     </row>
     <row r="1624">
@@ -82046,13 +82046,13 @@
         </is>
       </c>
       <c r="I1624" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="J1624" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="K1624" t="n">
-        <v>161</v>
+        <v>188</v>
       </c>
     </row>
     <row r="1625">
@@ -82097,13 +82097,13 @@
         </is>
       </c>
       <c r="I1625" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J1625" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="K1625" t="n">
-        <v>88</v>
+        <v>82</v>
       </c>
     </row>
     <row r="1626">
@@ -82148,13 +82148,13 @@
         </is>
       </c>
       <c r="I1626" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J1626" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K1626" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="1627">
@@ -82199,13 +82199,13 @@
         </is>
       </c>
       <c r="I1627" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J1627" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="K1627" t="n">
-        <v>154</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1628">
@@ -82252,7 +82252,7 @@
         <v>0</v>
       </c>
       <c r="K1628" t="n">
-        <v>207</v>
+        <v>218</v>
       </c>
     </row>
     <row r="1629">
@@ -82348,13 +82348,13 @@
         </is>
       </c>
       <c r="I1630" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J1630" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="K1630" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="1631">
@@ -82399,13 +82399,13 @@
         </is>
       </c>
       <c r="I1631" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J1631" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K1631" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="1632">
@@ -82450,13 +82450,13 @@
         </is>
       </c>
       <c r="I1632" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J1632" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K1632" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="1633">
@@ -82552,13 +82552,13 @@
         </is>
       </c>
       <c r="I1634" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J1634" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="K1634" t="n">
-        <v>111</v>
+        <v>121</v>
       </c>
     </row>
     <row r="1635">
@@ -82603,13 +82603,13 @@
         </is>
       </c>
       <c r="I1635" t="n">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="J1635" t="n">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="K1635" t="n">
-        <v>243</v>
+        <v>298</v>
       </c>
     </row>
     <row r="1636">
@@ -82654,13 +82654,13 @@
         </is>
       </c>
       <c r="I1636" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1636" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1636" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="1637">
@@ -82705,13 +82705,13 @@
         </is>
       </c>
       <c r="I1637" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J1637" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K1637" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="1638">
@@ -82756,13 +82756,13 @@
         </is>
       </c>
       <c r="I1638" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="J1638" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="K1638" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="1639">
@@ -82798,22 +82798,22 @@
       </c>
       <c r="G1639" t="inlineStr">
         <is>
-          <t>Jose Natan</t>
+          <t>Jose Borges</t>
         </is>
       </c>
       <c r="H1639" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="I1639" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="J1639" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="K1639" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1640">
@@ -82849,7 +82849,7 @@
       </c>
       <c r="G1640" t="inlineStr">
         <is>
-          <t>João Oliveira</t>
+          <t>Jose Natan</t>
         </is>
       </c>
       <c r="H1640" t="inlineStr">
@@ -82858,13 +82858,13 @@
         </is>
       </c>
       <c r="I1640" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="J1640" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="K1640" t="n">
-        <v>21</v>
+        <v>147</v>
       </c>
     </row>
     <row r="1641">
@@ -82900,22 +82900,22 @@
       </c>
       <c r="G1641" t="inlineStr">
         <is>
-          <t>Juan Ribeiro</t>
+          <t>João Oliveira</t>
         </is>
       </c>
       <c r="H1641" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I1641" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J1641" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K1641" t="n">
-        <v>96</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1642">
@@ -82951,22 +82951,22 @@
       </c>
       <c r="G1642" t="inlineStr">
         <is>
-          <t>Juliana Valeria</t>
+          <t>Juan Ribeiro</t>
         </is>
       </c>
       <c r="H1642" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I1642" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J1642" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K1642" t="n">
-        <v>145</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1643">
@@ -83002,7 +83002,7 @@
       </c>
       <c r="G1643" t="inlineStr">
         <is>
-          <t>Juliane Vaz</t>
+          <t>Juliana Valeria</t>
         </is>
       </c>
       <c r="H1643" t="inlineStr">
@@ -83011,13 +83011,13 @@
         </is>
       </c>
       <c r="I1643" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="J1643" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="K1643" t="n">
-        <v>295</v>
+        <v>150</v>
       </c>
     </row>
     <row r="1644">
@@ -83053,22 +83053,22 @@
       </c>
       <c r="G1644" t="inlineStr">
         <is>
-          <t>Katia Xavier</t>
+          <t>Juliane Vaz</t>
         </is>
       </c>
       <c r="H1644" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I1644" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J1644" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K1644" t="n">
-        <v>115</v>
+        <v>296</v>
       </c>
     </row>
     <row r="1645">
@@ -83104,22 +83104,22 @@
       </c>
       <c r="G1645" t="inlineStr">
         <is>
-          <t>Larissa Félix</t>
+          <t>Katia Xavier</t>
         </is>
       </c>
       <c r="H1645" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I1645" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J1645" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K1645" t="n">
-        <v>217</v>
+        <v>103</v>
       </c>
     </row>
     <row r="1646">
@@ -83155,22 +83155,22 @@
       </c>
       <c r="G1646" t="inlineStr">
         <is>
-          <t>Léia de Oliveira</t>
+          <t>Larissa Félix</t>
         </is>
       </c>
       <c r="H1646" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I1646" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J1646" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="K1646" t="n">
-        <v>135</v>
+        <v>224</v>
       </c>
     </row>
     <row r="1647">
@@ -83206,7 +83206,7 @@
       </c>
       <c r="G1647" t="inlineStr">
         <is>
-          <t>Maria Gualberto</t>
+          <t>Léia de Oliveira</t>
         </is>
       </c>
       <c r="H1647" t="inlineStr">
@@ -83215,13 +83215,13 @@
         </is>
       </c>
       <c r="I1647" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J1647" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K1647" t="n">
-        <v>111</v>
+        <v>142</v>
       </c>
     </row>
     <row r="1648">
@@ -83257,22 +83257,22 @@
       </c>
       <c r="G1648" t="inlineStr">
         <is>
-          <t>Nathany Silva</t>
+          <t>Maria Gualberto</t>
         </is>
       </c>
       <c r="H1648" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I1648" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J1648" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K1648" t="n">
-        <v>0</v>
+        <v>112</v>
       </c>
     </row>
     <row r="1649">
@@ -83308,22 +83308,22 @@
       </c>
       <c r="G1649" t="inlineStr">
         <is>
-          <t>Priscila Moreira</t>
+          <t>Nathany Silva</t>
         </is>
       </c>
       <c r="H1649" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I1649" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J1649" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K1649" t="n">
-        <v>145</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1650">
@@ -83359,22 +83359,22 @@
       </c>
       <c r="G1650" t="inlineStr">
         <is>
-          <t>Regiane Santos</t>
+          <t>Priscila Moreira</t>
         </is>
       </c>
       <c r="H1650" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="I1650" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J1650" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K1650" t="n">
-        <v>68</v>
+        <v>145</v>
       </c>
     </row>
     <row r="1651">
@@ -83410,22 +83410,22 @@
       </c>
       <c r="G1651" t="inlineStr">
         <is>
-          <t>Shofia Gomes</t>
+          <t>Regiane Santos</t>
         </is>
       </c>
       <c r="H1651" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I1651" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J1651" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K1651" t="n">
-        <v>137</v>
+        <v>68</v>
       </c>
     </row>
     <row r="1652">
@@ -83461,22 +83461,22 @@
       </c>
       <c r="G1652" t="inlineStr">
         <is>
-          <t>Vanessa Tavares</t>
+          <t>Shofia Gomes</t>
         </is>
       </c>
       <c r="H1652" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="I1652" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J1652" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1652" t="n">
-        <v>90</v>
+        <v>138</v>
       </c>
     </row>
     <row r="1653">
@@ -83512,7 +83512,7 @@
       </c>
       <c r="G1653" t="inlineStr">
         <is>
-          <t>Willian Luz</t>
+          <t>Vanessa Tavares</t>
         </is>
       </c>
       <c r="H1653" t="inlineStr">
@@ -83521,13 +83521,13 @@
         </is>
       </c>
       <c r="I1653" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J1653" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="K1653" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="1654">
@@ -83563,7 +83563,7 @@
       </c>
       <c r="G1654" t="inlineStr">
         <is>
-          <t>Yasmim Oliveira</t>
+          <t>Willian Luz</t>
         </is>
       </c>
       <c r="H1654" t="inlineStr">
@@ -83572,13 +83572,13 @@
         </is>
       </c>
       <c r="I1654" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J1654" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K1654" t="n">
-        <v>54</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1655">
@@ -83609,23 +83609,27 @@
       </c>
       <c r="F1655" t="inlineStr">
         <is>
-          <t>ESCRITA FISCAL (Outsourcing)</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="G1655" t="inlineStr">
         <is>
-          <t>Claudineia Rodrigues</t>
-        </is>
-      </c>
-      <c r="H1655" t="inlineStr"/>
+          <t>Yasmim Oliveira</t>
+        </is>
+      </c>
+      <c r="H1655" t="inlineStr">
+        <is>
+          <t>Larice Souza</t>
+        </is>
+      </c>
       <c r="I1655" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J1655" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K1655" t="n">
-        <v>5</v>
+        <v>54</v>
       </c>
     </row>
     <row r="1656">
@@ -83661,14 +83665,10 @@
       </c>
       <c r="G1656" t="inlineStr">
         <is>
-          <t>Diego Pereira</t>
-        </is>
-      </c>
-      <c r="H1656" t="inlineStr">
-        <is>
-          <t>Thaiza Oliveira</t>
-        </is>
-      </c>
+          <t>Claudineia Rodrigues</t>
+        </is>
+      </c>
+      <c r="H1656" t="inlineStr"/>
       <c r="I1656" t="n">
         <v>0</v>
       </c>
@@ -83676,7 +83676,7 @@
         <v>0</v>
       </c>
       <c r="K1656" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1657">
@@ -83712,22 +83712,22 @@
       </c>
       <c r="G1657" t="inlineStr">
         <is>
-          <t>Gislaine Lima</t>
+          <t>Diego Pereira</t>
         </is>
       </c>
       <c r="H1657" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I1657" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J1657" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1657" t="n">
-        <v>38</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1658">
@@ -83763,7 +83763,7 @@
       </c>
       <c r="G1658" t="inlineStr">
         <is>
-          <t>Joanna Costa</t>
+          <t>Gislaine Lima</t>
         </is>
       </c>
       <c r="H1658" t="inlineStr">
@@ -83772,13 +83772,13 @@
         </is>
       </c>
       <c r="I1658" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J1658" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1658" t="n">
-        <v>61</v>
+        <v>39</v>
       </c>
     </row>
     <row r="1659">
@@ -83814,22 +83814,22 @@
       </c>
       <c r="G1659" t="inlineStr">
         <is>
-          <t>Jonatan Hayashibara</t>
+          <t>Joanna Costa</t>
         </is>
       </c>
       <c r="H1659" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I1659" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1659" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K1659" t="n">
-        <v>4</v>
+        <v>63</v>
       </c>
     </row>
     <row r="1660">
@@ -83865,22 +83865,22 @@
       </c>
       <c r="G1660" t="inlineStr">
         <is>
-          <t>João Oliveira</t>
+          <t>Jonatan Hayashibara</t>
         </is>
       </c>
       <c r="H1660" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
       <c r="I1660" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J1660" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K1660" t="n">
-        <v>70</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1661">
@@ -83916,12 +83916,12 @@
       </c>
       <c r="G1661" t="inlineStr">
         <is>
-          <t>Regiane Santos</t>
+          <t>Jose Borges</t>
         </is>
       </c>
       <c r="H1661" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="I1661" t="n">
@@ -83931,7 +83931,7 @@
         <v>1</v>
       </c>
       <c r="K1661" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1662">
@@ -83967,7 +83967,7 @@
       </c>
       <c r="G1662" t="inlineStr">
         <is>
-          <t>Yasmim Oliveira</t>
+          <t>João Oliveira</t>
         </is>
       </c>
       <c r="H1662" t="inlineStr">
@@ -83976,13 +83976,13 @@
         </is>
       </c>
       <c r="I1662" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="J1662" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="K1662" t="n">
-        <v>8</v>
+        <v>70</v>
       </c>
     </row>
     <row r="1663">
@@ -84013,23 +84013,27 @@
       </c>
       <c r="F1663" t="inlineStr">
         <is>
-          <t>FIN - CONTÁBIL</t>
+          <t>ESCRITA FISCAL (Outsourcing)</t>
         </is>
       </c>
       <c r="G1663" t="inlineStr">
         <is>
-          <t>Daniele Faria</t>
-        </is>
-      </c>
-      <c r="H1663" t="inlineStr"/>
+          <t>Regiane Santos</t>
+        </is>
+      </c>
+      <c r="H1663" t="inlineStr">
+        <is>
+          <t>Larice Souza</t>
+        </is>
+      </c>
       <c r="I1663" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="J1663" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="K1663" t="n">
-        <v>108</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1664">
@@ -84060,23 +84064,27 @@
       </c>
       <c r="F1664" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>ESCRITA FISCAL (Outsourcing)</t>
         </is>
       </c>
       <c r="G1664" t="inlineStr">
         <is>
-          <t>Ana Santana</t>
-        </is>
-      </c>
-      <c r="H1664" t="inlineStr"/>
+          <t>Yasmim Oliveira</t>
+        </is>
+      </c>
+      <c r="H1664" t="inlineStr">
+        <is>
+          <t>Larice Souza</t>
+        </is>
+      </c>
       <c r="I1664" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1664" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1664" t="n">
-        <v>587</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1665">
@@ -84107,23 +84115,23 @@
       </c>
       <c r="F1665" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>FIN - CONTÁBIL</t>
         </is>
       </c>
       <c r="G1665" t="inlineStr">
         <is>
-          <t>Andre Coelho</t>
+          <t>Daniele Faria</t>
         </is>
       </c>
       <c r="H1665" t="inlineStr"/>
       <c r="I1665" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="J1665" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="K1665" t="n">
-        <v>16</v>
+        <v>108</v>
       </c>
     </row>
     <row r="1666">
@@ -84159,18 +84167,18 @@
       </c>
       <c r="G1666" t="inlineStr">
         <is>
-          <t>Bianca Castro</t>
+          <t>Ana Santana</t>
         </is>
       </c>
       <c r="H1666" t="inlineStr"/>
       <c r="I1666" t="n">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="J1666" t="n">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="K1666" t="n">
-        <v>459</v>
+        <v>587</v>
       </c>
     </row>
     <row r="1667">
@@ -84206,7 +84214,7 @@
       </c>
       <c r="G1667" t="inlineStr">
         <is>
-          <t>Bruna Costa</t>
+          <t>Andre Coelho</t>
         </is>
       </c>
       <c r="H1667" t="inlineStr"/>
@@ -84217,7 +84225,7 @@
         <v>0</v>
       </c>
       <c r="K1667" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1668">
@@ -84253,18 +84261,18 @@
       </c>
       <c r="G1668" t="inlineStr">
         <is>
-          <t>Daniela Silva</t>
+          <t>Bianca Castro</t>
         </is>
       </c>
       <c r="H1668" t="inlineStr"/>
       <c r="I1668" t="n">
-        <v>97</v>
+        <v>5</v>
       </c>
       <c r="J1668" t="n">
-        <v>97</v>
+        <v>5</v>
       </c>
       <c r="K1668" t="n">
-        <v>302</v>
+        <v>458</v>
       </c>
     </row>
     <row r="1669">
@@ -84300,18 +84308,18 @@
       </c>
       <c r="G1669" t="inlineStr">
         <is>
-          <t>Isabelli Afonso</t>
+          <t>Bruna Costa</t>
         </is>
       </c>
       <c r="H1669" t="inlineStr"/>
       <c r="I1669" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J1669" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1669" t="n">
-        <v>234</v>
+        <v>34</v>
       </c>
     </row>
     <row r="1670">
@@ -84347,18 +84355,18 @@
       </c>
       <c r="G1670" t="inlineStr">
         <is>
-          <t>Jurema Damacena - SAC</t>
+          <t>Daniela Silva</t>
         </is>
       </c>
       <c r="H1670" t="inlineStr"/>
       <c r="I1670" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="J1670" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="K1670" t="n">
-        <v>1</v>
+        <v>302</v>
       </c>
     </row>
     <row r="1671">
@@ -84394,18 +84402,18 @@
       </c>
       <c r="G1671" t="inlineStr">
         <is>
-          <t>Leticia Queiroz</t>
+          <t>Isabelli Afonso</t>
         </is>
       </c>
       <c r="H1671" t="inlineStr"/>
       <c r="I1671" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J1671" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K1671" t="n">
-        <v>428</v>
+        <v>234</v>
       </c>
     </row>
     <row r="1672">
@@ -84441,18 +84449,18 @@
       </c>
       <c r="G1672" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Jurema Damacena - SAC</t>
         </is>
       </c>
       <c r="H1672" t="inlineStr"/>
       <c r="I1672" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J1672" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K1672" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1673">
@@ -84488,18 +84496,18 @@
       </c>
       <c r="G1673" t="inlineStr">
         <is>
-          <t>Victoria Virgens</t>
+          <t>Leticia Queiroz</t>
         </is>
       </c>
       <c r="H1673" t="inlineStr"/>
       <c r="I1673" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J1673" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K1673" t="n">
-        <v>309</v>
+        <v>428</v>
       </c>
     </row>
     <row r="1674">
@@ -84535,18 +84543,18 @@
       </c>
       <c r="G1674" t="inlineStr">
         <is>
-          <t>Yasmin Peixoto</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="H1674" t="inlineStr"/>
       <c r="I1674" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J1674" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="K1674" t="n">
-        <v>552</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1675">
@@ -84577,23 +84585,23 @@
       </c>
       <c r="F1675" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="G1675" t="inlineStr">
         <is>
-          <t>Andre Coelho</t>
+          <t>Victoria Virgens</t>
         </is>
       </c>
       <c r="H1675" t="inlineStr"/>
       <c r="I1675" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1675" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1675" t="n">
-        <v>4</v>
+        <v>309</v>
       </c>
     </row>
     <row r="1676">
@@ -84624,23 +84632,23 @@
       </c>
       <c r="F1676" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="G1676" t="inlineStr">
         <is>
-          <t>Beatriz Rangel</t>
+          <t>Yasmin Peixoto</t>
         </is>
       </c>
       <c r="H1676" t="inlineStr"/>
       <c r="I1676" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="J1676" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="K1676" t="n">
-        <v>375</v>
+        <v>554</v>
       </c>
     </row>
     <row r="1677">
@@ -84676,18 +84684,18 @@
       </c>
       <c r="G1677" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
+          <t>Andre Coelho</t>
         </is>
       </c>
       <c r="H1677" t="inlineStr"/>
       <c r="I1677" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="J1677" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="K1677" t="n">
-        <v>434</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1678">
@@ -84723,18 +84731,18 @@
       </c>
       <c r="G1678" t="inlineStr">
         <is>
-          <t>Cristiane Simões</t>
+          <t>Beatriz Rangel</t>
         </is>
       </c>
       <c r="H1678" t="inlineStr"/>
       <c r="I1678" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J1678" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K1678" t="n">
-        <v>305</v>
+        <v>375</v>
       </c>
     </row>
     <row r="1679">
@@ -84770,18 +84778,18 @@
       </c>
       <c r="G1679" t="inlineStr">
         <is>
-          <t>Daniel Oliveira</t>
+          <t>Bruno Contieri</t>
         </is>
       </c>
       <c r="H1679" t="inlineStr"/>
       <c r="I1679" t="n">
-        <v>1</v>
+        <v>95</v>
       </c>
       <c r="J1679" t="n">
-        <v>1</v>
+        <v>95</v>
       </c>
       <c r="K1679" t="n">
-        <v>399</v>
+        <v>434</v>
       </c>
     </row>
     <row r="1680">
@@ -84817,18 +84825,18 @@
       </c>
       <c r="G1680" t="inlineStr">
         <is>
-          <t>Diego Lima</t>
+          <t>Cristiane Simões</t>
         </is>
       </c>
       <c r="H1680" t="inlineStr"/>
       <c r="I1680" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J1680" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K1680" t="n">
-        <v>164</v>
+        <v>305</v>
       </c>
     </row>
     <row r="1681">
@@ -84864,18 +84872,18 @@
       </c>
       <c r="G1681" t="inlineStr">
         <is>
-          <t>Eduardo Aparicio</t>
+          <t>Daniel Oliveira</t>
         </is>
       </c>
       <c r="H1681" t="inlineStr"/>
       <c r="I1681" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J1681" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K1681" t="n">
-        <v>1</v>
+        <v>399</v>
       </c>
     </row>
     <row r="1682">
@@ -84911,18 +84919,18 @@
       </c>
       <c r="G1682" t="inlineStr">
         <is>
-          <t>Karine Gusmão</t>
+          <t>Diego Lima</t>
         </is>
       </c>
       <c r="H1682" t="inlineStr"/>
       <c r="I1682" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1682" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1682" t="n">
-        <v>93</v>
+        <v>164</v>
       </c>
     </row>
     <row r="1683">
@@ -84958,18 +84966,18 @@
       </c>
       <c r="G1683" t="inlineStr">
         <is>
-          <t>Luiz Ferreira</t>
+          <t>Eduardo Aparicio</t>
         </is>
       </c>
       <c r="H1683" t="inlineStr"/>
       <c r="I1683" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1683" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1683" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1684">
@@ -85005,7 +85013,7 @@
       </c>
       <c r="G1684" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Karine Gusmão</t>
         </is>
       </c>
       <c r="H1684" t="inlineStr"/>
@@ -85016,7 +85024,7 @@
         <v>0</v>
       </c>
       <c r="K1684" t="n">
-        <v>221</v>
+        <v>93</v>
       </c>
     </row>
     <row r="1685">
@@ -85052,7 +85060,7 @@
       </c>
       <c r="G1685" t="inlineStr">
         <is>
-          <t>Rodrigo Rego</t>
+          <t>Luiz Ferreira</t>
         </is>
       </c>
       <c r="H1685" t="inlineStr"/>
@@ -85063,7 +85071,7 @@
         <v>0</v>
       </c>
       <c r="K1685" t="n">
-        <v>460</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1686">
@@ -85099,18 +85107,18 @@
       </c>
       <c r="G1686" t="inlineStr">
         <is>
-          <t>Rogerio Egidio</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="H1686" t="inlineStr"/>
       <c r="I1686" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J1686" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K1686" t="n">
-        <v>383</v>
+        <v>221</v>
       </c>
     </row>
     <row r="1687">
@@ -85146,7 +85154,7 @@
       </c>
       <c r="G1687" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Rodrigo Rego</t>
         </is>
       </c>
       <c r="H1687" t="inlineStr"/>
@@ -85157,7 +85165,7 @@
         <v>2</v>
       </c>
       <c r="K1687" t="n">
-        <v>50</v>
+        <v>460</v>
       </c>
     </row>
     <row r="1688">
@@ -85193,18 +85201,18 @@
       </c>
       <c r="G1688" t="inlineStr">
         <is>
-          <t>Simone Marques</t>
+          <t>Rogerio Egidio</t>
         </is>
       </c>
       <c r="H1688" t="inlineStr"/>
       <c r="I1688" t="n">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="J1688" t="n">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="K1688" t="n">
-        <v>228</v>
+        <v>385</v>
       </c>
     </row>
     <row r="1689">
@@ -85240,18 +85248,18 @@
       </c>
       <c r="G1689" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="H1689" t="inlineStr"/>
       <c r="I1689" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1689" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1689" t="n">
-        <v>267</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1690">
@@ -85282,23 +85290,23 @@
       </c>
       <c r="F1690" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="G1690" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Simone Marques</t>
         </is>
       </c>
       <c r="H1690" t="inlineStr"/>
       <c r="I1690" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="J1690" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="K1690" t="n">
-        <v>1</v>
+        <v>229</v>
       </c>
     </row>
     <row r="1691">
@@ -85329,23 +85337,23 @@
       </c>
       <c r="F1691" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="G1691" t="inlineStr">
         <is>
-          <t>Jurema Damacena - SAC</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="H1691" t="inlineStr"/>
       <c r="I1691" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J1691" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K1691" t="n">
-        <v>52</v>
+        <v>267</v>
       </c>
     </row>
     <row r="1692">
@@ -85376,12 +85384,12 @@
       </c>
       <c r="F1692" t="inlineStr">
         <is>
-          <t>MG CONTABIFÁCIL - CTB</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="G1692" t="inlineStr">
         <is>
-          <t>Guilherme Delecrodio</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="H1692" t="inlineStr"/>
@@ -85423,19 +85431,23 @@
       </c>
       <c r="F1693" t="inlineStr">
         <is>
-          <t>MG EXPRESS - CTB</t>
-        </is>
-      </c>
-      <c r="G1693" t="inlineStr"/>
+          <t>GERENCIA MASTER</t>
+        </is>
+      </c>
+      <c r="G1693" t="inlineStr">
+        <is>
+          <t>Jurema Damacena - SAC</t>
+        </is>
+      </c>
       <c r="H1693" t="inlineStr"/>
       <c r="I1693" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J1693" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="K1693" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1694">
@@ -85466,7 +85478,7 @@
       </c>
       <c r="F1694" t="inlineStr">
         <is>
-          <t>MG EXPRESS - CTB</t>
+          <t>MG CONTABIFÁCIL - CTB</t>
         </is>
       </c>
       <c r="G1694" t="inlineStr">
@@ -85482,7 +85494,7 @@
         <v>0</v>
       </c>
       <c r="K1694" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1695">
@@ -85513,23 +85525,19 @@
       </c>
       <c r="F1695" t="inlineStr">
         <is>
-          <t>S.A.C</t>
-        </is>
-      </c>
-      <c r="G1695" t="inlineStr">
-        <is>
-          <t>Ana Celia - SAC</t>
-        </is>
-      </c>
+          <t>MG EXPRESS - CTB</t>
+        </is>
+      </c>
+      <c r="G1695" t="inlineStr"/>
       <c r="H1695" t="inlineStr"/>
       <c r="I1695" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J1695" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K1695" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1696">
@@ -85560,19 +85568,15 @@
       </c>
       <c r="F1696" t="inlineStr">
         <is>
-          <t>SANTOS - DP</t>
+          <t>MG EXPRESS - CTB</t>
         </is>
       </c>
       <c r="G1696" t="inlineStr">
         <is>
-          <t>Katia Valeria</t>
-        </is>
-      </c>
-      <c r="H1696" t="inlineStr">
-        <is>
-          <t>Katia Valeria</t>
-        </is>
-      </c>
+          <t>Guilherme Delecrodio</t>
+        </is>
+      </c>
+      <c r="H1696" t="inlineStr"/>
       <c r="I1696" t="n">
         <v>0</v>
       </c>
@@ -85580,7 +85584,7 @@
         <v>0</v>
       </c>
       <c r="K1696" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1697">
@@ -85606,28 +85610,28 @@
       </c>
       <c r="E1697" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F1697" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>S.A.C</t>
         </is>
       </c>
       <c r="G1697" t="inlineStr">
         <is>
-          <t>Jurema Damacena - SAC</t>
+          <t>Ana Celia - SAC</t>
         </is>
       </c>
       <c r="H1697" t="inlineStr"/>
       <c r="I1697" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J1697" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K1697" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1698">
@@ -85653,28 +85657,32 @@
       </c>
       <c r="E1698" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F1698" t="inlineStr">
         <is>
-          <t>SANTOS - ADM</t>
+          <t>SANTOS - DP</t>
         </is>
       </c>
       <c r="G1698" t="inlineStr">
         <is>
-          <t>Kauany Pereira</t>
-        </is>
-      </c>
-      <c r="H1698" t="inlineStr"/>
+          <t>Katia Valeria</t>
+        </is>
+      </c>
+      <c r="H1698" t="inlineStr">
+        <is>
+          <t>Katia Valeria</t>
+        </is>
+      </c>
       <c r="I1698" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="J1698" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="K1698" t="n">
-        <v>228</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1699">
@@ -85705,27 +85713,23 @@
       </c>
       <c r="F1699" t="inlineStr">
         <is>
-          <t>SANTOS - CTB</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="G1699" t="inlineStr">
         <is>
-          <t>Ivia Oliveira</t>
-        </is>
-      </c>
-      <c r="H1699" t="inlineStr">
-        <is>
-          <t>Roberto Silva</t>
-        </is>
-      </c>
+          <t>Jurema Damacena - SAC</t>
+        </is>
+      </c>
+      <c r="H1699" t="inlineStr"/>
       <c r="I1699" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1699" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1699" t="n">
-        <v>57</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1700">
@@ -85756,27 +85760,23 @@
       </c>
       <c r="F1700" t="inlineStr">
         <is>
-          <t>SANTOS - CTB</t>
+          <t>SANTOS - ADM</t>
         </is>
       </c>
       <c r="G1700" t="inlineStr">
         <is>
-          <t>Nata Trindade</t>
-        </is>
-      </c>
-      <c r="H1700" t="inlineStr">
-        <is>
-          <t>Roberto Silva</t>
-        </is>
-      </c>
+          <t>Kauany Pereira</t>
+        </is>
+      </c>
+      <c r="H1700" t="inlineStr"/>
       <c r="I1700" t="n">
-        <v>4</v>
+        <v>95</v>
       </c>
       <c r="J1700" t="n">
-        <v>4</v>
+        <v>95</v>
       </c>
       <c r="K1700" t="n">
-        <v>86</v>
+        <v>233</v>
       </c>
     </row>
     <row r="1701">
@@ -85812,14 +85812,14 @@
       </c>
       <c r="G1701" t="inlineStr">
         <is>
+          <t>Ivia Oliveira</t>
+        </is>
+      </c>
+      <c r="H1701" t="inlineStr">
+        <is>
           <t>Roberto Silva</t>
         </is>
       </c>
-      <c r="H1701" t="inlineStr">
-        <is>
-          <t>Roberto Silva</t>
-        </is>
-      </c>
       <c r="I1701" t="n">
         <v>0</v>
       </c>
@@ -85827,7 +85827,7 @@
         <v>0</v>
       </c>
       <c r="K1701" t="n">
-        <v>111</v>
+        <v>57</v>
       </c>
     </row>
     <row r="1702">
@@ -85863,7 +85863,7 @@
       </c>
       <c r="G1702" t="inlineStr">
         <is>
-          <t>Thaina Rodrigues</t>
+          <t>Nata Trindade</t>
         </is>
       </c>
       <c r="H1702" t="inlineStr">
@@ -85872,13 +85872,13 @@
         </is>
       </c>
       <c r="I1702" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J1702" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K1702" t="n">
-        <v>94</v>
+        <v>86</v>
       </c>
     </row>
     <row r="1703">
@@ -85909,27 +85909,27 @@
       </c>
       <c r="F1703" t="inlineStr">
         <is>
-          <t>SANTOS - DP</t>
+          <t>SANTOS - CTB</t>
         </is>
       </c>
       <c r="G1703" t="inlineStr">
         <is>
-          <t>Bruna Silva</t>
+          <t>Roberto Silva</t>
         </is>
       </c>
       <c r="H1703" t="inlineStr">
         <is>
-          <t>Katia Valeria</t>
+          <t>Roberto Silva</t>
         </is>
       </c>
       <c r="I1703" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J1703" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="K1703" t="n">
-        <v>14</v>
+        <v>113</v>
       </c>
     </row>
     <row r="1704">
@@ -85960,27 +85960,27 @@
       </c>
       <c r="F1704" t="inlineStr">
         <is>
-          <t>SANTOS - DP</t>
+          <t>SANTOS - CTB</t>
         </is>
       </c>
       <c r="G1704" t="inlineStr">
         <is>
-          <t>Carliane Silva</t>
+          <t>Thaina Rodrigues</t>
         </is>
       </c>
       <c r="H1704" t="inlineStr">
         <is>
-          <t>Katia Valeria</t>
+          <t>Roberto Silva</t>
         </is>
       </c>
       <c r="I1704" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J1704" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K1704" t="n">
-        <v>288</v>
+        <v>94</v>
       </c>
     </row>
     <row r="1705">
@@ -86016,7 +86016,7 @@
       </c>
       <c r="G1705" t="inlineStr">
         <is>
-          <t>Cintia Andrade</t>
+          <t>Bruna Silva</t>
         </is>
       </c>
       <c r="H1705" t="inlineStr">
@@ -86025,13 +86025,13 @@
         </is>
       </c>
       <c r="I1705" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J1705" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K1705" t="n">
-        <v>216</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1706">
@@ -86067,22 +86067,22 @@
       </c>
       <c r="G1706" t="inlineStr">
         <is>
+          <t>Carliane Silva</t>
+        </is>
+      </c>
+      <c r="H1706" t="inlineStr">
+        <is>
           <t>Katia Valeria</t>
         </is>
       </c>
-      <c r="H1706" t="inlineStr">
-        <is>
-          <t>Katia Valeria</t>
-        </is>
-      </c>
       <c r="I1706" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="J1706" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="K1706" t="n">
-        <v>352</v>
+        <v>316</v>
       </c>
     </row>
     <row r="1707">
@@ -86118,18 +86118,22 @@
       </c>
       <c r="G1707" t="inlineStr">
         <is>
-          <t>Patricia Melo</t>
-        </is>
-      </c>
-      <c r="H1707" t="inlineStr"/>
+          <t>Cintia Andrade</t>
+        </is>
+      </c>
+      <c r="H1707" t="inlineStr">
+        <is>
+          <t>Katia Valeria</t>
+        </is>
+      </c>
       <c r="I1707" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="J1707" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="K1707" t="n">
-        <v>0</v>
+        <v>227</v>
       </c>
     </row>
     <row r="1708">
@@ -86160,27 +86164,27 @@
       </c>
       <c r="F1708" t="inlineStr">
         <is>
-          <t>SANTOS - EF</t>
+          <t>SANTOS - DP</t>
         </is>
       </c>
       <c r="G1708" t="inlineStr">
         <is>
-          <t>Jasmina Melo</t>
+          <t>Katia Valeria</t>
         </is>
       </c>
       <c r="H1708" t="inlineStr">
         <is>
-          <t>Lidia Tavares</t>
+          <t>Katia Valeria</t>
         </is>
       </c>
       <c r="I1708" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="J1708" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="K1708" t="n">
-        <v>94</v>
+        <v>371</v>
       </c>
     </row>
     <row r="1709">
@@ -86211,27 +86215,23 @@
       </c>
       <c r="F1709" t="inlineStr">
         <is>
-          <t>SANTOS - EF</t>
+          <t>SANTOS - DP</t>
         </is>
       </c>
       <c r="G1709" t="inlineStr">
         <is>
-          <t>Karen Saadi</t>
-        </is>
-      </c>
-      <c r="H1709" t="inlineStr">
-        <is>
-          <t>Lidia Tavares</t>
-        </is>
-      </c>
+          <t>Patricia Melo</t>
+        </is>
+      </c>
+      <c r="H1709" t="inlineStr"/>
       <c r="I1709" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J1709" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K1709" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1710">
@@ -86267,7 +86267,7 @@
       </c>
       <c r="G1710" t="inlineStr">
         <is>
-          <t>Luckas Andrade</t>
+          <t>Jasmina Melo</t>
         </is>
       </c>
       <c r="H1710" t="inlineStr">
@@ -86276,13 +86276,13 @@
         </is>
       </c>
       <c r="I1710" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="J1710" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="K1710" t="n">
-        <v>108</v>
+        <v>98</v>
       </c>
     </row>
     <row r="1711">
@@ -86318,7 +86318,7 @@
       </c>
       <c r="G1711" t="inlineStr">
         <is>
-          <t>Mirian Rodrigues</t>
+          <t>Karen Saadi</t>
         </is>
       </c>
       <c r="H1711" t="inlineStr">
@@ -86327,13 +86327,13 @@
         </is>
       </c>
       <c r="I1711" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J1711" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K1711" t="n">
-        <v>115</v>
+        <v>79</v>
       </c>
     </row>
     <row r="1712">
@@ -86364,22 +86364,124 @@
       </c>
       <c r="F1712" t="inlineStr">
         <is>
+          <t>SANTOS - EF</t>
+        </is>
+      </c>
+      <c r="G1712" t="inlineStr">
+        <is>
+          <t>Luckas Andrade</t>
+        </is>
+      </c>
+      <c r="H1712" t="inlineStr">
+        <is>
+          <t>Lidia Tavares</t>
+        </is>
+      </c>
+      <c r="I1712" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1712" t="n">
+        <v>3</v>
+      </c>
+      <c r="K1712" t="n">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="1713">
+      <c r="A1713" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B1713" t="inlineStr">
+        <is>
+          <t>Segunda</t>
+        </is>
+      </c>
+      <c r="C1713" t="inlineStr">
+        <is>
+          <t>2026-W25</t>
+        </is>
+      </c>
+      <c r="D1713" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1713" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="F1713" t="inlineStr">
+        <is>
+          <t>SANTOS - EF</t>
+        </is>
+      </c>
+      <c r="G1713" t="inlineStr">
+        <is>
+          <t>Mirian Rodrigues</t>
+        </is>
+      </c>
+      <c r="H1713" t="inlineStr">
+        <is>
+          <t>Lidia Tavares</t>
+        </is>
+      </c>
+      <c r="I1713" t="n">
+        <v>5</v>
+      </c>
+      <c r="J1713" t="n">
+        <v>5</v>
+      </c>
+      <c r="K1713" t="n">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="1714">
+      <c r="A1714" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B1714" t="inlineStr">
+        <is>
+          <t>Segunda</t>
+        </is>
+      </c>
+      <c r="C1714" t="inlineStr">
+        <is>
+          <t>2026-W25</t>
+        </is>
+      </c>
+      <c r="D1714" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1714" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="F1714" t="inlineStr">
+        <is>
           <t>SANTOS - GC</t>
         </is>
       </c>
-      <c r="G1712" t="inlineStr">
+      <c r="G1714" t="inlineStr">
         <is>
           <t>Rafaella Massuia</t>
         </is>
       </c>
-      <c r="H1712" t="inlineStr"/>
-      <c r="I1712" t="n">
-        <v>14</v>
-      </c>
-      <c r="J1712" t="n">
-        <v>14</v>
-      </c>
-      <c r="K1712" t="n">
+      <c r="H1714" t="inlineStr"/>
+      <c r="I1714" t="n">
+        <v>13</v>
+      </c>
+      <c r="J1714" t="n">
+        <v>13</v>
+      </c>
+      <c r="K1714" t="n">
         <v>109</v>
       </c>
     </row>

--- a/data/historico/historico_baixas.xlsx
+++ b/data/historico/historico_baixas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1714"/>
+  <dimension ref="A1:K1716"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -71916,27 +71916,27 @@
       </c>
       <c r="F1424" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="G1424" t="inlineStr">
         <is>
-          <t>Elaine Assis</t>
+          <t>Ryan Godinho</t>
         </is>
       </c>
       <c r="H1424" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Karina Santos</t>
         </is>
       </c>
       <c r="I1424" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1424" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1424" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1425">
@@ -71972,12 +71972,12 @@
       </c>
       <c r="G1425" t="inlineStr">
         <is>
-          <t>Evellin Bispo</t>
+          <t>Elaine Assis</t>
         </is>
       </c>
       <c r="H1425" t="inlineStr">
         <is>
-          <t>Leandro Matos</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I1425" t="n">
@@ -71987,7 +71987,7 @@
         <v>0</v>
       </c>
       <c r="K1425" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1426">
@@ -72023,12 +72023,12 @@
       </c>
       <c r="G1426" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Evellin Bispo</t>
         </is>
       </c>
       <c r="H1426" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Leandro Matos</t>
         </is>
       </c>
       <c r="I1426" t="n">
@@ -72038,7 +72038,7 @@
         <v>0</v>
       </c>
       <c r="K1426" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1427">
@@ -72074,12 +72074,12 @@
       </c>
       <c r="G1427" t="inlineStr">
         <is>
-          <t>Jhenifer Tenorio</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="H1427" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I1427" t="n">
@@ -72089,7 +72089,7 @@
         <v>0</v>
       </c>
       <c r="K1427" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1428">
@@ -72125,12 +72125,12 @@
       </c>
       <c r="G1428" t="inlineStr">
         <is>
-          <t>Kaique Souza</t>
+          <t>Jhenifer Tenorio</t>
         </is>
       </c>
       <c r="H1428" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I1428" t="n">
@@ -72140,7 +72140,7 @@
         <v>0</v>
       </c>
       <c r="K1428" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1429">
@@ -72176,12 +72176,12 @@
       </c>
       <c r="G1429" t="inlineStr">
         <is>
-          <t>Mauricio Lermen</t>
+          <t>Kaique Souza</t>
         </is>
       </c>
       <c r="H1429" t="inlineStr">
         <is>
-          <t>Mauricio Lermen</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I1429" t="n">
@@ -72191,7 +72191,7 @@
         <v>0</v>
       </c>
       <c r="K1429" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="1430">
@@ -72227,18 +72227,22 @@
       </c>
       <c r="G1430" t="inlineStr">
         <is>
-          <t>Mikael Teixeira</t>
-        </is>
-      </c>
-      <c r="H1430" t="inlineStr"/>
+          <t>Mauricio Lermen</t>
+        </is>
+      </c>
+      <c r="H1430" t="inlineStr">
+        <is>
+          <t>Mauricio Lermen</t>
+        </is>
+      </c>
       <c r="I1430" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J1430" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1430" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1431">
@@ -72274,22 +72278,18 @@
       </c>
       <c r="G1431" t="inlineStr">
         <is>
-          <t>Tania Luz</t>
-        </is>
-      </c>
-      <c r="H1431" t="inlineStr">
-        <is>
-          <t>Sara Cavalheiro</t>
-        </is>
-      </c>
+          <t>Mikael Teixeira</t>
+        </is>
+      </c>
+      <c r="H1431" t="inlineStr"/>
       <c r="I1431" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J1431" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K1431" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1432">
@@ -72325,22 +72325,22 @@
       </c>
       <c r="G1432" t="inlineStr">
         <is>
-          <t>Vitor Guedes</t>
+          <t>Tania Luz</t>
         </is>
       </c>
       <c r="H1432" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I1432" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J1432" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K1432" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1433">
@@ -72371,27 +72371,27 @@
       </c>
       <c r="F1433" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="G1433" t="inlineStr">
         <is>
-          <t>Cristiana Grizostomo</t>
+          <t>Vitor Guedes</t>
         </is>
       </c>
       <c r="H1433" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I1433" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J1433" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1433" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1434">
@@ -72427,18 +72427,22 @@
       </c>
       <c r="G1434" t="inlineStr">
         <is>
-          <t>Denis Reis</t>
-        </is>
-      </c>
-      <c r="H1434" t="inlineStr"/>
+          <t>Cristiana Grizostomo</t>
+        </is>
+      </c>
+      <c r="H1434" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
       <c r="I1434" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1434" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1434" t="n">
         <v>3</v>
-      </c>
-      <c r="J1434" t="n">
-        <v>3</v>
-      </c>
-      <c r="K1434" t="n">
-        <v>19</v>
       </c>
     </row>
     <row r="1435">
@@ -72474,22 +72478,18 @@
       </c>
       <c r="G1435" t="inlineStr">
         <is>
-          <t>Priscila Volpe</t>
-        </is>
-      </c>
-      <c r="H1435" t="inlineStr">
-        <is>
-          <t>Nayara Oliveira</t>
-        </is>
-      </c>
+          <t>Denis Reis</t>
+        </is>
+      </c>
+      <c r="H1435" t="inlineStr"/>
       <c r="I1435" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1435" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K1435" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1436">
@@ -72525,7 +72525,7 @@
       </c>
       <c r="G1436" t="inlineStr">
         <is>
-          <t>Rosilene Santos</t>
+          <t>Priscila Volpe</t>
         </is>
       </c>
       <c r="H1436" t="inlineStr">
@@ -72540,7 +72540,7 @@
         <v>0</v>
       </c>
       <c r="K1436" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1437">
@@ -72571,27 +72571,27 @@
       </c>
       <c r="F1437" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="G1437" t="inlineStr">
         <is>
-          <t>Cristina Leite</t>
+          <t>Rosilene Santos</t>
         </is>
       </c>
       <c r="H1437" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
       <c r="I1437" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J1437" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K1437" t="n">
-        <v>78</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1438">
@@ -72622,23 +72622,27 @@
       </c>
       <c r="F1438" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="G1438" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
-        </is>
-      </c>
-      <c r="H1438" t="inlineStr"/>
+          <t>Cristina Leite</t>
+        </is>
+      </c>
+      <c r="H1438" t="inlineStr">
+        <is>
+          <t>Ricardo Fischer</t>
+        </is>
+      </c>
       <c r="I1438" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1438" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K1438" t="n">
-        <v>2</v>
+        <v>78</v>
       </c>
     </row>
     <row r="1439">
@@ -72674,7 +72678,7 @@
       </c>
       <c r="G1439" t="inlineStr">
         <is>
-          <t>Victoria Virgens</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="H1439" t="inlineStr"/>
@@ -72685,7 +72689,7 @@
         <v>0</v>
       </c>
       <c r="K1439" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1440">
@@ -72716,12 +72720,12 @@
       </c>
       <c r="F1440" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="G1440" t="inlineStr">
         <is>
-          <t>Cristiane Simões</t>
+          <t>Victoria Virgens</t>
         </is>
       </c>
       <c r="H1440" t="inlineStr"/>
@@ -72732,7 +72736,7 @@
         <v>0</v>
       </c>
       <c r="K1440" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1441">
@@ -72768,18 +72772,18 @@
       </c>
       <c r="G1441" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Cristiane Simões</t>
         </is>
       </c>
       <c r="H1441" t="inlineStr"/>
       <c r="I1441" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J1441" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1441" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1442">
@@ -72815,18 +72819,18 @@
       </c>
       <c r="G1442" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="H1442" t="inlineStr"/>
       <c r="I1442" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1442" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1442" t="n">
-        <v>4</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1443">
@@ -72862,7 +72866,7 @@
       </c>
       <c r="G1443" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="H1443" t="inlineStr"/>
@@ -72873,7 +72877,7 @@
         <v>0</v>
       </c>
       <c r="K1443" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1444">
@@ -72899,28 +72903,28 @@
       </c>
       <c r="E1444" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>GOIAS</t>
         </is>
       </c>
       <c r="F1444" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="G1444" t="inlineStr">
         <is>
-          <t>Caroline Alves</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="H1444" t="inlineStr"/>
       <c r="I1444" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J1444" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K1444" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1445">
@@ -72951,27 +72955,23 @@
       </c>
       <c r="F1445" t="inlineStr">
         <is>
-          <t>RJ - CTB</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="G1445" t="inlineStr">
         <is>
-          <t>Crislaine Maia</t>
-        </is>
-      </c>
-      <c r="H1445" t="inlineStr">
-        <is>
-          <t>Walace Gonçalves|Maicon Costa</t>
-        </is>
-      </c>
+          <t>Caroline Alves</t>
+        </is>
+      </c>
+      <c r="H1445" t="inlineStr"/>
       <c r="I1445" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J1445" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K1445" t="n">
-        <v>46</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1446">
@@ -73007,7 +73007,7 @@
       </c>
       <c r="G1446" t="inlineStr">
         <is>
-          <t>Gabriela Lopes</t>
+          <t>Crislaine Maia</t>
         </is>
       </c>
       <c r="H1446" t="inlineStr">
@@ -73016,13 +73016,13 @@
         </is>
       </c>
       <c r="I1446" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J1446" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="K1446" t="n">
-        <v>72</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1447">
@@ -73058,7 +73058,7 @@
       </c>
       <c r="G1447" t="inlineStr">
         <is>
-          <t>Jeniffer Cristina</t>
+          <t>Gabriela Lopes</t>
         </is>
       </c>
       <c r="H1447" t="inlineStr">
@@ -73067,13 +73067,13 @@
         </is>
       </c>
       <c r="I1447" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1447" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1447" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="1448">
@@ -73109,7 +73109,7 @@
       </c>
       <c r="G1448" t="inlineStr">
         <is>
-          <t>Jessica Roque</t>
+          <t>Jeniffer Cristina</t>
         </is>
       </c>
       <c r="H1448" t="inlineStr">
@@ -73118,13 +73118,13 @@
         </is>
       </c>
       <c r="I1448" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J1448" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K1448" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
     </row>
     <row r="1449">
@@ -73160,7 +73160,7 @@
       </c>
       <c r="G1449" t="inlineStr">
         <is>
-          <t>Kellem Freitas</t>
+          <t>Jessica Roque</t>
         </is>
       </c>
       <c r="H1449" t="inlineStr">
@@ -73169,13 +73169,13 @@
         </is>
       </c>
       <c r="I1449" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J1449" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="K1449" t="n">
-        <v>42</v>
+        <v>89</v>
       </c>
     </row>
     <row r="1450">
@@ -73211,7 +73211,7 @@
       </c>
       <c r="G1450" t="inlineStr">
         <is>
-          <t>Leidiane Paulino</t>
+          <t>Kellem Freitas</t>
         </is>
       </c>
       <c r="H1450" t="inlineStr">
@@ -73220,13 +73220,13 @@
         </is>
       </c>
       <c r="I1450" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="J1450" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="K1450" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1451">
@@ -73262,7 +73262,7 @@
       </c>
       <c r="G1451" t="inlineStr">
         <is>
-          <t>Leticia Barbosa</t>
+          <t>Leidiane Paulino</t>
         </is>
       </c>
       <c r="H1451" t="inlineStr">
@@ -73271,13 +73271,13 @@
         </is>
       </c>
       <c r="I1451" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1451" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1451" t="n">
-        <v>83</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1452">
@@ -73313,7 +73313,7 @@
       </c>
       <c r="G1452" t="inlineStr">
         <is>
-          <t>Luis Junior</t>
+          <t>Leticia Barbosa</t>
         </is>
       </c>
       <c r="H1452" t="inlineStr">
@@ -73328,7 +73328,7 @@
         <v>0</v>
       </c>
       <c r="K1452" t="n">
-        <v>14</v>
+        <v>83</v>
       </c>
     </row>
     <row r="1453">
@@ -73364,7 +73364,7 @@
       </c>
       <c r="G1453" t="inlineStr">
         <is>
-          <t>Nicoly Rodrigues</t>
+          <t>Luis Junior</t>
         </is>
       </c>
       <c r="H1453" t="inlineStr">
@@ -73379,7 +73379,7 @@
         <v>0</v>
       </c>
       <c r="K1453" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1454">
@@ -73415,7 +73415,7 @@
       </c>
       <c r="G1454" t="inlineStr">
         <is>
-          <t>Rafaella Silva</t>
+          <t>Nicoly Rodrigues</t>
         </is>
       </c>
       <c r="H1454" t="inlineStr">
@@ -73430,7 +73430,7 @@
         <v>0</v>
       </c>
       <c r="K1454" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1455">
@@ -73466,7 +73466,7 @@
       </c>
       <c r="G1455" t="inlineStr">
         <is>
-          <t>Rangel Rocha</t>
+          <t>Rafaella Silva</t>
         </is>
       </c>
       <c r="H1455" t="inlineStr">
@@ -73475,13 +73475,13 @@
         </is>
       </c>
       <c r="I1455" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J1455" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K1455" t="n">
-        <v>37</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1456">
@@ -73517,7 +73517,7 @@
       </c>
       <c r="G1456" t="inlineStr">
         <is>
-          <t>Simone Soares</t>
+          <t>Rangel Rocha</t>
         </is>
       </c>
       <c r="H1456" t="inlineStr">
@@ -73532,7 +73532,7 @@
         <v>7</v>
       </c>
       <c r="K1456" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
     </row>
     <row r="1457">
@@ -73568,7 +73568,7 @@
       </c>
       <c r="G1457" t="inlineStr">
         <is>
-          <t>Suzana Silva</t>
+          <t>Simone Soares</t>
         </is>
       </c>
       <c r="H1457" t="inlineStr">
@@ -73577,13 +73577,13 @@
         </is>
       </c>
       <c r="I1457" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J1457" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K1457" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1458">
@@ -73619,7 +73619,7 @@
       </c>
       <c r="G1458" t="inlineStr">
         <is>
-          <t>Veronica Barbosa</t>
+          <t>Suzana Silva</t>
         </is>
       </c>
       <c r="H1458" t="inlineStr">
@@ -73628,13 +73628,13 @@
         </is>
       </c>
       <c r="I1458" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J1458" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K1458" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="1459">
@@ -73670,7 +73670,7 @@
       </c>
       <c r="G1459" t="inlineStr">
         <is>
-          <t>Vitor Monteiro</t>
+          <t>Veronica Barbosa</t>
         </is>
       </c>
       <c r="H1459" t="inlineStr">
@@ -73679,13 +73679,13 @@
         </is>
       </c>
       <c r="I1459" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J1459" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K1459" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
     </row>
     <row r="1460">
@@ -73721,7 +73721,7 @@
       </c>
       <c r="G1460" t="inlineStr">
         <is>
-          <t>Vitoria Silva</t>
+          <t>Vitor Monteiro</t>
         </is>
       </c>
       <c r="H1460" t="inlineStr">
@@ -73730,13 +73730,13 @@
         </is>
       </c>
       <c r="I1460" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J1460" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K1460" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
     </row>
     <row r="1461">
@@ -73767,11 +73767,19 @@
       </c>
       <c r="F1461" t="inlineStr">
         <is>
-          <t>RJ - DP</t>
-        </is>
-      </c>
-      <c r="G1461" t="inlineStr"/>
-      <c r="H1461" t="inlineStr"/>
+          <t>RJ - CTB</t>
+        </is>
+      </c>
+      <c r="G1461" t="inlineStr">
+        <is>
+          <t>Vitoria Silva</t>
+        </is>
+      </c>
+      <c r="H1461" t="inlineStr">
+        <is>
+          <t>Walace Gonçalves|Maicon Costa</t>
+        </is>
+      </c>
       <c r="I1461" t="n">
         <v>0</v>
       </c>
@@ -73779,7 +73787,7 @@
         <v>0</v>
       </c>
       <c r="K1461" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="1462">
@@ -73813,24 +73821,16 @@
           <t>RJ - DP</t>
         </is>
       </c>
-      <c r="G1462" t="inlineStr">
-        <is>
-          <t>Barbara Mello</t>
-        </is>
-      </c>
-      <c r="H1462" t="inlineStr">
-        <is>
-          <t>Karina Oliveira|Liliane Costa</t>
-        </is>
-      </c>
+      <c r="G1462" t="inlineStr"/>
+      <c r="H1462" t="inlineStr"/>
       <c r="I1462" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J1462" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K1462" t="n">
-        <v>113</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1463">
@@ -73866,7 +73866,7 @@
       </c>
       <c r="G1463" t="inlineStr">
         <is>
-          <t>Debora Nunes</t>
+          <t>Barbara Mello</t>
         </is>
       </c>
       <c r="H1463" t="inlineStr">
@@ -73875,13 +73875,13 @@
         </is>
       </c>
       <c r="I1463" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J1463" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="K1463" t="n">
-        <v>100</v>
+        <v>113</v>
       </c>
     </row>
     <row r="1464">
@@ -73917,7 +73917,7 @@
       </c>
       <c r="G1464" t="inlineStr">
         <is>
-          <t>Graziele Almeida</t>
+          <t>Debora Nunes</t>
         </is>
       </c>
       <c r="H1464" t="inlineStr">
@@ -73932,7 +73932,7 @@
         <v>0</v>
       </c>
       <c r="K1464" t="n">
-        <v>88</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1465">
@@ -73968,7 +73968,7 @@
       </c>
       <c r="G1465" t="inlineStr">
         <is>
-          <t>Janiele Ferreira</t>
+          <t>Graziele Almeida</t>
         </is>
       </c>
       <c r="H1465" t="inlineStr">
@@ -73983,7 +73983,7 @@
         <v>0</v>
       </c>
       <c r="K1465" t="n">
-        <v>22</v>
+        <v>88</v>
       </c>
     </row>
     <row r="1466">
@@ -74019,7 +74019,7 @@
       </c>
       <c r="G1466" t="inlineStr">
         <is>
-          <t>Jefferson Barros</t>
+          <t>Janiele Ferreira</t>
         </is>
       </c>
       <c r="H1466" t="inlineStr">
@@ -74028,13 +74028,13 @@
         </is>
       </c>
       <c r="I1466" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J1466" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K1466" t="n">
-        <v>103</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1467">
@@ -74070,7 +74070,7 @@
       </c>
       <c r="G1467" t="inlineStr">
         <is>
-          <t>Karina Oliveira</t>
+          <t>Jefferson Barros</t>
         </is>
       </c>
       <c r="H1467" t="inlineStr">
@@ -74079,13 +74079,13 @@
         </is>
       </c>
       <c r="I1467" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J1467" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1467" t="n">
-        <v>31</v>
+        <v>103</v>
       </c>
     </row>
     <row r="1468">
@@ -74121,7 +74121,7 @@
       </c>
       <c r="G1468" t="inlineStr">
         <is>
-          <t>Leonardo Assunção</t>
+          <t>Karina Oliveira</t>
         </is>
       </c>
       <c r="H1468" t="inlineStr">
@@ -74130,13 +74130,13 @@
         </is>
       </c>
       <c r="I1468" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J1468" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K1468" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="1469">
@@ -74172,7 +74172,7 @@
       </c>
       <c r="G1469" t="inlineStr">
         <is>
-          <t>Liliane Costa</t>
+          <t>Leonardo Assunção</t>
         </is>
       </c>
       <c r="H1469" t="inlineStr">
@@ -74181,13 +74181,13 @@
         </is>
       </c>
       <c r="I1469" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1469" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K1469" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
     </row>
     <row r="1470">
@@ -74223,7 +74223,7 @@
       </c>
       <c r="G1470" t="inlineStr">
         <is>
-          <t>Luciene Pimenta</t>
+          <t>Liliane Costa</t>
         </is>
       </c>
       <c r="H1470" t="inlineStr">
@@ -74238,7 +74238,7 @@
         <v>0</v>
       </c>
       <c r="K1470" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1471">
@@ -74274,7 +74274,7 @@
       </c>
       <c r="G1471" t="inlineStr">
         <is>
-          <t>Lucirene Souza</t>
+          <t>Luciene Pimenta</t>
         </is>
       </c>
       <c r="H1471" t="inlineStr">
@@ -74283,13 +74283,13 @@
         </is>
       </c>
       <c r="I1471" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J1471" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K1471" t="n">
-        <v>86</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1472">
@@ -74325,7 +74325,7 @@
       </c>
       <c r="G1472" t="inlineStr">
         <is>
-          <t>Marlon Silva</t>
+          <t>Lucirene Souza</t>
         </is>
       </c>
       <c r="H1472" t="inlineStr">
@@ -74334,13 +74334,13 @@
         </is>
       </c>
       <c r="I1472" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J1472" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K1472" t="n">
-        <v>109</v>
+        <v>86</v>
       </c>
     </row>
     <row r="1473">
@@ -74376,7 +74376,7 @@
       </c>
       <c r="G1473" t="inlineStr">
         <is>
-          <t>Monique Britto</t>
+          <t>Marlon Silva</t>
         </is>
       </c>
       <c r="H1473" t="inlineStr">
@@ -74391,7 +74391,7 @@
         <v>0</v>
       </c>
       <c r="K1473" t="n">
-        <v>94</v>
+        <v>109</v>
       </c>
     </row>
     <row r="1474">
@@ -74427,7 +74427,7 @@
       </c>
       <c r="G1474" t="inlineStr">
         <is>
-          <t>Romulo Ferreira</t>
+          <t>Monique Britto</t>
         </is>
       </c>
       <c r="H1474" t="inlineStr">
@@ -74436,13 +74436,13 @@
         </is>
       </c>
       <c r="I1474" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J1474" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K1474" t="n">
-        <v>316</v>
+        <v>94</v>
       </c>
     </row>
     <row r="1475">
@@ -74478,7 +74478,7 @@
       </c>
       <c r="G1475" t="inlineStr">
         <is>
-          <t>Rosilene Silva</t>
+          <t>Romulo Ferreira</t>
         </is>
       </c>
       <c r="H1475" t="inlineStr">
@@ -74487,13 +74487,13 @@
         </is>
       </c>
       <c r="I1475" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J1475" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1475" t="n">
-        <v>30</v>
+        <v>316</v>
       </c>
     </row>
     <row r="1476">
@@ -74529,7 +74529,7 @@
       </c>
       <c r="G1476" t="inlineStr">
         <is>
-          <t>Thais Santos</t>
+          <t>Rosilene Silva</t>
         </is>
       </c>
       <c r="H1476" t="inlineStr">
@@ -74538,13 +74538,13 @@
         </is>
       </c>
       <c r="I1476" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J1476" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K1476" t="n">
-        <v>115</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1477">
@@ -74580,7 +74580,7 @@
       </c>
       <c r="G1477" t="inlineStr">
         <is>
-          <t>Vitoria Tavares</t>
+          <t>Thais Santos</t>
         </is>
       </c>
       <c r="H1477" t="inlineStr">
@@ -74589,13 +74589,13 @@
         </is>
       </c>
       <c r="I1477" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J1477" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K1477" t="n">
-        <v>181</v>
+        <v>115</v>
       </c>
     </row>
     <row r="1478">
@@ -74631,7 +74631,7 @@
       </c>
       <c r="G1478" t="inlineStr">
         <is>
-          <t>Viviane Moura</t>
+          <t>Vitoria Tavares</t>
         </is>
       </c>
       <c r="H1478" t="inlineStr">
@@ -74640,13 +74640,13 @@
         </is>
       </c>
       <c r="I1478" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1478" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1478" t="n">
-        <v>74</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1479">
@@ -74682,7 +74682,7 @@
       </c>
       <c r="G1479" t="inlineStr">
         <is>
-          <t>Yasmin Lopes</t>
+          <t>Viviane Moura</t>
         </is>
       </c>
       <c r="H1479" t="inlineStr">
@@ -74691,13 +74691,13 @@
         </is>
       </c>
       <c r="I1479" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J1479" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K1479" t="n">
-        <v>123</v>
+        <v>74</v>
       </c>
     </row>
     <row r="1480">
@@ -74728,27 +74728,27 @@
       </c>
       <c r="F1480" t="inlineStr">
         <is>
-          <t>RJ - EF</t>
+          <t>RJ - DP</t>
         </is>
       </c>
       <c r="G1480" t="inlineStr">
         <is>
-          <t>Altamir Nogueira</t>
+          <t>Yasmin Lopes</t>
         </is>
       </c>
       <c r="H1480" t="inlineStr">
         <is>
-          <t>Julio Santos|Jessica Benjamin</t>
+          <t>Karina Oliveira|Liliane Costa</t>
         </is>
       </c>
       <c r="I1480" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="J1480" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="K1480" t="n">
-        <v>218</v>
+        <v>123</v>
       </c>
     </row>
     <row r="1481">
@@ -74784,7 +74784,7 @@
       </c>
       <c r="G1481" t="inlineStr">
         <is>
-          <t>Beatriz Oliveira</t>
+          <t>Altamir Nogueira</t>
         </is>
       </c>
       <c r="H1481" t="inlineStr">
@@ -74793,13 +74793,13 @@
         </is>
       </c>
       <c r="I1481" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="J1481" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="K1481" t="n">
-        <v>127</v>
+        <v>218</v>
       </c>
     </row>
     <row r="1482">
@@ -74835,7 +74835,7 @@
       </c>
       <c r="G1482" t="inlineStr">
         <is>
-          <t>Glaucia Santos</t>
+          <t>Beatriz Oliveira</t>
         </is>
       </c>
       <c r="H1482" t="inlineStr">
@@ -74844,13 +74844,13 @@
         </is>
       </c>
       <c r="I1482" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="J1482" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="K1482" t="n">
-        <v>178</v>
+        <v>127</v>
       </c>
     </row>
     <row r="1483">
@@ -74886,7 +74886,7 @@
       </c>
       <c r="G1483" t="inlineStr">
         <is>
-          <t>Isabela Barbosa</t>
+          <t>Glaucia Santos</t>
         </is>
       </c>
       <c r="H1483" t="inlineStr">
@@ -74895,13 +74895,13 @@
         </is>
       </c>
       <c r="I1483" t="n">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="J1483" t="n">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="K1483" t="n">
-        <v>159</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1484">
@@ -74937,7 +74937,7 @@
       </c>
       <c r="G1484" t="inlineStr">
         <is>
-          <t>Jessica Benjamin</t>
+          <t>Isabela Barbosa</t>
         </is>
       </c>
       <c r="H1484" t="inlineStr">
@@ -74946,13 +74946,13 @@
         </is>
       </c>
       <c r="I1484" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="J1484" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="K1484" t="n">
-        <v>129</v>
+        <v>166</v>
       </c>
     </row>
     <row r="1485">
@@ -74988,7 +74988,7 @@
       </c>
       <c r="G1485" t="inlineStr">
         <is>
-          <t>Juliana Perfeito</t>
+          <t>Jessica Benjamin</t>
         </is>
       </c>
       <c r="H1485" t="inlineStr">
@@ -74997,13 +74997,13 @@
         </is>
       </c>
       <c r="I1485" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="J1485" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="K1485" t="n">
-        <v>105</v>
+        <v>129</v>
       </c>
     </row>
     <row r="1486">
@@ -75039,7 +75039,7 @@
       </c>
       <c r="G1486" t="inlineStr">
         <is>
-          <t>Julio Santos</t>
+          <t>Juliana Perfeito</t>
         </is>
       </c>
       <c r="H1486" t="inlineStr">
@@ -75048,13 +75048,13 @@
         </is>
       </c>
       <c r="I1486" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J1486" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="K1486" t="n">
-        <v>1</v>
+        <v>105</v>
       </c>
     </row>
     <row r="1487">
@@ -75090,7 +75090,7 @@
       </c>
       <c r="G1487" t="inlineStr">
         <is>
-          <t>Lais Catrine EF</t>
+          <t>Julio Santos</t>
         </is>
       </c>
       <c r="H1487" t="inlineStr">
@@ -75099,13 +75099,13 @@
         </is>
       </c>
       <c r="I1487" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J1487" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K1487" t="n">
-        <v>235</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1488">
@@ -75141,7 +75141,7 @@
       </c>
       <c r="G1488" t="inlineStr">
         <is>
-          <t>Luana Meneses</t>
+          <t>Lais Catrine EF</t>
         </is>
       </c>
       <c r="H1488" t="inlineStr">
@@ -75150,13 +75150,13 @@
         </is>
       </c>
       <c r="I1488" t="n">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="J1488" t="n">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="K1488" t="n">
-        <v>247</v>
+        <v>235</v>
       </c>
     </row>
     <row r="1489">
@@ -75192,7 +75192,7 @@
       </c>
       <c r="G1489" t="inlineStr">
         <is>
-          <t>Otacilia Ferreira</t>
+          <t>Luana Meneses</t>
         </is>
       </c>
       <c r="H1489" t="inlineStr">
@@ -75201,13 +75201,13 @@
         </is>
       </c>
       <c r="I1489" t="n">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="J1489" t="n">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="K1489" t="n">
-        <v>113</v>
+        <v>250</v>
       </c>
     </row>
     <row r="1490">
@@ -75243,7 +75243,7 @@
       </c>
       <c r="G1490" t="inlineStr">
         <is>
-          <t>Renata Paixão</t>
+          <t>Otacilia Ferreira</t>
         </is>
       </c>
       <c r="H1490" t="inlineStr">
@@ -75252,13 +75252,13 @@
         </is>
       </c>
       <c r="I1490" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J1490" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K1490" t="n">
-        <v>164</v>
+        <v>113</v>
       </c>
     </row>
     <row r="1491">
@@ -75294,7 +75294,7 @@
       </c>
       <c r="G1491" t="inlineStr">
         <is>
-          <t>Thamara Jordes</t>
+          <t>Renata Paixão</t>
         </is>
       </c>
       <c r="H1491" t="inlineStr">
@@ -75303,13 +75303,13 @@
         </is>
       </c>
       <c r="I1491" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J1491" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K1491" t="n">
-        <v>147</v>
+        <v>164</v>
       </c>
     </row>
     <row r="1492">
@@ -75345,7 +75345,7 @@
       </c>
       <c r="G1492" t="inlineStr">
         <is>
-          <t>Wellington Oliveira</t>
+          <t>Thamara Jordes</t>
         </is>
       </c>
       <c r="H1492" t="inlineStr">
@@ -75354,13 +75354,13 @@
         </is>
       </c>
       <c r="I1492" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J1492" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K1492" t="n">
-        <v>204</v>
+        <v>147</v>
       </c>
     </row>
     <row r="1493">
@@ -75391,23 +75391,27 @@
       </c>
       <c r="F1493" t="inlineStr">
         <is>
-          <t>RJ - GC</t>
+          <t>RJ - EF</t>
         </is>
       </c>
       <c r="G1493" t="inlineStr">
         <is>
-          <t>Bruno Mota</t>
-        </is>
-      </c>
-      <c r="H1493" t="inlineStr"/>
+          <t>Wellington Oliveira</t>
+        </is>
+      </c>
+      <c r="H1493" t="inlineStr">
+        <is>
+          <t>Julio Santos|Jessica Benjamin</t>
+        </is>
+      </c>
       <c r="I1493" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J1493" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1493" t="n">
-        <v>155</v>
+        <v>204</v>
       </c>
     </row>
     <row r="1494">
@@ -75443,18 +75447,18 @@
       </c>
       <c r="G1494" t="inlineStr">
         <is>
-          <t>Cavalcante Peres</t>
+          <t>Bruno Mota</t>
         </is>
       </c>
       <c r="H1494" t="inlineStr"/>
       <c r="I1494" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J1494" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K1494" t="n">
-        <v>87</v>
+        <v>155</v>
       </c>
     </row>
     <row r="1495">
@@ -75485,23 +75489,23 @@
       </c>
       <c r="F1495" t="inlineStr">
         <is>
-          <t>RJ - GC ADMINISTRATIVO</t>
+          <t>RJ - GC</t>
         </is>
       </c>
       <c r="G1495" t="inlineStr">
         <is>
-          <t>Amanda Mesquita</t>
+          <t>Cavalcante Peres</t>
         </is>
       </c>
       <c r="H1495" t="inlineStr"/>
       <c r="I1495" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J1495" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K1495" t="n">
-        <v>230</v>
+        <v>87</v>
       </c>
     </row>
     <row r="1496">
@@ -75537,18 +75541,18 @@
       </c>
       <c r="G1496" t="inlineStr">
         <is>
-          <t>Lohany Martins</t>
+          <t>Amanda Mesquita</t>
         </is>
       </c>
       <c r="H1496" t="inlineStr"/>
       <c r="I1496" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="J1496" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="K1496" t="n">
-        <v>401</v>
+        <v>230</v>
       </c>
     </row>
     <row r="1497">
@@ -75579,23 +75583,23 @@
       </c>
       <c r="F1497" t="inlineStr">
         <is>
-          <t>S.A.C</t>
+          <t>RJ - GC ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="G1497" t="inlineStr">
         <is>
-          <t>Milena Campos - SAC</t>
+          <t>Lohany Martins</t>
         </is>
       </c>
       <c r="H1497" t="inlineStr"/>
       <c r="I1497" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="J1497" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="K1497" t="n">
-        <v>1</v>
+        <v>403</v>
       </c>
     </row>
     <row r="1498">
@@ -75621,24 +75625,20 @@
       </c>
       <c r="E1498" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F1498" t="inlineStr">
         <is>
-          <t>CONTABILIDADE (Outsourcing)</t>
+          <t>S.A.C</t>
         </is>
       </c>
       <c r="G1498" t="inlineStr">
         <is>
-          <t>Aline Petrini</t>
-        </is>
-      </c>
-      <c r="H1498" t="inlineStr">
-        <is>
-          <t>Fernanda Araujo</t>
-        </is>
-      </c>
+          <t>Milena Campos - SAC</t>
+        </is>
+      </c>
+      <c r="H1498" t="inlineStr"/>
       <c r="I1498" t="n">
         <v>0</v>
       </c>
@@ -75646,7 +75646,7 @@
         <v>0</v>
       </c>
       <c r="K1498" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1499">
@@ -75682,12 +75682,12 @@
       </c>
       <c r="G1499" t="inlineStr">
         <is>
-          <t>Daniele Leite</t>
+          <t>Aline Petrini</t>
         </is>
       </c>
       <c r="H1499" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="I1499" t="n">
@@ -75697,7 +75697,7 @@
         <v>0</v>
       </c>
       <c r="K1499" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1500">
@@ -75733,12 +75733,12 @@
       </c>
       <c r="G1500" t="inlineStr">
         <is>
-          <t>Diogo Calazans</t>
+          <t>Daniele Leite</t>
         </is>
       </c>
       <c r="H1500" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I1500" t="n">
@@ -75748,7 +75748,7 @@
         <v>0</v>
       </c>
       <c r="K1500" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1501">
@@ -75784,12 +75784,12 @@
       </c>
       <c r="G1501" t="inlineStr">
         <is>
-          <t>Jaqueline Sousa</t>
+          <t>Diogo Calazans</t>
         </is>
       </c>
       <c r="H1501" t="inlineStr">
         <is>
-          <t>Lucas Fischer</t>
+          <t>Karina Santos</t>
         </is>
       </c>
       <c r="I1501" t="n">
@@ -75799,7 +75799,7 @@
         <v>0</v>
       </c>
       <c r="K1501" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1502">
@@ -75835,7 +75835,7 @@
       </c>
       <c r="G1502" t="inlineStr">
         <is>
-          <t>Leticia Medeiros</t>
+          <t>Jaqueline Sousa</t>
         </is>
       </c>
       <c r="H1502" t="inlineStr">
@@ -75844,13 +75844,13 @@
         </is>
       </c>
       <c r="I1502" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J1502" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1502" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1503">
@@ -75886,22 +75886,22 @@
       </c>
       <c r="G1503" t="inlineStr">
         <is>
-          <t>Patricia Borges</t>
+          <t>Leticia Medeiros</t>
         </is>
       </c>
       <c r="H1503" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Lucas Fischer</t>
         </is>
       </c>
       <c r="I1503" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J1503" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K1503" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1504">
@@ -75937,22 +75937,22 @@
       </c>
       <c r="G1504" t="inlineStr">
         <is>
-          <t>Rejane Coelho</t>
+          <t>Patricia Borges</t>
         </is>
       </c>
       <c r="H1504" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I1504" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J1504" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K1504" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1505">
@@ -75988,22 +75988,22 @@
       </c>
       <c r="G1505" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Rejane Coelho</t>
         </is>
       </c>
       <c r="H1505" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Karina Santos</t>
         </is>
       </c>
       <c r="I1505" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J1505" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K1505" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1506">
@@ -76039,12 +76039,12 @@
       </c>
       <c r="G1506" t="inlineStr">
         <is>
-          <t>Thiago Ceconelli</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="H1506" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="I1506" t="n">
@@ -76054,7 +76054,7 @@
         <v>0</v>
       </c>
       <c r="K1506" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1507">
@@ -76085,27 +76085,27 @@
       </c>
       <c r="F1507" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL HOLDING</t>
+          <t>CONTABILIDADE (Outsourcing)</t>
         </is>
       </c>
       <c r="G1507" t="inlineStr">
         <is>
-          <t>Ana Flavia Silva</t>
+          <t>Thiago Ceconelli</t>
         </is>
       </c>
       <c r="H1507" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Karina Santos</t>
         </is>
       </c>
       <c r="I1507" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="J1507" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="K1507" t="n">
-        <v>192</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1508">
@@ -76141,18 +76141,22 @@
       </c>
       <c r="G1508" t="inlineStr">
         <is>
-          <t>Daniele Faria</t>
-        </is>
-      </c>
-      <c r="H1508" t="inlineStr"/>
+          <t>Ana Flavia Silva</t>
+        </is>
+      </c>
+      <c r="H1508" t="inlineStr">
+        <is>
+          <t>Tatiana Linardi</t>
+        </is>
+      </c>
       <c r="I1508" t="n">
-        <v>3</v>
+        <v>73</v>
       </c>
       <c r="J1508" t="n">
-        <v>3</v>
+        <v>73</v>
       </c>
       <c r="K1508" t="n">
-        <v>5</v>
+        <v>192</v>
       </c>
     </row>
     <row r="1509">
@@ -76188,22 +76192,18 @@
       </c>
       <c r="G1509" t="inlineStr">
         <is>
-          <t>Vitor de Souza</t>
-        </is>
-      </c>
-      <c r="H1509" t="inlineStr">
-        <is>
-          <t>Tatiana Linardi</t>
-        </is>
-      </c>
+          <t>Daniele Faria</t>
+        </is>
+      </c>
+      <c r="H1509" t="inlineStr"/>
       <c r="I1509" t="n">
-        <v>141</v>
+        <v>3</v>
       </c>
       <c r="J1509" t="n">
-        <v>141</v>
+        <v>3</v>
       </c>
       <c r="K1509" t="n">
-        <v>282</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1510">
@@ -76239,7 +76239,7 @@
       </c>
       <c r="G1510" t="inlineStr">
         <is>
-          <t>Vitoria Regina</t>
+          <t>Vitor de Souza</t>
         </is>
       </c>
       <c r="H1510" t="inlineStr">
@@ -76248,13 +76248,13 @@
         </is>
       </c>
       <c r="I1510" t="n">
-        <v>76</v>
+        <v>141</v>
       </c>
       <c r="J1510" t="n">
-        <v>76</v>
+        <v>141</v>
       </c>
       <c r="K1510" t="n">
-        <v>220</v>
+        <v>282</v>
       </c>
     </row>
     <row r="1511">
@@ -76285,27 +76285,27 @@
       </c>
       <c r="F1511" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL INDUSTRIA</t>
+          <t>CTB - CONTÁBIL HOLDING</t>
         </is>
       </c>
       <c r="G1511" t="inlineStr">
         <is>
-          <t>Adriano Barros</t>
+          <t>Vitoria Regina</t>
         </is>
       </c>
       <c r="H1511" t="inlineStr">
         <is>
-          <t>Erika Santana|Isabella Nascimento</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="I1511" t="n">
-        <v>31</v>
+        <v>78</v>
       </c>
       <c r="J1511" t="n">
-        <v>31</v>
+        <v>78</v>
       </c>
       <c r="K1511" t="n">
-        <v>43</v>
+        <v>222</v>
       </c>
     </row>
     <row r="1512">
@@ -76341,7 +76341,7 @@
       </c>
       <c r="G1512" t="inlineStr">
         <is>
-          <t>Bianca Silva</t>
+          <t>Adriano Barros</t>
         </is>
       </c>
       <c r="H1512" t="inlineStr">
@@ -76350,13 +76350,13 @@
         </is>
       </c>
       <c r="I1512" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="J1512" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="K1512" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="1513">
@@ -76392,7 +76392,7 @@
       </c>
       <c r="G1513" t="inlineStr">
         <is>
-          <t>Emylle Souza</t>
+          <t>Bianca Silva</t>
         </is>
       </c>
       <c r="H1513" t="inlineStr">
@@ -76401,13 +76401,13 @@
         </is>
       </c>
       <c r="I1513" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J1513" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="K1513" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1514">
@@ -76443,7 +76443,7 @@
       </c>
       <c r="G1514" t="inlineStr">
         <is>
-          <t>Fatima Rocha</t>
+          <t>Emylle Souza</t>
         </is>
       </c>
       <c r="H1514" t="inlineStr">
@@ -76458,7 +76458,7 @@
         <v>0</v>
       </c>
       <c r="K1514" t="n">
-        <v>58</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1515">
@@ -76494,7 +76494,7 @@
       </c>
       <c r="G1515" t="inlineStr">
         <is>
-          <t>Gabriel Correia</t>
+          <t>Fatima Rocha</t>
         </is>
       </c>
       <c r="H1515" t="inlineStr">
@@ -76503,13 +76503,13 @@
         </is>
       </c>
       <c r="I1515" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J1515" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K1515" t="n">
-        <v>19</v>
+        <v>58</v>
       </c>
     </row>
     <row r="1516">
@@ -76545,7 +76545,7 @@
       </c>
       <c r="G1516" t="inlineStr">
         <is>
-          <t>Isabella Nascimento</t>
+          <t>Gabriel Correia</t>
         </is>
       </c>
       <c r="H1516" t="inlineStr">
@@ -76554,13 +76554,13 @@
         </is>
       </c>
       <c r="I1516" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1516" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K1516" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1517">
@@ -76596,7 +76596,7 @@
       </c>
       <c r="G1517" t="inlineStr">
         <is>
-          <t>Laisa Rocha</t>
+          <t>Isabella Nascimento</t>
         </is>
       </c>
       <c r="H1517" t="inlineStr">
@@ -76605,13 +76605,13 @@
         </is>
       </c>
       <c r="I1517" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J1517" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K1517" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1518">
@@ -76647,7 +76647,7 @@
       </c>
       <c r="G1518" t="inlineStr">
         <is>
-          <t>Lucas Alves</t>
+          <t>Laisa Rocha</t>
         </is>
       </c>
       <c r="H1518" t="inlineStr">
@@ -76656,13 +76656,13 @@
         </is>
       </c>
       <c r="I1518" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="J1518" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="K1518" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
     </row>
     <row r="1519">
@@ -76698,7 +76698,7 @@
       </c>
       <c r="G1519" t="inlineStr">
         <is>
-          <t>Luciana Silva</t>
+          <t>Lucas Alves</t>
         </is>
       </c>
       <c r="H1519" t="inlineStr">
@@ -76707,13 +76707,13 @@
         </is>
       </c>
       <c r="I1519" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="J1519" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="K1519" t="n">
-        <v>75</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1520">
@@ -76749,18 +76749,22 @@
       </c>
       <c r="G1520" t="inlineStr">
         <is>
-          <t>Luiz Ferreira</t>
-        </is>
-      </c>
-      <c r="H1520" t="inlineStr"/>
+          <t>Luciana Silva</t>
+        </is>
+      </c>
+      <c r="H1520" t="inlineStr">
+        <is>
+          <t>Erika Santana|Isabella Nascimento</t>
+        </is>
+      </c>
       <c r="I1520" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="J1520" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="K1520" t="n">
-        <v>5</v>
+        <v>76</v>
       </c>
     </row>
     <row r="1521">
@@ -76796,22 +76800,18 @@
       </c>
       <c r="G1521" t="inlineStr">
         <is>
-          <t>Marcus Oliveira</t>
-        </is>
-      </c>
-      <c r="H1521" t="inlineStr">
-        <is>
-          <t>Erika Santana|Isabella Nascimento</t>
-        </is>
-      </c>
+          <t>Luiz Ferreira</t>
+        </is>
+      </c>
+      <c r="H1521" t="inlineStr"/>
       <c r="I1521" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J1521" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K1521" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1522">
@@ -76847,7 +76847,7 @@
       </c>
       <c r="G1522" t="inlineStr">
         <is>
-          <t>Mariana Pires</t>
+          <t>Marcus Oliveira</t>
         </is>
       </c>
       <c r="H1522" t="inlineStr">
@@ -76856,13 +76856,13 @@
         </is>
       </c>
       <c r="I1522" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1522" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1522" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
     </row>
     <row r="1523">
@@ -76898,7 +76898,7 @@
       </c>
       <c r="G1523" t="inlineStr">
         <is>
-          <t>Marta Souza</t>
+          <t>Mariana Pires</t>
         </is>
       </c>
       <c r="H1523" t="inlineStr">
@@ -76907,13 +76907,13 @@
         </is>
       </c>
       <c r="I1523" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J1523" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1523" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="1524">
@@ -76949,7 +76949,7 @@
       </c>
       <c r="G1524" t="inlineStr">
         <is>
-          <t>Mateus Miranda</t>
+          <t>Marta Souza</t>
         </is>
       </c>
       <c r="H1524" t="inlineStr">
@@ -76958,13 +76958,13 @@
         </is>
       </c>
       <c r="I1524" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1524" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1524" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1525">
@@ -77000,7 +77000,7 @@
       </c>
       <c r="G1525" t="inlineStr">
         <is>
-          <t>Mirian Lima</t>
+          <t>Mateus Miranda</t>
         </is>
       </c>
       <c r="H1525" t="inlineStr">
@@ -77009,13 +77009,13 @@
         </is>
       </c>
       <c r="I1525" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="J1525" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K1525" t="n">
-        <v>36</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1526">
@@ -77051,7 +77051,7 @@
       </c>
       <c r="G1526" t="inlineStr">
         <is>
-          <t>Nathalia Lourenco</t>
+          <t>Mirian Lima</t>
         </is>
       </c>
       <c r="H1526" t="inlineStr">
@@ -77060,13 +77060,13 @@
         </is>
       </c>
       <c r="I1526" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J1526" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="K1526" t="n">
-        <v>58</v>
+        <v>36</v>
       </c>
     </row>
     <row r="1527">
@@ -77102,7 +77102,7 @@
       </c>
       <c r="G1527" t="inlineStr">
         <is>
-          <t>Nicolas Dias</t>
+          <t>Nathalia Lourenco</t>
         </is>
       </c>
       <c r="H1527" t="inlineStr">
@@ -77111,13 +77111,13 @@
         </is>
       </c>
       <c r="I1527" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="J1527" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="K1527" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="1528">
@@ -77153,7 +77153,7 @@
       </c>
       <c r="G1528" t="inlineStr">
         <is>
-          <t>Rodrigo Nunes</t>
+          <t>Nicolas Dias</t>
         </is>
       </c>
       <c r="H1528" t="inlineStr">
@@ -77162,13 +77162,13 @@
         </is>
       </c>
       <c r="I1528" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="J1528" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="K1528" t="n">
-        <v>13</v>
+        <v>59</v>
       </c>
     </row>
     <row r="1529">
@@ -77204,7 +77204,7 @@
       </c>
       <c r="G1529" t="inlineStr">
         <is>
-          <t>Thais Souza</t>
+          <t>Rodrigo Nunes</t>
         </is>
       </c>
       <c r="H1529" t="inlineStr">
@@ -77213,10 +77213,10 @@
         </is>
       </c>
       <c r="I1529" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1529" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1529" t="n">
         <v>13</v>
@@ -77255,7 +77255,7 @@
       </c>
       <c r="G1530" t="inlineStr">
         <is>
-          <t>Viviane Guedes</t>
+          <t>Thais Souza</t>
         </is>
       </c>
       <c r="H1530" t="inlineStr">
@@ -77270,7 +77270,7 @@
         <v>0</v>
       </c>
       <c r="K1530" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1531">
@@ -77301,27 +77301,27 @@
       </c>
       <c r="F1531" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="G1531" t="inlineStr">
         <is>
-          <t>Aline Petrini</t>
+          <t>Viviane Guedes</t>
         </is>
       </c>
       <c r="H1531" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Erika Santana|Isabella Nascimento</t>
         </is>
       </c>
       <c r="I1531" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J1531" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K1531" t="n">
-        <v>55</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1532">
@@ -77357,22 +77357,22 @@
       </c>
       <c r="G1532" t="inlineStr">
         <is>
-          <t>Ana Barbosa</t>
+          <t>Aline Petrini</t>
         </is>
       </c>
       <c r="H1532" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="I1532" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="J1532" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="K1532" t="n">
-        <v>64</v>
+        <v>55</v>
       </c>
     </row>
     <row r="1533">
@@ -77408,7 +77408,7 @@
       </c>
       <c r="G1533" t="inlineStr">
         <is>
-          <t>Daniele Leite</t>
+          <t>Ana Barbosa</t>
         </is>
       </c>
       <c r="H1533" t="inlineStr">
@@ -77417,13 +77417,13 @@
         </is>
       </c>
       <c r="I1533" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="J1533" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="K1533" t="n">
-        <v>13</v>
+        <v>65</v>
       </c>
     </row>
     <row r="1534">
@@ -77459,22 +77459,22 @@
       </c>
       <c r="G1534" t="inlineStr">
         <is>
-          <t>Danielle Silva</t>
+          <t>Daniele Leite</t>
         </is>
       </c>
       <c r="H1534" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I1534" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J1534" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K1534" t="n">
-        <v>81</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1535">
@@ -77510,7 +77510,7 @@
       </c>
       <c r="G1535" t="inlineStr">
         <is>
-          <t>Danilo Oliveira</t>
+          <t>Danielle Silva</t>
         </is>
       </c>
       <c r="H1535" t="inlineStr">
@@ -77525,7 +77525,7 @@
         <v>3</v>
       </c>
       <c r="K1535" t="n">
-        <v>38</v>
+        <v>81</v>
       </c>
     </row>
     <row r="1536">
@@ -77561,22 +77561,22 @@
       </c>
       <c r="G1536" t="inlineStr">
         <is>
-          <t>Debora Silva</t>
+          <t>Danilo Oliveira</t>
         </is>
       </c>
       <c r="H1536" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Karina Santos</t>
         </is>
       </c>
       <c r="I1536" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="J1536" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="K1536" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="1537">
@@ -77612,22 +77612,22 @@
       </c>
       <c r="G1537" t="inlineStr">
         <is>
-          <t>Diogo Calazans</t>
+          <t>Debora Silva</t>
         </is>
       </c>
       <c r="H1537" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="I1537" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J1537" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K1537" t="n">
-        <v>93</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1538">
@@ -77663,22 +77663,22 @@
       </c>
       <c r="G1538" t="inlineStr">
         <is>
-          <t>Eduardo Cruz</t>
+          <t>Diogo Calazans</t>
         </is>
       </c>
       <c r="H1538" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Karina Santos</t>
         </is>
       </c>
       <c r="I1538" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="J1538" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K1538" t="n">
-        <v>118</v>
+        <v>93</v>
       </c>
     </row>
     <row r="1539">
@@ -77714,22 +77714,22 @@
       </c>
       <c r="G1539" t="inlineStr">
         <is>
-          <t>Eveny Silva</t>
+          <t>Eduardo Cruz</t>
         </is>
       </c>
       <c r="H1539" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="I1539" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="J1539" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="K1539" t="n">
-        <v>103</v>
+        <v>140</v>
       </c>
     </row>
     <row r="1540">
@@ -77765,22 +77765,22 @@
       </c>
       <c r="G1540" t="inlineStr">
         <is>
-          <t>Everton Moura</t>
+          <t>Eveny Silva</t>
         </is>
       </c>
       <c r="H1540" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Karina Santos</t>
         </is>
       </c>
       <c r="I1540" t="n">
-        <v>5</v>
+        <v>63</v>
       </c>
       <c r="J1540" t="n">
-        <v>5</v>
+        <v>63</v>
       </c>
       <c r="K1540" t="n">
-        <v>14</v>
+        <v>112</v>
       </c>
     </row>
     <row r="1541">
@@ -77816,22 +77816,22 @@
       </c>
       <c r="G1541" t="inlineStr">
         <is>
-          <t>Guilherme Dantas</t>
+          <t>Everton Moura</t>
         </is>
       </c>
       <c r="H1541" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="I1541" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J1541" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K1541" t="n">
-        <v>53</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1542">
@@ -77867,22 +77867,22 @@
       </c>
       <c r="G1542" t="inlineStr">
         <is>
-          <t>Isabela Lemos</t>
+          <t>Guilherme Dantas</t>
         </is>
       </c>
       <c r="H1542" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I1542" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J1542" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K1542" t="n">
-        <v>30</v>
+        <v>53</v>
       </c>
     </row>
     <row r="1543">
@@ -77918,22 +77918,22 @@
       </c>
       <c r="G1543" t="inlineStr">
         <is>
-          <t>Jackson Silva</t>
+          <t>Isabela Lemos</t>
         </is>
       </c>
       <c r="H1543" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="I1543" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J1543" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K1543" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1544">
@@ -77969,22 +77969,22 @@
       </c>
       <c r="G1544" t="inlineStr">
         <is>
-          <t>Jaqueline Sousa</t>
+          <t>Jackson Silva</t>
         </is>
       </c>
       <c r="H1544" t="inlineStr">
         <is>
-          <t>Lucas Fischer</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I1544" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="J1544" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="K1544" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="1545">
@@ -78020,7 +78020,7 @@
       </c>
       <c r="G1545" t="inlineStr">
         <is>
-          <t>Leticia Medeiros</t>
+          <t>Jaqueline Sousa</t>
         </is>
       </c>
       <c r="H1545" t="inlineStr">
@@ -78029,13 +78029,13 @@
         </is>
       </c>
       <c r="I1545" t="n">
-        <v>64</v>
+        <v>19</v>
       </c>
       <c r="J1545" t="n">
-        <v>64</v>
+        <v>19</v>
       </c>
       <c r="K1545" t="n">
-        <v>141</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1546">
@@ -78071,22 +78071,22 @@
       </c>
       <c r="G1546" t="inlineStr">
         <is>
-          <t>Monica Medeiros</t>
+          <t>Leticia Medeiros</t>
         </is>
       </c>
       <c r="H1546" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Lucas Fischer</t>
         </is>
       </c>
       <c r="I1546" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="J1546" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="K1546" t="n">
-        <v>54</v>
+        <v>141</v>
       </c>
     </row>
     <row r="1547">
@@ -78122,22 +78122,22 @@
       </c>
       <c r="G1547" t="inlineStr">
         <is>
-          <t>Naiara Dutra</t>
+          <t>Monica Medeiros</t>
         </is>
       </c>
       <c r="H1547" t="inlineStr">
         <is>
-          <t>Lucas Fischer</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I1547" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="J1547" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="K1547" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="1548">
@@ -78173,22 +78173,22 @@
       </c>
       <c r="G1548" t="inlineStr">
         <is>
-          <t>Patricia Borges</t>
+          <t>Naiara Dutra</t>
         </is>
       </c>
       <c r="H1548" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Lucas Fischer</t>
         </is>
       </c>
       <c r="I1548" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="J1548" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="K1548" t="n">
-        <v>71</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1549">
@@ -78224,22 +78224,22 @@
       </c>
       <c r="G1549" t="inlineStr">
         <is>
-          <t>Paulo Silva</t>
+          <t>Patricia Borges</t>
         </is>
       </c>
       <c r="H1549" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I1549" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="J1549" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="K1549" t="n">
-        <v>83</v>
+        <v>71</v>
       </c>
     </row>
     <row r="1550">
@@ -78275,22 +78275,22 @@
       </c>
       <c r="G1550" t="inlineStr">
         <is>
-          <t>Rachel Lima</t>
+          <t>Paulo Silva</t>
         </is>
       </c>
       <c r="H1550" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="I1550" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="J1550" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="K1550" t="n">
-        <v>65</v>
+        <v>83</v>
       </c>
     </row>
     <row r="1551">
@@ -78326,7 +78326,7 @@
       </c>
       <c r="G1551" t="inlineStr">
         <is>
-          <t>Raiane Barbosa</t>
+          <t>Rachel Lima</t>
         </is>
       </c>
       <c r="H1551" t="inlineStr">
@@ -78335,13 +78335,13 @@
         </is>
       </c>
       <c r="I1551" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="J1551" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="K1551" t="n">
-        <v>119</v>
+        <v>65</v>
       </c>
     </row>
     <row r="1552">
@@ -78377,22 +78377,22 @@
       </c>
       <c r="G1552" t="inlineStr">
         <is>
-          <t>Rejane Coelho</t>
+          <t>Raiane Barbosa</t>
         </is>
       </c>
       <c r="H1552" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I1552" t="n">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="J1552" t="n">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="K1552" t="n">
-        <v>11</v>
+        <v>119</v>
       </c>
     </row>
     <row r="1553">
@@ -78428,22 +78428,22 @@
       </c>
       <c r="G1553" t="inlineStr">
         <is>
-          <t>Renata Alves - CTV</t>
+          <t>Rejane Coelho</t>
         </is>
       </c>
       <c r="H1553" t="inlineStr">
         <is>
-          <t>Lucas Fischer</t>
+          <t>Karina Santos</t>
         </is>
       </c>
       <c r="I1553" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="J1553" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="K1553" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1554">
@@ -78479,18 +78479,22 @@
       </c>
       <c r="G1554" t="inlineStr">
         <is>
-          <t>Renata Cavalheiro</t>
-        </is>
-      </c>
-      <c r="H1554" t="inlineStr"/>
+          <t>Renata Alves - CTV</t>
+        </is>
+      </c>
+      <c r="H1554" t="inlineStr">
+        <is>
+          <t>Lucas Fischer</t>
+        </is>
+      </c>
       <c r="I1554" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="J1554" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K1554" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
     </row>
     <row r="1555">
@@ -78526,22 +78530,18 @@
       </c>
       <c r="G1555" t="inlineStr">
         <is>
-          <t>Ryan Godinho</t>
-        </is>
-      </c>
-      <c r="H1555" t="inlineStr">
-        <is>
-          <t>Karina Santos</t>
-        </is>
-      </c>
+          <t>Renata Cavalheiro</t>
+        </is>
+      </c>
+      <c r="H1555" t="inlineStr"/>
       <c r="I1555" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J1555" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K1555" t="n">
-        <v>45</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1556">
@@ -78577,22 +78577,22 @@
       </c>
       <c r="G1556" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Ryan Godinho</t>
         </is>
       </c>
       <c r="H1556" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Karina Santos</t>
         </is>
       </c>
       <c r="I1556" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="J1556" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="K1556" t="n">
-        <v>4</v>
+        <v>56</v>
       </c>
     </row>
     <row r="1557">
@@ -78628,22 +78628,22 @@
       </c>
       <c r="G1557" t="inlineStr">
         <is>
-          <t>Vitor Domingues</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="H1557" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="I1557" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J1557" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K1557" t="n">
-        <v>78</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1558">
@@ -78674,27 +78674,27 @@
       </c>
       <c r="F1558" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO PESSOAL (Outsourcing)</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="G1558" t="inlineStr">
         <is>
-          <t>Bruna Santana</t>
+          <t>Vitor Domingues</t>
         </is>
       </c>
       <c r="H1558" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="I1558" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J1558" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K1558" t="n">
-        <v>4</v>
+        <v>78</v>
       </c>
     </row>
     <row r="1559">
@@ -78730,7 +78730,7 @@
       </c>
       <c r="G1559" t="inlineStr">
         <is>
-          <t>Camila Oliveira</t>
+          <t>Bruna Santana</t>
         </is>
       </c>
       <c r="H1559" t="inlineStr">
@@ -78739,13 +78739,13 @@
         </is>
       </c>
       <c r="I1559" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J1559" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1559" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1560">
@@ -78781,22 +78781,22 @@
       </c>
       <c r="G1560" t="inlineStr">
         <is>
-          <t>Elaine Assis</t>
+          <t>Camila Oliveira</t>
         </is>
       </c>
       <c r="H1560" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I1560" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1560" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1560" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1561">
@@ -78832,12 +78832,12 @@
       </c>
       <c r="G1561" t="inlineStr">
         <is>
-          <t>Fabiane Branco</t>
+          <t>Elaine Assis</t>
         </is>
       </c>
       <c r="H1561" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I1561" t="n">
@@ -78847,7 +78847,7 @@
         <v>0</v>
       </c>
       <c r="K1561" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1562">
@@ -78883,12 +78883,12 @@
       </c>
       <c r="G1562" t="inlineStr">
         <is>
-          <t>Jonas Nunes</t>
+          <t>Fabiane Branco</t>
         </is>
       </c>
       <c r="H1562" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I1562" t="n">
@@ -78898,7 +78898,7 @@
         <v>0</v>
       </c>
       <c r="K1562" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1563">
@@ -78929,12 +78929,12 @@
       </c>
       <c r="F1563" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>DEPARTAMENTO PESSOAL (Outsourcing)</t>
         </is>
       </c>
       <c r="G1563" t="inlineStr">
         <is>
-          <t>Aline Pereira</t>
+          <t>Jonas Nunes</t>
         </is>
       </c>
       <c r="H1563" t="inlineStr">
@@ -78949,7 +78949,7 @@
         <v>0</v>
       </c>
       <c r="K1563" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1564">
@@ -78985,7 +78985,7 @@
       </c>
       <c r="G1564" t="inlineStr">
         <is>
-          <t>Bruna Santana</t>
+          <t>Aline Pereira</t>
         </is>
       </c>
       <c r="H1564" t="inlineStr">
@@ -79000,7 +79000,7 @@
         <v>0</v>
       </c>
       <c r="K1564" t="n">
-        <v>129</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1565">
@@ -79036,7 +79036,7 @@
       </c>
       <c r="G1565" t="inlineStr">
         <is>
-          <t>Camila Oliveira</t>
+          <t>Bruna Santana</t>
         </is>
       </c>
       <c r="H1565" t="inlineStr">
@@ -79045,13 +79045,13 @@
         </is>
       </c>
       <c r="I1565" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J1565" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K1565" t="n">
-        <v>32</v>
+        <v>129</v>
       </c>
     </row>
     <row r="1566">
@@ -79087,22 +79087,22 @@
       </c>
       <c r="G1566" t="inlineStr">
         <is>
-          <t>Daniel Moraes</t>
+          <t>Camila Oliveira</t>
         </is>
       </c>
       <c r="H1566" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I1566" t="n">
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="J1566" t="n">
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="K1566" t="n">
-        <v>103</v>
+        <v>32</v>
       </c>
     </row>
     <row r="1567">
@@ -79138,7 +79138,7 @@
       </c>
       <c r="G1567" t="inlineStr">
         <is>
-          <t>Danilo Xavier</t>
+          <t>Daniel Moraes</t>
         </is>
       </c>
       <c r="H1567" t="inlineStr">
@@ -79147,13 +79147,13 @@
         </is>
       </c>
       <c r="I1567" t="n">
-        <v>1</v>
+        <v>62</v>
       </c>
       <c r="J1567" t="n">
-        <v>1</v>
+        <v>62</v>
       </c>
       <c r="K1567" t="n">
-        <v>178</v>
+        <v>113</v>
       </c>
     </row>
     <row r="1568">
@@ -79189,7 +79189,7 @@
       </c>
       <c r="G1568" t="inlineStr">
         <is>
-          <t>Elaine Assis</t>
+          <t>Danilo Xavier</t>
         </is>
       </c>
       <c r="H1568" t="inlineStr">
@@ -79198,13 +79198,13 @@
         </is>
       </c>
       <c r="I1568" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="J1568" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="K1568" t="n">
-        <v>84</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1569">
@@ -79240,22 +79240,22 @@
       </c>
       <c r="G1569" t="inlineStr">
         <is>
-          <t>Eliene Lima</t>
+          <t>Elaine Assis</t>
         </is>
       </c>
       <c r="H1569" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I1569" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J1569" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K1569" t="n">
-        <v>44</v>
+        <v>84</v>
       </c>
     </row>
     <row r="1570">
@@ -79291,22 +79291,22 @@
       </c>
       <c r="G1570" t="inlineStr">
         <is>
-          <t>Erica Oliveira</t>
+          <t>Eliene Lima</t>
         </is>
       </c>
       <c r="H1570" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I1570" t="n">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="J1570" t="n">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="K1570" t="n">
-        <v>86</v>
+        <v>44</v>
       </c>
     </row>
     <row r="1571">
@@ -79342,22 +79342,22 @@
       </c>
       <c r="G1571" t="inlineStr">
         <is>
-          <t>Evellin Bispo</t>
+          <t>Erica Oliveira</t>
         </is>
       </c>
       <c r="H1571" t="inlineStr">
         <is>
-          <t>Leandro Matos</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I1571" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="J1571" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="K1571" t="n">
-        <v>52</v>
+        <v>86</v>
       </c>
     </row>
     <row r="1572">
@@ -79393,12 +79393,12 @@
       </c>
       <c r="G1572" t="inlineStr">
         <is>
-          <t>Fabiane Branco</t>
+          <t>Evellin Bispo</t>
         </is>
       </c>
       <c r="H1572" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>Leandro Matos</t>
         </is>
       </c>
       <c r="I1572" t="n">
@@ -79408,7 +79408,7 @@
         <v>10</v>
       </c>
       <c r="K1572" t="n">
-        <v>141</v>
+        <v>52</v>
       </c>
     </row>
     <row r="1573">
@@ -79444,22 +79444,22 @@
       </c>
       <c r="G1573" t="inlineStr">
         <is>
-          <t>Franciele Alves</t>
+          <t>Fabiane Branco</t>
         </is>
       </c>
       <c r="H1573" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I1573" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J1573" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K1573" t="n">
-        <v>117</v>
+        <v>143</v>
       </c>
     </row>
     <row r="1574">
@@ -79495,22 +79495,22 @@
       </c>
       <c r="G1574" t="inlineStr">
         <is>
-          <t>Gabriela Peres</t>
+          <t>Franciele Alves</t>
         </is>
       </c>
       <c r="H1574" t="inlineStr">
         <is>
-          <t>Leandro Matos</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I1574" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J1574" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1574" t="n">
-        <v>14</v>
+        <v>117</v>
       </c>
     </row>
     <row r="1575">
@@ -79546,22 +79546,22 @@
       </c>
       <c r="G1575" t="inlineStr">
         <is>
-          <t>Grasiele Santos</t>
+          <t>Gabriela Peres</t>
         </is>
       </c>
       <c r="H1575" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Leandro Matos</t>
         </is>
       </c>
       <c r="I1575" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J1575" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K1575" t="n">
-        <v>149</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1576">
@@ -79597,22 +79597,22 @@
       </c>
       <c r="G1576" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Grasiele Santos</t>
         </is>
       </c>
       <c r="H1576" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I1576" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J1576" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K1576" t="n">
-        <v>230</v>
+        <v>158</v>
       </c>
     </row>
     <row r="1577">
@@ -79648,12 +79648,12 @@
       </c>
       <c r="G1577" t="inlineStr">
         <is>
-          <t>Janaina Rocha</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="H1577" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I1577" t="n">
@@ -79663,7 +79663,7 @@
         <v>0</v>
       </c>
       <c r="K1577" t="n">
-        <v>106</v>
+        <v>230</v>
       </c>
     </row>
     <row r="1578">
@@ -79699,22 +79699,22 @@
       </c>
       <c r="G1578" t="inlineStr">
         <is>
-          <t>Jayne Tavares</t>
+          <t>Janaina Rocha</t>
         </is>
       </c>
       <c r="H1578" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I1578" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J1578" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K1578" t="n">
-        <v>140</v>
+        <v>106</v>
       </c>
     </row>
     <row r="1579">
@@ -79750,22 +79750,22 @@
       </c>
       <c r="G1579" t="inlineStr">
         <is>
-          <t>Jhenifer Tenorio</t>
+          <t>Jayne Tavares</t>
         </is>
       </c>
       <c r="H1579" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I1579" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="J1579" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="K1579" t="n">
-        <v>134</v>
+        <v>140</v>
       </c>
     </row>
     <row r="1580">
@@ -79801,7 +79801,7 @@
       </c>
       <c r="G1580" t="inlineStr">
         <is>
-          <t>Jonas Nunes</t>
+          <t>Jhenifer Tenorio</t>
         </is>
       </c>
       <c r="H1580" t="inlineStr">
@@ -79810,13 +79810,13 @@
         </is>
       </c>
       <c r="I1580" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1580" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1580" t="n">
-        <v>114</v>
+        <v>134</v>
       </c>
     </row>
     <row r="1581">
@@ -79852,22 +79852,22 @@
       </c>
       <c r="G1581" t="inlineStr">
         <is>
-          <t>Kaique Souza</t>
+          <t>Jonas Nunes</t>
         </is>
       </c>
       <c r="H1581" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I1581" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="J1581" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="K1581" t="n">
-        <v>154</v>
+        <v>114</v>
       </c>
     </row>
     <row r="1582">
@@ -79903,7 +79903,7 @@
       </c>
       <c r="G1582" t="inlineStr">
         <is>
-          <t>Karine Sousa</t>
+          <t>Kaique Souza</t>
         </is>
       </c>
       <c r="H1582" t="inlineStr">
@@ -79912,13 +79912,13 @@
         </is>
       </c>
       <c r="I1582" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="J1582" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="K1582" t="n">
-        <v>114</v>
+        <v>154</v>
       </c>
     </row>
     <row r="1583">
@@ -79954,22 +79954,22 @@
       </c>
       <c r="G1583" t="inlineStr">
         <is>
-          <t>Laysla Alves</t>
+          <t>Karine Sousa</t>
         </is>
       </c>
       <c r="H1583" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I1583" t="n">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="J1583" t="n">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="K1583" t="n">
-        <v>87</v>
+        <v>114</v>
       </c>
     </row>
     <row r="1584">
@@ -80005,22 +80005,22 @@
       </c>
       <c r="G1584" t="inlineStr">
         <is>
-          <t>Luana Marques</t>
+          <t>Laysla Alves</t>
         </is>
       </c>
       <c r="H1584" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I1584" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J1584" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K1584" t="n">
-        <v>19</v>
+        <v>87</v>
       </c>
     </row>
     <row r="1585">
@@ -80056,7 +80056,7 @@
       </c>
       <c r="G1585" t="inlineStr">
         <is>
-          <t>Maria Pires</t>
+          <t>Luana Marques</t>
         </is>
       </c>
       <c r="H1585" t="inlineStr">
@@ -80065,13 +80065,13 @@
         </is>
       </c>
       <c r="I1585" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="J1585" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K1585" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1586">
@@ -80107,22 +80107,22 @@
       </c>
       <c r="G1586" t="inlineStr">
         <is>
-          <t>Mauricio Lermen</t>
+          <t>Maria Pires</t>
         </is>
       </c>
       <c r="H1586" t="inlineStr">
         <is>
-          <t>Mauricio Lermen</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I1586" t="n">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="J1586" t="n">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="K1586" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1587">
@@ -80158,22 +80158,22 @@
       </c>
       <c r="G1587" t="inlineStr">
         <is>
-          <t>Micaele Cordeiro</t>
+          <t>Mauricio Lermen</t>
         </is>
       </c>
       <c r="H1587" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>Mauricio Lermen</t>
         </is>
       </c>
       <c r="I1587" t="n">
-        <v>46</v>
+        <v>4</v>
       </c>
       <c r="J1587" t="n">
-        <v>46</v>
+        <v>4</v>
       </c>
       <c r="K1587" t="n">
-        <v>164</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1588">
@@ -80209,7 +80209,7 @@
       </c>
       <c r="G1588" t="inlineStr">
         <is>
-          <t>Michele Silva</t>
+          <t>Micaele Cordeiro</t>
         </is>
       </c>
       <c r="H1588" t="inlineStr">
@@ -80218,13 +80218,13 @@
         </is>
       </c>
       <c r="I1588" t="n">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="J1588" t="n">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="K1588" t="n">
-        <v>101</v>
+        <v>164</v>
       </c>
     </row>
     <row r="1589">
@@ -80260,18 +80260,22 @@
       </c>
       <c r="G1589" t="inlineStr">
         <is>
-          <t>Mikael Teixeira</t>
-        </is>
-      </c>
-      <c r="H1589" t="inlineStr"/>
+          <t>Michele Silva</t>
+        </is>
+      </c>
+      <c r="H1589" t="inlineStr">
+        <is>
+          <t>Sara Cavalheiro</t>
+        </is>
+      </c>
       <c r="I1589" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="J1589" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="K1589" t="n">
-        <v>7</v>
+        <v>101</v>
       </c>
     </row>
     <row r="1590">
@@ -80307,22 +80311,18 @@
       </c>
       <c r="G1590" t="inlineStr">
         <is>
-          <t>Murilo Marques</t>
-        </is>
-      </c>
-      <c r="H1590" t="inlineStr">
-        <is>
-          <t>David Bragança</t>
-        </is>
-      </c>
+          <t>Mikael Teixeira</t>
+        </is>
+      </c>
+      <c r="H1590" t="inlineStr"/>
       <c r="I1590" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J1590" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K1590" t="n">
-        <v>62</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1591">
@@ -80358,22 +80358,22 @@
       </c>
       <c r="G1591" t="inlineStr">
         <is>
-          <t>Natalia Batista</t>
+          <t>Murilo Marques</t>
         </is>
       </c>
       <c r="H1591" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I1591" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="J1591" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="K1591" t="n">
-        <v>129</v>
+        <v>62</v>
       </c>
     </row>
     <row r="1592">
@@ -80409,22 +80409,22 @@
       </c>
       <c r="G1592" t="inlineStr">
         <is>
-          <t>Natalia Silva</t>
+          <t>Natalia Batista</t>
         </is>
       </c>
       <c r="H1592" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I1592" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="J1592" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="K1592" t="n">
-        <v>122</v>
+        <v>129</v>
       </c>
     </row>
     <row r="1593">
@@ -80460,22 +80460,22 @@
       </c>
       <c r="G1593" t="inlineStr">
         <is>
-          <t>Oliene Mariano</t>
+          <t>Natalia Silva</t>
         </is>
       </c>
       <c r="H1593" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I1593" t="n">
-        <v>73</v>
+        <v>2</v>
       </c>
       <c r="J1593" t="n">
-        <v>73</v>
+        <v>2</v>
       </c>
       <c r="K1593" t="n">
-        <v>169</v>
+        <v>122</v>
       </c>
     </row>
     <row r="1594">
@@ -80511,22 +80511,22 @@
       </c>
       <c r="G1594" t="inlineStr">
         <is>
-          <t>Priscila Aguiar</t>
+          <t>Oliene Mariano</t>
         </is>
       </c>
       <c r="H1594" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I1594" t="n">
-        <v>13</v>
+        <v>76</v>
       </c>
       <c r="J1594" t="n">
-        <v>13</v>
+        <v>76</v>
       </c>
       <c r="K1594" t="n">
-        <v>125</v>
+        <v>169</v>
       </c>
     </row>
     <row r="1595">
@@ -80562,7 +80562,7 @@
       </c>
       <c r="G1595" t="inlineStr">
         <is>
-          <t>Rebeca Ribeiro</t>
+          <t>Priscila Aguiar</t>
         </is>
       </c>
       <c r="H1595" t="inlineStr">
@@ -80571,13 +80571,13 @@
         </is>
       </c>
       <c r="I1595" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="J1595" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="K1595" t="n">
-        <v>66</v>
+        <v>125</v>
       </c>
     </row>
     <row r="1596">
@@ -80613,7 +80613,7 @@
       </c>
       <c r="G1596" t="inlineStr">
         <is>
-          <t>Roberta Souza</t>
+          <t>Rebeca Ribeiro</t>
         </is>
       </c>
       <c r="H1596" t="inlineStr">
@@ -80622,13 +80622,13 @@
         </is>
       </c>
       <c r="I1596" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="J1596" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="K1596" t="n">
-        <v>142</v>
+        <v>66</v>
       </c>
     </row>
     <row r="1597">
@@ -80664,7 +80664,7 @@
       </c>
       <c r="G1597" t="inlineStr">
         <is>
-          <t>Ronildo Santos</t>
+          <t>Roberta Souza</t>
         </is>
       </c>
       <c r="H1597" t="inlineStr">
@@ -80673,13 +80673,13 @@
         </is>
       </c>
       <c r="I1597" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="J1597" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="K1597" t="n">
-        <v>6</v>
+        <v>148</v>
       </c>
     </row>
     <row r="1598">
@@ -80715,22 +80715,22 @@
       </c>
       <c r="G1598" t="inlineStr">
         <is>
-          <t>Rozania Santos</t>
+          <t>Ronildo Santos</t>
         </is>
       </c>
       <c r="H1598" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I1598" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J1598" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K1598" t="n">
-        <v>148</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1599">
@@ -80766,22 +80766,22 @@
       </c>
       <c r="G1599" t="inlineStr">
         <is>
-          <t>Santos Karina</t>
+          <t>Rozania Santos</t>
         </is>
       </c>
       <c r="H1599" t="inlineStr">
         <is>
-          <t>Leandro Matos</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I1599" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J1599" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K1599" t="n">
-        <v>4</v>
+        <v>148</v>
       </c>
     </row>
     <row r="1600">
@@ -80817,22 +80817,22 @@
       </c>
       <c r="G1600" t="inlineStr">
         <is>
-          <t>Sibelly Pereira</t>
+          <t>Santos Karina</t>
         </is>
       </c>
       <c r="H1600" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Leandro Matos</t>
         </is>
       </c>
       <c r="I1600" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="J1600" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K1600" t="n">
-        <v>128</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1601">
@@ -80868,22 +80868,22 @@
       </c>
       <c r="G1601" t="inlineStr">
         <is>
-          <t>Tania Luz</t>
+          <t>Sibelly Pereira</t>
         </is>
       </c>
       <c r="H1601" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I1601" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="J1601" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="K1601" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="1602">
@@ -80919,22 +80919,22 @@
       </c>
       <c r="G1602" t="inlineStr">
         <is>
-          <t>Vitor Guedes</t>
+          <t>Tania Luz</t>
         </is>
       </c>
       <c r="H1602" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I1602" t="n">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="J1602" t="n">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="K1602" t="n">
-        <v>170</v>
+        <v>125</v>
       </c>
     </row>
     <row r="1603">
@@ -80965,27 +80965,27 @@
       </c>
       <c r="F1603" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="G1603" t="inlineStr">
         <is>
-          <t>Andrea Medeiros</t>
+          <t>Vitor Guedes</t>
         </is>
       </c>
       <c r="H1603" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I1603" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J1603" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="K1603" t="n">
-        <v>80</v>
+        <v>170</v>
       </c>
     </row>
     <row r="1604">
@@ -81021,7 +81021,7 @@
       </c>
       <c r="G1604" t="inlineStr">
         <is>
-          <t>Caroline Nascimento</t>
+          <t>Andrea Medeiros</t>
         </is>
       </c>
       <c r="H1604" t="inlineStr">
@@ -81030,13 +81030,13 @@
         </is>
       </c>
       <c r="I1604" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J1604" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K1604" t="n">
-        <v>173</v>
+        <v>80</v>
       </c>
     </row>
     <row r="1605">
@@ -81072,7 +81072,7 @@
       </c>
       <c r="G1605" t="inlineStr">
         <is>
-          <t>Cristiana Grizostomo</t>
+          <t>Caroline Nascimento</t>
         </is>
       </c>
       <c r="H1605" t="inlineStr">
@@ -81081,13 +81081,13 @@
         </is>
       </c>
       <c r="I1605" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J1605" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K1605" t="n">
-        <v>90</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1606">
@@ -81123,18 +81123,22 @@
       </c>
       <c r="G1606" t="inlineStr">
         <is>
-          <t>Denis Reis</t>
-        </is>
-      </c>
-      <c r="H1606" t="inlineStr"/>
+          <t>Cristiana Grizostomo</t>
+        </is>
+      </c>
+      <c r="H1606" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
       <c r="I1606" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="J1606" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="K1606" t="n">
-        <v>119</v>
+        <v>90</v>
       </c>
     </row>
     <row r="1607">
@@ -81170,22 +81174,18 @@
       </c>
       <c r="G1607" t="inlineStr">
         <is>
-          <t>Eliane Moreira</t>
-        </is>
-      </c>
-      <c r="H1607" t="inlineStr">
-        <is>
-          <t>Nayara Oliveira</t>
-        </is>
-      </c>
+          <t>Denis Reis</t>
+        </is>
+      </c>
+      <c r="H1607" t="inlineStr"/>
       <c r="I1607" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J1607" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K1607" t="n">
-        <v>174</v>
+        <v>123</v>
       </c>
     </row>
     <row r="1608">
@@ -81221,7 +81221,7 @@
       </c>
       <c r="G1608" t="inlineStr">
         <is>
-          <t>Gustavo Tonan</t>
+          <t>Eliane Moreira</t>
         </is>
       </c>
       <c r="H1608" t="inlineStr">
@@ -81230,13 +81230,13 @@
         </is>
       </c>
       <c r="I1608" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="J1608" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="K1608" t="n">
-        <v>138</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1609">
@@ -81272,7 +81272,7 @@
       </c>
       <c r="G1609" t="inlineStr">
         <is>
-          <t>Jonatan Hayashibara</t>
+          <t>Gustavo Tonan</t>
         </is>
       </c>
       <c r="H1609" t="inlineStr">
@@ -81281,13 +81281,13 @@
         </is>
       </c>
       <c r="I1609" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="J1609" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="K1609" t="n">
-        <v>666</v>
+        <v>138</v>
       </c>
     </row>
     <row r="1610">
@@ -81323,7 +81323,7 @@
       </c>
       <c r="G1610" t="inlineStr">
         <is>
-          <t>Lais Arruda</t>
+          <t>Jonatan Hayashibara</t>
         </is>
       </c>
       <c r="H1610" t="inlineStr">
@@ -81332,13 +81332,13 @@
         </is>
       </c>
       <c r="I1610" t="n">
-        <v>16</v>
+        <v>65</v>
       </c>
       <c r="J1610" t="n">
-        <v>16</v>
+        <v>65</v>
       </c>
       <c r="K1610" t="n">
-        <v>141</v>
+        <v>692</v>
       </c>
     </row>
     <row r="1611">
@@ -81374,7 +81374,7 @@
       </c>
       <c r="G1611" t="inlineStr">
         <is>
-          <t>Luan Batista</t>
+          <t>Lais Arruda</t>
         </is>
       </c>
       <c r="H1611" t="inlineStr">
@@ -81383,13 +81383,13 @@
         </is>
       </c>
       <c r="I1611" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="J1611" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="K1611" t="n">
-        <v>113</v>
+        <v>142</v>
       </c>
     </row>
     <row r="1612">
@@ -81425,7 +81425,7 @@
       </c>
       <c r="G1612" t="inlineStr">
         <is>
-          <t>Maria Garcia</t>
+          <t>Luan Batista</t>
         </is>
       </c>
       <c r="H1612" t="inlineStr">
@@ -81434,13 +81434,13 @@
         </is>
       </c>
       <c r="I1612" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J1612" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K1612" t="n">
-        <v>110</v>
+        <v>119</v>
       </c>
     </row>
     <row r="1613">
@@ -81476,7 +81476,7 @@
       </c>
       <c r="G1613" t="inlineStr">
         <is>
-          <t>Priscila Volpe</t>
+          <t>Maria Garcia</t>
         </is>
       </c>
       <c r="H1613" t="inlineStr">
@@ -81485,13 +81485,13 @@
         </is>
       </c>
       <c r="I1613" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J1613" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K1613" t="n">
-        <v>22</v>
+        <v>111</v>
       </c>
     </row>
     <row r="1614">
@@ -81527,7 +81527,7 @@
       </c>
       <c r="G1614" t="inlineStr">
         <is>
-          <t>Rodrigo Souza</t>
+          <t>Priscila Volpe</t>
         </is>
       </c>
       <c r="H1614" t="inlineStr">
@@ -81536,13 +81536,13 @@
         </is>
       </c>
       <c r="I1614" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J1614" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K1614" t="n">
-        <v>149</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1615">
@@ -81578,7 +81578,7 @@
       </c>
       <c r="G1615" t="inlineStr">
         <is>
-          <t>Romario Silva</t>
+          <t>Rodrigo Souza</t>
         </is>
       </c>
       <c r="H1615" t="inlineStr">
@@ -81587,13 +81587,13 @@
         </is>
       </c>
       <c r="I1615" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J1615" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="K1615" t="n">
-        <v>279</v>
+        <v>152</v>
       </c>
     </row>
     <row r="1616">
@@ -81629,7 +81629,7 @@
       </c>
       <c r="G1616" t="inlineStr">
         <is>
-          <t>Rosilene Santos</t>
+          <t>Romario Silva</t>
         </is>
       </c>
       <c r="H1616" t="inlineStr">
@@ -81638,13 +81638,13 @@
         </is>
       </c>
       <c r="I1616" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J1616" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K1616" t="n">
-        <v>82</v>
+        <v>281</v>
       </c>
     </row>
     <row r="1617">
@@ -81680,7 +81680,7 @@
       </c>
       <c r="G1617" t="inlineStr">
         <is>
-          <t>Suede Gomes</t>
+          <t>Rosilene Santos</t>
         </is>
       </c>
       <c r="H1617" t="inlineStr">
@@ -81689,13 +81689,13 @@
         </is>
       </c>
       <c r="I1617" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J1617" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K1617" t="n">
-        <v>67</v>
+        <v>82</v>
       </c>
     </row>
     <row r="1618">
@@ -81731,7 +81731,7 @@
       </c>
       <c r="G1618" t="inlineStr">
         <is>
-          <t>Taina Silva</t>
+          <t>Suede Gomes</t>
         </is>
       </c>
       <c r="H1618" t="inlineStr">
@@ -81740,13 +81740,13 @@
         </is>
       </c>
       <c r="I1618" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J1618" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K1618" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="1619">
@@ -81782,7 +81782,7 @@
       </c>
       <c r="G1619" t="inlineStr">
         <is>
-          <t>Thayna Melo</t>
+          <t>Taina Silva</t>
         </is>
       </c>
       <c r="H1619" t="inlineStr">
@@ -81797,7 +81797,7 @@
         <v>0</v>
       </c>
       <c r="K1619" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="1620">
@@ -81833,7 +81833,7 @@
       </c>
       <c r="G1620" t="inlineStr">
         <is>
-          <t>Vanessa Santana</t>
+          <t>Thayna Melo</t>
         </is>
       </c>
       <c r="H1620" t="inlineStr">
@@ -81842,13 +81842,13 @@
         </is>
       </c>
       <c r="I1620" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J1620" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K1620" t="n">
-        <v>200</v>
+        <v>72</v>
       </c>
     </row>
     <row r="1621">
@@ -81879,27 +81879,27 @@
       </c>
       <c r="F1621" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="G1621" t="inlineStr">
         <is>
-          <t>Alaine Neres</t>
+          <t>Vanessa Santana</t>
         </is>
       </c>
       <c r="H1621" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
       <c r="I1621" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="J1621" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="K1621" t="n">
-        <v>214</v>
+        <v>200</v>
       </c>
     </row>
     <row r="1622">
@@ -81935,22 +81935,22 @@
       </c>
       <c r="G1622" t="inlineStr">
         <is>
-          <t>Andre Silva</t>
+          <t>Alaine Neres</t>
         </is>
       </c>
       <c r="H1622" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I1622" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="J1622" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="K1622" t="n">
-        <v>117</v>
+        <v>214</v>
       </c>
     </row>
     <row r="1623">
@@ -81986,22 +81986,22 @@
       </c>
       <c r="G1623" t="inlineStr">
         <is>
-          <t>Anna Ramalho</t>
+          <t>Andre Silva</t>
         </is>
       </c>
       <c r="H1623" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I1623" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="J1623" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="K1623" t="n">
-        <v>107</v>
+        <v>122</v>
       </c>
     </row>
     <row r="1624">
@@ -82037,7 +82037,7 @@
       </c>
       <c r="G1624" t="inlineStr">
         <is>
-          <t>Beatriz Ferreira</t>
+          <t>Anna Ramalho</t>
         </is>
       </c>
       <c r="H1624" t="inlineStr">
@@ -82046,13 +82046,13 @@
         </is>
       </c>
       <c r="I1624" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="J1624" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="K1624" t="n">
-        <v>188</v>
+        <v>107</v>
       </c>
     </row>
     <row r="1625">
@@ -82088,22 +82088,22 @@
       </c>
       <c r="G1625" t="inlineStr">
         <is>
-          <t>Brenda Batista</t>
+          <t>Beatriz Ferreira</t>
         </is>
       </c>
       <c r="H1625" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="I1625" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J1625" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="K1625" t="n">
-        <v>82</v>
+        <v>188</v>
       </c>
     </row>
     <row r="1626">
@@ -82139,22 +82139,22 @@
       </c>
       <c r="G1626" t="inlineStr">
         <is>
-          <t>Bruna Souza</t>
+          <t>Brenda Batista</t>
         </is>
       </c>
       <c r="H1626" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I1626" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="J1626" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="K1626" t="n">
-        <v>89</v>
+        <v>83</v>
       </c>
     </row>
     <row r="1627">
@@ -82190,22 +82190,22 @@
       </c>
       <c r="G1627" t="inlineStr">
         <is>
-          <t>Bruno Henrique</t>
+          <t>Bruna Souza</t>
         </is>
       </c>
       <c r="H1627" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I1627" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="J1627" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="K1627" t="n">
-        <v>163</v>
+        <v>91</v>
       </c>
     </row>
     <row r="1628">
@@ -82241,18 +82241,22 @@
       </c>
       <c r="G1628" t="inlineStr">
         <is>
-          <t>Claudineia Rodrigues</t>
-        </is>
-      </c>
-      <c r="H1628" t="inlineStr"/>
+          <t>Bruno Henrique</t>
+        </is>
+      </c>
+      <c r="H1628" t="inlineStr">
+        <is>
+          <t>Lorrane Santos</t>
+        </is>
+      </c>
       <c r="I1628" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J1628" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K1628" t="n">
-        <v>218</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1629">
@@ -82288,22 +82292,18 @@
       </c>
       <c r="G1629" t="inlineStr">
         <is>
-          <t>Cristina Leite</t>
-        </is>
-      </c>
-      <c r="H1629" t="inlineStr">
-        <is>
-          <t>Ricardo Fischer</t>
-        </is>
-      </c>
+          <t>Claudineia Rodrigues</t>
+        </is>
+      </c>
+      <c r="H1629" t="inlineStr"/>
       <c r="I1629" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J1629" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K1629" t="n">
-        <v>167</v>
+        <v>218</v>
       </c>
     </row>
     <row r="1630">
@@ -82339,22 +82339,22 @@
       </c>
       <c r="G1630" t="inlineStr">
         <is>
-          <t>Davi Santos</t>
+          <t>Cristina Leite</t>
         </is>
       </c>
       <c r="H1630" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="I1630" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="J1630" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="K1630" t="n">
-        <v>140</v>
+        <v>168</v>
       </c>
     </row>
     <row r="1631">
@@ -82390,22 +82390,22 @@
       </c>
       <c r="G1631" t="inlineStr">
         <is>
-          <t>Deleia Oliveira</t>
+          <t>Davi Santos</t>
         </is>
       </c>
       <c r="H1631" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I1631" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="J1631" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="K1631" t="n">
-        <v>166</v>
+        <v>139</v>
       </c>
     </row>
     <row r="1632">
@@ -82441,22 +82441,22 @@
       </c>
       <c r="G1632" t="inlineStr">
         <is>
-          <t>Diego Pereira</t>
+          <t>Deleia Oliveira</t>
         </is>
       </c>
       <c r="H1632" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I1632" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="J1632" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="K1632" t="n">
-        <v>115</v>
+        <v>167</v>
       </c>
     </row>
     <row r="1633">
@@ -82492,22 +82492,22 @@
       </c>
       <c r="G1633" t="inlineStr">
         <is>
-          <t>Eduardo Lopes</t>
+          <t>Diego Pereira</t>
         </is>
       </c>
       <c r="H1633" t="inlineStr">
         <is>
-          <t>Idna Sousa</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I1633" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="J1633" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="K1633" t="n">
-        <v>71</v>
+        <v>115</v>
       </c>
     </row>
     <row r="1634">
@@ -82543,22 +82543,22 @@
       </c>
       <c r="G1634" t="inlineStr">
         <is>
-          <t>Gislaine Lima</t>
+          <t>Eduardo Lopes</t>
         </is>
       </c>
       <c r="H1634" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Idna Sousa</t>
         </is>
       </c>
       <c r="I1634" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J1634" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K1634" t="n">
-        <v>121</v>
+        <v>71</v>
       </c>
     </row>
     <row r="1635">
@@ -82594,22 +82594,22 @@
       </c>
       <c r="G1635" t="inlineStr">
         <is>
-          <t>Gustavo Santos</t>
+          <t>Gislaine Lima</t>
         </is>
       </c>
       <c r="H1635" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I1635" t="n">
-        <v>68</v>
+        <v>22</v>
       </c>
       <c r="J1635" t="n">
-        <v>68</v>
+        <v>22</v>
       </c>
       <c r="K1635" t="n">
-        <v>298</v>
+        <v>125</v>
       </c>
     </row>
     <row r="1636">
@@ -82645,22 +82645,22 @@
       </c>
       <c r="G1636" t="inlineStr">
         <is>
-          <t>Igor Valezi</t>
+          <t>Gustavo Santos</t>
         </is>
       </c>
       <c r="H1636" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="I1636" t="n">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="J1636" t="n">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="K1636" t="n">
-        <v>102</v>
+        <v>298</v>
       </c>
     </row>
     <row r="1637">
@@ -82696,22 +82696,22 @@
       </c>
       <c r="G1637" t="inlineStr">
         <is>
-          <t>Izabely Araujo</t>
+          <t>Igor Valezi</t>
         </is>
       </c>
       <c r="H1637" t="inlineStr">
         <is>
-          <t>Idna Sousa</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I1637" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="J1637" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="K1637" t="n">
-        <v>79</v>
+        <v>102</v>
       </c>
     </row>
     <row r="1638">
@@ -82747,22 +82747,22 @@
       </c>
       <c r="G1638" t="inlineStr">
         <is>
-          <t>Joanna Costa</t>
+          <t>Izabely Araujo</t>
         </is>
       </c>
       <c r="H1638" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Idna Sousa</t>
         </is>
       </c>
       <c r="I1638" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J1638" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="K1638" t="n">
-        <v>51</v>
+        <v>79</v>
       </c>
     </row>
     <row r="1639">
@@ -82798,22 +82798,22 @@
       </c>
       <c r="G1639" t="inlineStr">
         <is>
-          <t>Jose Borges</t>
+          <t>Joanna Costa</t>
         </is>
       </c>
       <c r="H1639" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I1639" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="J1639" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="K1639" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
     </row>
     <row r="1640">
@@ -82849,22 +82849,22 @@
       </c>
       <c r="G1640" t="inlineStr">
         <is>
-          <t>Jose Natan</t>
+          <t>Jose Borges</t>
         </is>
       </c>
       <c r="H1640" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="I1640" t="n">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="J1640" t="n">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="K1640" t="n">
-        <v>147</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1641">
@@ -82900,7 +82900,7 @@
       </c>
       <c r="G1641" t="inlineStr">
         <is>
-          <t>João Oliveira</t>
+          <t>Jose Natan</t>
         </is>
       </c>
       <c r="H1641" t="inlineStr">
@@ -82909,13 +82909,13 @@
         </is>
       </c>
       <c r="I1641" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J1641" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K1641" t="n">
-        <v>21</v>
+        <v>148</v>
       </c>
     </row>
     <row r="1642">
@@ -82951,22 +82951,22 @@
       </c>
       <c r="G1642" t="inlineStr">
         <is>
-          <t>Juan Ribeiro</t>
+          <t>João Oliveira</t>
         </is>
       </c>
       <c r="H1642" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I1642" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J1642" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K1642" t="n">
-        <v>100</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1643">
@@ -83002,22 +83002,22 @@
       </c>
       <c r="G1643" t="inlineStr">
         <is>
-          <t>Juliana Valeria</t>
+          <t>Juan Ribeiro</t>
         </is>
       </c>
       <c r="H1643" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I1643" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J1643" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K1643" t="n">
-        <v>150</v>
+        <v>101</v>
       </c>
     </row>
     <row r="1644">
@@ -83053,7 +83053,7 @@
       </c>
       <c r="G1644" t="inlineStr">
         <is>
-          <t>Juliane Vaz</t>
+          <t>Juliana Valeria</t>
         </is>
       </c>
       <c r="H1644" t="inlineStr">
@@ -83062,13 +83062,13 @@
         </is>
       </c>
       <c r="I1644" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="J1644" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="K1644" t="n">
-        <v>296</v>
+        <v>151</v>
       </c>
     </row>
     <row r="1645">
@@ -83104,22 +83104,22 @@
       </c>
       <c r="G1645" t="inlineStr">
         <is>
-          <t>Katia Xavier</t>
+          <t>Juliane Vaz</t>
         </is>
       </c>
       <c r="H1645" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I1645" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J1645" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K1645" t="n">
-        <v>103</v>
+        <v>298</v>
       </c>
     </row>
     <row r="1646">
@@ -83155,22 +83155,22 @@
       </c>
       <c r="G1646" t="inlineStr">
         <is>
-          <t>Larissa Félix</t>
+          <t>Katia Xavier</t>
         </is>
       </c>
       <c r="H1646" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I1646" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="J1646" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="K1646" t="n">
-        <v>224</v>
+        <v>103</v>
       </c>
     </row>
     <row r="1647">
@@ -83206,22 +83206,22 @@
       </c>
       <c r="G1647" t="inlineStr">
         <is>
-          <t>Léia de Oliveira</t>
+          <t>Larissa Félix</t>
         </is>
       </c>
       <c r="H1647" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I1647" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J1647" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K1647" t="n">
-        <v>142</v>
+        <v>224</v>
       </c>
     </row>
     <row r="1648">
@@ -83257,7 +83257,7 @@
       </c>
       <c r="G1648" t="inlineStr">
         <is>
-          <t>Maria Gualberto</t>
+          <t>Léia de Oliveira</t>
         </is>
       </c>
       <c r="H1648" t="inlineStr">
@@ -83266,13 +83266,13 @@
         </is>
       </c>
       <c r="I1648" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="J1648" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="K1648" t="n">
-        <v>112</v>
+        <v>143</v>
       </c>
     </row>
     <row r="1649">
@@ -83308,12 +83308,12 @@
       </c>
       <c r="G1649" t="inlineStr">
         <is>
-          <t>Nathany Silva</t>
+          <t>Maria Gualberto</t>
         </is>
       </c>
       <c r="H1649" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I1649" t="n">
@@ -83323,7 +83323,7 @@
         <v>8</v>
       </c>
       <c r="K1649" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
     </row>
     <row r="1650">
@@ -83359,22 +83359,22 @@
       </c>
       <c r="G1650" t="inlineStr">
         <is>
-          <t>Priscila Moreira</t>
+          <t>Nathany Silva</t>
         </is>
       </c>
       <c r="H1650" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I1650" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J1650" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K1650" t="n">
-        <v>145</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1651">
@@ -83410,22 +83410,22 @@
       </c>
       <c r="G1651" t="inlineStr">
         <is>
-          <t>Regiane Santos</t>
+          <t>Priscila Moreira</t>
         </is>
       </c>
       <c r="H1651" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="I1651" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J1651" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1651" t="n">
-        <v>68</v>
+        <v>144</v>
       </c>
     </row>
     <row r="1652">
@@ -83461,22 +83461,22 @@
       </c>
       <c r="G1652" t="inlineStr">
         <is>
-          <t>Shofia Gomes</t>
+          <t>Regiane Santos</t>
         </is>
       </c>
       <c r="H1652" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Larice Souza</t>
         </is>
       </c>
       <c r="I1652" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J1652" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K1652" t="n">
-        <v>138</v>
+        <v>68</v>
       </c>
     </row>
     <row r="1653">
@@ -83512,22 +83512,22 @@
       </c>
       <c r="G1653" t="inlineStr">
         <is>
-          <t>Vanessa Tavares</t>
+          <t>Shofia Gomes</t>
         </is>
       </c>
       <c r="H1653" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="I1653" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J1653" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K1653" t="n">
-        <v>92</v>
+        <v>141</v>
       </c>
     </row>
     <row r="1654">
@@ -83563,7 +83563,7 @@
       </c>
       <c r="G1654" t="inlineStr">
         <is>
-          <t>Willian Luz</t>
+          <t>Vanessa Tavares</t>
         </is>
       </c>
       <c r="H1654" t="inlineStr">
@@ -83572,13 +83572,13 @@
         </is>
       </c>
       <c r="I1654" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J1654" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="K1654" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="1655">
@@ -83614,7 +83614,7 @@
       </c>
       <c r="G1655" t="inlineStr">
         <is>
-          <t>Yasmim Oliveira</t>
+          <t>Willian Luz</t>
         </is>
       </c>
       <c r="H1655" t="inlineStr">
@@ -83623,13 +83623,13 @@
         </is>
       </c>
       <c r="I1655" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J1655" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K1655" t="n">
-        <v>54</v>
+        <v>101</v>
       </c>
     </row>
     <row r="1656">
@@ -83660,23 +83660,27 @@
       </c>
       <c r="F1656" t="inlineStr">
         <is>
-          <t>ESCRITA FISCAL (Outsourcing)</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="G1656" t="inlineStr">
         <is>
-          <t>Claudineia Rodrigues</t>
-        </is>
-      </c>
-      <c r="H1656" t="inlineStr"/>
+          <t>Yasmim Oliveira</t>
+        </is>
+      </c>
+      <c r="H1656" t="inlineStr">
+        <is>
+          <t>Larice Souza</t>
+        </is>
+      </c>
       <c r="I1656" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J1656" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K1656" t="n">
-        <v>6</v>
+        <v>54</v>
       </c>
     </row>
     <row r="1657">
@@ -83712,14 +83716,10 @@
       </c>
       <c r="G1657" t="inlineStr">
         <is>
-          <t>Diego Pereira</t>
-        </is>
-      </c>
-      <c r="H1657" t="inlineStr">
-        <is>
-          <t>Thaiza Oliveira</t>
-        </is>
-      </c>
+          <t>Claudineia Rodrigues</t>
+        </is>
+      </c>
+      <c r="H1657" t="inlineStr"/>
       <c r="I1657" t="n">
         <v>0</v>
       </c>
@@ -83727,7 +83727,7 @@
         <v>0</v>
       </c>
       <c r="K1657" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1658">
@@ -83763,22 +83763,22 @@
       </c>
       <c r="G1658" t="inlineStr">
         <is>
-          <t>Gislaine Lima</t>
+          <t>Diego Pereira</t>
         </is>
       </c>
       <c r="H1658" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I1658" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J1658" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K1658" t="n">
-        <v>39</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1659">
@@ -83814,7 +83814,7 @@
       </c>
       <c r="G1659" t="inlineStr">
         <is>
-          <t>Joanna Costa</t>
+          <t>Gislaine Lima</t>
         </is>
       </c>
       <c r="H1659" t="inlineStr">
@@ -83823,13 +83823,13 @@
         </is>
       </c>
       <c r="I1659" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J1659" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K1659" t="n">
-        <v>63</v>
+        <v>39</v>
       </c>
     </row>
     <row r="1660">
@@ -83865,22 +83865,22 @@
       </c>
       <c r="G1660" t="inlineStr">
         <is>
-          <t>Jonatan Hayashibara</t>
+          <t>Joanna Costa</t>
         </is>
       </c>
       <c r="H1660" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I1660" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1660" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K1660" t="n">
-        <v>4</v>
+        <v>63</v>
       </c>
     </row>
     <row r="1661">
@@ -83916,22 +83916,22 @@
       </c>
       <c r="G1661" t="inlineStr">
         <is>
-          <t>Jose Borges</t>
+          <t>Jonatan Hayashibara</t>
         </is>
       </c>
       <c r="H1661" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
       <c r="I1661" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J1661" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1661" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1662">
@@ -83967,22 +83967,22 @@
       </c>
       <c r="G1662" t="inlineStr">
         <is>
-          <t>João Oliveira</t>
+          <t>Jose Borges</t>
         </is>
       </c>
       <c r="H1662" t="inlineStr">
         <is>
-          <t>Larice Souza</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="I1662" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="J1662" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="K1662" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1663">
@@ -84018,7 +84018,7 @@
       </c>
       <c r="G1663" t="inlineStr">
         <is>
-          <t>Regiane Santos</t>
+          <t>João Oliveira</t>
         </is>
       </c>
       <c r="H1663" t="inlineStr">
@@ -84027,13 +84027,13 @@
         </is>
       </c>
       <c r="I1663" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="J1663" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="K1663" t="n">
-        <v>19</v>
+        <v>70</v>
       </c>
     </row>
     <row r="1664">
@@ -84069,7 +84069,7 @@
       </c>
       <c r="G1664" t="inlineStr">
         <is>
-          <t>Yasmim Oliveira</t>
+          <t>Regiane Santos</t>
         </is>
       </c>
       <c r="H1664" t="inlineStr">
@@ -84084,7 +84084,7 @@
         <v>1</v>
       </c>
       <c r="K1664" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1665">
@@ -84115,23 +84115,27 @@
       </c>
       <c r="F1665" t="inlineStr">
         <is>
-          <t>FIN - CONTÁBIL</t>
+          <t>ESCRITA FISCAL (Outsourcing)</t>
         </is>
       </c>
       <c r="G1665" t="inlineStr">
         <is>
-          <t>Daniele Faria</t>
-        </is>
-      </c>
-      <c r="H1665" t="inlineStr"/>
+          <t>Yasmim Oliveira</t>
+        </is>
+      </c>
+      <c r="H1665" t="inlineStr">
+        <is>
+          <t>Larice Souza</t>
+        </is>
+      </c>
       <c r="I1665" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="J1665" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="K1665" t="n">
-        <v>108</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1666">
@@ -84162,23 +84166,23 @@
       </c>
       <c r="F1666" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>FIN - CONTÁBIL</t>
         </is>
       </c>
       <c r="G1666" t="inlineStr">
         <is>
-          <t>Ana Santana</t>
+          <t>Daniele Faria</t>
         </is>
       </c>
       <c r="H1666" t="inlineStr"/>
       <c r="I1666" t="n">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="J1666" t="n">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="K1666" t="n">
-        <v>587</v>
+        <v>108</v>
       </c>
     </row>
     <row r="1667">
@@ -84214,18 +84218,18 @@
       </c>
       <c r="G1667" t="inlineStr">
         <is>
-          <t>Andre Coelho</t>
+          <t>Ana Santana</t>
         </is>
       </c>
       <c r="H1667" t="inlineStr"/>
       <c r="I1667" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="J1667" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="K1667" t="n">
-        <v>16</v>
+        <v>588</v>
       </c>
     </row>
     <row r="1668">
@@ -84261,18 +84265,18 @@
       </c>
       <c r="G1668" t="inlineStr">
         <is>
-          <t>Bianca Castro</t>
+          <t>Andre Coelho</t>
         </is>
       </c>
       <c r="H1668" t="inlineStr"/>
       <c r="I1668" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J1668" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K1668" t="n">
-        <v>458</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1669">
@@ -84308,18 +84312,18 @@
       </c>
       <c r="G1669" t="inlineStr">
         <is>
-          <t>Bruna Costa</t>
+          <t>Bianca Castro</t>
         </is>
       </c>
       <c r="H1669" t="inlineStr"/>
       <c r="I1669" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J1669" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K1669" t="n">
-        <v>34</v>
+        <v>458</v>
       </c>
     </row>
     <row r="1670">
@@ -84355,18 +84359,18 @@
       </c>
       <c r="G1670" t="inlineStr">
         <is>
-          <t>Daniela Silva</t>
+          <t>Bruna Costa</t>
         </is>
       </c>
       <c r="H1670" t="inlineStr"/>
       <c r="I1670" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="J1670" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="K1670" t="n">
-        <v>302</v>
+        <v>34</v>
       </c>
     </row>
     <row r="1671">
@@ -84402,18 +84406,18 @@
       </c>
       <c r="G1671" t="inlineStr">
         <is>
-          <t>Isabelli Afonso</t>
+          <t>Daniela Silva</t>
         </is>
       </c>
       <c r="H1671" t="inlineStr"/>
       <c r="I1671" t="n">
-        <v>1</v>
+        <v>98</v>
       </c>
       <c r="J1671" t="n">
-        <v>1</v>
+        <v>98</v>
       </c>
       <c r="K1671" t="n">
-        <v>234</v>
+        <v>302</v>
       </c>
     </row>
     <row r="1672">
@@ -84449,18 +84453,18 @@
       </c>
       <c r="G1672" t="inlineStr">
         <is>
-          <t>Jurema Damacena - SAC</t>
+          <t>Isabelli Afonso</t>
         </is>
       </c>
       <c r="H1672" t="inlineStr"/>
       <c r="I1672" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1672" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1672" t="n">
-        <v>1</v>
+        <v>234</v>
       </c>
     </row>
     <row r="1673">
@@ -84496,18 +84500,18 @@
       </c>
       <c r="G1673" t="inlineStr">
         <is>
-          <t>Leticia Queiroz</t>
+          <t>Jurema Damacena - SAC</t>
         </is>
       </c>
       <c r="H1673" t="inlineStr"/>
       <c r="I1673" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J1673" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K1673" t="n">
-        <v>428</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1674">
@@ -84543,18 +84547,18 @@
       </c>
       <c r="G1674" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Leticia Queiroz</t>
         </is>
       </c>
       <c r="H1674" t="inlineStr"/>
       <c r="I1674" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J1674" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K1674" t="n">
-        <v>13</v>
+        <v>428</v>
       </c>
     </row>
     <row r="1675">
@@ -84590,18 +84594,18 @@
       </c>
       <c r="G1675" t="inlineStr">
         <is>
-          <t>Victoria Virgens</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="H1675" t="inlineStr"/>
       <c r="I1675" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J1675" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1675" t="n">
-        <v>309</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1676">
@@ -84637,18 +84641,18 @@
       </c>
       <c r="G1676" t="inlineStr">
         <is>
-          <t>Yasmin Peixoto</t>
+          <t>Victoria Virgens</t>
         </is>
       </c>
       <c r="H1676" t="inlineStr"/>
       <c r="I1676" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="J1676" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="K1676" t="n">
-        <v>554</v>
+        <v>309</v>
       </c>
     </row>
     <row r="1677">
@@ -84679,23 +84683,23 @@
       </c>
       <c r="F1677" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="G1677" t="inlineStr">
         <is>
-          <t>Andre Coelho</t>
+          <t>Yasmin Peixoto</t>
         </is>
       </c>
       <c r="H1677" t="inlineStr"/>
       <c r="I1677" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J1677" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K1677" t="n">
-        <v>4</v>
+        <v>554</v>
       </c>
     </row>
     <row r="1678">
@@ -84731,18 +84735,18 @@
       </c>
       <c r="G1678" t="inlineStr">
         <is>
-          <t>Beatriz Rangel</t>
+          <t>Andre Coelho</t>
         </is>
       </c>
       <c r="H1678" t="inlineStr"/>
       <c r="I1678" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J1678" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K1678" t="n">
-        <v>375</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1679">
@@ -84778,18 +84782,18 @@
       </c>
       <c r="G1679" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
+          <t>Beatriz Rangel</t>
         </is>
       </c>
       <c r="H1679" t="inlineStr"/>
       <c r="I1679" t="n">
-        <v>95</v>
+        <v>5</v>
       </c>
       <c r="J1679" t="n">
-        <v>95</v>
+        <v>5</v>
       </c>
       <c r="K1679" t="n">
-        <v>434</v>
+        <v>375</v>
       </c>
     </row>
     <row r="1680">
@@ -84825,18 +84829,18 @@
       </c>
       <c r="G1680" t="inlineStr">
         <is>
-          <t>Cristiane Simões</t>
+          <t>Bruno Contieri</t>
         </is>
       </c>
       <c r="H1680" t="inlineStr"/>
       <c r="I1680" t="n">
-        <v>4</v>
+        <v>96</v>
       </c>
       <c r="J1680" t="n">
-        <v>4</v>
+        <v>96</v>
       </c>
       <c r="K1680" t="n">
-        <v>305</v>
+        <v>434</v>
       </c>
     </row>
     <row r="1681">
@@ -84872,18 +84876,18 @@
       </c>
       <c r="G1681" t="inlineStr">
         <is>
-          <t>Daniel Oliveira</t>
+          <t>Cristiane Simões</t>
         </is>
       </c>
       <c r="H1681" t="inlineStr"/>
       <c r="I1681" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J1681" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K1681" t="n">
-        <v>399</v>
+        <v>303</v>
       </c>
     </row>
     <row r="1682">
@@ -84919,18 +84923,18 @@
       </c>
       <c r="G1682" t="inlineStr">
         <is>
-          <t>Diego Lima</t>
+          <t>Daniel Oliveira</t>
         </is>
       </c>
       <c r="H1682" t="inlineStr"/>
       <c r="I1682" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J1682" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K1682" t="n">
-        <v>164</v>
+        <v>401</v>
       </c>
     </row>
     <row r="1683">
@@ -84966,7 +84970,7 @@
       </c>
       <c r="G1683" t="inlineStr">
         <is>
-          <t>Eduardo Aparicio</t>
+          <t>Diego Lima</t>
         </is>
       </c>
       <c r="H1683" t="inlineStr"/>
@@ -84977,7 +84981,7 @@
         <v>1</v>
       </c>
       <c r="K1683" t="n">
-        <v>1</v>
+        <v>164</v>
       </c>
     </row>
     <row r="1684">
@@ -85013,18 +85017,18 @@
       </c>
       <c r="G1684" t="inlineStr">
         <is>
-          <t>Karine Gusmão</t>
+          <t>Eduardo Aparicio</t>
         </is>
       </c>
       <c r="H1684" t="inlineStr"/>
       <c r="I1684" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1684" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1684" t="n">
-        <v>93</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1685">
@@ -85060,7 +85064,7 @@
       </c>
       <c r="G1685" t="inlineStr">
         <is>
-          <t>Luiz Ferreira</t>
+          <t>Karine Gusmão</t>
         </is>
       </c>
       <c r="H1685" t="inlineStr"/>
@@ -85071,7 +85075,7 @@
         <v>0</v>
       </c>
       <c r="K1685" t="n">
-        <v>17</v>
+        <v>93</v>
       </c>
     </row>
     <row r="1686">
@@ -85107,18 +85111,18 @@
       </c>
       <c r="G1686" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Luiz Ferreira</t>
         </is>
       </c>
       <c r="H1686" t="inlineStr"/>
       <c r="I1686" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J1686" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1686" t="n">
-        <v>221</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1687">
@@ -85154,18 +85158,18 @@
       </c>
       <c r="G1687" t="inlineStr">
         <is>
-          <t>Rodrigo Rego</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="H1687" t="inlineStr"/>
       <c r="I1687" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J1687" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K1687" t="n">
-        <v>460</v>
+        <v>221</v>
       </c>
     </row>
     <row r="1688">
@@ -85201,18 +85205,18 @@
       </c>
       <c r="G1688" t="inlineStr">
         <is>
-          <t>Rogerio Egidio</t>
+          <t>Rodrigo Rego</t>
         </is>
       </c>
       <c r="H1688" t="inlineStr"/>
       <c r="I1688" t="n">
-        <v>53</v>
+        <v>2</v>
       </c>
       <c r="J1688" t="n">
-        <v>53</v>
+        <v>2</v>
       </c>
       <c r="K1688" t="n">
-        <v>385</v>
+        <v>460</v>
       </c>
     </row>
     <row r="1689">
@@ -85248,18 +85252,18 @@
       </c>
       <c r="G1689" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Rogerio Egidio</t>
         </is>
       </c>
       <c r="H1689" t="inlineStr"/>
       <c r="I1689" t="n">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="J1689" t="n">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="K1689" t="n">
-        <v>50</v>
+        <v>384</v>
       </c>
     </row>
     <row r="1690">
@@ -85295,18 +85299,18 @@
       </c>
       <c r="G1690" t="inlineStr">
         <is>
-          <t>Simone Marques</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="H1690" t="inlineStr"/>
       <c r="I1690" t="n">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="J1690" t="n">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="K1690" t="n">
-        <v>229</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1691">
@@ -85342,18 +85346,18 @@
       </c>
       <c r="G1691" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Simone Marques</t>
         </is>
       </c>
       <c r="H1691" t="inlineStr"/>
       <c r="I1691" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="J1691" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="K1691" t="n">
-        <v>267</v>
+        <v>229</v>
       </c>
     </row>
     <row r="1692">
@@ -85384,12 +85388,12 @@
       </c>
       <c r="F1692" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="G1692" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="H1692" t="inlineStr"/>
@@ -85400,7 +85404,7 @@
         <v>0</v>
       </c>
       <c r="K1692" t="n">
-        <v>1</v>
+        <v>267</v>
       </c>
     </row>
     <row r="1693">
@@ -85436,18 +85440,18 @@
       </c>
       <c r="G1693" t="inlineStr">
         <is>
-          <t>Jurema Damacena - SAC</t>
+          <t>Edimir Santos</t>
         </is>
       </c>
       <c r="H1693" t="inlineStr"/>
       <c r="I1693" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J1693" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K1693" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1694">
@@ -85478,23 +85482,23 @@
       </c>
       <c r="F1694" t="inlineStr">
         <is>
-          <t>MG CONTABIFÁCIL - CTB</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="G1694" t="inlineStr">
         <is>
-          <t>Guilherme Delecrodio</t>
+          <t>Jurema Damacena - SAC</t>
         </is>
       </c>
       <c r="H1694" t="inlineStr"/>
       <c r="I1694" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J1694" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K1694" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1695">
@@ -85525,19 +85529,23 @@
       </c>
       <c r="F1695" t="inlineStr">
         <is>
-          <t>MG EXPRESS - CTB</t>
-        </is>
-      </c>
-      <c r="G1695" t="inlineStr"/>
+          <t>MG CONTABIFÁCIL - CTB</t>
+        </is>
+      </c>
+      <c r="G1695" t="inlineStr">
+        <is>
+          <t>Guilherme Delecrodio</t>
+        </is>
+      </c>
       <c r="H1695" t="inlineStr"/>
       <c r="I1695" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J1695" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K1695" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1696">
@@ -85571,20 +85579,16 @@
           <t>MG EXPRESS - CTB</t>
         </is>
       </c>
-      <c r="G1696" t="inlineStr">
-        <is>
-          <t>Guilherme Delecrodio</t>
-        </is>
-      </c>
+      <c r="G1696" t="inlineStr"/>
       <c r="H1696" t="inlineStr"/>
       <c r="I1696" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J1696" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K1696" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1697">
@@ -85615,12 +85619,12 @@
       </c>
       <c r="F1697" t="inlineStr">
         <is>
-          <t>S.A.C</t>
+          <t>MG EXPRESS - CTB</t>
         </is>
       </c>
       <c r="G1697" t="inlineStr">
         <is>
-          <t>Ana Celia - SAC</t>
+          <t>Guilherme Delecrodio</t>
         </is>
       </c>
       <c r="H1697" t="inlineStr"/>
@@ -85631,7 +85635,7 @@
         <v>0</v>
       </c>
       <c r="K1697" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1698">
@@ -85662,19 +85666,15 @@
       </c>
       <c r="F1698" t="inlineStr">
         <is>
-          <t>SANTOS - DP</t>
+          <t>S.A.C</t>
         </is>
       </c>
       <c r="G1698" t="inlineStr">
         <is>
-          <t>Katia Valeria</t>
-        </is>
-      </c>
-      <c r="H1698" t="inlineStr">
-        <is>
-          <t>Katia Valeria</t>
-        </is>
-      </c>
+          <t>Ana Celia - SAC</t>
+        </is>
+      </c>
+      <c r="H1698" t="inlineStr"/>
       <c r="I1698" t="n">
         <v>0</v>
       </c>
@@ -85682,7 +85682,7 @@
         <v>0</v>
       </c>
       <c r="K1698" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1699">
@@ -85708,28 +85708,28 @@
       </c>
       <c r="E1699" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F1699" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>S.A.C</t>
         </is>
       </c>
       <c r="G1699" t="inlineStr">
         <is>
-          <t>Jurema Damacena - SAC</t>
+          <t>Sarah Amaro</t>
         </is>
       </c>
       <c r="H1699" t="inlineStr"/>
       <c r="I1699" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J1699" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K1699" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1700">
@@ -85755,28 +85755,32 @@
       </c>
       <c r="E1700" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F1700" t="inlineStr">
         <is>
-          <t>SANTOS - ADM</t>
+          <t>SANTOS - DP</t>
         </is>
       </c>
       <c r="G1700" t="inlineStr">
         <is>
-          <t>Kauany Pereira</t>
-        </is>
-      </c>
-      <c r="H1700" t="inlineStr"/>
+          <t>Katia Valeria</t>
+        </is>
+      </c>
+      <c r="H1700" t="inlineStr">
+        <is>
+          <t>Katia Valeria</t>
+        </is>
+      </c>
       <c r="I1700" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="J1700" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="K1700" t="n">
-        <v>233</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1701">
@@ -85807,27 +85811,23 @@
       </c>
       <c r="F1701" t="inlineStr">
         <is>
-          <t>SANTOS - CTB</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="G1701" t="inlineStr">
         <is>
-          <t>Ivia Oliveira</t>
-        </is>
-      </c>
-      <c r="H1701" t="inlineStr">
-        <is>
-          <t>Roberto Silva</t>
-        </is>
-      </c>
+          <t>Jurema Damacena - SAC</t>
+        </is>
+      </c>
+      <c r="H1701" t="inlineStr"/>
       <c r="I1701" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1701" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1701" t="n">
-        <v>57</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1702">
@@ -85858,27 +85858,23 @@
       </c>
       <c r="F1702" t="inlineStr">
         <is>
-          <t>SANTOS - CTB</t>
+          <t>SANTOS - ADM</t>
         </is>
       </c>
       <c r="G1702" t="inlineStr">
         <is>
-          <t>Nata Trindade</t>
-        </is>
-      </c>
-      <c r="H1702" t="inlineStr">
-        <is>
-          <t>Roberto Silva</t>
-        </is>
-      </c>
+          <t>Kauany Pereira</t>
+        </is>
+      </c>
+      <c r="H1702" t="inlineStr"/>
       <c r="I1702" t="n">
-        <v>4</v>
+        <v>95</v>
       </c>
       <c r="J1702" t="n">
-        <v>4</v>
+        <v>95</v>
       </c>
       <c r="K1702" t="n">
-        <v>86</v>
+        <v>233</v>
       </c>
     </row>
     <row r="1703">
@@ -85914,22 +85910,22 @@
       </c>
       <c r="G1703" t="inlineStr">
         <is>
+          <t>Ivia Oliveira</t>
+        </is>
+      </c>
+      <c r="H1703" t="inlineStr">
+        <is>
           <t>Roberto Silva</t>
         </is>
       </c>
-      <c r="H1703" t="inlineStr">
-        <is>
-          <t>Roberto Silva</t>
-        </is>
-      </c>
       <c r="I1703" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J1703" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K1703" t="n">
-        <v>113</v>
+        <v>57</v>
       </c>
     </row>
     <row r="1704">
@@ -85965,7 +85961,7 @@
       </c>
       <c r="G1704" t="inlineStr">
         <is>
-          <t>Thaina Rodrigues</t>
+          <t>Nata Trindade</t>
         </is>
       </c>
       <c r="H1704" t="inlineStr">
@@ -85974,13 +85970,13 @@
         </is>
       </c>
       <c r="I1704" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J1704" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K1704" t="n">
-        <v>94</v>
+        <v>86</v>
       </c>
     </row>
     <row r="1705">
@@ -86011,27 +86007,27 @@
       </c>
       <c r="F1705" t="inlineStr">
         <is>
-          <t>SANTOS - DP</t>
+          <t>SANTOS - CTB</t>
         </is>
       </c>
       <c r="G1705" t="inlineStr">
         <is>
-          <t>Bruna Silva</t>
+          <t>Roberto Silva</t>
         </is>
       </c>
       <c r="H1705" t="inlineStr">
         <is>
-          <t>Katia Valeria</t>
+          <t>Roberto Silva</t>
         </is>
       </c>
       <c r="I1705" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J1705" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="K1705" t="n">
-        <v>14</v>
+        <v>113</v>
       </c>
     </row>
     <row r="1706">
@@ -86062,27 +86058,27 @@
       </c>
       <c r="F1706" t="inlineStr">
         <is>
-          <t>SANTOS - DP</t>
+          <t>SANTOS - CTB</t>
         </is>
       </c>
       <c r="G1706" t="inlineStr">
         <is>
-          <t>Carliane Silva</t>
+          <t>Thaina Rodrigues</t>
         </is>
       </c>
       <c r="H1706" t="inlineStr">
         <is>
-          <t>Katia Valeria</t>
+          <t>Roberto Silva</t>
         </is>
       </c>
       <c r="I1706" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="J1706" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K1706" t="n">
-        <v>316</v>
+        <v>94</v>
       </c>
     </row>
     <row r="1707">
@@ -86118,7 +86114,7 @@
       </c>
       <c r="G1707" t="inlineStr">
         <is>
-          <t>Cintia Andrade</t>
+          <t>Bruna Silva</t>
         </is>
       </c>
       <c r="H1707" t="inlineStr">
@@ -86127,13 +86123,13 @@
         </is>
       </c>
       <c r="I1707" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J1707" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="K1707" t="n">
-        <v>227</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1708">
@@ -86169,22 +86165,22 @@
       </c>
       <c r="G1708" t="inlineStr">
         <is>
+          <t>Carliane Silva</t>
+        </is>
+      </c>
+      <c r="H1708" t="inlineStr">
+        <is>
           <t>Katia Valeria</t>
         </is>
       </c>
-      <c r="H1708" t="inlineStr">
-        <is>
-          <t>Katia Valeria</t>
-        </is>
-      </c>
       <c r="I1708" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="J1708" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="K1708" t="n">
-        <v>371</v>
+        <v>316</v>
       </c>
     </row>
     <row r="1709">
@@ -86220,18 +86216,22 @@
       </c>
       <c r="G1709" t="inlineStr">
         <is>
-          <t>Patricia Melo</t>
-        </is>
-      </c>
-      <c r="H1709" t="inlineStr"/>
+          <t>Cintia Andrade</t>
+        </is>
+      </c>
+      <c r="H1709" t="inlineStr">
+        <is>
+          <t>Katia Valeria</t>
+        </is>
+      </c>
       <c r="I1709" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="J1709" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="K1709" t="n">
-        <v>0</v>
+        <v>227</v>
       </c>
     </row>
     <row r="1710">
@@ -86262,27 +86262,27 @@
       </c>
       <c r="F1710" t="inlineStr">
         <is>
-          <t>SANTOS - EF</t>
+          <t>SANTOS - DP</t>
         </is>
       </c>
       <c r="G1710" t="inlineStr">
         <is>
-          <t>Jasmina Melo</t>
+          <t>Katia Valeria</t>
         </is>
       </c>
       <c r="H1710" t="inlineStr">
         <is>
-          <t>Lidia Tavares</t>
+          <t>Katia Valeria</t>
         </is>
       </c>
       <c r="I1710" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="J1710" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="K1710" t="n">
-        <v>98</v>
+        <v>371</v>
       </c>
     </row>
     <row r="1711">
@@ -86313,27 +86313,23 @@
       </c>
       <c r="F1711" t="inlineStr">
         <is>
-          <t>SANTOS - EF</t>
+          <t>SANTOS - DP</t>
         </is>
       </c>
       <c r="G1711" t="inlineStr">
         <is>
-          <t>Karen Saadi</t>
-        </is>
-      </c>
-      <c r="H1711" t="inlineStr">
-        <is>
-          <t>Lidia Tavares</t>
-        </is>
-      </c>
+          <t>Patricia Melo</t>
+        </is>
+      </c>
+      <c r="H1711" t="inlineStr"/>
       <c r="I1711" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J1711" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K1711" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1712">
@@ -86369,7 +86365,7 @@
       </c>
       <c r="G1712" t="inlineStr">
         <is>
-          <t>Luckas Andrade</t>
+          <t>Jasmina Melo</t>
         </is>
       </c>
       <c r="H1712" t="inlineStr">
@@ -86378,13 +86374,13 @@
         </is>
       </c>
       <c r="I1712" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="J1712" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="K1712" t="n">
-        <v>109</v>
+        <v>99</v>
       </c>
     </row>
     <row r="1713">
@@ -86420,7 +86416,7 @@
       </c>
       <c r="G1713" t="inlineStr">
         <is>
-          <t>Mirian Rodrigues</t>
+          <t>Karen Saadi</t>
         </is>
       </c>
       <c r="H1713" t="inlineStr">
@@ -86435,7 +86431,7 @@
         <v>5</v>
       </c>
       <c r="K1713" t="n">
-        <v>117</v>
+        <v>79</v>
       </c>
     </row>
     <row r="1714">
@@ -86466,22 +86462,124 @@
       </c>
       <c r="F1714" t="inlineStr">
         <is>
+          <t>SANTOS - EF</t>
+        </is>
+      </c>
+      <c r="G1714" t="inlineStr">
+        <is>
+          <t>Luckas Andrade</t>
+        </is>
+      </c>
+      <c r="H1714" t="inlineStr">
+        <is>
+          <t>Lidia Tavares</t>
+        </is>
+      </c>
+      <c r="I1714" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1714" t="n">
+        <v>3</v>
+      </c>
+      <c r="K1714" t="n">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="1715">
+      <c r="A1715" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B1715" t="inlineStr">
+        <is>
+          <t>Segunda</t>
+        </is>
+      </c>
+      <c r="C1715" t="inlineStr">
+        <is>
+          <t>2026-W25</t>
+        </is>
+      </c>
+      <c r="D1715" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1715" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="F1715" t="inlineStr">
+        <is>
+          <t>SANTOS - EF</t>
+        </is>
+      </c>
+      <c r="G1715" t="inlineStr">
+        <is>
+          <t>Mirian Rodrigues</t>
+        </is>
+      </c>
+      <c r="H1715" t="inlineStr">
+        <is>
+          <t>Lidia Tavares</t>
+        </is>
+      </c>
+      <c r="I1715" t="n">
+        <v>5</v>
+      </c>
+      <c r="J1715" t="n">
+        <v>5</v>
+      </c>
+      <c r="K1715" t="n">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="1716">
+      <c r="A1716" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B1716" t="inlineStr">
+        <is>
+          <t>Segunda</t>
+        </is>
+      </c>
+      <c r="C1716" t="inlineStr">
+        <is>
+          <t>2026-W25</t>
+        </is>
+      </c>
+      <c r="D1716" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E1716" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="F1716" t="inlineStr">
+        <is>
           <t>SANTOS - GC</t>
         </is>
       </c>
-      <c r="G1714" t="inlineStr">
+      <c r="G1716" t="inlineStr">
         <is>
           <t>Rafaella Massuia</t>
         </is>
       </c>
-      <c r="H1714" t="inlineStr"/>
-      <c r="I1714" t="n">
+      <c r="H1716" t="inlineStr"/>
+      <c r="I1716" t="n">
         <v>13</v>
       </c>
-      <c r="J1714" t="n">
+      <c r="J1716" t="n">
         <v>13</v>
       </c>
-      <c r="K1714" t="n">
+      <c r="K1716" t="n">
         <v>109</v>
       </c>
     </row>

--- a/data/historico/historico_baixas.xlsx
+++ b/data/historico/historico_baixas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2016"/>
+  <dimension ref="A1:K2015"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -86778,13 +86778,13 @@
         </is>
       </c>
       <c r="I1720" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1720" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1720" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1721">
@@ -86829,13 +86829,13 @@
         </is>
       </c>
       <c r="I1721" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1721" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K1721" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1722">
@@ -87033,13 +87033,13 @@
         </is>
       </c>
       <c r="I1725" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1725" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K1725" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1726">
@@ -87386,13 +87386,13 @@
         </is>
       </c>
       <c r="I1732" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J1732" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K1732" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1733">
@@ -87637,13 +87637,13 @@
         </is>
       </c>
       <c r="I1737" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1737" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1737" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1738">
@@ -87688,13 +87688,13 @@
         </is>
       </c>
       <c r="I1738" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J1738" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K1738" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="1739">
@@ -88068,13 +88068,13 @@
         </is>
       </c>
       <c r="I1746" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J1746" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="K1746" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
     </row>
     <row r="1747">
@@ -88170,13 +88170,13 @@
         </is>
       </c>
       <c r="I1748" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J1748" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="K1748" t="n">
-        <v>76</v>
+        <v>89</v>
       </c>
     </row>
     <row r="1749">
@@ -88323,13 +88323,13 @@
         </is>
       </c>
       <c r="I1751" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1751" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K1751" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1752">
@@ -88374,13 +88374,13 @@
         </is>
       </c>
       <c r="I1752" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J1752" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K1752" t="n">
-        <v>83</v>
+        <v>93</v>
       </c>
     </row>
     <row r="1753">
@@ -88578,13 +88578,13 @@
         </is>
       </c>
       <c r="I1756" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1756" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K1756" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="1757">
@@ -88629,13 +88629,13 @@
         </is>
       </c>
       <c r="I1757" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J1757" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="K1757" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
     </row>
     <row r="1758">
@@ -88731,13 +88731,13 @@
         </is>
       </c>
       <c r="I1759" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1759" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K1759" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="1760">
@@ -88927,10 +88927,10 @@
         </is>
       </c>
       <c r="I1763" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J1763" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K1763" t="n">
         <v>113</v>
@@ -88978,13 +88978,13 @@
         </is>
       </c>
       <c r="I1764" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1764" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1764" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="1765">
@@ -89029,10 +89029,10 @@
         </is>
       </c>
       <c r="I1765" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1765" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K1765" t="n">
         <v>88</v>
@@ -89080,13 +89080,13 @@
         </is>
       </c>
       <c r="I1766" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1766" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1766" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1767">
@@ -89233,13 +89233,13 @@
         </is>
       </c>
       <c r="I1769" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J1769" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="K1769" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1770">
@@ -89386,13 +89386,13 @@
         </is>
       </c>
       <c r="I1772" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1772" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K1772" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="1773">
@@ -89692,10 +89692,10 @@
         </is>
       </c>
       <c r="I1778" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1778" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1778" t="n">
         <v>181</v>
@@ -89794,10 +89794,10 @@
         </is>
       </c>
       <c r="I1780" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J1780" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K1780" t="n">
         <v>123</v>
@@ -89896,13 +89896,13 @@
         </is>
       </c>
       <c r="I1782" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J1782" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K1782" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="1783">
@@ -89947,13 +89947,13 @@
         </is>
       </c>
       <c r="I1783" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1783" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K1783" t="n">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="1784">
@@ -90049,13 +90049,13 @@
         </is>
       </c>
       <c r="I1785" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1785" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K1785" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="1786">
@@ -90100,13 +90100,13 @@
         </is>
       </c>
       <c r="I1786" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1786" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K1786" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="1787">
@@ -90253,10 +90253,10 @@
         </is>
       </c>
       <c r="I1789" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1789" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K1789" t="n">
         <v>250</v>
@@ -90304,13 +90304,13 @@
         </is>
       </c>
       <c r="I1790" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1790" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K1790" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="1791">
@@ -90406,13 +90406,13 @@
         </is>
       </c>
       <c r="I1792" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J1792" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="K1792" t="n">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="1793">
@@ -90504,7 +90504,7 @@
       </c>
       <c r="H1794" t="inlineStr"/>
       <c r="I1794" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1794" t="n">
         <v>1</v>
@@ -90551,13 +90551,13 @@
       </c>
       <c r="H1795" t="inlineStr"/>
       <c r="I1795" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J1795" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="K1795" t="n">
-        <v>87</v>
+        <v>99</v>
       </c>
     </row>
     <row r="1796">
@@ -90598,13 +90598,13 @@
       </c>
       <c r="H1796" t="inlineStr"/>
       <c r="I1796" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J1796" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K1796" t="n">
-        <v>252</v>
+        <v>257</v>
       </c>
     </row>
     <row r="1797">
@@ -90845,13 +90845,13 @@
         </is>
       </c>
       <c r="I1801" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1801" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K1801" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1802">
@@ -90947,13 +90947,13 @@
         </is>
       </c>
       <c r="I1803" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1803" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K1803" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1804">
@@ -91202,13 +91202,13 @@
         </is>
       </c>
       <c r="I1808" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J1808" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="K1808" t="n">
-        <v>193</v>
+        <v>197</v>
       </c>
     </row>
     <row r="1809">
@@ -91300,13 +91300,13 @@
         </is>
       </c>
       <c r="I1810" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1810" t="n">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="K1810" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="1811">
@@ -91351,13 +91351,13 @@
         </is>
       </c>
       <c r="I1811" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1811" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="K1811" t="n">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="1812">
@@ -91504,13 +91504,13 @@
         </is>
       </c>
       <c r="I1814" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1814" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1814" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="1815">
@@ -91606,13 +91606,13 @@
         </is>
       </c>
       <c r="I1816" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1816" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K1816" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1817">
@@ -91708,13 +91708,13 @@
         </is>
       </c>
       <c r="I1818" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1818" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K1818" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="1819">
@@ -91810,13 +91810,13 @@
         </is>
       </c>
       <c r="I1820" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J1820" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="K1820" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
     </row>
     <row r="1821">
@@ -92112,13 +92112,13 @@
         </is>
       </c>
       <c r="I1826" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1826" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K1826" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="1827">
@@ -92163,13 +92163,13 @@
         </is>
       </c>
       <c r="I1827" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1827" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K1827" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="1828">
@@ -92418,13 +92418,13 @@
         </is>
       </c>
       <c r="I1832" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J1832" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K1832" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="1833">
@@ -92469,13 +92469,13 @@
         </is>
       </c>
       <c r="I1833" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1833" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K1833" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="1834">
@@ -92520,10 +92520,10 @@
         </is>
       </c>
       <c r="I1834" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1834" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K1834" t="n">
         <v>14</v>
@@ -92673,13 +92673,13 @@
         </is>
       </c>
       <c r="I1837" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J1837" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="K1837" t="n">
-        <v>49</v>
+        <v>63</v>
       </c>
     </row>
     <row r="1838">
@@ -92724,13 +92724,13 @@
         </is>
       </c>
       <c r="I1838" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="J1838" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="K1838" t="n">
-        <v>93</v>
+        <v>167</v>
       </c>
     </row>
     <row r="1839">
@@ -92826,13 +92826,13 @@
         </is>
       </c>
       <c r="I1840" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="J1840" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="K1840" t="n">
-        <v>113</v>
+        <v>140</v>
       </c>
     </row>
     <row r="1841">
@@ -92934,7 +92934,7 @@
         <v>0</v>
       </c>
       <c r="K1842" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="1843">
@@ -92979,13 +92979,13 @@
         </is>
       </c>
       <c r="I1843" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J1843" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K1843" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="1844">
@@ -93030,13 +93030,13 @@
         </is>
       </c>
       <c r="I1844" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1844" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K1844" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="1845">
@@ -93132,13 +93132,13 @@
         </is>
       </c>
       <c r="I1846" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1846" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="K1846" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="1847">
@@ -93336,13 +93336,13 @@
         </is>
       </c>
       <c r="I1850" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1850" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K1850" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="1851">
@@ -93387,13 +93387,13 @@
         </is>
       </c>
       <c r="I1851" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1851" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K1851" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="1852">
@@ -93638,13 +93638,13 @@
         </is>
       </c>
       <c r="I1856" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J1856" t="n">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="K1856" t="n">
-        <v>56</v>
+        <v>81</v>
       </c>
     </row>
     <row r="1857">
@@ -93689,13 +93689,13 @@
         </is>
       </c>
       <c r="I1857" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1857" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1857" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1858">
@@ -93740,13 +93740,13 @@
         </is>
       </c>
       <c r="I1858" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="J1858" t="n">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="K1858" t="n">
-        <v>107</v>
+        <v>133</v>
       </c>
     </row>
     <row r="1859">
@@ -93944,13 +93944,13 @@
         </is>
       </c>
       <c r="I1862" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J1862" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K1862" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1863">
@@ -94097,13 +94097,13 @@
         </is>
       </c>
       <c r="I1865" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J1865" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K1865" t="n">
-        <v>129</v>
+        <v>141</v>
       </c>
     </row>
     <row r="1866">
@@ -94199,13 +94199,13 @@
         </is>
       </c>
       <c r="I1867" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1867" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="K1867" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="1868">
@@ -94250,13 +94250,13 @@
         </is>
       </c>
       <c r="I1868" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J1868" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K1868" t="n">
-        <v>178</v>
+        <v>196</v>
       </c>
     </row>
     <row r="1869">
@@ -94301,13 +94301,13 @@
         </is>
       </c>
       <c r="I1869" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J1869" t="n">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="K1869" t="n">
-        <v>84</v>
+        <v>105</v>
       </c>
     </row>
     <row r="1870">
@@ -94505,13 +94505,13 @@
         </is>
       </c>
       <c r="I1873" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="J1873" t="n">
-        <v>12</v>
+        <v>69</v>
       </c>
       <c r="K1873" t="n">
-        <v>143</v>
+        <v>200</v>
       </c>
     </row>
     <row r="1874">
@@ -94562,7 +94562,7 @@
         <v>0</v>
       </c>
       <c r="K1874" t="n">
-        <v>117</v>
+        <v>129</v>
       </c>
     </row>
     <row r="1875">
@@ -94658,13 +94658,13 @@
         </is>
       </c>
       <c r="I1876" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J1876" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="K1876" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="1877">
@@ -94709,13 +94709,13 @@
         </is>
       </c>
       <c r="I1877" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J1877" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K1877" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="1878">
@@ -94760,13 +94760,13 @@
         </is>
       </c>
       <c r="I1878" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1878" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1878" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="1879">
@@ -94913,13 +94913,13 @@
         </is>
       </c>
       <c r="I1881" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J1881" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K1881" t="n">
-        <v>114</v>
+        <v>123</v>
       </c>
     </row>
     <row r="1882">
@@ -94964,13 +94964,13 @@
         </is>
       </c>
       <c r="I1882" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J1882" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="K1882" t="n">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="1883">
@@ -95015,13 +95015,13 @@
         </is>
       </c>
       <c r="I1883" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1883" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K1883" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="1884">
@@ -95168,10 +95168,10 @@
         </is>
       </c>
       <c r="I1886" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J1886" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="K1886" t="n">
         <v>1</v>
@@ -95225,7 +95225,7 @@
         <v>4</v>
       </c>
       <c r="K1887" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1888">
@@ -95276,7 +95276,7 @@
         <v>46</v>
       </c>
       <c r="K1888" t="n">
-        <v>164</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1889">
@@ -95368,10 +95368,10 @@
       </c>
       <c r="H1890" t="inlineStr"/>
       <c r="I1890" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1890" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K1890" t="n">
         <v>7</v>
@@ -95470,13 +95470,13 @@
         </is>
       </c>
       <c r="I1892" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J1892" t="n">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="K1892" t="n">
-        <v>131</v>
+        <v>147</v>
       </c>
     </row>
     <row r="1893">
@@ -95572,13 +95572,13 @@
         </is>
       </c>
       <c r="I1894" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J1894" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="K1894" t="n">
-        <v>173</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1895">
@@ -95623,13 +95623,13 @@
         </is>
       </c>
       <c r="I1895" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J1895" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="K1895" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="1896">
@@ -95725,13 +95725,13 @@
         </is>
       </c>
       <c r="I1897" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J1897" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="K1897" t="n">
-        <v>152</v>
+        <v>162</v>
       </c>
     </row>
     <row r="1898">
@@ -95776,7 +95776,7 @@
         </is>
       </c>
       <c r="I1898" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1898" t="n">
         <v>1</v>
@@ -95827,13 +95827,13 @@
         </is>
       </c>
       <c r="I1899" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="J1899" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="K1899" t="n">
-        <v>148</v>
+        <v>194</v>
       </c>
     </row>
     <row r="1900">
@@ -95929,13 +95929,13 @@
         </is>
       </c>
       <c r="I1901" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="J1901" t="n">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="K1901" t="n">
-        <v>136</v>
+        <v>159</v>
       </c>
     </row>
     <row r="1902">
@@ -95980,10 +95980,10 @@
         </is>
       </c>
       <c r="I1902" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1902" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K1902" t="n">
         <v>125</v>
@@ -96031,13 +96031,13 @@
         </is>
       </c>
       <c r="I1903" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J1903" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K1903" t="n">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1904">
@@ -96082,13 +96082,13 @@
         </is>
       </c>
       <c r="I1904" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1904" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K1904" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="1905">
@@ -96184,13 +96184,13 @@
         </is>
       </c>
       <c r="I1906" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1906" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K1906" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="1907">
@@ -96234,10 +96234,10 @@
         <v>0</v>
       </c>
       <c r="J1907" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K1907" t="n">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="1908">
@@ -96333,13 +96333,13 @@
         </is>
       </c>
       <c r="I1909" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1909" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K1909" t="n">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="1910">
@@ -96384,13 +96384,13 @@
         </is>
       </c>
       <c r="I1910" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="J1910" t="n">
-        <v>140</v>
+        <v>187</v>
       </c>
       <c r="K1910" t="n">
-        <v>768</v>
+        <v>815</v>
       </c>
     </row>
     <row r="1911">
@@ -96435,13 +96435,13 @@
         </is>
       </c>
       <c r="I1911" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1911" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K1911" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="1912">
@@ -96486,13 +96486,13 @@
         </is>
       </c>
       <c r="I1912" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1912" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K1912" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="1913">
@@ -96690,13 +96690,13 @@
         </is>
       </c>
       <c r="I1916" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J1916" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K1916" t="n">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="1917">
@@ -96741,13 +96741,13 @@
         </is>
       </c>
       <c r="I1917" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1917" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K1917" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="1918">
@@ -96843,10 +96843,10 @@
         </is>
       </c>
       <c r="I1919" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1919" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1919" t="n">
         <v>71</v>
@@ -96894,13 +96894,13 @@
         </is>
       </c>
       <c r="I1920" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1920" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1920" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="1921">
@@ -96996,13 +96996,13 @@
         </is>
       </c>
       <c r="I1922" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J1922" t="n">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="K1922" t="n">
-        <v>214</v>
+        <v>226</v>
       </c>
     </row>
     <row r="1923">
@@ -97047,13 +97047,13 @@
         </is>
       </c>
       <c r="I1923" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J1923" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="K1923" t="n">
-        <v>127</v>
+        <v>139</v>
       </c>
     </row>
     <row r="1924">
@@ -97149,13 +97149,13 @@
         </is>
       </c>
       <c r="I1925" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1925" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K1925" t="n">
-        <v>197</v>
+        <v>200</v>
       </c>
     </row>
     <row r="1926">
@@ -97206,7 +97206,7 @@
         <v>24</v>
       </c>
       <c r="K1926" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="1927">
@@ -97302,13 +97302,13 @@
         </is>
       </c>
       <c r="I1928" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J1928" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="K1928" t="n">
-        <v>164</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1929">
@@ -97349,13 +97349,13 @@
       </c>
       <c r="H1929" t="inlineStr"/>
       <c r="I1929" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1929" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1929" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="1930">
@@ -97400,13 +97400,13 @@
         </is>
       </c>
       <c r="I1930" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J1930" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="K1930" t="n">
-        <v>172</v>
+        <v>182</v>
       </c>
     </row>
     <row r="1931">
@@ -97451,13 +97451,13 @@
         </is>
       </c>
       <c r="I1931" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J1931" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="K1931" t="n">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="1932">
@@ -97502,13 +97502,13 @@
         </is>
       </c>
       <c r="I1932" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J1932" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K1932" t="n">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1933">
@@ -97604,13 +97604,13 @@
         </is>
       </c>
       <c r="I1934" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J1934" t="n">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="K1934" t="n">
-        <v>78</v>
+        <v>102</v>
       </c>
     </row>
     <row r="1935">
@@ -97655,13 +97655,13 @@
         </is>
       </c>
       <c r="I1935" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1935" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K1935" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="1936">
@@ -97808,13 +97808,13 @@
         </is>
       </c>
       <c r="I1938" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J1938" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="K1938" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1939">
@@ -97961,13 +97961,13 @@
         </is>
       </c>
       <c r="I1941" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J1941" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="K1941" t="n">
-        <v>154</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1942">
@@ -98063,13 +98063,13 @@
         </is>
       </c>
       <c r="I1943" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1943" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K1943" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="1944">
@@ -98114,13 +98114,13 @@
         </is>
       </c>
       <c r="I1944" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1944" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K1944" t="n">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="1945">
@@ -98165,13 +98165,13 @@
         </is>
       </c>
       <c r="I1945" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="J1945" t="n">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="K1945" t="n">
-        <v>317</v>
+        <v>343</v>
       </c>
     </row>
     <row r="1946">
@@ -98216,13 +98216,13 @@
         </is>
       </c>
       <c r="I1946" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1946" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K1946" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="1947">
@@ -98318,13 +98318,13 @@
         </is>
       </c>
       <c r="I1948" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J1948" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="K1948" t="n">
-        <v>143</v>
+        <v>155</v>
       </c>
     </row>
     <row r="1949">
@@ -98369,13 +98369,13 @@
         </is>
       </c>
       <c r="I1949" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J1949" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="K1949" t="n">
-        <v>119</v>
+        <v>127</v>
       </c>
     </row>
     <row r="1950">
@@ -98471,13 +98471,13 @@
         </is>
       </c>
       <c r="I1951" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1951" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K1951" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="1952">
@@ -98573,13 +98573,13 @@
         </is>
       </c>
       <c r="I1953" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1953" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K1953" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="1954">
@@ -98624,13 +98624,13 @@
         </is>
       </c>
       <c r="I1954" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J1954" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="K1954" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1955">
@@ -98675,13 +98675,13 @@
         </is>
       </c>
       <c r="I1955" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J1955" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="K1955" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="1956">
@@ -99275,10 +99275,10 @@
       </c>
       <c r="H1967" t="inlineStr"/>
       <c r="I1967" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="J1967" t="n">
-        <v>45</v>
+        <v>150</v>
       </c>
       <c r="K1967" t="n">
         <v>588</v>
@@ -99375,7 +99375,7 @@
         <v>5</v>
       </c>
       <c r="K1969" t="n">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="1970">
@@ -99604,13 +99604,13 @@
       </c>
       <c r="H1974" t="inlineStr"/>
       <c r="I1974" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1974" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K1974" t="n">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="1975">
@@ -99651,10 +99651,10 @@
       </c>
       <c r="H1975" t="inlineStr"/>
       <c r="I1975" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1975" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1975" t="n">
         <v>13</v>
@@ -99745,13 +99745,13 @@
       </c>
       <c r="H1977" t="inlineStr"/>
       <c r="I1977" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="J1977" t="n">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="K1977" t="n">
-        <v>554</v>
+        <v>558</v>
       </c>
     </row>
     <row r="1978">
@@ -99839,10 +99839,10 @@
       </c>
       <c r="H1979" t="inlineStr"/>
       <c r="I1979" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="J1979" t="n">
-        <v>5</v>
+        <v>107</v>
       </c>
       <c r="K1979" t="n">
         <v>375</v>
@@ -99939,7 +99939,7 @@
         <v>5</v>
       </c>
       <c r="K1981" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="1982">
@@ -99980,10 +99980,10 @@
       </c>
       <c r="H1982" t="inlineStr"/>
       <c r="I1982" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J1982" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K1982" t="n">
         <v>401</v>
@@ -100027,13 +100027,13 @@
       </c>
       <c r="H1983" t="inlineStr"/>
       <c r="I1983" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J1983" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="K1983" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="1984">
@@ -100215,10 +100215,10 @@
       </c>
       <c r="H1987" t="inlineStr"/>
       <c r="I1987" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J1987" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1987" t="n">
         <v>221</v>
@@ -100262,13 +100262,13 @@
       </c>
       <c r="H1988" t="inlineStr"/>
       <c r="I1988" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1988" t="n">
         <v>65</v>
       </c>
       <c r="K1988" t="n">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="1989">
@@ -100309,13 +100309,13 @@
       </c>
       <c r="H1989" t="inlineStr"/>
       <c r="I1989" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="J1989" t="n">
-        <v>46</v>
+        <v>82</v>
       </c>
       <c r="K1989" t="n">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="1990">
@@ -100356,10 +100356,10 @@
       </c>
       <c r="H1990" t="inlineStr"/>
       <c r="I1990" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1990" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1990" t="n">
         <v>50</v>
@@ -100403,13 +100403,13 @@
       </c>
       <c r="H1991" t="inlineStr"/>
       <c r="I1991" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1991" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="K1991" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="1992">
@@ -100492,18 +100492,18 @@
       </c>
       <c r="G1993" t="inlineStr">
         <is>
-          <t>Edimir Santos</t>
+          <t>Jurema Damacena - SAC</t>
         </is>
       </c>
       <c r="H1993" t="inlineStr"/>
       <c r="I1993" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J1993" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K1993" t="n">
-        <v>1</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1994">
@@ -100534,12 +100534,12 @@
       </c>
       <c r="F1994" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>MG CONTABIFÁCIL - CTB</t>
         </is>
       </c>
       <c r="G1994" t="inlineStr">
         <is>
-          <t>Jurema Damacena - SAC</t>
+          <t>Guilherme Delecrodio</t>
         </is>
       </c>
       <c r="H1994" t="inlineStr"/>
@@ -100547,10 +100547,10 @@
         <v>0</v>
       </c>
       <c r="J1994" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K1994" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1995">
@@ -100581,23 +100581,19 @@
       </c>
       <c r="F1995" t="inlineStr">
         <is>
-          <t>MG CONTABIFÁCIL - CTB</t>
-        </is>
-      </c>
-      <c r="G1995" t="inlineStr">
-        <is>
-          <t>Guilherme Delecrodio</t>
-        </is>
-      </c>
+          <t>MG EXPRESS - CTB</t>
+        </is>
+      </c>
+      <c r="G1995" t="inlineStr"/>
       <c r="H1995" t="inlineStr"/>
       <c r="I1995" t="n">
         <v>0</v>
       </c>
       <c r="J1995" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K1995" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1996">
@@ -100631,16 +100627,20 @@
           <t>MG EXPRESS - CTB</t>
         </is>
       </c>
-      <c r="G1996" t="inlineStr"/>
+      <c r="G1996" t="inlineStr">
+        <is>
+          <t>Guilherme Delecrodio</t>
+        </is>
+      </c>
       <c r="H1996" t="inlineStr"/>
       <c r="I1996" t="n">
         <v>0</v>
       </c>
       <c r="J1996" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1996" t="n">
         <v>5</v>
-      </c>
-      <c r="K1996" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="1997">
@@ -100671,23 +100671,23 @@
       </c>
       <c r="F1997" t="inlineStr">
         <is>
-          <t>MG EXPRESS - CTB</t>
+          <t>S.A.C</t>
         </is>
       </c>
       <c r="G1997" t="inlineStr">
         <is>
-          <t>Guilherme Delecrodio</t>
+          <t>Ana Celia - SAC</t>
         </is>
       </c>
       <c r="H1997" t="inlineStr"/>
       <c r="I1997" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1997" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1997" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1998">
@@ -100723,7 +100723,7 @@
       </c>
       <c r="G1998" t="inlineStr">
         <is>
-          <t>Ana Celia - SAC</t>
+          <t>Sarah Amaro</t>
         </is>
       </c>
       <c r="H1998" t="inlineStr"/>
@@ -100731,10 +100731,10 @@
         <v>0</v>
       </c>
       <c r="J1998" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1998" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1999">
@@ -100765,23 +100765,27 @@
       </c>
       <c r="F1999" t="inlineStr">
         <is>
-          <t>S.A.C</t>
+          <t>SANTOS - DP</t>
         </is>
       </c>
       <c r="G1999" t="inlineStr">
         <is>
-          <t>Sarah Amaro</t>
-        </is>
-      </c>
-      <c r="H1999" t="inlineStr"/>
+          <t>Katia Valeria</t>
+        </is>
+      </c>
+      <c r="H1999" t="inlineStr">
+        <is>
+          <t>Katia Valeria</t>
+        </is>
+      </c>
       <c r="I1999" t="n">
         <v>0</v>
       </c>
       <c r="J1999" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1999" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2000">
@@ -100807,32 +100811,28 @@
       </c>
       <c r="E2000" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F2000" t="inlineStr">
         <is>
-          <t>SANTOS - DP</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="G2000" t="inlineStr">
         <is>
-          <t>Katia Valeria</t>
-        </is>
-      </c>
-      <c r="H2000" t="inlineStr">
-        <is>
-          <t>Katia Valeria</t>
-        </is>
-      </c>
+          <t>Jurema Damacena - SAC</t>
+        </is>
+      </c>
+      <c r="H2000" t="inlineStr"/>
       <c r="I2000" t="n">
         <v>0</v>
       </c>
       <c r="J2000" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K2000" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2001">
@@ -100863,12 +100863,12 @@
       </c>
       <c r="F2001" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>SANTOS - ADM</t>
         </is>
       </c>
       <c r="G2001" t="inlineStr">
         <is>
-          <t>Jurema Damacena - SAC</t>
+          <t>Kauany Pereira</t>
         </is>
       </c>
       <c r="H2001" t="inlineStr"/>
@@ -100876,10 +100876,10 @@
         <v>0</v>
       </c>
       <c r="J2001" t="n">
-        <v>2</v>
+        <v>95</v>
       </c>
       <c r="K2001" t="n">
-        <v>7</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2002">
@@ -100910,23 +100910,27 @@
       </c>
       <c r="F2002" t="inlineStr">
         <is>
-          <t>SANTOS - ADM</t>
+          <t>SANTOS - CTB</t>
         </is>
       </c>
       <c r="G2002" t="inlineStr">
         <is>
-          <t>Kauany Pereira</t>
-        </is>
-      </c>
-      <c r="H2002" t="inlineStr"/>
+          <t>Ivia Oliveira</t>
+        </is>
+      </c>
+      <c r="H2002" t="inlineStr">
+        <is>
+          <t>Roberto Silva</t>
+        </is>
+      </c>
       <c r="I2002" t="n">
         <v>0</v>
       </c>
       <c r="J2002" t="n">
-        <v>95</v>
+        <v>6</v>
       </c>
       <c r="K2002" t="n">
-        <v>233</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2003">
@@ -100962,7 +100966,7 @@
       </c>
       <c r="G2003" t="inlineStr">
         <is>
-          <t>Ivia Oliveira</t>
+          <t>Nata Trindade</t>
         </is>
       </c>
       <c r="H2003" t="inlineStr">
@@ -100974,10 +100978,10 @@
         <v>0</v>
       </c>
       <c r="J2003" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K2003" t="n">
-        <v>63</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2004">
@@ -101013,7 +101017,7 @@
       </c>
       <c r="G2004" t="inlineStr">
         <is>
-          <t>Nata Trindade</t>
+          <t>Roberto Silva</t>
         </is>
       </c>
       <c r="H2004" t="inlineStr">
@@ -101025,10 +101029,10 @@
         <v>0</v>
       </c>
       <c r="J2004" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K2004" t="n">
-        <v>90</v>
+        <v>118</v>
       </c>
     </row>
     <row r="2005">
@@ -101064,22 +101068,22 @@
       </c>
       <c r="G2005" t="inlineStr">
         <is>
+          <t>Thaina Rodrigues</t>
+        </is>
+      </c>
+      <c r="H2005" t="inlineStr">
+        <is>
           <t>Roberto Silva</t>
         </is>
       </c>
-      <c r="H2005" t="inlineStr">
-        <is>
-          <t>Roberto Silva</t>
-        </is>
-      </c>
       <c r="I2005" t="n">
         <v>0</v>
       </c>
       <c r="J2005" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K2005" t="n">
-        <v>118</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2006">
@@ -101110,27 +101114,27 @@
       </c>
       <c r="F2006" t="inlineStr">
         <is>
-          <t>SANTOS - CTB</t>
+          <t>SANTOS - DP</t>
         </is>
       </c>
       <c r="G2006" t="inlineStr">
         <is>
-          <t>Thaina Rodrigues</t>
+          <t>Bruna Silva</t>
         </is>
       </c>
       <c r="H2006" t="inlineStr">
         <is>
-          <t>Roberto Silva</t>
+          <t>Katia Valeria</t>
         </is>
       </c>
       <c r="I2006" t="n">
         <v>0</v>
       </c>
       <c r="J2006" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="K2006" t="n">
-        <v>97</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2007">
@@ -101166,7 +101170,7 @@
       </c>
       <c r="G2007" t="inlineStr">
         <is>
-          <t>Bruna Silva</t>
+          <t>Carliane Silva</t>
         </is>
       </c>
       <c r="H2007" t="inlineStr">
@@ -101175,13 +101179,13 @@
         </is>
       </c>
       <c r="I2007" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J2007" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="K2007" t="n">
-        <v>14</v>
+        <v>316</v>
       </c>
     </row>
     <row r="2008">
@@ -101217,7 +101221,7 @@
       </c>
       <c r="G2008" t="inlineStr">
         <is>
-          <t>Carliane Silva</t>
+          <t>Cintia Andrade</t>
         </is>
       </c>
       <c r="H2008" t="inlineStr">
@@ -101226,13 +101230,13 @@
         </is>
       </c>
       <c r="I2008" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J2008" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="K2008" t="n">
-        <v>316</v>
+        <v>228</v>
       </c>
     </row>
     <row r="2009">
@@ -101268,7 +101272,7 @@
       </c>
       <c r="G2009" t="inlineStr">
         <is>
-          <t>Cintia Andrade</t>
+          <t>Katia Valeria</t>
         </is>
       </c>
       <c r="H2009" t="inlineStr">
@@ -101280,10 +101284,10 @@
         <v>0</v>
       </c>
       <c r="J2009" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="K2009" t="n">
-        <v>227</v>
+        <v>373</v>
       </c>
     </row>
     <row r="2010">
@@ -101319,22 +101323,18 @@
       </c>
       <c r="G2010" t="inlineStr">
         <is>
-          <t>Katia Valeria</t>
-        </is>
-      </c>
-      <c r="H2010" t="inlineStr">
-        <is>
-          <t>Katia Valeria</t>
-        </is>
-      </c>
+          <t>Patricia Melo</t>
+        </is>
+      </c>
+      <c r="H2010" t="inlineStr"/>
       <c r="I2010" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J2010" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="K2010" t="n">
-        <v>368</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2011">
@@ -101365,23 +101365,27 @@
       </c>
       <c r="F2011" t="inlineStr">
         <is>
-          <t>SANTOS - DP</t>
+          <t>SANTOS - EF</t>
         </is>
       </c>
       <c r="G2011" t="inlineStr">
         <is>
-          <t>Patricia Melo</t>
-        </is>
-      </c>
-      <c r="H2011" t="inlineStr"/>
+          <t>Jasmina Melo</t>
+        </is>
+      </c>
+      <c r="H2011" t="inlineStr">
+        <is>
+          <t>Lidia Tavares</t>
+        </is>
+      </c>
       <c r="I2011" t="n">
         <v>0</v>
       </c>
       <c r="J2011" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="K2011" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2012">
@@ -101417,7 +101421,7 @@
       </c>
       <c r="G2012" t="inlineStr">
         <is>
-          <t>Jasmina Melo</t>
+          <t>Karen Saadi</t>
         </is>
       </c>
       <c r="H2012" t="inlineStr">
@@ -101429,10 +101433,10 @@
         <v>0</v>
       </c>
       <c r="J2012" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="K2012" t="n">
-        <v>106</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2013">
@@ -101468,7 +101472,7 @@
       </c>
       <c r="G2013" t="inlineStr">
         <is>
-          <t>Karen Saadi</t>
+          <t>Luckas Andrade</t>
         </is>
       </c>
       <c r="H2013" t="inlineStr">
@@ -101477,13 +101481,13 @@
         </is>
       </c>
       <c r="I2013" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2013" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K2013" t="n">
-        <v>79</v>
+        <v>110</v>
       </c>
     </row>
     <row r="2014">
@@ -101519,7 +101523,7 @@
       </c>
       <c r="G2014" t="inlineStr">
         <is>
-          <t>Luckas Andrade</t>
+          <t>Mirian Rodrigues</t>
         </is>
       </c>
       <c r="H2014" t="inlineStr">
@@ -101531,10 +101535,10 @@
         <v>0</v>
       </c>
       <c r="J2014" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K2014" t="n">
-        <v>111</v>
+        <v>118</v>
       </c>
     </row>
     <row r="2015">
@@ -101565,74 +101569,23 @@
       </c>
       <c r="F2015" t="inlineStr">
         <is>
-          <t>SANTOS - EF</t>
+          <t>SANTOS - GC</t>
         </is>
       </c>
       <c r="G2015" t="inlineStr">
         <is>
-          <t>Mirian Rodrigues</t>
-        </is>
-      </c>
-      <c r="H2015" t="inlineStr">
-        <is>
-          <t>Lidia Tavares</t>
-        </is>
-      </c>
+          <t>Rafaella Massuia</t>
+        </is>
+      </c>
+      <c r="H2015" t="inlineStr"/>
       <c r="I2015" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J2015" t="n">
-        <v>6</v>
+        <v>109</v>
       </c>
       <c r="K2015" t="n">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="2016">
-      <c r="A2016" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="B2016" t="inlineStr">
-        <is>
-          <t>Terça</t>
-        </is>
-      </c>
-      <c r="C2016" t="inlineStr">
-        <is>
-          <t>2026-W25</t>
-        </is>
-      </c>
-      <c r="D2016" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="E2016" t="inlineStr">
-        <is>
-          <t>Santos</t>
-        </is>
-      </c>
-      <c r="F2016" t="inlineStr">
-        <is>
-          <t>SANTOS - GC</t>
-        </is>
-      </c>
-      <c r="G2016" t="inlineStr">
-        <is>
-          <t>Rafaella Massuia</t>
-        </is>
-      </c>
-      <c r="H2016" t="inlineStr"/>
-      <c r="I2016" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2016" t="n">
-        <v>14</v>
-      </c>
-      <c r="K2016" t="n">
-        <v>110</v>
+        <v>205</v>
       </c>
     </row>
   </sheetData>

--- a/data/historico/historico_baixas.xlsx
+++ b/data/historico/historico_baixas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2015"/>
+  <dimension ref="A1:K2016"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -86625,13 +86625,13 @@
         </is>
       </c>
       <c r="I1717" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1717" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1717" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1718">
@@ -87437,13 +87437,13 @@
         </is>
       </c>
       <c r="I1733" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1733" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1733" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1734">
@@ -87637,13 +87637,13 @@
         </is>
       </c>
       <c r="I1737" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J1737" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1737" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1738">
@@ -88170,13 +88170,13 @@
         </is>
       </c>
       <c r="I1748" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J1748" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K1748" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="1749">
@@ -88272,13 +88272,13 @@
         </is>
       </c>
       <c r="I1750" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1750" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K1750" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="1751">
@@ -88323,13 +88323,13 @@
         </is>
       </c>
       <c r="I1751" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J1751" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K1751" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="1752">
@@ -88374,13 +88374,13 @@
         </is>
       </c>
       <c r="I1752" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="J1752" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="K1752" t="n">
-        <v>93</v>
+        <v>99</v>
       </c>
     </row>
     <row r="1753">
@@ -88629,13 +88629,13 @@
         </is>
       </c>
       <c r="I1757" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="J1757" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="K1757" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1758">
@@ -88927,10 +88927,10 @@
         </is>
       </c>
       <c r="I1763" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J1763" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K1763" t="n">
         <v>113</v>
@@ -89029,13 +89029,13 @@
         </is>
       </c>
       <c r="I1765" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="J1765" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="K1765" t="n">
-        <v>88</v>
+        <v>104</v>
       </c>
     </row>
     <row r="1766">
@@ -89080,10 +89080,10 @@
         </is>
       </c>
       <c r="I1766" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J1766" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K1766" t="n">
         <v>24</v>
@@ -89341,7 +89341,7 @@
         <v>0</v>
       </c>
       <c r="K1771" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1772">
@@ -89443,7 +89443,7 @@
         <v>0</v>
       </c>
       <c r="K1773" t="n">
-        <v>109</v>
+        <v>117</v>
       </c>
     </row>
     <row r="1774">
@@ -89692,10 +89692,10 @@
         </is>
       </c>
       <c r="I1778" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J1778" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K1778" t="n">
         <v>181</v>
@@ -89794,10 +89794,10 @@
         </is>
       </c>
       <c r="I1780" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J1780" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K1780" t="n">
         <v>123</v>
@@ -89998,13 +89998,13 @@
         </is>
       </c>
       <c r="I1784" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J1784" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="K1784" t="n">
-        <v>172</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1785">
@@ -90253,13 +90253,13 @@
         </is>
       </c>
       <c r="I1789" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J1789" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K1789" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="1790">
@@ -90406,13 +90406,13 @@
         </is>
       </c>
       <c r="I1792" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J1792" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K1792" t="n">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="1793">
@@ -90504,13 +90504,13 @@
       </c>
       <c r="H1794" t="inlineStr"/>
       <c r="I1794" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="J1794" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="K1794" t="n">
-        <v>155</v>
+        <v>193</v>
       </c>
     </row>
     <row r="1795">
@@ -90557,7 +90557,7 @@
         <v>19</v>
       </c>
       <c r="K1795" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="1796">
@@ -90645,13 +90645,13 @@
       </c>
       <c r="H1797" t="inlineStr"/>
       <c r="I1797" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="J1797" t="n">
-        <v>90</v>
+        <v>128</v>
       </c>
       <c r="K1797" t="n">
-        <v>437</v>
+        <v>475</v>
       </c>
     </row>
     <row r="1798">
@@ -90692,13 +90692,13 @@
       </c>
       <c r="H1798" t="inlineStr"/>
       <c r="I1798" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1798" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1798" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1799">
@@ -91049,13 +91049,13 @@
         </is>
       </c>
       <c r="I1805" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1805" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K1805" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1806">
@@ -91151,13 +91151,13 @@
         </is>
       </c>
       <c r="I1807" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1807" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K1807" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1808">
@@ -91202,13 +91202,13 @@
         </is>
       </c>
       <c r="I1808" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J1808" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="K1808" t="n">
-        <v>197</v>
+        <v>203</v>
       </c>
     </row>
     <row r="1809">
@@ -91300,13 +91300,13 @@
         </is>
       </c>
       <c r="I1810" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J1810" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="K1810" t="n">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="1811">
@@ -91402,13 +91402,13 @@
         </is>
       </c>
       <c r="I1812" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1812" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K1812" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="1813">
@@ -91504,13 +91504,13 @@
         </is>
       </c>
       <c r="I1814" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J1814" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1814" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1815">
@@ -91555,13 +91555,13 @@
         </is>
       </c>
       <c r="I1815" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1815" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K1815" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="1816">
@@ -91606,13 +91606,13 @@
         </is>
       </c>
       <c r="I1816" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J1816" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K1816" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1817">
@@ -91708,13 +91708,13 @@
         </is>
       </c>
       <c r="I1818" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J1818" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K1818" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="1819">
@@ -91810,13 +91810,13 @@
         </is>
       </c>
       <c r="I1820" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J1820" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K1820" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="1821">
@@ -91908,13 +91908,13 @@
         </is>
       </c>
       <c r="I1822" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1822" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K1822" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="1823">
@@ -92112,13 +92112,13 @@
         </is>
       </c>
       <c r="I1826" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J1826" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K1826" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="1827">
@@ -92163,13 +92163,13 @@
         </is>
       </c>
       <c r="I1827" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J1827" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K1827" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="1828">
@@ -92469,13 +92469,13 @@
         </is>
       </c>
       <c r="I1833" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J1833" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K1833" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="1834">
@@ -92520,10 +92520,10 @@
         </is>
       </c>
       <c r="I1834" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J1834" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K1834" t="n">
         <v>14</v>
@@ -92571,13 +92571,13 @@
         </is>
       </c>
       <c r="I1835" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="J1835" t="n">
-        <v>3</v>
+        <v>67</v>
       </c>
       <c r="K1835" t="n">
-        <v>81</v>
+        <v>145</v>
       </c>
     </row>
     <row r="1836">
@@ -92622,13 +92622,13 @@
         </is>
       </c>
       <c r="I1836" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J1836" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="K1836" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1837">
@@ -92724,13 +92724,13 @@
         </is>
       </c>
       <c r="I1838" t="n">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="J1838" t="n">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="K1838" t="n">
-        <v>167</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1839">
@@ -92826,13 +92826,13 @@
         </is>
       </c>
       <c r="I1840" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="J1840" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="K1840" t="n">
-        <v>140</v>
+        <v>148</v>
       </c>
     </row>
     <row r="1841">
@@ -92877,13 +92877,13 @@
         </is>
       </c>
       <c r="I1841" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1841" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K1841" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1842">
@@ -92934,7 +92934,7 @@
         <v>0</v>
       </c>
       <c r="K1842" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="1843">
@@ -92979,13 +92979,13 @@
         </is>
       </c>
       <c r="I1843" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J1843" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="K1843" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="1844">
@@ -93030,13 +93030,13 @@
         </is>
       </c>
       <c r="I1844" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J1844" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K1844" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="1845">
@@ -93132,13 +93132,13 @@
         </is>
       </c>
       <c r="I1846" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J1846" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="K1846" t="n">
-        <v>148</v>
+        <v>154</v>
       </c>
     </row>
     <row r="1847">
@@ -93183,13 +93183,13 @@
         </is>
       </c>
       <c r="I1847" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1847" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K1847" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="1848">
@@ -93285,13 +93285,13 @@
         </is>
       </c>
       <c r="I1849" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1849" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="K1849" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="1850">
@@ -93336,13 +93336,13 @@
         </is>
       </c>
       <c r="I1850" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J1850" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K1850" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="1851">
@@ -93387,13 +93387,13 @@
         </is>
       </c>
       <c r="I1851" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J1851" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K1851" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="1852">
@@ -93489,13 +93489,13 @@
         </is>
       </c>
       <c r="I1853" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1853" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K1853" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1854">
@@ -93638,13 +93638,13 @@
         </is>
       </c>
       <c r="I1856" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J1856" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="K1856" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="1857">
@@ -93689,13 +93689,13 @@
         </is>
       </c>
       <c r="I1857" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J1857" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K1857" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1858">
@@ -93740,13 +93740,13 @@
         </is>
       </c>
       <c r="I1858" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="J1858" t="n">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="K1858" t="n">
-        <v>133</v>
+        <v>145</v>
       </c>
     </row>
     <row r="1859">
@@ -94097,10 +94097,10 @@
         </is>
       </c>
       <c r="I1865" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J1865" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K1865" t="n">
         <v>141</v>
@@ -94199,13 +94199,13 @@
         </is>
       </c>
       <c r="I1867" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="J1867" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="K1867" t="n">
-        <v>119</v>
+        <v>127</v>
       </c>
     </row>
     <row r="1868">
@@ -94301,13 +94301,13 @@
         </is>
       </c>
       <c r="I1869" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J1869" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K1869" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="1870">
@@ -94352,13 +94352,13 @@
         </is>
       </c>
       <c r="I1870" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1870" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K1870" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="1871">
@@ -94658,13 +94658,13 @@
         </is>
       </c>
       <c r="I1876" t="n">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="J1876" t="n">
-        <v>27</v>
+        <v>61</v>
       </c>
       <c r="K1876" t="n">
-        <v>161</v>
+        <v>195</v>
       </c>
     </row>
     <row r="1877">
@@ -94760,13 +94760,13 @@
         </is>
       </c>
       <c r="I1878" t="n">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="J1878" t="n">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="K1878" t="n">
-        <v>107</v>
+        <v>151</v>
       </c>
     </row>
     <row r="1879">
@@ -94811,13 +94811,13 @@
         </is>
       </c>
       <c r="I1879" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J1879" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="K1879" t="n">
-        <v>140</v>
+        <v>147</v>
       </c>
     </row>
     <row r="1880">
@@ -94913,13 +94913,13 @@
         </is>
       </c>
       <c r="I1881" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="J1881" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="K1881" t="n">
-        <v>123</v>
+        <v>131</v>
       </c>
     </row>
     <row r="1882">
@@ -95117,13 +95117,13 @@
         </is>
       </c>
       <c r="I1885" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1885" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K1885" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1886">
@@ -95470,13 +95470,13 @@
         </is>
       </c>
       <c r="I1892" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J1892" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K1892" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="1893">
@@ -95572,13 +95572,13 @@
         </is>
       </c>
       <c r="I1894" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J1894" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="K1894" t="n">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="1895">
@@ -95623,13 +95623,13 @@
         </is>
       </c>
       <c r="I1895" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J1895" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K1895" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="1896">
@@ -95725,10 +95725,10 @@
         </is>
       </c>
       <c r="I1897" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J1897" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K1897" t="n">
         <v>162</v>
@@ -96031,13 +96031,13 @@
         </is>
       </c>
       <c r="I1903" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="J1903" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="K1903" t="n">
-        <v>174</v>
+        <v>190</v>
       </c>
     </row>
     <row r="1904">
@@ -96282,13 +96282,13 @@
         </is>
       </c>
       <c r="I1908" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1908" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K1908" t="n">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1909">
@@ -96333,13 +96333,13 @@
         </is>
       </c>
       <c r="I1909" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J1909" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K1909" t="n">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="1910">
@@ -96384,13 +96384,13 @@
         </is>
       </c>
       <c r="I1910" t="n">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="J1910" t="n">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="K1910" t="n">
-        <v>815</v>
+        <v>830</v>
       </c>
     </row>
     <row r="1911">
@@ -96537,13 +96537,13 @@
         </is>
       </c>
       <c r="I1913" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1913" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K1913" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="1914">
@@ -96639,13 +96639,13 @@
         </is>
       </c>
       <c r="I1915" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1915" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K1915" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="1916">
@@ -96690,13 +96690,13 @@
         </is>
       </c>
       <c r="I1916" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J1916" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K1916" t="n">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="1917">
@@ -96996,13 +96996,13 @@
         </is>
       </c>
       <c r="I1922" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J1922" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K1922" t="n">
-        <v>226</v>
+        <v>229</v>
       </c>
     </row>
     <row r="1923">
@@ -97047,13 +97047,13 @@
         </is>
       </c>
       <c r="I1923" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J1923" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K1923" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="1924">
@@ -97251,13 +97251,13 @@
         </is>
       </c>
       <c r="I1927" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1927" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K1927" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1928">
@@ -97302,13 +97302,13 @@
         </is>
       </c>
       <c r="I1928" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J1928" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="K1928" t="n">
-        <v>173</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1929">
@@ -97349,10 +97349,10 @@
       </c>
       <c r="H1929" t="inlineStr"/>
       <c r="I1929" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J1929" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1929" t="n">
         <v>222</v>
@@ -97451,13 +97451,13 @@
         </is>
       </c>
       <c r="I1931" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J1931" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K1931" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="1932">
@@ -97502,13 +97502,13 @@
         </is>
       </c>
       <c r="I1932" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J1932" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K1932" t="n">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1933">
@@ -97553,13 +97553,13 @@
         </is>
       </c>
       <c r="I1933" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1933" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K1933" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="1934">
@@ -97655,13 +97655,13 @@
         </is>
       </c>
       <c r="I1935" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J1935" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="K1935" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
     </row>
     <row r="1936">
@@ -97706,13 +97706,13 @@
         </is>
       </c>
       <c r="I1936" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1936" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K1936" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="1937">
@@ -97865,7 +97865,7 @@
         <v>17</v>
       </c>
       <c r="K1939" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="1940">
@@ -97961,13 +97961,13 @@
         </is>
       </c>
       <c r="I1941" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J1941" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K1941" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="1942">
@@ -98063,13 +98063,13 @@
         </is>
       </c>
       <c r="I1943" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J1943" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K1943" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="1944">
@@ -98114,13 +98114,13 @@
         </is>
       </c>
       <c r="I1944" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J1944" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K1944" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="1945">
@@ -98165,13 +98165,13 @@
         </is>
       </c>
       <c r="I1945" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="J1945" t="n">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="K1945" t="n">
-        <v>343</v>
+        <v>362</v>
       </c>
     </row>
     <row r="1946">
@@ -98216,13 +98216,13 @@
         </is>
       </c>
       <c r="I1946" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="J1946" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K1946" t="n">
-        <v>117</v>
+        <v>127</v>
       </c>
     </row>
     <row r="1947">
@@ -98267,13 +98267,13 @@
         </is>
       </c>
       <c r="I1947" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1947" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K1947" t="n">
-        <v>227</v>
+        <v>224</v>
       </c>
     </row>
     <row r="1948">
@@ -98318,13 +98318,13 @@
         </is>
       </c>
       <c r="I1948" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J1948" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="K1948" t="n">
-        <v>155</v>
+        <v>162</v>
       </c>
     </row>
     <row r="1949">
@@ -98369,13 +98369,13 @@
         </is>
       </c>
       <c r="I1949" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J1949" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K1949" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="1950">
@@ -98471,13 +98471,13 @@
         </is>
       </c>
       <c r="I1951" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J1951" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K1951" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="1952">
@@ -98573,13 +98573,13 @@
         </is>
       </c>
       <c r="I1953" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J1953" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K1953" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="1954">
@@ -98624,13 +98624,13 @@
         </is>
       </c>
       <c r="I1954" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J1954" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K1954" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="1955">
@@ -98675,13 +98675,13 @@
         </is>
       </c>
       <c r="I1955" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J1955" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K1955" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="1956">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="I1956" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J1956" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="K1956" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="1957">
@@ -99130,13 +99130,13 @@
         </is>
       </c>
       <c r="I1964" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1964" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1964" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1965">
@@ -99181,13 +99181,13 @@
         </is>
       </c>
       <c r="I1965" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1965" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1965" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1966">
@@ -99275,10 +99275,10 @@
       </c>
       <c r="H1967" t="inlineStr"/>
       <c r="I1967" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="J1967" t="n">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="K1967" t="n">
         <v>588</v>
@@ -99372,7 +99372,7 @@
         <v>0</v>
       </c>
       <c r="J1969" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K1969" t="n">
         <v>457</v>
@@ -99458,18 +99458,18 @@
       </c>
       <c r="G1971" t="inlineStr">
         <is>
-          <t>Daniela Silva</t>
+          <t>Clara Maria</t>
         </is>
       </c>
       <c r="H1971" t="inlineStr"/>
       <c r="I1971" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1971" t="n">
-        <v>154</v>
+        <v>0</v>
       </c>
       <c r="K1971" t="n">
-        <v>302</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1972">
@@ -99505,7 +99505,7 @@
       </c>
       <c r="G1972" t="inlineStr">
         <is>
-          <t>Isabelli Afonso</t>
+          <t>Daniela Silva</t>
         </is>
       </c>
       <c r="H1972" t="inlineStr"/>
@@ -99513,10 +99513,10 @@
         <v>0</v>
       </c>
       <c r="J1972" t="n">
-        <v>1</v>
+        <v>154</v>
       </c>
       <c r="K1972" t="n">
-        <v>234</v>
+        <v>302</v>
       </c>
     </row>
     <row r="1973">
@@ -99552,18 +99552,18 @@
       </c>
       <c r="G1973" t="inlineStr">
         <is>
-          <t>Jurema Damacena - SAC</t>
+          <t>Isabelli Afonso</t>
         </is>
       </c>
       <c r="H1973" t="inlineStr"/>
       <c r="I1973" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1973" t="n">
         <v>1</v>
       </c>
       <c r="K1973" t="n">
-        <v>1</v>
+        <v>234</v>
       </c>
     </row>
     <row r="1974">
@@ -99599,18 +99599,18 @@
       </c>
       <c r="G1974" t="inlineStr">
         <is>
-          <t>Leticia Queiroz</t>
+          <t>Jurema Damacena - SAC</t>
         </is>
       </c>
       <c r="H1974" t="inlineStr"/>
       <c r="I1974" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J1974" t="n">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="K1974" t="n">
-        <v>430</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1975">
@@ -99646,18 +99646,18 @@
       </c>
       <c r="G1975" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Leticia Queiroz</t>
         </is>
       </c>
       <c r="H1975" t="inlineStr"/>
       <c r="I1975" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J1975" t="n">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="K1975" t="n">
-        <v>13</v>
+        <v>430</v>
       </c>
     </row>
     <row r="1976">
@@ -99693,18 +99693,18 @@
       </c>
       <c r="G1976" t="inlineStr">
         <is>
-          <t>Victoria Virgens</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="H1976" t="inlineStr"/>
       <c r="I1976" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1976" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K1976" t="n">
-        <v>309</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1977">
@@ -99740,18 +99740,18 @@
       </c>
       <c r="G1977" t="inlineStr">
         <is>
-          <t>Yasmin Peixoto</t>
+          <t>Victoria Virgens</t>
         </is>
       </c>
       <c r="H1977" t="inlineStr"/>
       <c r="I1977" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="J1977" t="n">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="K1977" t="n">
-        <v>558</v>
+        <v>309</v>
       </c>
     </row>
     <row r="1978">
@@ -99782,23 +99782,23 @@
       </c>
       <c r="F1978" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="G1978" t="inlineStr">
         <is>
-          <t>Andre Coelho</t>
+          <t>Yasmin Peixoto</t>
         </is>
       </c>
       <c r="H1978" t="inlineStr"/>
       <c r="I1978" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="J1978" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="K1978" t="n">
-        <v>4</v>
+        <v>558</v>
       </c>
     </row>
     <row r="1979">
@@ -99834,18 +99834,18 @@
       </c>
       <c r="G1979" t="inlineStr">
         <is>
-          <t>Beatriz Rangel</t>
+          <t>Andre Coelho</t>
         </is>
       </c>
       <c r="H1979" t="inlineStr"/>
       <c r="I1979" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="J1979" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="K1979" t="n">
-        <v>375</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1980">
@@ -99881,18 +99881,18 @@
       </c>
       <c r="G1980" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
+          <t>Beatriz Rangel</t>
         </is>
       </c>
       <c r="H1980" t="inlineStr"/>
       <c r="I1980" t="n">
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="J1980" t="n">
-        <v>152</v>
+        <v>207</v>
       </c>
       <c r="K1980" t="n">
-        <v>434</v>
+        <v>473</v>
       </c>
     </row>
     <row r="1981">
@@ -99928,18 +99928,18 @@
       </c>
       <c r="G1981" t="inlineStr">
         <is>
-          <t>Cristiane Simões</t>
+          <t>Bruno Contieri</t>
         </is>
       </c>
       <c r="H1981" t="inlineStr"/>
       <c r="I1981" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J1981" t="n">
-        <v>5</v>
+        <v>152</v>
       </c>
       <c r="K1981" t="n">
-        <v>303</v>
+        <v>434</v>
       </c>
     </row>
     <row r="1982">
@@ -99975,18 +99975,18 @@
       </c>
       <c r="G1982" t="inlineStr">
         <is>
-          <t>Daniel Oliveira</t>
+          <t>Cristiane Simões</t>
         </is>
       </c>
       <c r="H1982" t="inlineStr"/>
       <c r="I1982" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J1982" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="K1982" t="n">
-        <v>401</v>
+        <v>303</v>
       </c>
     </row>
     <row r="1983">
@@ -100022,18 +100022,18 @@
       </c>
       <c r="G1983" t="inlineStr">
         <is>
-          <t>Diego Lima</t>
+          <t>Daniel Oliveira</t>
         </is>
       </c>
       <c r="H1983" t="inlineStr"/>
       <c r="I1983" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="J1983" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K1983" t="n">
-        <v>166</v>
+        <v>400</v>
       </c>
     </row>
     <row r="1984">
@@ -100069,18 +100069,18 @@
       </c>
       <c r="G1984" t="inlineStr">
         <is>
-          <t>Eduardo Aparicio</t>
+          <t>Diego Lima</t>
         </is>
       </c>
       <c r="H1984" t="inlineStr"/>
       <c r="I1984" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J1984" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="K1984" t="n">
-        <v>1</v>
+        <v>166</v>
       </c>
     </row>
     <row r="1985">
@@ -100116,7 +100116,7 @@
       </c>
       <c r="G1985" t="inlineStr">
         <is>
-          <t>Karine Gusmão</t>
+          <t>Eduardo Aparicio</t>
         </is>
       </c>
       <c r="H1985" t="inlineStr"/>
@@ -100124,10 +100124,10 @@
         <v>0</v>
       </c>
       <c r="J1985" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1985" t="n">
-        <v>93</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1986">
@@ -100163,7 +100163,7 @@
       </c>
       <c r="G1986" t="inlineStr">
         <is>
-          <t>Luiz Ferreira</t>
+          <t>Karine Gusmão</t>
         </is>
       </c>
       <c r="H1986" t="inlineStr"/>
@@ -100174,7 +100174,7 @@
         <v>0</v>
       </c>
       <c r="K1986" t="n">
-        <v>17</v>
+        <v>93</v>
       </c>
     </row>
     <row r="1987">
@@ -100210,18 +100210,18 @@
       </c>
       <c r="G1987" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Luiz Ferreira</t>
         </is>
       </c>
       <c r="H1987" t="inlineStr"/>
       <c r="I1987" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J1987" t="n">
         <v>3</v>
       </c>
       <c r="K1987" t="n">
-        <v>221</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1988">
@@ -100257,18 +100257,18 @@
       </c>
       <c r="G1988" t="inlineStr">
         <is>
-          <t>Rodrigo Rego</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="H1988" t="inlineStr"/>
       <c r="I1988" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J1988" t="n">
-        <v>65</v>
+        <v>3</v>
       </c>
       <c r="K1988" t="n">
-        <v>459</v>
+        <v>221</v>
       </c>
     </row>
     <row r="1989">
@@ -100304,18 +100304,18 @@
       </c>
       <c r="G1989" t="inlineStr">
         <is>
-          <t>Rogerio Egidio</t>
+          <t>Rodrigo Rego</t>
         </is>
       </c>
       <c r="H1989" t="inlineStr"/>
       <c r="I1989" t="n">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="J1989" t="n">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="K1989" t="n">
-        <v>386</v>
+        <v>459</v>
       </c>
     </row>
     <row r="1990">
@@ -100351,18 +100351,18 @@
       </c>
       <c r="G1990" t="inlineStr">
         <is>
-          <t>Sergio Fernandes</t>
+          <t>Rogerio Egidio</t>
         </is>
       </c>
       <c r="H1990" t="inlineStr"/>
       <c r="I1990" t="n">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="J1990" t="n">
-        <v>3</v>
+        <v>82</v>
       </c>
       <c r="K1990" t="n">
-        <v>50</v>
+        <v>385</v>
       </c>
     </row>
     <row r="1991">
@@ -100398,7 +100398,7 @@
       </c>
       <c r="G1991" t="inlineStr">
         <is>
-          <t>Simone Marques</t>
+          <t>Sergio Fernandes</t>
         </is>
       </c>
       <c r="H1991" t="inlineStr"/>
@@ -100406,10 +100406,10 @@
         <v>3</v>
       </c>
       <c r="J1991" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="K1991" t="n">
-        <v>230</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1992">
@@ -100445,18 +100445,18 @@
       </c>
       <c r="G1992" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Simone Marques</t>
         </is>
       </c>
       <c r="H1992" t="inlineStr"/>
       <c r="I1992" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1992" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="K1992" t="n">
-        <v>267</v>
+        <v>230</v>
       </c>
     </row>
     <row r="1993">
@@ -100487,23 +100487,23 @@
       </c>
       <c r="F1993" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="G1993" t="inlineStr">
         <is>
-          <t>Jurema Damacena - SAC</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="H1993" t="inlineStr"/>
       <c r="I1993" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J1993" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K1993" t="n">
-        <v>49</v>
+        <v>265</v>
       </c>
     </row>
     <row r="1994">
@@ -100534,23 +100534,23 @@
       </c>
       <c r="F1994" t="inlineStr">
         <is>
-          <t>MG CONTABIFÁCIL - CTB</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="G1994" t="inlineStr">
         <is>
-          <t>Guilherme Delecrodio</t>
+          <t>Jurema Damacena - SAC</t>
         </is>
       </c>
       <c r="H1994" t="inlineStr"/>
       <c r="I1994" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J1994" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K1994" t="n">
-        <v>1</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1995">
@@ -100581,19 +100581,23 @@
       </c>
       <c r="F1995" t="inlineStr">
         <is>
-          <t>MG EXPRESS - CTB</t>
-        </is>
-      </c>
-      <c r="G1995" t="inlineStr"/>
+          <t>MG CONTABIFÁCIL - CTB</t>
+        </is>
+      </c>
+      <c r="G1995" t="inlineStr">
+        <is>
+          <t>Guilherme Delecrodio</t>
+        </is>
+      </c>
       <c r="H1995" t="inlineStr"/>
       <c r="I1995" t="n">
         <v>0</v>
       </c>
       <c r="J1995" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K1995" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1996">
@@ -100627,20 +100631,16 @@
           <t>MG EXPRESS - CTB</t>
         </is>
       </c>
-      <c r="G1996" t="inlineStr">
-        <is>
-          <t>Guilherme Delecrodio</t>
-        </is>
-      </c>
+      <c r="G1996" t="inlineStr"/>
       <c r="H1996" t="inlineStr"/>
       <c r="I1996" t="n">
         <v>0</v>
       </c>
       <c r="J1996" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K1996" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1997">
@@ -100671,23 +100671,23 @@
       </c>
       <c r="F1997" t="inlineStr">
         <is>
-          <t>S.A.C</t>
+          <t>MG EXPRESS - CTB</t>
         </is>
       </c>
       <c r="G1997" t="inlineStr">
         <is>
-          <t>Ana Celia - SAC</t>
+          <t>Guilherme Delecrodio</t>
         </is>
       </c>
       <c r="H1997" t="inlineStr"/>
       <c r="I1997" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J1997" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1997" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1998">
@@ -100723,18 +100723,18 @@
       </c>
       <c r="G1998" t="inlineStr">
         <is>
-          <t>Sarah Amaro</t>
+          <t>Ana Celia - SAC</t>
         </is>
       </c>
       <c r="H1998" t="inlineStr"/>
       <c r="I1998" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1998" t="n">
         <v>1</v>
       </c>
       <c r="K1998" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1999">
@@ -100765,27 +100765,23 @@
       </c>
       <c r="F1999" t="inlineStr">
         <is>
-          <t>SANTOS - DP</t>
+          <t>S.A.C</t>
         </is>
       </c>
       <c r="G1999" t="inlineStr">
         <is>
-          <t>Katia Valeria</t>
-        </is>
-      </c>
-      <c r="H1999" t="inlineStr">
-        <is>
-          <t>Katia Valeria</t>
-        </is>
-      </c>
+          <t>Sarah Amaro</t>
+        </is>
+      </c>
+      <c r="H1999" t="inlineStr"/>
       <c r="I1999" t="n">
         <v>0</v>
       </c>
       <c r="J1999" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1999" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2000">
@@ -100811,28 +100807,32 @@
       </c>
       <c r="E2000" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F2000" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>SANTOS - DP</t>
         </is>
       </c>
       <c r="G2000" t="inlineStr">
         <is>
-          <t>Jurema Damacena - SAC</t>
-        </is>
-      </c>
-      <c r="H2000" t="inlineStr"/>
+          <t>Katia Valeria</t>
+        </is>
+      </c>
+      <c r="H2000" t="inlineStr">
+        <is>
+          <t>Katia Valeria</t>
+        </is>
+      </c>
       <c r="I2000" t="n">
         <v>0</v>
       </c>
       <c r="J2000" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K2000" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2001">
@@ -100863,12 +100863,12 @@
       </c>
       <c r="F2001" t="inlineStr">
         <is>
-          <t>SANTOS - ADM</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="G2001" t="inlineStr">
         <is>
-          <t>Kauany Pereira</t>
+          <t>Jurema Damacena - SAC</t>
         </is>
       </c>
       <c r="H2001" t="inlineStr"/>
@@ -100876,10 +100876,10 @@
         <v>0</v>
       </c>
       <c r="J2001" t="n">
-        <v>95</v>
+        <v>2</v>
       </c>
       <c r="K2001" t="n">
-        <v>233</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2002">
@@ -100910,27 +100910,23 @@
       </c>
       <c r="F2002" t="inlineStr">
         <is>
-          <t>SANTOS - CTB</t>
+          <t>SANTOS - ADM</t>
         </is>
       </c>
       <c r="G2002" t="inlineStr">
         <is>
-          <t>Ivia Oliveira</t>
-        </is>
-      </c>
-      <c r="H2002" t="inlineStr">
-        <is>
-          <t>Roberto Silva</t>
-        </is>
-      </c>
+          <t>Kauany Pereira</t>
+        </is>
+      </c>
+      <c r="H2002" t="inlineStr"/>
       <c r="I2002" t="n">
         <v>0</v>
       </c>
       <c r="J2002" t="n">
-        <v>6</v>
+        <v>95</v>
       </c>
       <c r="K2002" t="n">
-        <v>63</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2003">
@@ -100966,7 +100962,7 @@
       </c>
       <c r="G2003" t="inlineStr">
         <is>
-          <t>Nata Trindade</t>
+          <t>Ivia Oliveira</t>
         </is>
       </c>
       <c r="H2003" t="inlineStr">
@@ -100975,13 +100971,13 @@
         </is>
       </c>
       <c r="I2003" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2003" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K2003" t="n">
-        <v>90</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2004">
@@ -101017,22 +101013,22 @@
       </c>
       <c r="G2004" t="inlineStr">
         <is>
+          <t>Nata Trindade</t>
+        </is>
+      </c>
+      <c r="H2004" t="inlineStr">
+        <is>
           <t>Roberto Silva</t>
         </is>
       </c>
-      <c r="H2004" t="inlineStr">
-        <is>
-          <t>Roberto Silva</t>
-        </is>
-      </c>
       <c r="I2004" t="n">
         <v>0</v>
       </c>
       <c r="J2004" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K2004" t="n">
-        <v>118</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2005">
@@ -101068,7 +101064,7 @@
       </c>
       <c r="G2005" t="inlineStr">
         <is>
-          <t>Thaina Rodrigues</t>
+          <t>Roberto Silva</t>
         </is>
       </c>
       <c r="H2005" t="inlineStr">
@@ -101080,10 +101076,10 @@
         <v>0</v>
       </c>
       <c r="J2005" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K2005" t="n">
-        <v>97</v>
+        <v>118</v>
       </c>
     </row>
     <row r="2006">
@@ -101114,27 +101110,27 @@
       </c>
       <c r="F2006" t="inlineStr">
         <is>
-          <t>SANTOS - DP</t>
+          <t>SANTOS - CTB</t>
         </is>
       </c>
       <c r="G2006" t="inlineStr">
         <is>
-          <t>Bruna Silva</t>
+          <t>Thaina Rodrigues</t>
         </is>
       </c>
       <c r="H2006" t="inlineStr">
         <is>
-          <t>Katia Valeria</t>
+          <t>Roberto Silva</t>
         </is>
       </c>
       <c r="I2006" t="n">
         <v>0</v>
       </c>
       <c r="J2006" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="K2006" t="n">
-        <v>14</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2007">
@@ -101170,7 +101166,7 @@
       </c>
       <c r="G2007" t="inlineStr">
         <is>
-          <t>Carliane Silva</t>
+          <t>Bruna Silva</t>
         </is>
       </c>
       <c r="H2007" t="inlineStr">
@@ -101179,13 +101175,13 @@
         </is>
       </c>
       <c r="I2007" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J2007" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="K2007" t="n">
-        <v>316</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2008">
@@ -101221,7 +101217,7 @@
       </c>
       <c r="G2008" t="inlineStr">
         <is>
-          <t>Cintia Andrade</t>
+          <t>Carliane Silva</t>
         </is>
       </c>
       <c r="H2008" t="inlineStr">
@@ -101230,13 +101226,13 @@
         </is>
       </c>
       <c r="I2008" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J2008" t="n">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="K2008" t="n">
-        <v>228</v>
+        <v>317</v>
       </c>
     </row>
     <row r="2009">
@@ -101272,22 +101268,22 @@
       </c>
       <c r="G2009" t="inlineStr">
         <is>
+          <t>Cintia Andrade</t>
+        </is>
+      </c>
+      <c r="H2009" t="inlineStr">
+        <is>
           <t>Katia Valeria</t>
         </is>
       </c>
-      <c r="H2009" t="inlineStr">
-        <is>
-          <t>Katia Valeria</t>
-        </is>
-      </c>
       <c r="I2009" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J2009" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="K2009" t="n">
-        <v>373</v>
+        <v>228</v>
       </c>
     </row>
     <row r="2010">
@@ -101323,18 +101319,22 @@
       </c>
       <c r="G2010" t="inlineStr">
         <is>
-          <t>Patricia Melo</t>
-        </is>
-      </c>
-      <c r="H2010" t="inlineStr"/>
+          <t>Katia Valeria</t>
+        </is>
+      </c>
+      <c r="H2010" t="inlineStr">
+        <is>
+          <t>Katia Valeria</t>
+        </is>
+      </c>
       <c r="I2010" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J2010" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="K2010" t="n">
-        <v>0</v>
+        <v>373</v>
       </c>
     </row>
     <row r="2011">
@@ -101365,27 +101365,23 @@
       </c>
       <c r="F2011" t="inlineStr">
         <is>
-          <t>SANTOS - EF</t>
+          <t>SANTOS - DP</t>
         </is>
       </c>
       <c r="G2011" t="inlineStr">
         <is>
-          <t>Jasmina Melo</t>
-        </is>
-      </c>
-      <c r="H2011" t="inlineStr">
-        <is>
-          <t>Lidia Tavares</t>
-        </is>
-      </c>
+          <t>Patricia Melo</t>
+        </is>
+      </c>
+      <c r="H2011" t="inlineStr"/>
       <c r="I2011" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J2011" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="K2011" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2012">
@@ -101421,7 +101417,7 @@
       </c>
       <c r="G2012" t="inlineStr">
         <is>
-          <t>Karen Saadi</t>
+          <t>Jasmina Melo</t>
         </is>
       </c>
       <c r="H2012" t="inlineStr">
@@ -101430,13 +101426,13 @@
         </is>
       </c>
       <c r="I2012" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J2012" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="K2012" t="n">
-        <v>79</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2013">
@@ -101472,7 +101468,7 @@
       </c>
       <c r="G2013" t="inlineStr">
         <is>
-          <t>Luckas Andrade</t>
+          <t>Karen Saadi</t>
         </is>
       </c>
       <c r="H2013" t="inlineStr">
@@ -101481,13 +101477,13 @@
         </is>
       </c>
       <c r="I2013" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2013" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K2013" t="n">
-        <v>110</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2014">
@@ -101523,7 +101519,7 @@
       </c>
       <c r="G2014" t="inlineStr">
         <is>
-          <t>Mirian Rodrigues</t>
+          <t>Luckas Andrade</t>
         </is>
       </c>
       <c r="H2014" t="inlineStr">
@@ -101532,13 +101528,13 @@
         </is>
       </c>
       <c r="I2014" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J2014" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K2014" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="2015">
@@ -101569,22 +101565,73 @@
       </c>
       <c r="F2015" t="inlineStr">
         <is>
+          <t>SANTOS - EF</t>
+        </is>
+      </c>
+      <c r="G2015" t="inlineStr">
+        <is>
+          <t>Mirian Rodrigues</t>
+        </is>
+      </c>
+      <c r="H2015" t="inlineStr">
+        <is>
+          <t>Lidia Tavares</t>
+        </is>
+      </c>
+      <c r="I2015" t="n">
+        <v>2</v>
+      </c>
+      <c r="J2015" t="n">
+        <v>8</v>
+      </c>
+      <c r="K2015" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2016">
+      <c r="A2016" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B2016" t="inlineStr">
+        <is>
+          <t>Terça</t>
+        </is>
+      </c>
+      <c r="C2016" t="inlineStr">
+        <is>
+          <t>2026-W25</t>
+        </is>
+      </c>
+      <c r="D2016" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E2016" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="F2016" t="inlineStr">
+        <is>
           <t>SANTOS - GC</t>
         </is>
       </c>
-      <c r="G2015" t="inlineStr">
+      <c r="G2016" t="inlineStr">
         <is>
           <t>Rafaella Massuia</t>
         </is>
       </c>
-      <c r="H2015" t="inlineStr"/>
-      <c r="I2015" t="n">
-        <v>100</v>
-      </c>
-      <c r="J2015" t="n">
+      <c r="H2016" t="inlineStr"/>
+      <c r="I2016" t="n">
+        <v>101</v>
+      </c>
+      <c r="J2016" t="n">
         <v>109</v>
       </c>
-      <c r="K2015" t="n">
+      <c r="K2016" t="n">
         <v>205</v>
       </c>
     </row>

--- a/data/historico/historico_baixas.xlsx
+++ b/data/historico/historico_baixas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2016"/>
+  <dimension ref="A1:K2017"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -86625,13 +86625,13 @@
         </is>
       </c>
       <c r="I1717" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J1717" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K1717" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1718">
@@ -88002,7 +88002,7 @@
       </c>
       <c r="E1745" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>GOIAS</t>
         </is>
       </c>
       <c r="F1745" t="inlineStr">
@@ -88012,18 +88012,18 @@
       </c>
       <c r="G1745" t="inlineStr">
         <is>
-          <t>Caroline Alves</t>
+          <t>Jurema Damacena - SAC</t>
         </is>
       </c>
       <c r="H1745" t="inlineStr"/>
       <c r="I1745" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1745" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K1745" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1746">
@@ -88054,27 +88054,23 @@
       </c>
       <c r="F1746" t="inlineStr">
         <is>
-          <t>RJ - CTB</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="G1746" t="inlineStr">
         <is>
-          <t>Crislaine Maia</t>
-        </is>
-      </c>
-      <c r="H1746" t="inlineStr">
-        <is>
-          <t>Walace Gonçalves|Maicon Costa</t>
-        </is>
-      </c>
+          <t>Caroline Alves</t>
+        </is>
+      </c>
+      <c r="H1746" t="inlineStr"/>
       <c r="I1746" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J1746" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="K1746" t="n">
-        <v>54</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1747">
@@ -88110,7 +88106,7 @@
       </c>
       <c r="G1747" t="inlineStr">
         <is>
-          <t>Gabriela Lopes</t>
+          <t>Crislaine Maia</t>
         </is>
       </c>
       <c r="H1747" t="inlineStr">
@@ -88119,13 +88115,13 @@
         </is>
       </c>
       <c r="I1747" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J1747" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="K1747" t="n">
-        <v>72</v>
+        <v>54</v>
       </c>
     </row>
     <row r="1748">
@@ -88161,7 +88157,7 @@
       </c>
       <c r="G1748" t="inlineStr">
         <is>
-          <t>Jeniffer Cristina</t>
+          <t>Gabriela Lopes</t>
         </is>
       </c>
       <c r="H1748" t="inlineStr">
@@ -88170,13 +88166,13 @@
         </is>
       </c>
       <c r="I1748" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J1748" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="K1748" t="n">
-        <v>90</v>
+        <v>72</v>
       </c>
     </row>
     <row r="1749">
@@ -88212,7 +88208,7 @@
       </c>
       <c r="G1749" t="inlineStr">
         <is>
-          <t>Jessica Roque</t>
+          <t>Jeniffer Cristina</t>
         </is>
       </c>
       <c r="H1749" t="inlineStr">
@@ -88221,13 +88217,13 @@
         </is>
       </c>
       <c r="I1749" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J1749" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="K1749" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="1750">
@@ -88263,7 +88259,7 @@
       </c>
       <c r="G1750" t="inlineStr">
         <is>
-          <t>Kellem Freitas</t>
+          <t>Jessica Roque</t>
         </is>
       </c>
       <c r="H1750" t="inlineStr">
@@ -88272,13 +88268,13 @@
         </is>
       </c>
       <c r="I1750" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J1750" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="K1750" t="n">
-        <v>43</v>
+        <v>92</v>
       </c>
     </row>
     <row r="1751">
@@ -88314,7 +88310,7 @@
       </c>
       <c r="G1751" t="inlineStr">
         <is>
-          <t>Leidiane Paulino</t>
+          <t>Kellem Freitas</t>
         </is>
       </c>
       <c r="H1751" t="inlineStr">
@@ -88323,13 +88319,13 @@
         </is>
       </c>
       <c r="I1751" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J1751" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="K1751" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
     </row>
     <row r="1752">
@@ -88365,7 +88361,7 @@
       </c>
       <c r="G1752" t="inlineStr">
         <is>
-          <t>Leticia Barbosa</t>
+          <t>Leidiane Paulino</t>
         </is>
       </c>
       <c r="H1752" t="inlineStr">
@@ -88374,13 +88370,13 @@
         </is>
       </c>
       <c r="I1752" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="J1752" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K1752" t="n">
-        <v>99</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1753">
@@ -88416,7 +88412,7 @@
       </c>
       <c r="G1753" t="inlineStr">
         <is>
-          <t>Luis Junior</t>
+          <t>Leticia Barbosa</t>
         </is>
       </c>
       <c r="H1753" t="inlineStr">
@@ -88425,13 +88421,13 @@
         </is>
       </c>
       <c r="I1753" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J1753" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K1753" t="n">
-        <v>14</v>
+        <v>99</v>
       </c>
     </row>
     <row r="1754">
@@ -88467,7 +88463,7 @@
       </c>
       <c r="G1754" t="inlineStr">
         <is>
-          <t>Nicoly Rodrigues</t>
+          <t>Luis Junior</t>
         </is>
       </c>
       <c r="H1754" t="inlineStr">
@@ -88482,7 +88478,7 @@
         <v>0</v>
       </c>
       <c r="K1754" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1755">
@@ -88518,7 +88514,7 @@
       </c>
       <c r="G1755" t="inlineStr">
         <is>
-          <t>Rafaella Silva</t>
+          <t>Nicoly Rodrigues</t>
         </is>
       </c>
       <c r="H1755" t="inlineStr">
@@ -88533,7 +88529,7 @@
         <v>0</v>
       </c>
       <c r="K1755" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1756">
@@ -88569,7 +88565,7 @@
       </c>
       <c r="G1756" t="inlineStr">
         <is>
-          <t>Rangel Rocha</t>
+          <t>Rafaella Silva</t>
         </is>
       </c>
       <c r="H1756" t="inlineStr">
@@ -88578,13 +88574,13 @@
         </is>
       </c>
       <c r="I1756" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J1756" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K1756" t="n">
-        <v>38</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1757">
@@ -88620,7 +88616,7 @@
       </c>
       <c r="G1757" t="inlineStr">
         <is>
-          <t>Simone Soares</t>
+          <t>Rangel Rocha</t>
         </is>
       </c>
       <c r="H1757" t="inlineStr">
@@ -88629,13 +88625,13 @@
         </is>
       </c>
       <c r="I1757" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="J1757" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="K1757" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="1758">
@@ -88671,7 +88667,7 @@
       </c>
       <c r="G1758" t="inlineStr">
         <is>
-          <t>Suzana Silva</t>
+          <t>Simone Soares</t>
         </is>
       </c>
       <c r="H1758" t="inlineStr">
@@ -88680,13 +88676,13 @@
         </is>
       </c>
       <c r="I1758" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J1758" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="K1758" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1759">
@@ -88722,7 +88718,7 @@
       </c>
       <c r="G1759" t="inlineStr">
         <is>
-          <t>Veronica Barbosa</t>
+          <t>Suzana Silva</t>
         </is>
       </c>
       <c r="H1759" t="inlineStr">
@@ -88731,13 +88727,13 @@
         </is>
       </c>
       <c r="I1759" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J1759" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="K1759" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="1760">
@@ -88773,7 +88769,7 @@
       </c>
       <c r="G1760" t="inlineStr">
         <is>
-          <t>Vitor Monteiro</t>
+          <t>Veronica Barbosa</t>
         </is>
       </c>
       <c r="H1760" t="inlineStr">
@@ -88782,13 +88778,13 @@
         </is>
       </c>
       <c r="I1760" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1760" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K1760" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
     </row>
     <row r="1761">
@@ -88824,7 +88820,7 @@
       </c>
       <c r="G1761" t="inlineStr">
         <is>
-          <t>Vitoria Silva</t>
+          <t>Vitor Monteiro</t>
         </is>
       </c>
       <c r="H1761" t="inlineStr">
@@ -88836,10 +88832,10 @@
         <v>0</v>
       </c>
       <c r="J1761" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K1761" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
     </row>
     <row r="1762">
@@ -88870,11 +88866,19 @@
       </c>
       <c r="F1762" t="inlineStr">
         <is>
-          <t>RJ - DP</t>
-        </is>
-      </c>
-      <c r="G1762" t="inlineStr"/>
-      <c r="H1762" t="inlineStr"/>
+          <t>RJ - CTB</t>
+        </is>
+      </c>
+      <c r="G1762" t="inlineStr">
+        <is>
+          <t>Vitoria Silva</t>
+        </is>
+      </c>
+      <c r="H1762" t="inlineStr">
+        <is>
+          <t>Walace Gonçalves|Maicon Costa</t>
+        </is>
+      </c>
       <c r="I1762" t="n">
         <v>0</v>
       </c>
@@ -88882,7 +88886,7 @@
         <v>0</v>
       </c>
       <c r="K1762" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="1763">
@@ -88916,24 +88920,16 @@
           <t>RJ - DP</t>
         </is>
       </c>
-      <c r="G1763" t="inlineStr">
-        <is>
-          <t>Barbara Mello</t>
-        </is>
-      </c>
-      <c r="H1763" t="inlineStr">
-        <is>
-          <t>Karina Oliveira|Liliane Costa</t>
-        </is>
-      </c>
+      <c r="G1763" t="inlineStr"/>
+      <c r="H1763" t="inlineStr"/>
       <c r="I1763" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J1763" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K1763" t="n">
-        <v>113</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1764">
@@ -88969,7 +88965,7 @@
       </c>
       <c r="G1764" t="inlineStr">
         <is>
-          <t>Debora Nunes</t>
+          <t>Barbara Mello</t>
         </is>
       </c>
       <c r="H1764" t="inlineStr">
@@ -88978,13 +88974,13 @@
         </is>
       </c>
       <c r="I1764" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J1764" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="K1764" t="n">
-        <v>101</v>
+        <v>113</v>
       </c>
     </row>
     <row r="1765">
@@ -89020,7 +89016,7 @@
       </c>
       <c r="G1765" t="inlineStr">
         <is>
-          <t>Graziele Almeida</t>
+          <t>Debora Nunes</t>
         </is>
       </c>
       <c r="H1765" t="inlineStr">
@@ -89029,13 +89025,13 @@
         </is>
       </c>
       <c r="I1765" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="J1765" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="K1765" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="1766">
@@ -89071,7 +89067,7 @@
       </c>
       <c r="G1766" t="inlineStr">
         <is>
-          <t>Janiele Ferreira</t>
+          <t>Graziele Almeida</t>
         </is>
       </c>
       <c r="H1766" t="inlineStr">
@@ -89080,13 +89076,13 @@
         </is>
       </c>
       <c r="I1766" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J1766" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="K1766" t="n">
-        <v>24</v>
+        <v>104</v>
       </c>
     </row>
     <row r="1767">
@@ -89122,7 +89118,7 @@
       </c>
       <c r="G1767" t="inlineStr">
         <is>
-          <t>Jefferson Barros</t>
+          <t>Janiele Ferreira</t>
         </is>
       </c>
       <c r="H1767" t="inlineStr">
@@ -89131,13 +89127,13 @@
         </is>
       </c>
       <c r="I1767" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J1767" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K1767" t="n">
-        <v>103</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1768">
@@ -89173,7 +89169,7 @@
       </c>
       <c r="G1768" t="inlineStr">
         <is>
-          <t>Karina Oliveira</t>
+          <t>Jefferson Barros</t>
         </is>
       </c>
       <c r="H1768" t="inlineStr">
@@ -89182,13 +89178,13 @@
         </is>
       </c>
       <c r="I1768" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1768" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K1768" t="n">
-        <v>31</v>
+        <v>105</v>
       </c>
     </row>
     <row r="1769">
@@ -89224,7 +89220,7 @@
       </c>
       <c r="G1769" t="inlineStr">
         <is>
-          <t>Leonardo Assunção</t>
+          <t>Karina Oliveira</t>
         </is>
       </c>
       <c r="H1769" t="inlineStr">
@@ -89233,13 +89229,13 @@
         </is>
       </c>
       <c r="I1769" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J1769" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="K1769" t="n">
-        <v>46</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1770">
@@ -89275,7 +89271,7 @@
       </c>
       <c r="G1770" t="inlineStr">
         <is>
-          <t>Liliane Costa</t>
+          <t>Leonardo Assunção</t>
         </is>
       </c>
       <c r="H1770" t="inlineStr">
@@ -89284,13 +89280,13 @@
         </is>
       </c>
       <c r="I1770" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J1770" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="K1770" t="n">
-        <v>17</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1771">
@@ -89326,7 +89322,7 @@
       </c>
       <c r="G1771" t="inlineStr">
         <is>
-          <t>Luciene Pimenta</t>
+          <t>Liliane Costa</t>
         </is>
       </c>
       <c r="H1771" t="inlineStr">
@@ -89341,7 +89337,7 @@
         <v>0</v>
       </c>
       <c r="K1771" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1772">
@@ -89377,7 +89373,7 @@
       </c>
       <c r="G1772" t="inlineStr">
         <is>
-          <t>Lucirene Souza</t>
+          <t>Luciene Pimenta</t>
         </is>
       </c>
       <c r="H1772" t="inlineStr">
@@ -89386,13 +89382,13 @@
         </is>
       </c>
       <c r="I1772" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J1772" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K1772" t="n">
-        <v>90</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1773">
@@ -89428,7 +89424,7 @@
       </c>
       <c r="G1773" t="inlineStr">
         <is>
-          <t>Marlon Silva</t>
+          <t>Lucirene Souza</t>
         </is>
       </c>
       <c r="H1773" t="inlineStr">
@@ -89437,13 +89433,13 @@
         </is>
       </c>
       <c r="I1773" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1773" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K1773" t="n">
-        <v>117</v>
+        <v>90</v>
       </c>
     </row>
     <row r="1774">
@@ -89479,7 +89475,7 @@
       </c>
       <c r="G1774" t="inlineStr">
         <is>
-          <t>Monique Britto</t>
+          <t>Marlon Silva</t>
         </is>
       </c>
       <c r="H1774" t="inlineStr">
@@ -89494,7 +89490,7 @@
         <v>0</v>
       </c>
       <c r="K1774" t="n">
-        <v>94</v>
+        <v>117</v>
       </c>
     </row>
     <row r="1775">
@@ -89530,7 +89526,7 @@
       </c>
       <c r="G1775" t="inlineStr">
         <is>
-          <t>Romulo Ferreira</t>
+          <t>Monique Britto</t>
         </is>
       </c>
       <c r="H1775" t="inlineStr">
@@ -89542,10 +89538,10 @@
         <v>0</v>
       </c>
       <c r="J1775" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K1775" t="n">
-        <v>316</v>
+        <v>94</v>
       </c>
     </row>
     <row r="1776">
@@ -89581,7 +89577,7 @@
       </c>
       <c r="G1776" t="inlineStr">
         <is>
-          <t>Rosilene Silva</t>
+          <t>Romulo Ferreira</t>
         </is>
       </c>
       <c r="H1776" t="inlineStr">
@@ -89590,13 +89586,13 @@
         </is>
       </c>
       <c r="I1776" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1776" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K1776" t="n">
-        <v>30</v>
+        <v>316</v>
       </c>
     </row>
     <row r="1777">
@@ -89632,7 +89628,7 @@
       </c>
       <c r="G1777" t="inlineStr">
         <is>
-          <t>Thais Santos</t>
+          <t>Rosilene Silva</t>
         </is>
       </c>
       <c r="H1777" t="inlineStr">
@@ -89644,10 +89640,10 @@
         <v>0</v>
       </c>
       <c r="J1777" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K1777" t="n">
-        <v>115</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1778">
@@ -89683,7 +89679,7 @@
       </c>
       <c r="G1778" t="inlineStr">
         <is>
-          <t>Vitoria Tavares</t>
+          <t>Thais Santos</t>
         </is>
       </c>
       <c r="H1778" t="inlineStr">
@@ -89692,13 +89688,13 @@
         </is>
       </c>
       <c r="I1778" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J1778" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K1778" t="n">
-        <v>181</v>
+        <v>115</v>
       </c>
     </row>
     <row r="1779">
@@ -89734,7 +89730,7 @@
       </c>
       <c r="G1779" t="inlineStr">
         <is>
-          <t>Viviane Moura</t>
+          <t>Vitoria Tavares</t>
         </is>
       </c>
       <c r="H1779" t="inlineStr">
@@ -89743,13 +89739,13 @@
         </is>
       </c>
       <c r="I1779" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1779" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K1779" t="n">
-        <v>76</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1780">
@@ -89785,7 +89781,7 @@
       </c>
       <c r="G1780" t="inlineStr">
         <is>
-          <t>Yasmin Lopes</t>
+          <t>Viviane Moura</t>
         </is>
       </c>
       <c r="H1780" t="inlineStr">
@@ -89794,13 +89790,13 @@
         </is>
       </c>
       <c r="I1780" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J1780" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="K1780" t="n">
-        <v>123</v>
+        <v>76</v>
       </c>
     </row>
     <row r="1781">
@@ -89831,27 +89827,27 @@
       </c>
       <c r="F1781" t="inlineStr">
         <is>
-          <t>RJ - EF</t>
+          <t>RJ - DP</t>
         </is>
       </c>
       <c r="G1781" t="inlineStr">
         <is>
-          <t>Altamir Nogueira</t>
+          <t>Yasmin Lopes</t>
         </is>
       </c>
       <c r="H1781" t="inlineStr">
         <is>
-          <t>Julio Santos|Jessica Benjamin</t>
+          <t>Karina Oliveira|Liliane Costa</t>
         </is>
       </c>
       <c r="I1781" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J1781" t="n">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="K1781" t="n">
-        <v>218</v>
+        <v>123</v>
       </c>
     </row>
     <row r="1782">
@@ -89887,7 +89883,7 @@
       </c>
       <c r="G1782" t="inlineStr">
         <is>
-          <t>Beatriz Oliveira</t>
+          <t>Altamir Nogueira</t>
         </is>
       </c>
       <c r="H1782" t="inlineStr">
@@ -89896,13 +89892,13 @@
         </is>
       </c>
       <c r="I1782" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J1782" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="K1782" t="n">
-        <v>131</v>
+        <v>218</v>
       </c>
     </row>
     <row r="1783">
@@ -89938,7 +89934,7 @@
       </c>
       <c r="G1783" t="inlineStr">
         <is>
-          <t>Glaucia Santos</t>
+          <t>Beatriz Oliveira</t>
         </is>
       </c>
       <c r="H1783" t="inlineStr">
@@ -89947,13 +89943,13 @@
         </is>
       </c>
       <c r="I1783" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J1783" t="n">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="K1783" t="n">
-        <v>197</v>
+        <v>131</v>
       </c>
     </row>
     <row r="1784">
@@ -89989,7 +89985,7 @@
       </c>
       <c r="G1784" t="inlineStr">
         <is>
-          <t>Isabela Barbosa</t>
+          <t>Glaucia Santos</t>
         </is>
       </c>
       <c r="H1784" t="inlineStr">
@@ -89998,13 +89994,13 @@
         </is>
       </c>
       <c r="I1784" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J1784" t="n">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="K1784" t="n">
-        <v>178</v>
+        <v>197</v>
       </c>
     </row>
     <row r="1785">
@@ -90040,7 +90036,7 @@
       </c>
       <c r="G1785" t="inlineStr">
         <is>
-          <t>Jessica Benjamin</t>
+          <t>Isabela Barbosa</t>
         </is>
       </c>
       <c r="H1785" t="inlineStr">
@@ -90049,13 +90045,13 @@
         </is>
       </c>
       <c r="I1785" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J1785" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="K1785" t="n">
-        <v>131</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1786">
@@ -90091,7 +90087,7 @@
       </c>
       <c r="G1786" t="inlineStr">
         <is>
-          <t>Juliana Perfeito</t>
+          <t>Jessica Benjamin</t>
         </is>
       </c>
       <c r="H1786" t="inlineStr">
@@ -90103,10 +90099,10 @@
         <v>2</v>
       </c>
       <c r="J1786" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="K1786" t="n">
-        <v>109</v>
+        <v>131</v>
       </c>
     </row>
     <row r="1787">
@@ -90142,7 +90138,7 @@
       </c>
       <c r="G1787" t="inlineStr">
         <is>
-          <t>Julio Santos</t>
+          <t>Juliana Perfeito</t>
         </is>
       </c>
       <c r="H1787" t="inlineStr">
@@ -90151,13 +90147,13 @@
         </is>
       </c>
       <c r="I1787" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1787" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="K1787" t="n">
-        <v>1</v>
+        <v>110</v>
       </c>
     </row>
     <row r="1788">
@@ -90193,7 +90189,7 @@
       </c>
       <c r="G1788" t="inlineStr">
         <is>
-          <t>Lais Catrine EF</t>
+          <t>Julio Santos</t>
         </is>
       </c>
       <c r="H1788" t="inlineStr">
@@ -90205,10 +90201,10 @@
         <v>0</v>
       </c>
       <c r="J1788" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K1788" t="n">
-        <v>235</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1789">
@@ -90244,7 +90240,7 @@
       </c>
       <c r="G1789" t="inlineStr">
         <is>
-          <t>Luana Meneses</t>
+          <t>Lais Catrine EF</t>
         </is>
       </c>
       <c r="H1789" t="inlineStr">
@@ -90253,13 +90249,13 @@
         </is>
       </c>
       <c r="I1789" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J1789" t="n">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="K1789" t="n">
-        <v>251</v>
+        <v>235</v>
       </c>
     </row>
     <row r="1790">
@@ -90295,7 +90291,7 @@
       </c>
       <c r="G1790" t="inlineStr">
         <is>
-          <t>Otacilia Ferreira</t>
+          <t>Luana Meneses</t>
         </is>
       </c>
       <c r="H1790" t="inlineStr">
@@ -90304,13 +90300,13 @@
         </is>
       </c>
       <c r="I1790" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J1790" t="n">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="K1790" t="n">
-        <v>114</v>
+        <v>251</v>
       </c>
     </row>
     <row r="1791">
@@ -90346,7 +90342,7 @@
       </c>
       <c r="G1791" t="inlineStr">
         <is>
-          <t>Renata Paixão</t>
+          <t>Otacilia Ferreira</t>
         </is>
       </c>
       <c r="H1791" t="inlineStr">
@@ -90355,13 +90351,13 @@
         </is>
       </c>
       <c r="I1791" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J1791" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="K1791" t="n">
-        <v>164</v>
+        <v>117</v>
       </c>
     </row>
     <row r="1792">
@@ -90397,7 +90393,7 @@
       </c>
       <c r="G1792" t="inlineStr">
         <is>
-          <t>Thamara Jordes</t>
+          <t>Renata Paixão</t>
         </is>
       </c>
       <c r="H1792" t="inlineStr">
@@ -90406,10 +90402,10 @@
         </is>
       </c>
       <c r="I1792" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J1792" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K1792" t="n">
         <v>164</v>
@@ -90448,7 +90444,7 @@
       </c>
       <c r="G1793" t="inlineStr">
         <is>
-          <t>Wellington Oliveira</t>
+          <t>Thamara Jordes</t>
         </is>
       </c>
       <c r="H1793" t="inlineStr">
@@ -90457,13 +90453,13 @@
         </is>
       </c>
       <c r="I1793" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J1793" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="K1793" t="n">
-        <v>204</v>
+        <v>166</v>
       </c>
     </row>
     <row r="1794">
@@ -90494,23 +90490,27 @@
       </c>
       <c r="F1794" t="inlineStr">
         <is>
-          <t>RJ - GC</t>
+          <t>RJ - EF</t>
         </is>
       </c>
       <c r="G1794" t="inlineStr">
         <is>
-          <t>Bruno Mota</t>
-        </is>
-      </c>
-      <c r="H1794" t="inlineStr"/>
+          <t>Wellington Oliveira</t>
+        </is>
+      </c>
+      <c r="H1794" t="inlineStr">
+        <is>
+          <t>Julio Santos|Jessica Benjamin</t>
+        </is>
+      </c>
       <c r="I1794" t="n">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="J1794" t="n">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="K1794" t="n">
-        <v>193</v>
+        <v>207</v>
       </c>
     </row>
     <row r="1795">
@@ -90546,18 +90546,18 @@
       </c>
       <c r="G1795" t="inlineStr">
         <is>
-          <t>Cavalcante Peres</t>
+          <t>Bruno Mota</t>
         </is>
       </c>
       <c r="H1795" t="inlineStr"/>
       <c r="I1795" t="n">
-        <v>14</v>
+        <v>193</v>
       </c>
       <c r="J1795" t="n">
-        <v>19</v>
+        <v>192</v>
       </c>
       <c r="K1795" t="n">
-        <v>98</v>
+        <v>344</v>
       </c>
     </row>
     <row r="1796">
@@ -90588,23 +90588,23 @@
       </c>
       <c r="F1796" t="inlineStr">
         <is>
-          <t>RJ - GC ADMINISTRATIVO</t>
+          <t>RJ - GC</t>
         </is>
       </c>
       <c r="G1796" t="inlineStr">
         <is>
-          <t>Amanda Mesquita</t>
+          <t>Cavalcante Peres</t>
         </is>
       </c>
       <c r="H1796" t="inlineStr"/>
       <c r="I1796" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J1796" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="K1796" t="n">
-        <v>257</v>
+        <v>98</v>
       </c>
     </row>
     <row r="1797">
@@ -90640,18 +90640,18 @@
       </c>
       <c r="G1797" t="inlineStr">
         <is>
-          <t>Lohany Martins</t>
+          <t>Amanda Mesquita</t>
         </is>
       </c>
       <c r="H1797" t="inlineStr"/>
       <c r="I1797" t="n">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="J1797" t="n">
-        <v>128</v>
+        <v>27</v>
       </c>
       <c r="K1797" t="n">
-        <v>475</v>
+        <v>257</v>
       </c>
     </row>
     <row r="1798">
@@ -90682,23 +90682,23 @@
       </c>
       <c r="F1798" t="inlineStr">
         <is>
-          <t>S.A.C</t>
+          <t>RJ - GC ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="G1798" t="inlineStr">
         <is>
-          <t>Milena Campos - SAC</t>
+          <t>Lohany Martins</t>
         </is>
       </c>
       <c r="H1798" t="inlineStr"/>
       <c r="I1798" t="n">
-        <v>1</v>
+        <v>85</v>
       </c>
       <c r="J1798" t="n">
-        <v>1</v>
+        <v>175</v>
       </c>
       <c r="K1798" t="n">
-        <v>2</v>
+        <v>522</v>
       </c>
     </row>
     <row r="1799">
@@ -90724,32 +90724,28 @@
       </c>
       <c r="E1799" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F1799" t="inlineStr">
         <is>
-          <t>CONTABILIDADE (Outsourcing)</t>
+          <t>S.A.C</t>
         </is>
       </c>
       <c r="G1799" t="inlineStr">
         <is>
-          <t>Aline Petrini</t>
-        </is>
-      </c>
-      <c r="H1799" t="inlineStr">
-        <is>
-          <t>Fernanda Araujo</t>
-        </is>
-      </c>
+          <t>Milena Campos - SAC</t>
+        </is>
+      </c>
+      <c r="H1799" t="inlineStr"/>
       <c r="I1799" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1799" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1799" t="n">
         <v>2</v>
-      </c>
-      <c r="K1799" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="1800">
@@ -90785,22 +90781,22 @@
       </c>
       <c r="G1800" t="inlineStr">
         <is>
-          <t>Daniele Leite</t>
+          <t>Aline Petrini</t>
         </is>
       </c>
       <c r="H1800" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="I1800" t="n">
         <v>0</v>
       </c>
       <c r="J1800" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1800" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1801">
@@ -90836,22 +90832,22 @@
       </c>
       <c r="G1801" t="inlineStr">
         <is>
-          <t>Diogo Calazans</t>
+          <t>Daniele Leite</t>
         </is>
       </c>
       <c r="H1801" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I1801" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J1801" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K1801" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1802">
@@ -90887,22 +90883,22 @@
       </c>
       <c r="G1802" t="inlineStr">
         <is>
-          <t>Jaqueline Sousa</t>
+          <t>Diogo Calazans</t>
         </is>
       </c>
       <c r="H1802" t="inlineStr">
         <is>
-          <t>Lucas Fischer</t>
+          <t>Karina Santos</t>
         </is>
       </c>
       <c r="I1802" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1802" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K1802" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1803">
@@ -90938,7 +90934,7 @@
       </c>
       <c r="G1803" t="inlineStr">
         <is>
-          <t>Leticia Medeiros</t>
+          <t>Jaqueline Sousa</t>
         </is>
       </c>
       <c r="H1803" t="inlineStr">
@@ -90947,13 +90943,13 @@
         </is>
       </c>
       <c r="I1803" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J1803" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K1803" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1804">
@@ -90989,22 +90985,22 @@
       </c>
       <c r="G1804" t="inlineStr">
         <is>
-          <t>Patricia Borges</t>
+          <t>Leticia Medeiros</t>
         </is>
       </c>
       <c r="H1804" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Lucas Fischer</t>
         </is>
       </c>
       <c r="I1804" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1804" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K1804" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1805">
@@ -91040,22 +91036,22 @@
       </c>
       <c r="G1805" t="inlineStr">
         <is>
-          <t>Rejane Coelho</t>
+          <t>Patricia Borges</t>
         </is>
       </c>
       <c r="H1805" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I1805" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J1805" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K1805" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1806">
@@ -91091,22 +91087,22 @@
       </c>
       <c r="G1806" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Rejane Coelho</t>
         </is>
       </c>
       <c r="H1806" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Karina Santos</t>
         </is>
       </c>
       <c r="I1806" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1806" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K1806" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1807">
@@ -91142,22 +91138,22 @@
       </c>
       <c r="G1807" t="inlineStr">
         <is>
-          <t>Thiago Ceconelli</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="H1807" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="I1807" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J1807" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K1807" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1808">
@@ -91188,27 +91184,27 @@
       </c>
       <c r="F1808" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL HOLDING</t>
+          <t>CONTABILIDADE (Outsourcing)</t>
         </is>
       </c>
       <c r="G1808" t="inlineStr">
         <is>
-          <t>Ana Flavia Silva</t>
+          <t>Thiago Ceconelli</t>
         </is>
       </c>
       <c r="H1808" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Karina Santos</t>
         </is>
       </c>
       <c r="I1808" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J1808" t="n">
-        <v>84</v>
+        <v>3</v>
       </c>
       <c r="K1808" t="n">
-        <v>203</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1809">
@@ -91244,18 +91240,22 @@
       </c>
       <c r="G1809" t="inlineStr">
         <is>
-          <t>Daniele Faria</t>
-        </is>
-      </c>
-      <c r="H1809" t="inlineStr"/>
+          <t>Ana Flavia Silva</t>
+        </is>
+      </c>
+      <c r="H1809" t="inlineStr">
+        <is>
+          <t>Tatiana Linardi</t>
+        </is>
+      </c>
       <c r="I1809" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J1809" t="n">
-        <v>3</v>
+        <v>84</v>
       </c>
       <c r="K1809" t="n">
-        <v>5</v>
+        <v>203</v>
       </c>
     </row>
     <row r="1810">
@@ -91291,22 +91291,18 @@
       </c>
       <c r="G1810" t="inlineStr">
         <is>
-          <t>Vitor de Souza</t>
-        </is>
-      </c>
-      <c r="H1810" t="inlineStr">
-        <is>
-          <t>Tatiana Linardi</t>
-        </is>
-      </c>
+          <t>Daniele Faria</t>
+        </is>
+      </c>
+      <c r="H1810" t="inlineStr"/>
       <c r="I1810" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1810" t="n">
+        <v>3</v>
+      </c>
+      <c r="K1810" t="n">
         <v>5</v>
-      </c>
-      <c r="J1810" t="n">
-        <v>147</v>
-      </c>
-      <c r="K1810" t="n">
-        <v>288</v>
       </c>
     </row>
     <row r="1811">
@@ -91342,7 +91338,7 @@
       </c>
       <c r="G1811" t="inlineStr">
         <is>
-          <t>Vitoria Regina</t>
+          <t>Vitor de Souza</t>
         </is>
       </c>
       <c r="H1811" t="inlineStr">
@@ -91351,13 +91347,13 @@
         </is>
       </c>
       <c r="I1811" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J1811" t="n">
-        <v>81</v>
+        <v>150</v>
       </c>
       <c r="K1811" t="n">
-        <v>225</v>
+        <v>291</v>
       </c>
     </row>
     <row r="1812">
@@ -91388,27 +91384,27 @@
       </c>
       <c r="F1812" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL INDUSTRIA</t>
+          <t>CTB - CONTÁBIL HOLDING</t>
         </is>
       </c>
       <c r="G1812" t="inlineStr">
         <is>
-          <t>Adriano Barros</t>
+          <t>Vitoria Regina</t>
         </is>
       </c>
       <c r="H1812" t="inlineStr">
         <is>
-          <t>Erika Santana|Isabella Nascimento</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="I1812" t="n">
         <v>3</v>
       </c>
       <c r="J1812" t="n">
-        <v>33</v>
+        <v>81</v>
       </c>
       <c r="K1812" t="n">
-        <v>45</v>
+        <v>225</v>
       </c>
     </row>
     <row r="1813">
@@ -91444,7 +91440,7 @@
       </c>
       <c r="G1813" t="inlineStr">
         <is>
-          <t>Bianca Silva</t>
+          <t>Adriano Barros</t>
         </is>
       </c>
       <c r="H1813" t="inlineStr">
@@ -91453,13 +91449,13 @@
         </is>
       </c>
       <c r="I1813" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J1813" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="K1813" t="n">
-        <v>34</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1814">
@@ -91495,7 +91491,7 @@
       </c>
       <c r="G1814" t="inlineStr">
         <is>
-          <t>Emylle Souza</t>
+          <t>Bianca Silva</t>
         </is>
       </c>
       <c r="H1814" t="inlineStr">
@@ -91504,13 +91500,13 @@
         </is>
       </c>
       <c r="I1814" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J1814" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K1814" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
     </row>
     <row r="1815">
@@ -91546,7 +91542,7 @@
       </c>
       <c r="G1815" t="inlineStr">
         <is>
-          <t>Fatima Rocha</t>
+          <t>Emylle Souza</t>
         </is>
       </c>
       <c r="H1815" t="inlineStr">
@@ -91555,13 +91551,13 @@
         </is>
       </c>
       <c r="I1815" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="J1815" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="K1815" t="n">
-        <v>62</v>
+        <v>34</v>
       </c>
     </row>
     <row r="1816">
@@ -91597,7 +91593,7 @@
       </c>
       <c r="G1816" t="inlineStr">
         <is>
-          <t>Gabriel Correia</t>
+          <t>Fatima Rocha</t>
         </is>
       </c>
       <c r="H1816" t="inlineStr">
@@ -91606,13 +91602,13 @@
         </is>
       </c>
       <c r="I1816" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J1816" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K1816" t="n">
-        <v>24</v>
+        <v>64</v>
       </c>
     </row>
     <row r="1817">
@@ -91648,7 +91644,7 @@
       </c>
       <c r="G1817" t="inlineStr">
         <is>
-          <t>Isabella Nascimento</t>
+          <t>Gabriel Correia</t>
         </is>
       </c>
       <c r="H1817" t="inlineStr">
@@ -91657,13 +91653,13 @@
         </is>
       </c>
       <c r="I1817" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="J1817" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="K1817" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
     </row>
     <row r="1818">
@@ -91699,7 +91695,7 @@
       </c>
       <c r="G1818" t="inlineStr">
         <is>
-          <t>Laisa Rocha</t>
+          <t>Isabella Nascimento</t>
         </is>
       </c>
       <c r="H1818" t="inlineStr">
@@ -91708,13 +91704,13 @@
         </is>
       </c>
       <c r="I1818" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J1818" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K1818" t="n">
-        <v>43</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1819">
@@ -91750,7 +91746,7 @@
       </c>
       <c r="G1819" t="inlineStr">
         <is>
-          <t>Lucas Alves</t>
+          <t>Laisa Rocha</t>
         </is>
       </c>
       <c r="H1819" t="inlineStr">
@@ -91759,13 +91755,13 @@
         </is>
       </c>
       <c r="I1819" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J1819" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="K1819" t="n">
-        <v>19</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1820">
@@ -91801,7 +91797,7 @@
       </c>
       <c r="G1820" t="inlineStr">
         <is>
-          <t>Luciana Silva</t>
+          <t>Lucas Alves</t>
         </is>
       </c>
       <c r="H1820" t="inlineStr">
@@ -91810,13 +91806,13 @@
         </is>
       </c>
       <c r="I1820" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J1820" t="n">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="K1820" t="n">
-        <v>82</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1821">
@@ -91852,18 +91848,22 @@
       </c>
       <c r="G1821" t="inlineStr">
         <is>
-          <t>Luiz Ferreira</t>
-        </is>
-      </c>
-      <c r="H1821" t="inlineStr"/>
+          <t>Luciana Silva</t>
+        </is>
+      </c>
+      <c r="H1821" t="inlineStr">
+        <is>
+          <t>Erika Santana|Isabella Nascimento</t>
+        </is>
+      </c>
       <c r="I1821" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J1821" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="K1821" t="n">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="1822">
@@ -91899,22 +91899,18 @@
       </c>
       <c r="G1822" t="inlineStr">
         <is>
-          <t>Marcus Oliveira</t>
-        </is>
-      </c>
-      <c r="H1822" t="inlineStr">
-        <is>
-          <t>Erika Santana|Isabella Nascimento</t>
-        </is>
-      </c>
+          <t>Luiz Ferreira</t>
+        </is>
+      </c>
+      <c r="H1822" t="inlineStr"/>
       <c r="I1822" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="J1822" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="K1822" t="n">
-        <v>62</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1823">
@@ -91950,7 +91946,7 @@
       </c>
       <c r="G1823" t="inlineStr">
         <is>
-          <t>Mariana Pires</t>
+          <t>Marcus Oliveira</t>
         </is>
       </c>
       <c r="H1823" t="inlineStr">
@@ -91959,13 +91955,13 @@
         </is>
       </c>
       <c r="I1823" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J1823" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K1823" t="n">
-        <v>36</v>
+        <v>65</v>
       </c>
     </row>
     <row r="1824">
@@ -92001,7 +91997,7 @@
       </c>
       <c r="G1824" t="inlineStr">
         <is>
-          <t>Marta Souza</t>
+          <t>Mariana Pires</t>
         </is>
       </c>
       <c r="H1824" t="inlineStr">
@@ -92013,10 +92009,10 @@
         <v>0</v>
       </c>
       <c r="J1824" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1824" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="1825">
@@ -92052,7 +92048,7 @@
       </c>
       <c r="G1825" t="inlineStr">
         <is>
-          <t>Mateus Miranda</t>
+          <t>Marta Souza</t>
         </is>
       </c>
       <c r="H1825" t="inlineStr">
@@ -92064,10 +92060,10 @@
         <v>0</v>
       </c>
       <c r="J1825" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1825" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1826">
@@ -92103,7 +92099,7 @@
       </c>
       <c r="G1826" t="inlineStr">
         <is>
-          <t>Mirian Lima</t>
+          <t>Mateus Miranda</t>
         </is>
       </c>
       <c r="H1826" t="inlineStr">
@@ -92112,13 +92108,13 @@
         </is>
       </c>
       <c r="I1826" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J1826" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K1826" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1827">
@@ -92154,7 +92150,7 @@
       </c>
       <c r="G1827" t="inlineStr">
         <is>
-          <t>Nathalia Lourenco</t>
+          <t>Mirian Lima</t>
         </is>
       </c>
       <c r="H1827" t="inlineStr">
@@ -92163,13 +92159,13 @@
         </is>
       </c>
       <c r="I1827" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J1827" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K1827" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
     </row>
     <row r="1828">
@@ -92205,7 +92201,7 @@
       </c>
       <c r="G1828" t="inlineStr">
         <is>
-          <t>Nicolas Dias</t>
+          <t>Nathalia Lourenco</t>
         </is>
       </c>
       <c r="H1828" t="inlineStr">
@@ -92214,10 +92210,10 @@
         </is>
       </c>
       <c r="I1828" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1828" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="K1828" t="n">
         <v>60</v>
@@ -92256,7 +92252,7 @@
       </c>
       <c r="G1829" t="inlineStr">
         <is>
-          <t>Rodrigo Nunes</t>
+          <t>Nicolas Dias</t>
         </is>
       </c>
       <c r="H1829" t="inlineStr">
@@ -92265,13 +92261,13 @@
         </is>
       </c>
       <c r="I1829" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1829" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="K1829" t="n">
-        <v>13</v>
+        <v>61</v>
       </c>
     </row>
     <row r="1830">
@@ -92307,7 +92303,7 @@
       </c>
       <c r="G1830" t="inlineStr">
         <is>
-          <t>Thais Souza</t>
+          <t>Rodrigo Nunes</t>
         </is>
       </c>
       <c r="H1830" t="inlineStr">
@@ -92319,7 +92315,7 @@
         <v>0</v>
       </c>
       <c r="J1830" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1830" t="n">
         <v>13</v>
@@ -92358,7 +92354,7 @@
       </c>
       <c r="G1831" t="inlineStr">
         <is>
-          <t>Viviane Guedes</t>
+          <t>Thais Souza</t>
         </is>
       </c>
       <c r="H1831" t="inlineStr">
@@ -92367,13 +92363,13 @@
         </is>
       </c>
       <c r="I1831" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1831" t="n">
         <v>1</v>
       </c>
       <c r="K1831" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1832">
@@ -92404,27 +92400,27 @@
       </c>
       <c r="F1832" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="G1832" t="inlineStr">
         <is>
-          <t>Aline Petrini</t>
+          <t>Viviane Guedes</t>
         </is>
       </c>
       <c r="H1832" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Erika Santana|Isabella Nascimento</t>
         </is>
       </c>
       <c r="I1832" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1832" t="n">
         <v>4</v>
       </c>
-      <c r="J1832" t="n">
-        <v>12</v>
-      </c>
       <c r="K1832" t="n">
-        <v>62</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1833">
@@ -92460,22 +92456,22 @@
       </c>
       <c r="G1833" t="inlineStr">
         <is>
-          <t>Ana Barbosa</t>
+          <t>Aline Petrini</t>
         </is>
       </c>
       <c r="H1833" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="I1833" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J1833" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="K1833" t="n">
-        <v>72</v>
+        <v>62</v>
       </c>
     </row>
     <row r="1834">
@@ -92511,7 +92507,7 @@
       </c>
       <c r="G1834" t="inlineStr">
         <is>
-          <t>Daniele Leite</t>
+          <t>Ana Barbosa</t>
         </is>
       </c>
       <c r="H1834" t="inlineStr">
@@ -92520,13 +92516,13 @@
         </is>
       </c>
       <c r="I1834" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J1834" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="K1834" t="n">
-        <v>14</v>
+        <v>72</v>
       </c>
     </row>
     <row r="1835">
@@ -92562,22 +92558,22 @@
       </c>
       <c r="G1835" t="inlineStr">
         <is>
-          <t>Danielle Silva</t>
+          <t>Daniele Leite</t>
         </is>
       </c>
       <c r="H1835" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I1835" t="n">
-        <v>64</v>
+        <v>3</v>
       </c>
       <c r="J1835" t="n">
-        <v>67</v>
+        <v>11</v>
       </c>
       <c r="K1835" t="n">
-        <v>145</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1836">
@@ -92613,7 +92609,7 @@
       </c>
       <c r="G1836" t="inlineStr">
         <is>
-          <t>Danilo Oliveira</t>
+          <t>Danielle Silva</t>
         </is>
       </c>
       <c r="H1836" t="inlineStr">
@@ -92622,13 +92618,13 @@
         </is>
       </c>
       <c r="I1836" t="n">
-        <v>11</v>
+        <v>64</v>
       </c>
       <c r="J1836" t="n">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="K1836" t="n">
-        <v>49</v>
+        <v>145</v>
       </c>
     </row>
     <row r="1837">
@@ -92664,22 +92660,22 @@
       </c>
       <c r="G1837" t="inlineStr">
         <is>
-          <t>Debora Silva</t>
+          <t>Danilo Oliveira</t>
         </is>
       </c>
       <c r="H1837" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Karina Santos</t>
         </is>
       </c>
       <c r="I1837" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J1837" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="K1837" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
     </row>
     <row r="1838">
@@ -92715,22 +92711,22 @@
       </c>
       <c r="G1838" t="inlineStr">
         <is>
-          <t>Diogo Calazans</t>
+          <t>Debora Silva</t>
         </is>
       </c>
       <c r="H1838" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="I1838" t="n">
-        <v>86</v>
+        <v>14</v>
       </c>
       <c r="J1838" t="n">
-        <v>86</v>
+        <v>32</v>
       </c>
       <c r="K1838" t="n">
-        <v>179</v>
+        <v>63</v>
       </c>
     </row>
     <row r="1839">
@@ -92766,22 +92762,22 @@
       </c>
       <c r="G1839" t="inlineStr">
         <is>
-          <t>Eduardo Cruz</t>
+          <t>Diogo Calazans</t>
         </is>
       </c>
       <c r="H1839" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Karina Santos</t>
         </is>
       </c>
       <c r="I1839" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="J1839" t="n">
-        <v>58</v>
+        <v>94</v>
       </c>
       <c r="K1839" t="n">
-        <v>141</v>
+        <v>187</v>
       </c>
     </row>
     <row r="1840">
@@ -92817,22 +92813,22 @@
       </c>
       <c r="G1840" t="inlineStr">
         <is>
-          <t>Eveny Silva</t>
+          <t>Eduardo Cruz</t>
         </is>
       </c>
       <c r="H1840" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="I1840" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="J1840" t="n">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="K1840" t="n">
-        <v>148</v>
+        <v>142</v>
       </c>
     </row>
     <row r="1841">
@@ -92868,22 +92864,22 @@
       </c>
       <c r="G1841" t="inlineStr">
         <is>
-          <t>Everton Moura</t>
+          <t>Eveny Silva</t>
         </is>
       </c>
       <c r="H1841" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Karina Santos</t>
         </is>
       </c>
       <c r="I1841" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="J1841" t="n">
-        <v>10</v>
+        <v>103</v>
       </c>
       <c r="K1841" t="n">
-        <v>19</v>
+        <v>151</v>
       </c>
     </row>
     <row r="1842">
@@ -92919,22 +92915,22 @@
       </c>
       <c r="G1842" t="inlineStr">
         <is>
-          <t>Guilherme Dantas</t>
+          <t>Everton Moura</t>
         </is>
       </c>
       <c r="H1842" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="I1842" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1842" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K1842" t="n">
-        <v>60</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1843">
@@ -92970,22 +92966,22 @@
       </c>
       <c r="G1843" t="inlineStr">
         <is>
-          <t>Isabela Lemos</t>
+          <t>Guilherme Dantas</t>
         </is>
       </c>
       <c r="H1843" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I1843" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J1843" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K1843" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
     </row>
     <row r="1844">
@@ -93021,22 +93017,22 @@
       </c>
       <c r="G1844" t="inlineStr">
         <is>
-          <t>Jackson Silva</t>
+          <t>Isabela Lemos</t>
         </is>
       </c>
       <c r="H1844" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="I1844" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J1844" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K1844" t="n">
-        <v>69</v>
+        <v>45</v>
       </c>
     </row>
     <row r="1845">
@@ -93072,22 +93068,22 @@
       </c>
       <c r="G1845" t="inlineStr">
         <is>
-          <t>Jaqueline Sousa</t>
+          <t>Jackson Silva</t>
         </is>
       </c>
       <c r="H1845" t="inlineStr">
         <is>
-          <t>Lucas Fischer</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I1845" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J1845" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="K1845" t="n">
-        <v>54</v>
+        <v>69</v>
       </c>
     </row>
     <row r="1846">
@@ -93123,7 +93119,7 @@
       </c>
       <c r="G1846" t="inlineStr">
         <is>
-          <t>Leticia Medeiros</t>
+          <t>Jaqueline Sousa</t>
         </is>
       </c>
       <c r="H1846" t="inlineStr">
@@ -93132,13 +93128,13 @@
         </is>
       </c>
       <c r="I1846" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J1846" t="n">
-        <v>77</v>
+        <v>23</v>
       </c>
       <c r="K1846" t="n">
-        <v>154</v>
+        <v>54</v>
       </c>
     </row>
     <row r="1847">
@@ -93174,22 +93170,22 @@
       </c>
       <c r="G1847" t="inlineStr">
         <is>
-          <t>Monica Medeiros</t>
+          <t>Leticia Medeiros</t>
         </is>
       </c>
       <c r="H1847" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Lucas Fischer</t>
         </is>
       </c>
       <c r="I1847" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J1847" t="n">
-        <v>5</v>
+        <v>79</v>
       </c>
       <c r="K1847" t="n">
-        <v>59</v>
+        <v>156</v>
       </c>
     </row>
     <row r="1848">
@@ -93225,22 +93221,22 @@
       </c>
       <c r="G1848" t="inlineStr">
         <is>
-          <t>Naiara Dutra</t>
+          <t>Monica Medeiros</t>
         </is>
       </c>
       <c r="H1848" t="inlineStr">
         <is>
-          <t>Lucas Fischer</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I1848" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1848" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="K1848" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
     </row>
     <row r="1849">
@@ -93276,22 +93272,22 @@
       </c>
       <c r="G1849" t="inlineStr">
         <is>
-          <t>Patricia Borges</t>
+          <t>Naiara Dutra</t>
         </is>
       </c>
       <c r="H1849" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Lucas Fischer</t>
         </is>
       </c>
       <c r="I1849" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J1849" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="K1849" t="n">
-        <v>75</v>
+        <v>52</v>
       </c>
     </row>
     <row r="1850">
@@ -93327,22 +93323,22 @@
       </c>
       <c r="G1850" t="inlineStr">
         <is>
-          <t>Paulo Silva</t>
+          <t>Patricia Borges</t>
         </is>
       </c>
       <c r="H1850" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I1850" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J1850" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="K1850" t="n">
-        <v>87</v>
+        <v>75</v>
       </c>
     </row>
     <row r="1851">
@@ -93378,22 +93374,22 @@
       </c>
       <c r="G1851" t="inlineStr">
         <is>
-          <t>Rachel Lima</t>
+          <t>Paulo Silva</t>
         </is>
       </c>
       <c r="H1851" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="I1851" t="n">
         <v>4</v>
       </c>
       <c r="J1851" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="K1851" t="n">
-        <v>71</v>
+        <v>87</v>
       </c>
     </row>
     <row r="1852">
@@ -93429,7 +93425,7 @@
       </c>
       <c r="G1852" t="inlineStr">
         <is>
-          <t>Raiane Barbosa</t>
+          <t>Rachel Lima</t>
         </is>
       </c>
       <c r="H1852" t="inlineStr">
@@ -93438,13 +93434,13 @@
         </is>
       </c>
       <c r="I1852" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J1852" t="n">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="K1852" t="n">
-        <v>120</v>
+        <v>73</v>
       </c>
     </row>
     <row r="1853">
@@ -93480,22 +93476,22 @@
       </c>
       <c r="G1853" t="inlineStr">
         <is>
-          <t>Rejane Coelho</t>
+          <t>Raiane Barbosa</t>
         </is>
       </c>
       <c r="H1853" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I1853" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J1853" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="K1853" t="n">
-        <v>12</v>
+        <v>120</v>
       </c>
     </row>
     <row r="1854">
@@ -93531,22 +93527,22 @@
       </c>
       <c r="G1854" t="inlineStr">
         <is>
-          <t>Renata Alves - CTV</t>
+          <t>Rejane Coelho</t>
         </is>
       </c>
       <c r="H1854" t="inlineStr">
         <is>
-          <t>Lucas Fischer</t>
+          <t>Karina Santos</t>
         </is>
       </c>
       <c r="I1854" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1854" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="K1854" t="n">
-        <v>44</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1855">
@@ -93582,18 +93578,22 @@
       </c>
       <c r="G1855" t="inlineStr">
         <is>
-          <t>Renata Cavalheiro</t>
-        </is>
-      </c>
-      <c r="H1855" t="inlineStr"/>
+          <t>Renata Alves - CTV</t>
+        </is>
+      </c>
+      <c r="H1855" t="inlineStr">
+        <is>
+          <t>Lucas Fischer</t>
+        </is>
+      </c>
       <c r="I1855" t="n">
         <v>0</v>
       </c>
       <c r="J1855" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K1855" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
     </row>
     <row r="1856">
@@ -93629,22 +93629,18 @@
       </c>
       <c r="G1856" t="inlineStr">
         <is>
-          <t>Ryan Godinho</t>
-        </is>
-      </c>
-      <c r="H1856" t="inlineStr">
-        <is>
-          <t>Karina Santos</t>
-        </is>
-      </c>
+          <t>Renata Cavalheiro</t>
+        </is>
+      </c>
+      <c r="H1856" t="inlineStr"/>
       <c r="I1856" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J1856" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="K1856" t="n">
-        <v>86</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1857">
@@ -93680,22 +93676,22 @@
       </c>
       <c r="G1857" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Ryan Godinho</t>
         </is>
       </c>
       <c r="H1857" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Karina Santos</t>
         </is>
       </c>
       <c r="I1857" t="n">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="J1857" t="n">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="K1857" t="n">
-        <v>6</v>
+        <v>90</v>
       </c>
     </row>
     <row r="1858">
@@ -93731,22 +93727,22 @@
       </c>
       <c r="G1858" t="inlineStr">
         <is>
-          <t>Vitor Domingues</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="H1858" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="I1858" t="n">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="J1858" t="n">
-        <v>74</v>
+        <v>4</v>
       </c>
       <c r="K1858" t="n">
-        <v>145</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1859">
@@ -93777,27 +93773,27 @@
       </c>
       <c r="F1859" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO PESSOAL (Outsourcing)</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="G1859" t="inlineStr">
         <is>
-          <t>Bruna Santana</t>
+          <t>Vitor Domingues</t>
         </is>
       </c>
       <c r="H1859" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="I1859" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="J1859" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="K1859" t="n">
-        <v>4</v>
+        <v>149</v>
       </c>
     </row>
     <row r="1860">
@@ -93833,7 +93829,7 @@
       </c>
       <c r="G1860" t="inlineStr">
         <is>
-          <t>Camila Oliveira</t>
+          <t>Bruna Santana</t>
         </is>
       </c>
       <c r="H1860" t="inlineStr">
@@ -93845,10 +93841,10 @@
         <v>0</v>
       </c>
       <c r="J1860" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1860" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1861">
@@ -93884,22 +93880,22 @@
       </c>
       <c r="G1861" t="inlineStr">
         <is>
-          <t>Elaine Assis</t>
+          <t>Camila Oliveira</t>
         </is>
       </c>
       <c r="H1861" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I1861" t="n">
         <v>0</v>
       </c>
       <c r="J1861" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1861" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1862">
@@ -93935,22 +93931,22 @@
       </c>
       <c r="G1862" t="inlineStr">
         <is>
-          <t>Fabiane Branco</t>
+          <t>Elaine Assis</t>
         </is>
       </c>
       <c r="H1862" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I1862" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1862" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1862" t="n">
         <v>7</v>
-      </c>
-      <c r="J1862" t="n">
-        <v>6</v>
-      </c>
-      <c r="K1862" t="n">
-        <v>16</v>
       </c>
     </row>
     <row r="1863">
@@ -93986,22 +93982,22 @@
       </c>
       <c r="G1863" t="inlineStr">
         <is>
-          <t>Jonas Nunes</t>
+          <t>Fabiane Branco</t>
         </is>
       </c>
       <c r="H1863" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I1863" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J1863" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K1863" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1864">
@@ -94032,12 +94028,12 @@
       </c>
       <c r="F1864" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>DEPARTAMENTO PESSOAL (Outsourcing)</t>
         </is>
       </c>
       <c r="G1864" t="inlineStr">
         <is>
-          <t>Aline Pereira</t>
+          <t>Jonas Nunes</t>
         </is>
       </c>
       <c r="H1864" t="inlineStr">
@@ -94052,7 +94048,7 @@
         <v>0</v>
       </c>
       <c r="K1864" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1865">
@@ -94088,7 +94084,7 @@
       </c>
       <c r="G1865" t="inlineStr">
         <is>
-          <t>Bruna Santana</t>
+          <t>Aline Pereira</t>
         </is>
       </c>
       <c r="H1865" t="inlineStr">
@@ -94097,13 +94093,13 @@
         </is>
       </c>
       <c r="I1865" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J1865" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K1865" t="n">
-        <v>141</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1866">
@@ -94139,7 +94135,7 @@
       </c>
       <c r="G1866" t="inlineStr">
         <is>
-          <t>Camila Oliveira</t>
+          <t>Bruna Santana</t>
         </is>
       </c>
       <c r="H1866" t="inlineStr">
@@ -94148,13 +94144,13 @@
         </is>
       </c>
       <c r="I1866" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J1866" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="K1866" t="n">
-        <v>32</v>
+        <v>151</v>
       </c>
     </row>
     <row r="1867">
@@ -94190,22 +94186,22 @@
       </c>
       <c r="G1867" t="inlineStr">
         <is>
-          <t>Daniel Moraes</t>
+          <t>Camila Oliveira</t>
         </is>
       </c>
       <c r="H1867" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I1867" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J1867" t="n">
-        <v>76</v>
+        <v>8</v>
       </c>
       <c r="K1867" t="n">
-        <v>127</v>
+        <v>32</v>
       </c>
     </row>
     <row r="1868">
@@ -94241,7 +94237,7 @@
       </c>
       <c r="G1868" t="inlineStr">
         <is>
-          <t>Danilo Xavier</t>
+          <t>Daniel Moraes</t>
         </is>
       </c>
       <c r="H1868" t="inlineStr">
@@ -94250,13 +94246,13 @@
         </is>
       </c>
       <c r="I1868" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="J1868" t="n">
-        <v>20</v>
+        <v>76</v>
       </c>
       <c r="K1868" t="n">
-        <v>196</v>
+        <v>127</v>
       </c>
     </row>
     <row r="1869">
@@ -94292,7 +94288,7 @@
       </c>
       <c r="G1869" t="inlineStr">
         <is>
-          <t>Elaine Assis</t>
+          <t>Danilo Xavier</t>
         </is>
       </c>
       <c r="H1869" t="inlineStr">
@@ -94301,13 +94297,13 @@
         </is>
       </c>
       <c r="I1869" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J1869" t="n">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="K1869" t="n">
-        <v>108</v>
+        <v>196</v>
       </c>
     </row>
     <row r="1870">
@@ -94343,22 +94339,22 @@
       </c>
       <c r="G1870" t="inlineStr">
         <is>
-          <t>Eliene Lima</t>
+          <t>Elaine Assis</t>
         </is>
       </c>
       <c r="H1870" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I1870" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="J1870" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="K1870" t="n">
-        <v>45</v>
+        <v>108</v>
       </c>
     </row>
     <row r="1871">
@@ -94394,22 +94390,22 @@
       </c>
       <c r="G1871" t="inlineStr">
         <is>
-          <t>Erica Oliveira</t>
+          <t>Eliene Lima</t>
         </is>
       </c>
       <c r="H1871" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I1871" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1871" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="K1871" t="n">
-        <v>87</v>
+        <v>45</v>
       </c>
     </row>
     <row r="1872">
@@ -94445,22 +94441,22 @@
       </c>
       <c r="G1872" t="inlineStr">
         <is>
-          <t>Evellin Bispo</t>
+          <t>Erica Oliveira</t>
         </is>
       </c>
       <c r="H1872" t="inlineStr">
         <is>
-          <t>Leandro Matos</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I1872" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1872" t="n">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="K1872" t="n">
-        <v>52</v>
+        <v>88</v>
       </c>
     </row>
     <row r="1873">
@@ -94496,22 +94492,22 @@
       </c>
       <c r="G1873" t="inlineStr">
         <is>
-          <t>Fabiane Branco</t>
+          <t>Evellin Bispo</t>
         </is>
       </c>
       <c r="H1873" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>Leandro Matos</t>
         </is>
       </c>
       <c r="I1873" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="J1873" t="n">
-        <v>69</v>
+        <v>10</v>
       </c>
       <c r="K1873" t="n">
-        <v>200</v>
+        <v>52</v>
       </c>
     </row>
     <row r="1874">
@@ -94547,22 +94543,22 @@
       </c>
       <c r="G1874" t="inlineStr">
         <is>
-          <t>Franciele Alves</t>
+          <t>Fabiane Branco</t>
         </is>
       </c>
       <c r="H1874" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I1874" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="J1874" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="K1874" t="n">
-        <v>129</v>
+        <v>201</v>
       </c>
     </row>
     <row r="1875">
@@ -94598,22 +94594,22 @@
       </c>
       <c r="G1875" t="inlineStr">
         <is>
-          <t>Gabriela Peres</t>
+          <t>Franciele Alves</t>
         </is>
       </c>
       <c r="H1875" t="inlineStr">
         <is>
-          <t>Leandro Matos</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I1875" t="n">
         <v>0</v>
       </c>
       <c r="J1875" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1875" t="n">
-        <v>14</v>
+        <v>129</v>
       </c>
     </row>
     <row r="1876">
@@ -94649,22 +94645,22 @@
       </c>
       <c r="G1876" t="inlineStr">
         <is>
-          <t>Grasiele Santos</t>
+          <t>Gabriela Peres</t>
         </is>
       </c>
       <c r="H1876" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Leandro Matos</t>
         </is>
       </c>
       <c r="I1876" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="J1876" t="n">
-        <v>61</v>
+        <v>4</v>
       </c>
       <c r="K1876" t="n">
-        <v>195</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1877">
@@ -94700,22 +94696,22 @@
       </c>
       <c r="G1877" t="inlineStr">
         <is>
-          <t>Jakeline Silva</t>
+          <t>Grasiele Santos</t>
         </is>
       </c>
       <c r="H1877" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I1877" t="n">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="J1877" t="n">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="K1877" t="n">
-        <v>231</v>
+        <v>195</v>
       </c>
     </row>
     <row r="1878">
@@ -94751,22 +94747,22 @@
       </c>
       <c r="G1878" t="inlineStr">
         <is>
-          <t>Janaina Rocha</t>
+          <t>Jakeline Silva</t>
         </is>
       </c>
       <c r="H1878" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I1878" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="J1878" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="K1878" t="n">
-        <v>151</v>
+        <v>231</v>
       </c>
     </row>
     <row r="1879">
@@ -94802,22 +94798,22 @@
       </c>
       <c r="G1879" t="inlineStr">
         <is>
-          <t>Jayne Tavares</t>
+          <t>Janaina Rocha</t>
         </is>
       </c>
       <c r="H1879" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I1879" t="n">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="J1879" t="n">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="K1879" t="n">
-        <v>147</v>
+        <v>157</v>
       </c>
     </row>
     <row r="1880">
@@ -94853,22 +94849,22 @@
       </c>
       <c r="G1880" t="inlineStr">
         <is>
-          <t>Jhenifer Tenorio</t>
+          <t>Jayne Tavares</t>
         </is>
       </c>
       <c r="H1880" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I1880" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J1880" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="K1880" t="n">
-        <v>134</v>
+        <v>147</v>
       </c>
     </row>
     <row r="1881">
@@ -94904,7 +94900,7 @@
       </c>
       <c r="G1881" t="inlineStr">
         <is>
-          <t>Jonas Nunes</t>
+          <t>Jhenifer Tenorio</t>
         </is>
       </c>
       <c r="H1881" t="inlineStr">
@@ -94913,13 +94909,13 @@
         </is>
       </c>
       <c r="I1881" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="J1881" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="K1881" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="1882">
@@ -94955,22 +94951,22 @@
       </c>
       <c r="G1882" t="inlineStr">
         <is>
-          <t>Kaique Souza</t>
+          <t>Jonas Nunes</t>
         </is>
       </c>
       <c r="H1882" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I1882" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="J1882" t="n">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="K1882" t="n">
-        <v>159</v>
+        <v>131</v>
       </c>
     </row>
     <row r="1883">
@@ -95006,7 +95002,7 @@
       </c>
       <c r="G1883" t="inlineStr">
         <is>
-          <t>Karine Sousa</t>
+          <t>Kaique Souza</t>
         </is>
       </c>
       <c r="H1883" t="inlineStr">
@@ -95015,13 +95011,13 @@
         </is>
       </c>
       <c r="I1883" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J1883" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="K1883" t="n">
-        <v>117</v>
+        <v>159</v>
       </c>
     </row>
     <row r="1884">
@@ -95057,22 +95053,22 @@
       </c>
       <c r="G1884" t="inlineStr">
         <is>
-          <t>Laysla Alves</t>
+          <t>Karine Sousa</t>
         </is>
       </c>
       <c r="H1884" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I1884" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1884" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="K1884" t="n">
-        <v>87</v>
+        <v>117</v>
       </c>
     </row>
     <row r="1885">
@@ -95108,22 +95104,22 @@
       </c>
       <c r="G1885" t="inlineStr">
         <is>
-          <t>Luana Marques</t>
+          <t>Laysla Alves</t>
         </is>
       </c>
       <c r="H1885" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I1885" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J1885" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K1885" t="n">
-        <v>22</v>
+        <v>87</v>
       </c>
     </row>
     <row r="1886">
@@ -95159,7 +95155,7 @@
       </c>
       <c r="G1886" t="inlineStr">
         <is>
-          <t>Maria Pires</t>
+          <t>Luana Marques</t>
         </is>
       </c>
       <c r="H1886" t="inlineStr">
@@ -95168,13 +95164,13 @@
         </is>
       </c>
       <c r="I1886" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="J1886" t="n">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="K1886" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1887">
@@ -95210,22 +95206,22 @@
       </c>
       <c r="G1887" t="inlineStr">
         <is>
-          <t>Mauricio Lermen</t>
+          <t>Maria Pires</t>
         </is>
       </c>
       <c r="H1887" t="inlineStr">
         <is>
-          <t>Mauricio Lermen</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I1887" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J1887" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="K1887" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1888">
@@ -95261,22 +95257,22 @@
       </c>
       <c r="G1888" t="inlineStr">
         <is>
-          <t>Micaele Cordeiro</t>
+          <t>Mauricio Lermen</t>
         </is>
       </c>
       <c r="H1888" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>Mauricio Lermen</t>
         </is>
       </c>
       <c r="I1888" t="n">
         <v>0</v>
       </c>
       <c r="J1888" t="n">
-        <v>46</v>
+        <v>4</v>
       </c>
       <c r="K1888" t="n">
-        <v>177</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1889">
@@ -95312,7 +95308,7 @@
       </c>
       <c r="G1889" t="inlineStr">
         <is>
-          <t>Michele Silva</t>
+          <t>Mi